--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD23DA69-DDE6-954E-9DA6-D2BA393469A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA8A404-F944-824E-86A1-5A8221B1DFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="19120" windowHeight="16240" activeTab="3" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="-27340" yWindow="500" windowWidth="19120" windowHeight="16240" activeTab="4" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5006" uniqueCount="1270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5006" uniqueCount="1269">
   <si>
     <t>page_id</t>
   </si>
@@ -1787,9 +1787,6 @@
     <t>Beischrift</t>
   </si>
   <si>
-    <t>Beziehung</t>
-  </si>
-  <si>
     <t>gl_beischrift</t>
   </si>
   <si>
@@ -1808,9 +1805,6 @@
     <t>Rückenschutzformel</t>
   </si>
   <si>
-    <t>Inschrift:</t>
-  </si>
-  <si>
     <t>Blickt in die selbe Richtung wie das Dargestellte</t>
   </si>
   <si>
@@ -1823,21 +1817,12 @@
     <t>Sonstiges</t>
   </si>
   <si>
-    <t>Szenentitel:</t>
-  </si>
-  <si>
     <t>im Infinitiv</t>
   </si>
   <si>
-    <t>Wörtliche Rede:</t>
-  </si>
-  <si>
     <t>mit und ohne Einleitung</t>
   </si>
   <si>
-    <t>Rückenschutzformel:</t>
-  </si>
-  <si>
     <t>am häufigsten bei König, auch bei Gottheit</t>
   </si>
   <si>
@@ -3852,6 +3837,18 @@
   </si>
   <si>
     <t>Worte zu sprechen durch [Gottheit] / [König] / [Person] NN: Ich habe dir gegeben [Gaben], die bei mir sind.</t>
+  </si>
+  <si>
+    <t>Inschrift</t>
+  </si>
+  <si>
+    <t>[Beziehung]</t>
+  </si>
+  <si>
+    <t>[Szenentitel]</t>
+  </si>
+  <si>
+    <t>[Rückenschutzformel]</t>
   </si>
 </sst>
 </file>
@@ -4503,7 +4500,7 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="D9" t="s">
         <v>74</v>
@@ -4520,7 +4517,7 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>1219</v>
+        <v>1214</v>
       </c>
       <c r="D10" t="s">
         <v>75</v>
@@ -4616,16 +4613,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D16" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F16">
         <v>150</v>
@@ -5024,7 +5021,7 @@
         <v>396</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="F18" s="13">
         <v>3</v>
@@ -5041,7 +5038,7 @@
         <v>571</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="F19" s="13">
         <v>4</v>
@@ -5058,7 +5055,7 @@
         <v>575</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="F20" s="13">
         <v>5</v>
@@ -5089,7 +5086,7 @@
         <v>27</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="F23" s="17">
         <v>2</v>
@@ -5168,7 +5165,7 @@
         <v>24</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F30" s="22">
         <v>1</v>
@@ -5182,10 +5179,10 @@
         <v>26</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>588</v>
+        <v>1265</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F31" s="22">
         <v>2</v>
@@ -5199,7 +5196,7 @@
         <v>24</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F32" s="22">
         <v>3</v>
@@ -5213,10 +5210,10 @@
         <v>26</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>593</v>
+        <v>606</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F33" s="22">
         <v>4</v>
@@ -5230,10 +5227,10 @@
         <v>26</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="F34" s="22">
         <v>5</v>
@@ -5247,10 +5244,10 @@
         <v>26</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="F35" s="22">
         <v>6</v>
@@ -5304,10 +5301,10 @@
         <v>177</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>337</v>
@@ -5373,7 +5370,7 @@
         <v>54</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="K4" s="4">
         <v>3</v>
@@ -5402,7 +5399,7 @@
         <v>178</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="K5" s="4">
         <v>4</v>
@@ -5422,7 +5419,7 @@
         <v>192</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>54</v>
@@ -5451,7 +5448,7 @@
         <v>54</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="K8" s="4">
         <v>2</v>
@@ -5468,7 +5465,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>202</v>
@@ -5477,7 +5474,7 @@
         <v>54</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="K9" s="4">
         <v>3</v>
@@ -5494,7 +5491,7 @@
         <v>55</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1241</v>
+        <v>1236</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>203</v>
@@ -5503,7 +5500,7 @@
         <v>54</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="K10" s="4">
         <v>4</v>
@@ -5520,7 +5517,7 @@
         <v>55</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>204</v>
@@ -5529,7 +5526,7 @@
         <v>54</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="K11" s="4">
         <v>5</v>
@@ -5546,7 +5543,7 @@
         <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1263</v>
+        <v>1258</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>54</v>
@@ -5566,7 +5563,7 @@
         <v>55</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>54</v>
@@ -5595,7 +5592,7 @@
         <v>54</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="K15" s="4">
         <v>3</v>
@@ -5621,7 +5618,7 @@
         <v>54</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="K16" s="4">
         <v>4</v>
@@ -5638,7 +5635,7 @@
         <v>55</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>54</v>
@@ -5664,7 +5661,7 @@
         <v>54</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="4">
@@ -5688,7 +5685,7 @@
         <v>54</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="4">
@@ -5706,7 +5703,7 @@
         <v>55</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>446</v>
@@ -5715,7 +5712,7 @@
         <v>54</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="K20" s="4">
         <v>8</v>
@@ -5732,7 +5729,7 @@
         <v>55</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>454</v>
@@ -5741,7 +5738,7 @@
         <v>54</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="K21" s="4">
         <v>9</v>
@@ -5780,7 +5777,7 @@
         <v>55</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>502</v>
@@ -5789,7 +5786,7 @@
         <v>54</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="K25" s="4">
         <v>1</v>
@@ -5806,7 +5803,7 @@
         <v>55</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>504</v>
@@ -5815,7 +5812,7 @@
         <v>54</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="K26" s="4">
         <v>2</v>
@@ -5832,7 +5829,7 @@
         <v>55</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>505</v>
@@ -5841,7 +5838,7 @@
         <v>54</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="K27" s="4">
         <v>3</v>
@@ -5867,7 +5864,7 @@
         <v>54</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="K28" s="4">
         <v>4</v>
@@ -5887,7 +5884,7 @@
         <v>192</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1264</v>
+        <v>1259</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>54</v>
@@ -5907,7 +5904,7 @@
         <v>55</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>530</v>
@@ -5916,7 +5913,7 @@
         <v>54</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="K31" s="4">
         <v>2</v>
@@ -5965,7 +5962,7 @@
         <v>54</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="K33" s="4">
         <v>4</v>
@@ -5973,7 +5970,7 @@
     </row>
     <row r="35" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>24</v>
@@ -5988,7 +5985,7 @@
         <v>54</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="K35" s="4">
         <v>1</v>
@@ -5996,7 +5993,7 @@
     </row>
     <row r="36" spans="1:11" ht="51" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>26</v>
@@ -6008,7 +6005,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>54</v>
@@ -6019,7 +6016,7 @@
     </row>
     <row r="37" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>28</v>
@@ -6031,13 +6028,13 @@
         <v>29</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>54</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="K37" s="4">
         <v>3</v>
@@ -6045,7 +6042,7 @@
     </row>
     <row r="38" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>32</v>
@@ -6057,7 +6054,7 @@
         <v>33</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="K38" s="4">
         <v>4</v>
@@ -7518,7 +7515,7 @@
     </row>
     <row r="64" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B64" s="12">
         <v>16</v>
@@ -7535,7 +7532,7 @@
     </row>
     <row r="65" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B65" s="12">
         <v>17</v>
@@ -7550,7 +7547,7 @@
         <v>381</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
       <c r="L65" s="12" t="str">
         <f t="shared" ref="L65:L78" si="11">_xlfn.TEXTJOIN("", TRUE, E65:K65)</f>
@@ -7562,7 +7559,7 @@
     </row>
     <row r="66" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B66" s="12">
         <v>18</v>
@@ -7577,7 +7574,7 @@
         <v>381</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="L66" s="12" t="str">
         <f t="shared" si="11"/>
@@ -7589,7 +7586,7 @@
     </row>
     <row r="67" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B67" s="12">
         <v>19</v>
@@ -7604,7 +7601,7 @@
         <v>381</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="L67" s="12" t="str">
         <f t="shared" ref="L67" si="12">_xlfn.TEXTJOIN("", TRUE, E67:K67)</f>
@@ -7616,7 +7613,7 @@
     </row>
     <row r="68" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B68" s="12">
         <v>20</v>
@@ -7625,7 +7622,7 @@
         <v>45</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="N68" s="12" t="s">
         <v>92</v>
@@ -7633,7 +7630,7 @@
     </row>
     <row r="69" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B69" s="12">
         <v>21</v>
@@ -7650,7 +7647,7 @@
     </row>
     <row r="70" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B70" s="12">
         <v>22</v>
@@ -7665,7 +7662,7 @@
         <v>382</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="L70" s="12" t="str">
         <f t="shared" si="11"/>
@@ -7677,7 +7674,7 @@
     </row>
     <row r="71" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B71" s="12">
         <v>23</v>
@@ -7692,7 +7689,7 @@
         <v>382</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="L71" s="12" t="str">
         <f t="shared" si="11"/>
@@ -7704,7 +7701,7 @@
     </row>
     <row r="72" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B72" s="12">
         <v>24</v>
@@ -7721,7 +7718,7 @@
     </row>
     <row r="73" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B73" s="12">
         <v>25</v>
@@ -7736,7 +7733,7 @@
         <v>382</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="L73" s="12" t="str">
         <f t="shared" ref="L73" si="13">_xlfn.TEXTJOIN("", TRUE, E73:K73)</f>
@@ -7748,7 +7745,7 @@
     </row>
     <row r="74" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B74" s="12">
         <v>26</v>
@@ -7765,7 +7762,7 @@
     </row>
     <row r="75" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B75" s="12">
         <v>27</v>
@@ -7780,7 +7777,7 @@
         <v>382</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="L75" s="12" t="str">
         <f t="shared" ref="L75" si="14">_xlfn.TEXTJOIN("", TRUE, E75:K75)</f>
@@ -7792,7 +7789,7 @@
     </row>
     <row r="76" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B76" s="12">
         <v>28</v>
@@ -7809,7 +7806,7 @@
     </row>
     <row r="77" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B77" s="12">
         <v>29</v>
@@ -7826,7 +7823,7 @@
     </row>
     <row r="78" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B78" s="12">
         <v>30</v>
@@ -7841,7 +7838,7 @@
         <v>385</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="L78" s="12" t="str">
         <f t="shared" si="11"/>
@@ -7853,7 +7850,7 @@
     </row>
     <row r="79" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B79" s="12">
         <v>31</v>
@@ -7868,7 +7865,7 @@
         <v>385</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="L79" s="12" t="str">
         <f t="shared" ref="L79" si="15">_xlfn.TEXTJOIN("", TRUE, E79:K79)</f>
@@ -7880,7 +7877,7 @@
     </row>
     <row r="80" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="13" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B80" s="12">
         <v>32</v>
@@ -7897,7 +7894,7 @@
     </row>
     <row r="81" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="13" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="B81" s="12">
         <v>1</v>
@@ -7914,7 +7911,7 @@
     </row>
     <row r="82" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="13" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="B82" s="12">
         <v>2</v>
@@ -7929,7 +7926,7 @@
         <v>389</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="L82" s="12" t="str">
         <f t="shared" ref="L82:L83" si="16">_xlfn.TEXTJOIN("", TRUE, E82:K82)</f>
@@ -7941,7 +7938,7 @@
     </row>
     <row r="83" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="13" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="B83" s="12">
         <v>3</v>
@@ -7956,7 +7953,7 @@
         <v>389</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="L83" s="12" t="str">
         <f t="shared" si="16"/>
@@ -7968,7 +7965,7 @@
     </row>
     <row r="84" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="13" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="B84" s="12">
         <v>4</v>
@@ -7985,7 +7982,7 @@
     </row>
     <row r="85" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="13" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="B85" s="12">
         <v>5</v>
@@ -8015,7 +8012,7 @@
     </row>
     <row r="86" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="13" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="B86" s="12">
         <v>1</v>
@@ -8024,7 +8021,7 @@
         <v>17</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="N86" s="12" t="s">
         <v>92</v>
@@ -8032,7 +8029,7 @@
     </row>
     <row r="87" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="13" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="B87" s="12">
         <v>2</v>
@@ -8692,7 +8689,7 @@
     </row>
     <row r="125" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" s="21" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B125" s="21">
         <v>1</v>
@@ -8701,7 +8698,7 @@
         <v>45</v>
       </c>
       <c r="D125" s="21" t="s">
-        <v>581</v>
+        <v>1266</v>
       </c>
       <c r="N125" s="21" t="s">
         <v>90</v>
@@ -8709,7 +8706,7 @@
     </row>
     <row r="126" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="21" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B126" s="21">
         <v>2</v>
@@ -8718,7 +8715,7 @@
         <v>45</v>
       </c>
       <c r="D126" s="21" t="s">
-        <v>611</v>
+        <v>1267</v>
       </c>
       <c r="N126" s="21" t="s">
         <v>90</v>
@@ -8726,7 +8723,7 @@
     </row>
     <row r="127" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="21" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B127" s="21">
         <v>3</v>
@@ -8735,10 +8732,10 @@
         <v>46</v>
       </c>
       <c r="D127" s="21" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="M127" s="21" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="N127" s="21" t="s">
         <v>90</v>
@@ -8746,7 +8743,7 @@
     </row>
     <row r="128" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="21" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B128" s="21">
         <v>4</v>
@@ -8755,7 +8752,7 @@
         <v>45</v>
       </c>
       <c r="D128" s="21" t="s">
-        <v>587</v>
+        <v>1268</v>
       </c>
       <c r="N128" s="21" t="s">
         <v>90</v>
@@ -8763,7 +8760,7 @@
     </row>
     <row r="130" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A130" s="22" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B130" s="21">
         <v>1</v>
@@ -8772,7 +8769,7 @@
         <v>45</v>
       </c>
       <c r="D130" s="21" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="N130" s="21" t="s">
         <v>90</v>
@@ -8780,7 +8777,7 @@
     </row>
     <row r="131" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A131" s="22" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B131" s="21">
         <v>2</v>
@@ -8800,7 +8797,7 @@
     </row>
     <row r="132" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A132" s="22" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B132" s="21">
         <v>3</v>
@@ -8817,7 +8814,7 @@
     </row>
     <row r="133" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A133" s="22" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B133" s="21">
         <v>4</v>
@@ -8837,7 +8834,7 @@
     </row>
     <row r="134" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A134" s="22" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B134" s="21">
         <v>5</v>
@@ -8854,7 +8851,7 @@
     </row>
     <row r="135" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="22" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B135" s="21">
         <v>6</v>
@@ -8874,7 +8871,7 @@
     </row>
     <row r="136" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A136" s="22" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B136" s="21">
         <v>7</v>
@@ -8891,7 +8888,7 @@
     </row>
     <row r="137" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A137" s="22" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B137" s="21">
         <v>8</v>
@@ -8900,7 +8897,7 @@
         <v>45</v>
       </c>
       <c r="D137" s="21" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="N137" s="21" t="s">
         <v>90</v>
@@ -8908,7 +8905,7 @@
     </row>
     <row r="139" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A139" s="5" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -8917,10 +8914,10 @@
         <v>47</v>
       </c>
       <c r="F139" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="H139" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="I139" t="s">
         <v>116</v>
@@ -8935,7 +8932,7 @@
     </row>
     <row r="140" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A140" s="5" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B140">
         <v>2</v>
@@ -8944,7 +8941,7 @@
         <v>45</v>
       </c>
       <c r="D140" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="N140" t="s">
         <v>90</v>
@@ -8952,7 +8949,7 @@
     </row>
     <row r="141" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B141">
         <v>3</v>
@@ -8961,7 +8958,7 @@
         <v>47</v>
       </c>
       <c r="F141" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
       <c r="H141" t="s">
         <v>390</v>
@@ -8979,7 +8976,7 @@
     </row>
     <row r="142" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A142" s="5" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B142">
         <v>4</v>
@@ -8996,7 +8993,7 @@
     </row>
     <row r="143" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A143" s="5" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B143">
         <v>5</v>
@@ -9016,7 +9013,7 @@
     </row>
     <row r="144" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A144" s="5" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B144">
         <v>6</v>
@@ -9033,7 +9030,7 @@
     </row>
     <row r="145" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A145" s="5" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B145">
         <v>7</v>
@@ -9053,7 +9050,7 @@
     </row>
     <row r="146" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A146" s="5" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B146">
         <v>8</v>
@@ -9070,7 +9067,7 @@
     </row>
     <row r="147" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B147">
         <v>9</v>
@@ -9090,7 +9087,7 @@
     </row>
     <row r="148" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A148" s="5" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B148">
         <v>10</v>
@@ -9099,10 +9096,10 @@
         <v>47</v>
       </c>
       <c r="F148" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="H148" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="I148" t="s">
         <v>116</v>
@@ -9117,7 +9114,7 @@
     </row>
     <row r="149" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A149" s="5" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B149">
         <v>11</v>
@@ -9126,7 +9123,7 @@
         <v>45</v>
       </c>
       <c r="D149" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="N149" t="s">
         <v>90</v>
@@ -9134,7 +9131,7 @@
     </row>
     <row r="150" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A150" s="5" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B150">
         <v>12</v>
@@ -9154,7 +9151,7 @@
     </row>
     <row r="151" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A151" s="5" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B151">
         <v>13</v>
@@ -9163,10 +9160,10 @@
         <v>47</v>
       </c>
       <c r="F151" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="H151" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="I151" t="s">
         <v>116</v>
@@ -9181,7 +9178,7 @@
     </row>
     <row r="152" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A152" s="5" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B152">
         <v>14</v>
@@ -9190,7 +9187,7 @@
         <v>45</v>
       </c>
       <c r="D152" t="s">
-        <v>1268</v>
+        <v>1263</v>
       </c>
       <c r="N152" t="s">
         <v>90</v>
@@ -9198,7 +9195,7 @@
     </row>
     <row r="153" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A153" s="5" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -9207,7 +9204,7 @@
         <v>17</v>
       </c>
       <c r="D153" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="N153" t="s">
         <v>92</v>
@@ -9215,7 +9212,7 @@
     </row>
     <row r="154" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A154" s="5" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="B154">
         <v>2</v>
@@ -9224,10 +9221,10 @@
         <v>47</v>
       </c>
       <c r="F154" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="H154" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="L154" t="str">
         <f t="shared" ref="L154:L156" si="32">_xlfn.TEXTJOIN("", TRUE, E154:K154)</f>
@@ -9239,7 +9236,7 @@
     </row>
     <row r="155" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A155" s="5" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="B155">
         <v>3</v>
@@ -9248,10 +9245,10 @@
         <v>47</v>
       </c>
       <c r="F155" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="H155" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="L155" t="str">
         <f t="shared" si="32"/>
@@ -9263,7 +9260,7 @@
     </row>
     <row r="156" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A156" s="5" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="B156">
         <v>4</v>
@@ -9272,10 +9269,10 @@
         <v>47</v>
       </c>
       <c r="F156" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="H156" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="L156" t="str">
         <f t="shared" si="32"/>
@@ -9287,7 +9284,7 @@
     </row>
     <row r="157" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A157" s="5" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="B157">
         <v>5</v>
@@ -9296,7 +9293,7 @@
         <v>45</v>
       </c>
       <c r="D157" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="N157" t="s">
         <v>92</v>
@@ -9304,7 +9301,7 @@
     </row>
     <row r="158" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A158" s="5" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="B158">
         <v>6</v>
@@ -9313,7 +9310,7 @@
         <v>17</v>
       </c>
       <c r="D158" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="N158" t="s">
         <v>93</v>
@@ -9321,7 +9318,7 @@
     </row>
     <row r="159" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A159" s="5" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="B159">
         <v>7</v>
@@ -9330,10 +9327,10 @@
         <v>47</v>
       </c>
       <c r="F159" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="H159" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="L159" t="str">
         <f t="shared" ref="L159:L163" si="33">_xlfn.TEXTJOIN("", TRUE, E159:K159)</f>
@@ -9345,7 +9342,7 @@
     </row>
     <row r="160" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A160" s="5" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="B160">
         <v>8</v>
@@ -9354,10 +9351,10 @@
         <v>47</v>
       </c>
       <c r="F160" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="H160" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="L160" t="str">
         <f t="shared" si="33"/>
@@ -9369,7 +9366,7 @@
     </row>
     <row r="161" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A161" s="5" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="B161">
         <v>9</v>
@@ -9378,10 +9375,10 @@
         <v>47</v>
       </c>
       <c r="F161" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="H161" t="s">
-        <v>1237</v>
+        <v>1232</v>
       </c>
       <c r="L161" t="str">
         <f t="shared" si="33"/>
@@ -9393,7 +9390,7 @@
     </row>
     <row r="162" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A162" s="5" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="B162">
         <v>10</v>
@@ -9402,10 +9399,10 @@
         <v>47</v>
       </c>
       <c r="F162" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="H162" t="s">
-        <v>1238</v>
+        <v>1233</v>
       </c>
       <c r="L162" t="str">
         <f t="shared" si="33"/>
@@ -9417,7 +9414,7 @@
     </row>
     <row r="163" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A163" s="5" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="B163">
         <v>11</v>
@@ -9426,10 +9423,10 @@
         <v>47</v>
       </c>
       <c r="F163" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="H163" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="L163" t="str">
         <f t="shared" si="33"/>
@@ -9471,7 +9468,7 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -9480,7 +9477,7 @@
         <v>45</v>
       </c>
       <c r="D175" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="N175" t="s">
         <v>90</v>
@@ -9488,7 +9485,7 @@
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="B176" s="27">
         <v>2</v>
@@ -9497,7 +9494,7 @@
         <v>45</v>
       </c>
       <c r="D176" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="N176" t="s">
         <v>90</v>
@@ -9505,7 +9502,7 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="B177">
         <v>3</v>
@@ -9535,7 +9532,7 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="B178" s="27">
         <v>4</v>
@@ -9565,7 +9562,7 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="B179">
         <v>5</v>
@@ -9574,7 +9571,7 @@
         <v>45</v>
       </c>
       <c r="D179" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="N179" t="s">
         <v>90</v>
@@ -9582,7 +9579,7 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="B180" s="27">
         <v>6</v>
@@ -9605,7 +9602,7 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -9614,7 +9611,7 @@
         <v>45</v>
       </c>
       <c r="D182" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="N182" t="s">
         <v>90</v>
@@ -9622,7 +9619,7 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="B183" s="27">
         <v>2</v>
@@ -9631,7 +9628,7 @@
         <v>45</v>
       </c>
       <c r="D183" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
       <c r="N183" t="s">
         <v>90</v>
@@ -9639,7 +9636,7 @@
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="B184">
         <v>3</v>
@@ -9669,7 +9666,7 @@
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="B185" s="27">
         <v>4</v>
@@ -9699,7 +9696,7 @@
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="B186">
         <v>5</v>
@@ -9708,7 +9705,7 @@
         <v>45</v>
       </c>
       <c r="D186" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="N186" t="s">
         <v>90</v>
@@ -9716,7 +9713,7 @@
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="B187" s="27">
         <v>6</v>
@@ -12153,7 +12150,7 @@
         <v>39</v>
       </c>
       <c r="K128" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
@@ -13726,7 +13723,7 @@
         <v>39</v>
       </c>
       <c r="K238" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.2">
@@ -13781,7 +13778,7 @@
         <v>39</v>
       </c>
       <c r="K241" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.2">
@@ -13801,7 +13798,7 @@
         <v>512</v>
       </c>
       <c r="G242" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
       <c r="H242" t="s">
         <v>116</v>
@@ -13828,7 +13825,7 @@
         <v>512</v>
       </c>
       <c r="G243" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="H243" t="s">
         <v>116</v>
@@ -13855,7 +13852,7 @@
         <v>512</v>
       </c>
       <c r="G244" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="H244" t="s">
         <v>116</v>
@@ -13876,7 +13873,7 @@
         <v>27</v>
       </c>
       <c r="K245" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.2">
@@ -13890,7 +13887,7 @@
         <v>39</v>
       </c>
       <c r="K246" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.2">
@@ -13910,7 +13907,7 @@
         <v>512</v>
       </c>
       <c r="G247" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
       <c r="H247" t="s">
         <v>116</v>
@@ -13937,7 +13934,7 @@
         <v>512</v>
       </c>
       <c r="G248" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="H248" t="s">
         <v>116</v>
@@ -13958,7 +13955,7 @@
         <v>27</v>
       </c>
       <c r="K249" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.2">
@@ -13992,7 +13989,7 @@
         <v>512</v>
       </c>
       <c r="G251" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="H251" t="s">
         <v>116</v>
@@ -14019,7 +14016,7 @@
         <v>512</v>
       </c>
       <c r="G252" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="H252" t="s">
         <v>116</v>
@@ -14236,10 +14233,10 @@
         <v>507</v>
       </c>
       <c r="F266" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="G266" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
       <c r="H266" t="s">
         <v>116</v>
@@ -14274,7 +14271,7 @@
         <v>39</v>
       </c>
       <c r="K268" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.2">
@@ -14291,10 +14288,10 @@
         <v>507</v>
       </c>
       <c r="F269" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="G269" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="H269" t="s">
         <v>116</v>
@@ -14318,10 +14315,10 @@
         <v>507</v>
       </c>
       <c r="F270" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="G270" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="H270" t="s">
         <v>116</v>
@@ -14342,7 +14339,7 @@
         <v>27</v>
       </c>
       <c r="K271" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.2">
@@ -15013,7 +15010,7 @@
         <v>39</v>
       </c>
       <c r="K311" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.2">
@@ -15033,7 +15030,7 @@
         <v>556</v>
       </c>
       <c r="G312" t="s">
-        <v>1267</v>
+        <v>1262</v>
       </c>
       <c r="H312" t="s">
         <v>116</v>
@@ -15054,7 +15051,7 @@
         <v>27</v>
       </c>
       <c r="K313" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.2">
@@ -15123,7 +15120,7 @@
         <v>39</v>
       </c>
       <c r="K317" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.2">
@@ -15169,7 +15166,7 @@
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B321" s="27">
         <v>1</v>
@@ -15178,12 +15175,12 @@
         <v>39</v>
       </c>
       <c r="K321" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B322" s="27">
         <v>1</v>
@@ -15192,12 +15189,12 @@
         <v>27</v>
       </c>
       <c r="K322" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B323" s="27">
         <v>1</v>
@@ -15206,12 +15203,12 @@
         <v>40</v>
       </c>
       <c r="K323" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B324" s="27">
         <v>1</v>
@@ -15220,12 +15217,12 @@
         <v>41</v>
       </c>
       <c r="K324" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B325" s="27">
         <v>2</v>
@@ -15234,12 +15231,12 @@
         <v>39</v>
       </c>
       <c r="K325" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B326" s="27">
         <v>2</v>
@@ -15248,12 +15245,12 @@
         <v>27</v>
       </c>
       <c r="K326" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B327" s="27">
         <v>2</v>
@@ -15262,12 +15259,12 @@
         <v>40</v>
       </c>
       <c r="K327" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B328" s="27">
         <v>2</v>
@@ -15276,12 +15273,12 @@
         <v>41</v>
       </c>
       <c r="K328" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B329" s="27">
         <v>3</v>
@@ -15290,12 +15287,12 @@
         <v>39</v>
       </c>
       <c r="K329" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B330" s="27">
         <v>3</v>
@@ -15304,12 +15301,12 @@
         <v>27</v>
       </c>
       <c r="K330" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B331" s="27">
         <v>3</v>
@@ -15318,12 +15315,12 @@
         <v>40</v>
       </c>
       <c r="K331" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B332" s="27">
         <v>3</v>
@@ -15644,12 +15641,12 @@
         <v>111</v>
       </c>
       <c r="K352" t="s">
-        <v>1251</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B354" s="27">
         <v>1</v>
@@ -15663,7 +15660,7 @@
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B355" s="27">
         <v>1</v>
@@ -15690,7 +15687,7 @@
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B356" s="27">
         <v>1</v>
@@ -15854,7 +15851,7 @@
         <v>39</v>
       </c>
       <c r="K370" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.2">
@@ -15868,10 +15865,10 @@
         <v>108</v>
       </c>
       <c r="E371" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="G371" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="H371" t="s">
         <v>116</v>
@@ -15892,10 +15889,10 @@
         <v>108</v>
       </c>
       <c r="E372" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="G372" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="H372" t="s">
         <v>116</v>
@@ -15916,10 +15913,10 @@
         <v>108</v>
       </c>
       <c r="E373" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="G373" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="H373" t="s">
         <v>116</v>
@@ -15940,10 +15937,10 @@
         <v>108</v>
       </c>
       <c r="E374" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="G374" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="H374" t="s">
         <v>116</v>
@@ -15967,10 +15964,10 @@
         <v>108</v>
       </c>
       <c r="E375" t="s">
+        <v>608</v>
+      </c>
+      <c r="G375" t="s">
         <v>613</v>
-      </c>
-      <c r="G375" t="s">
-        <v>618</v>
       </c>
       <c r="H375" t="s">
         <v>116</v>
@@ -15994,10 +15991,10 @@
         <v>108</v>
       </c>
       <c r="E376" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="G376" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="H376" t="s">
         <v>116</v>
@@ -16021,10 +16018,10 @@
         <v>108</v>
       </c>
       <c r="E377" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="G377" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="H377" t="s">
         <v>116</v>
@@ -16093,7 +16090,7 @@
         <v>39</v>
       </c>
       <c r="K384" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.2">
@@ -16107,10 +16104,10 @@
         <v>108</v>
       </c>
       <c r="E385" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="G385" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="H385" t="s">
         <v>116</v>
@@ -16131,10 +16128,10 @@
         <v>108</v>
       </c>
       <c r="E386" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="G386" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="H386" t="s">
         <v>116</v>
@@ -16155,10 +16152,10 @@
         <v>108</v>
       </c>
       <c r="E387" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="G387" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="H387" t="s">
         <v>116</v>
@@ -16179,10 +16176,10 @@
         <v>108</v>
       </c>
       <c r="E388" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="G388" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H388" t="s">
         <v>116</v>
@@ -16203,10 +16200,10 @@
         <v>108</v>
       </c>
       <c r="E389" t="s">
+        <v>617</v>
+      </c>
+      <c r="G389" t="s">
         <v>622</v>
-      </c>
-      <c r="G389" t="s">
-        <v>627</v>
       </c>
       <c r="H389" t="s">
         <v>116</v>
@@ -16227,10 +16224,10 @@
         <v>108</v>
       </c>
       <c r="E390" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="G390" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="H390" t="s">
         <v>116</v>
@@ -16296,7 +16293,7 @@
         <v>39</v>
       </c>
       <c r="K396" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.2">
@@ -16310,10 +16307,10 @@
         <v>108</v>
       </c>
       <c r="E397" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="G397" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="H397" t="s">
         <v>116</v>
@@ -16334,10 +16331,10 @@
         <v>108</v>
       </c>
       <c r="E398" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="G398" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="H398" t="s">
         <v>116</v>
@@ -16358,10 +16355,10 @@
         <v>108</v>
       </c>
       <c r="E399" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="G399" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="H399" t="s">
         <v>116</v>
@@ -16382,10 +16379,10 @@
         <v>108</v>
       </c>
       <c r="E400" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="G400" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="H400" t="s">
         <v>116</v>
@@ -16406,10 +16403,10 @@
         <v>108</v>
       </c>
       <c r="E401" t="s">
+        <v>625</v>
+      </c>
+      <c r="G401" t="s">
         <v>630</v>
-      </c>
-      <c r="G401" t="s">
-        <v>635</v>
       </c>
       <c r="H401" t="s">
         <v>116</v>
@@ -16433,13 +16430,13 @@
         <v>109</v>
       </c>
       <c r="E402" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F402" t="s">
         <v>114</v>
       </c>
       <c r="G402" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="H402" t="s">
         <v>116</v>
@@ -16474,12 +16471,12 @@
         <v>111</v>
       </c>
       <c r="K404" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B406" s="27">
         <v>1</v>
@@ -16488,12 +16485,12 @@
         <v>39</v>
       </c>
       <c r="K406" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B407" s="27">
         <v>1</v>
@@ -16502,13 +16499,13 @@
         <v>108</v>
       </c>
       <c r="E407" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F407" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G407" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="H407" t="s">
         <v>116</v>
@@ -16520,7 +16517,7 @@
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B408" s="27">
         <v>1</v>
@@ -16529,13 +16526,13 @@
         <v>108</v>
       </c>
       <c r="E408" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F408" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G408" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="H408" t="s">
         <v>116</v>
@@ -16547,7 +16544,7 @@
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B409" s="27">
         <v>1</v>
@@ -16556,13 +16553,13 @@
         <v>108</v>
       </c>
       <c r="E409" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F409" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G409" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="H409" t="s">
         <v>116</v>
@@ -16577,7 +16574,7 @@
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B410" s="27">
         <v>1</v>
@@ -16586,13 +16583,13 @@
         <v>108</v>
       </c>
       <c r="E410" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F410" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G410" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="H410" t="s">
         <v>116</v>
@@ -16607,7 +16604,7 @@
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B411" s="27">
         <v>1</v>
@@ -16616,12 +16613,12 @@
         <v>27</v>
       </c>
       <c r="K411" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B413" s="27">
         <v>2</v>
@@ -16630,12 +16627,12 @@
         <v>39</v>
       </c>
       <c r="K413" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B414" s="27">
         <v>2</v>
@@ -16644,13 +16641,13 @@
         <v>108</v>
       </c>
       <c r="E414" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F414" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="G414" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="H414" t="s">
         <v>116</v>
@@ -16662,7 +16659,7 @@
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B415" s="27">
         <v>2</v>
@@ -16671,12 +16668,12 @@
         <v>27</v>
       </c>
       <c r="K415" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B417" s="27">
         <v>3</v>
@@ -16685,12 +16682,12 @@
         <v>39</v>
       </c>
       <c r="K417" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B418" s="27">
         <v>3</v>
@@ -16699,13 +16696,13 @@
         <v>108</v>
       </c>
       <c r="E418" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F418" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="G418" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="H418" t="s">
         <v>116</v>
@@ -16717,7 +16714,7 @@
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B419" s="27">
         <v>3</v>
@@ -16726,13 +16723,13 @@
         <v>108</v>
       </c>
       <c r="E419" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F419" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="G419" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="H419" t="s">
         <v>116</v>
@@ -16744,7 +16741,7 @@
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B420" s="27">
         <v>3</v>
@@ -16753,13 +16750,13 @@
         <v>108</v>
       </c>
       <c r="E420" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F420" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="G420" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="H420" t="s">
         <v>116</v>
@@ -16771,7 +16768,7 @@
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B421" s="27">
         <v>3</v>
@@ -16780,13 +16777,13 @@
         <v>108</v>
       </c>
       <c r="E421" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F421" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="G421" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="H421" t="s">
         <v>116</v>
@@ -16801,7 +16798,7 @@
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B422" s="27">
         <v>3</v>
@@ -16810,12 +16807,12 @@
         <v>27</v>
       </c>
       <c r="K422" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B424" s="27">
         <v>4</v>
@@ -16824,12 +16821,12 @@
         <v>39</v>
       </c>
       <c r="K424" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B425" s="27">
         <v>4</v>
@@ -16838,13 +16835,13 @@
         <v>108</v>
       </c>
       <c r="E425" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F425" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="G425" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="H425" t="s">
         <v>116</v>
@@ -16859,7 +16856,7 @@
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B426" s="27">
         <v>4</v>
@@ -16868,13 +16865,13 @@
         <v>108</v>
       </c>
       <c r="E426" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F426" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="G426" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="H426" t="s">
         <v>116</v>
@@ -16889,7 +16886,7 @@
     </row>
     <row r="427" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B427" s="27">
         <v>4</v>
@@ -16898,13 +16895,13 @@
         <v>108</v>
       </c>
       <c r="E427" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F427" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="G427" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="H427" t="s">
         <v>116</v>
@@ -16919,7 +16916,7 @@
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B428" s="27">
         <v>4</v>
@@ -16928,13 +16925,13 @@
         <v>108</v>
       </c>
       <c r="E428" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F428" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="G428" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="H428" t="s">
         <v>116</v>
@@ -16949,7 +16946,7 @@
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B429" s="27">
         <v>4</v>
@@ -16958,13 +16955,13 @@
         <v>108</v>
       </c>
       <c r="E429" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F429" t="s">
+        <v>654</v>
+      </c>
+      <c r="G429" t="s">
         <v>659</v>
-      </c>
-      <c r="G429" t="s">
-        <v>664</v>
       </c>
       <c r="H429" t="s">
         <v>116</v>
@@ -16979,7 +16976,7 @@
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B430" s="27">
         <v>4</v>
@@ -16988,19 +16985,19 @@
         <v>108</v>
       </c>
       <c r="E430" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F430" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="G430" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="H430" t="s">
         <v>116</v>
       </c>
       <c r="J430" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="K430" t="str">
         <f t="shared" si="86"/>
@@ -17009,7 +17006,7 @@
     </row>
     <row r="431" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B431" s="27">
         <v>4</v>
@@ -17018,13 +17015,13 @@
         <v>108</v>
       </c>
       <c r="E431" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F431" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="G431" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="H431" t="s">
         <v>116</v>
@@ -17039,7 +17036,7 @@
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B432" s="27">
         <v>4</v>
@@ -17048,13 +17045,13 @@
         <v>108</v>
       </c>
       <c r="E432" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F432" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="G432" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="H432" t="s">
         <v>116</v>
@@ -17069,7 +17066,7 @@
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B433" s="27">
         <v>4</v>
@@ -17078,13 +17075,13 @@
         <v>108</v>
       </c>
       <c r="E433" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F433" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="G433" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="H433" t="s">
         <v>116</v>
@@ -17099,7 +17096,7 @@
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B434" s="27">
         <v>4</v>
@@ -17108,7 +17105,7 @@
         <v>27</v>
       </c>
       <c r="K434" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
     </row>
     <row r="440" spans="1:11" x14ac:dyDescent="0.2">
@@ -17122,7 +17119,7 @@
         <v>39</v>
       </c>
       <c r="K440" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.2">
@@ -17136,10 +17133,10 @@
         <v>108</v>
       </c>
       <c r="E441" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="G441" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="H441" t="s">
         <v>116</v>
@@ -17160,10 +17157,10 @@
         <v>108</v>
       </c>
       <c r="E442" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="G442" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="H442" t="s">
         <v>116</v>
@@ -17184,10 +17181,10 @@
         <v>108</v>
       </c>
       <c r="E443" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="G443" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="H443" t="s">
         <v>116</v>
@@ -17208,10 +17205,10 @@
         <v>108</v>
       </c>
       <c r="E444" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="G444" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="H444" t="s">
         <v>116</v>
@@ -17235,10 +17232,10 @@
         <v>108</v>
       </c>
       <c r="E445" t="s">
+        <v>666</v>
+      </c>
+      <c r="G445" t="s">
         <v>671</v>
-      </c>
-      <c r="G445" t="s">
-        <v>676</v>
       </c>
       <c r="H445" t="s">
         <v>116</v>
@@ -17262,10 +17259,10 @@
         <v>108</v>
       </c>
       <c r="E446" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="G446" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="H446" t="s">
         <v>116</v>
@@ -17289,16 +17286,16 @@
         <v>108</v>
       </c>
       <c r="E447" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="G447" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="H447" t="s">
         <v>116</v>
       </c>
       <c r="J447" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="K447" t="str">
         <f t="shared" si="87"/>
@@ -17341,12 +17338,12 @@
         <v>111</v>
       </c>
       <c r="K450" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B452" s="27">
         <v>1</v>
@@ -17355,12 +17352,12 @@
         <v>39</v>
       </c>
       <c r="K452" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B453" s="27">
         <v>1</v>
@@ -17369,13 +17366,13 @@
         <v>108</v>
       </c>
       <c r="E453" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="F453" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="G453" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="H453" t="s">
         <v>116</v>
@@ -17387,7 +17384,7 @@
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B454" s="27">
         <v>1</v>
@@ -17396,13 +17393,13 @@
         <v>108</v>
       </c>
       <c r="E454" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="F454" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="G454" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="H454" t="s">
         <v>116</v>
@@ -17414,7 +17411,7 @@
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B455" s="27">
         <v>1</v>
@@ -17423,7 +17420,7 @@
         <v>27</v>
       </c>
       <c r="K455" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.2">
@@ -17437,7 +17434,7 @@
         <v>39</v>
       </c>
       <c r="K458" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.2">
@@ -17451,10 +17448,10 @@
         <v>108</v>
       </c>
       <c r="E459" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="G459" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="H459" t="s">
         <v>116</v>
@@ -17475,10 +17472,10 @@
         <v>108</v>
       </c>
       <c r="E460" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="G460" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="H460" t="s">
         <v>116</v>
@@ -17499,16 +17496,16 @@
         <v>108</v>
       </c>
       <c r="E461" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="G461" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="H461" t="s">
         <v>116</v>
       </c>
       <c r="J461" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="K461" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D461:J461)</f>
@@ -17526,10 +17523,10 @@
         <v>108</v>
       </c>
       <c r="E462" t="s">
+        <v>681</v>
+      </c>
+      <c r="G462" t="s">
         <v>686</v>
-      </c>
-      <c r="G462" t="s">
-        <v>691</v>
       </c>
       <c r="H462" t="s">
         <v>116</v>
@@ -17553,10 +17550,10 @@
         <v>108</v>
       </c>
       <c r="E463" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="G463" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="H463" t="s">
         <v>116</v>
@@ -17605,12 +17602,12 @@
         <v>111</v>
       </c>
       <c r="K466" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B468" s="27">
         <v>1</v>
@@ -17619,12 +17616,12 @@
         <v>39</v>
       </c>
       <c r="K468" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B469" s="27">
         <v>1</v>
@@ -17633,13 +17630,13 @@
         <v>108</v>
       </c>
       <c r="E469" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="F469" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="G469" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="H469" t="s">
         <v>116</v>
@@ -17651,7 +17648,7 @@
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B470" s="27">
         <v>1</v>
@@ -17660,12 +17657,12 @@
         <v>27</v>
       </c>
       <c r="K470" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B472" s="27">
         <v>2</v>
@@ -17674,12 +17671,12 @@
         <v>39</v>
       </c>
       <c r="K472" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B473" s="27">
         <v>2</v>
@@ -17688,13 +17685,13 @@
         <v>108</v>
       </c>
       <c r="E473" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="F473" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="G473" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="H473" t="s">
         <v>116</v>
@@ -17706,7 +17703,7 @@
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B474" s="27">
         <v>2</v>
@@ -17715,12 +17712,12 @@
         <v>27</v>
       </c>
       <c r="K474" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B476" s="27">
         <v>3</v>
@@ -17729,12 +17726,12 @@
         <v>39</v>
       </c>
       <c r="K476" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B477" s="27">
         <v>3</v>
@@ -17743,13 +17740,13 @@
         <v>108</v>
       </c>
       <c r="E477" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="F477" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="G477" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="H477" t="s">
         <v>116</v>
@@ -17761,7 +17758,7 @@
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B478" s="27">
         <v>3</v>
@@ -17770,12 +17767,12 @@
         <v>27</v>
       </c>
       <c r="K478" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B480" s="27">
         <v>4</v>
@@ -17784,12 +17781,12 @@
         <v>39</v>
       </c>
       <c r="K480" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B481" s="27">
         <v>4</v>
@@ -17798,13 +17795,13 @@
         <v>108</v>
       </c>
       <c r="E481" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="F481" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="G481" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="H481" t="s">
         <v>116</v>
@@ -17816,7 +17813,7 @@
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B482" s="27">
         <v>4</v>
@@ -17825,12 +17822,12 @@
         <v>27</v>
       </c>
       <c r="K482" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B484" s="27">
         <v>5</v>
@@ -17839,12 +17836,12 @@
         <v>39</v>
       </c>
       <c r="K484" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B485" s="27">
         <v>5</v>
@@ -17853,19 +17850,19 @@
         <v>108</v>
       </c>
       <c r="E485" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="F485" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="G485" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="H485" t="s">
         <v>116</v>
       </c>
       <c r="J485" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="K485" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D485:J485)</f>
@@ -17874,7 +17871,7 @@
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B486" s="27">
         <v>5</v>
@@ -17883,12 +17880,12 @@
         <v>27</v>
       </c>
       <c r="K486" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B488" s="27">
         <v>6</v>
@@ -17897,12 +17894,12 @@
         <v>39</v>
       </c>
       <c r="K488" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
     </row>
     <row r="489" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B489" s="27">
         <v>6</v>
@@ -17911,19 +17908,19 @@
         <v>108</v>
       </c>
       <c r="E489" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="F489" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="G489" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="H489" t="s">
         <v>116</v>
       </c>
       <c r="J489" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="K489" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D489:J489)</f>
@@ -17932,7 +17929,7 @@
     </row>
     <row r="490" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B490" s="27">
         <v>6</v>
@@ -17941,12 +17938,12 @@
         <v>27</v>
       </c>
       <c r="K490" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
     </row>
     <row r="492" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B492" s="27">
         <v>7</v>
@@ -17955,12 +17952,12 @@
         <v>39</v>
       </c>
       <c r="K492" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="493" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B493" s="27">
         <v>7</v>
@@ -17969,19 +17966,19 @@
         <v>108</v>
       </c>
       <c r="E493" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="F493" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="G493" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="H493" t="s">
         <v>116</v>
       </c>
       <c r="J493" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="K493" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D493:J493)</f>
@@ -17990,7 +17987,7 @@
     </row>
     <row r="494" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B494" s="27">
         <v>7</v>
@@ -17999,12 +17996,12 @@
         <v>27</v>
       </c>
       <c r="K494" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
     </row>
     <row r="496" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B496" s="27">
         <v>8</v>
@@ -18013,12 +18010,12 @@
         <v>39</v>
       </c>
       <c r="K496" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
     </row>
     <row r="497" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B497" s="27">
         <v>8</v>
@@ -18027,13 +18024,13 @@
         <v>108</v>
       </c>
       <c r="E497" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="F497" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="G497" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="H497" t="s">
         <v>116</v>
@@ -18045,7 +18042,7 @@
     </row>
     <row r="498" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B498" s="27">
         <v>8</v>
@@ -18054,7 +18051,7 @@
         <v>27</v>
       </c>
       <c r="K498" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
     </row>
     <row r="502" spans="1:11" x14ac:dyDescent="0.2">
@@ -18068,7 +18065,7 @@
         <v>39</v>
       </c>
       <c r="K502" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
     </row>
     <row r="503" spans="1:11" x14ac:dyDescent="0.2">
@@ -18082,10 +18079,10 @@
         <v>108</v>
       </c>
       <c r="E503" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="G503" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="H503" t="s">
         <v>116</v>
@@ -18106,10 +18103,10 @@
         <v>108</v>
       </c>
       <c r="E504" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="G504" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="H504" t="s">
         <v>116</v>
@@ -18130,10 +18127,10 @@
         <v>108</v>
       </c>
       <c r="E505" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="G505" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="H505" t="s">
         <v>116</v>
@@ -18154,10 +18151,10 @@
         <v>108</v>
       </c>
       <c r="E506" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="G506" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="H506" t="s">
         <v>116</v>
@@ -18234,10 +18231,10 @@
         <v>108</v>
       </c>
       <c r="E513" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="G513" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="H513" t="s">
         <v>116</v>
@@ -18258,10 +18255,10 @@
         <v>108</v>
       </c>
       <c r="E514" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="G514" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="H514" t="s">
         <v>116</v>
@@ -18282,10 +18279,10 @@
         <v>108</v>
       </c>
       <c r="E515" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="G515" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="H515" t="s">
         <v>116</v>
@@ -18306,10 +18303,10 @@
         <v>108</v>
       </c>
       <c r="E516" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="G516" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="H516" t="s">
         <v>116</v>
@@ -18333,10 +18330,10 @@
         <v>108</v>
       </c>
       <c r="E517" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="G517" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="H517" t="s">
         <v>116</v>
@@ -18360,10 +18357,10 @@
         <v>108</v>
       </c>
       <c r="E518" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="G518" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="H518" t="s">
         <v>116</v>
@@ -18387,10 +18384,10 @@
         <v>108</v>
       </c>
       <c r="E519" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="G519" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="H519" t="s">
         <v>116</v>
@@ -18414,10 +18411,10 @@
         <v>108</v>
       </c>
       <c r="E520" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="G520" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="H520" t="s">
         <v>116</v>
@@ -18441,10 +18438,10 @@
         <v>108</v>
       </c>
       <c r="E521" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="G521" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="H521" t="s">
         <v>116</v>
@@ -18468,10 +18465,10 @@
         <v>108</v>
       </c>
       <c r="E522" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="G522" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="H522" t="s">
         <v>116</v>
@@ -18495,13 +18492,13 @@
         <v>109</v>
       </c>
       <c r="E523" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F523" t="s">
         <v>114</v>
       </c>
       <c r="G523" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="H523" t="s">
         <v>116</v>
@@ -18536,12 +18533,12 @@
         <v>111</v>
       </c>
       <c r="K525" t="s">
-        <v>1255</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="527" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B527" s="27">
         <v>1</v>
@@ -18550,12 +18547,12 @@
         <v>39</v>
       </c>
       <c r="K527" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
     </row>
     <row r="528" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B528" s="27">
         <v>1</v>
@@ -18564,13 +18561,13 @@
         <v>108</v>
       </c>
       <c r="E528" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F528" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="G528" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="H528" t="s">
         <v>116</v>
@@ -18582,7 +18579,7 @@
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B529" s="27">
         <v>1</v>
@@ -18591,13 +18588,13 @@
         <v>108</v>
       </c>
       <c r="E529" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F529" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="G529" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="H529" t="s">
         <v>116</v>
@@ -18609,7 +18606,7 @@
     </row>
     <row r="530" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B530" s="27">
         <v>1</v>
@@ -18618,13 +18615,13 @@
         <v>108</v>
       </c>
       <c r="E530" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F530" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="G530" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="H530" t="s">
         <v>116</v>
@@ -18636,7 +18633,7 @@
     </row>
     <row r="531" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B531" s="27">
         <v>1</v>
@@ -18645,13 +18642,13 @@
         <v>108</v>
       </c>
       <c r="E531" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F531" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="G531" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="H531" t="s">
         <v>116</v>
@@ -18666,7 +18663,7 @@
     </row>
     <row r="532" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B532" s="27">
         <v>1</v>
@@ -18675,13 +18672,13 @@
         <v>108</v>
       </c>
       <c r="E532" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F532" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="G532" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="H532" t="s">
         <v>116</v>
@@ -18696,7 +18693,7 @@
     </row>
     <row r="533" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B533" s="27">
         <v>1</v>
@@ -18705,12 +18702,12 @@
         <v>27</v>
       </c>
       <c r="K533" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
     </row>
     <row r="535" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B535" s="27">
         <v>2</v>
@@ -18719,12 +18716,12 @@
         <v>39</v>
       </c>
       <c r="K535" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
     </row>
     <row r="536" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B536" s="27">
         <v>2</v>
@@ -18733,13 +18730,13 @@
         <v>108</v>
       </c>
       <c r="E536" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F536" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="G536" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="H536" t="s">
         <v>116</v>
@@ -18751,7 +18748,7 @@
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B537" s="27">
         <v>2</v>
@@ -18760,13 +18757,13 @@
         <v>108</v>
       </c>
       <c r="E537" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F537" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="G537" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="K537" t="str">
         <f t="shared" si="89"/>
@@ -18775,7 +18772,7 @@
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B538" s="27">
         <v>2</v>
@@ -18784,13 +18781,13 @@
         <v>108</v>
       </c>
       <c r="E538" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F538" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="G538" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="K538" t="str">
         <f t="shared" si="89"/>
@@ -18799,7 +18796,7 @@
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B539" s="27">
         <v>2</v>
@@ -18808,13 +18805,13 @@
         <v>108</v>
       </c>
       <c r="E539" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F539" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="G539" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="K539" t="str">
         <f t="shared" si="89"/>
@@ -18823,7 +18820,7 @@
     </row>
     <row r="540" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B540" s="27">
         <v>2</v>
@@ -18832,13 +18829,13 @@
         <v>108</v>
       </c>
       <c r="E540" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F540" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="G540" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="K540" t="str">
         <f t="shared" si="89"/>
@@ -18847,7 +18844,7 @@
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B541" s="27">
         <v>2</v>
@@ -18856,13 +18853,13 @@
         <v>108</v>
       </c>
       <c r="E541" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F541" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="G541" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="K541" t="str">
         <f t="shared" si="89"/>
@@ -18871,7 +18868,7 @@
     </row>
     <row r="542" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B542" s="27">
         <v>2</v>
@@ -18880,13 +18877,13 @@
         <v>108</v>
       </c>
       <c r="E542" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F542" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="G542" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="K542" t="str">
         <f t="shared" si="89"/>
@@ -18895,7 +18892,7 @@
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B543" s="27">
         <v>2</v>
@@ -18904,13 +18901,13 @@
         <v>108</v>
       </c>
       <c r="E543" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F543" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="G543" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="K543" t="str">
         <f t="shared" si="89"/>
@@ -18919,7 +18916,7 @@
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B544" s="27">
         <v>2</v>
@@ -18928,16 +18925,16 @@
         <v>108</v>
       </c>
       <c r="E544" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F544" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="G544" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="J544" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="K544" t="str">
         <f t="shared" si="89"/>
@@ -18946,7 +18943,7 @@
     </row>
     <row r="545" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B545" s="27">
         <v>2</v>
@@ -18955,12 +18952,12 @@
         <v>27</v>
       </c>
       <c r="K545" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
     </row>
     <row r="547" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B547" s="27">
         <v>3</v>
@@ -18969,12 +18966,12 @@
         <v>39</v>
       </c>
       <c r="K547" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
     </row>
     <row r="548" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B548" s="27">
         <v>3</v>
@@ -18983,13 +18980,13 @@
         <v>108</v>
       </c>
       <c r="E548" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F548" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="G548" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="K548" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D548:J548)</f>
@@ -18998,7 +18995,7 @@
     </row>
     <row r="549" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B549" s="27">
         <v>3</v>
@@ -19007,12 +19004,12 @@
         <v>27</v>
       </c>
       <c r="K549" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
     </row>
     <row r="551" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B551" s="27">
         <v>4</v>
@@ -19021,12 +19018,12 @@
         <v>39</v>
       </c>
       <c r="K551" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
     </row>
     <row r="552" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B552" s="27">
         <v>4</v>
@@ -19035,13 +19032,13 @@
         <v>108</v>
       </c>
       <c r="E552" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F552" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="G552" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="H552" t="s">
         <v>116</v>
@@ -19053,7 +19050,7 @@
     </row>
     <row r="553" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B553" s="27">
         <v>4</v>
@@ -19062,12 +19059,12 @@
         <v>27</v>
       </c>
       <c r="K553" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
     </row>
     <row r="555" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B555" s="27">
         <v>5</v>
@@ -19076,12 +19073,12 @@
         <v>39</v>
       </c>
       <c r="K555" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
     </row>
     <row r="556" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B556" s="27">
         <v>5</v>
@@ -19090,13 +19087,13 @@
         <v>108</v>
       </c>
       <c r="E556" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F556" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="G556" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="K556" t="str">
         <f t="shared" ref="K556:K562" si="90">_xlfn.TEXTJOIN("", TRUE, D556:J556)</f>
@@ -19105,7 +19102,7 @@
     </row>
     <row r="557" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B557" s="27">
         <v>5</v>
@@ -19114,13 +19111,13 @@
         <v>108</v>
       </c>
       <c r="E557" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F557" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="G557" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="K557" t="str">
         <f t="shared" si="90"/>
@@ -19129,7 +19126,7 @@
     </row>
     <row r="558" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B558" s="27">
         <v>5</v>
@@ -19138,13 +19135,13 @@
         <v>108</v>
       </c>
       <c r="E558" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F558" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="G558" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="J558" t="s">
         <v>201</v>
@@ -19156,7 +19153,7 @@
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B559" s="27">
         <v>5</v>
@@ -19165,13 +19162,13 @@
         <v>108</v>
       </c>
       <c r="E559" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F559" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="G559" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="J559" t="s">
         <v>201</v>
@@ -19183,7 +19180,7 @@
     </row>
     <row r="560" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B560" s="27">
         <v>5</v>
@@ -19192,16 +19189,16 @@
         <v>108</v>
       </c>
       <c r="E560" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F560" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="G560" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="J560" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="K560" t="str">
         <f t="shared" si="90"/>
@@ -19210,7 +19207,7 @@
     </row>
     <row r="561" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B561" s="27">
         <v>5</v>
@@ -19219,13 +19216,13 @@
         <v>108</v>
       </c>
       <c r="E561" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F561" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="G561" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="J561" t="s">
         <v>236</v>
@@ -19237,7 +19234,7 @@
     </row>
     <row r="562" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B562" s="27">
         <v>5</v>
@@ -19246,16 +19243,16 @@
         <v>108</v>
       </c>
       <c r="E562" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F562" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="G562" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="J562" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="K562" t="str">
         <f t="shared" si="90"/>
@@ -19264,7 +19261,7 @@
     </row>
     <row r="563" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B563" s="27">
         <v>5</v>
@@ -19273,12 +19270,12 @@
         <v>27</v>
       </c>
       <c r="K563" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
     </row>
     <row r="565" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B565" s="27">
         <v>6</v>
@@ -19287,12 +19284,12 @@
         <v>39</v>
       </c>
       <c r="K565" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
     </row>
     <row r="566" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B566" s="27">
         <v>6</v>
@@ -19301,13 +19298,13 @@
         <v>108</v>
       </c>
       <c r="E566" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F566" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="G566" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="K566" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D566:J566)</f>
@@ -19316,7 +19313,7 @@
     </row>
     <row r="567" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B567" s="27">
         <v>6</v>
@@ -19325,13 +19322,13 @@
         <v>108</v>
       </c>
       <c r="E567" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F567" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="G567" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K567" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D567:J567)</f>
@@ -19340,7 +19337,7 @@
     </row>
     <row r="568" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B568" s="27">
         <v>6</v>
@@ -19349,12 +19346,12 @@
         <v>27</v>
       </c>
       <c r="K568" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
     </row>
     <row r="570" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B570" s="27">
         <v>7</v>
@@ -19363,12 +19360,12 @@
         <v>39</v>
       </c>
       <c r="K570" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
     </row>
     <row r="571" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B571" s="27">
         <v>7</v>
@@ -19377,13 +19374,13 @@
         <v>108</v>
       </c>
       <c r="E571" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="F571" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="G571" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="H571" t="s">
         <v>116</v>
@@ -19395,7 +19392,7 @@
     </row>
     <row r="572" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B572" s="27">
         <v>7</v>
@@ -19404,7 +19401,7 @@
         <v>27</v>
       </c>
       <c r="K572" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
     </row>
     <row r="579" spans="1:11" x14ac:dyDescent="0.2">
@@ -19418,7 +19415,7 @@
         <v>39</v>
       </c>
       <c r="K579" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
     </row>
     <row r="580" spans="1:11" x14ac:dyDescent="0.2">
@@ -19432,10 +19429,10 @@
         <v>108</v>
       </c>
       <c r="E580" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="G580" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="K580" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D580:J580)</f>
@@ -19453,10 +19450,10 @@
         <v>108</v>
       </c>
       <c r="E581" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="G581" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="J581" t="s">
         <v>201</v>
@@ -19477,10 +19474,10 @@
         <v>108</v>
       </c>
       <c r="E582" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="G582" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="J582" t="s">
         <v>237</v>
@@ -19537,7 +19534,7 @@
         <v>39</v>
       </c>
       <c r="K588" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
     </row>
     <row r="589" spans="1:11" x14ac:dyDescent="0.2">
@@ -19551,10 +19548,10 @@
         <v>108</v>
       </c>
       <c r="E589" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="G589" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="K589" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D589:J589)</f>
@@ -19572,10 +19569,10 @@
         <v>108</v>
       </c>
       <c r="E590" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="G590" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="K590" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D590:J590)</f>
@@ -19593,10 +19590,10 @@
         <v>108</v>
       </c>
       <c r="E591" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="G591" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="J591" t="s">
         <v>128</v>
@@ -19617,10 +19614,10 @@
         <v>108</v>
       </c>
       <c r="E592" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="G592" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="J592" t="s">
         <v>128</v>
@@ -19641,13 +19638,13 @@
         <v>109</v>
       </c>
       <c r="E593" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="F593" t="s">
         <v>114</v>
       </c>
       <c r="G593" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="H593" t="s">
         <v>116</v>
@@ -19682,12 +19679,12 @@
         <v>111</v>
       </c>
       <c r="K595" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="597" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B597" s="27">
         <v>1</v>
@@ -19696,12 +19693,12 @@
         <v>39</v>
       </c>
       <c r="K597" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
     </row>
     <row r="598" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B598" s="27">
         <v>1</v>
@@ -19710,13 +19707,13 @@
         <v>108</v>
       </c>
       <c r="E598" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="F598" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="G598" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="H598" t="s">
         <v>116</v>
@@ -19728,7 +19725,7 @@
     </row>
     <row r="599" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B599" s="27">
         <v>1</v>
@@ -19737,12 +19734,12 @@
         <v>27</v>
       </c>
       <c r="K599" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
     </row>
     <row r="601" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B601" s="27">
         <v>2</v>
@@ -19751,12 +19748,12 @@
         <v>39</v>
       </c>
       <c r="K601" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
     </row>
     <row r="602" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B602" s="27">
         <v>2</v>
@@ -19765,13 +19762,13 @@
         <v>108</v>
       </c>
       <c r="E602" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="F602" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="G602" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="K602" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D602:J602)</f>
@@ -19780,7 +19777,7 @@
     </row>
     <row r="603" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B603" s="27">
         <v>2</v>
@@ -19789,13 +19786,13 @@
         <v>108</v>
       </c>
       <c r="E603" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="F603" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="G603" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="K603" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D603:J603)</f>
@@ -19804,7 +19801,7 @@
     </row>
     <row r="604" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B604" s="27">
         <v>2</v>
@@ -19813,7 +19810,7 @@
         <v>27</v>
       </c>
       <c r="K604" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
     </row>
     <row r="607" spans="1:11" x14ac:dyDescent="0.2">
@@ -19827,7 +19824,7 @@
         <v>39</v>
       </c>
       <c r="K607" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
     </row>
     <row r="608" spans="1:11" x14ac:dyDescent="0.2">
@@ -19841,10 +19838,10 @@
         <v>108</v>
       </c>
       <c r="E608" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="G608" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="K608" t="str">
         <f t="shared" ref="K608:K619" si="91">_xlfn.TEXTJOIN("", TRUE, D608:J608)</f>
@@ -19862,10 +19859,10 @@
         <v>108</v>
       </c>
       <c r="E609" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="G609" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="J609" t="s">
         <v>201</v>
@@ -19886,10 +19883,10 @@
         <v>108</v>
       </c>
       <c r="E610" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="G610" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="J610" t="s">
         <v>201</v>
@@ -19910,10 +19907,10 @@
         <v>108</v>
       </c>
       <c r="E611" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="G611" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="J611" t="s">
         <v>201</v>
@@ -19934,10 +19931,10 @@
         <v>108</v>
       </c>
       <c r="E612" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="G612" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="J612" t="s">
         <v>236</v>
@@ -19958,13 +19955,13 @@
         <v>108</v>
       </c>
       <c r="E613" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="G613" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="J613" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="K613" t="str">
         <f t="shared" si="91"/>
@@ -19982,10 +19979,10 @@
         <v>108</v>
       </c>
       <c r="E614" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="G614" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="J614" t="s">
         <v>128</v>
@@ -20006,10 +20003,10 @@
         <v>108</v>
       </c>
       <c r="E615" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="G615" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="J615" t="s">
         <v>128</v>
@@ -20030,13 +20027,13 @@
         <v>109</v>
       </c>
       <c r="E616" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F616" t="s">
         <v>114</v>
       </c>
       <c r="G616" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="J616" t="s">
         <v>201</v>
@@ -20057,13 +20054,13 @@
         <v>109</v>
       </c>
       <c r="E617" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F617" t="s">
         <v>114</v>
       </c>
       <c r="G617" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="J617" t="s">
         <v>236</v>
@@ -20084,13 +20081,13 @@
         <v>109</v>
       </c>
       <c r="E618" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F618" t="s">
         <v>114</v>
       </c>
       <c r="G618" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="J618" t="s">
         <v>236</v>
@@ -20111,16 +20108,16 @@
         <v>109</v>
       </c>
       <c r="E619" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F619" t="s">
         <v>114</v>
       </c>
       <c r="G619" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="J619" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="K619" t="str">
         <f t="shared" si="91"/>
@@ -20152,12 +20149,12 @@
         <v>111</v>
       </c>
       <c r="K621" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="623" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B623" s="27">
         <v>1</v>
@@ -20166,12 +20163,12 @@
         <v>39</v>
       </c>
       <c r="K623" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
     </row>
     <row r="624" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B624" s="27">
         <v>1</v>
@@ -20180,13 +20177,13 @@
         <v>108</v>
       </c>
       <c r="E624" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F624" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="G624" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="K624" t="str">
         <f t="shared" ref="K624:K629" si="92">_xlfn.TEXTJOIN("", TRUE, D624:J624)</f>
@@ -20195,7 +20192,7 @@
     </row>
     <row r="625" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B625" s="27">
         <v>1</v>
@@ -20204,13 +20201,13 @@
         <v>108</v>
       </c>
       <c r="E625" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F625" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="G625" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="K625" t="str">
         <f t="shared" si="92"/>
@@ -20219,7 +20216,7 @@
     </row>
     <row r="626" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B626" s="27">
         <v>1</v>
@@ -20228,13 +20225,13 @@
         <v>108</v>
       </c>
       <c r="E626" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F626" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="G626" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="J626" t="s">
         <v>201</v>
@@ -20246,7 +20243,7 @@
     </row>
     <row r="627" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B627" s="27">
         <v>1</v>
@@ -20255,13 +20252,13 @@
         <v>108</v>
       </c>
       <c r="E627" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F627" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="G627" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="J627" t="s">
         <v>236</v>
@@ -20273,7 +20270,7 @@
     </row>
     <row r="628" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B628" s="27">
         <v>1</v>
@@ -20282,13 +20279,13 @@
         <v>108</v>
       </c>
       <c r="E628" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F628" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="G628" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="J628" t="s">
         <v>236</v>
@@ -20300,7 +20297,7 @@
     </row>
     <row r="629" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B629" s="27">
         <v>1</v>
@@ -20309,13 +20306,13 @@
         <v>108</v>
       </c>
       <c r="E629" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F629" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="G629" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="J629" t="s">
         <v>236</v>
@@ -20327,7 +20324,7 @@
     </row>
     <row r="630" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B630" s="27">
         <v>1</v>
@@ -20336,12 +20333,12 @@
         <v>27</v>
       </c>
       <c r="K630" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
     </row>
     <row r="632" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B632" s="27">
         <v>2</v>
@@ -20350,12 +20347,12 @@
         <v>39</v>
       </c>
       <c r="K632" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
     </row>
     <row r="633" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A633" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B633" s="27">
         <v>2</v>
@@ -20364,13 +20361,13 @@
         <v>108</v>
       </c>
       <c r="E633" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F633" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="G633" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="K633" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D633:J633)</f>
@@ -20379,7 +20376,7 @@
     </row>
     <row r="634" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A634" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B634" s="27">
         <v>2</v>
@@ -20388,13 +20385,13 @@
         <v>108</v>
       </c>
       <c r="E634" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F634" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="G634" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="J634" t="s">
         <v>201</v>
@@ -20406,7 +20403,7 @@
     </row>
     <row r="635" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B635" s="27">
         <v>2</v>
@@ -20415,13 +20412,13 @@
         <v>108</v>
       </c>
       <c r="E635" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F635" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="G635" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="J635" t="s">
         <v>236</v>
@@ -20433,7 +20430,7 @@
     </row>
     <row r="636" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B636" s="27">
         <v>2</v>
@@ -20442,13 +20439,13 @@
         <v>108</v>
       </c>
       <c r="E636" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F636" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="G636" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="J636" t="s">
         <v>236</v>
@@ -20460,7 +20457,7 @@
     </row>
     <row r="637" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A637" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B637" s="27">
         <v>2</v>
@@ -20469,16 +20466,16 @@
         <v>108</v>
       </c>
       <c r="E637" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F637" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="G637" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="J637" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="K637" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D637:J637)</f>
@@ -20487,7 +20484,7 @@
     </row>
     <row r="638" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A638" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B638" s="27">
         <v>2</v>
@@ -20496,7 +20493,7 @@
         <v>27</v>
       </c>
       <c r="K638" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
     </row>
     <row r="640" spans="1:11" x14ac:dyDescent="0.2">
@@ -20510,7 +20507,7 @@
         <v>39</v>
       </c>
       <c r="K640" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
     </row>
     <row r="641" spans="1:11" x14ac:dyDescent="0.2">
@@ -20524,10 +20521,10 @@
         <v>108</v>
       </c>
       <c r="E641" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="G641" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="H641" t="s">
         <v>116</v>
@@ -20548,13 +20545,13 @@
         <v>109</v>
       </c>
       <c r="E642" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="F642" t="s">
         <v>114</v>
       </c>
       <c r="G642" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="K642" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D642:J642)</f>
@@ -20572,13 +20569,13 @@
         <v>109</v>
       </c>
       <c r="E643" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="F643" t="s">
         <v>114</v>
       </c>
       <c r="G643" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="K643" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D643:J643)</f>
@@ -20621,7 +20618,7 @@
         <v>39</v>
       </c>
       <c r="K648" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
     </row>
     <row r="649" spans="1:11" x14ac:dyDescent="0.2">
@@ -20635,10 +20632,10 @@
         <v>108</v>
       </c>
       <c r="E649" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="G649" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="K649" t="str">
         <f t="shared" ref="K649:K660" si="93">_xlfn.TEXTJOIN("", TRUE, D649:J649)</f>
@@ -20656,10 +20653,10 @@
         <v>108</v>
       </c>
       <c r="E650" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="G650" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="K650" t="str">
         <f t="shared" si="93"/>
@@ -20677,10 +20674,10 @@
         <v>108</v>
       </c>
       <c r="E651" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="G651" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="J651" t="s">
         <v>201</v>
@@ -20701,10 +20698,10 @@
         <v>108</v>
       </c>
       <c r="E652" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="G652" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="J652" t="s">
         <v>201</v>
@@ -20725,10 +20722,10 @@
         <v>108</v>
       </c>
       <c r="E653" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="G653" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="J653" t="s">
         <v>236</v>
@@ -20749,10 +20746,10 @@
         <v>108</v>
       </c>
       <c r="E654" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="G654" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="J654" t="s">
         <v>236</v>
@@ -20773,10 +20770,10 @@
         <v>108</v>
       </c>
       <c r="E655" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="G655" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="J655" t="s">
         <v>237</v>
@@ -20797,10 +20794,10 @@
         <v>108</v>
       </c>
       <c r="E656" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="G656" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="J656" t="s">
         <v>237</v>
@@ -20821,10 +20818,10 @@
         <v>108</v>
       </c>
       <c r="E657" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="G657" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="J657" t="s">
         <v>128</v>
@@ -20845,10 +20842,10 @@
         <v>108</v>
       </c>
       <c r="E658" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="G658" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="J658" t="s">
         <v>128</v>
@@ -20869,13 +20866,13 @@
         <v>109</v>
       </c>
       <c r="E659" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="F659" t="s">
         <v>114</v>
       </c>
       <c r="G659" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="J659" t="s">
         <v>201</v>
@@ -20896,13 +20893,13 @@
         <v>109</v>
       </c>
       <c r="E660" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="F660" t="s">
         <v>114</v>
       </c>
       <c r="G660" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="J660" t="s">
         <v>236</v>
@@ -20948,7 +20945,7 @@
         <v>39</v>
       </c>
       <c r="K665" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
     </row>
     <row r="666" spans="1:11" x14ac:dyDescent="0.2">
@@ -20962,10 +20959,10 @@
         <v>108</v>
       </c>
       <c r="E666" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="G666" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="K666" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D666:J666)</f>
@@ -20983,10 +20980,10 @@
         <v>108</v>
       </c>
       <c r="E667" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="G667" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="K667" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D667:J667)</f>
@@ -21004,10 +21001,10 @@
         <v>108</v>
       </c>
       <c r="E668" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="G668" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="K668" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D668:J668)</f>
@@ -21025,13 +21022,13 @@
         <v>109</v>
       </c>
       <c r="E669" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="F669" t="s">
         <v>114</v>
       </c>
       <c r="G669" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="H669" t="s">
         <v>116</v>
@@ -21077,7 +21074,7 @@
         <v>39</v>
       </c>
       <c r="K674" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
     </row>
     <row r="675" spans="1:11" x14ac:dyDescent="0.2">
@@ -21091,10 +21088,10 @@
         <v>108</v>
       </c>
       <c r="E675" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="G675" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="K675" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D675:J675)</f>
@@ -21112,10 +21109,10 @@
         <v>108</v>
       </c>
       <c r="E676" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="G676" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="K676" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D676:J676)</f>
@@ -21133,10 +21130,10 @@
         <v>108</v>
       </c>
       <c r="E677" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="G677" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="K677" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D677:J677)</f>
@@ -21183,12 +21180,12 @@
         <v>111</v>
       </c>
       <c r="K680" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="682" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A682" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="B682" s="27">
         <v>1</v>
@@ -21197,12 +21194,12 @@
         <v>39</v>
       </c>
       <c r="K682" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
     </row>
     <row r="683" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A683" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="B683" s="27">
         <v>1</v>
@@ -21211,13 +21208,13 @@
         <v>108</v>
       </c>
       <c r="E683" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="F683" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="G683" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="K683" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D683:J683)</f>
@@ -21226,7 +21223,7 @@
     </row>
     <row r="684" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A684" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="B684" s="27">
         <v>1</v>
@@ -21235,13 +21232,13 @@
         <v>108</v>
       </c>
       <c r="E684" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="F684" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="G684" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="K684" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D684:J684)</f>
@@ -21250,7 +21247,7 @@
     </row>
     <row r="685" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A685" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="B685" s="27">
         <v>1</v>
@@ -21259,13 +21256,13 @@
         <v>108</v>
       </c>
       <c r="E685" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="F685" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="G685" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="K685" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D685:J685)</f>
@@ -21274,7 +21271,7 @@
     </row>
     <row r="686" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A686" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="B686" s="27">
         <v>1</v>
@@ -21283,7 +21280,7 @@
         <v>27</v>
       </c>
       <c r="K686" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
     </row>
     <row r="691" spans="1:11" x14ac:dyDescent="0.2">
@@ -21297,7 +21294,7 @@
         <v>39</v>
       </c>
       <c r="K691" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
     </row>
     <row r="692" spans="1:11" x14ac:dyDescent="0.2">
@@ -21311,10 +21308,10 @@
         <v>108</v>
       </c>
       <c r="E692" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="G692" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="K692" t="str">
         <f t="shared" ref="K692:K698" si="94">_xlfn.TEXTJOIN("", TRUE, D692:J692)</f>
@@ -21332,10 +21329,10 @@
         <v>108</v>
       </c>
       <c r="E693" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="G693" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="J693" t="s">
         <v>237</v>
@@ -21356,10 +21353,10 @@
         <v>108</v>
       </c>
       <c r="E694" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="G694" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="J694" t="s">
         <v>237</v>
@@ -21380,10 +21377,10 @@
         <v>108</v>
       </c>
       <c r="E695" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="G695" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="J695" t="s">
         <v>237</v>
@@ -21404,10 +21401,10 @@
         <v>108</v>
       </c>
       <c r="E696" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="G696" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="J696" t="s">
         <v>128</v>
@@ -21428,13 +21425,13 @@
         <v>109</v>
       </c>
       <c r="E697" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="F697" t="s">
         <v>114</v>
       </c>
       <c r="G697" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="K697" t="str">
         <f t="shared" si="94"/>
@@ -21452,13 +21449,13 @@
         <v>109</v>
       </c>
       <c r="E698" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="F698" t="s">
         <v>114</v>
       </c>
       <c r="G698" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="K698" t="str">
         <f t="shared" si="94"/>
@@ -21490,12 +21487,12 @@
         <v>111</v>
       </c>
       <c r="K700" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="702" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A702" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B702" s="27">
         <v>1</v>
@@ -21504,12 +21501,12 @@
         <v>39</v>
       </c>
       <c r="K702" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="703" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A703" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B703" s="27">
         <v>1</v>
@@ -21518,13 +21515,13 @@
         <v>108</v>
       </c>
       <c r="E703" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="F703" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="G703" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="K703" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D703:J703)</f>
@@ -21533,7 +21530,7 @@
     </row>
     <row r="704" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A704" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B704" s="27">
         <v>1</v>
@@ -21542,13 +21539,13 @@
         <v>108</v>
       </c>
       <c r="E704" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="F704" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="G704" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="K704" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D704:J704)</f>
@@ -21557,7 +21554,7 @@
     </row>
     <row r="705" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A705" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B705" s="27">
         <v>1</v>
@@ -21566,13 +21563,13 @@
         <v>108</v>
       </c>
       <c r="E705" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="F705" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="G705" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="K705" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D705:J705)</f>
@@ -21581,7 +21578,7 @@
     </row>
     <row r="706" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A706" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B706" s="27">
         <v>1</v>
@@ -21590,13 +21587,13 @@
         <v>108</v>
       </c>
       <c r="E706" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="F706" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="G706" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="K706" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D706:J706)</f>
@@ -21605,7 +21602,7 @@
     </row>
     <row r="707" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A707" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B707" s="27">
         <v>1</v>
@@ -21614,13 +21611,13 @@
         <v>108</v>
       </c>
       <c r="E707" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="F707" t="s">
+        <v>941</v>
+      </c>
+      <c r="G707" t="s">
         <v>946</v>
-      </c>
-      <c r="G707" t="s">
-        <v>951</v>
       </c>
       <c r="K707" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D707:J707)</f>
@@ -21629,7 +21626,7 @@
     </row>
     <row r="708" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A708" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B708" s="27">
         <v>1</v>
@@ -21638,7 +21635,7 @@
         <v>27</v>
       </c>
       <c r="K708" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
     </row>
     <row r="712" spans="1:11" x14ac:dyDescent="0.2">
@@ -21652,7 +21649,7 @@
         <v>39</v>
       </c>
       <c r="K712" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
     </row>
     <row r="713" spans="1:11" x14ac:dyDescent="0.2">
@@ -21666,10 +21663,10 @@
         <v>108</v>
       </c>
       <c r="E713" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="G713" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="K713" t="str">
         <f t="shared" ref="K713:K718" si="95">_xlfn.TEXTJOIN("", TRUE, D713:J713)</f>
@@ -21687,10 +21684,10 @@
         <v>108</v>
       </c>
       <c r="E714" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="G714" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="K714" t="str">
         <f t="shared" si="95"/>
@@ -21708,10 +21705,10 @@
         <v>108</v>
       </c>
       <c r="E715" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="G715" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="K715" t="str">
         <f t="shared" si="95"/>
@@ -21729,10 +21726,10 @@
         <v>108</v>
       </c>
       <c r="E716" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="G716" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="K716" t="str">
         <f t="shared" si="95"/>
@@ -21750,10 +21747,10 @@
         <v>108</v>
       </c>
       <c r="E717" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="G717" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="J717" t="s">
         <v>237</v>
@@ -21814,7 +21811,7 @@
         <v>39</v>
       </c>
       <c r="K723" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
     </row>
     <row r="724" spans="1:11" x14ac:dyDescent="0.2">
@@ -21828,10 +21825,10 @@
         <v>108</v>
       </c>
       <c r="E724" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="G724" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="K724" t="str">
         <f t="shared" ref="K724:K730" si="96">_xlfn.TEXTJOIN("", TRUE, D724:J724)</f>
@@ -21849,10 +21846,10 @@
         <v>108</v>
       </c>
       <c r="E725" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="G725" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="J725" t="s">
         <v>201</v>
@@ -21873,10 +21870,10 @@
         <v>108</v>
       </c>
       <c r="E726" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="G726" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="J726" t="s">
         <v>201</v>
@@ -21897,10 +21894,10 @@
         <v>108</v>
       </c>
       <c r="E727" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="G727" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="J727" t="s">
         <v>201</v>
@@ -21921,10 +21918,10 @@
         <v>108</v>
       </c>
       <c r="E728" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="G728" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="J728" t="s">
         <v>237</v>
@@ -21945,10 +21942,10 @@
         <v>108</v>
       </c>
       <c r="E729" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="G729" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="J729" t="s">
         <v>128</v>
@@ -22009,7 +22006,7 @@
         <v>39</v>
       </c>
       <c r="K735" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="736" spans="1:11" x14ac:dyDescent="0.2">
@@ -22023,10 +22020,10 @@
         <v>108</v>
       </c>
       <c r="E736" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="G736" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="K736" t="str">
         <f t="shared" ref="K736:K743" si="97">_xlfn.TEXTJOIN("", TRUE, D736:J736)</f>
@@ -22044,10 +22041,10 @@
         <v>108</v>
       </c>
       <c r="E737" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="G737" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="J737" t="s">
         <v>201</v>
@@ -22068,10 +22065,10 @@
         <v>108</v>
       </c>
       <c r="E738" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="G738" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="J738" t="s">
         <v>237</v>
@@ -22092,10 +22089,10 @@
         <v>108</v>
       </c>
       <c r="E739" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="G739" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="J739" t="s">
         <v>237</v>
@@ -22116,13 +22113,13 @@
         <v>108</v>
       </c>
       <c r="E740" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="G740" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="J740" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="K740" t="str">
         <f t="shared" si="97"/>
@@ -22140,10 +22137,10 @@
         <v>108</v>
       </c>
       <c r="E741" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="G741" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="J741" t="s">
         <v>128</v>
@@ -22164,10 +22161,10 @@
         <v>108</v>
       </c>
       <c r="E742" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="G742" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="J742" t="s">
         <v>128</v>
@@ -22228,7 +22225,7 @@
         <v>39</v>
       </c>
       <c r="K748" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
     </row>
     <row r="749" spans="1:11" x14ac:dyDescent="0.2">
@@ -22242,10 +22239,10 @@
         <v>108</v>
       </c>
       <c r="E749" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="G749" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="K749" t="str">
         <f t="shared" ref="K749:K755" si="98">_xlfn.TEXTJOIN("", TRUE, D749:J749)</f>
@@ -22263,10 +22260,10 @@
         <v>108</v>
       </c>
       <c r="E750" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="G750" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="K750" t="str">
         <f t="shared" si="98"/>
@@ -22284,10 +22281,10 @@
         <v>108</v>
       </c>
       <c r="E751" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="G751" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="J751" t="s">
         <v>237</v>
@@ -22308,10 +22305,10 @@
         <v>108</v>
       </c>
       <c r="E752" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="G752" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="J752" t="s">
         <v>128</v>
@@ -22332,10 +22329,10 @@
         <v>108</v>
       </c>
       <c r="E753" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="G753" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="J753" t="s">
         <v>128</v>
@@ -22356,13 +22353,13 @@
         <v>109</v>
       </c>
       <c r="E754" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="F754" t="s">
         <v>114</v>
       </c>
       <c r="G754" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="J754" t="s">
         <v>237</v>
@@ -22383,13 +22380,13 @@
         <v>109</v>
       </c>
       <c r="E755" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="F755" t="s">
         <v>114</v>
       </c>
       <c r="G755" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="J755" t="s">
         <v>237</v>
@@ -22435,7 +22432,7 @@
         <v>39</v>
       </c>
       <c r="K760" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
     </row>
     <row r="761" spans="1:11" x14ac:dyDescent="0.2">
@@ -22449,10 +22446,10 @@
         <v>108</v>
       </c>
       <c r="E761" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="G761" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="K761" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D761:J761)</f>
@@ -22470,10 +22467,10 @@
         <v>108</v>
       </c>
       <c r="E762" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="G762" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="K762" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D762:J762)</f>
@@ -22491,10 +22488,10 @@
         <v>108</v>
       </c>
       <c r="E763" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="G763" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="J763" t="s">
         <v>237</v>
@@ -22515,10 +22512,10 @@
         <v>108</v>
       </c>
       <c r="E764" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="G764" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="J764" t="s">
         <v>128</v>
@@ -22539,13 +22536,13 @@
         <v>109</v>
       </c>
       <c r="E765" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="F765" t="s">
         <v>114</v>
       </c>
       <c r="G765" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="H765" t="s">
         <v>116</v>
@@ -22594,7 +22591,7 @@
         <v>39</v>
       </c>
       <c r="K770" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
     </row>
     <row r="771" spans="1:11" x14ac:dyDescent="0.2">
@@ -22608,10 +22605,10 @@
         <v>108</v>
       </c>
       <c r="E771" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="G771" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="K771" t="str">
         <f t="shared" ref="K771:K778" si="99">_xlfn.TEXTJOIN("", TRUE, D771:J771)</f>
@@ -22629,13 +22626,13 @@
         <v>108</v>
       </c>
       <c r="E772" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="G772" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="J772" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="K772" t="str">
         <f t="shared" si="99"/>
@@ -22653,10 +22650,10 @@
         <v>108</v>
       </c>
       <c r="E773" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="G773" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="J773" t="s">
         <v>128</v>
@@ -22677,10 +22674,10 @@
         <v>108</v>
       </c>
       <c r="E774" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="G774" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="J774" t="s">
         <v>128</v>
@@ -22701,13 +22698,13 @@
         <v>109</v>
       </c>
       <c r="E775" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="F775" t="s">
         <v>114</v>
       </c>
       <c r="G775" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="J775" t="s">
         <v>201</v>
@@ -22728,13 +22725,13 @@
         <v>109</v>
       </c>
       <c r="E776" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="F776" t="s">
         <v>114</v>
       </c>
       <c r="G776" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="J776" t="s">
         <v>236</v>
@@ -22755,13 +22752,13 @@
         <v>109</v>
       </c>
       <c r="E777" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="F777" t="s">
         <v>114</v>
       </c>
       <c r="G777" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="J777" t="s">
         <v>237</v>
@@ -22782,13 +22779,13 @@
         <v>109</v>
       </c>
       <c r="E778" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="F778" t="s">
         <v>114</v>
       </c>
       <c r="G778" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="J778" t="s">
         <v>237</v>
@@ -22834,7 +22831,7 @@
         <v>39</v>
       </c>
       <c r="K783" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
     </row>
     <row r="784" spans="1:11" x14ac:dyDescent="0.2">
@@ -22848,7 +22845,7 @@
         <v>108</v>
       </c>
       <c r="E784" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="K784" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D784:J784)</f>
@@ -22906,7 +22903,7 @@
         <v>39</v>
       </c>
       <c r="K790" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
     </row>
     <row r="791" spans="1:11" x14ac:dyDescent="0.2">
@@ -22920,10 +22917,10 @@
         <v>108</v>
       </c>
       <c r="E791" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="G791" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="K791" t="str">
         <f t="shared" ref="K791:K797" si="100">_xlfn.TEXTJOIN("", TRUE, D791:J791)</f>
@@ -22941,10 +22938,10 @@
         <v>108</v>
       </c>
       <c r="E792" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="G792" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="J792" t="s">
         <v>201</v>
@@ -22965,10 +22962,10 @@
         <v>108</v>
       </c>
       <c r="E793" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="G793" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="J793" t="s">
         <v>201</v>
@@ -22989,13 +22986,13 @@
         <v>108</v>
       </c>
       <c r="E794" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="G794" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="J794" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="K794" t="str">
         <f t="shared" si="100"/>
@@ -23013,13 +23010,13 @@
         <v>108</v>
       </c>
       <c r="E795" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="G795" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="J795" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="K795" t="str">
         <f t="shared" si="100"/>
@@ -23037,13 +23034,13 @@
         <v>108</v>
       </c>
       <c r="E796" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="G796" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="J796" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="K796" t="str">
         <f t="shared" si="100"/>
@@ -23101,7 +23098,7 @@
         <v>39</v>
       </c>
       <c r="K802" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
     </row>
     <row r="803" spans="1:11" x14ac:dyDescent="0.2">
@@ -23115,10 +23112,10 @@
         <v>108</v>
       </c>
       <c r="E803" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="G803" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="J803" t="s">
         <v>201</v>
@@ -23139,10 +23136,10 @@
         <v>108</v>
       </c>
       <c r="E804" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="G804" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="J804" t="s">
         <v>236</v>
@@ -23163,10 +23160,10 @@
         <v>108</v>
       </c>
       <c r="E805" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="G805" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="J805" t="s">
         <v>236</v>
@@ -23187,10 +23184,10 @@
         <v>108</v>
       </c>
       <c r="E806" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="G806" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="J806" t="s">
         <v>236</v>
@@ -23211,10 +23208,10 @@
         <v>108</v>
       </c>
       <c r="E807" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="G807" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="J807" t="s">
         <v>236</v>
@@ -23235,10 +23232,10 @@
         <v>108</v>
       </c>
       <c r="E808" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="G808" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="J808" t="s">
         <v>236</v>
@@ -23259,10 +23256,10 @@
         <v>108</v>
       </c>
       <c r="E809" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="G809" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="J809" t="s">
         <v>236</v>
@@ -23283,13 +23280,13 @@
         <v>108</v>
       </c>
       <c r="E810" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="G810" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="J810" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="K810" t="str">
         <f t="shared" si="101"/>
@@ -23307,13 +23304,13 @@
         <v>108</v>
       </c>
       <c r="E811" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="G811" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="J811" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="K811" t="str">
         <f t="shared" si="101"/>
@@ -23331,13 +23328,13 @@
         <v>108</v>
       </c>
       <c r="E812" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="G812" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="J812" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="K812" t="str">
         <f t="shared" si="101"/>
@@ -23355,13 +23352,13 @@
         <v>108</v>
       </c>
       <c r="E813" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="G813" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="J813" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="K813" t="str">
         <f t="shared" si="101"/>
@@ -23379,13 +23376,13 @@
         <v>108</v>
       </c>
       <c r="E814" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="G814" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="J814" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="K814" t="str">
         <f t="shared" si="101"/>
@@ -23403,13 +23400,13 @@
         <v>109</v>
       </c>
       <c r="E815" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="F815" t="s">
         <v>114</v>
       </c>
       <c r="G815" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="K815" t="str">
         <f t="shared" si="101"/>
@@ -23427,13 +23424,13 @@
         <v>109</v>
       </c>
       <c r="E816" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="F816" t="s">
         <v>114</v>
       </c>
       <c r="G816" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="K816" t="str">
         <f t="shared" si="101"/>
@@ -23490,10 +23487,10 @@
         <v>108</v>
       </c>
       <c r="E822" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="G822" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="K822" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D822:J822)</f>
@@ -23511,10 +23508,10 @@
         <v>108</v>
       </c>
       <c r="E823" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="G823" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="J823" t="s">
         <v>201</v>
@@ -23535,10 +23532,10 @@
         <v>108</v>
       </c>
       <c r="E824" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="G824" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="J824" t="s">
         <v>201</v>
@@ -23599,7 +23596,7 @@
         <v>39</v>
       </c>
       <c r="K830" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
     </row>
     <row r="831" spans="1:11" x14ac:dyDescent="0.2">
@@ -23613,10 +23610,10 @@
         <v>108</v>
       </c>
       <c r="E831" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="G831" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="K831" t="str">
         <f t="shared" ref="K831:K837" si="102">_xlfn.TEXTJOIN("", TRUE, D831:J831)</f>
@@ -23634,10 +23631,10 @@
         <v>108</v>
       </c>
       <c r="E832" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="G832" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="K832" t="str">
         <f t="shared" si="102"/>
@@ -23655,10 +23652,10 @@
         <v>108</v>
       </c>
       <c r="E833" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="G833" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="J833" t="s">
         <v>201</v>
@@ -23679,10 +23676,10 @@
         <v>108</v>
       </c>
       <c r="E834" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="G834" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="J834" t="s">
         <v>237</v>
@@ -23703,13 +23700,13 @@
         <v>109</v>
       </c>
       <c r="E835" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="F835" t="s">
         <v>114</v>
       </c>
       <c r="G835" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="K835" t="str">
         <f t="shared" si="102"/>
@@ -23727,13 +23724,13 @@
         <v>109</v>
       </c>
       <c r="E836" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="F836" t="s">
         <v>114</v>
       </c>
       <c r="G836" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="K836" t="str">
         <f t="shared" si="102"/>
@@ -23751,16 +23748,16 @@
         <v>109</v>
       </c>
       <c r="E837" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="F837" t="s">
         <v>114</v>
       </c>
       <c r="G837" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="J837" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="K837" t="str">
         <f t="shared" si="102"/>
@@ -23792,12 +23789,12 @@
         <v>111</v>
       </c>
       <c r="K839" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="841" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A841" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="B841" s="27">
         <v>1</v>
@@ -23806,12 +23803,12 @@
         <v>39</v>
       </c>
       <c r="K841" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="842" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A842" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="B842" s="27">
         <v>1</v>
@@ -23820,19 +23817,19 @@
         <v>108</v>
       </c>
       <c r="E842" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="F842" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="G842" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="H842" t="s">
         <v>116</v>
       </c>
       <c r="J842" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="K842" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D842:J842)</f>
@@ -23841,7 +23838,7 @@
     </row>
     <row r="843" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A843" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="B843" s="27">
         <v>1</v>
@@ -23850,7 +23847,7 @@
         <v>27</v>
       </c>
       <c r="K843" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
     </row>
     <row r="849" spans="1:11" x14ac:dyDescent="0.2">
@@ -23864,7 +23861,7 @@
         <v>39</v>
       </c>
       <c r="K849" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
     </row>
     <row r="850" spans="1:11" x14ac:dyDescent="0.2">
@@ -23878,10 +23875,10 @@
         <v>108</v>
       </c>
       <c r="E850" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="G850" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="K850" t="str">
         <f t="shared" ref="K850:K858" si="103">_xlfn.TEXTJOIN("", TRUE, D850:J850)</f>
@@ -23899,10 +23896,10 @@
         <v>108</v>
       </c>
       <c r="E851" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="G851" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="K851" t="str">
         <f t="shared" si="103"/>
@@ -23920,10 +23917,10 @@
         <v>108</v>
       </c>
       <c r="E852" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="G852" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="K852" t="str">
         <f t="shared" si="103"/>
@@ -23941,10 +23938,10 @@
         <v>108</v>
       </c>
       <c r="E853" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="G853" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="K853" t="str">
         <f t="shared" si="103"/>
@@ -23962,10 +23959,10 @@
         <v>108</v>
       </c>
       <c r="E854" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="G854" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="J854" t="s">
         <v>201</v>
@@ -23986,10 +23983,10 @@
         <v>108</v>
       </c>
       <c r="E855" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="G855" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="J855" t="s">
         <v>236</v>
@@ -24010,13 +24007,13 @@
         <v>108</v>
       </c>
       <c r="E856" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="G856" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="J856" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="K856" t="str">
         <f t="shared" si="103"/>
@@ -24034,13 +24031,13 @@
         <v>109</v>
       </c>
       <c r="E857" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="F857" t="s">
         <v>114</v>
       </c>
       <c r="G857" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="K857" t="str">
         <f t="shared" si="103"/>
@@ -24058,13 +24055,13 @@
         <v>109</v>
       </c>
       <c r="E858" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="F858" t="s">
         <v>114</v>
       </c>
       <c r="G858" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="K858" t="str">
         <f t="shared" si="103"/>
@@ -24121,10 +24118,10 @@
         <v>108</v>
       </c>
       <c r="E864" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="G864" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K864" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D864:J864)</f>
@@ -24142,10 +24139,10 @@
         <v>108</v>
       </c>
       <c r="E865" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="G865" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="K865" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D865:J865)</f>
@@ -24163,10 +24160,10 @@
         <v>108</v>
       </c>
       <c r="E866" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="G866" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="J866" t="s">
         <v>201</v>
@@ -24187,10 +24184,10 @@
         <v>108</v>
       </c>
       <c r="E867" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="G867" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="J867" t="s">
         <v>236</v>
@@ -24240,12 +24237,12 @@
         <v>111</v>
       </c>
       <c r="K870" t="s">
-        <v>1261</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="872" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A872" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B872" s="27">
         <v>1</v>
@@ -24254,12 +24251,12 @@
         <v>39</v>
       </c>
       <c r="K872" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="873" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A873" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B873" s="27">
         <v>1</v>
@@ -24268,13 +24265,13 @@
         <v>108</v>
       </c>
       <c r="E873" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="F873" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="G873" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="H873" t="s">
         <v>116</v>
@@ -24286,7 +24283,7 @@
     </row>
     <row r="874" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A874" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B874" s="27">
         <v>1</v>
@@ -24295,12 +24292,12 @@
         <v>27</v>
       </c>
       <c r="K874" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="876" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A876" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B876" s="27">
         <v>2</v>
@@ -24309,12 +24306,12 @@
         <v>39</v>
       </c>
       <c r="K876" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="877" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A877" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B877" s="27">
         <v>2</v>
@@ -24323,13 +24320,13 @@
         <v>108</v>
       </c>
       <c r="E877" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="F877" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="G877" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="H877" t="s">
         <v>116</v>
@@ -24341,7 +24338,7 @@
     </row>
     <row r="878" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A878" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B878" s="27">
         <v>2</v>
@@ -24350,12 +24347,12 @@
         <v>27</v>
       </c>
       <c r="K878" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="880" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A880" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B880" s="27">
         <v>3</v>
@@ -24364,12 +24361,12 @@
         <v>39</v>
       </c>
       <c r="K880" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="881" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A881" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B881" s="27">
         <v>3</v>
@@ -24378,13 +24375,13 @@
         <v>108</v>
       </c>
       <c r="E881" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="F881" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="G881" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="H881" t="s">
         <v>116</v>
@@ -24399,7 +24396,7 @@
     </row>
     <row r="882" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A882" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B882" s="27">
         <v>3</v>
@@ -24408,12 +24405,12 @@
         <v>27</v>
       </c>
       <c r="K882" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="884" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A884" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B884" s="27">
         <v>4</v>
@@ -24422,12 +24419,12 @@
         <v>39</v>
       </c>
       <c r="K884" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="885" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A885" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B885" s="27">
         <v>4</v>
@@ -24436,13 +24433,13 @@
         <v>108</v>
       </c>
       <c r="E885" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="F885" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G885" t="s">
         <v>1041</v>
-      </c>
-      <c r="G885" t="s">
-        <v>1046</v>
       </c>
       <c r="H885" t="s">
         <v>116</v>
@@ -24454,7 +24451,7 @@
     </row>
     <row r="886" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A886" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B886" s="27">
         <v>4</v>
@@ -24463,12 +24460,12 @@
         <v>27</v>
       </c>
       <c r="K886" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="888" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A888" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B888" s="27">
         <v>5</v>
@@ -24477,12 +24474,12 @@
         <v>39</v>
       </c>
       <c r="K888" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="889" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A889" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B889" s="27">
         <v>5</v>
@@ -24491,13 +24488,13 @@
         <v>108</v>
       </c>
       <c r="E889" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="F889" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="G889" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="H889" t="s">
         <v>116</v>
@@ -24509,7 +24506,7 @@
     </row>
     <row r="890" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A890" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B890" s="27">
         <v>5</v>
@@ -24518,12 +24515,12 @@
         <v>27</v>
       </c>
       <c r="K890" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="892" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A892" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B892" s="27">
         <v>6</v>
@@ -24532,12 +24529,12 @@
         <v>39</v>
       </c>
       <c r="K892" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="893" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A893" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B893" s="27">
         <v>6</v>
@@ -24546,13 +24543,13 @@
         <v>108</v>
       </c>
       <c r="E893" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="F893" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="G893" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="H893" t="s">
         <v>116</v>
@@ -24564,7 +24561,7 @@
     </row>
     <row r="894" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A894" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B894" s="27">
         <v>6</v>
@@ -24573,7 +24570,7 @@
         <v>27</v>
       </c>
       <c r="K894" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="896" spans="1:11" x14ac:dyDescent="0.2">
@@ -24587,7 +24584,7 @@
         <v>39</v>
       </c>
       <c r="K896" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
     </row>
     <row r="897" spans="1:11" x14ac:dyDescent="0.2">
@@ -24601,10 +24598,10 @@
         <v>108</v>
       </c>
       <c r="E897" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="G897" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="K897" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D897:J897)</f>
@@ -24622,10 +24619,10 @@
         <v>108</v>
       </c>
       <c r="E898" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="G898" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="K898" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D898:J898)</f>
@@ -24643,10 +24640,10 @@
         <v>108</v>
       </c>
       <c r="E899" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="G899" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="K899" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D899:J899)</f>
@@ -24704,7 +24701,7 @@
         <v>39</v>
       </c>
       <c r="K905" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
     </row>
     <row r="906" spans="1:11" x14ac:dyDescent="0.2">
@@ -24718,10 +24715,10 @@
         <v>108</v>
       </c>
       <c r="E906" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="G906" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="K906" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D906:J906)</f>
@@ -24739,13 +24736,13 @@
         <v>108</v>
       </c>
       <c r="E907" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="G907" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="J907" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="K907" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D907:J907)</f>
@@ -24763,13 +24760,13 @@
         <v>109</v>
       </c>
       <c r="E908" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="F908" t="s">
         <v>114</v>
       </c>
       <c r="G908" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="K908" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D908:J908)</f>
@@ -24787,13 +24784,13 @@
         <v>109</v>
       </c>
       <c r="E909" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="F909" t="s">
         <v>114</v>
       </c>
       <c r="G909" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="K909" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D909:J909)</f>
@@ -24836,7 +24833,7 @@
         <v>39</v>
       </c>
       <c r="K914" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
     </row>
     <row r="915" spans="1:11" x14ac:dyDescent="0.2">
@@ -24850,10 +24847,10 @@
         <v>108</v>
       </c>
       <c r="E915" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="G915" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="K915" t="str">
         <f t="shared" ref="K915:K922" si="104">_xlfn.TEXTJOIN("", TRUE, D915:J915)</f>
@@ -24871,10 +24868,10 @@
         <v>108</v>
       </c>
       <c r="E916" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="G916" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="K916" t="str">
         <f t="shared" si="104"/>
@@ -24892,10 +24889,10 @@
         <v>108</v>
       </c>
       <c r="E917" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="G917" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="K917" t="str">
         <f t="shared" si="104"/>
@@ -24913,10 +24910,10 @@
         <v>108</v>
       </c>
       <c r="E918" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="G918" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
       <c r="K918" t="str">
         <f t="shared" si="104"/>
@@ -24934,10 +24931,10 @@
         <v>108</v>
       </c>
       <c r="E919" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="G919" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="J919" t="s">
         <v>128</v>
@@ -24958,10 +24955,10 @@
         <v>108</v>
       </c>
       <c r="E920" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="G920" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="J920" t="s">
         <v>128</v>
@@ -24982,13 +24979,13 @@
         <v>109</v>
       </c>
       <c r="E921" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="F921" t="s">
         <v>114</v>
       </c>
       <c r="G921" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="K921" t="str">
         <f t="shared" si="104"/>
@@ -25006,13 +25003,13 @@
         <v>109</v>
       </c>
       <c r="E922" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="F922" t="s">
         <v>114</v>
       </c>
       <c r="G922" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="K922" t="str">
         <f t="shared" si="104"/>
@@ -25055,7 +25052,7 @@
         <v>39</v>
       </c>
       <c r="K927" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
     </row>
     <row r="928" spans="1:11" x14ac:dyDescent="0.2">
@@ -25069,10 +25066,10 @@
         <v>108</v>
       </c>
       <c r="E928" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="G928" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="K928" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D928:J928)</f>
@@ -25090,10 +25087,10 @@
         <v>108</v>
       </c>
       <c r="E929" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="G929" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
       <c r="K929" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D929:J929)</f>
@@ -25111,10 +25108,10 @@
         <v>108</v>
       </c>
       <c r="E930" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="G930" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
       <c r="J930" t="s">
         <v>237</v>
@@ -25175,7 +25172,7 @@
         <v>39</v>
       </c>
       <c r="K936" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
     </row>
     <row r="937" spans="1:11" x14ac:dyDescent="0.2">
@@ -25189,10 +25186,10 @@
         <v>108</v>
       </c>
       <c r="E937" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="G937" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="K937" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D937:J937)</f>
@@ -25210,10 +25207,10 @@
         <v>108</v>
       </c>
       <c r="E938" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="G938" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="K938" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D938:J938)</f>
@@ -25231,10 +25228,10 @@
         <v>108</v>
       </c>
       <c r="E939" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="G939" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="K939" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D939:J939)</f>
@@ -25252,10 +25249,10 @@
         <v>108</v>
       </c>
       <c r="E940" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="G940" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="J940" t="s">
         <v>237</v>
@@ -25276,13 +25273,13 @@
         <v>109</v>
       </c>
       <c r="E941" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="F941" t="s">
         <v>114</v>
       </c>
       <c r="G941" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="K941" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D941:J941)</f>
@@ -25325,7 +25322,7 @@
         <v>39</v>
       </c>
       <c r="K946" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
     </row>
     <row r="947" spans="1:11" x14ac:dyDescent="0.2">
@@ -25339,10 +25336,10 @@
         <v>108</v>
       </c>
       <c r="E947" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="G947" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="K947" t="str">
         <f t="shared" ref="K947:K955" si="105">_xlfn.TEXTJOIN("", TRUE, D947:J947)</f>
@@ -25360,10 +25357,10 @@
         <v>108</v>
       </c>
       <c r="E948" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="G948" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="K948" t="str">
         <f t="shared" si="105"/>
@@ -25381,10 +25378,10 @@
         <v>108</v>
       </c>
       <c r="E949" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="G949" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="K949" t="str">
         <f t="shared" si="105"/>
@@ -25402,13 +25399,13 @@
         <v>108</v>
       </c>
       <c r="E950" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="G950" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="J950" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="K950" t="str">
         <f t="shared" si="105"/>
@@ -25426,10 +25423,10 @@
         <v>108</v>
       </c>
       <c r="E951" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="G951" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="J951" t="s">
         <v>128</v>
@@ -25450,10 +25447,10 @@
         <v>108</v>
       </c>
       <c r="E952" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="G952" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="J952" t="s">
         <v>128</v>
@@ -25474,10 +25471,10 @@
         <v>108</v>
       </c>
       <c r="E953" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="G953" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="J953" t="s">
         <v>128</v>
@@ -25498,13 +25495,13 @@
         <v>109</v>
       </c>
       <c r="E954" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="F954" t="s">
         <v>114</v>
       </c>
       <c r="G954" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
       <c r="K954" t="str">
         <f t="shared" si="105"/>
@@ -25522,13 +25519,13 @@
         <v>109</v>
       </c>
       <c r="E955" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="F955" t="s">
         <v>114</v>
       </c>
       <c r="G955" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="K955" t="str">
         <f t="shared" si="105"/>
@@ -25571,7 +25568,7 @@
         <v>39</v>
       </c>
       <c r="K960" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
     </row>
     <row r="961" spans="1:11" x14ac:dyDescent="0.2">
@@ -25585,10 +25582,10 @@
         <v>108</v>
       </c>
       <c r="E961" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="G961" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="K961" t="str">
         <f t="shared" ref="K961:K967" si="106">_xlfn.TEXTJOIN("", TRUE, D961:J961)</f>
@@ -25606,10 +25603,10 @@
         <v>108</v>
       </c>
       <c r="E962" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="G962" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="J962" t="s">
         <v>201</v>
@@ -25630,10 +25627,10 @@
         <v>108</v>
       </c>
       <c r="E963" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="G963" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="J963" t="s">
         <v>201</v>
@@ -25654,10 +25651,10 @@
         <v>108</v>
       </c>
       <c r="E964" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="G964" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="J964" t="s">
         <v>237</v>
@@ -25678,10 +25675,10 @@
         <v>108</v>
       </c>
       <c r="E965" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="G965" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="J965" t="s">
         <v>128</v>
@@ -25702,10 +25699,10 @@
         <v>108</v>
       </c>
       <c r="E966" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="G966" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="J966" t="s">
         <v>128</v>
@@ -25766,7 +25763,7 @@
         <v>39</v>
       </c>
       <c r="K972" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
     </row>
     <row r="973" spans="1:11" x14ac:dyDescent="0.2">
@@ -25780,10 +25777,10 @@
         <v>108</v>
       </c>
       <c r="E973" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="G973" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="K973" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D973:J973)</f>
@@ -25801,13 +25798,13 @@
         <v>109</v>
       </c>
       <c r="E974" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="F974" t="s">
         <v>114</v>
       </c>
       <c r="G974" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="K974" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D974:J974)</f>
@@ -25850,7 +25847,7 @@
         <v>39</v>
       </c>
       <c r="K979" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
     </row>
     <row r="980" spans="1:11" x14ac:dyDescent="0.2">
@@ -25864,10 +25861,10 @@
         <v>108</v>
       </c>
       <c r="E980" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="G980" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="K980" t="str">
         <f t="shared" ref="K980:K985" si="107">_xlfn.TEXTJOIN("", TRUE, D980:J980)</f>
@@ -25885,10 +25882,10 @@
         <v>108</v>
       </c>
       <c r="E981" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="G981" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="J981" t="s">
         <v>201</v>
@@ -25909,10 +25906,10 @@
         <v>108</v>
       </c>
       <c r="E982" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="G982" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="J982" t="s">
         <v>236</v>
@@ -25933,10 +25930,10 @@
         <v>108</v>
       </c>
       <c r="E983" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="G983" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="J983" t="s">
         <v>237</v>
@@ -25957,13 +25954,13 @@
         <v>108</v>
       </c>
       <c r="E984" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="G984" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="J984" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="K984" t="str">
         <f t="shared" si="107"/>
@@ -26010,12 +26007,12 @@
         <v>111</v>
       </c>
       <c r="K987" t="s">
-        <v>1262</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="989" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A989" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="B989" s="27">
         <v>1</v>
@@ -26024,12 +26021,12 @@
         <v>39</v>
       </c>
       <c r="K989" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="990" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A990" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="B990" s="27">
         <v>1</v>
@@ -26038,13 +26035,13 @@
         <v>108</v>
       </c>
       <c r="E990" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="F990" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
       <c r="G990" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="K990" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D990:J990)</f>
@@ -26053,7 +26050,7 @@
     </row>
     <row r="991" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A991" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="B991" s="27">
         <v>1</v>
@@ -26062,13 +26059,13 @@
         <v>108</v>
       </c>
       <c r="E991" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="F991" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
       <c r="G991" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="K991" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D991:J991)</f>
@@ -26077,7 +26074,7 @@
     </row>
     <row r="992" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A992" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="B992" s="27">
         <v>1</v>
@@ -26086,13 +26083,13 @@
         <v>108</v>
       </c>
       <c r="E992" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="F992" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G992" t="s">
         <v>1108</v>
-      </c>
-      <c r="G992" t="s">
-        <v>1113</v>
       </c>
       <c r="J992" t="s">
         <v>128</v>
@@ -26104,7 +26101,7 @@
     </row>
     <row r="993" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A993" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="B993" s="27">
         <v>1</v>
@@ -26113,12 +26110,12 @@
         <v>27</v>
       </c>
       <c r="K993" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="995" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A995" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="B995" s="27">
         <v>2</v>
@@ -26127,12 +26124,12 @@
         <v>39</v>
       </c>
       <c r="K995" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="996" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A996" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="B996" s="27">
         <v>2</v>
@@ -26141,13 +26138,13 @@
         <v>108</v>
       </c>
       <c r="E996" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="F996" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="G996" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="K996" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D996:J996)</f>
@@ -26156,7 +26153,7 @@
     </row>
     <row r="997" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A997" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="B997" s="27">
         <v>2</v>
@@ -26165,16 +26162,16 @@
         <v>108</v>
       </c>
       <c r="E997" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="F997" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="G997" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="J997" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="K997" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D997:J997)</f>
@@ -26183,7 +26180,7 @@
     </row>
     <row r="998" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A998" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="B998" s="27">
         <v>2</v>
@@ -26192,7 +26189,7 @@
         <v>27</v>
       </c>
       <c r="K998" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="1001" spans="1:11" x14ac:dyDescent="0.2">
@@ -26206,7 +26203,7 @@
         <v>39</v>
       </c>
       <c r="K1001" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
     </row>
     <row r="1002" spans="1:11" x14ac:dyDescent="0.2">
@@ -26220,10 +26217,10 @@
         <v>108</v>
       </c>
       <c r="E1002" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G1002" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="K1002" t="str">
         <f t="shared" ref="K1002:K1016" si="108">_xlfn.TEXTJOIN("", TRUE, D1002:J1002)</f>
@@ -26241,10 +26238,10 @@
         <v>108</v>
       </c>
       <c r="E1003" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G1003" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
       <c r="J1003" t="s">
         <v>201</v>
@@ -26265,10 +26262,10 @@
         <v>108</v>
       </c>
       <c r="E1004" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G1004" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="J1004" t="s">
         <v>236</v>
@@ -26289,13 +26286,13 @@
         <v>108</v>
       </c>
       <c r="E1005" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G1005" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="J1005" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
       <c r="K1005" t="str">
         <f t="shared" si="108"/>
@@ -26313,10 +26310,10 @@
         <v>108</v>
       </c>
       <c r="E1006" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G1006" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="J1006" t="s">
         <v>237</v>
@@ -26337,13 +26334,13 @@
         <v>108</v>
       </c>
       <c r="E1007" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G1007" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="J1007" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="K1007" t="str">
         <f t="shared" si="108"/>
@@ -26361,13 +26358,13 @@
         <v>108</v>
       </c>
       <c r="E1008" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G1008" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="J1008" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="K1008" t="str">
         <f t="shared" si="108"/>
@@ -26385,13 +26382,13 @@
         <v>108</v>
       </c>
       <c r="E1009" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G1009" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="J1009" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="K1009" t="str">
         <f t="shared" si="108"/>
@@ -26409,13 +26406,13 @@
         <v>108</v>
       </c>
       <c r="E1010" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G1010" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="J1010" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="K1010" t="str">
         <f t="shared" si="108"/>
@@ -26433,13 +26430,13 @@
         <v>108</v>
       </c>
       <c r="E1011" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G1011" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="J1011" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="K1011" t="str">
         <f t="shared" si="108"/>
@@ -26457,10 +26454,10 @@
         <v>108</v>
       </c>
       <c r="E1012" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G1012" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="J1012" t="s">
         <v>128</v>
@@ -26481,10 +26478,10 @@
         <v>108</v>
       </c>
       <c r="E1013" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G1013" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="J1013" t="s">
         <v>128</v>
@@ -26505,13 +26502,13 @@
         <v>109</v>
       </c>
       <c r="E1014" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="F1014" t="s">
         <v>114</v>
       </c>
       <c r="G1014" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
       <c r="K1014" t="str">
         <f t="shared" si="108"/>
@@ -26529,13 +26526,13 @@
         <v>109</v>
       </c>
       <c r="E1015" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="F1015" t="s">
         <v>114</v>
       </c>
       <c r="G1015" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="K1015" t="str">
         <f t="shared" si="108"/>
@@ -26553,13 +26550,13 @@
         <v>109</v>
       </c>
       <c r="E1016" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="F1016" t="s">
         <v>114</v>
       </c>
       <c r="G1016" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="J1016" t="s">
         <v>236</v>
@@ -26605,7 +26602,7 @@
         <v>39</v>
       </c>
       <c r="K1021" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
     </row>
     <row r="1022" spans="1:11" x14ac:dyDescent="0.2">
@@ -26619,10 +26616,10 @@
         <v>108</v>
       </c>
       <c r="E1022" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="G1022" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
       <c r="K1022" t="str">
         <f t="shared" ref="K1022:K1027" si="109">_xlfn.TEXTJOIN("", TRUE, D1022:J1022)</f>
@@ -26640,10 +26637,10 @@
         <v>108</v>
       </c>
       <c r="E1023" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="G1023" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="J1023" t="s">
         <v>201</v>
@@ -26664,10 +26661,10 @@
         <v>108</v>
       </c>
       <c r="E1024" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="G1024" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="J1024" t="s">
         <v>236</v>
@@ -26688,10 +26685,10 @@
         <v>108</v>
       </c>
       <c r="E1025" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="G1025" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
       <c r="J1025" t="s">
         <v>237</v>
@@ -26712,10 +26709,10 @@
         <v>108</v>
       </c>
       <c r="E1026" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="G1026" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="J1026" t="s">
         <v>128</v>
@@ -26776,7 +26773,7 @@
         <v>39</v>
       </c>
       <c r="K1032" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
     </row>
     <row r="1033" spans="1:11" x14ac:dyDescent="0.2">
@@ -26790,10 +26787,10 @@
         <v>108</v>
       </c>
       <c r="E1033" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G1033" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
       <c r="K1033" t="str">
         <f t="shared" ref="K1033:K1043" si="110">_xlfn.TEXTJOIN("", TRUE, D1033:J1033)</f>
@@ -26811,10 +26808,10 @@
         <v>108</v>
       </c>
       <c r="E1034" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G1034" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="K1034" t="str">
         <f t="shared" si="110"/>
@@ -26832,10 +26829,10 @@
         <v>108</v>
       </c>
       <c r="E1035" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G1035" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
       <c r="K1035" t="str">
         <f t="shared" si="110"/>
@@ -26853,10 +26850,10 @@
         <v>108</v>
       </c>
       <c r="E1036" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G1036" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
       <c r="J1036" t="s">
         <v>236</v>
@@ -26877,10 +26874,10 @@
         <v>108</v>
       </c>
       <c r="E1037" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G1037" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="J1037" t="s">
         <v>236</v>
@@ -26901,10 +26898,10 @@
         <v>108</v>
       </c>
       <c r="E1038" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G1038" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="J1038" t="s">
         <v>128</v>
@@ -26925,10 +26922,10 @@
         <v>108</v>
       </c>
       <c r="E1039" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G1039" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="J1039" t="s">
         <v>128</v>
@@ -26949,10 +26946,10 @@
         <v>108</v>
       </c>
       <c r="E1040" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G1040" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="J1040" t="s">
         <v>128</v>
@@ -26973,10 +26970,10 @@
         <v>108</v>
       </c>
       <c r="E1041" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G1041" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
       <c r="J1041" t="s">
         <v>128</v>
@@ -26997,13 +26994,13 @@
         <v>109</v>
       </c>
       <c r="E1042" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="F1042" t="s">
         <v>114</v>
       </c>
       <c r="G1042" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
       <c r="J1042" t="s">
         <v>128</v>
@@ -27024,13 +27021,13 @@
         <v>109</v>
       </c>
       <c r="E1043" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="F1043" t="s">
         <v>114</v>
       </c>
       <c r="G1043" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="J1043" t="s">
         <v>128</v>
@@ -27076,7 +27073,7 @@
         <v>39</v>
       </c>
       <c r="K1048" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
     </row>
     <row r="1049" spans="1:11" x14ac:dyDescent="0.2">
@@ -27090,10 +27087,10 @@
         <v>108</v>
       </c>
       <c r="E1049" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="G1049" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="J1049" t="s">
         <v>201</v>
@@ -27114,10 +27111,10 @@
         <v>108</v>
       </c>
       <c r="E1050" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="G1050" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="J1050" t="s">
         <v>201</v>
@@ -27138,10 +27135,10 @@
         <v>108</v>
       </c>
       <c r="E1051" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="G1051" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
       <c r="J1051" t="s">
         <v>236</v>
@@ -27162,10 +27159,10 @@
         <v>108</v>
       </c>
       <c r="E1052" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="G1052" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="J1052" t="s">
         <v>236</v>
@@ -27186,10 +27183,10 @@
         <v>108</v>
       </c>
       <c r="E1053" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="G1053" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
       <c r="J1053" t="s">
         <v>236</v>
@@ -27250,7 +27247,7 @@
         <v>39</v>
       </c>
       <c r="K1059" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
     </row>
     <row r="1060" spans="1:11" x14ac:dyDescent="0.2">
@@ -27264,10 +27261,10 @@
         <v>108</v>
       </c>
       <c r="E1060" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="G1060" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="J1060" t="s">
         <v>201</v>
@@ -27288,10 +27285,10 @@
         <v>108</v>
       </c>
       <c r="E1061" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="G1061" t="s">
-        <v>1156</v>
+        <v>1151</v>
       </c>
       <c r="J1061" t="s">
         <v>236</v>
@@ -27312,10 +27309,10 @@
         <v>108</v>
       </c>
       <c r="E1062" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="G1062" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="J1062" t="s">
         <v>236</v>
@@ -27336,10 +27333,10 @@
         <v>108</v>
       </c>
       <c r="E1063" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="G1063" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
       <c r="J1063" t="s">
         <v>236</v>
@@ -27360,10 +27357,10 @@
         <v>108</v>
       </c>
       <c r="E1064" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="G1064" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="J1064" t="s">
         <v>236</v>
@@ -27384,10 +27381,10 @@
         <v>108</v>
       </c>
       <c r="E1065" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="G1065" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
       <c r="J1065" t="s">
         <v>236</v>
@@ -27408,13 +27405,13 @@
         <v>108</v>
       </c>
       <c r="E1066" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="G1066" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="J1066" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="K1066" t="str">
         <f t="shared" si="112"/>
@@ -27432,13 +27429,13 @@
         <v>108</v>
       </c>
       <c r="E1067" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="G1067" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="J1067" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="K1067" t="str">
         <f t="shared" si="112"/>
@@ -27456,13 +27453,13 @@
         <v>108</v>
       </c>
       <c r="E1068" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="G1068" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="J1068" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="K1068" t="str">
         <f t="shared" si="112"/>
@@ -27480,13 +27477,13 @@
         <v>108</v>
       </c>
       <c r="E1069" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="G1069" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
       <c r="J1069" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="K1069" t="str">
         <f t="shared" si="112"/>
@@ -27504,16 +27501,16 @@
         <v>109</v>
       </c>
       <c r="E1070" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="F1070" t="s">
         <v>114</v>
       </c>
       <c r="G1070" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="J1070" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="K1070" t="str">
         <f t="shared" si="112"/>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA8A404-F944-824E-86A1-5A8221B1DFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4897661F-05D6-5E4E-8384-7643D2948209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27340" yWindow="500" windowWidth="19120" windowHeight="16240" activeTab="4" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="-28800" yWindow="500" windowWidth="14660" windowHeight="16240" activeTab="3" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5006" uniqueCount="1269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5006" uniqueCount="1267">
   <si>
     <t>page_id</t>
   </si>
@@ -1787,6 +1787,9 @@
     <t>Beischrift</t>
   </si>
   <si>
+    <t>Beziehung</t>
+  </si>
+  <si>
     <t>gl_beischrift</t>
   </si>
   <si>
@@ -3840,15 +3843,6 @@
   </si>
   <si>
     <t>Inschrift</t>
-  </si>
-  <si>
-    <t>[Beziehung]</t>
-  </si>
-  <si>
-    <t>[Szenentitel]</t>
-  </si>
-  <si>
-    <t>[Rückenschutzformel]</t>
   </si>
 </sst>
 </file>
@@ -4500,7 +4494,7 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="D9" t="s">
         <v>74</v>
@@ -4517,7 +4511,7 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="D10" t="s">
         <v>75</v>
@@ -4613,16 +4607,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D16" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F16">
         <v>150</v>
@@ -5021,7 +5015,7 @@
         <v>396</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="F18" s="13">
         <v>3</v>
@@ -5038,7 +5032,7 @@
         <v>571</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F19" s="13">
         <v>4</v>
@@ -5055,7 +5049,7 @@
         <v>575</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="F20" s="13">
         <v>5</v>
@@ -5086,7 +5080,7 @@
         <v>27</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="F23" s="17">
         <v>2</v>
@@ -5165,7 +5159,7 @@
         <v>24</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F30" s="22">
         <v>1</v>
@@ -5179,10 +5173,10 @@
         <v>26</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F31" s="22">
         <v>2</v>
@@ -5196,7 +5190,7 @@
         <v>24</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F32" s="22">
         <v>3</v>
@@ -5210,10 +5204,10 @@
         <v>26</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F33" s="22">
         <v>4</v>
@@ -5227,10 +5221,10 @@
         <v>26</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F34" s="22">
         <v>5</v>
@@ -5244,10 +5238,10 @@
         <v>26</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F35" s="22">
         <v>6</v>
@@ -5301,10 +5295,10 @@
         <v>177</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>337</v>
@@ -5370,7 +5364,7 @@
         <v>54</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="K4" s="4">
         <v>3</v>
@@ -5399,7 +5393,7 @@
         <v>178</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="K5" s="4">
         <v>4</v>
@@ -5419,7 +5413,7 @@
         <v>192</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>54</v>
@@ -5448,7 +5442,7 @@
         <v>54</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="K8" s="4">
         <v>2</v>
@@ -5465,7 +5459,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>202</v>
@@ -5474,7 +5468,7 @@
         <v>54</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="K9" s="4">
         <v>3</v>
@@ -5491,7 +5485,7 @@
         <v>55</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>203</v>
@@ -5500,7 +5494,7 @@
         <v>54</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="K10" s="4">
         <v>4</v>
@@ -5517,7 +5511,7 @@
         <v>55</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>204</v>
@@ -5526,7 +5520,7 @@
         <v>54</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="K11" s="4">
         <v>5</v>
@@ -5543,7 +5537,7 @@
         <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>54</v>
@@ -5563,7 +5557,7 @@
         <v>55</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>54</v>
@@ -5592,7 +5586,7 @@
         <v>54</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="K15" s="4">
         <v>3</v>
@@ -5618,7 +5612,7 @@
         <v>54</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="K16" s="4">
         <v>4</v>
@@ -5635,7 +5629,7 @@
         <v>55</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>54</v>
@@ -5661,7 +5655,7 @@
         <v>54</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="4">
@@ -5685,7 +5679,7 @@
         <v>54</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="4">
@@ -5703,7 +5697,7 @@
         <v>55</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>446</v>
@@ -5712,7 +5706,7 @@
         <v>54</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="K20" s="4">
         <v>8</v>
@@ -5729,7 +5723,7 @@
         <v>55</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>454</v>
@@ -5738,7 +5732,7 @@
         <v>54</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="K21" s="4">
         <v>9</v>
@@ -5777,7 +5771,7 @@
         <v>55</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>502</v>
@@ -5786,7 +5780,7 @@
         <v>54</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="K25" s="4">
         <v>1</v>
@@ -5803,7 +5797,7 @@
         <v>55</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>504</v>
@@ -5812,7 +5806,7 @@
         <v>54</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="K26" s="4">
         <v>2</v>
@@ -5829,7 +5823,7 @@
         <v>55</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>505</v>
@@ -5838,7 +5832,7 @@
         <v>54</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="K27" s="4">
         <v>3</v>
@@ -5864,7 +5858,7 @@
         <v>54</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="K28" s="4">
         <v>4</v>
@@ -5884,7 +5878,7 @@
         <v>192</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>54</v>
@@ -5904,7 +5898,7 @@
         <v>55</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>530</v>
@@ -5913,7 +5907,7 @@
         <v>54</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="K31" s="4">
         <v>2</v>
@@ -5962,7 +5956,7 @@
         <v>54</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="K33" s="4">
         <v>4</v>
@@ -5970,7 +5964,7 @@
     </row>
     <row r="35" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>24</v>
@@ -5985,7 +5979,7 @@
         <v>54</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="K35" s="4">
         <v>1</v>
@@ -5993,7 +5987,7 @@
     </row>
     <row r="36" spans="1:11" ht="51" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>26</v>
@@ -6005,7 +5999,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>54</v>
@@ -6016,7 +6010,7 @@
     </row>
     <row r="37" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>28</v>
@@ -6028,13 +6022,13 @@
         <v>29</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>54</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="K37" s="4">
         <v>3</v>
@@ -6042,7 +6036,7 @@
     </row>
     <row r="38" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>32</v>
@@ -6054,7 +6048,7 @@
         <v>33</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="K38" s="4">
         <v>4</v>
@@ -7515,7 +7509,7 @@
     </row>
     <row r="64" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B64" s="12">
         <v>16</v>
@@ -7532,7 +7526,7 @@
     </row>
     <row r="65" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B65" s="12">
         <v>17</v>
@@ -7547,7 +7541,7 @@
         <v>381</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="L65" s="12" t="str">
         <f t="shared" ref="L65:L78" si="11">_xlfn.TEXTJOIN("", TRUE, E65:K65)</f>
@@ -7559,7 +7553,7 @@
     </row>
     <row r="66" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B66" s="12">
         <v>18</v>
@@ -7574,7 +7568,7 @@
         <v>381</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="L66" s="12" t="str">
         <f t="shared" si="11"/>
@@ -7586,7 +7580,7 @@
     </row>
     <row r="67" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B67" s="12">
         <v>19</v>
@@ -7601,7 +7595,7 @@
         <v>381</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="L67" s="12" t="str">
         <f t="shared" ref="L67" si="12">_xlfn.TEXTJOIN("", TRUE, E67:K67)</f>
@@ -7613,7 +7607,7 @@
     </row>
     <row r="68" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B68" s="12">
         <v>20</v>
@@ -7622,7 +7616,7 @@
         <v>45</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="N68" s="12" t="s">
         <v>92</v>
@@ -7630,7 +7624,7 @@
     </row>
     <row r="69" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B69" s="12">
         <v>21</v>
@@ -7647,7 +7641,7 @@
     </row>
     <row r="70" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B70" s="12">
         <v>22</v>
@@ -7662,7 +7656,7 @@
         <v>382</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="L70" s="12" t="str">
         <f t="shared" si="11"/>
@@ -7674,7 +7668,7 @@
     </row>
     <row r="71" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B71" s="12">
         <v>23</v>
@@ -7689,7 +7683,7 @@
         <v>382</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="L71" s="12" t="str">
         <f t="shared" si="11"/>
@@ -7701,7 +7695,7 @@
     </row>
     <row r="72" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B72" s="12">
         <v>24</v>
@@ -7718,7 +7712,7 @@
     </row>
     <row r="73" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B73" s="12">
         <v>25</v>
@@ -7733,7 +7727,7 @@
         <v>382</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="L73" s="12" t="str">
         <f t="shared" ref="L73" si="13">_xlfn.TEXTJOIN("", TRUE, E73:K73)</f>
@@ -7745,7 +7739,7 @@
     </row>
     <row r="74" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B74" s="12">
         <v>26</v>
@@ -7762,7 +7756,7 @@
     </row>
     <row r="75" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B75" s="12">
         <v>27</v>
@@ -7777,7 +7771,7 @@
         <v>382</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="L75" s="12" t="str">
         <f t="shared" ref="L75" si="14">_xlfn.TEXTJOIN("", TRUE, E75:K75)</f>
@@ -7789,7 +7783,7 @@
     </row>
     <row r="76" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B76" s="12">
         <v>28</v>
@@ -7806,7 +7800,7 @@
     </row>
     <row r="77" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B77" s="12">
         <v>29</v>
@@ -7823,7 +7817,7 @@
     </row>
     <row r="78" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B78" s="12">
         <v>30</v>
@@ -7838,7 +7832,7 @@
         <v>385</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="L78" s="12" t="str">
         <f t="shared" si="11"/>
@@ -7850,7 +7844,7 @@
     </row>
     <row r="79" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B79" s="12">
         <v>31</v>
@@ -7865,7 +7859,7 @@
         <v>385</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="L79" s="12" t="str">
         <f t="shared" ref="L79" si="15">_xlfn.TEXTJOIN("", TRUE, E79:K79)</f>
@@ -7877,7 +7871,7 @@
     </row>
     <row r="80" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="13" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B80" s="12">
         <v>32</v>
@@ -7894,7 +7888,7 @@
     </row>
     <row r="81" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="13" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B81" s="12">
         <v>1</v>
@@ -7911,7 +7905,7 @@
     </row>
     <row r="82" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="13" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B82" s="12">
         <v>2</v>
@@ -7926,7 +7920,7 @@
         <v>389</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="L82" s="12" t="str">
         <f t="shared" ref="L82:L83" si="16">_xlfn.TEXTJOIN("", TRUE, E82:K82)</f>
@@ -7938,7 +7932,7 @@
     </row>
     <row r="83" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="13" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B83" s="12">
         <v>3</v>
@@ -7953,7 +7947,7 @@
         <v>389</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="L83" s="12" t="str">
         <f t="shared" si="16"/>
@@ -7965,7 +7959,7 @@
     </row>
     <row r="84" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="13" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B84" s="12">
         <v>4</v>
@@ -7982,7 +7976,7 @@
     </row>
     <row r="85" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="13" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B85" s="12">
         <v>5</v>
@@ -8012,7 +8006,7 @@
     </row>
     <row r="86" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="13" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B86" s="12">
         <v>1</v>
@@ -8021,7 +8015,7 @@
         <v>17</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="N86" s="12" t="s">
         <v>92</v>
@@ -8029,7 +8023,7 @@
     </row>
     <row r="87" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="13" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B87" s="12">
         <v>2</v>
@@ -8689,7 +8683,7 @@
     </row>
     <row r="125" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" s="21" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B125" s="21">
         <v>1</v>
@@ -8698,7 +8692,7 @@
         <v>45</v>
       </c>
       <c r="D125" s="21" t="s">
-        <v>1266</v>
+        <v>581</v>
       </c>
       <c r="N125" s="21" t="s">
         <v>90</v>
@@ -8706,7 +8700,7 @@
     </row>
     <row r="126" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="21" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B126" s="21">
         <v>2</v>
@@ -8715,7 +8709,7 @@
         <v>45</v>
       </c>
       <c r="D126" s="21" t="s">
-        <v>1267</v>
+        <v>607</v>
       </c>
       <c r="N126" s="21" t="s">
         <v>90</v>
@@ -8723,7 +8717,7 @@
     </row>
     <row r="127" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="21" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B127" s="21">
         <v>3</v>
@@ -8732,10 +8726,10 @@
         <v>46</v>
       </c>
       <c r="D127" s="21" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M127" s="21" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N127" s="21" t="s">
         <v>90</v>
@@ -8743,7 +8737,7 @@
     </row>
     <row r="128" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="21" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B128" s="21">
         <v>4</v>
@@ -8752,7 +8746,7 @@
         <v>45</v>
       </c>
       <c r="D128" s="21" t="s">
-        <v>1268</v>
+        <v>587</v>
       </c>
       <c r="N128" s="21" t="s">
         <v>90</v>
@@ -8760,7 +8754,7 @@
     </row>
     <row r="130" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A130" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B130" s="21">
         <v>1</v>
@@ -8769,7 +8763,7 @@
         <v>45</v>
       </c>
       <c r="D130" s="21" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N130" s="21" t="s">
         <v>90</v>
@@ -8777,7 +8771,7 @@
     </row>
     <row r="131" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A131" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B131" s="21">
         <v>2</v>
@@ -8797,7 +8791,7 @@
     </row>
     <row r="132" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A132" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B132" s="21">
         <v>3</v>
@@ -8814,7 +8808,7 @@
     </row>
     <row r="133" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A133" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B133" s="21">
         <v>4</v>
@@ -8834,7 +8828,7 @@
     </row>
     <row r="134" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A134" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B134" s="21">
         <v>5</v>
@@ -8851,7 +8845,7 @@
     </row>
     <row r="135" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B135" s="21">
         <v>6</v>
@@ -8871,7 +8865,7 @@
     </row>
     <row r="136" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A136" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B136" s="21">
         <v>7</v>
@@ -8888,7 +8882,7 @@
     </row>
     <row r="137" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A137" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B137" s="21">
         <v>8</v>
@@ -8897,7 +8891,7 @@
         <v>45</v>
       </c>
       <c r="D137" s="21" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N137" s="21" t="s">
         <v>90</v>
@@ -8905,7 +8899,7 @@
     </row>
     <row r="139" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A139" s="5" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -8914,10 +8908,10 @@
         <v>47</v>
       </c>
       <c r="F139" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H139" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="I139" t="s">
         <v>116</v>
@@ -8932,7 +8926,7 @@
     </row>
     <row r="140" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A140" s="5" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B140">
         <v>2</v>
@@ -8941,7 +8935,7 @@
         <v>45</v>
       </c>
       <c r="D140" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="N140" t="s">
         <v>90</v>
@@ -8949,7 +8943,7 @@
     </row>
     <row r="141" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B141">
         <v>3</v>
@@ -8958,7 +8952,7 @@
         <v>47</v>
       </c>
       <c r="F141" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H141" t="s">
         <v>390</v>
@@ -8976,7 +8970,7 @@
     </row>
     <row r="142" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A142" s="5" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B142">
         <v>4</v>
@@ -8993,7 +8987,7 @@
     </row>
     <row r="143" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A143" s="5" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B143">
         <v>5</v>
@@ -9013,7 +9007,7 @@
     </row>
     <row r="144" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A144" s="5" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B144">
         <v>6</v>
@@ -9030,7 +9024,7 @@
     </row>
     <row r="145" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A145" s="5" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B145">
         <v>7</v>
@@ -9050,7 +9044,7 @@
     </row>
     <row r="146" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A146" s="5" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B146">
         <v>8</v>
@@ -9067,7 +9061,7 @@
     </row>
     <row r="147" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B147">
         <v>9</v>
@@ -9087,7 +9081,7 @@
     </row>
     <row r="148" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A148" s="5" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B148">
         <v>10</v>
@@ -9096,10 +9090,10 @@
         <v>47</v>
       </c>
       <c r="F148" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H148" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="I148" t="s">
         <v>116</v>
@@ -9114,7 +9108,7 @@
     </row>
     <row r="149" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A149" s="5" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B149">
         <v>11</v>
@@ -9123,7 +9117,7 @@
         <v>45</v>
       </c>
       <c r="D149" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="N149" t="s">
         <v>90</v>
@@ -9131,7 +9125,7 @@
     </row>
     <row r="150" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A150" s="5" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B150">
         <v>12</v>
@@ -9151,7 +9145,7 @@
     </row>
     <row r="151" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A151" s="5" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B151">
         <v>13</v>
@@ -9160,10 +9154,10 @@
         <v>47</v>
       </c>
       <c r="F151" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H151" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="I151" t="s">
         <v>116</v>
@@ -9178,7 +9172,7 @@
     </row>
     <row r="152" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A152" s="5" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B152">
         <v>14</v>
@@ -9187,7 +9181,7 @@
         <v>45</v>
       </c>
       <c r="D152" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="N152" t="s">
         <v>90</v>
@@ -9195,7 +9189,7 @@
     </row>
     <row r="153" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A153" s="5" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -9204,7 +9198,7 @@
         <v>17</v>
       </c>
       <c r="D153" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="N153" t="s">
         <v>92</v>
@@ -9212,7 +9206,7 @@
     </row>
     <row r="154" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A154" s="5" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B154">
         <v>2</v>
@@ -9221,10 +9215,10 @@
         <v>47</v>
       </c>
       <c r="F154" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H154" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="L154" t="str">
         <f t="shared" ref="L154:L156" si="32">_xlfn.TEXTJOIN("", TRUE, E154:K154)</f>
@@ -9236,7 +9230,7 @@
     </row>
     <row r="155" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A155" s="5" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B155">
         <v>3</v>
@@ -9245,10 +9239,10 @@
         <v>47</v>
       </c>
       <c r="F155" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H155" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="L155" t="str">
         <f t="shared" si="32"/>
@@ -9260,7 +9254,7 @@
     </row>
     <row r="156" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A156" s="5" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B156">
         <v>4</v>
@@ -9269,10 +9263,10 @@
         <v>47</v>
       </c>
       <c r="F156" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H156" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="L156" t="str">
         <f t="shared" si="32"/>
@@ -9284,7 +9278,7 @@
     </row>
     <row r="157" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A157" s="5" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B157">
         <v>5</v>
@@ -9293,7 +9287,7 @@
         <v>45</v>
       </c>
       <c r="D157" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="N157" t="s">
         <v>92</v>
@@ -9301,7 +9295,7 @@
     </row>
     <row r="158" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A158" s="5" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B158">
         <v>6</v>
@@ -9310,7 +9304,7 @@
         <v>17</v>
       </c>
       <c r="D158" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="N158" t="s">
         <v>93</v>
@@ -9318,7 +9312,7 @@
     </row>
     <row r="159" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A159" s="5" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B159">
         <v>7</v>
@@ -9327,10 +9321,10 @@
         <v>47</v>
       </c>
       <c r="F159" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H159" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="L159" t="str">
         <f t="shared" ref="L159:L163" si="33">_xlfn.TEXTJOIN("", TRUE, E159:K159)</f>
@@ -9342,7 +9336,7 @@
     </row>
     <row r="160" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A160" s="5" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B160">
         <v>8</v>
@@ -9351,10 +9345,10 @@
         <v>47</v>
       </c>
       <c r="F160" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H160" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="L160" t="str">
         <f t="shared" si="33"/>
@@ -9366,7 +9360,7 @@
     </row>
     <row r="161" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A161" s="5" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B161">
         <v>9</v>
@@ -9375,10 +9369,10 @@
         <v>47</v>
       </c>
       <c r="F161" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H161" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="L161" t="str">
         <f t="shared" si="33"/>
@@ -9390,7 +9384,7 @@
     </row>
     <row r="162" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A162" s="5" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B162">
         <v>10</v>
@@ -9399,10 +9393,10 @@
         <v>47</v>
       </c>
       <c r="F162" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H162" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="L162" t="str">
         <f t="shared" si="33"/>
@@ -9414,7 +9408,7 @@
     </row>
     <row r="163" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A163" s="5" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B163">
         <v>11</v>
@@ -9423,10 +9417,10 @@
         <v>47</v>
       </c>
       <c r="F163" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H163" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="L163" t="str">
         <f t="shared" si="33"/>
@@ -9468,7 +9462,7 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -9477,7 +9471,7 @@
         <v>45</v>
       </c>
       <c r="D175" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="N175" t="s">
         <v>90</v>
@@ -9485,7 +9479,7 @@
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B176" s="27">
         <v>2</v>
@@ -9494,7 +9488,7 @@
         <v>45</v>
       </c>
       <c r="D176" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="N176" t="s">
         <v>90</v>
@@ -9502,7 +9496,7 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B177">
         <v>3</v>
@@ -9532,7 +9526,7 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B178" s="27">
         <v>4</v>
@@ -9562,7 +9556,7 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B179">
         <v>5</v>
@@ -9571,7 +9565,7 @@
         <v>45</v>
       </c>
       <c r="D179" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="N179" t="s">
         <v>90</v>
@@ -9579,7 +9573,7 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B180" s="27">
         <v>6</v>
@@ -9602,7 +9596,7 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -9611,7 +9605,7 @@
         <v>45</v>
       </c>
       <c r="D182" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="N182" t="s">
         <v>90</v>
@@ -9619,7 +9613,7 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B183" s="27">
         <v>2</v>
@@ -9628,7 +9622,7 @@
         <v>45</v>
       </c>
       <c r="D183" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="N183" t="s">
         <v>90</v>
@@ -9636,7 +9630,7 @@
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B184">
         <v>3</v>
@@ -9666,7 +9660,7 @@
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B185" s="27">
         <v>4</v>
@@ -9696,7 +9690,7 @@
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B186">
         <v>5</v>
@@ -9705,7 +9699,7 @@
         <v>45</v>
       </c>
       <c r="D186" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="N186" t="s">
         <v>90</v>
@@ -9713,7 +9707,7 @@
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B187" s="27">
         <v>6</v>
@@ -12150,7 +12144,7 @@
         <v>39</v>
       </c>
       <c r="K128" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
@@ -13723,7 +13717,7 @@
         <v>39</v>
       </c>
       <c r="K238" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.2">
@@ -13778,7 +13772,7 @@
         <v>39</v>
       </c>
       <c r="K241" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.2">
@@ -13798,7 +13792,7 @@
         <v>512</v>
       </c>
       <c r="G242" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H242" t="s">
         <v>116</v>
@@ -13825,7 +13819,7 @@
         <v>512</v>
       </c>
       <c r="G243" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H243" t="s">
         <v>116</v>
@@ -13852,7 +13846,7 @@
         <v>512</v>
       </c>
       <c r="G244" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H244" t="s">
         <v>116</v>
@@ -13873,7 +13867,7 @@
         <v>27</v>
       </c>
       <c r="K245" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.2">
@@ -13887,7 +13881,7 @@
         <v>39</v>
       </c>
       <c r="K246" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.2">
@@ -13907,7 +13901,7 @@
         <v>512</v>
       </c>
       <c r="G247" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H247" t="s">
         <v>116</v>
@@ -13934,7 +13928,7 @@
         <v>512</v>
       </c>
       <c r="G248" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H248" t="s">
         <v>116</v>
@@ -13955,7 +13949,7 @@
         <v>27</v>
       </c>
       <c r="K249" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.2">
@@ -13989,7 +13983,7 @@
         <v>512</v>
       </c>
       <c r="G251" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H251" t="s">
         <v>116</v>
@@ -14016,7 +14010,7 @@
         <v>512</v>
       </c>
       <c r="G252" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H252" t="s">
         <v>116</v>
@@ -14233,10 +14227,10 @@
         <v>507</v>
       </c>
       <c r="F266" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G266" t="s">
         <v>1163</v>
-      </c>
-      <c r="G266" t="s">
-        <v>1162</v>
       </c>
       <c r="H266" t="s">
         <v>116</v>
@@ -14271,7 +14265,7 @@
         <v>39</v>
       </c>
       <c r="K268" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.2">
@@ -14288,10 +14282,10 @@
         <v>507</v>
       </c>
       <c r="F269" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="G269" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H269" t="s">
         <v>116</v>
@@ -14315,10 +14309,10 @@
         <v>507</v>
       </c>
       <c r="F270" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="G270" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H270" t="s">
         <v>116</v>
@@ -14339,7 +14333,7 @@
         <v>27</v>
       </c>
       <c r="K271" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.2">
@@ -15010,7 +15004,7 @@
         <v>39</v>
       </c>
       <c r="K311" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.2">
@@ -15030,7 +15024,7 @@
         <v>556</v>
       </c>
       <c r="G312" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H312" t="s">
         <v>116</v>
@@ -15051,7 +15045,7 @@
         <v>27</v>
       </c>
       <c r="K313" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.2">
@@ -15120,7 +15114,7 @@
         <v>39</v>
       </c>
       <c r="K317" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.2">
@@ -15166,7 +15160,7 @@
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B321" s="27">
         <v>1</v>
@@ -15175,12 +15169,12 @@
         <v>39</v>
       </c>
       <c r="K321" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B322" s="27">
         <v>1</v>
@@ -15189,12 +15183,12 @@
         <v>27</v>
       </c>
       <c r="K322" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B323" s="27">
         <v>1</v>
@@ -15203,12 +15197,12 @@
         <v>40</v>
       </c>
       <c r="K323" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B324" s="27">
         <v>1</v>
@@ -15217,12 +15211,12 @@
         <v>41</v>
       </c>
       <c r="K324" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B325" s="27">
         <v>2</v>
@@ -15231,12 +15225,12 @@
         <v>39</v>
       </c>
       <c r="K325" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B326" s="27">
         <v>2</v>
@@ -15245,12 +15239,12 @@
         <v>27</v>
       </c>
       <c r="K326" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B327" s="27">
         <v>2</v>
@@ -15259,12 +15253,12 @@
         <v>40</v>
       </c>
       <c r="K327" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B328" s="27">
         <v>2</v>
@@ -15273,12 +15267,12 @@
         <v>41</v>
       </c>
       <c r="K328" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B329" s="27">
         <v>3</v>
@@ -15287,12 +15281,12 @@
         <v>39</v>
       </c>
       <c r="K329" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B330" s="27">
         <v>3</v>
@@ -15301,12 +15295,12 @@
         <v>27</v>
       </c>
       <c r="K330" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B331" s="27">
         <v>3</v>
@@ -15315,12 +15309,12 @@
         <v>40</v>
       </c>
       <c r="K331" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B332" s="27">
         <v>3</v>
@@ -15641,12 +15635,12 @@
         <v>111</v>
       </c>
       <c r="K352" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B354" s="27">
         <v>1</v>
@@ -15660,7 +15654,7 @@
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B355" s="27">
         <v>1</v>
@@ -15687,7 +15681,7 @@
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B356" s="27">
         <v>1</v>
@@ -15851,7 +15845,7 @@
         <v>39</v>
       </c>
       <c r="K370" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.2">
@@ -15865,10 +15859,10 @@
         <v>108</v>
       </c>
       <c r="E371" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G371" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H371" t="s">
         <v>116</v>
@@ -15889,10 +15883,10 @@
         <v>108</v>
       </c>
       <c r="E372" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G372" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H372" t="s">
         <v>116</v>
@@ -15913,10 +15907,10 @@
         <v>108</v>
       </c>
       <c r="E373" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G373" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H373" t="s">
         <v>116</v>
@@ -15937,10 +15931,10 @@
         <v>108</v>
       </c>
       <c r="E374" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G374" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H374" t="s">
         <v>116</v>
@@ -15964,10 +15958,10 @@
         <v>108</v>
       </c>
       <c r="E375" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G375" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H375" t="s">
         <v>116</v>
@@ -15991,10 +15985,10 @@
         <v>108</v>
       </c>
       <c r="E376" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G376" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H376" t="s">
         <v>116</v>
@@ -16018,10 +16012,10 @@
         <v>108</v>
       </c>
       <c r="E377" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G377" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H377" t="s">
         <v>116</v>
@@ -16090,7 +16084,7 @@
         <v>39</v>
       </c>
       <c r="K384" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.2">
@@ -16104,10 +16098,10 @@
         <v>108</v>
       </c>
       <c r="E385" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G385" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H385" t="s">
         <v>116</v>
@@ -16128,10 +16122,10 @@
         <v>108</v>
       </c>
       <c r="E386" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G386" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H386" t="s">
         <v>116</v>
@@ -16152,10 +16146,10 @@
         <v>108</v>
       </c>
       <c r="E387" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G387" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H387" t="s">
         <v>116</v>
@@ -16176,10 +16170,10 @@
         <v>108</v>
       </c>
       <c r="E388" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G388" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H388" t="s">
         <v>116</v>
@@ -16200,10 +16194,10 @@
         <v>108</v>
       </c>
       <c r="E389" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G389" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H389" t="s">
         <v>116</v>
@@ -16224,10 +16218,10 @@
         <v>108</v>
       </c>
       <c r="E390" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G390" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H390" t="s">
         <v>116</v>
@@ -16293,7 +16287,7 @@
         <v>39</v>
       </c>
       <c r="K396" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.2">
@@ -16307,10 +16301,10 @@
         <v>108</v>
       </c>
       <c r="E397" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G397" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H397" t="s">
         <v>116</v>
@@ -16331,10 +16325,10 @@
         <v>108</v>
       </c>
       <c r="E398" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G398" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H398" t="s">
         <v>116</v>
@@ -16355,10 +16349,10 @@
         <v>108</v>
       </c>
       <c r="E399" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G399" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H399" t="s">
         <v>116</v>
@@ -16379,10 +16373,10 @@
         <v>108</v>
       </c>
       <c r="E400" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G400" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H400" t="s">
         <v>116</v>
@@ -16403,10 +16397,10 @@
         <v>108</v>
       </c>
       <c r="E401" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G401" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H401" t="s">
         <v>116</v>
@@ -16430,13 +16424,13 @@
         <v>109</v>
       </c>
       <c r="E402" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F402" t="s">
         <v>114</v>
       </c>
       <c r="G402" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H402" t="s">
         <v>116</v>
@@ -16471,12 +16465,12 @@
         <v>111</v>
       </c>
       <c r="K404" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B406" s="27">
         <v>1</v>
@@ -16485,12 +16479,12 @@
         <v>39</v>
       </c>
       <c r="K406" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B407" s="27">
         <v>1</v>
@@ -16499,13 +16493,13 @@
         <v>108</v>
       </c>
       <c r="E407" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F407" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G407" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H407" t="s">
         <v>116</v>
@@ -16517,7 +16511,7 @@
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B408" s="27">
         <v>1</v>
@@ -16526,13 +16520,13 @@
         <v>108</v>
       </c>
       <c r="E408" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F408" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G408" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H408" t="s">
         <v>116</v>
@@ -16544,7 +16538,7 @@
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B409" s="27">
         <v>1</v>
@@ -16553,13 +16547,13 @@
         <v>108</v>
       </c>
       <c r="E409" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F409" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G409" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H409" t="s">
         <v>116</v>
@@ -16574,7 +16568,7 @@
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B410" s="27">
         <v>1</v>
@@ -16583,13 +16577,13 @@
         <v>108</v>
       </c>
       <c r="E410" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F410" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G410" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H410" t="s">
         <v>116</v>
@@ -16604,7 +16598,7 @@
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B411" s="27">
         <v>1</v>
@@ -16613,12 +16607,12 @@
         <v>27</v>
       </c>
       <c r="K411" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B413" s="27">
         <v>2</v>
@@ -16627,12 +16621,12 @@
         <v>39</v>
       </c>
       <c r="K413" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B414" s="27">
         <v>2</v>
@@ -16641,13 +16635,13 @@
         <v>108</v>
       </c>
       <c r="E414" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F414" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G414" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H414" t="s">
         <v>116</v>
@@ -16659,7 +16653,7 @@
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B415" s="27">
         <v>2</v>
@@ -16668,12 +16662,12 @@
         <v>27</v>
       </c>
       <c r="K415" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B417" s="27">
         <v>3</v>
@@ -16682,12 +16676,12 @@
         <v>39</v>
       </c>
       <c r="K417" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B418" s="27">
         <v>3</v>
@@ -16696,13 +16690,13 @@
         <v>108</v>
       </c>
       <c r="E418" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F418" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G418" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H418" t="s">
         <v>116</v>
@@ -16714,7 +16708,7 @@
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B419" s="27">
         <v>3</v>
@@ -16723,13 +16717,13 @@
         <v>108</v>
       </c>
       <c r="E419" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F419" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G419" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H419" t="s">
         <v>116</v>
@@ -16741,7 +16735,7 @@
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B420" s="27">
         <v>3</v>
@@ -16750,13 +16744,13 @@
         <v>108</v>
       </c>
       <c r="E420" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F420" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G420" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H420" t="s">
         <v>116</v>
@@ -16768,7 +16762,7 @@
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B421" s="27">
         <v>3</v>
@@ -16777,13 +16771,13 @@
         <v>108</v>
       </c>
       <c r="E421" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F421" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G421" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H421" t="s">
         <v>116</v>
@@ -16798,7 +16792,7 @@
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B422" s="27">
         <v>3</v>
@@ -16807,12 +16801,12 @@
         <v>27</v>
       </c>
       <c r="K422" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B424" s="27">
         <v>4</v>
@@ -16821,12 +16815,12 @@
         <v>39</v>
       </c>
       <c r="K424" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B425" s="27">
         <v>4</v>
@@ -16835,13 +16829,13 @@
         <v>108</v>
       </c>
       <c r="E425" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F425" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G425" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H425" t="s">
         <v>116</v>
@@ -16856,7 +16850,7 @@
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B426" s="27">
         <v>4</v>
@@ -16865,13 +16859,13 @@
         <v>108</v>
       </c>
       <c r="E426" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F426" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G426" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H426" t="s">
         <v>116</v>
@@ -16886,7 +16880,7 @@
     </row>
     <row r="427" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B427" s="27">
         <v>4</v>
@@ -16895,13 +16889,13 @@
         <v>108</v>
       </c>
       <c r="E427" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F427" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G427" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H427" t="s">
         <v>116</v>
@@ -16916,7 +16910,7 @@
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B428" s="27">
         <v>4</v>
@@ -16925,13 +16919,13 @@
         <v>108</v>
       </c>
       <c r="E428" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F428" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G428" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H428" t="s">
         <v>116</v>
@@ -16946,7 +16940,7 @@
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B429" s="27">
         <v>4</v>
@@ -16955,13 +16949,13 @@
         <v>108</v>
       </c>
       <c r="E429" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F429" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G429" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H429" t="s">
         <v>116</v>
@@ -16976,7 +16970,7 @@
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B430" s="27">
         <v>4</v>
@@ -16985,19 +16979,19 @@
         <v>108</v>
       </c>
       <c r="E430" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F430" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G430" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H430" t="s">
         <v>116</v>
       </c>
       <c r="J430" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K430" t="str">
         <f t="shared" si="86"/>
@@ -17006,7 +17000,7 @@
     </row>
     <row r="431" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B431" s="27">
         <v>4</v>
@@ -17015,13 +17009,13 @@
         <v>108</v>
       </c>
       <c r="E431" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F431" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G431" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H431" t="s">
         <v>116</v>
@@ -17036,7 +17030,7 @@
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B432" s="27">
         <v>4</v>
@@ -17045,13 +17039,13 @@
         <v>108</v>
       </c>
       <c r="E432" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F432" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G432" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H432" t="s">
         <v>116</v>
@@ -17066,7 +17060,7 @@
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B433" s="27">
         <v>4</v>
@@ -17075,13 +17069,13 @@
         <v>108</v>
       </c>
       <c r="E433" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F433" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G433" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H433" t="s">
         <v>116</v>
@@ -17096,7 +17090,7 @@
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B434" s="27">
         <v>4</v>
@@ -17105,7 +17099,7 @@
         <v>27</v>
       </c>
       <c r="K434" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="440" spans="1:11" x14ac:dyDescent="0.2">
@@ -17119,7 +17113,7 @@
         <v>39</v>
       </c>
       <c r="K440" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.2">
@@ -17133,10 +17127,10 @@
         <v>108</v>
       </c>
       <c r="E441" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G441" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H441" t="s">
         <v>116</v>
@@ -17157,10 +17151,10 @@
         <v>108</v>
       </c>
       <c r="E442" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G442" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H442" t="s">
         <v>116</v>
@@ -17181,10 +17175,10 @@
         <v>108</v>
       </c>
       <c r="E443" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G443" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H443" t="s">
         <v>116</v>
@@ -17205,10 +17199,10 @@
         <v>108</v>
       </c>
       <c r="E444" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G444" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H444" t="s">
         <v>116</v>
@@ -17232,10 +17226,10 @@
         <v>108</v>
       </c>
       <c r="E445" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G445" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H445" t="s">
         <v>116</v>
@@ -17259,10 +17253,10 @@
         <v>108</v>
       </c>
       <c r="E446" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G446" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H446" t="s">
         <v>116</v>
@@ -17286,16 +17280,16 @@
         <v>108</v>
       </c>
       <c r="E447" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G447" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H447" t="s">
         <v>116</v>
       </c>
       <c r="J447" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K447" t="str">
         <f t="shared" si="87"/>
@@ -17338,12 +17332,12 @@
         <v>111</v>
       </c>
       <c r="K450" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B452" s="27">
         <v>1</v>
@@ -17352,12 +17346,12 @@
         <v>39</v>
       </c>
       <c r="K452" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B453" s="27">
         <v>1</v>
@@ -17366,13 +17360,13 @@
         <v>108</v>
       </c>
       <c r="E453" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F453" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G453" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H453" t="s">
         <v>116</v>
@@ -17384,7 +17378,7 @@
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B454" s="27">
         <v>1</v>
@@ -17393,13 +17387,13 @@
         <v>108</v>
       </c>
       <c r="E454" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F454" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G454" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H454" t="s">
         <v>116</v>
@@ -17411,7 +17405,7 @@
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B455" s="27">
         <v>1</v>
@@ -17420,7 +17414,7 @@
         <v>27</v>
       </c>
       <c r="K455" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.2">
@@ -17434,7 +17428,7 @@
         <v>39</v>
       </c>
       <c r="K458" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.2">
@@ -17448,10 +17442,10 @@
         <v>108</v>
       </c>
       <c r="E459" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G459" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H459" t="s">
         <v>116</v>
@@ -17472,10 +17466,10 @@
         <v>108</v>
       </c>
       <c r="E460" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G460" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H460" t="s">
         <v>116</v>
@@ -17496,16 +17490,16 @@
         <v>108</v>
       </c>
       <c r="E461" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G461" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H461" t="s">
         <v>116</v>
       </c>
       <c r="J461" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K461" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D461:J461)</f>
@@ -17523,10 +17517,10 @@
         <v>108</v>
       </c>
       <c r="E462" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G462" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H462" t="s">
         <v>116</v>
@@ -17550,10 +17544,10 @@
         <v>108</v>
       </c>
       <c r="E463" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G463" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H463" t="s">
         <v>116</v>
@@ -17602,12 +17596,12 @@
         <v>111</v>
       </c>
       <c r="K466" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B468" s="27">
         <v>1</v>
@@ -17616,12 +17610,12 @@
         <v>39</v>
       </c>
       <c r="K468" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B469" s="27">
         <v>1</v>
@@ -17630,13 +17624,13 @@
         <v>108</v>
       </c>
       <c r="E469" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F469" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="G469" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H469" t="s">
         <v>116</v>
@@ -17648,7 +17642,7 @@
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B470" s="27">
         <v>1</v>
@@ -17657,12 +17651,12 @@
         <v>27</v>
       </c>
       <c r="K470" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B472" s="27">
         <v>2</v>
@@ -17671,12 +17665,12 @@
         <v>39</v>
       </c>
       <c r="K472" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B473" s="27">
         <v>2</v>
@@ -17685,13 +17679,13 @@
         <v>108</v>
       </c>
       <c r="E473" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F473" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G473" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H473" t="s">
         <v>116</v>
@@ -17703,7 +17697,7 @@
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B474" s="27">
         <v>2</v>
@@ -17712,12 +17706,12 @@
         <v>27</v>
       </c>
       <c r="K474" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B476" s="27">
         <v>3</v>
@@ -17726,12 +17720,12 @@
         <v>39</v>
       </c>
       <c r="K476" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B477" s="27">
         <v>3</v>
@@ -17740,13 +17734,13 @@
         <v>108</v>
       </c>
       <c r="E477" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F477" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G477" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H477" t="s">
         <v>116</v>
@@ -17758,7 +17752,7 @@
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B478" s="27">
         <v>3</v>
@@ -17767,12 +17761,12 @@
         <v>27</v>
       </c>
       <c r="K478" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B480" s="27">
         <v>4</v>
@@ -17781,12 +17775,12 @@
         <v>39</v>
       </c>
       <c r="K480" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B481" s="27">
         <v>4</v>
@@ -17795,13 +17789,13 @@
         <v>108</v>
       </c>
       <c r="E481" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F481" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="G481" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H481" t="s">
         <v>116</v>
@@ -17813,7 +17807,7 @@
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B482" s="27">
         <v>4</v>
@@ -17822,12 +17816,12 @@
         <v>27</v>
       </c>
       <c r="K482" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B484" s="27">
         <v>5</v>
@@ -17836,12 +17830,12 @@
         <v>39</v>
       </c>
       <c r="K484" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B485" s="27">
         <v>5</v>
@@ -17850,19 +17844,19 @@
         <v>108</v>
       </c>
       <c r="E485" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F485" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G485" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H485" t="s">
         <v>116</v>
       </c>
       <c r="J485" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K485" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D485:J485)</f>
@@ -17871,7 +17865,7 @@
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B486" s="27">
         <v>5</v>
@@ -17880,12 +17874,12 @@
         <v>27</v>
       </c>
       <c r="K486" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B488" s="27">
         <v>6</v>
@@ -17894,12 +17888,12 @@
         <v>39</v>
       </c>
       <c r="K488" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="489" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B489" s="27">
         <v>6</v>
@@ -17908,19 +17902,19 @@
         <v>108</v>
       </c>
       <c r="E489" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F489" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G489" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H489" t="s">
         <v>116</v>
       </c>
       <c r="J489" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K489" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D489:J489)</f>
@@ -17929,7 +17923,7 @@
     </row>
     <row r="490" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B490" s="27">
         <v>6</v>
@@ -17938,12 +17932,12 @@
         <v>27</v>
       </c>
       <c r="K490" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="492" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B492" s="27">
         <v>7</v>
@@ -17952,12 +17946,12 @@
         <v>39</v>
       </c>
       <c r="K492" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="493" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B493" s="27">
         <v>7</v>
@@ -17966,19 +17960,19 @@
         <v>108</v>
       </c>
       <c r="E493" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F493" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G493" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H493" t="s">
         <v>116</v>
       </c>
       <c r="J493" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K493" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D493:J493)</f>
@@ -17987,7 +17981,7 @@
     </row>
     <row r="494" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B494" s="27">
         <v>7</v>
@@ -17996,12 +17990,12 @@
         <v>27</v>
       </c>
       <c r="K494" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="496" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B496" s="27">
         <v>8</v>
@@ -18010,12 +18004,12 @@
         <v>39</v>
       </c>
       <c r="K496" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="497" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B497" s="27">
         <v>8</v>
@@ -18024,13 +18018,13 @@
         <v>108</v>
       </c>
       <c r="E497" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F497" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="G497" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H497" t="s">
         <v>116</v>
@@ -18042,7 +18036,7 @@
     </row>
     <row r="498" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B498" s="27">
         <v>8</v>
@@ -18051,7 +18045,7 @@
         <v>27</v>
       </c>
       <c r="K498" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="502" spans="1:11" x14ac:dyDescent="0.2">
@@ -18065,7 +18059,7 @@
         <v>39</v>
       </c>
       <c r="K502" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="503" spans="1:11" x14ac:dyDescent="0.2">
@@ -18079,10 +18073,10 @@
         <v>108</v>
       </c>
       <c r="E503" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G503" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H503" t="s">
         <v>116</v>
@@ -18103,10 +18097,10 @@
         <v>108</v>
       </c>
       <c r="E504" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G504" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H504" t="s">
         <v>116</v>
@@ -18127,10 +18121,10 @@
         <v>108</v>
       </c>
       <c r="E505" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G505" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H505" t="s">
         <v>116</v>
@@ -18151,10 +18145,10 @@
         <v>108</v>
       </c>
       <c r="E506" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G506" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H506" t="s">
         <v>116</v>
@@ -18231,10 +18225,10 @@
         <v>108</v>
       </c>
       <c r="E513" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G513" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H513" t="s">
         <v>116</v>
@@ -18255,10 +18249,10 @@
         <v>108</v>
       </c>
       <c r="E514" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G514" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H514" t="s">
         <v>116</v>
@@ -18279,10 +18273,10 @@
         <v>108</v>
       </c>
       <c r="E515" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G515" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H515" t="s">
         <v>116</v>
@@ -18303,10 +18297,10 @@
         <v>108</v>
       </c>
       <c r="E516" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G516" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H516" t="s">
         <v>116</v>
@@ -18330,10 +18324,10 @@
         <v>108</v>
       </c>
       <c r="E517" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G517" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H517" t="s">
         <v>116</v>
@@ -18357,10 +18351,10 @@
         <v>108</v>
       </c>
       <c r="E518" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G518" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H518" t="s">
         <v>116</v>
@@ -18384,10 +18378,10 @@
         <v>108</v>
       </c>
       <c r="E519" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G519" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H519" t="s">
         <v>116</v>
@@ -18411,10 +18405,10 @@
         <v>108</v>
       </c>
       <c r="E520" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G520" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H520" t="s">
         <v>116</v>
@@ -18438,10 +18432,10 @@
         <v>108</v>
       </c>
       <c r="E521" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G521" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H521" t="s">
         <v>116</v>
@@ -18465,10 +18459,10 @@
         <v>108</v>
       </c>
       <c r="E522" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G522" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H522" t="s">
         <v>116</v>
@@ -18492,13 +18486,13 @@
         <v>109</v>
       </c>
       <c r="E523" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F523" t="s">
         <v>114</v>
       </c>
       <c r="G523" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H523" t="s">
         <v>116</v>
@@ -18533,12 +18527,12 @@
         <v>111</v>
       </c>
       <c r="K525" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="527" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B527" s="27">
         <v>1</v>
@@ -18547,12 +18541,12 @@
         <v>39</v>
       </c>
       <c r="K527" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="528" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B528" s="27">
         <v>1</v>
@@ -18561,13 +18555,13 @@
         <v>108</v>
       </c>
       <c r="E528" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F528" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="G528" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H528" t="s">
         <v>116</v>
@@ -18579,7 +18573,7 @@
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B529" s="27">
         <v>1</v>
@@ -18588,13 +18582,13 @@
         <v>108</v>
       </c>
       <c r="E529" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F529" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="G529" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H529" t="s">
         <v>116</v>
@@ -18606,7 +18600,7 @@
     </row>
     <row r="530" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B530" s="27">
         <v>1</v>
@@ -18615,13 +18609,13 @@
         <v>108</v>
       </c>
       <c r="E530" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F530" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="G530" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H530" t="s">
         <v>116</v>
@@ -18633,7 +18627,7 @@
     </row>
     <row r="531" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B531" s="27">
         <v>1</v>
@@ -18642,13 +18636,13 @@
         <v>108</v>
       </c>
       <c r="E531" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F531" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="G531" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H531" t="s">
         <v>116</v>
@@ -18663,7 +18657,7 @@
     </row>
     <row r="532" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B532" s="27">
         <v>1</v>
@@ -18672,13 +18666,13 @@
         <v>108</v>
       </c>
       <c r="E532" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F532" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="G532" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H532" t="s">
         <v>116</v>
@@ -18693,7 +18687,7 @@
     </row>
     <row r="533" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B533" s="27">
         <v>1</v>
@@ -18702,12 +18696,12 @@
         <v>27</v>
       </c>
       <c r="K533" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="535" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B535" s="27">
         <v>2</v>
@@ -18716,12 +18710,12 @@
         <v>39</v>
       </c>
       <c r="K535" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="536" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B536" s="27">
         <v>2</v>
@@ -18730,13 +18724,13 @@
         <v>108</v>
       </c>
       <c r="E536" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F536" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G536" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H536" t="s">
         <v>116</v>
@@ -18748,7 +18742,7 @@
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B537" s="27">
         <v>2</v>
@@ -18757,13 +18751,13 @@
         <v>108</v>
       </c>
       <c r="E537" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F537" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G537" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="K537" t="str">
         <f t="shared" si="89"/>
@@ -18772,7 +18766,7 @@
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B538" s="27">
         <v>2</v>
@@ -18781,13 +18775,13 @@
         <v>108</v>
       </c>
       <c r="E538" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F538" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G538" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="K538" t="str">
         <f t="shared" si="89"/>
@@ -18796,7 +18790,7 @@
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B539" s="27">
         <v>2</v>
@@ -18805,13 +18799,13 @@
         <v>108</v>
       </c>
       <c r="E539" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F539" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G539" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="K539" t="str">
         <f t="shared" si="89"/>
@@ -18820,7 +18814,7 @@
     </row>
     <row r="540" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B540" s="27">
         <v>2</v>
@@ -18829,13 +18823,13 @@
         <v>108</v>
       </c>
       <c r="E540" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F540" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G540" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="K540" t="str">
         <f t="shared" si="89"/>
@@ -18844,7 +18838,7 @@
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B541" s="27">
         <v>2</v>
@@ -18853,13 +18847,13 @@
         <v>108</v>
       </c>
       <c r="E541" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F541" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G541" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="K541" t="str">
         <f t="shared" si="89"/>
@@ -18868,7 +18862,7 @@
     </row>
     <row r="542" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B542" s="27">
         <v>2</v>
@@ -18877,13 +18871,13 @@
         <v>108</v>
       </c>
       <c r="E542" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F542" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G542" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="K542" t="str">
         <f t="shared" si="89"/>
@@ -18892,7 +18886,7 @@
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B543" s="27">
         <v>2</v>
@@ -18901,13 +18895,13 @@
         <v>108</v>
       </c>
       <c r="E543" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F543" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G543" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="K543" t="str">
         <f t="shared" si="89"/>
@@ -18916,7 +18910,7 @@
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B544" s="27">
         <v>2</v>
@@ -18925,16 +18919,16 @@
         <v>108</v>
       </c>
       <c r="E544" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F544" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G544" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="J544" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="K544" t="str">
         <f t="shared" si="89"/>
@@ -18943,7 +18937,7 @@
     </row>
     <row r="545" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B545" s="27">
         <v>2</v>
@@ -18952,12 +18946,12 @@
         <v>27</v>
       </c>
       <c r="K545" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="547" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B547" s="27">
         <v>3</v>
@@ -18966,12 +18960,12 @@
         <v>39</v>
       </c>
       <c r="K547" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="548" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B548" s="27">
         <v>3</v>
@@ -18980,13 +18974,13 @@
         <v>108</v>
       </c>
       <c r="E548" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F548" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="G548" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="K548" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D548:J548)</f>
@@ -18995,7 +18989,7 @@
     </row>
     <row r="549" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B549" s="27">
         <v>3</v>
@@ -19004,12 +18998,12 @@
         <v>27</v>
       </c>
       <c r="K549" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="551" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B551" s="27">
         <v>4</v>
@@ -19018,12 +19012,12 @@
         <v>39</v>
       </c>
       <c r="K551" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="552" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B552" s="27">
         <v>4</v>
@@ -19032,13 +19026,13 @@
         <v>108</v>
       </c>
       <c r="E552" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F552" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="G552" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H552" t="s">
         <v>116</v>
@@ -19050,7 +19044,7 @@
     </row>
     <row r="553" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B553" s="27">
         <v>4</v>
@@ -19059,12 +19053,12 @@
         <v>27</v>
       </c>
       <c r="K553" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="555" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B555" s="27">
         <v>5</v>
@@ -19073,12 +19067,12 @@
         <v>39</v>
       </c>
       <c r="K555" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="556" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B556" s="27">
         <v>5</v>
@@ -19087,13 +19081,13 @@
         <v>108</v>
       </c>
       <c r="E556" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F556" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G556" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="K556" t="str">
         <f t="shared" ref="K556:K562" si="90">_xlfn.TEXTJOIN("", TRUE, D556:J556)</f>
@@ -19102,7 +19096,7 @@
     </row>
     <row r="557" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B557" s="27">
         <v>5</v>
@@ -19111,13 +19105,13 @@
         <v>108</v>
       </c>
       <c r="E557" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F557" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G557" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="K557" t="str">
         <f t="shared" si="90"/>
@@ -19126,7 +19120,7 @@
     </row>
     <row r="558" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B558" s="27">
         <v>5</v>
@@ -19135,13 +19129,13 @@
         <v>108</v>
       </c>
       <c r="E558" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F558" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G558" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="J558" t="s">
         <v>201</v>
@@ -19153,7 +19147,7 @@
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B559" s="27">
         <v>5</v>
@@ -19162,13 +19156,13 @@
         <v>108</v>
       </c>
       <c r="E559" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F559" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G559" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="J559" t="s">
         <v>201</v>
@@ -19180,7 +19174,7 @@
     </row>
     <row r="560" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B560" s="27">
         <v>5</v>
@@ -19189,16 +19183,16 @@
         <v>108</v>
       </c>
       <c r="E560" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F560" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G560" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="J560" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="K560" t="str">
         <f t="shared" si="90"/>
@@ -19207,7 +19201,7 @@
     </row>
     <row r="561" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B561" s="27">
         <v>5</v>
@@ -19216,13 +19210,13 @@
         <v>108</v>
       </c>
       <c r="E561" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F561" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G561" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="J561" t="s">
         <v>236</v>
@@ -19234,7 +19228,7 @@
     </row>
     <row r="562" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B562" s="27">
         <v>5</v>
@@ -19243,16 +19237,16 @@
         <v>108</v>
       </c>
       <c r="E562" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F562" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G562" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="J562" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K562" t="str">
         <f t="shared" si="90"/>
@@ -19261,7 +19255,7 @@
     </row>
     <row r="563" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B563" s="27">
         <v>5</v>
@@ -19270,12 +19264,12 @@
         <v>27</v>
       </c>
       <c r="K563" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="565" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B565" s="27">
         <v>6</v>
@@ -19284,12 +19278,12 @@
         <v>39</v>
       </c>
       <c r="K565" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="566" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B566" s="27">
         <v>6</v>
@@ -19298,13 +19292,13 @@
         <v>108</v>
       </c>
       <c r="E566" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F566" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G566" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="K566" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D566:J566)</f>
@@ -19313,7 +19307,7 @@
     </row>
     <row r="567" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B567" s="27">
         <v>6</v>
@@ -19322,13 +19316,13 @@
         <v>108</v>
       </c>
       <c r="E567" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F567" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G567" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="K567" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D567:J567)</f>
@@ -19337,7 +19331,7 @@
     </row>
     <row r="568" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B568" s="27">
         <v>6</v>
@@ -19346,12 +19340,12 @@
         <v>27</v>
       </c>
       <c r="K568" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="570" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B570" s="27">
         <v>7</v>
@@ -19360,12 +19354,12 @@
         <v>39</v>
       </c>
       <c r="K570" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="571" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B571" s="27">
         <v>7</v>
@@ -19374,13 +19368,13 @@
         <v>108</v>
       </c>
       <c r="E571" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F571" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G571" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H571" t="s">
         <v>116</v>
@@ -19392,7 +19386,7 @@
     </row>
     <row r="572" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B572" s="27">
         <v>7</v>
@@ -19401,7 +19395,7 @@
         <v>27</v>
       </c>
       <c r="K572" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="579" spans="1:11" x14ac:dyDescent="0.2">
@@ -19415,7 +19409,7 @@
         <v>39</v>
       </c>
       <c r="K579" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="580" spans="1:11" x14ac:dyDescent="0.2">
@@ -19429,10 +19423,10 @@
         <v>108</v>
       </c>
       <c r="E580" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G580" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K580" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D580:J580)</f>
@@ -19450,10 +19444,10 @@
         <v>108</v>
       </c>
       <c r="E581" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G581" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="J581" t="s">
         <v>201</v>
@@ -19474,10 +19468,10 @@
         <v>108</v>
       </c>
       <c r="E582" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G582" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="J582" t="s">
         <v>237</v>
@@ -19534,7 +19528,7 @@
         <v>39</v>
       </c>
       <c r="K588" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="589" spans="1:11" x14ac:dyDescent="0.2">
@@ -19548,10 +19542,10 @@
         <v>108</v>
       </c>
       <c r="E589" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="G589" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="K589" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D589:J589)</f>
@@ -19569,10 +19563,10 @@
         <v>108</v>
       </c>
       <c r="E590" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="G590" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="K590" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D590:J590)</f>
@@ -19590,10 +19584,10 @@
         <v>108</v>
       </c>
       <c r="E591" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="G591" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="J591" t="s">
         <v>128</v>
@@ -19614,10 +19608,10 @@
         <v>108</v>
       </c>
       <c r="E592" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="G592" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="J592" t="s">
         <v>128</v>
@@ -19638,13 +19632,13 @@
         <v>109</v>
       </c>
       <c r="E593" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F593" t="s">
         <v>114</v>
       </c>
       <c r="G593" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H593" t="s">
         <v>116</v>
@@ -19679,12 +19673,12 @@
         <v>111</v>
       </c>
       <c r="K595" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="597" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B597" s="27">
         <v>1</v>
@@ -19693,12 +19687,12 @@
         <v>39</v>
       </c>
       <c r="K597" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="598" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B598" s="27">
         <v>1</v>
@@ -19707,13 +19701,13 @@
         <v>108</v>
       </c>
       <c r="E598" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F598" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G598" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H598" t="s">
         <v>116</v>
@@ -19725,7 +19719,7 @@
     </row>
     <row r="599" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B599" s="27">
         <v>1</v>
@@ -19734,12 +19728,12 @@
         <v>27</v>
       </c>
       <c r="K599" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="601" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B601" s="27">
         <v>2</v>
@@ -19748,12 +19742,12 @@
         <v>39</v>
       </c>
       <c r="K601" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="602" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B602" s="27">
         <v>2</v>
@@ -19762,13 +19756,13 @@
         <v>108</v>
       </c>
       <c r="E602" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F602" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G602" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="K602" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D602:J602)</f>
@@ -19777,7 +19771,7 @@
     </row>
     <row r="603" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B603" s="27">
         <v>2</v>
@@ -19786,13 +19780,13 @@
         <v>108</v>
       </c>
       <c r="E603" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F603" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G603" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="K603" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D603:J603)</f>
@@ -19801,7 +19795,7 @@
     </row>
     <row r="604" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B604" s="27">
         <v>2</v>
@@ -19810,7 +19804,7 @@
         <v>27</v>
       </c>
       <c r="K604" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="607" spans="1:11" x14ac:dyDescent="0.2">
@@ -19824,7 +19818,7 @@
         <v>39</v>
       </c>
       <c r="K607" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="608" spans="1:11" x14ac:dyDescent="0.2">
@@ -19838,10 +19832,10 @@
         <v>108</v>
       </c>
       <c r="E608" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G608" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="K608" t="str">
         <f t="shared" ref="K608:K619" si="91">_xlfn.TEXTJOIN("", TRUE, D608:J608)</f>
@@ -19859,10 +19853,10 @@
         <v>108</v>
       </c>
       <c r="E609" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G609" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="J609" t="s">
         <v>201</v>
@@ -19883,10 +19877,10 @@
         <v>108</v>
       </c>
       <c r="E610" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G610" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="J610" t="s">
         <v>201</v>
@@ -19907,10 +19901,10 @@
         <v>108</v>
       </c>
       <c r="E611" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G611" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="J611" t="s">
         <v>201</v>
@@ -19931,10 +19925,10 @@
         <v>108</v>
       </c>
       <c r="E612" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G612" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="J612" t="s">
         <v>236</v>
@@ -19955,13 +19949,13 @@
         <v>108</v>
       </c>
       <c r="E613" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G613" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="J613" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K613" t="str">
         <f t="shared" si="91"/>
@@ -19979,10 +19973,10 @@
         <v>108</v>
       </c>
       <c r="E614" t="s">
+        <v>848</v>
+      </c>
+      <c r="G614" t="s">
         <v>847</v>
-      </c>
-      <c r="G614" t="s">
-        <v>846</v>
       </c>
       <c r="J614" t="s">
         <v>128</v>
@@ -20003,10 +19997,10 @@
         <v>108</v>
       </c>
       <c r="E615" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G615" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="J615" t="s">
         <v>128</v>
@@ -20027,13 +20021,13 @@
         <v>109</v>
       </c>
       <c r="E616" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F616" t="s">
         <v>114</v>
       </c>
       <c r="G616" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="J616" t="s">
         <v>201</v>
@@ -20054,13 +20048,13 @@
         <v>109</v>
       </c>
       <c r="E617" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F617" t="s">
         <v>114</v>
       </c>
       <c r="G617" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="J617" t="s">
         <v>236</v>
@@ -20081,13 +20075,13 @@
         <v>109</v>
       </c>
       <c r="E618" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F618" t="s">
         <v>114</v>
       </c>
       <c r="G618" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="J618" t="s">
         <v>236</v>
@@ -20108,16 +20102,16 @@
         <v>109</v>
       </c>
       <c r="E619" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F619" t="s">
         <v>114</v>
       </c>
       <c r="G619" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="J619" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K619" t="str">
         <f t="shared" si="91"/>
@@ -20149,12 +20143,12 @@
         <v>111</v>
       </c>
       <c r="K621" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="623" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B623" s="27">
         <v>1</v>
@@ -20163,12 +20157,12 @@
         <v>39</v>
       </c>
       <c r="K623" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="624" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B624" s="27">
         <v>1</v>
@@ -20177,13 +20171,13 @@
         <v>108</v>
       </c>
       <c r="E624" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F624" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G624" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="K624" t="str">
         <f t="shared" ref="K624:K629" si="92">_xlfn.TEXTJOIN("", TRUE, D624:J624)</f>
@@ -20192,7 +20186,7 @@
     </row>
     <row r="625" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B625" s="27">
         <v>1</v>
@@ -20201,13 +20195,13 @@
         <v>108</v>
       </c>
       <c r="E625" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F625" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G625" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="K625" t="str">
         <f t="shared" si="92"/>
@@ -20216,7 +20210,7 @@
     </row>
     <row r="626" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B626" s="27">
         <v>1</v>
@@ -20225,13 +20219,13 @@
         <v>108</v>
       </c>
       <c r="E626" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F626" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G626" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="J626" t="s">
         <v>201</v>
@@ -20243,7 +20237,7 @@
     </row>
     <row r="627" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B627" s="27">
         <v>1</v>
@@ -20252,13 +20246,13 @@
         <v>108</v>
       </c>
       <c r="E627" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F627" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G627" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="J627" t="s">
         <v>236</v>
@@ -20270,7 +20264,7 @@
     </row>
     <row r="628" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B628" s="27">
         <v>1</v>
@@ -20279,13 +20273,13 @@
         <v>108</v>
       </c>
       <c r="E628" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F628" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G628" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="J628" t="s">
         <v>236</v>
@@ -20297,7 +20291,7 @@
     </row>
     <row r="629" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B629" s="27">
         <v>1</v>
@@ -20306,13 +20300,13 @@
         <v>108</v>
       </c>
       <c r="E629" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F629" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G629" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="J629" t="s">
         <v>236</v>
@@ -20324,7 +20318,7 @@
     </row>
     <row r="630" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B630" s="27">
         <v>1</v>
@@ -20333,12 +20327,12 @@
         <v>27</v>
       </c>
       <c r="K630" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="632" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B632" s="27">
         <v>2</v>
@@ -20347,12 +20341,12 @@
         <v>39</v>
       </c>
       <c r="K632" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="633" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A633" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B633" s="27">
         <v>2</v>
@@ -20361,13 +20355,13 @@
         <v>108</v>
       </c>
       <c r="E633" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F633" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="G633" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="K633" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D633:J633)</f>
@@ -20376,7 +20370,7 @@
     </row>
     <row r="634" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A634" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B634" s="27">
         <v>2</v>
@@ -20385,13 +20379,13 @@
         <v>108</v>
       </c>
       <c r="E634" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F634" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="G634" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="J634" t="s">
         <v>201</v>
@@ -20403,7 +20397,7 @@
     </row>
     <row r="635" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B635" s="27">
         <v>2</v>
@@ -20412,13 +20406,13 @@
         <v>108</v>
       </c>
       <c r="E635" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F635" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="G635" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="J635" t="s">
         <v>236</v>
@@ -20430,7 +20424,7 @@
     </row>
     <row r="636" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B636" s="27">
         <v>2</v>
@@ -20439,13 +20433,13 @@
         <v>108</v>
       </c>
       <c r="E636" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F636" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="G636" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="J636" t="s">
         <v>236</v>
@@ -20457,7 +20451,7 @@
     </row>
     <row r="637" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A637" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B637" s="27">
         <v>2</v>
@@ -20466,16 +20460,16 @@
         <v>108</v>
       </c>
       <c r="E637" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F637" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="G637" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="J637" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K637" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D637:J637)</f>
@@ -20484,7 +20478,7 @@
     </row>
     <row r="638" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A638" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B638" s="27">
         <v>2</v>
@@ -20493,7 +20487,7 @@
         <v>27</v>
       </c>
       <c r="K638" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="640" spans="1:11" x14ac:dyDescent="0.2">
@@ -20507,7 +20501,7 @@
         <v>39</v>
       </c>
       <c r="K640" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="641" spans="1:11" x14ac:dyDescent="0.2">
@@ -20521,10 +20515,10 @@
         <v>108</v>
       </c>
       <c r="E641" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="G641" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H641" t="s">
         <v>116</v>
@@ -20545,13 +20539,13 @@
         <v>109</v>
       </c>
       <c r="E642" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F642" t="s">
         <v>114</v>
       </c>
       <c r="G642" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="K642" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D642:J642)</f>
@@ -20569,13 +20563,13 @@
         <v>109</v>
       </c>
       <c r="E643" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F643" t="s">
         <v>114</v>
       </c>
       <c r="G643" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="K643" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D643:J643)</f>
@@ -20618,7 +20612,7 @@
         <v>39</v>
       </c>
       <c r="K648" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="649" spans="1:11" x14ac:dyDescent="0.2">
@@ -20632,10 +20626,10 @@
         <v>108</v>
       </c>
       <c r="E649" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G649" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="K649" t="str">
         <f t="shared" ref="K649:K660" si="93">_xlfn.TEXTJOIN("", TRUE, D649:J649)</f>
@@ -20653,10 +20647,10 @@
         <v>108</v>
       </c>
       <c r="E650" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G650" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="K650" t="str">
         <f t="shared" si="93"/>
@@ -20674,10 +20668,10 @@
         <v>108</v>
       </c>
       <c r="E651" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G651" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="J651" t="s">
         <v>201</v>
@@ -20698,10 +20692,10 @@
         <v>108</v>
       </c>
       <c r="E652" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G652" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="J652" t="s">
         <v>201</v>
@@ -20722,10 +20716,10 @@
         <v>108</v>
       </c>
       <c r="E653" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G653" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="J653" t="s">
         <v>236</v>
@@ -20746,10 +20740,10 @@
         <v>108</v>
       </c>
       <c r="E654" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G654" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="J654" t="s">
         <v>236</v>
@@ -20770,10 +20764,10 @@
         <v>108</v>
       </c>
       <c r="E655" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G655" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="J655" t="s">
         <v>237</v>
@@ -20794,10 +20788,10 @@
         <v>108</v>
       </c>
       <c r="E656" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G656" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="J656" t="s">
         <v>237</v>
@@ -20818,10 +20812,10 @@
         <v>108</v>
       </c>
       <c r="E657" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G657" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="J657" t="s">
         <v>128</v>
@@ -20842,10 +20836,10 @@
         <v>108</v>
       </c>
       <c r="E658" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G658" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="J658" t="s">
         <v>128</v>
@@ -20866,13 +20860,13 @@
         <v>109</v>
       </c>
       <c r="E659" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F659" t="s">
         <v>114</v>
       </c>
       <c r="G659" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="J659" t="s">
         <v>201</v>
@@ -20893,13 +20887,13 @@
         <v>109</v>
       </c>
       <c r="E660" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F660" t="s">
         <v>114</v>
       </c>
       <c r="G660" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="J660" t="s">
         <v>236</v>
@@ -20945,7 +20939,7 @@
         <v>39</v>
       </c>
       <c r="K665" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="666" spans="1:11" x14ac:dyDescent="0.2">
@@ -20959,10 +20953,10 @@
         <v>108</v>
       </c>
       <c r="E666" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="G666" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="K666" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D666:J666)</f>
@@ -20980,10 +20974,10 @@
         <v>108</v>
       </c>
       <c r="E667" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="G667" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="K667" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D667:J667)</f>
@@ -21001,10 +20995,10 @@
         <v>108</v>
       </c>
       <c r="E668" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="G668" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="K668" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D668:J668)</f>
@@ -21022,13 +21016,13 @@
         <v>109</v>
       </c>
       <c r="E669" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F669" t="s">
         <v>114</v>
       </c>
       <c r="G669" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H669" t="s">
         <v>116</v>
@@ -21074,7 +21068,7 @@
         <v>39</v>
       </c>
       <c r="K674" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="675" spans="1:11" x14ac:dyDescent="0.2">
@@ -21088,10 +21082,10 @@
         <v>108</v>
       </c>
       <c r="E675" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="G675" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="K675" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D675:J675)</f>
@@ -21109,10 +21103,10 @@
         <v>108</v>
       </c>
       <c r="E676" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="G676" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="K676" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D676:J676)</f>
@@ -21130,10 +21124,10 @@
         <v>108</v>
       </c>
       <c r="E677" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="G677" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="K677" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D677:J677)</f>
@@ -21180,12 +21174,12 @@
         <v>111</v>
       </c>
       <c r="K680" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="682" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A682" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B682" s="27">
         <v>1</v>
@@ -21194,12 +21188,12 @@
         <v>39</v>
       </c>
       <c r="K682" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="683" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A683" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B683" s="27">
         <v>1</v>
@@ -21208,13 +21202,13 @@
         <v>108</v>
       </c>
       <c r="E683" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F683" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="G683" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="K683" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D683:J683)</f>
@@ -21223,7 +21217,7 @@
     </row>
     <row r="684" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A684" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B684" s="27">
         <v>1</v>
@@ -21232,13 +21226,13 @@
         <v>108</v>
       </c>
       <c r="E684" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F684" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="G684" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="K684" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D684:J684)</f>
@@ -21247,7 +21241,7 @@
     </row>
     <row r="685" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A685" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B685" s="27">
         <v>1</v>
@@ -21256,13 +21250,13 @@
         <v>108</v>
       </c>
       <c r="E685" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F685" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="G685" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="K685" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D685:J685)</f>
@@ -21271,7 +21265,7 @@
     </row>
     <row r="686" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A686" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B686" s="27">
         <v>1</v>
@@ -21280,7 +21274,7 @@
         <v>27</v>
       </c>
       <c r="K686" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="691" spans="1:11" x14ac:dyDescent="0.2">
@@ -21294,7 +21288,7 @@
         <v>39</v>
       </c>
       <c r="K691" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="692" spans="1:11" x14ac:dyDescent="0.2">
@@ -21308,10 +21302,10 @@
         <v>108</v>
       </c>
       <c r="E692" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G692" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="K692" t="str">
         <f t="shared" ref="K692:K698" si="94">_xlfn.TEXTJOIN("", TRUE, D692:J692)</f>
@@ -21329,10 +21323,10 @@
         <v>108</v>
       </c>
       <c r="E693" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G693" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="J693" t="s">
         <v>237</v>
@@ -21353,10 +21347,10 @@
         <v>108</v>
       </c>
       <c r="E694" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G694" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="J694" t="s">
         <v>237</v>
@@ -21377,10 +21371,10 @@
         <v>108</v>
       </c>
       <c r="E695" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G695" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="J695" t="s">
         <v>237</v>
@@ -21401,10 +21395,10 @@
         <v>108</v>
       </c>
       <c r="E696" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G696" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="J696" t="s">
         <v>128</v>
@@ -21425,13 +21419,13 @@
         <v>109</v>
       </c>
       <c r="E697" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F697" t="s">
         <v>114</v>
       </c>
       <c r="G697" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="K697" t="str">
         <f t="shared" si="94"/>
@@ -21449,13 +21443,13 @@
         <v>109</v>
       </c>
       <c r="E698" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F698" t="s">
         <v>114</v>
       </c>
       <c r="G698" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="K698" t="str">
         <f t="shared" si="94"/>
@@ -21487,12 +21481,12 @@
         <v>111</v>
       </c>
       <c r="K700" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="702" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A702" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B702" s="27">
         <v>1</v>
@@ -21501,12 +21495,12 @@
         <v>39</v>
       </c>
       <c r="K702" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="703" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A703" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B703" s="27">
         <v>1</v>
@@ -21515,13 +21509,13 @@
         <v>108</v>
       </c>
       <c r="E703" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F703" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G703" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="K703" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D703:J703)</f>
@@ -21530,7 +21524,7 @@
     </row>
     <row r="704" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A704" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B704" s="27">
         <v>1</v>
@@ -21539,13 +21533,13 @@
         <v>108</v>
       </c>
       <c r="E704" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F704" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G704" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="K704" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D704:J704)</f>
@@ -21554,7 +21548,7 @@
     </row>
     <row r="705" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A705" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B705" s="27">
         <v>1</v>
@@ -21563,13 +21557,13 @@
         <v>108</v>
       </c>
       <c r="E705" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F705" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G705" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="K705" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D705:J705)</f>
@@ -21578,7 +21572,7 @@
     </row>
     <row r="706" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A706" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B706" s="27">
         <v>1</v>
@@ -21587,13 +21581,13 @@
         <v>108</v>
       </c>
       <c r="E706" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F706" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G706" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="K706" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D706:J706)</f>
@@ -21602,7 +21596,7 @@
     </row>
     <row r="707" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A707" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B707" s="27">
         <v>1</v>
@@ -21611,13 +21605,13 @@
         <v>108</v>
       </c>
       <c r="E707" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F707" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G707" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="K707" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D707:J707)</f>
@@ -21626,7 +21620,7 @@
     </row>
     <row r="708" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A708" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B708" s="27">
         <v>1</v>
@@ -21635,7 +21629,7 @@
         <v>27</v>
       </c>
       <c r="K708" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="712" spans="1:11" x14ac:dyDescent="0.2">
@@ -21649,7 +21643,7 @@
         <v>39</v>
       </c>
       <c r="K712" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="713" spans="1:11" x14ac:dyDescent="0.2">
@@ -21663,10 +21657,10 @@
         <v>108</v>
       </c>
       <c r="E713" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G713" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="K713" t="str">
         <f t="shared" ref="K713:K718" si="95">_xlfn.TEXTJOIN("", TRUE, D713:J713)</f>
@@ -21684,10 +21678,10 @@
         <v>108</v>
       </c>
       <c r="E714" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G714" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="K714" t="str">
         <f t="shared" si="95"/>
@@ -21705,10 +21699,10 @@
         <v>108</v>
       </c>
       <c r="E715" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G715" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="K715" t="str">
         <f t="shared" si="95"/>
@@ -21726,10 +21720,10 @@
         <v>108</v>
       </c>
       <c r="E716" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G716" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="K716" t="str">
         <f t="shared" si="95"/>
@@ -21747,10 +21741,10 @@
         <v>108</v>
       </c>
       <c r="E717" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G717" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="J717" t="s">
         <v>237</v>
@@ -21811,7 +21805,7 @@
         <v>39</v>
       </c>
       <c r="K723" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="724" spans="1:11" x14ac:dyDescent="0.2">
@@ -21825,10 +21819,10 @@
         <v>108</v>
       </c>
       <c r="E724" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="G724" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="K724" t="str">
         <f t="shared" ref="K724:K730" si="96">_xlfn.TEXTJOIN("", TRUE, D724:J724)</f>
@@ -21846,10 +21840,10 @@
         <v>108</v>
       </c>
       <c r="E725" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="G725" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="J725" t="s">
         <v>201</v>
@@ -21870,10 +21864,10 @@
         <v>108</v>
       </c>
       <c r="E726" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="G726" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="J726" t="s">
         <v>201</v>
@@ -21894,10 +21888,10 @@
         <v>108</v>
       </c>
       <c r="E727" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="G727" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="J727" t="s">
         <v>201</v>
@@ -21918,10 +21912,10 @@
         <v>108</v>
       </c>
       <c r="E728" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="G728" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="J728" t="s">
         <v>237</v>
@@ -21942,10 +21936,10 @@
         <v>108</v>
       </c>
       <c r="E729" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="G729" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="J729" t="s">
         <v>128</v>
@@ -22006,7 +22000,7 @@
         <v>39</v>
       </c>
       <c r="K735" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="736" spans="1:11" x14ac:dyDescent="0.2">
@@ -22020,10 +22014,10 @@
         <v>108</v>
       </c>
       <c r="E736" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G736" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="K736" t="str">
         <f t="shared" ref="K736:K743" si="97">_xlfn.TEXTJOIN("", TRUE, D736:J736)</f>
@@ -22041,10 +22035,10 @@
         <v>108</v>
       </c>
       <c r="E737" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G737" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="J737" t="s">
         <v>201</v>
@@ -22065,10 +22059,10 @@
         <v>108</v>
       </c>
       <c r="E738" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G738" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="J738" t="s">
         <v>237</v>
@@ -22089,10 +22083,10 @@
         <v>108</v>
       </c>
       <c r="E739" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G739" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="J739" t="s">
         <v>237</v>
@@ -22113,13 +22107,13 @@
         <v>108</v>
       </c>
       <c r="E740" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G740" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="J740" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K740" t="str">
         <f t="shared" si="97"/>
@@ -22137,10 +22131,10 @@
         <v>108</v>
       </c>
       <c r="E741" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G741" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="J741" t="s">
         <v>128</v>
@@ -22161,10 +22155,10 @@
         <v>108</v>
       </c>
       <c r="E742" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G742" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="J742" t="s">
         <v>128</v>
@@ -22225,7 +22219,7 @@
         <v>39</v>
       </c>
       <c r="K748" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="749" spans="1:11" x14ac:dyDescent="0.2">
@@ -22239,10 +22233,10 @@
         <v>108</v>
       </c>
       <c r="E749" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="G749" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="K749" t="str">
         <f t="shared" ref="K749:K755" si="98">_xlfn.TEXTJOIN("", TRUE, D749:J749)</f>
@@ -22260,10 +22254,10 @@
         <v>108</v>
       </c>
       <c r="E750" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="G750" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="K750" t="str">
         <f t="shared" si="98"/>
@@ -22281,10 +22275,10 @@
         <v>108</v>
       </c>
       <c r="E751" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="G751" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="J751" t="s">
         <v>237</v>
@@ -22305,10 +22299,10 @@
         <v>108</v>
       </c>
       <c r="E752" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="G752" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="J752" t="s">
         <v>128</v>
@@ -22329,10 +22323,10 @@
         <v>108</v>
       </c>
       <c r="E753" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="G753" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="J753" t="s">
         <v>128</v>
@@ -22353,13 +22347,13 @@
         <v>109</v>
       </c>
       <c r="E754" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F754" t="s">
         <v>114</v>
       </c>
       <c r="G754" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="J754" t="s">
         <v>237</v>
@@ -22380,13 +22374,13 @@
         <v>109</v>
       </c>
       <c r="E755" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F755" t="s">
         <v>114</v>
       </c>
       <c r="G755" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="J755" t="s">
         <v>237</v>
@@ -22432,7 +22426,7 @@
         <v>39</v>
       </c>
       <c r="K760" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="761" spans="1:11" x14ac:dyDescent="0.2">
@@ -22446,10 +22440,10 @@
         <v>108</v>
       </c>
       <c r="E761" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="G761" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="K761" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D761:J761)</f>
@@ -22467,10 +22461,10 @@
         <v>108</v>
       </c>
       <c r="E762" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="G762" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="K762" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D762:J762)</f>
@@ -22488,10 +22482,10 @@
         <v>108</v>
       </c>
       <c r="E763" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="G763" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="J763" t="s">
         <v>237</v>
@@ -22512,10 +22506,10 @@
         <v>108</v>
       </c>
       <c r="E764" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="G764" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="J764" t="s">
         <v>128</v>
@@ -22536,13 +22530,13 @@
         <v>109</v>
       </c>
       <c r="E765" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="F765" t="s">
         <v>114</v>
       </c>
       <c r="G765" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H765" t="s">
         <v>116</v>
@@ -22591,7 +22585,7 @@
         <v>39</v>
       </c>
       <c r="K770" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="771" spans="1:11" x14ac:dyDescent="0.2">
@@ -22605,10 +22599,10 @@
         <v>108</v>
       </c>
       <c r="E771" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="G771" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="K771" t="str">
         <f t="shared" ref="K771:K778" si="99">_xlfn.TEXTJOIN("", TRUE, D771:J771)</f>
@@ -22626,13 +22620,13 @@
         <v>108</v>
       </c>
       <c r="E772" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="G772" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="J772" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K772" t="str">
         <f t="shared" si="99"/>
@@ -22650,10 +22644,10 @@
         <v>108</v>
       </c>
       <c r="E773" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="G773" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="J773" t="s">
         <v>128</v>
@@ -22674,10 +22668,10 @@
         <v>108</v>
       </c>
       <c r="E774" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="G774" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="J774" t="s">
         <v>128</v>
@@ -22698,13 +22692,13 @@
         <v>109</v>
       </c>
       <c r="E775" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F775" t="s">
         <v>114</v>
       </c>
       <c r="G775" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="J775" t="s">
         <v>201</v>
@@ -22725,13 +22719,13 @@
         <v>109</v>
       </c>
       <c r="E776" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F776" t="s">
         <v>114</v>
       </c>
       <c r="G776" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="J776" t="s">
         <v>236</v>
@@ -22752,13 +22746,13 @@
         <v>109</v>
       </c>
       <c r="E777" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F777" t="s">
         <v>114</v>
       </c>
       <c r="G777" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="J777" t="s">
         <v>237</v>
@@ -22779,13 +22773,13 @@
         <v>109</v>
       </c>
       <c r="E778" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F778" t="s">
         <v>114</v>
       </c>
       <c r="G778" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="J778" t="s">
         <v>237</v>
@@ -22831,7 +22825,7 @@
         <v>39</v>
       </c>
       <c r="K783" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="784" spans="1:11" x14ac:dyDescent="0.2">
@@ -22845,7 +22839,7 @@
         <v>108</v>
       </c>
       <c r="E784" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="K784" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D784:J784)</f>
@@ -22903,7 +22897,7 @@
         <v>39</v>
       </c>
       <c r="K790" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="791" spans="1:11" x14ac:dyDescent="0.2">
@@ -22917,10 +22911,10 @@
         <v>108</v>
       </c>
       <c r="E791" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="G791" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="K791" t="str">
         <f t="shared" ref="K791:K797" si="100">_xlfn.TEXTJOIN("", TRUE, D791:J791)</f>
@@ -22938,10 +22932,10 @@
         <v>108</v>
       </c>
       <c r="E792" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="G792" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="J792" t="s">
         <v>201</v>
@@ -22962,10 +22956,10 @@
         <v>108</v>
       </c>
       <c r="E793" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="G793" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="J793" t="s">
         <v>201</v>
@@ -22986,13 +22980,13 @@
         <v>108</v>
       </c>
       <c r="E794" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="G794" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="J794" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K794" t="str">
         <f t="shared" si="100"/>
@@ -23010,13 +23004,13 @@
         <v>108</v>
       </c>
       <c r="E795" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="G795" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="J795" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K795" t="str">
         <f t="shared" si="100"/>
@@ -23034,13 +23028,13 @@
         <v>108</v>
       </c>
       <c r="E796" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="G796" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="J796" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K796" t="str">
         <f t="shared" si="100"/>
@@ -23098,7 +23092,7 @@
         <v>39</v>
       </c>
       <c r="K802" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="803" spans="1:11" x14ac:dyDescent="0.2">
@@ -23112,10 +23106,10 @@
         <v>108</v>
       </c>
       <c r="E803" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G803" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="J803" t="s">
         <v>201</v>
@@ -23136,10 +23130,10 @@
         <v>108</v>
       </c>
       <c r="E804" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G804" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="J804" t="s">
         <v>236</v>
@@ -23160,10 +23154,10 @@
         <v>108</v>
       </c>
       <c r="E805" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G805" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="J805" t="s">
         <v>236</v>
@@ -23184,10 +23178,10 @@
         <v>108</v>
       </c>
       <c r="E806" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G806" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="J806" t="s">
         <v>236</v>
@@ -23208,10 +23202,10 @@
         <v>108</v>
       </c>
       <c r="E807" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G807" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="J807" t="s">
         <v>236</v>
@@ -23232,10 +23226,10 @@
         <v>108</v>
       </c>
       <c r="E808" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G808" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="J808" t="s">
         <v>236</v>
@@ -23256,10 +23250,10 @@
         <v>108</v>
       </c>
       <c r="E809" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G809" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="J809" t="s">
         <v>236</v>
@@ -23280,13 +23274,13 @@
         <v>108</v>
       </c>
       <c r="E810" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G810" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="J810" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="K810" t="str">
         <f t="shared" si="101"/>
@@ -23304,13 +23298,13 @@
         <v>108</v>
       </c>
       <c r="E811" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G811" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="J811" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="K811" t="str">
         <f t="shared" si="101"/>
@@ -23328,13 +23322,13 @@
         <v>108</v>
       </c>
       <c r="E812" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G812" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="J812" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="K812" t="str">
         <f t="shared" si="101"/>
@@ -23352,13 +23346,13 @@
         <v>108</v>
       </c>
       <c r="E813" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G813" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="J813" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="K813" t="str">
         <f t="shared" si="101"/>
@@ -23376,13 +23370,13 @@
         <v>108</v>
       </c>
       <c r="E814" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G814" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="J814" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="K814" t="str">
         <f t="shared" si="101"/>
@@ -23400,13 +23394,13 @@
         <v>109</v>
       </c>
       <c r="E815" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="F815" t="s">
         <v>114</v>
       </c>
       <c r="G815" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="K815" t="str">
         <f t="shared" si="101"/>
@@ -23424,13 +23418,13 @@
         <v>109</v>
       </c>
       <c r="E816" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="F816" t="s">
         <v>114</v>
       </c>
       <c r="G816" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="K816" t="str">
         <f t="shared" si="101"/>
@@ -23487,10 +23481,10 @@
         <v>108</v>
       </c>
       <c r="E822" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="G822" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="K822" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D822:J822)</f>
@@ -23508,10 +23502,10 @@
         <v>108</v>
       </c>
       <c r="E823" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="G823" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="J823" t="s">
         <v>201</v>
@@ -23532,10 +23526,10 @@
         <v>108</v>
       </c>
       <c r="E824" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="G824" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="J824" t="s">
         <v>201</v>
@@ -23596,7 +23590,7 @@
         <v>39</v>
       </c>
       <c r="K830" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="831" spans="1:11" x14ac:dyDescent="0.2">
@@ -23610,10 +23604,10 @@
         <v>108</v>
       </c>
       <c r="E831" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G831" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="K831" t="str">
         <f t="shared" ref="K831:K837" si="102">_xlfn.TEXTJOIN("", TRUE, D831:J831)</f>
@@ -23631,10 +23625,10 @@
         <v>108</v>
       </c>
       <c r="E832" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G832" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="K832" t="str">
         <f t="shared" si="102"/>
@@ -23652,10 +23646,10 @@
         <v>108</v>
       </c>
       <c r="E833" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G833" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="J833" t="s">
         <v>201</v>
@@ -23676,10 +23670,10 @@
         <v>108</v>
       </c>
       <c r="E834" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G834" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="J834" t="s">
         <v>237</v>
@@ -23700,13 +23694,13 @@
         <v>109</v>
       </c>
       <c r="E835" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F835" t="s">
         <v>114</v>
       </c>
       <c r="G835" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="K835" t="str">
         <f t="shared" si="102"/>
@@ -23724,13 +23718,13 @@
         <v>109</v>
       </c>
       <c r="E836" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F836" t="s">
         <v>114</v>
       </c>
       <c r="G836" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="K836" t="str">
         <f t="shared" si="102"/>
@@ -23748,16 +23742,16 @@
         <v>109</v>
       </c>
       <c r="E837" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F837" t="s">
         <v>114</v>
       </c>
       <c r="G837" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="J837" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="K837" t="str">
         <f t="shared" si="102"/>
@@ -23789,12 +23783,12 @@
         <v>111</v>
       </c>
       <c r="K839" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="841" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A841" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B841" s="27">
         <v>1</v>
@@ -23803,12 +23797,12 @@
         <v>39</v>
       </c>
       <c r="K841" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="842" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A842" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B842" s="27">
         <v>1</v>
@@ -23817,19 +23811,19 @@
         <v>108</v>
       </c>
       <c r="E842" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F842" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G842" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H842" t="s">
         <v>116</v>
       </c>
       <c r="J842" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="K842" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D842:J842)</f>
@@ -23838,7 +23832,7 @@
     </row>
     <row r="843" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A843" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B843" s="27">
         <v>1</v>
@@ -23847,7 +23841,7 @@
         <v>27</v>
       </c>
       <c r="K843" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="849" spans="1:11" x14ac:dyDescent="0.2">
@@ -23861,7 +23855,7 @@
         <v>39</v>
       </c>
       <c r="K849" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="850" spans="1:11" x14ac:dyDescent="0.2">
@@ -23875,10 +23869,10 @@
         <v>108</v>
       </c>
       <c r="E850" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G850" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="K850" t="str">
         <f t="shared" ref="K850:K858" si="103">_xlfn.TEXTJOIN("", TRUE, D850:J850)</f>
@@ -23896,10 +23890,10 @@
         <v>108</v>
       </c>
       <c r="E851" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G851" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="K851" t="str">
         <f t="shared" si="103"/>
@@ -23917,10 +23911,10 @@
         <v>108</v>
       </c>
       <c r="E852" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G852" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="K852" t="str">
         <f t="shared" si="103"/>
@@ -23938,10 +23932,10 @@
         <v>108</v>
       </c>
       <c r="E853" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G853" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="K853" t="str">
         <f t="shared" si="103"/>
@@ -23959,10 +23953,10 @@
         <v>108</v>
       </c>
       <c r="E854" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G854" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="J854" t="s">
         <v>201</v>
@@ -23983,10 +23977,10 @@
         <v>108</v>
       </c>
       <c r="E855" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G855" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="J855" t="s">
         <v>236</v>
@@ -24007,13 +24001,13 @@
         <v>108</v>
       </c>
       <c r="E856" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G856" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="J856" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="K856" t="str">
         <f t="shared" si="103"/>
@@ -24031,13 +24025,13 @@
         <v>109</v>
       </c>
       <c r="E857" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F857" t="s">
         <v>114</v>
       </c>
       <c r="G857" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="K857" t="str">
         <f t="shared" si="103"/>
@@ -24055,13 +24049,13 @@
         <v>109</v>
       </c>
       <c r="E858" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F858" t="s">
         <v>114</v>
       </c>
       <c r="G858" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="K858" t="str">
         <f t="shared" si="103"/>
@@ -24118,10 +24112,10 @@
         <v>108</v>
       </c>
       <c r="E864" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="G864" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="K864" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D864:J864)</f>
@@ -24139,10 +24133,10 @@
         <v>108</v>
       </c>
       <c r="E865" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="G865" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="K865" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D865:J865)</f>
@@ -24160,10 +24154,10 @@
         <v>108</v>
       </c>
       <c r="E866" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="G866" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="J866" t="s">
         <v>201</v>
@@ -24184,10 +24178,10 @@
         <v>108</v>
       </c>
       <c r="E867" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="G867" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="J867" t="s">
         <v>236</v>
@@ -24237,12 +24231,12 @@
         <v>111</v>
       </c>
       <c r="K870" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="872" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A872" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B872" s="27">
         <v>1</v>
@@ -24251,12 +24245,12 @@
         <v>39</v>
       </c>
       <c r="K872" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="873" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A873" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B873" s="27">
         <v>1</v>
@@ -24265,13 +24259,13 @@
         <v>108</v>
       </c>
       <c r="E873" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F873" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="G873" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H873" t="s">
         <v>116</v>
@@ -24283,7 +24277,7 @@
     </row>
     <row r="874" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A874" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B874" s="27">
         <v>1</v>
@@ -24292,12 +24286,12 @@
         <v>27</v>
       </c>
       <c r="K874" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="876" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A876" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B876" s="27">
         <v>2</v>
@@ -24306,12 +24300,12 @@
         <v>39</v>
       </c>
       <c r="K876" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="877" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A877" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B877" s="27">
         <v>2</v>
@@ -24320,13 +24314,13 @@
         <v>108</v>
       </c>
       <c r="E877" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F877" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="G877" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H877" t="s">
         <v>116</v>
@@ -24338,7 +24332,7 @@
     </row>
     <row r="878" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A878" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B878" s="27">
         <v>2</v>
@@ -24347,12 +24341,12 @@
         <v>27</v>
       </c>
       <c r="K878" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="880" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A880" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B880" s="27">
         <v>3</v>
@@ -24361,12 +24355,12 @@
         <v>39</v>
       </c>
       <c r="K880" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="881" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A881" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B881" s="27">
         <v>3</v>
@@ -24375,13 +24369,13 @@
         <v>108</v>
       </c>
       <c r="E881" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F881" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="G881" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H881" t="s">
         <v>116</v>
@@ -24396,7 +24390,7 @@
     </row>
     <row r="882" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A882" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B882" s="27">
         <v>3</v>
@@ -24405,12 +24399,12 @@
         <v>27</v>
       </c>
       <c r="K882" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="884" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A884" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B884" s="27">
         <v>4</v>
@@ -24419,12 +24413,12 @@
         <v>39</v>
       </c>
       <c r="K884" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="885" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A885" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B885" s="27">
         <v>4</v>
@@ -24433,13 +24427,13 @@
         <v>108</v>
       </c>
       <c r="E885" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F885" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="G885" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H885" t="s">
         <v>116</v>
@@ -24451,7 +24445,7 @@
     </row>
     <row r="886" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A886" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B886" s="27">
         <v>4</v>
@@ -24460,12 +24454,12 @@
         <v>27</v>
       </c>
       <c r="K886" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="888" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A888" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B888" s="27">
         <v>5</v>
@@ -24474,12 +24468,12 @@
         <v>39</v>
       </c>
       <c r="K888" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="889" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A889" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B889" s="27">
         <v>5</v>
@@ -24488,13 +24482,13 @@
         <v>108</v>
       </c>
       <c r="E889" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F889" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="G889" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H889" t="s">
         <v>116</v>
@@ -24506,7 +24500,7 @@
     </row>
     <row r="890" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A890" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B890" s="27">
         <v>5</v>
@@ -24515,12 +24509,12 @@
         <v>27</v>
       </c>
       <c r="K890" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="892" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A892" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B892" s="27">
         <v>6</v>
@@ -24529,12 +24523,12 @@
         <v>39</v>
       </c>
       <c r="K892" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="893" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A893" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B893" s="27">
         <v>6</v>
@@ -24543,13 +24537,13 @@
         <v>108</v>
       </c>
       <c r="E893" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F893" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="G893" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H893" t="s">
         <v>116</v>
@@ -24561,7 +24555,7 @@
     </row>
     <row r="894" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A894" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B894" s="27">
         <v>6</v>
@@ -24570,7 +24564,7 @@
         <v>27</v>
       </c>
       <c r="K894" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="896" spans="1:11" x14ac:dyDescent="0.2">
@@ -24584,7 +24578,7 @@
         <v>39</v>
       </c>
       <c r="K896" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="897" spans="1:11" x14ac:dyDescent="0.2">
@@ -24598,10 +24592,10 @@
         <v>108</v>
       </c>
       <c r="E897" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G897" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="K897" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D897:J897)</f>
@@ -24619,10 +24613,10 @@
         <v>108</v>
       </c>
       <c r="E898" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G898" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="K898" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D898:J898)</f>
@@ -24640,10 +24634,10 @@
         <v>108</v>
       </c>
       <c r="E899" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G899" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="K899" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D899:J899)</f>
@@ -24701,7 +24695,7 @@
         <v>39</v>
       </c>
       <c r="K905" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="906" spans="1:11" x14ac:dyDescent="0.2">
@@ -24715,10 +24709,10 @@
         <v>108</v>
       </c>
       <c r="E906" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G906" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="K906" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D906:J906)</f>
@@ -24736,13 +24730,13 @@
         <v>108</v>
       </c>
       <c r="E907" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G907" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="J907" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K907" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D907:J907)</f>
@@ -24760,13 +24754,13 @@
         <v>109</v>
       </c>
       <c r="E908" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F908" t="s">
         <v>114</v>
       </c>
       <c r="G908" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="K908" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D908:J908)</f>
@@ -24784,13 +24778,13 @@
         <v>109</v>
       </c>
       <c r="E909" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F909" t="s">
         <v>114</v>
       </c>
       <c r="G909" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="K909" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D909:J909)</f>
@@ -24833,7 +24827,7 @@
         <v>39</v>
       </c>
       <c r="K914" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="915" spans="1:11" x14ac:dyDescent="0.2">
@@ -24847,10 +24841,10 @@
         <v>108</v>
       </c>
       <c r="E915" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="G915" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="K915" t="str">
         <f t="shared" ref="K915:K922" si="104">_xlfn.TEXTJOIN("", TRUE, D915:J915)</f>
@@ -24868,10 +24862,10 @@
         <v>108</v>
       </c>
       <c r="E916" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="G916" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="K916" t="str">
         <f t="shared" si="104"/>
@@ -24889,10 +24883,10 @@
         <v>108</v>
       </c>
       <c r="E917" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="G917" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="K917" t="str">
         <f t="shared" si="104"/>
@@ -24910,10 +24904,10 @@
         <v>108</v>
       </c>
       <c r="E918" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="G918" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="K918" t="str">
         <f t="shared" si="104"/>
@@ -24931,10 +24925,10 @@
         <v>108</v>
       </c>
       <c r="E919" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="G919" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="J919" t="s">
         <v>128</v>
@@ -24955,10 +24949,10 @@
         <v>108</v>
       </c>
       <c r="E920" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="G920" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="J920" t="s">
         <v>128</v>
@@ -24979,13 +24973,13 @@
         <v>109</v>
       </c>
       <c r="E921" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="F921" t="s">
         <v>114</v>
       </c>
       <c r="G921" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="K921" t="str">
         <f t="shared" si="104"/>
@@ -25003,13 +24997,13 @@
         <v>109</v>
       </c>
       <c r="E922" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="F922" t="s">
         <v>114</v>
       </c>
       <c r="G922" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="K922" t="str">
         <f t="shared" si="104"/>
@@ -25052,7 +25046,7 @@
         <v>39</v>
       </c>
       <c r="K927" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="928" spans="1:11" x14ac:dyDescent="0.2">
@@ -25066,10 +25060,10 @@
         <v>108</v>
       </c>
       <c r="E928" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="G928" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="K928" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D928:J928)</f>
@@ -25087,10 +25081,10 @@
         <v>108</v>
       </c>
       <c r="E929" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="G929" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="K929" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D929:J929)</f>
@@ -25108,10 +25102,10 @@
         <v>108</v>
       </c>
       <c r="E930" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="G930" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="J930" t="s">
         <v>237</v>
@@ -25172,7 +25166,7 @@
         <v>39</v>
       </c>
       <c r="K936" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="937" spans="1:11" x14ac:dyDescent="0.2">
@@ -25186,10 +25180,10 @@
         <v>108</v>
       </c>
       <c r="E937" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="G937" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="K937" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D937:J937)</f>
@@ -25207,10 +25201,10 @@
         <v>108</v>
       </c>
       <c r="E938" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="G938" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="K938" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D938:J938)</f>
@@ -25228,10 +25222,10 @@
         <v>108</v>
       </c>
       <c r="E939" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="G939" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="K939" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D939:J939)</f>
@@ -25249,10 +25243,10 @@
         <v>108</v>
       </c>
       <c r="E940" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="G940" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="J940" t="s">
         <v>237</v>
@@ -25273,13 +25267,13 @@
         <v>109</v>
       </c>
       <c r="E941" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="F941" t="s">
         <v>114</v>
       </c>
       <c r="G941" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="K941" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D941:J941)</f>
@@ -25322,7 +25316,7 @@
         <v>39</v>
       </c>
       <c r="K946" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="947" spans="1:11" x14ac:dyDescent="0.2">
@@ -25336,10 +25330,10 @@
         <v>108</v>
       </c>
       <c r="E947" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G947" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="K947" t="str">
         <f t="shared" ref="K947:K955" si="105">_xlfn.TEXTJOIN("", TRUE, D947:J947)</f>
@@ -25357,10 +25351,10 @@
         <v>108</v>
       </c>
       <c r="E948" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G948" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="K948" t="str">
         <f t="shared" si="105"/>
@@ -25378,10 +25372,10 @@
         <v>108</v>
       </c>
       <c r="E949" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G949" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="K949" t="str">
         <f t="shared" si="105"/>
@@ -25399,13 +25393,13 @@
         <v>108</v>
       </c>
       <c r="E950" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G950" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="J950" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="K950" t="str">
         <f t="shared" si="105"/>
@@ -25423,10 +25417,10 @@
         <v>108</v>
       </c>
       <c r="E951" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G951" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="J951" t="s">
         <v>128</v>
@@ -25447,10 +25441,10 @@
         <v>108</v>
       </c>
       <c r="E952" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G952" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J952" t="s">
         <v>128</v>
@@ -25471,10 +25465,10 @@
         <v>108</v>
       </c>
       <c r="E953" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G953" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="J953" t="s">
         <v>128</v>
@@ -25495,13 +25489,13 @@
         <v>109</v>
       </c>
       <c r="E954" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F954" t="s">
         <v>114</v>
       </c>
       <c r="G954" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="K954" t="str">
         <f t="shared" si="105"/>
@@ -25519,13 +25513,13 @@
         <v>109</v>
       </c>
       <c r="E955" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F955" t="s">
         <v>114</v>
       </c>
       <c r="G955" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="K955" t="str">
         <f t="shared" si="105"/>
@@ -25568,7 +25562,7 @@
         <v>39</v>
       </c>
       <c r="K960" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="961" spans="1:11" x14ac:dyDescent="0.2">
@@ -25582,10 +25576,10 @@
         <v>108</v>
       </c>
       <c r="E961" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="G961" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="K961" t="str">
         <f t="shared" ref="K961:K967" si="106">_xlfn.TEXTJOIN("", TRUE, D961:J961)</f>
@@ -25603,10 +25597,10 @@
         <v>108</v>
       </c>
       <c r="E962" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="G962" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="J962" t="s">
         <v>201</v>
@@ -25627,10 +25621,10 @@
         <v>108</v>
       </c>
       <c r="E963" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="G963" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="J963" t="s">
         <v>201</v>
@@ -25651,10 +25645,10 @@
         <v>108</v>
       </c>
       <c r="E964" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="G964" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="J964" t="s">
         <v>237</v>
@@ -25675,10 +25669,10 @@
         <v>108</v>
       </c>
       <c r="E965" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="G965" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J965" t="s">
         <v>128</v>
@@ -25699,10 +25693,10 @@
         <v>108</v>
       </c>
       <c r="E966" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="G966" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="J966" t="s">
         <v>128</v>
@@ -25763,7 +25757,7 @@
         <v>39</v>
       </c>
       <c r="K972" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="973" spans="1:11" x14ac:dyDescent="0.2">
@@ -25777,10 +25771,10 @@
         <v>108</v>
       </c>
       <c r="E973" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="G973" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="K973" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D973:J973)</f>
@@ -25798,13 +25792,13 @@
         <v>109</v>
       </c>
       <c r="E974" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="F974" t="s">
         <v>114</v>
       </c>
       <c r="G974" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="K974" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D974:J974)</f>
@@ -25847,7 +25841,7 @@
         <v>39</v>
       </c>
       <c r="K979" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="980" spans="1:11" x14ac:dyDescent="0.2">
@@ -25861,10 +25855,10 @@
         <v>108</v>
       </c>
       <c r="E980" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="G980" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="K980" t="str">
         <f t="shared" ref="K980:K985" si="107">_xlfn.TEXTJOIN("", TRUE, D980:J980)</f>
@@ -25882,10 +25876,10 @@
         <v>108</v>
       </c>
       <c r="E981" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="G981" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J981" t="s">
         <v>201</v>
@@ -25906,10 +25900,10 @@
         <v>108</v>
       </c>
       <c r="E982" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="G982" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="J982" t="s">
         <v>236</v>
@@ -25930,10 +25924,10 @@
         <v>108</v>
       </c>
       <c r="E983" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="G983" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="J983" t="s">
         <v>237</v>
@@ -25954,13 +25948,13 @@
         <v>108</v>
       </c>
       <c r="E984" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="G984" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="J984" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K984" t="str">
         <f t="shared" si="107"/>
@@ -26007,12 +26001,12 @@
         <v>111</v>
       </c>
       <c r="K987" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="989" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A989" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B989" s="27">
         <v>1</v>
@@ -26021,12 +26015,12 @@
         <v>39</v>
       </c>
       <c r="K989" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="990" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A990" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B990" s="27">
         <v>1</v>
@@ -26035,13 +26029,13 @@
         <v>108</v>
       </c>
       <c r="E990" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F990" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="G990" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="K990" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D990:J990)</f>
@@ -26050,7 +26044,7 @@
     </row>
     <row r="991" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A991" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B991" s="27">
         <v>1</v>
@@ -26059,13 +26053,13 @@
         <v>108</v>
       </c>
       <c r="E991" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F991" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="G991" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="K991" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D991:J991)</f>
@@ -26074,7 +26068,7 @@
     </row>
     <row r="992" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A992" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B992" s="27">
         <v>1</v>
@@ -26083,13 +26077,13 @@
         <v>108</v>
       </c>
       <c r="E992" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F992" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="G992" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="J992" t="s">
         <v>128</v>
@@ -26101,7 +26095,7 @@
     </row>
     <row r="993" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A993" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B993" s="27">
         <v>1</v>
@@ -26110,12 +26104,12 @@
         <v>27</v>
       </c>
       <c r="K993" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="995" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A995" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B995" s="27">
         <v>2</v>
@@ -26124,12 +26118,12 @@
         <v>39</v>
       </c>
       <c r="K995" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="996" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A996" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B996" s="27">
         <v>2</v>
@@ -26138,13 +26132,13 @@
         <v>108</v>
       </c>
       <c r="E996" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F996" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="G996" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="K996" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D996:J996)</f>
@@ -26153,7 +26147,7 @@
     </row>
     <row r="997" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A997" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B997" s="27">
         <v>2</v>
@@ -26162,16 +26156,16 @@
         <v>108</v>
       </c>
       <c r="E997" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F997" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="G997" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="J997" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K997" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D997:J997)</f>
@@ -26180,7 +26174,7 @@
     </row>
     <row r="998" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A998" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B998" s="27">
         <v>2</v>
@@ -26189,7 +26183,7 @@
         <v>27</v>
       </c>
       <c r="K998" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="1001" spans="1:11" x14ac:dyDescent="0.2">
@@ -26203,7 +26197,7 @@
         <v>39</v>
       </c>
       <c r="K1001" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="1002" spans="1:11" x14ac:dyDescent="0.2">
@@ -26217,10 +26211,10 @@
         <v>108</v>
       </c>
       <c r="E1002" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G1002" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="K1002" t="str">
         <f t="shared" ref="K1002:K1016" si="108">_xlfn.TEXTJOIN("", TRUE, D1002:J1002)</f>
@@ -26238,10 +26232,10 @@
         <v>108</v>
       </c>
       <c r="E1003" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G1003" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="J1003" t="s">
         <v>201</v>
@@ -26262,10 +26256,10 @@
         <v>108</v>
       </c>
       <c r="E1004" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G1004" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="J1004" t="s">
         <v>236</v>
@@ -26286,13 +26280,13 @@
         <v>108</v>
       </c>
       <c r="E1005" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G1005" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="J1005" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="K1005" t="str">
         <f t="shared" si="108"/>
@@ -26310,10 +26304,10 @@
         <v>108</v>
       </c>
       <c r="E1006" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G1006" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="J1006" t="s">
         <v>237</v>
@@ -26334,13 +26328,13 @@
         <v>108</v>
       </c>
       <c r="E1007" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G1007" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="J1007" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K1007" t="str">
         <f t="shared" si="108"/>
@@ -26358,13 +26352,13 @@
         <v>108</v>
       </c>
       <c r="E1008" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G1008" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="J1008" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K1008" t="str">
         <f t="shared" si="108"/>
@@ -26382,13 +26376,13 @@
         <v>108</v>
       </c>
       <c r="E1009" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G1009" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="J1009" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K1009" t="str">
         <f t="shared" si="108"/>
@@ -26406,13 +26400,13 @@
         <v>108</v>
       </c>
       <c r="E1010" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G1010" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="J1010" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="K1010" t="str">
         <f t="shared" si="108"/>
@@ -26430,13 +26424,13 @@
         <v>108</v>
       </c>
       <c r="E1011" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G1011" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="J1011" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="K1011" t="str">
         <f t="shared" si="108"/>
@@ -26454,10 +26448,10 @@
         <v>108</v>
       </c>
       <c r="E1012" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G1012" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="J1012" t="s">
         <v>128</v>
@@ -26478,10 +26472,10 @@
         <v>108</v>
       </c>
       <c r="E1013" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G1013" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="J1013" t="s">
         <v>128</v>
@@ -26502,13 +26496,13 @@
         <v>109</v>
       </c>
       <c r="E1014" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F1014" t="s">
         <v>114</v>
       </c>
       <c r="G1014" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="K1014" t="str">
         <f t="shared" si="108"/>
@@ -26526,13 +26520,13 @@
         <v>109</v>
       </c>
       <c r="E1015" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F1015" t="s">
         <v>114</v>
       </c>
       <c r="G1015" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="K1015" t="str">
         <f t="shared" si="108"/>
@@ -26550,13 +26544,13 @@
         <v>109</v>
       </c>
       <c r="E1016" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F1016" t="s">
         <v>114</v>
       </c>
       <c r="G1016" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="J1016" t="s">
         <v>236</v>
@@ -26602,7 +26596,7 @@
         <v>39</v>
       </c>
       <c r="K1021" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="1022" spans="1:11" x14ac:dyDescent="0.2">
@@ -26616,10 +26610,10 @@
         <v>108</v>
       </c>
       <c r="E1022" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G1022" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="K1022" t="str">
         <f t="shared" ref="K1022:K1027" si="109">_xlfn.TEXTJOIN("", TRUE, D1022:J1022)</f>
@@ -26637,10 +26631,10 @@
         <v>108</v>
       </c>
       <c r="E1023" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G1023" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="J1023" t="s">
         <v>201</v>
@@ -26661,10 +26655,10 @@
         <v>108</v>
       </c>
       <c r="E1024" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G1024" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="J1024" t="s">
         <v>236</v>
@@ -26685,10 +26679,10 @@
         <v>108</v>
       </c>
       <c r="E1025" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G1025" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="J1025" t="s">
         <v>237</v>
@@ -26709,10 +26703,10 @@
         <v>108</v>
       </c>
       <c r="E1026" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G1026" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="J1026" t="s">
         <v>128</v>
@@ -26773,7 +26767,7 @@
         <v>39</v>
       </c>
       <c r="K1032" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="1033" spans="1:11" x14ac:dyDescent="0.2">
@@ -26787,10 +26781,10 @@
         <v>108</v>
       </c>
       <c r="E1033" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G1033" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="K1033" t="str">
         <f t="shared" ref="K1033:K1043" si="110">_xlfn.TEXTJOIN("", TRUE, D1033:J1033)</f>
@@ -26808,10 +26802,10 @@
         <v>108</v>
       </c>
       <c r="E1034" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G1034" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="K1034" t="str">
         <f t="shared" si="110"/>
@@ -26829,10 +26823,10 @@
         <v>108</v>
       </c>
       <c r="E1035" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G1035" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="K1035" t="str">
         <f t="shared" si="110"/>
@@ -26850,10 +26844,10 @@
         <v>108</v>
       </c>
       <c r="E1036" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G1036" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="J1036" t="s">
         <v>236</v>
@@ -26874,10 +26868,10 @@
         <v>108</v>
       </c>
       <c r="E1037" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G1037" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="J1037" t="s">
         <v>236</v>
@@ -26898,10 +26892,10 @@
         <v>108</v>
       </c>
       <c r="E1038" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G1038" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="J1038" t="s">
         <v>128</v>
@@ -26922,10 +26916,10 @@
         <v>108</v>
       </c>
       <c r="E1039" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G1039" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="J1039" t="s">
         <v>128</v>
@@ -26946,10 +26940,10 @@
         <v>108</v>
       </c>
       <c r="E1040" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G1040" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="J1040" t="s">
         <v>128</v>
@@ -26970,10 +26964,10 @@
         <v>108</v>
       </c>
       <c r="E1041" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G1041" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="J1041" t="s">
         <v>128</v>
@@ -26994,13 +26988,13 @@
         <v>109</v>
       </c>
       <c r="E1042" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="F1042" t="s">
         <v>114</v>
       </c>
       <c r="G1042" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="J1042" t="s">
         <v>128</v>
@@ -27021,13 +27015,13 @@
         <v>109</v>
       </c>
       <c r="E1043" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="F1043" t="s">
         <v>114</v>
       </c>
       <c r="G1043" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="J1043" t="s">
         <v>128</v>
@@ -27073,7 +27067,7 @@
         <v>39</v>
       </c>
       <c r="K1048" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="1049" spans="1:11" x14ac:dyDescent="0.2">
@@ -27087,10 +27081,10 @@
         <v>108</v>
       </c>
       <c r="E1049" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="G1049" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="J1049" t="s">
         <v>201</v>
@@ -27111,10 +27105,10 @@
         <v>108</v>
       </c>
       <c r="E1050" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="G1050" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="J1050" t="s">
         <v>201</v>
@@ -27135,10 +27129,10 @@
         <v>108</v>
       </c>
       <c r="E1051" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="G1051" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="J1051" t="s">
         <v>236</v>
@@ -27159,10 +27153,10 @@
         <v>108</v>
       </c>
       <c r="E1052" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="G1052" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="J1052" t="s">
         <v>236</v>
@@ -27183,10 +27177,10 @@
         <v>108</v>
       </c>
       <c r="E1053" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="G1053" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="J1053" t="s">
         <v>236</v>
@@ -27247,7 +27241,7 @@
         <v>39</v>
       </c>
       <c r="K1059" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="1060" spans="1:11" x14ac:dyDescent="0.2">
@@ -27261,10 +27255,10 @@
         <v>108</v>
       </c>
       <c r="E1060" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="G1060" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="J1060" t="s">
         <v>201</v>
@@ -27285,10 +27279,10 @@
         <v>108</v>
       </c>
       <c r="E1061" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="G1061" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="J1061" t="s">
         <v>236</v>
@@ -27309,10 +27303,10 @@
         <v>108</v>
       </c>
       <c r="E1062" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="G1062" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="J1062" t="s">
         <v>236</v>
@@ -27333,10 +27327,10 @@
         <v>108</v>
       </c>
       <c r="E1063" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="G1063" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="J1063" t="s">
         <v>236</v>
@@ -27357,10 +27351,10 @@
         <v>108</v>
       </c>
       <c r="E1064" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="G1064" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="J1064" t="s">
         <v>236</v>
@@ -27381,10 +27375,10 @@
         <v>108</v>
       </c>
       <c r="E1065" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="G1065" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="J1065" t="s">
         <v>236</v>
@@ -27405,13 +27399,13 @@
         <v>108</v>
       </c>
       <c r="E1066" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="G1066" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="J1066" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K1066" t="str">
         <f t="shared" si="112"/>
@@ -27429,13 +27423,13 @@
         <v>108</v>
       </c>
       <c r="E1067" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="G1067" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="J1067" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K1067" t="str">
         <f t="shared" si="112"/>
@@ -27453,13 +27447,13 @@
         <v>108</v>
       </c>
       <c r="E1068" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="G1068" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="J1068" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="K1068" t="str">
         <f t="shared" si="112"/>
@@ -27477,13 +27471,13 @@
         <v>108</v>
       </c>
       <c r="E1069" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="G1069" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="J1069" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="K1069" t="str">
         <f t="shared" si="112"/>
@@ -27501,16 +27495,16 @@
         <v>109</v>
       </c>
       <c r="E1070" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="F1070" t="s">
         <v>114</v>
       </c>
       <c r="G1070" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="J1070" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K1070" t="str">
         <f t="shared" si="112"/>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892AB45D-60B7-EC4B-9DCB-CEC110A7DC57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181E7229-2626-644B-A843-16906D62F368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28800" yWindow="500" windowWidth="14660" windowHeight="16240" activeTab="5" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDB85DE-9336-7C44-B2C0-2763281AA6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5FEAD4-54F3-3C43-9DD8-1E2DF8CDC7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4720" yWindow="1320" windowWidth="20180" windowHeight="16240" activeTab="4" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="-21400" yWindow="500" windowWidth="20180" windowHeight="16240" activeTab="4" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5FEAD4-54F3-3C43-9DD8-1E2DF8CDC7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF0187C-B475-4E4F-9728-6B06706DC459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21400" yWindow="500" windowWidth="20180" windowHeight="16240" activeTab="4" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="-21400" yWindow="500" windowWidth="20180" windowHeight="16240" activeTab="2" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572965D0-70B1-7D4C-B525-65FF37DF30BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1FC0BD-37A7-AF45-9DAE-662FD4FCA442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6860" yWindow="1020" windowWidth="27740" windowHeight="19300" activeTab="5" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="5940" yWindow="500" windowWidth="27740" windowHeight="19300" activeTab="1" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5472" uniqueCount="1268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5475" uniqueCount="1270">
   <si>
     <t>page_id</t>
   </si>
@@ -3746,9 +3746,6 @@
     <t>Worte zu sprechen durch [Gottheit] / [König] / [Person] NN: Ich habe dir gegeben [Gaben], die bei mir sind.</t>
   </si>
   <si>
-    <t>Inschrift</t>
-  </si>
-  <si>
     <t>(AR; MR)</t>
   </si>
   <si>
@@ -3846,6 +3843,15 @@
   </si>
   <si>
     <t>(AR; Sp.)</t>
+  </si>
+  <si>
+    <t>[Szenentitel]</t>
+  </si>
+  <si>
+    <t>[Rückenschutzformel]</t>
+  </si>
+  <si>
+    <t>[Beziehung]</t>
   </si>
 </sst>
 </file>
@@ -3879,7 +3885,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3928,6 +3934,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -3941,7 +3953,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4005,6 +4017,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -4489,20 +4502,20 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="9" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="31" t="s">
         <v>1182</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="31">
         <v>70</v>
       </c>
     </row>
@@ -4632,7 +4645,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{244ECE21-4B85-B642-91D8-6A98EB98549E}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -4737,6 +4750,20 @@
       </c>
       <c r="D7" s="21">
         <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="31">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4751,7 +4778,7 @@
   <cols>
     <col min="1" max="1" width="14.83203125" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="4" customWidth="1"/>
     <col min="4" max="4" width="26" style="4" customWidth="1"/>
     <col min="5" max="5" width="23.83203125" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="4" bestFit="1" customWidth="1"/>
@@ -5175,8 +5202,8 @@
       <c r="B31" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="22" t="s">
-        <v>1234</v>
+      <c r="C31" s="21" t="s">
+        <v>563</v>
       </c>
       <c r="D31" s="22" t="s">
         <v>570</v>
@@ -6384,7 +6411,7 @@
         <v>45</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="N14" s="9" t="s">
         <v>92</v>
@@ -6431,7 +6458,7 @@
         <v>45</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>92</v>
@@ -6478,7 +6505,7 @@
         <v>45</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="N18" s="9" t="s">
         <v>92</v>
@@ -6525,7 +6552,7 @@
         <v>45</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>92</v>
@@ -6572,7 +6599,7 @@
         <v>45</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="N22" s="9" t="s">
         <v>92</v>
@@ -6619,7 +6646,7 @@
         <v>45</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="N24" s="9" t="s">
         <v>92</v>
@@ -7619,7 +7646,7 @@
         <v>45</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="N68" s="12" t="s">
         <v>92</v>
@@ -7707,7 +7734,7 @@
         <v>45</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="N72" s="12" t="s">
         <v>93</v>
@@ -7751,7 +7778,7 @@
         <v>45</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="N74" s="12" t="s">
         <v>93</v>
@@ -7795,7 +7822,7 @@
         <v>45</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="N76" s="12" t="s">
         <v>93</v>
@@ -7883,7 +7910,7 @@
         <v>45</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="N80" s="12" t="s">
         <v>95</v>
@@ -8349,7 +8376,7 @@
         <v>45</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="N108" s="16" t="s">
         <v>92</v>
@@ -8678,7 +8705,7 @@
         <v>45</v>
       </c>
       <c r="D123" s="18" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="N123" s="18" t="s">
         <v>93</v>
@@ -8695,7 +8722,7 @@
         <v>45</v>
       </c>
       <c r="D125" s="21" t="s">
-        <v>563</v>
+        <v>1269</v>
       </c>
       <c r="N125" s="21" t="s">
         <v>90</v>
@@ -8712,7 +8739,7 @@
         <v>45</v>
       </c>
       <c r="D126" s="21" t="s">
-        <v>589</v>
+        <v>1267</v>
       </c>
       <c r="N126" s="21" t="s">
         <v>90</v>
@@ -8749,7 +8776,7 @@
         <v>45</v>
       </c>
       <c r="D128" s="21" t="s">
-        <v>569</v>
+        <v>1268</v>
       </c>
       <c r="N128" s="21" t="s">
         <v>90</v>
@@ -9290,7 +9317,7 @@
         <v>45</v>
       </c>
       <c r="D157" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="N157" t="s">
         <v>92</v>
@@ -10161,13 +10188,13 @@
         <v>113</v>
       </c>
       <c r="I33" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J33" t="s">
         <v>1244</v>
       </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>1245</v>
-      </c>
-      <c r="K33" t="s">
-        <v>1246</v>
       </c>
       <c r="L33" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D33:K33)</f>
@@ -10273,13 +10300,13 @@
         <v>113</v>
       </c>
       <c r="I39" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J39" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K39" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L39" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D39:K39)</f>
@@ -10620,13 +10647,13 @@
         <v>113</v>
       </c>
       <c r="I56" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J56" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="K56" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L56" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D56:K56)</f>
@@ -10756,13 +10783,13 @@
         <v>113</v>
       </c>
       <c r="I63" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J63" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K63" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L63" t="str">
         <f t="shared" ref="L63:L65" si="10">_xlfn.TEXTJOIN("", TRUE, D63:K63)</f>
@@ -10789,13 +10816,13 @@
         <v>113</v>
       </c>
       <c r="I64" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J64" t="s">
         <v>1198</v>
       </c>
       <c r="K64" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L64" t="str">
         <f t="shared" si="10"/>
@@ -10822,13 +10849,13 @@
         <v>113</v>
       </c>
       <c r="I65" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J65" t="s">
         <v>1198</v>
       </c>
       <c r="K65" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L65" t="str">
         <f t="shared" si="10"/>
@@ -10934,13 +10961,13 @@
         <v>113</v>
       </c>
       <c r="I71" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J71" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="K71" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L71" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D71:K71)</f>
@@ -10991,13 +11018,13 @@
         <v>113</v>
       </c>
       <c r="I73" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J73" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K73" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L73" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D73:K73)</f>
@@ -11103,13 +11130,13 @@
         <v>113</v>
       </c>
       <c r="I79" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J79" t="s">
         <v>1198</v>
       </c>
       <c r="K79" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L79" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D79:K79)</f>
@@ -11160,13 +11187,13 @@
         <v>113</v>
       </c>
       <c r="I81" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J81" t="s">
         <v>1198</v>
       </c>
       <c r="K81" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L81" t="str">
         <f t="shared" ref="L81:L83" si="14">_xlfn.TEXTJOIN("", TRUE, D81:K81)</f>
@@ -11193,13 +11220,13 @@
         <v>113</v>
       </c>
       <c r="I82" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J82" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K82" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L82" t="str">
         <f t="shared" si="14"/>
@@ -11226,13 +11253,13 @@
         <v>113</v>
       </c>
       <c r="I83" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J83" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K83" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L83" t="str">
         <f t="shared" si="14"/>
@@ -11316,13 +11343,13 @@
         <v>113</v>
       </c>
       <c r="I86" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J86" t="s">
         <v>1198</v>
       </c>
       <c r="K86" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L86" t="str">
         <f t="shared" ref="L86:L87" si="16">_xlfn.TEXTJOIN("", TRUE, D86:K86)</f>
@@ -11352,13 +11379,13 @@
         <v>113</v>
       </c>
       <c r="I87" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J87" t="s">
         <v>1198</v>
       </c>
       <c r="K87" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L87" t="str">
         <f t="shared" si="16"/>
@@ -11618,13 +11645,13 @@
         <v>113</v>
       </c>
       <c r="I101" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J101" t="s">
         <v>1244</v>
       </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>1245</v>
-      </c>
-      <c r="K101" t="s">
-        <v>1246</v>
       </c>
       <c r="L101" t="str">
         <f t="shared" ref="L101:L109" si="21">_xlfn.TEXTJOIN("", TRUE, D101:K101)</f>
@@ -11651,13 +11678,13 @@
         <v>113</v>
       </c>
       <c r="I102" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J102" t="s">
         <v>1244</v>
       </c>
-      <c r="J102" t="s">
+      <c r="K102" t="s">
         <v>1245</v>
-      </c>
-      <c r="K102" t="s">
-        <v>1246</v>
       </c>
       <c r="L102" t="str">
         <f t="shared" si="21"/>
@@ -11684,13 +11711,13 @@
         <v>113</v>
       </c>
       <c r="I103" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J103" t="s">
         <v>1244</v>
       </c>
-      <c r="J103" t="s">
+      <c r="K103" t="s">
         <v>1245</v>
-      </c>
-      <c r="K103" t="s">
-        <v>1246</v>
       </c>
       <c r="L103" t="str">
         <f t="shared" si="21"/>
@@ -11717,13 +11744,13 @@
         <v>113</v>
       </c>
       <c r="I104" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J104" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="K104" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L104" t="str">
         <f t="shared" si="21"/>
@@ -11750,13 +11777,13 @@
         <v>113</v>
       </c>
       <c r="I105" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J105" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K105" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L105" t="str">
         <f t="shared" si="21"/>
@@ -11783,13 +11810,13 @@
         <v>113</v>
       </c>
       <c r="I106" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J106" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K106" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L106" t="str">
         <f t="shared" si="21"/>
@@ -11816,13 +11843,13 @@
         <v>113</v>
       </c>
       <c r="I107" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J107" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K107" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L107" t="str">
         <f t="shared" si="21"/>
@@ -11849,13 +11876,13 @@
         <v>113</v>
       </c>
       <c r="I108" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J108" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="K108" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L108" t="str">
         <f t="shared" si="21"/>
@@ -11882,13 +11909,13 @@
         <v>113</v>
       </c>
       <c r="I109" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J109" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="K109" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L109" t="str">
         <f t="shared" si="21"/>
@@ -12071,13 +12098,13 @@
         <v>113</v>
       </c>
       <c r="I116" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J116" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K116" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L116" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D116:K116)</f>
@@ -12204,13 +12231,13 @@
         <v>113</v>
       </c>
       <c r="I123" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J123" t="s">
         <v>1198</v>
       </c>
       <c r="K123" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L123" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D123:K123)</f>
@@ -12267,13 +12294,13 @@
         <v>113</v>
       </c>
       <c r="I125" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J125" t="s">
         <v>1244</v>
       </c>
-      <c r="J125" t="s">
+      <c r="K125" t="s">
         <v>1245</v>
-      </c>
-      <c r="K125" t="s">
-        <v>1246</v>
       </c>
       <c r="L125" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D125:K125)</f>
@@ -12864,13 +12891,13 @@
         <v>113</v>
       </c>
       <c r="I166" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J166" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K166" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L166" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D166:K166)</f>
@@ -13045,13 +13072,13 @@
         <v>113</v>
       </c>
       <c r="I175" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J175" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K175" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L175" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D175:K175)</f>
@@ -13316,13 +13343,13 @@
         <v>113</v>
       </c>
       <c r="I193" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J193" t="s">
         <v>1244</v>
       </c>
-      <c r="J193" t="s">
+      <c r="K193" t="s">
         <v>1245</v>
-      </c>
-      <c r="K193" t="s">
-        <v>1246</v>
       </c>
       <c r="L193" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D193:K193)</f>
@@ -13380,13 +13407,13 @@
         <v>113</v>
       </c>
       <c r="I197" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J197" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="K197" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L197" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D197:K197)</f>
@@ -13444,13 +13471,13 @@
         <v>113</v>
       </c>
       <c r="I201" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J201" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="K201" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L201" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D201:K201)</f>
@@ -13712,13 +13739,13 @@
         <v>113</v>
       </c>
       <c r="I226" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J226" t="s">
         <v>1198</v>
       </c>
       <c r="K226" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L226" t="str">
         <f t="shared" ref="L226:L228" si="48">_xlfn.TEXTJOIN("", TRUE, D226:K226)</f>
@@ -13745,13 +13772,13 @@
         <v>113</v>
       </c>
       <c r="I227" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J227" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="K227" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L227" t="str">
         <f t="shared" si="48"/>
@@ -13778,13 +13805,13 @@
         <v>113</v>
       </c>
       <c r="I228" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J228" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="K228" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L228" t="str">
         <f t="shared" si="48"/>
@@ -14837,13 +14864,13 @@
         <v>113</v>
       </c>
       <c r="I290" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J290" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K290" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L290" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D290:K290)</f>
@@ -15764,13 +15791,13 @@
         <v>113</v>
       </c>
       <c r="I348" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J348" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K348" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L348" t="str">
         <f t="shared" ref="L348:L349" si="75">_xlfn.TEXTJOIN("", TRUE, D348:K348)</f>
@@ -15797,13 +15824,13 @@
         <v>113</v>
       </c>
       <c r="I349" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J349" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K349" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L349" t="str">
         <f t="shared" si="75"/>
@@ -16167,13 +16194,13 @@
         <v>113</v>
       </c>
       <c r="I374" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J374" t="s">
         <v>1244</v>
       </c>
-      <c r="J374" t="s">
+      <c r="K374" t="s">
         <v>1245</v>
-      </c>
-      <c r="K374" t="s">
-        <v>1246</v>
       </c>
       <c r="L374" t="str">
         <f t="shared" ref="L374:L377" si="77">_xlfn.TEXTJOIN("", TRUE, D374:K374)</f>
@@ -16200,13 +16227,13 @@
         <v>113</v>
       </c>
       <c r="I375" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J375" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K375" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L375" t="str">
         <f t="shared" si="77"/>
@@ -16233,13 +16260,13 @@
         <v>113</v>
       </c>
       <c r="I376" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J376" t="s">
         <v>1198</v>
       </c>
       <c r="K376" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L376" t="str">
         <f t="shared" si="77"/>
@@ -16266,13 +16293,13 @@
         <v>113</v>
       </c>
       <c r="I377" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J377" t="s">
         <v>1198</v>
       </c>
       <c r="K377" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L377" t="str">
         <f t="shared" si="77"/>
@@ -16478,13 +16505,13 @@
         <v>113</v>
       </c>
       <c r="I390" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J390" t="s">
         <v>1198</v>
       </c>
       <c r="K390" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L390" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D390:K390)</f>
@@ -16663,13 +16690,13 @@
         <v>113</v>
       </c>
       <c r="I401" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J401" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="K401" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L401" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D401:K401)</f>
@@ -16822,13 +16849,13 @@
         <v>113</v>
       </c>
       <c r="I409" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J409" t="s">
         <v>1244</v>
       </c>
-      <c r="J409" t="s">
+      <c r="K409" t="s">
         <v>1245</v>
-      </c>
-      <c r="K409" t="s">
-        <v>1246</v>
       </c>
       <c r="L409" t="str">
         <f t="shared" ref="L409:L410" si="80">_xlfn.TEXTJOIN("", TRUE, D409:K409)</f>
@@ -16858,13 +16885,13 @@
         <v>113</v>
       </c>
       <c r="I410" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J410" t="s">
         <v>1244</v>
       </c>
-      <c r="J410" t="s">
+      <c r="K410" t="s">
         <v>1245</v>
-      </c>
-      <c r="K410" t="s">
-        <v>1246</v>
       </c>
       <c r="L410" t="str">
         <f t="shared" si="80"/>
@@ -17058,13 +17085,13 @@
         <v>113</v>
       </c>
       <c r="I421" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J421" t="s">
         <v>1198</v>
       </c>
       <c r="K421" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L421" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D421:K421)</f>
@@ -17122,13 +17149,13 @@
         <v>113</v>
       </c>
       <c r="I425" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J425" t="s">
         <v>1244</v>
       </c>
-      <c r="J425" t="s">
+      <c r="K425" t="s">
         <v>1245</v>
-      </c>
-      <c r="K425" t="s">
-        <v>1246</v>
       </c>
       <c r="L425" t="str">
         <f t="shared" ref="L425:L433" si="81">_xlfn.TEXTJOIN("", TRUE, D425:K425)</f>
@@ -17158,13 +17185,13 @@
         <v>113</v>
       </c>
       <c r="I426" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J426" t="s">
         <v>1244</v>
       </c>
-      <c r="J426" t="s">
+      <c r="K426" t="s">
         <v>1245</v>
-      </c>
-      <c r="K426" t="s">
-        <v>1246</v>
       </c>
       <c r="L426" t="str">
         <f t="shared" si="81"/>
@@ -17194,13 +17221,13 @@
         <v>113</v>
       </c>
       <c r="I427" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J427" t="s">
         <v>1244</v>
       </c>
-      <c r="J427" t="s">
+      <c r="K427" t="s">
         <v>1245</v>
-      </c>
-      <c r="K427" t="s">
-        <v>1246</v>
       </c>
       <c r="L427" t="str">
         <f t="shared" si="81"/>
@@ -17230,13 +17257,13 @@
         <v>113</v>
       </c>
       <c r="I428" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J428" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K428" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L428" t="str">
         <f t="shared" si="81"/>
@@ -17266,13 +17293,13 @@
         <v>113</v>
       </c>
       <c r="I429" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J429" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K429" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L429" t="str">
         <f t="shared" si="81"/>
@@ -17302,13 +17329,13 @@
         <v>113</v>
       </c>
       <c r="I430" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J430" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="K430" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L430" t="str">
         <f t="shared" si="81"/>
@@ -17338,13 +17365,13 @@
         <v>113</v>
       </c>
       <c r="I431" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J431" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K431" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L431" t="str">
         <f t="shared" si="81"/>
@@ -17374,13 +17401,13 @@
         <v>113</v>
       </c>
       <c r="I432" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J432" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K432" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L432" t="str">
         <f t="shared" si="81"/>
@@ -17410,13 +17437,13 @@
         <v>113</v>
       </c>
       <c r="I433" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J433" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K433" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L433" t="str">
         <f t="shared" si="81"/>
@@ -17543,13 +17570,13 @@
         <v>113</v>
       </c>
       <c r="I444" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J444" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K444" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L444" t="str">
         <f t="shared" ref="L444:L447" si="83">_xlfn.TEXTJOIN("", TRUE, D444:K444)</f>
@@ -17576,13 +17603,13 @@
         <v>113</v>
       </c>
       <c r="I445" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J445" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K445" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L445" t="str">
         <f t="shared" si="83"/>
@@ -17609,13 +17636,13 @@
         <v>113</v>
       </c>
       <c r="I446" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J446" t="s">
         <v>1198</v>
       </c>
       <c r="K446" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L446" t="str">
         <f t="shared" si="83"/>
@@ -17642,13 +17669,13 @@
         <v>113</v>
       </c>
       <c r="I447" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J447" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="K447" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L447" t="str">
         <f t="shared" si="83"/>
@@ -17858,13 +17885,13 @@
         <v>113</v>
       </c>
       <c r="I461" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J461" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="K461" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L461" t="str">
         <f t="shared" ref="L461:L463" si="84">_xlfn.TEXTJOIN("", TRUE, D461:K461)</f>
@@ -17891,13 +17918,13 @@
         <v>113</v>
       </c>
       <c r="I462" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J462" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K462" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L462" t="str">
         <f t="shared" si="84"/>
@@ -17924,13 +17951,13 @@
         <v>113</v>
       </c>
       <c r="I463" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J463" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K463" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L463" t="str">
         <f t="shared" si="84"/>
@@ -18233,13 +18260,13 @@
         <v>113</v>
       </c>
       <c r="I485" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J485" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="K485" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L485" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D485:K485)</f>
@@ -18297,13 +18324,13 @@
         <v>113</v>
       </c>
       <c r="I489" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J489" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="K489" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L489" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D489:K489)</f>
@@ -18361,13 +18388,13 @@
         <v>113</v>
       </c>
       <c r="I493" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J493" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="K493" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L493" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D493:K493)</f>
@@ -18701,13 +18728,13 @@
         <v>113</v>
       </c>
       <c r="I516" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J516" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K516" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L516" t="str">
         <f t="shared" ref="L516:L522" si="86">_xlfn.TEXTJOIN("", TRUE, D516:K516)</f>
@@ -18734,13 +18761,13 @@
         <v>113</v>
       </c>
       <c r="I517" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J517" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K517" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L517" t="str">
         <f t="shared" si="86"/>
@@ -18767,13 +18794,13 @@
         <v>113</v>
       </c>
       <c r="I518" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J518" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K518" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L518" t="str">
         <f t="shared" si="86"/>
@@ -18800,13 +18827,13 @@
         <v>113</v>
       </c>
       <c r="I519" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J519" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K519" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L519" t="str">
         <f t="shared" si="86"/>
@@ -18833,13 +18860,13 @@
         <v>113</v>
       </c>
       <c r="I520" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J520" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K520" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L520" t="str">
         <f t="shared" si="86"/>
@@ -18866,13 +18893,13 @@
         <v>113</v>
       </c>
       <c r="I521" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J521" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K521" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L521" t="str">
         <f t="shared" si="86"/>
@@ -18899,13 +18926,13 @@
         <v>113</v>
       </c>
       <c r="I522" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J522" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K522" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L522" t="str">
         <f t="shared" si="86"/>
@@ -19085,13 +19112,13 @@
         <v>113</v>
       </c>
       <c r="I531" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J531" t="s">
         <v>1198</v>
       </c>
       <c r="K531" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L531" t="str">
         <f t="shared" ref="L531:L532" si="87">_xlfn.TEXTJOIN("", TRUE, D531:K531)</f>
@@ -19121,13 +19148,13 @@
         <v>113</v>
       </c>
       <c r="I532" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J532" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K532" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L532" t="str">
         <f t="shared" si="87"/>
@@ -19377,13 +19404,13 @@
         <v>787</v>
       </c>
       <c r="I544" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J544" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="K544" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L544" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D544:K544)</f>
@@ -19593,13 +19620,13 @@
         <v>792</v>
       </c>
       <c r="I558" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J558" t="s">
         <v>1244</v>
       </c>
-      <c r="J558" t="s">
+      <c r="K558" t="s">
         <v>1245</v>
-      </c>
-      <c r="K558" t="s">
-        <v>1246</v>
       </c>
       <c r="L558" t="str">
         <f t="shared" ref="L558:L562" si="90">_xlfn.TEXTJOIN("", TRUE, D558:K558)</f>
@@ -19626,13 +19653,13 @@
         <v>793</v>
       </c>
       <c r="I559" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J559" t="s">
         <v>1244</v>
       </c>
-      <c r="J559" t="s">
+      <c r="K559" t="s">
         <v>1245</v>
-      </c>
-      <c r="K559" t="s">
-        <v>1246</v>
       </c>
       <c r="L559" t="str">
         <f t="shared" si="90"/>
@@ -19659,13 +19686,13 @@
         <v>794</v>
       </c>
       <c r="I560" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J560" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="K560" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L560" t="str">
         <f t="shared" si="90"/>
@@ -19692,13 +19719,13 @@
         <v>795</v>
       </c>
       <c r="I561" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J561" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K561" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L561" t="str">
         <f t="shared" si="90"/>
@@ -19725,13 +19752,13 @@
         <v>796</v>
       </c>
       <c r="I562" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J562" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="K562" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L562" t="str">
         <f t="shared" si="90"/>
@@ -19935,13 +19962,13 @@
         <v>801</v>
       </c>
       <c r="I581" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J581" t="s">
         <v>1244</v>
       </c>
-      <c r="J581" t="s">
+      <c r="K581" t="s">
         <v>1245</v>
-      </c>
-      <c r="K581" t="s">
-        <v>1246</v>
       </c>
       <c r="L581" t="str">
         <f t="shared" ref="L581:L582" si="91">_xlfn.TEXTJOIN("", TRUE, D581:K581)</f>
@@ -19965,13 +19992,13 @@
         <v>802</v>
       </c>
       <c r="I582" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J582" t="s">
         <v>1198</v>
       </c>
       <c r="K582" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L582" t="str">
         <f t="shared" si="91"/>
@@ -20087,13 +20114,13 @@
         <v>805</v>
       </c>
       <c r="I591" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J591" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K591" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L591" t="str">
         <f t="shared" ref="L591:L592" si="92">_xlfn.TEXTJOIN("", TRUE, D591:K591)</f>
@@ -20117,13 +20144,13 @@
         <v>806</v>
       </c>
       <c r="I592" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J592" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K592" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L592" t="str">
         <f t="shared" si="92"/>
@@ -20368,13 +20395,13 @@
         <v>820</v>
       </c>
       <c r="I609" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J609" t="s">
         <v>1244</v>
       </c>
-      <c r="J609" t="s">
+      <c r="K609" t="s">
         <v>1245</v>
-      </c>
-      <c r="K609" t="s">
-        <v>1246</v>
       </c>
       <c r="L609" t="str">
         <f t="shared" ref="L609:L619" si="94">_xlfn.TEXTJOIN("", TRUE, D609:K609)</f>
@@ -20398,13 +20425,13 @@
         <v>821</v>
       </c>
       <c r="I610" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J610" t="s">
         <v>1244</v>
       </c>
-      <c r="J610" t="s">
+      <c r="K610" t="s">
         <v>1245</v>
-      </c>
-      <c r="K610" t="s">
-        <v>1246</v>
       </c>
       <c r="L610" t="str">
         <f t="shared" si="94"/>
@@ -20428,13 +20455,13 @@
         <v>822</v>
       </c>
       <c r="I611" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J611" t="s">
         <v>1244</v>
       </c>
-      <c r="J611" t="s">
+      <c r="K611" t="s">
         <v>1245</v>
-      </c>
-      <c r="K611" t="s">
-        <v>1246</v>
       </c>
       <c r="L611" t="str">
         <f t="shared" si="94"/>
@@ -20458,13 +20485,13 @@
         <v>823</v>
       </c>
       <c r="I612" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J612" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K612" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L612" t="str">
         <f t="shared" si="94"/>
@@ -20488,13 +20515,13 @@
         <v>824</v>
       </c>
       <c r="I613" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J613" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="K613" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L613" t="str">
         <f t="shared" si="94"/>
@@ -20518,13 +20545,13 @@
         <v>825</v>
       </c>
       <c r="I614" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J614" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K614" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L614" t="str">
         <f t="shared" si="94"/>
@@ -20548,13 +20575,13 @@
         <v>818</v>
       </c>
       <c r="I615" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J615" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K615" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L615" t="str">
         <f t="shared" si="94"/>
@@ -20581,13 +20608,13 @@
         <v>859</v>
       </c>
       <c r="I616" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J616" t="s">
         <v>1244</v>
       </c>
-      <c r="J616" t="s">
+      <c r="K616" t="s">
         <v>1245</v>
-      </c>
-      <c r="K616" t="s">
-        <v>1246</v>
       </c>
       <c r="L616" t="str">
         <f t="shared" si="94"/>
@@ -20614,13 +20641,13 @@
         <v>860</v>
       </c>
       <c r="I617" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J617" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K617" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L617" t="str">
         <f t="shared" si="94"/>
@@ -20647,13 +20674,13 @@
         <v>861</v>
       </c>
       <c r="I618" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J618" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K618" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L618" t="str">
         <f t="shared" si="94"/>
@@ -20680,13 +20707,13 @@
         <v>862</v>
       </c>
       <c r="I619" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J619" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="K619" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L619" t="str">
         <f t="shared" si="94"/>
@@ -20803,13 +20830,13 @@
         <v>872</v>
       </c>
       <c r="I626" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J626" t="s">
         <v>1244</v>
       </c>
-      <c r="J626" t="s">
+      <c r="K626" t="s">
         <v>1245</v>
-      </c>
-      <c r="K626" t="s">
-        <v>1246</v>
       </c>
       <c r="L626" t="str">
         <f t="shared" ref="L626:L629" si="96">_xlfn.TEXTJOIN("", TRUE, D626:K626)</f>
@@ -20836,13 +20863,13 @@
         <v>873</v>
       </c>
       <c r="I627" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J627" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K627" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L627" t="str">
         <f t="shared" si="96"/>
@@ -20869,13 +20896,13 @@
         <v>874</v>
       </c>
       <c r="I628" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J628" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K628" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L628" t="str">
         <f t="shared" si="96"/>
@@ -20902,13 +20929,13 @@
         <v>875</v>
       </c>
       <c r="I629" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J629" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K629" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L629" t="str">
         <f t="shared" si="96"/>
@@ -20987,13 +21014,13 @@
         <v>877</v>
       </c>
       <c r="I634" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J634" t="s">
         <v>1244</v>
       </c>
-      <c r="J634" t="s">
+      <c r="K634" t="s">
         <v>1245</v>
-      </c>
-      <c r="K634" t="s">
-        <v>1246</v>
       </c>
       <c r="L634" t="str">
         <f t="shared" ref="L634:L637" si="97">_xlfn.TEXTJOIN("", TRUE, D634:K634)</f>
@@ -21020,13 +21047,13 @@
         <v>878</v>
       </c>
       <c r="I635" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J635" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K635" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L635" t="str">
         <f t="shared" si="97"/>
@@ -21053,13 +21080,13 @@
         <v>879</v>
       </c>
       <c r="I636" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J636" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K636" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L636" t="str">
         <f t="shared" si="97"/>
@@ -21086,13 +21113,13 @@
         <v>880</v>
       </c>
       <c r="I637" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J637" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="K637" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L637" t="str">
         <f t="shared" si="97"/>
@@ -21297,13 +21324,13 @@
         <v>887</v>
       </c>
       <c r="I651" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J651" t="s">
         <v>1244</v>
       </c>
-      <c r="J651" t="s">
+      <c r="K651" t="s">
         <v>1245</v>
-      </c>
-      <c r="K651" t="s">
-        <v>1246</v>
       </c>
       <c r="L651" t="str">
         <f t="shared" ref="L651:L660" si="99">_xlfn.TEXTJOIN("", TRUE, D651:K651)</f>
@@ -21327,13 +21354,13 @@
         <v>888</v>
       </c>
       <c r="I652" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J652" t="s">
         <v>1244</v>
       </c>
-      <c r="J652" t="s">
+      <c r="K652" t="s">
         <v>1245</v>
-      </c>
-      <c r="K652" t="s">
-        <v>1246</v>
       </c>
       <c r="L652" t="str">
         <f t="shared" si="99"/>
@@ -21357,13 +21384,13 @@
         <v>889</v>
       </c>
       <c r="I653" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J653" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K653" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L653" t="str">
         <f t="shared" si="99"/>
@@ -21387,13 +21414,13 @@
         <v>890</v>
       </c>
       <c r="I654" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J654" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K654" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L654" t="str">
         <f t="shared" si="99"/>
@@ -21417,13 +21444,13 @@
         <v>891</v>
       </c>
       <c r="I655" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J655" t="s">
         <v>1198</v>
       </c>
       <c r="K655" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L655" t="str">
         <f t="shared" si="99"/>
@@ -21447,13 +21474,13 @@
         <v>892</v>
       </c>
       <c r="I656" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J656" t="s">
         <v>1198</v>
       </c>
       <c r="K656" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L656" t="str">
         <f t="shared" si="99"/>
@@ -21477,13 +21504,13 @@
         <v>893</v>
       </c>
       <c r="I657" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J657" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K657" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L657" t="str">
         <f t="shared" si="99"/>
@@ -21507,13 +21534,13 @@
         <v>884</v>
       </c>
       <c r="I658" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J658" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K658" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L658" t="str">
         <f t="shared" si="99"/>
@@ -21540,13 +21567,13 @@
         <v>894</v>
       </c>
       <c r="I659" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J659" t="s">
         <v>1244</v>
       </c>
-      <c r="J659" t="s">
+      <c r="K659" t="s">
         <v>1245</v>
-      </c>
-      <c r="K659" t="s">
-        <v>1246</v>
       </c>
       <c r="L659" t="str">
         <f t="shared" si="99"/>
@@ -21573,13 +21600,13 @@
         <v>895</v>
       </c>
       <c r="I660" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J660" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K660" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L660" t="str">
         <f t="shared" si="99"/>
@@ -22012,13 +22039,13 @@
         <v>911</v>
       </c>
       <c r="I693" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J693" t="s">
         <v>1198</v>
       </c>
       <c r="K693" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L693" t="str">
         <f t="shared" ref="L693:L696" si="101">_xlfn.TEXTJOIN("", TRUE, D693:K693)</f>
@@ -22042,13 +22069,13 @@
         <v>912</v>
       </c>
       <c r="I694" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J694" t="s">
         <v>1198</v>
       </c>
       <c r="K694" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L694" t="str">
         <f t="shared" si="101"/>
@@ -22072,13 +22099,13 @@
         <v>913</v>
       </c>
       <c r="I695" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J695" t="s">
         <v>1198</v>
       </c>
       <c r="K695" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L695" t="str">
         <f t="shared" si="101"/>
@@ -22102,13 +22129,13 @@
         <v>914</v>
       </c>
       <c r="I696" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J696" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K696" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L696" t="str">
         <f t="shared" si="101"/>
@@ -22454,13 +22481,13 @@
         <v>930</v>
       </c>
       <c r="I717" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J717" t="s">
         <v>1198</v>
       </c>
       <c r="K717" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L717" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D717:K717)</f>
@@ -22559,13 +22586,13 @@
         <v>932</v>
       </c>
       <c r="I725" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J725" t="s">
         <v>1244</v>
       </c>
-      <c r="J725" t="s">
+      <c r="K725" t="s">
         <v>1245</v>
-      </c>
-      <c r="K725" t="s">
-        <v>1246</v>
       </c>
       <c r="L725" t="str">
         <f t="shared" ref="L725:L729" si="104">_xlfn.TEXTJOIN("", TRUE, D725:K725)</f>
@@ -22589,13 +22616,13 @@
         <v>933</v>
       </c>
       <c r="I726" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J726" t="s">
         <v>1244</v>
       </c>
-      <c r="J726" t="s">
+      <c r="K726" t="s">
         <v>1245</v>
-      </c>
-      <c r="K726" t="s">
-        <v>1246</v>
       </c>
       <c r="L726" t="str">
         <f t="shared" si="104"/>
@@ -22619,13 +22646,13 @@
         <v>934</v>
       </c>
       <c r="I727" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J727" t="s">
         <v>1244</v>
       </c>
-      <c r="J727" t="s">
+      <c r="K727" t="s">
         <v>1245</v>
-      </c>
-      <c r="K727" t="s">
-        <v>1246</v>
       </c>
       <c r="L727" t="str">
         <f t="shared" si="104"/>
@@ -22649,13 +22676,13 @@
         <v>935</v>
       </c>
       <c r="I728" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J728" t="s">
         <v>1198</v>
       </c>
       <c r="K728" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L728" t="str">
         <f t="shared" si="104"/>
@@ -22679,13 +22706,13 @@
         <v>936</v>
       </c>
       <c r="I729" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J729" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K729" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L729" t="str">
         <f t="shared" si="104"/>
@@ -22784,13 +22811,13 @@
         <v>938</v>
       </c>
       <c r="I737" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J737" t="s">
         <v>1244</v>
       </c>
-      <c r="J737" t="s">
+      <c r="K737" t="s">
         <v>1245</v>
-      </c>
-      <c r="K737" t="s">
-        <v>1246</v>
       </c>
       <c r="L737" t="str">
         <f t="shared" ref="L737:L742" si="106">_xlfn.TEXTJOIN("", TRUE, D737:K737)</f>
@@ -22814,13 +22841,13 @@
         <v>939</v>
       </c>
       <c r="I738" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J738" t="s">
         <v>1198</v>
       </c>
       <c r="K738" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L738" t="str">
         <f t="shared" si="106"/>
@@ -22844,13 +22871,13 @@
         <v>940</v>
       </c>
       <c r="I739" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J739" t="s">
         <v>1198</v>
       </c>
       <c r="K739" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L739" t="str">
         <f t="shared" si="106"/>
@@ -22874,13 +22901,13 @@
         <v>941</v>
       </c>
       <c r="I740" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J740" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="K740" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L740" t="str">
         <f t="shared" si="106"/>
@@ -22904,13 +22931,13 @@
         <v>942</v>
       </c>
       <c r="I741" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J741" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K741" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L741" t="str">
         <f t="shared" si="106"/>
@@ -22934,13 +22961,13 @@
         <v>943</v>
       </c>
       <c r="I742" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J742" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K742" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L742" t="str">
         <f t="shared" si="106"/>
@@ -23060,13 +23087,13 @@
         <v>946</v>
       </c>
       <c r="I751" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J751" t="s">
         <v>1198</v>
       </c>
       <c r="K751" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L751" t="str">
         <f t="shared" ref="L751:L755" si="108">_xlfn.TEXTJOIN("", TRUE, D751:K751)</f>
@@ -23090,13 +23117,13 @@
         <v>947</v>
       </c>
       <c r="I752" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J752" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K752" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L752" t="str">
         <f t="shared" si="108"/>
@@ -23120,13 +23147,13 @@
         <v>948</v>
       </c>
       <c r="I753" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J753" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K753" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L753" t="str">
         <f t="shared" si="108"/>
@@ -23153,13 +23180,13 @@
         <v>949</v>
       </c>
       <c r="I754" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J754" t="s">
         <v>1198</v>
       </c>
       <c r="K754" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L754" t="str">
         <f t="shared" si="108"/>
@@ -23186,13 +23213,13 @@
         <v>950</v>
       </c>
       <c r="I755" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J755" t="s">
         <v>1198</v>
       </c>
       <c r="K755" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L755" t="str">
         <f t="shared" si="108"/>
@@ -23297,13 +23324,13 @@
         <v>953</v>
       </c>
       <c r="I763" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J763" t="s">
         <v>1198</v>
       </c>
       <c r="K763" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L763" t="str">
         <f t="shared" ref="L763:L765" si="109">_xlfn.TEXTJOIN("", TRUE, D763:K763)</f>
@@ -23327,13 +23354,13 @@
         <v>954</v>
       </c>
       <c r="I764" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J764" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K764" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L764" t="str">
         <f t="shared" si="109"/>
@@ -23363,13 +23390,13 @@
         <v>113</v>
       </c>
       <c r="I765" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J765" t="s">
         <v>1244</v>
       </c>
-      <c r="J765" t="s">
+      <c r="K765" t="s">
         <v>1245</v>
-      </c>
-      <c r="K765" t="s">
-        <v>1246</v>
       </c>
       <c r="L765" t="str">
         <f t="shared" si="109"/>
@@ -23453,13 +23480,13 @@
         <v>957</v>
       </c>
       <c r="I772" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J772" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="K772" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L772" t="str">
         <f t="shared" ref="L772:L778" si="111">_xlfn.TEXTJOIN("", TRUE, D772:K772)</f>
@@ -23483,13 +23510,13 @@
         <v>958</v>
       </c>
       <c r="I773" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J773" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K773" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L773" t="str">
         <f t="shared" si="111"/>
@@ -23513,13 +23540,13 @@
         <v>959</v>
       </c>
       <c r="I774" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J774" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K774" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L774" t="str">
         <f t="shared" si="111"/>
@@ -23546,13 +23573,13 @@
         <v>960</v>
       </c>
       <c r="I775" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J775" t="s">
         <v>1244</v>
       </c>
-      <c r="J775" t="s">
+      <c r="K775" t="s">
         <v>1245</v>
-      </c>
-      <c r="K775" t="s">
-        <v>1246</v>
       </c>
       <c r="L775" t="str">
         <f t="shared" si="111"/>
@@ -23579,13 +23606,13 @@
         <v>961</v>
       </c>
       <c r="I776" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J776" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K776" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L776" t="str">
         <f t="shared" si="111"/>
@@ -23612,13 +23639,13 @@
         <v>962</v>
       </c>
       <c r="I777" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J777" t="s">
         <v>1198</v>
       </c>
       <c r="K777" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L777" t="str">
         <f t="shared" si="111"/>
@@ -23645,13 +23672,13 @@
         <v>963</v>
       </c>
       <c r="I778" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J778" t="s">
         <v>1198</v>
       </c>
       <c r="K778" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L778" t="str">
         <f t="shared" si="111"/>
@@ -23807,13 +23834,13 @@
         <v>965</v>
       </c>
       <c r="I792" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J792" t="s">
         <v>1244</v>
       </c>
-      <c r="J792" t="s">
+      <c r="K792" t="s">
         <v>1245</v>
-      </c>
-      <c r="K792" t="s">
-        <v>1246</v>
       </c>
       <c r="L792" t="str">
         <f t="shared" ref="L792:L796" si="113">_xlfn.TEXTJOIN("", TRUE, D792:K792)</f>
@@ -23837,13 +23864,13 @@
         <v>966</v>
       </c>
       <c r="I793" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J793" t="s">
         <v>1244</v>
       </c>
-      <c r="J793" t="s">
+      <c r="K793" t="s">
         <v>1245</v>
-      </c>
-      <c r="K793" t="s">
-        <v>1246</v>
       </c>
       <c r="L793" t="str">
         <f t="shared" si="113"/>
@@ -23867,13 +23894,13 @@
         <v>967</v>
       </c>
       <c r="I794" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J794" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="K794" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L794" t="str">
         <f t="shared" si="113"/>
@@ -23897,13 +23924,13 @@
         <v>968</v>
       </c>
       <c r="I795" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J795" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="K795" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L795" t="str">
         <f t="shared" si="113"/>
@@ -23927,13 +23954,13 @@
         <v>969</v>
       </c>
       <c r="I796" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J796" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="K796" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L796" t="str">
         <f t="shared" si="113"/>
@@ -24011,13 +24038,13 @@
         <v>970</v>
       </c>
       <c r="I803" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J803" t="s">
         <v>1244</v>
       </c>
-      <c r="J803" t="s">
+      <c r="K803" t="s">
         <v>1245</v>
-      </c>
-      <c r="K803" t="s">
-        <v>1246</v>
       </c>
       <c r="L803" t="str">
         <f t="shared" ref="L803:L814" si="114">_xlfn.TEXTJOIN("", TRUE, D803:K803)</f>
@@ -24041,13 +24068,13 @@
         <v>971</v>
       </c>
       <c r="I804" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J804" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K804" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L804" t="str">
         <f t="shared" si="114"/>
@@ -24071,13 +24098,13 @@
         <v>972</v>
       </c>
       <c r="I805" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J805" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K805" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L805" t="str">
         <f t="shared" si="114"/>
@@ -24101,13 +24128,13 @@
         <v>973</v>
       </c>
       <c r="I806" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J806" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K806" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L806" t="str">
         <f t="shared" si="114"/>
@@ -24131,13 +24158,13 @@
         <v>974</v>
       </c>
       <c r="I807" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J807" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K807" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L807" t="str">
         <f t="shared" si="114"/>
@@ -24161,13 +24188,13 @@
         <v>975</v>
       </c>
       <c r="I808" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J808" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K808" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L808" t="str">
         <f t="shared" si="114"/>
@@ -24191,13 +24218,13 @@
         <v>976</v>
       </c>
       <c r="I809" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J809" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K809" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L809" t="str">
         <f t="shared" si="114"/>
@@ -24221,13 +24248,13 @@
         <v>977</v>
       </c>
       <c r="I810" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J810" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="K810" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L810" t="str">
         <f t="shared" si="114"/>
@@ -24251,13 +24278,13 @@
         <v>978</v>
       </c>
       <c r="I811" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J811" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="K811" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L811" t="str">
         <f t="shared" si="114"/>
@@ -24281,13 +24308,13 @@
         <v>981</v>
       </c>
       <c r="I812" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J812" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="K812" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L812" t="str">
         <f t="shared" si="114"/>
@@ -24311,13 +24338,13 @@
         <v>982</v>
       </c>
       <c r="I813" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J813" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="K813" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L813" t="str">
         <f t="shared" si="114"/>
@@ -24341,13 +24368,13 @@
         <v>983</v>
       </c>
       <c r="I814" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J814" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="K814" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L814" t="str">
         <f t="shared" si="114"/>
@@ -24479,13 +24506,13 @@
         <v>985</v>
       </c>
       <c r="I823" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J823" t="s">
         <v>1244</v>
       </c>
-      <c r="J823" t="s">
+      <c r="K823" t="s">
         <v>1245</v>
-      </c>
-      <c r="K823" t="s">
-        <v>1246</v>
       </c>
       <c r="L823" t="str">
         <f t="shared" ref="L823:L824" si="116">_xlfn.TEXTJOIN("", TRUE, D823:K823)</f>
@@ -24509,13 +24536,13 @@
         <v>986</v>
       </c>
       <c r="I824" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J824" t="s">
         <v>1244</v>
       </c>
-      <c r="J824" t="s">
+      <c r="K824" t="s">
         <v>1245</v>
-      </c>
-      <c r="K824" t="s">
-        <v>1246</v>
       </c>
       <c r="L824" t="str">
         <f t="shared" si="116"/>
@@ -24635,13 +24662,13 @@
         <v>989</v>
       </c>
       <c r="I833" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J833" t="s">
         <v>1244</v>
       </c>
-      <c r="J833" t="s">
+      <c r="K833" t="s">
         <v>1245</v>
-      </c>
-      <c r="K833" t="s">
-        <v>1246</v>
       </c>
       <c r="L833" t="str">
         <f t="shared" ref="L833:L834" si="118">_xlfn.TEXTJOIN("", TRUE, D833:K833)</f>
@@ -24665,13 +24692,13 @@
         <v>990</v>
       </c>
       <c r="I834" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J834" t="s">
         <v>1198</v>
       </c>
       <c r="K834" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L834" t="str">
         <f t="shared" si="118"/>
@@ -24746,13 +24773,13 @@
         <v>993</v>
       </c>
       <c r="I837" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J837" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="K837" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L837" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D837:K837)</f>
@@ -24824,13 +24851,13 @@
         <v>113</v>
       </c>
       <c r="I842" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J842" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="K842" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L842" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D842:K842)</f>
@@ -24966,13 +24993,13 @@
         <v>1001</v>
       </c>
       <c r="I854" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J854" t="s">
         <v>1244</v>
       </c>
-      <c r="J854" t="s">
+      <c r="K854" t="s">
         <v>1245</v>
-      </c>
-      <c r="K854" t="s">
-        <v>1246</v>
       </c>
       <c r="L854" t="str">
         <f t="shared" ref="L854:L856" si="120">_xlfn.TEXTJOIN("", TRUE, D854:K854)</f>
@@ -24996,13 +25023,13 @@
         <v>1002</v>
       </c>
       <c r="I855" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J855" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K855" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L855" t="str">
         <f t="shared" si="120"/>
@@ -25026,13 +25053,13 @@
         <v>1003</v>
       </c>
       <c r="I856" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J856" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="K856" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L856" t="str">
         <f t="shared" si="120"/>
@@ -25185,13 +25212,13 @@
         <v>1008</v>
       </c>
       <c r="I866" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J866" t="s">
         <v>1244</v>
       </c>
-      <c r="J866" t="s">
+      <c r="K866" t="s">
         <v>1245</v>
-      </c>
-      <c r="K866" t="s">
-        <v>1246</v>
       </c>
       <c r="L866" t="str">
         <f t="shared" ref="L866:L867" si="121">_xlfn.TEXTJOIN("", TRUE, D866:K866)</f>
@@ -25215,13 +25242,13 @@
         <v>1009</v>
       </c>
       <c r="I867" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J867" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K867" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L867" t="str">
         <f t="shared" si="121"/>
@@ -25418,13 +25445,13 @@
         <v>113</v>
       </c>
       <c r="I881" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J881" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="K881" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L881" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D881:K881)</f>
@@ -25779,13 +25806,13 @@
         <v>1034</v>
       </c>
       <c r="I907" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J907" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="K907" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L907" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D907:K907)</f>
@@ -25980,13 +26007,13 @@
         <v>1041</v>
       </c>
       <c r="I919" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J919" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K919" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L919" t="str">
         <f t="shared" ref="L919:L920" si="123">_xlfn.TEXTJOIN("", TRUE, D919:K919)</f>
@@ -26010,13 +26037,13 @@
         <v>1042</v>
       </c>
       <c r="I920" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J920" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K920" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L920" t="str">
         <f t="shared" si="123"/>
@@ -26169,13 +26196,13 @@
         <v>1047</v>
       </c>
       <c r="I930" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J930" t="s">
         <v>1198</v>
       </c>
       <c r="K930" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L930" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D930:K930)</f>
@@ -26316,13 +26343,13 @@
         <v>1051</v>
       </c>
       <c r="I940" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J940" t="s">
         <v>1198</v>
       </c>
       <c r="K940" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L940" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D940:K940)</f>
@@ -26472,13 +26499,13 @@
         <v>1056</v>
       </c>
       <c r="I950" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J950" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="K950" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L950" t="str">
         <f t="shared" ref="L950:L953" si="125">_xlfn.TEXTJOIN("", TRUE, D950:K950)</f>
@@ -26502,13 +26529,13 @@
         <v>1057</v>
       </c>
       <c r="I951" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J951" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K951" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L951" t="str">
         <f t="shared" si="125"/>
@@ -26532,13 +26559,13 @@
         <v>1058</v>
       </c>
       <c r="I952" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J952" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K952" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L952" t="str">
         <f t="shared" si="125"/>
@@ -26562,13 +26589,13 @@
         <v>1059</v>
       </c>
       <c r="I953" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J953" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K953" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L953" t="str">
         <f t="shared" si="125"/>
@@ -26700,13 +26727,13 @@
         <v>1063</v>
       </c>
       <c r="I962" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J962" t="s">
         <v>1244</v>
       </c>
-      <c r="J962" t="s">
+      <c r="K962" t="s">
         <v>1245</v>
-      </c>
-      <c r="K962" t="s">
-        <v>1246</v>
       </c>
       <c r="L962" t="str">
         <f t="shared" ref="L962:L966" si="127">_xlfn.TEXTJOIN("", TRUE, D962:K962)</f>
@@ -26730,13 +26757,13 @@
         <v>1064</v>
       </c>
       <c r="I963" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J963" t="s">
         <v>1244</v>
       </c>
-      <c r="J963" t="s">
+      <c r="K963" t="s">
         <v>1245</v>
-      </c>
-      <c r="K963" t="s">
-        <v>1246</v>
       </c>
       <c r="L963" t="str">
         <f t="shared" si="127"/>
@@ -26760,13 +26787,13 @@
         <v>1065</v>
       </c>
       <c r="I964" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J964" t="s">
         <v>1198</v>
       </c>
       <c r="K964" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L964" t="str">
         <f t="shared" si="127"/>
@@ -26790,13 +26817,13 @@
         <v>1066</v>
       </c>
       <c r="I965" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J965" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K965" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L965" t="str">
         <f t="shared" si="127"/>
@@ -26820,13 +26847,13 @@
         <v>1067</v>
       </c>
       <c r="I966" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J966" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K966" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L966" t="str">
         <f t="shared" si="127"/>
@@ -27009,13 +27036,13 @@
         <v>1071</v>
       </c>
       <c r="I981" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J981" t="s">
         <v>1244</v>
       </c>
-      <c r="J981" t="s">
+      <c r="K981" t="s">
         <v>1245</v>
-      </c>
-      <c r="K981" t="s">
-        <v>1246</v>
       </c>
       <c r="L981" t="str">
         <f t="shared" ref="L981:L984" si="129">_xlfn.TEXTJOIN("", TRUE, D981:K981)</f>
@@ -27039,13 +27066,13 @@
         <v>1072</v>
       </c>
       <c r="I982" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J982" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K982" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L982" t="str">
         <f t="shared" si="129"/>
@@ -27069,13 +27096,13 @@
         <v>1073</v>
       </c>
       <c r="I983" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J983" t="s">
         <v>1198</v>
       </c>
       <c r="K983" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L983" t="str">
         <f t="shared" si="129"/>
@@ -27099,13 +27126,13 @@
         <v>1074</v>
       </c>
       <c r="I984" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J984" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="K984" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L984" t="str">
         <f t="shared" si="129"/>
@@ -27237,13 +27264,13 @@
         <v>1081</v>
       </c>
       <c r="I992" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J992" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K992" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L992" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D992:K992)</f>
@@ -27322,13 +27349,13 @@
         <v>1084</v>
       </c>
       <c r="I997" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J997" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="K997" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L997" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D997:K997)</f>
@@ -27401,13 +27428,13 @@
         <v>1087</v>
       </c>
       <c r="I1003" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J1003" t="s">
         <v>1244</v>
       </c>
-      <c r="J1003" t="s">
+      <c r="K1003" t="s">
         <v>1245</v>
-      </c>
-      <c r="K1003" t="s">
-        <v>1246</v>
       </c>
       <c r="L1003" t="str">
         <f t="shared" ref="L1003:L1013" si="131">_xlfn.TEXTJOIN("", TRUE, D1003:K1003)</f>
@@ -27431,13 +27458,13 @@
         <v>1088</v>
       </c>
       <c r="I1004" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1004" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K1004" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1004" t="str">
         <f t="shared" si="131"/>
@@ -27461,13 +27488,13 @@
         <v>1089</v>
       </c>
       <c r="I1005" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1005" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="K1005" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1005" t="str">
         <f t="shared" si="131"/>
@@ -27491,13 +27518,13 @@
         <v>1090</v>
       </c>
       <c r="I1006" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1006" t="s">
         <v>1198</v>
       </c>
       <c r="K1006" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1006" t="str">
         <f t="shared" si="131"/>
@@ -27521,13 +27548,13 @@
         <v>1091</v>
       </c>
       <c r="I1007" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1007" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="K1007" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1007" t="str">
         <f t="shared" si="131"/>
@@ -27551,13 +27578,13 @@
         <v>1092</v>
       </c>
       <c r="I1008" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1008" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="K1008" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1008" t="str">
         <f t="shared" si="131"/>
@@ -27581,13 +27608,13 @@
         <v>1093</v>
       </c>
       <c r="I1009" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1009" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="K1009" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1009" t="str">
         <f t="shared" si="131"/>
@@ -27611,13 +27638,13 @@
         <v>1094</v>
       </c>
       <c r="I1010" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1010" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="K1010" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1010" t="str">
         <f t="shared" si="131"/>
@@ -27641,13 +27668,13 @@
         <v>1095</v>
       </c>
       <c r="I1011" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1011" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="K1011" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1011" t="str">
         <f t="shared" si="131"/>
@@ -27671,13 +27698,13 @@
         <v>1096</v>
       </c>
       <c r="I1012" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1012" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K1012" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1012" t="str">
         <f t="shared" si="131"/>
@@ -27701,13 +27728,13 @@
         <v>1085</v>
       </c>
       <c r="I1013" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1013" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K1013" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1013" t="str">
         <f t="shared" si="131"/>
@@ -27782,13 +27809,13 @@
         <v>1099</v>
       </c>
       <c r="I1016" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1016" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K1016" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1016" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D1016:K1016)</f>
@@ -27872,13 +27899,13 @@
         <v>1101</v>
       </c>
       <c r="I1023" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J1023" t="s">
         <v>1244</v>
       </c>
-      <c r="J1023" t="s">
+      <c r="K1023" t="s">
         <v>1245</v>
-      </c>
-      <c r="K1023" t="s">
-        <v>1246</v>
       </c>
       <c r="L1023" t="str">
         <f t="shared" ref="L1023:L1026" si="133">_xlfn.TEXTJOIN("", TRUE, D1023:K1023)</f>
@@ -27902,13 +27929,13 @@
         <v>1102</v>
       </c>
       <c r="I1024" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1024" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K1024" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1024" t="str">
         <f t="shared" si="133"/>
@@ -27932,13 +27959,13 @@
         <v>1103</v>
       </c>
       <c r="I1025" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1025" t="s">
         <v>1198</v>
       </c>
       <c r="K1025" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1025" t="str">
         <f t="shared" si="133"/>
@@ -27962,13 +27989,13 @@
         <v>1104</v>
       </c>
       <c r="I1026" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1026" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K1026" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1026" t="str">
         <f t="shared" si="133"/>
@@ -28109,13 +28136,13 @@
         <v>1109</v>
       </c>
       <c r="I1036" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1036" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K1036" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1036" t="str">
         <f t="shared" ref="L1036:L1043" si="135">_xlfn.TEXTJOIN("", TRUE, D1036:K1036)</f>
@@ -28139,13 +28166,13 @@
         <v>1110</v>
       </c>
       <c r="I1037" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1037" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K1037" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1037" t="str">
         <f t="shared" si="135"/>
@@ -28169,13 +28196,13 @@
         <v>1111</v>
       </c>
       <c r="I1038" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1038" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K1038" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1038" t="str">
         <f t="shared" si="135"/>
@@ -28199,13 +28226,13 @@
         <v>1112</v>
       </c>
       <c r="I1039" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1039" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K1039" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1039" t="str">
         <f t="shared" si="135"/>
@@ -28229,13 +28256,13 @@
         <v>1113</v>
       </c>
       <c r="I1040" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1040" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K1040" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1040" t="str">
         <f t="shared" si="135"/>
@@ -28259,13 +28286,13 @@
         <v>1105</v>
       </c>
       <c r="I1041" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1041" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K1041" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1041" t="str">
         <f t="shared" si="135"/>
@@ -28292,13 +28319,13 @@
         <v>1114</v>
       </c>
       <c r="I1042" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1042" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K1042" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1042" t="str">
         <f t="shared" si="135"/>
@@ -28325,13 +28352,13 @@
         <v>1115</v>
       </c>
       <c r="I1043" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1043" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K1043" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1043" t="str">
         <f t="shared" si="135"/>
@@ -28394,13 +28421,13 @@
         <v>1116</v>
       </c>
       <c r="I1049" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J1049" t="s">
         <v>1244</v>
       </c>
-      <c r="J1049" t="s">
+      <c r="K1049" t="s">
         <v>1245</v>
-      </c>
-      <c r="K1049" t="s">
-        <v>1246</v>
       </c>
       <c r="L1049" t="str">
         <f t="shared" ref="L1049:L1053" si="136">_xlfn.TEXTJOIN("", TRUE, D1049:K1049)</f>
@@ -28424,13 +28451,13 @@
         <v>1117</v>
       </c>
       <c r="I1050" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J1050" t="s">
         <v>1244</v>
       </c>
-      <c r="J1050" t="s">
+      <c r="K1050" t="s">
         <v>1245</v>
-      </c>
-      <c r="K1050" t="s">
-        <v>1246</v>
       </c>
       <c r="L1050" t="str">
         <f t="shared" si="136"/>
@@ -28454,13 +28481,13 @@
         <v>1118</v>
       </c>
       <c r="I1051" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1051" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K1051" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1051" t="str">
         <f t="shared" si="136"/>
@@ -28484,13 +28511,13 @@
         <v>1119</v>
       </c>
       <c r="I1052" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1052" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K1052" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1052" t="str">
         <f t="shared" si="136"/>
@@ -28514,13 +28541,13 @@
         <v>1120</v>
       </c>
       <c r="I1053" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1053" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K1053" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1053" t="str">
         <f t="shared" si="136"/>
@@ -28598,13 +28625,13 @@
         <v>1121</v>
       </c>
       <c r="I1060" t="s">
+        <v>1243</v>
+      </c>
+      <c r="J1060" t="s">
         <v>1244</v>
       </c>
-      <c r="J1060" t="s">
+      <c r="K1060" t="s">
         <v>1245</v>
-      </c>
-      <c r="K1060" t="s">
-        <v>1246</v>
       </c>
       <c r="L1060" t="str">
         <f t="shared" ref="L1060:L1070" si="138">_xlfn.TEXTJOIN("", TRUE, D1060:K1060)</f>
@@ -28628,13 +28655,13 @@
         <v>1122</v>
       </c>
       <c r="I1061" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1061" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K1061" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1061" t="str">
         <f t="shared" si="138"/>
@@ -28658,13 +28685,13 @@
         <v>1123</v>
       </c>
       <c r="I1062" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1062" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K1062" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1062" t="str">
         <f t="shared" si="138"/>
@@ -28688,13 +28715,13 @@
         <v>1124</v>
       </c>
       <c r="I1063" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1063" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K1063" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1063" t="str">
         <f t="shared" si="138"/>
@@ -28718,13 +28745,13 @@
         <v>1125</v>
       </c>
       <c r="I1064" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1064" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K1064" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1064" t="str">
         <f t="shared" si="138"/>
@@ -28748,13 +28775,13 @@
         <v>1126</v>
       </c>
       <c r="I1065" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1065" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K1065" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1065" t="str">
         <f t="shared" si="138"/>
@@ -28778,13 +28805,13 @@
         <v>1127</v>
       </c>
       <c r="I1066" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1066" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="K1066" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1066" t="str">
         <f t="shared" si="138"/>
@@ -28808,13 +28835,13 @@
         <v>1128</v>
       </c>
       <c r="I1067" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1067" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="K1067" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1067" t="str">
         <f t="shared" si="138"/>
@@ -28838,13 +28865,13 @@
         <v>1129</v>
       </c>
       <c r="I1068" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1068" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="K1068" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1068" t="str">
         <f t="shared" si="138"/>
@@ -28868,13 +28895,13 @@
         <v>1130</v>
       </c>
       <c r="I1069" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1069" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="K1069" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1069" t="str">
         <f t="shared" si="138"/>
@@ -28901,13 +28928,13 @@
         <v>1131</v>
       </c>
       <c r="I1070" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J1070" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="K1070" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="L1070" t="str">
         <f t="shared" si="138"/>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1FC0BD-37A7-AF45-9DAE-662FD4FCA442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DD6DC7-2897-4149-BA23-6CC88C59D1A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5940" yWindow="500" windowWidth="27740" windowHeight="19300" activeTab="1" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="5720" yWindow="500" windowWidth="27740" windowHeight="19300" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5475" uniqueCount="1270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5472" uniqueCount="1270">
   <si>
     <t>page_id</t>
   </si>
@@ -4645,7 +4645,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{244ECE21-4B85-B642-91D8-6A98EB98549E}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -4750,20 +4750,6 @@
       </c>
       <c r="D7" s="21">
         <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="31">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8783D71-99A1-694A-A8CC-137AEDA0240A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589C6578-A421-524E-90D6-1F77991CC40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28800" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="5" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5476" uniqueCount="1274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5473" uniqueCount="1273">
   <si>
     <t>page_id</t>
   </si>
@@ -3648,9 +3648,6 @@
   </si>
   <si>
     <t>(Gr.)</t>
-  </si>
-  <si>
-    <t>(Abk.)</t>
   </si>
   <si>
     <t>(MR)</t>
@@ -8724,7 +8721,7 @@
         <v>45</v>
       </c>
       <c r="D125" s="21" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="N125" s="21" t="s">
         <v>90</v>
@@ -8741,7 +8738,7 @@
         <v>45</v>
       </c>
       <c r="D126" s="21" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="N126" s="21" t="s">
         <v>90</v>
@@ -8778,7 +8775,7 @@
         <v>45</v>
       </c>
       <c r="D128" s="21" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="N128" s="21" t="s">
         <v>90</v>
@@ -10625,7 +10622,7 @@
         <v>113</v>
       </c>
       <c r="L55" t="str">
-        <f t="shared" ref="L55:L58" si="8">_xlfn.TEXTJOIN("", TRUE, D55:J55)</f>
+        <f>_xlfn.TEXTJOIN("", TRUE, D55:H55)</f>
         <v>02_Slots/Gaben/0030_Gefluegel/0001_Apd_01.png</v>
       </c>
     </row>
@@ -10637,7 +10634,7 @@
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>105</v>
+        <v>276</v>
       </c>
       <c r="E56" t="s">
         <v>258</v>
@@ -10648,18 +10645,9 @@
       <c r="H56" t="s">
         <v>113</v>
       </c>
-      <c r="I56" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J56" t="s">
-        <v>1202</v>
-      </c>
-      <c r="K56" t="s">
-        <v>1200</v>
-      </c>
       <c r="L56" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D56:K56)</f>
-        <v>02_Slots/Gaben/0030_Gefluegel/0010_Apd_Abk_01.png &lt;sup&gt;(Abk.)&lt;/sup&gt;</v>
+        <v>02_Slots/Gaben/0030_Gefluegel/0010_Apd_Abk_01.png</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
@@ -10682,7 +10670,7 @@
         <v>113</v>
       </c>
       <c r="L57" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="L55:L58" si="8">_xlfn.TEXTJOIN("", TRUE, D57:J57)</f>
         <v>02_Slots/Gaben/0030_Gefluegel/0020_Apd_Abk_02.png</v>
       </c>
     </row>
@@ -10788,7 +10776,7 @@
         <v>1198</v>
       </c>
       <c r="J63" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K63" t="s">
         <v>1200</v>
@@ -11023,7 +11011,7 @@
         <v>1198</v>
       </c>
       <c r="J73" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K73" t="s">
         <v>1200</v>
@@ -11749,7 +11737,7 @@
         <v>1198</v>
       </c>
       <c r="J104" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="K104" t="s">
         <v>1200</v>
@@ -11782,7 +11770,7 @@
         <v>1198</v>
       </c>
       <c r="J105" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K105" t="s">
         <v>1200</v>
@@ -11815,7 +11803,7 @@
         <v>1198</v>
       </c>
       <c r="J106" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K106" t="s">
         <v>1200</v>
@@ -11848,7 +11836,7 @@
         <v>1198</v>
       </c>
       <c r="J107" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K107" t="s">
         <v>1200</v>
@@ -11881,7 +11869,7 @@
         <v>1198</v>
       </c>
       <c r="J108" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="K108" t="s">
         <v>1200</v>
@@ -11914,7 +11902,7 @@
         <v>1198</v>
       </c>
       <c r="J109" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="K109" t="s">
         <v>1200</v>
@@ -12103,7 +12091,7 @@
         <v>1198</v>
       </c>
       <c r="J116" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K116" t="s">
         <v>1200</v>
@@ -12896,7 +12884,7 @@
         <v>1198</v>
       </c>
       <c r="J166" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K166" t="s">
         <v>1200</v>
@@ -13077,7 +13065,7 @@
         <v>1198</v>
       </c>
       <c r="J175" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K175" t="s">
         <v>1200</v>
@@ -13412,7 +13400,7 @@
         <v>1198</v>
       </c>
       <c r="J197" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="K197" t="s">
         <v>1200</v>
@@ -13476,7 +13464,7 @@
         <v>1198</v>
       </c>
       <c r="J201" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="K201" t="s">
         <v>1200</v>
@@ -15469,7 +15457,7 @@
         <v>39</v>
       </c>
       <c r="L325" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.2">
@@ -15746,7 +15734,7 @@
         <v>39</v>
       </c>
       <c r="L343" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.2">
@@ -15760,7 +15748,7 @@
         <v>105</v>
       </c>
       <c r="E344" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="G344" t="s">
         <v>1025</v>
@@ -15781,7 +15769,7 @@
         <v>105</v>
       </c>
       <c r="E345" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="G345" t="s">
         <v>1026</v>
@@ -15811,7 +15799,7 @@
         <v>105</v>
       </c>
       <c r="E346" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="G346" t="s">
         <v>1027</v>
@@ -15820,7 +15808,7 @@
         <v>1198</v>
       </c>
       <c r="J346" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K346" t="s">
         <v>1200</v>
@@ -15841,7 +15829,7 @@
         <v>105</v>
       </c>
       <c r="E347" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="G347" t="s">
         <v>1028</v>
@@ -15871,7 +15859,7 @@
         <v>105</v>
       </c>
       <c r="E348" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="G348" t="s">
         <v>1029</v>
@@ -15880,7 +15868,7 @@
         <v>1198</v>
       </c>
       <c r="J348" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="K348" t="s">
         <v>1200</v>
@@ -15958,7 +15946,7 @@
         <v>105</v>
       </c>
       <c r="E354" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="F354" t="s">
         <v>1031</v>
@@ -15982,7 +15970,7 @@
         <v>105</v>
       </c>
       <c r="E355" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="F355" t="s">
         <v>1031</v>
@@ -16006,7 +15994,7 @@
         <v>105</v>
       </c>
       <c r="E356" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="F356" t="s">
         <v>1031</v>
@@ -16067,7 +16055,7 @@
         <v>105</v>
       </c>
       <c r="E360" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="F360" t="s">
         <v>1037</v>
@@ -16092,7 +16080,7 @@
       </c>
       <c r="D361" s="32"/>
       <c r="E361" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="F361" t="s">
         <v>1037</v>
@@ -16104,7 +16092,7 @@
         <v>1198</v>
       </c>
       <c r="J361" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="K361" t="s">
         <v>1200</v>
@@ -16186,7 +16174,7 @@
       </c>
       <c r="D369" s="32"/>
       <c r="E369" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="G369" t="s">
         <v>121</v>
@@ -16211,7 +16199,7 @@
       </c>
       <c r="D370" s="32"/>
       <c r="E370" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="G370" t="s">
         <v>123</v>
@@ -16245,7 +16233,7 @@
       </c>
       <c r="D371" s="32"/>
       <c r="E371" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="G371" t="s">
         <v>124</v>
@@ -16279,7 +16267,7 @@
       </c>
       <c r="D372" s="32"/>
       <c r="E372" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F372" t="s">
         <v>111</v>
@@ -16426,7 +16414,7 @@
       </c>
       <c r="D381" s="32"/>
       <c r="E381" s="32" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="G381" t="s">
         <v>127</v>
@@ -16501,7 +16489,7 @@
       <c r="D386" s="32"/>
       <c r="E386" s="32"/>
       <c r="L386" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.2">
@@ -16516,10 +16504,10 @@
       </c>
       <c r="D387" s="32"/>
       <c r="E387" s="32" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G387" t="s">
         <v>1230</v>
-      </c>
-      <c r="G387" t="s">
-        <v>1231</v>
       </c>
       <c r="H387" t="s">
         <v>113</v>
@@ -16606,7 +16594,7 @@
       </c>
       <c r="D393" s="32"/>
       <c r="E393" s="32" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G393" t="s">
         <v>589</v>
@@ -16631,7 +16619,7 @@
       </c>
       <c r="D394" s="32"/>
       <c r="E394" s="32" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G394" t="s">
         <v>590</v>
@@ -16656,7 +16644,7 @@
       </c>
       <c r="D395" s="32"/>
       <c r="E395" s="32" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G395" t="s">
         <v>591</v>
@@ -16681,7 +16669,7 @@
       </c>
       <c r="D396" s="32"/>
       <c r="E396" s="32" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G396" t="s">
         <v>592</v>
@@ -16715,7 +16703,7 @@
       </c>
       <c r="D397" s="32"/>
       <c r="E397" s="32" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G397" t="s">
         <v>593</v>
@@ -16727,7 +16715,7 @@
         <v>1198</v>
       </c>
       <c r="J397" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K397" t="s">
         <v>1200</v>
@@ -16749,7 +16737,7 @@
       </c>
       <c r="D398" s="32"/>
       <c r="E398" s="32" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G398" t="s">
         <v>594</v>
@@ -16783,7 +16771,7 @@
       </c>
       <c r="D399" s="32"/>
       <c r="E399" s="32" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G399" t="s">
         <v>595</v>
@@ -16879,7 +16867,7 @@
         <v>105</v>
       </c>
       <c r="E407" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="G407" t="s">
         <v>597</v>
@@ -16903,7 +16891,7 @@
         <v>105</v>
       </c>
       <c r="E408" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="G408" t="s">
         <v>598</v>
@@ -16927,7 +16915,7 @@
         <v>105</v>
       </c>
       <c r="E409" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="G409" t="s">
         <v>599</v>
@@ -16951,7 +16939,7 @@
         <v>105</v>
       </c>
       <c r="E410" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="G410" t="s">
         <v>600</v>
@@ -16975,7 +16963,7 @@
         <v>105</v>
       </c>
       <c r="E411" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="G411" t="s">
         <v>601</v>
@@ -16999,7 +16987,7 @@
         <v>105</v>
       </c>
       <c r="E412" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="G412" t="s">
         <v>602</v>
@@ -17088,7 +17076,7 @@
         <v>105</v>
       </c>
       <c r="E419" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="G419" t="s">
         <v>604</v>
@@ -17112,7 +17100,7 @@
         <v>105</v>
       </c>
       <c r="E420" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="G420" t="s">
         <v>605</v>
@@ -17136,7 +17124,7 @@
         <v>105</v>
       </c>
       <c r="E421" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="G421" t="s">
         <v>606</v>
@@ -17160,7 +17148,7 @@
         <v>105</v>
       </c>
       <c r="E422" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="G422" t="s">
         <v>607</v>
@@ -17184,7 +17172,7 @@
         <v>105</v>
       </c>
       <c r="E423" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="G423" t="s">
         <v>608</v>
@@ -17217,7 +17205,7 @@
         <v>106</v>
       </c>
       <c r="E424" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F424" t="s">
         <v>111</v>
@@ -17286,7 +17274,7 @@
         <v>105</v>
       </c>
       <c r="E429" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F429" t="s">
         <v>612</v>
@@ -17313,7 +17301,7 @@
         <v>105</v>
       </c>
       <c r="E430" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F430" t="s">
         <v>612</v>
@@ -17340,7 +17328,7 @@
         <v>105</v>
       </c>
       <c r="E431" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F431" t="s">
         <v>612</v>
@@ -17376,7 +17364,7 @@
         <v>105</v>
       </c>
       <c r="E432" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F432" t="s">
         <v>612</v>
@@ -17440,7 +17428,7 @@
         <v>105</v>
       </c>
       <c r="E436" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F436" t="s">
         <v>619</v>
@@ -17495,7 +17483,7 @@
         <v>105</v>
       </c>
       <c r="E440" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F440" t="s">
         <v>625</v>
@@ -17522,7 +17510,7 @@
         <v>105</v>
       </c>
       <c r="E441" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F441" t="s">
         <v>625</v>
@@ -17549,7 +17537,7 @@
         <v>105</v>
       </c>
       <c r="E442" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F442" t="s">
         <v>625</v>
@@ -17576,7 +17564,7 @@
         <v>105</v>
       </c>
       <c r="E443" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F443" t="s">
         <v>625</v>
@@ -17640,7 +17628,7 @@
         <v>105</v>
       </c>
       <c r="E447" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F447" t="s">
         <v>632</v>
@@ -17676,7 +17664,7 @@
         <v>105</v>
       </c>
       <c r="E448" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F448" t="s">
         <v>632</v>
@@ -17712,7 +17700,7 @@
         <v>105</v>
       </c>
       <c r="E449" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F449" t="s">
         <v>632</v>
@@ -17748,7 +17736,7 @@
         <v>105</v>
       </c>
       <c r="E450" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F450" t="s">
         <v>632</v>
@@ -17763,7 +17751,7 @@
         <v>1198</v>
       </c>
       <c r="J450" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K450" t="s">
         <v>1200</v>
@@ -17784,7 +17772,7 @@
         <v>105</v>
       </c>
       <c r="E451" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F451" t="s">
         <v>632</v>
@@ -17799,7 +17787,7 @@
         <v>1198</v>
       </c>
       <c r="J451" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K451" t="s">
         <v>1200</v>
@@ -17820,7 +17808,7 @@
         <v>105</v>
       </c>
       <c r="E452" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F452" t="s">
         <v>632</v>
@@ -17835,7 +17823,7 @@
         <v>1198</v>
       </c>
       <c r="J452" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="K452" t="s">
         <v>1200</v>
@@ -17856,7 +17844,7 @@
         <v>105</v>
       </c>
       <c r="E453" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F453" t="s">
         <v>632</v>
@@ -17892,7 +17880,7 @@
         <v>105</v>
       </c>
       <c r="E454" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F454" t="s">
         <v>632</v>
@@ -17928,7 +17916,7 @@
         <v>105</v>
       </c>
       <c r="E455" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F455" t="s">
         <v>632</v>
@@ -17992,7 +17980,7 @@
         <v>105</v>
       </c>
       <c r="E463" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="G463" t="s">
         <v>643</v>
@@ -18016,7 +18004,7 @@
         <v>105</v>
       </c>
       <c r="E464" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="G464" t="s">
         <v>644</v>
@@ -18040,7 +18028,7 @@
         <v>105</v>
       </c>
       <c r="E465" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="G465" t="s">
         <v>645</v>
@@ -18064,7 +18052,7 @@
         <v>105</v>
       </c>
       <c r="E466" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="G466" t="s">
         <v>646</v>
@@ -18076,7 +18064,7 @@
         <v>1198</v>
       </c>
       <c r="J466" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K466" t="s">
         <v>1200</v>
@@ -18097,7 +18085,7 @@
         <v>105</v>
       </c>
       <c r="E467" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="G467" t="s">
         <v>647</v>
@@ -18109,7 +18097,7 @@
         <v>1198</v>
       </c>
       <c r="J467" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K467" t="s">
         <v>1200</v>
@@ -18130,7 +18118,7 @@
         <v>105</v>
       </c>
       <c r="E468" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="G468" t="s">
         <v>648</v>
@@ -18163,7 +18151,7 @@
         <v>105</v>
       </c>
       <c r="E469" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="G469" t="s">
         <v>649</v>
@@ -18175,7 +18163,7 @@
         <v>1198</v>
       </c>
       <c r="J469" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="K469" t="s">
         <v>1200</v>
@@ -18249,7 +18237,7 @@
         <v>105</v>
       </c>
       <c r="E475" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F475" t="s">
         <v>652</v>
@@ -18276,7 +18264,7 @@
         <v>105</v>
       </c>
       <c r="E476" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F476" t="s">
         <v>652</v>
@@ -18331,7 +18319,7 @@
         <v>105</v>
       </c>
       <c r="E481" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="G481" t="s">
         <v>657</v>
@@ -18355,7 +18343,7 @@
         <v>105</v>
       </c>
       <c r="E482" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="G482" t="s">
         <v>658</v>
@@ -18379,7 +18367,7 @@
         <v>105</v>
       </c>
       <c r="E483" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="G483" t="s">
         <v>659</v>
@@ -18391,7 +18379,7 @@
         <v>1198</v>
       </c>
       <c r="J483" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="K483" t="s">
         <v>1200</v>
@@ -18412,7 +18400,7 @@
         <v>105</v>
       </c>
       <c r="E484" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="G484" t="s">
         <v>660</v>
@@ -18445,7 +18433,7 @@
         <v>105</v>
       </c>
       <c r="E485" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="G485" t="s">
         <v>661</v>
@@ -18531,7 +18519,7 @@
         <v>105</v>
       </c>
       <c r="E491" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F491" t="s">
         <v>662</v>
@@ -18586,7 +18574,7 @@
         <v>105</v>
       </c>
       <c r="E495" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F495" t="s">
         <v>665</v>
@@ -18641,7 +18629,7 @@
         <v>105</v>
       </c>
       <c r="E499" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F499" t="s">
         <v>668</v>
@@ -18696,7 +18684,7 @@
         <v>105</v>
       </c>
       <c r="E503" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F503" t="s">
         <v>670</v>
@@ -18751,7 +18739,7 @@
         <v>105</v>
       </c>
       <c r="E507" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F507" t="s">
         <v>674</v>
@@ -18766,7 +18754,7 @@
         <v>1198</v>
       </c>
       <c r="J507" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="K507" t="s">
         <v>1200</v>
@@ -18815,7 +18803,7 @@
         <v>105</v>
       </c>
       <c r="E511" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F511" t="s">
         <v>675</v>
@@ -18830,7 +18818,7 @@
         <v>1198</v>
       </c>
       <c r="J511" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="K511" t="s">
         <v>1200</v>
@@ -18879,7 +18867,7 @@
         <v>105</v>
       </c>
       <c r="E515" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F515" t="s">
         <v>676</v>
@@ -18894,7 +18882,7 @@
         <v>1198</v>
       </c>
       <c r="J515" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="K515" t="s">
         <v>1200</v>
@@ -18943,7 +18931,7 @@
         <v>105</v>
       </c>
       <c r="E519" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F519" t="s">
         <v>677</v>
@@ -18998,7 +18986,7 @@
         <v>105</v>
       </c>
       <c r="E525" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G525" t="s">
         <v>688</v>
@@ -19022,7 +19010,7 @@
         <v>105</v>
       </c>
       <c r="E526" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G526" t="s">
         <v>689</v>
@@ -19046,7 +19034,7 @@
         <v>105</v>
       </c>
       <c r="E527" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G527" t="s">
         <v>690</v>
@@ -19070,7 +19058,7 @@
         <v>105</v>
       </c>
       <c r="E528" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G528" t="s">
         <v>691</v>
@@ -19150,7 +19138,7 @@
         <v>105</v>
       </c>
       <c r="E535" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="G535" t="s">
         <v>732</v>
@@ -19174,7 +19162,7 @@
         <v>105</v>
       </c>
       <c r="E536" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="G536" t="s">
         <v>733</v>
@@ -19198,7 +19186,7 @@
         <v>105</v>
       </c>
       <c r="E537" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="G537" t="s">
         <v>734</v>
@@ -19222,7 +19210,7 @@
         <v>105</v>
       </c>
       <c r="E538" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="G538" t="s">
         <v>735</v>
@@ -19234,7 +19222,7 @@
         <v>1198</v>
       </c>
       <c r="J538" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K538" t="s">
         <v>1200</v>
@@ -19255,7 +19243,7 @@
         <v>105</v>
       </c>
       <c r="E539" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="G539" t="s">
         <v>736</v>
@@ -19267,7 +19255,7 @@
         <v>1198</v>
       </c>
       <c r="J539" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K539" t="s">
         <v>1200</v>
@@ -19288,7 +19276,7 @@
         <v>105</v>
       </c>
       <c r="E540" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="G540" t="s">
         <v>737</v>
@@ -19300,7 +19288,7 @@
         <v>1198</v>
       </c>
       <c r="J540" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K540" t="s">
         <v>1200</v>
@@ -19321,7 +19309,7 @@
         <v>105</v>
       </c>
       <c r="E541" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="G541" t="s">
         <v>738</v>
@@ -19354,7 +19342,7 @@
         <v>105</v>
       </c>
       <c r="E542" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="G542" t="s">
         <v>739</v>
@@ -19387,7 +19375,7 @@
         <v>105</v>
       </c>
       <c r="E543" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="G543" t="s">
         <v>740</v>
@@ -19420,7 +19408,7 @@
         <v>105</v>
       </c>
       <c r="E544" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="G544" t="s">
         <v>741</v>
@@ -19453,7 +19441,7 @@
         <v>106</v>
       </c>
       <c r="E545" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F545" t="s">
         <v>111</v>
@@ -19522,7 +19510,7 @@
         <v>105</v>
       </c>
       <c r="E550" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F550" t="s">
         <v>755</v>
@@ -19549,7 +19537,7 @@
         <v>105</v>
       </c>
       <c r="E551" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F551" t="s">
         <v>755</v>
@@ -19576,7 +19564,7 @@
         <v>105</v>
       </c>
       <c r="E552" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F552" t="s">
         <v>755</v>
@@ -19603,7 +19591,7 @@
         <v>105</v>
       </c>
       <c r="E553" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F553" t="s">
         <v>755</v>
@@ -19639,7 +19627,7 @@
         <v>105</v>
       </c>
       <c r="E554" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F554" t="s">
         <v>755</v>
@@ -19703,7 +19691,7 @@
         <v>105</v>
       </c>
       <c r="E558" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F558" t="s">
         <v>756</v>
@@ -19730,7 +19718,7 @@
         <v>105</v>
       </c>
       <c r="E559" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F559" t="s">
         <v>756</v>
@@ -19754,7 +19742,7 @@
         <v>105</v>
       </c>
       <c r="E560" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F560" t="s">
         <v>756</v>
@@ -19778,7 +19766,7 @@
         <v>105</v>
       </c>
       <c r="E561" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F561" t="s">
         <v>756</v>
@@ -19802,7 +19790,7 @@
         <v>105</v>
       </c>
       <c r="E562" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F562" t="s">
         <v>756</v>
@@ -19826,7 +19814,7 @@
         <v>105</v>
       </c>
       <c r="E563" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F563" t="s">
         <v>756</v>
@@ -19850,7 +19838,7 @@
         <v>105</v>
       </c>
       <c r="E564" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F564" t="s">
         <v>756</v>
@@ -19874,7 +19862,7 @@
         <v>105</v>
       </c>
       <c r="E565" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F565" t="s">
         <v>756</v>
@@ -19898,7 +19886,7 @@
         <v>105</v>
       </c>
       <c r="E566" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F566" t="s">
         <v>756</v>
@@ -19910,7 +19898,7 @@
         <v>1198</v>
       </c>
       <c r="J566" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="K566" t="s">
         <v>1200</v>
@@ -19959,7 +19947,7 @@
         <v>105</v>
       </c>
       <c r="E570" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F570" t="s">
         <v>757</v>
@@ -20011,7 +19999,7 @@
         <v>105</v>
       </c>
       <c r="E574" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F574" t="s">
         <v>758</v>
@@ -20066,7 +20054,7 @@
         <v>105</v>
       </c>
       <c r="E578" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F578" t="s">
         <v>759</v>
@@ -20090,7 +20078,7 @@
         <v>105</v>
       </c>
       <c r="E579" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F579" t="s">
         <v>759</v>
@@ -20114,7 +20102,7 @@
         <v>105</v>
       </c>
       <c r="E580" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F580" t="s">
         <v>759</v>
@@ -20147,7 +20135,7 @@
         <v>105</v>
       </c>
       <c r="E581" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F581" t="s">
         <v>759</v>
@@ -20180,7 +20168,7 @@
         <v>105</v>
       </c>
       <c r="E582" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F582" t="s">
         <v>759</v>
@@ -20192,7 +20180,7 @@
         <v>1198</v>
       </c>
       <c r="J582" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="K582" t="s">
         <v>1200</v>
@@ -20213,7 +20201,7 @@
         <v>105</v>
       </c>
       <c r="E583" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F583" t="s">
         <v>759</v>
@@ -20225,7 +20213,7 @@
         <v>1198</v>
       </c>
       <c r="J583" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K583" t="s">
         <v>1200</v>
@@ -20246,7 +20234,7 @@
         <v>105</v>
       </c>
       <c r="E584" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F584" t="s">
         <v>759</v>
@@ -20258,7 +20246,7 @@
         <v>1198</v>
       </c>
       <c r="J584" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="K584" t="s">
         <v>1200</v>
@@ -20307,7 +20295,7 @@
         <v>105</v>
       </c>
       <c r="E588" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F588" t="s">
         <v>760</v>
@@ -20331,7 +20319,7 @@
         <v>105</v>
       </c>
       <c r="E589" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F589" t="s">
         <v>760</v>
@@ -20383,7 +20371,7 @@
         <v>105</v>
       </c>
       <c r="E593" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F593" t="s">
         <v>761</v>
@@ -20438,7 +20426,7 @@
         <v>105</v>
       </c>
       <c r="E602" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="G602" t="s">
         <v>788</v>
@@ -20459,7 +20447,7 @@
         <v>105</v>
       </c>
       <c r="E603" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="G603" t="s">
         <v>789</v>
@@ -20489,7 +20477,7 @@
         <v>105</v>
       </c>
       <c r="E604" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="G604" t="s">
         <v>790</v>
@@ -20569,7 +20557,7 @@
         <v>105</v>
       </c>
       <c r="E611" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="G611" t="s">
         <v>791</v>
@@ -20590,7 +20578,7 @@
         <v>105</v>
       </c>
       <c r="E612" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="G612" t="s">
         <v>792</v>
@@ -20611,7 +20599,7 @@
         <v>105</v>
       </c>
       <c r="E613" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="G613" t="s">
         <v>793</v>
@@ -20641,7 +20629,7 @@
         <v>105</v>
       </c>
       <c r="E614" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="G614" t="s">
         <v>794</v>
@@ -20671,7 +20659,7 @@
         <v>106</v>
       </c>
       <c r="E615" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="F615" t="s">
         <v>111</v>
@@ -20740,7 +20728,7 @@
         <v>105</v>
       </c>
       <c r="E620" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="F620" t="s">
         <v>804</v>
@@ -20795,7 +20783,7 @@
         <v>105</v>
       </c>
       <c r="E624" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="F624" t="s">
         <v>805</v>
@@ -20819,7 +20807,7 @@
         <v>105</v>
       </c>
       <c r="E625" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="F625" t="s">
         <v>805</v>
@@ -20871,7 +20859,7 @@
         <v>105</v>
       </c>
       <c r="E630" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="G630" t="s">
         <v>807</v>
@@ -20892,7 +20880,7 @@
         <v>105</v>
       </c>
       <c r="E631" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="G631" t="s">
         <v>808</v>
@@ -20922,7 +20910,7 @@
         <v>105</v>
       </c>
       <c r="E632" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="G632" t="s">
         <v>809</v>
@@ -20952,7 +20940,7 @@
         <v>105</v>
       </c>
       <c r="E633" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="G633" t="s">
         <v>810</v>
@@ -20982,7 +20970,7 @@
         <v>105</v>
       </c>
       <c r="E634" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="G634" t="s">
         <v>811</v>
@@ -20991,7 +20979,7 @@
         <v>1198</v>
       </c>
       <c r="J634" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K634" t="s">
         <v>1200</v>
@@ -21012,7 +21000,7 @@
         <v>105</v>
       </c>
       <c r="E635" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="G635" t="s">
         <v>812</v>
@@ -21021,7 +21009,7 @@
         <v>1198</v>
       </c>
       <c r="J635" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="K635" t="s">
         <v>1200</v>
@@ -21042,7 +21030,7 @@
         <v>105</v>
       </c>
       <c r="E636" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="G636" t="s">
         <v>813</v>
@@ -21072,7 +21060,7 @@
         <v>105</v>
       </c>
       <c r="E637" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="G637" t="s">
         <v>806</v>
@@ -21102,7 +21090,7 @@
         <v>106</v>
       </c>
       <c r="E638" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F638" t="s">
         <v>111</v>
@@ -21135,7 +21123,7 @@
         <v>106</v>
       </c>
       <c r="E639" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F639" t="s">
         <v>111</v>
@@ -21147,7 +21135,7 @@
         <v>1198</v>
       </c>
       <c r="J639" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K639" t="s">
         <v>1200</v>
@@ -21168,7 +21156,7 @@
         <v>106</v>
       </c>
       <c r="E640" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F640" t="s">
         <v>111</v>
@@ -21180,7 +21168,7 @@
         <v>1198</v>
       </c>
       <c r="J640" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K640" t="s">
         <v>1200</v>
@@ -21201,7 +21189,7 @@
         <v>106</v>
       </c>
       <c r="E641" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F641" t="s">
         <v>111</v>
@@ -21213,7 +21201,7 @@
         <v>1198</v>
       </c>
       <c r="J641" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="K641" t="s">
         <v>1200</v>
@@ -21276,7 +21264,7 @@
         <v>105</v>
       </c>
       <c r="E646" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F646" t="s">
         <v>819</v>
@@ -21300,7 +21288,7 @@
         <v>105</v>
       </c>
       <c r="E647" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F647" t="s">
         <v>819</v>
@@ -21324,7 +21312,7 @@
         <v>105</v>
       </c>
       <c r="E648" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F648" t="s">
         <v>819</v>
@@ -21357,7 +21345,7 @@
         <v>105</v>
       </c>
       <c r="E649" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F649" t="s">
         <v>819</v>
@@ -21369,7 +21357,7 @@
         <v>1198</v>
       </c>
       <c r="J649" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K649" t="s">
         <v>1200</v>
@@ -21390,7 +21378,7 @@
         <v>105</v>
       </c>
       <c r="E650" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F650" t="s">
         <v>819</v>
@@ -21402,7 +21390,7 @@
         <v>1198</v>
       </c>
       <c r="J650" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K650" t="s">
         <v>1200</v>
@@ -21423,7 +21411,7 @@
         <v>105</v>
       </c>
       <c r="E651" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F651" t="s">
         <v>819</v>
@@ -21435,7 +21423,7 @@
         <v>1198</v>
       </c>
       <c r="J651" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K651" t="s">
         <v>1200</v>
@@ -21484,7 +21472,7 @@
         <v>105</v>
       </c>
       <c r="E655" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F655" t="s">
         <v>824</v>
@@ -21508,7 +21496,7 @@
         <v>105</v>
       </c>
       <c r="E656" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F656" t="s">
         <v>824</v>
@@ -21541,7 +21529,7 @@
         <v>105</v>
       </c>
       <c r="E657" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F657" t="s">
         <v>824</v>
@@ -21553,7 +21541,7 @@
         <v>1198</v>
       </c>
       <c r="J657" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K657" t="s">
         <v>1200</v>
@@ -21574,7 +21562,7 @@
         <v>105</v>
       </c>
       <c r="E658" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F658" t="s">
         <v>824</v>
@@ -21586,7 +21574,7 @@
         <v>1198</v>
       </c>
       <c r="J658" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K658" t="s">
         <v>1200</v>
@@ -21607,7 +21595,7 @@
         <v>105</v>
       </c>
       <c r="E659" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F659" t="s">
         <v>824</v>
@@ -21619,7 +21607,7 @@
         <v>1198</v>
       </c>
       <c r="J659" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="K659" t="s">
         <v>1200</v>
@@ -21668,7 +21656,7 @@
         <v>105</v>
       </c>
       <c r="E663" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="G663" t="s">
         <v>836</v>
@@ -21692,7 +21680,7 @@
         <v>106</v>
       </c>
       <c r="E664" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F664" t="s">
         <v>111</v>
@@ -21716,7 +21704,7 @@
         <v>106</v>
       </c>
       <c r="E665" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F665" t="s">
         <v>111</v>
@@ -21779,7 +21767,7 @@
         <v>105</v>
       </c>
       <c r="E671" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="G671" t="s">
         <v>840</v>
@@ -21800,7 +21788,7 @@
         <v>105</v>
       </c>
       <c r="E672" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="G672" t="s">
         <v>841</v>
@@ -21821,7 +21809,7 @@
         <v>105</v>
       </c>
       <c r="E673" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="G673" t="s">
         <v>842</v>
@@ -21851,7 +21839,7 @@
         <v>105</v>
       </c>
       <c r="E674" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="G674" t="s">
         <v>843</v>
@@ -21881,7 +21869,7 @@
         <v>105</v>
       </c>
       <c r="E675" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="G675" t="s">
         <v>844</v>
@@ -21890,7 +21878,7 @@
         <v>1198</v>
       </c>
       <c r="J675" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K675" t="s">
         <v>1200</v>
@@ -21911,7 +21899,7 @@
         <v>105</v>
       </c>
       <c r="E676" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="G676" t="s">
         <v>845</v>
@@ -21920,7 +21908,7 @@
         <v>1198</v>
       </c>
       <c r="J676" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K676" t="s">
         <v>1200</v>
@@ -21941,7 +21929,7 @@
         <v>105</v>
       </c>
       <c r="E677" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="G677" t="s">
         <v>846</v>
@@ -21971,7 +21959,7 @@
         <v>105</v>
       </c>
       <c r="E678" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="G678" t="s">
         <v>847</v>
@@ -22001,7 +21989,7 @@
         <v>105</v>
       </c>
       <c r="E679" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="G679" t="s">
         <v>848</v>
@@ -22031,7 +22019,7 @@
         <v>105</v>
       </c>
       <c r="E680" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="G680" t="s">
         <v>839</v>
@@ -22061,7 +22049,7 @@
         <v>106</v>
       </c>
       <c r="E681" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="F681" t="s">
         <v>111</v>
@@ -22094,7 +22082,7 @@
         <v>106</v>
       </c>
       <c r="E682" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="F682" t="s">
         <v>111</v>
@@ -22106,7 +22094,7 @@
         <v>1198</v>
       </c>
       <c r="J682" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K682" t="s">
         <v>1200</v>
@@ -22166,7 +22154,7 @@
         <v>105</v>
       </c>
       <c r="E688" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="G688" t="s">
         <v>851</v>
@@ -22187,7 +22175,7 @@
         <v>105</v>
       </c>
       <c r="E689" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="G689" t="s">
         <v>852</v>
@@ -22208,7 +22196,7 @@
         <v>105</v>
       </c>
       <c r="E690" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="G690" t="s">
         <v>853</v>
@@ -22229,7 +22217,7 @@
         <v>106</v>
       </c>
       <c r="E691" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="F691" t="s">
         <v>111</v>
@@ -22295,7 +22283,7 @@
         <v>105</v>
       </c>
       <c r="E697" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="G697" t="s">
         <v>855</v>
@@ -22316,7 +22304,7 @@
         <v>105</v>
       </c>
       <c r="E698" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="G698" t="s">
         <v>856</v>
@@ -22337,7 +22325,7 @@
         <v>105</v>
       </c>
       <c r="E699" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="G699" t="s">
         <v>857</v>
@@ -22415,7 +22403,7 @@
         <v>105</v>
       </c>
       <c r="E705" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="F705" t="s">
         <v>861</v>
@@ -22439,7 +22427,7 @@
         <v>105</v>
       </c>
       <c r="E706" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="F706" t="s">
         <v>861</v>
@@ -22463,7 +22451,7 @@
         <v>105</v>
       </c>
       <c r="E707" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="F707" t="s">
         <v>861</v>
@@ -22515,7 +22503,7 @@
         <v>105</v>
       </c>
       <c r="E714" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="G714" t="s">
         <v>865</v>
@@ -22536,7 +22524,7 @@
         <v>105</v>
       </c>
       <c r="E715" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="G715" t="s">
         <v>866</v>
@@ -22566,7 +22554,7 @@
         <v>105</v>
       </c>
       <c r="E716" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="G716" t="s">
         <v>867</v>
@@ -22596,7 +22584,7 @@
         <v>105</v>
       </c>
       <c r="E717" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="G717" t="s">
         <v>868</v>
@@ -22626,7 +22614,7 @@
         <v>105</v>
       </c>
       <c r="E718" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="G718" t="s">
         <v>869</v>
@@ -22656,7 +22644,7 @@
         <v>106</v>
       </c>
       <c r="E719" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F719" t="s">
         <v>111</v>
@@ -22680,7 +22668,7 @@
         <v>106</v>
       </c>
       <c r="E720" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F720" t="s">
         <v>111</v>
@@ -22746,7 +22734,7 @@
         <v>105</v>
       </c>
       <c r="E725" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F725" t="s">
         <v>875</v>
@@ -22770,7 +22758,7 @@
         <v>105</v>
       </c>
       <c r="E726" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F726" t="s">
         <v>875</v>
@@ -22794,7 +22782,7 @@
         <v>105</v>
       </c>
       <c r="E727" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F727" t="s">
         <v>875</v>
@@ -22818,7 +22806,7 @@
         <v>105</v>
       </c>
       <c r="E728" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F728" t="s">
         <v>875</v>
@@ -22842,7 +22830,7 @@
         <v>105</v>
       </c>
       <c r="E729" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F729" t="s">
         <v>875</v>
@@ -22894,7 +22882,7 @@
         <v>105</v>
       </c>
       <c r="E735" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="G735" t="s">
         <v>881</v>
@@ -22915,7 +22903,7 @@
         <v>105</v>
       </c>
       <c r="E736" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="G736" t="s">
         <v>882</v>
@@ -22936,7 +22924,7 @@
         <v>105</v>
       </c>
       <c r="E737" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="G737" t="s">
         <v>883</v>
@@ -22957,7 +22945,7 @@
         <v>105</v>
       </c>
       <c r="E738" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="G738" t="s">
         <v>884</v>
@@ -22978,7 +22966,7 @@
         <v>105</v>
       </c>
       <c r="E739" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="G739" t="s">
         <v>885</v>
@@ -23062,7 +23050,7 @@
         <v>105</v>
       </c>
       <c r="E746" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="G746" t="s">
         <v>886</v>
@@ -23083,7 +23071,7 @@
         <v>105</v>
       </c>
       <c r="E747" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="G747" t="s">
         <v>887</v>
@@ -23113,7 +23101,7 @@
         <v>105</v>
       </c>
       <c r="E748" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="G748" t="s">
         <v>888</v>
@@ -23143,7 +23131,7 @@
         <v>105</v>
       </c>
       <c r="E749" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="G749" t="s">
         <v>889</v>
@@ -23173,7 +23161,7 @@
         <v>105</v>
       </c>
       <c r="E750" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="G750" t="s">
         <v>890</v>
@@ -23203,7 +23191,7 @@
         <v>105</v>
       </c>
       <c r="E751" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="G751" t="s">
         <v>891</v>
@@ -23287,7 +23275,7 @@
         <v>105</v>
       </c>
       <c r="E758" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="G758" t="s">
         <v>892</v>
@@ -23308,7 +23296,7 @@
         <v>105</v>
       </c>
       <c r="E759" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="G759" t="s">
         <v>893</v>
@@ -23338,7 +23326,7 @@
         <v>105</v>
       </c>
       <c r="E760" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="G760" t="s">
         <v>894</v>
@@ -23368,7 +23356,7 @@
         <v>105</v>
       </c>
       <c r="E761" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="G761" t="s">
         <v>895</v>
@@ -23398,7 +23386,7 @@
         <v>105</v>
       </c>
       <c r="E762" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="G762" t="s">
         <v>896</v>
@@ -23407,7 +23395,7 @@
         <v>1198</v>
       </c>
       <c r="J762" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="K762" t="s">
         <v>1200</v>
@@ -23428,7 +23416,7 @@
         <v>105</v>
       </c>
       <c r="E763" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="G763" t="s">
         <v>897</v>
@@ -23458,7 +23446,7 @@
         <v>105</v>
       </c>
       <c r="E764" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="G764" t="s">
         <v>898</v>
@@ -23542,7 +23530,7 @@
         <v>105</v>
       </c>
       <c r="E771" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="G771" t="s">
         <v>899</v>
@@ -23563,7 +23551,7 @@
         <v>105</v>
       </c>
       <c r="E772" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="G772" t="s">
         <v>900</v>
@@ -23584,7 +23572,7 @@
         <v>105</v>
       </c>
       <c r="E773" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="G773" t="s">
         <v>901</v>
@@ -23614,7 +23602,7 @@
         <v>105</v>
       </c>
       <c r="E774" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="G774" t="s">
         <v>902</v>
@@ -23644,7 +23632,7 @@
         <v>105</v>
       </c>
       <c r="E775" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="G775" t="s">
         <v>903</v>
@@ -23674,7 +23662,7 @@
         <v>106</v>
       </c>
       <c r="E776" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="F776" t="s">
         <v>111</v>
@@ -23707,7 +23695,7 @@
         <v>106</v>
       </c>
       <c r="E777" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="F777" t="s">
         <v>111</v>
@@ -23779,7 +23767,7 @@
         <v>105</v>
       </c>
       <c r="E783" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="G783" t="s">
         <v>906</v>
@@ -23800,7 +23788,7 @@
         <v>105</v>
       </c>
       <c r="E784" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="G784" t="s">
         <v>907</v>
@@ -23821,7 +23809,7 @@
         <v>105</v>
       </c>
       <c r="E785" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="G785" t="s">
         <v>908</v>
@@ -23851,7 +23839,7 @@
         <v>105</v>
       </c>
       <c r="E786" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="G786" t="s">
         <v>909</v>
@@ -23881,7 +23869,7 @@
         <v>106</v>
       </c>
       <c r="E787" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="F787" t="s">
         <v>111</v>
@@ -23956,7 +23944,7 @@
         <v>105</v>
       </c>
       <c r="E793" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="G793" t="s">
         <v>911</v>
@@ -23977,7 +23965,7 @@
         <v>105</v>
       </c>
       <c r="E794" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="G794" t="s">
         <v>912</v>
@@ -23986,7 +23974,7 @@
         <v>1198</v>
       </c>
       <c r="J794" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="K794" t="s">
         <v>1200</v>
@@ -24007,7 +23995,7 @@
         <v>105</v>
       </c>
       <c r="E795" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="G795" t="s">
         <v>913</v>
@@ -24037,7 +24025,7 @@
         <v>105</v>
       </c>
       <c r="E796" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="G796" t="s">
         <v>914</v>
@@ -24067,7 +24055,7 @@
         <v>106</v>
       </c>
       <c r="E797" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F797" t="s">
         <v>111</v>
@@ -24100,7 +24088,7 @@
         <v>106</v>
       </c>
       <c r="E798" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F798" t="s">
         <v>111</v>
@@ -24112,7 +24100,7 @@
         <v>1198</v>
       </c>
       <c r="J798" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K798" t="s">
         <v>1200</v>
@@ -24133,7 +24121,7 @@
         <v>106</v>
       </c>
       <c r="E799" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F799" t="s">
         <v>111</v>
@@ -24166,7 +24154,7 @@
         <v>106</v>
       </c>
       <c r="E800" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F800" t="s">
         <v>111</v>
@@ -24238,7 +24226,7 @@
         <v>105</v>
       </c>
       <c r="E806" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="L806" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D806:J806)</f>
@@ -24310,7 +24298,7 @@
         <v>105</v>
       </c>
       <c r="E813" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="G813" t="s">
         <v>919</v>
@@ -24331,7 +24319,7 @@
         <v>105</v>
       </c>
       <c r="E814" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="G814" t="s">
         <v>920</v>
@@ -24361,7 +24349,7 @@
         <v>105</v>
       </c>
       <c r="E815" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="G815" t="s">
         <v>921</v>
@@ -24391,7 +24379,7 @@
         <v>105</v>
       </c>
       <c r="E816" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="G816" t="s">
         <v>922</v>
@@ -24400,7 +24388,7 @@
         <v>1198</v>
       </c>
       <c r="J816" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="K816" t="s">
         <v>1200</v>
@@ -24421,7 +24409,7 @@
         <v>105</v>
       </c>
       <c r="E817" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="G817" t="s">
         <v>923</v>
@@ -24430,7 +24418,7 @@
         <v>1198</v>
       </c>
       <c r="J817" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="K817" t="s">
         <v>1200</v>
@@ -24451,7 +24439,7 @@
         <v>105</v>
       </c>
       <c r="E818" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="G818" t="s">
         <v>924</v>
@@ -24460,7 +24448,7 @@
         <v>1198</v>
       </c>
       <c r="J818" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="K818" t="s">
         <v>1200</v>
@@ -24535,7 +24523,7 @@
         <v>105</v>
       </c>
       <c r="E825" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G825" t="s">
         <v>925</v>
@@ -24565,7 +24553,7 @@
         <v>105</v>
       </c>
       <c r="E826" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G826" t="s">
         <v>926</v>
@@ -24574,7 +24562,7 @@
         <v>1198</v>
       </c>
       <c r="J826" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K826" t="s">
         <v>1200</v>
@@ -24595,7 +24583,7 @@
         <v>105</v>
       </c>
       <c r="E827" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G827" t="s">
         <v>927</v>
@@ -24604,7 +24592,7 @@
         <v>1198</v>
       </c>
       <c r="J827" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K827" t="s">
         <v>1200</v>
@@ -24625,7 +24613,7 @@
         <v>105</v>
       </c>
       <c r="E828" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G828" t="s">
         <v>928</v>
@@ -24634,7 +24622,7 @@
         <v>1198</v>
       </c>
       <c r="J828" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K828" t="s">
         <v>1200</v>
@@ -24655,7 +24643,7 @@
         <v>105</v>
       </c>
       <c r="E829" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G829" t="s">
         <v>929</v>
@@ -24664,7 +24652,7 @@
         <v>1198</v>
       </c>
       <c r="J829" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K829" t="s">
         <v>1200</v>
@@ -24685,7 +24673,7 @@
         <v>105</v>
       </c>
       <c r="E830" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G830" t="s">
         <v>930</v>
@@ -24694,7 +24682,7 @@
         <v>1198</v>
       </c>
       <c r="J830" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K830" t="s">
         <v>1200</v>
@@ -24715,7 +24703,7 @@
         <v>105</v>
       </c>
       <c r="E831" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G831" t="s">
         <v>931</v>
@@ -24724,7 +24712,7 @@
         <v>1198</v>
       </c>
       <c r="J831" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K831" t="s">
         <v>1200</v>
@@ -24745,7 +24733,7 @@
         <v>105</v>
       </c>
       <c r="E832" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G832" t="s">
         <v>932</v>
@@ -24754,7 +24742,7 @@
         <v>1198</v>
       </c>
       <c r="J832" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="K832" t="s">
         <v>1200</v>
@@ -24775,7 +24763,7 @@
         <v>105</v>
       </c>
       <c r="E833" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G833" t="s">
         <v>933</v>
@@ -24784,7 +24772,7 @@
         <v>1198</v>
       </c>
       <c r="J833" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="K833" t="s">
         <v>1200</v>
@@ -24805,7 +24793,7 @@
         <v>105</v>
       </c>
       <c r="E834" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G834" t="s">
         <v>936</v>
@@ -24814,7 +24802,7 @@
         <v>1198</v>
       </c>
       <c r="J834" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="K834" t="s">
         <v>1200</v>
@@ -24835,7 +24823,7 @@
         <v>105</v>
       </c>
       <c r="E835" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G835" t="s">
         <v>937</v>
@@ -24844,7 +24832,7 @@
         <v>1198</v>
       </c>
       <c r="J835" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="K835" t="s">
         <v>1200</v>
@@ -24865,7 +24853,7 @@
         <v>105</v>
       </c>
       <c r="E836" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G836" t="s">
         <v>938</v>
@@ -24874,7 +24862,7 @@
         <v>1198</v>
       </c>
       <c r="J836" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="K836" t="s">
         <v>1200</v>
@@ -24895,7 +24883,7 @@
         <v>106</v>
       </c>
       <c r="E837" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="F837" t="s">
         <v>111</v>
@@ -24919,7 +24907,7 @@
         <v>106</v>
       </c>
       <c r="E838" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="F838" t="s">
         <v>111</v>
@@ -24982,7 +24970,7 @@
         <v>105</v>
       </c>
       <c r="E844" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="G844" t="s">
         <v>939</v>
@@ -25003,7 +24991,7 @@
         <v>105</v>
       </c>
       <c r="E845" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="G845" t="s">
         <v>940</v>
@@ -25033,7 +25021,7 @@
         <v>105</v>
       </c>
       <c r="E846" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="G846" t="s">
         <v>941</v>
@@ -25117,7 +25105,7 @@
         <v>105</v>
       </c>
       <c r="E853" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="G853" t="s">
         <v>942</v>
@@ -25138,7 +25126,7 @@
         <v>105</v>
       </c>
       <c r="E854" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="G854" t="s">
         <v>943</v>
@@ -25159,7 +25147,7 @@
         <v>105</v>
       </c>
       <c r="E855" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="G855" t="s">
         <v>944</v>
@@ -25189,7 +25177,7 @@
         <v>105</v>
       </c>
       <c r="E856" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="G856" t="s">
         <v>945</v>
@@ -25219,7 +25207,7 @@
         <v>106</v>
       </c>
       <c r="E857" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="F857" t="s">
         <v>111</v>
@@ -25243,7 +25231,7 @@
         <v>106</v>
       </c>
       <c r="E858" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="F858" t="s">
         <v>111</v>
@@ -25267,7 +25255,7 @@
         <v>106</v>
       </c>
       <c r="E859" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="F859" t="s">
         <v>111</v>
@@ -25279,7 +25267,7 @@
         <v>1198</v>
       </c>
       <c r="J859" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="K859" t="s">
         <v>1200</v>
@@ -25342,7 +25330,7 @@
         <v>105</v>
       </c>
       <c r="E864" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="F864" t="s">
         <v>950</v>
@@ -25357,7 +25345,7 @@
         <v>1198</v>
       </c>
       <c r="J864" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="K864" t="s">
         <v>1200</v>
@@ -25406,7 +25394,7 @@
         <v>105</v>
       </c>
       <c r="E872" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="G872" t="s">
         <v>952</v>
@@ -25427,7 +25415,7 @@
         <v>105</v>
       </c>
       <c r="E873" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="G873" t="s">
         <v>953</v>
@@ -25448,7 +25436,7 @@
         <v>105</v>
       </c>
       <c r="E874" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="G874" t="s">
         <v>954</v>
@@ -25469,7 +25457,7 @@
         <v>105</v>
       </c>
       <c r="E875" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="G875" t="s">
         <v>955</v>
@@ -25490,7 +25478,7 @@
         <v>105</v>
       </c>
       <c r="E876" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="G876" t="s">
         <v>956</v>
@@ -25520,7 +25508,7 @@
         <v>105</v>
       </c>
       <c r="E877" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="G877" t="s">
         <v>957</v>
@@ -25529,7 +25517,7 @@
         <v>1198</v>
       </c>
       <c r="J877" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K877" t="s">
         <v>1200</v>
@@ -25550,7 +25538,7 @@
         <v>105</v>
       </c>
       <c r="E878" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="G878" t="s">
         <v>958</v>
@@ -25559,7 +25547,7 @@
         <v>1198</v>
       </c>
       <c r="J878" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="K878" t="s">
         <v>1200</v>
@@ -25580,7 +25568,7 @@
         <v>106</v>
       </c>
       <c r="E879" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="F879" t="s">
         <v>111</v>
@@ -25604,7 +25592,7 @@
         <v>106</v>
       </c>
       <c r="E880" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="F880" t="s">
         <v>111</v>
@@ -25667,7 +25655,7 @@
         <v>105</v>
       </c>
       <c r="E886" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="G886" t="s">
         <v>961</v>
@@ -25688,7 +25676,7 @@
         <v>105</v>
       </c>
       <c r="E887" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="G887" t="s">
         <v>962</v>
@@ -25709,7 +25697,7 @@
         <v>105</v>
       </c>
       <c r="E888" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="G888" t="s">
         <v>963</v>
@@ -25739,7 +25727,7 @@
         <v>105</v>
       </c>
       <c r="E889" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="G889" t="s">
         <v>964</v>
@@ -25748,7 +25736,7 @@
         <v>1198</v>
       </c>
       <c r="J889" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K889" t="s">
         <v>1200</v>
@@ -25826,7 +25814,7 @@
         <v>105</v>
       </c>
       <c r="E895" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="F895" t="s">
         <v>965</v>
@@ -25881,7 +25869,7 @@
         <v>105</v>
       </c>
       <c r="E899" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="F899" t="s">
         <v>965</v>
@@ -25936,7 +25924,7 @@
         <v>105</v>
       </c>
       <c r="E903" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="F903" t="s">
         <v>965</v>
@@ -26000,7 +25988,7 @@
         <v>105</v>
       </c>
       <c r="E907" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="F907" t="s">
         <v>965</v>
@@ -26055,7 +26043,7 @@
         <v>105</v>
       </c>
       <c r="E911" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="F911" t="s">
         <v>965</v>
@@ -26110,7 +26098,7 @@
         <v>105</v>
       </c>
       <c r="E915" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="F915" t="s">
         <v>965</v>
@@ -26165,7 +26153,7 @@
         <v>105</v>
       </c>
       <c r="E919" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="G919" t="s">
         <v>985</v>
@@ -26186,7 +26174,7 @@
         <v>105</v>
       </c>
       <c r="E920" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="G920" t="s">
         <v>986</v>
@@ -26207,7 +26195,7 @@
         <v>105</v>
       </c>
       <c r="E921" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="G921" t="s">
         <v>987</v>
@@ -26282,7 +26270,7 @@
         <v>105</v>
       </c>
       <c r="E928" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="G928" t="s">
         <v>988</v>
@@ -26303,7 +26291,7 @@
         <v>105</v>
       </c>
       <c r="E929" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="G929" t="s">
         <v>989</v>
@@ -26312,7 +26300,7 @@
         <v>1198</v>
       </c>
       <c r="J929" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="K929" t="s">
         <v>1200</v>
@@ -26333,7 +26321,7 @@
         <v>106</v>
       </c>
       <c r="E930" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="F930" t="s">
         <v>111</v>
@@ -26357,7 +26345,7 @@
         <v>106</v>
       </c>
       <c r="E931" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="F931" t="s">
         <v>111</v>
@@ -26420,7 +26408,7 @@
         <v>105</v>
       </c>
       <c r="E937" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="G937" t="s">
         <v>992</v>
@@ -26441,7 +26429,7 @@
         <v>105</v>
       </c>
       <c r="E938" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="G938" t="s">
         <v>993</v>
@@ -26462,7 +26450,7 @@
         <v>105</v>
       </c>
       <c r="E939" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="G939" t="s">
         <v>994</v>
@@ -26483,7 +26471,7 @@
         <v>105</v>
       </c>
       <c r="E940" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="G940" t="s">
         <v>995</v>
@@ -26504,7 +26492,7 @@
         <v>105</v>
       </c>
       <c r="E941" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="G941" t="s">
         <v>996</v>
@@ -26534,7 +26522,7 @@
         <v>105</v>
       </c>
       <c r="E942" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="G942" t="s">
         <v>997</v>
@@ -26564,7 +26552,7 @@
         <v>106</v>
       </c>
       <c r="E943" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="F943" t="s">
         <v>111</v>
@@ -26588,7 +26576,7 @@
         <v>106</v>
       </c>
       <c r="E944" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="F944" t="s">
         <v>111</v>
@@ -26651,7 +26639,7 @@
         <v>105</v>
       </c>
       <c r="E950" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="G950" t="s">
         <v>1000</v>
@@ -26672,7 +26660,7 @@
         <v>105</v>
       </c>
       <c r="E951" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="G951" t="s">
         <v>1001</v>
@@ -26693,7 +26681,7 @@
         <v>105</v>
       </c>
       <c r="E952" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="G952" t="s">
         <v>1002</v>
@@ -26777,7 +26765,7 @@
         <v>105</v>
       </c>
       <c r="E959" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="G959" t="s">
         <v>1003</v>
@@ -26798,7 +26786,7 @@
         <v>105</v>
       </c>
       <c r="E960" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="G960" t="s">
         <v>1004</v>
@@ -26819,7 +26807,7 @@
         <v>105</v>
       </c>
       <c r="E961" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="G961" t="s">
         <v>1005</v>
@@ -26840,7 +26828,7 @@
         <v>105</v>
       </c>
       <c r="E962" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="G962" t="s">
         <v>1006</v>
@@ -26870,7 +26858,7 @@
         <v>106</v>
       </c>
       <c r="E963" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="F963" t="s">
         <v>111</v>
@@ -26933,7 +26921,7 @@
         <v>105</v>
       </c>
       <c r="E969" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="G969" t="s">
         <v>1008</v>
@@ -26954,7 +26942,7 @@
         <v>105</v>
       </c>
       <c r="E970" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="G970" t="s">
         <v>1009</v>
@@ -26975,7 +26963,7 @@
         <v>105</v>
       </c>
       <c r="E971" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="G971" t="s">
         <v>1010</v>
@@ -26996,7 +26984,7 @@
         <v>105</v>
       </c>
       <c r="E972" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="G972" t="s">
         <v>1011</v>
@@ -27005,7 +26993,7 @@
         <v>1198</v>
       </c>
       <c r="J972" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="K972" t="s">
         <v>1200</v>
@@ -27026,7 +27014,7 @@
         <v>105</v>
       </c>
       <c r="E973" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="G973" t="s">
         <v>1012</v>
@@ -27056,7 +27044,7 @@
         <v>105</v>
       </c>
       <c r="E974" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="G974" t="s">
         <v>1013</v>
@@ -27086,7 +27074,7 @@
         <v>105</v>
       </c>
       <c r="E975" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="G975" t="s">
         <v>1014</v>
@@ -27116,7 +27104,7 @@
         <v>106</v>
       </c>
       <c r="E976" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F976" t="s">
         <v>111</v>
@@ -27140,7 +27128,7 @@
         <v>106</v>
       </c>
       <c r="E977" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F977" t="s">
         <v>111</v>
@@ -27203,7 +27191,7 @@
         <v>105</v>
       </c>
       <c r="E983" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G983" t="s">
         <v>1017</v>
@@ -27224,7 +27212,7 @@
         <v>105</v>
       </c>
       <c r="E984" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G984" t="s">
         <v>1018</v>
@@ -27254,7 +27242,7 @@
         <v>105</v>
       </c>
       <c r="E985" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G985" t="s">
         <v>1019</v>
@@ -27284,7 +27272,7 @@
         <v>105</v>
       </c>
       <c r="E986" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G986" t="s">
         <v>1020</v>
@@ -27314,7 +27302,7 @@
         <v>105</v>
       </c>
       <c r="E987" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G987" t="s">
         <v>1021</v>
@@ -27344,7 +27332,7 @@
         <v>105</v>
       </c>
       <c r="E988" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G988" t="s">
         <v>1022</v>
@@ -27428,7 +27416,7 @@
         <v>105</v>
       </c>
       <c r="E995" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="G995" t="s">
         <v>1023</v>
@@ -27449,7 +27437,7 @@
         <v>106</v>
       </c>
       <c r="E996" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="F996" t="s">
         <v>111</v>
@@ -27512,7 +27500,7 @@
         <v>105</v>
       </c>
       <c r="E1002" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G1002" t="s">
         <v>1041</v>
@@ -27533,7 +27521,7 @@
         <v>105</v>
       </c>
       <c r="E1003" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G1003" t="s">
         <v>1042</v>
@@ -27563,7 +27551,7 @@
         <v>105</v>
       </c>
       <c r="E1004" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G1004" t="s">
         <v>1043</v>
@@ -27572,7 +27560,7 @@
         <v>1198</v>
       </c>
       <c r="J1004" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K1004" t="s">
         <v>1200</v>
@@ -27593,7 +27581,7 @@
         <v>105</v>
       </c>
       <c r="E1005" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G1005" t="s">
         <v>1044</v>
@@ -27602,7 +27590,7 @@
         <v>1198</v>
       </c>
       <c r="J1005" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="K1005" t="s">
         <v>1200</v>
@@ -27623,7 +27611,7 @@
         <v>105</v>
       </c>
       <c r="E1006" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G1006" t="s">
         <v>1045</v>
@@ -27653,7 +27641,7 @@
         <v>105</v>
       </c>
       <c r="E1007" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G1007" t="s">
         <v>1046</v>
@@ -27662,7 +27650,7 @@
         <v>1198</v>
       </c>
       <c r="J1007" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="K1007" t="s">
         <v>1200</v>
@@ -27683,7 +27671,7 @@
         <v>105</v>
       </c>
       <c r="E1008" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G1008" t="s">
         <v>1047</v>
@@ -27692,7 +27680,7 @@
         <v>1198</v>
       </c>
       <c r="J1008" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="K1008" t="s">
         <v>1200</v>
@@ -27713,7 +27701,7 @@
         <v>105</v>
       </c>
       <c r="E1009" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G1009" t="s">
         <v>1048</v>
@@ -27722,7 +27710,7 @@
         <v>1198</v>
       </c>
       <c r="J1009" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="K1009" t="s">
         <v>1200</v>
@@ -27743,7 +27731,7 @@
         <v>105</v>
       </c>
       <c r="E1010" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G1010" t="s">
         <v>1049</v>
@@ -27752,7 +27740,7 @@
         <v>1198</v>
       </c>
       <c r="J1010" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="K1010" t="s">
         <v>1200</v>
@@ -27773,7 +27761,7 @@
         <v>105</v>
       </c>
       <c r="E1011" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G1011" t="s">
         <v>1050</v>
@@ -27782,7 +27770,7 @@
         <v>1198</v>
       </c>
       <c r="J1011" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="K1011" t="s">
         <v>1200</v>
@@ -27803,7 +27791,7 @@
         <v>105</v>
       </c>
       <c r="E1012" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G1012" t="s">
         <v>1051</v>
@@ -27833,7 +27821,7 @@
         <v>105</v>
       </c>
       <c r="E1013" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G1013" t="s">
         <v>1040</v>
@@ -27863,7 +27851,7 @@
         <v>106</v>
       </c>
       <c r="E1014" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="F1014" t="s">
         <v>111</v>
@@ -27887,7 +27875,7 @@
         <v>106</v>
       </c>
       <c r="E1015" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="F1015" t="s">
         <v>111</v>
@@ -27911,7 +27899,7 @@
         <v>106</v>
       </c>
       <c r="E1016" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="F1016" t="s">
         <v>111</v>
@@ -27923,7 +27911,7 @@
         <v>1198</v>
       </c>
       <c r="J1016" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K1016" t="s">
         <v>1200</v>
@@ -27983,7 +27971,7 @@
         <v>105</v>
       </c>
       <c r="E1022" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="G1022" t="s">
         <v>1055</v>
@@ -28004,7 +27992,7 @@
         <v>105</v>
       </c>
       <c r="E1023" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="G1023" t="s">
         <v>1056</v>
@@ -28034,7 +28022,7 @@
         <v>105</v>
       </c>
       <c r="E1024" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="G1024" t="s">
         <v>1057</v>
@@ -28043,7 +28031,7 @@
         <v>1198</v>
       </c>
       <c r="J1024" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K1024" t="s">
         <v>1200</v>
@@ -28064,7 +28052,7 @@
         <v>105</v>
       </c>
       <c r="E1025" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="G1025" t="s">
         <v>1058</v>
@@ -28094,7 +28082,7 @@
         <v>105</v>
       </c>
       <c r="E1026" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="G1026" t="s">
         <v>1059</v>
@@ -28178,7 +28166,7 @@
         <v>105</v>
       </c>
       <c r="E1033" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G1033" t="s">
         <v>1061</v>
@@ -28199,7 +28187,7 @@
         <v>105</v>
       </c>
       <c r="E1034" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G1034" t="s">
         <v>1062</v>
@@ -28220,7 +28208,7 @@
         <v>105</v>
       </c>
       <c r="E1035" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G1035" t="s">
         <v>1063</v>
@@ -28241,7 +28229,7 @@
         <v>105</v>
       </c>
       <c r="E1036" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G1036" t="s">
         <v>1064</v>
@@ -28250,7 +28238,7 @@
         <v>1198</v>
       </c>
       <c r="J1036" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K1036" t="s">
         <v>1200</v>
@@ -28271,7 +28259,7 @@
         <v>105</v>
       </c>
       <c r="E1037" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G1037" t="s">
         <v>1065</v>
@@ -28280,7 +28268,7 @@
         <v>1198</v>
       </c>
       <c r="J1037" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K1037" t="s">
         <v>1200</v>
@@ -28301,7 +28289,7 @@
         <v>105</v>
       </c>
       <c r="E1038" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G1038" t="s">
         <v>1066</v>
@@ -28331,7 +28319,7 @@
         <v>105</v>
       </c>
       <c r="E1039" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G1039" t="s">
         <v>1067</v>
@@ -28361,7 +28349,7 @@
         <v>105</v>
       </c>
       <c r="E1040" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G1040" t="s">
         <v>1068</v>
@@ -28391,7 +28379,7 @@
         <v>105</v>
       </c>
       <c r="E1041" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G1041" t="s">
         <v>1060</v>
@@ -28421,7 +28409,7 @@
         <v>106</v>
       </c>
       <c r="E1042" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="F1042" t="s">
         <v>111</v>
@@ -28454,7 +28442,7 @@
         <v>106</v>
       </c>
       <c r="E1043" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="F1043" t="s">
         <v>111</v>
@@ -28526,7 +28514,7 @@
         <v>105</v>
       </c>
       <c r="E1049" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="G1049" t="s">
         <v>1071</v>
@@ -28556,7 +28544,7 @@
         <v>105</v>
       </c>
       <c r="E1050" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="G1050" t="s">
         <v>1072</v>
@@ -28586,7 +28574,7 @@
         <v>105</v>
       </c>
       <c r="E1051" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="G1051" t="s">
         <v>1073</v>
@@ -28595,7 +28583,7 @@
         <v>1198</v>
       </c>
       <c r="J1051" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K1051" t="s">
         <v>1200</v>
@@ -28616,7 +28604,7 @@
         <v>105</v>
       </c>
       <c r="E1052" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="G1052" t="s">
         <v>1074</v>
@@ -28625,7 +28613,7 @@
         <v>1198</v>
       </c>
       <c r="J1052" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K1052" t="s">
         <v>1200</v>
@@ -28646,7 +28634,7 @@
         <v>105</v>
       </c>
       <c r="E1053" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="G1053" t="s">
         <v>1075</v>
@@ -28655,7 +28643,7 @@
         <v>1198</v>
       </c>
       <c r="J1053" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K1053" t="s">
         <v>1200</v>
@@ -28730,7 +28718,7 @@
         <v>105</v>
       </c>
       <c r="E1060" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G1060" t="s">
         <v>1076</v>
@@ -28760,7 +28748,7 @@
         <v>105</v>
       </c>
       <c r="E1061" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G1061" t="s">
         <v>1077</v>
@@ -28769,7 +28757,7 @@
         <v>1198</v>
       </c>
       <c r="J1061" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K1061" t="s">
         <v>1200</v>
@@ -28790,7 +28778,7 @@
         <v>105</v>
       </c>
       <c r="E1062" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G1062" t="s">
         <v>1078</v>
@@ -28799,7 +28787,7 @@
         <v>1198</v>
       </c>
       <c r="J1062" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K1062" t="s">
         <v>1200</v>
@@ -28820,7 +28808,7 @@
         <v>105</v>
       </c>
       <c r="E1063" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G1063" t="s">
         <v>1079</v>
@@ -28829,7 +28817,7 @@
         <v>1198</v>
       </c>
       <c r="J1063" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K1063" t="s">
         <v>1200</v>
@@ -28850,7 +28838,7 @@
         <v>105</v>
       </c>
       <c r="E1064" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G1064" t="s">
         <v>1080</v>
@@ -28859,7 +28847,7 @@
         <v>1198</v>
       </c>
       <c r="J1064" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K1064" t="s">
         <v>1200</v>
@@ -28880,7 +28868,7 @@
         <v>105</v>
       </c>
       <c r="E1065" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G1065" t="s">
         <v>1081</v>
@@ -28889,7 +28877,7 @@
         <v>1198</v>
       </c>
       <c r="J1065" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K1065" t="s">
         <v>1200</v>
@@ -28910,7 +28898,7 @@
         <v>105</v>
       </c>
       <c r="E1066" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G1066" t="s">
         <v>1082</v>
@@ -28919,7 +28907,7 @@
         <v>1198</v>
       </c>
       <c r="J1066" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="K1066" t="s">
         <v>1200</v>
@@ -28940,7 +28928,7 @@
         <v>105</v>
       </c>
       <c r="E1067" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G1067" t="s">
         <v>1083</v>
@@ -28949,7 +28937,7 @@
         <v>1198</v>
       </c>
       <c r="J1067" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="K1067" t="s">
         <v>1200</v>
@@ -28970,7 +28958,7 @@
         <v>105</v>
       </c>
       <c r="E1068" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G1068" t="s">
         <v>1084</v>
@@ -28979,7 +28967,7 @@
         <v>1198</v>
       </c>
       <c r="J1068" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="K1068" t="s">
         <v>1200</v>
@@ -29000,7 +28988,7 @@
         <v>105</v>
       </c>
       <c r="E1069" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G1069" t="s">
         <v>1085</v>
@@ -29009,7 +28997,7 @@
         <v>1198</v>
       </c>
       <c r="J1069" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="K1069" t="s">
         <v>1200</v>
@@ -29030,7 +29018,7 @@
         <v>106</v>
       </c>
       <c r="E1070" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="F1070" t="s">
         <v>111</v>
@@ -29042,7 +29030,7 @@
         <v>1198</v>
       </c>
       <c r="J1070" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="K1070" t="s">
         <v>1200</v>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589C6578-A421-524E-90D6-1F77991CC40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DC3380-A992-124B-82C5-3098548C4EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="5" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="1240" yWindow="500" windowWidth="21640" windowHeight="19440" activeTab="3" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5473" uniqueCount="1273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5600" uniqueCount="1283">
   <si>
     <t>page_id</t>
   </si>
@@ -3707,15 +3707,6 @@
     <t>(AR; Sp.)</t>
   </si>
   <si>
-    <t>[Szenentitel]</t>
-  </si>
-  <si>
-    <t>[Rückenschutzformel]</t>
-  </si>
-  <si>
-    <t>[Beziehung]</t>
-  </si>
-  <si>
     <t>*di(⸗i) n⸗k*</t>
   </si>
   <si>
@@ -3861,6 +3852,45 @@
   </si>
   <si>
     <t>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/</t>
+  </si>
+  <si>
+    <t>Filiationsangabe</t>
+  </si>
+  <si>
+    <t>AR:</t>
+  </si>
+  <si>
+    <t>MR:</t>
+  </si>
+  <si>
+    <t>ab NR:</t>
+  </si>
+  <si>
+    <t>gl_person_filiation_AR</t>
+  </si>
+  <si>
+    <t>gl_person_filiation_MR</t>
+  </si>
+  <si>
+    <t>gl_person_filiation_NR</t>
+  </si>
+  <si>
+    <t>(= Vater)</t>
+  </si>
+  <si>
+    <t>*sꜣ⸗f*</t>
+  </si>
+  <si>
+    <t>(= Sohn)</t>
+  </si>
+  <si>
+    <t>*sꜣ*</t>
+  </si>
+  <si>
+    <t>bei Töchtern: *sꜣ.t* „Tochter“( statt *sꜣ*)</t>
+  </si>
+  <si>
+    <t>bei Müttern im AR: *sꜣ⸗s*</t>
   </si>
 </sst>
 </file>
@@ -5283,7 +5313,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEDD5969-C8E3-C04D-AF17-FDEFB8218719}">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="4" bestFit="1" customWidth="1"/>
@@ -5672,7 +5702,7 @@
         <v>77</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>55</v>
@@ -5683,9 +5713,7 @@
       <c r="G18" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>1090</v>
-      </c>
+      <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="4">
         <v>6</v>
@@ -5701,14 +5729,11 @@
       <c r="C19" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>427</v>
-      </c>
       <c r="G19" s="4" t="s">
         <v>54</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="4">
@@ -5720,231 +5745,259 @@
         <v>77</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>1164</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>431</v>
+      <c r="E20" s="2" t="s">
+        <v>427</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J20" s="2" t="s">
-        <v>1097</v>
-      </c>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
       <c r="K20" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>77</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>1165</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>439</v>
-      </c>
       <c r="G21" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J21" s="2" t="s">
-        <v>1099</v>
-      </c>
+      <c r="I21" s="5" t="s">
+        <v>1091</v>
+      </c>
+      <c r="J21" s="5"/>
       <c r="K21" s="4">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>77</v>
       </c>
+      <c r="B22" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="C22" s="4" t="s">
         <v>55</v>
       </c>
+      <c r="D22" s="4" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>1097</v>
+      </c>
       <c r="K22" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="51" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>77</v>
       </c>
+      <c r="B23" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="C23" s="4" t="s">
         <v>55</v>
       </c>
+      <c r="D23" s="4" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>1099</v>
+      </c>
       <c r="K23" s="4">
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>1270</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K24" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>468</v>
+        <v>77</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>1166</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>484</v>
+      <c r="E25" s="4" t="s">
+        <v>1271</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J25" s="2" t="s">
-        <v>1099</v>
-      </c>
       <c r="K25" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>468</v>
+        <v>77</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>1167</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>486</v>
-      </c>
       <c r="G26" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J26" s="2" t="s">
-        <v>1099</v>
+      <c r="I26" s="5" t="s">
+        <v>1274</v>
       </c>
       <c r="K26" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>468</v>
+        <v>77</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>487</v>
+      <c r="E27" s="4" t="s">
+        <v>1272</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J27" s="2" t="s">
-        <v>1099</v>
-      </c>
       <c r="K27" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>468</v>
+        <v>77</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="G28" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J28" s="2" t="s">
-        <v>1099</v>
+      <c r="I28" s="5" t="s">
+        <v>1275</v>
       </c>
       <c r="K28" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K29" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>1183</v>
+        <v>55</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>54</v>
       </c>
+      <c r="I30" s="5" t="s">
+        <v>1276</v>
+      </c>
       <c r="K30" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>1169</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>512</v>
+      <c r="E31" s="2" t="s">
+        <v>1281</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J31" s="2" t="s">
-        <v>1098</v>
-      </c>
       <c r="K31" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>26</v>
@@ -5952,134 +6005,307 @@
       <c r="C32" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="E32" s="2" t="s">
-        <v>535</v>
+        <v>1282</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>54</v>
       </c>
       <c r="K32" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K42" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K43" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K44" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
+    <row r="45" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K45" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B47" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K47" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C48" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D48" s="4" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="K48" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K49" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>1165</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F50" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G50" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="J50" s="2" t="s">
         <v>1099</v>
       </c>
-      <c r="K33" s="4">
+      <c r="K50" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
+    <row r="52" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B52" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C52" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D52" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G52" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="I35" s="5" t="s">
+      <c r="I52" s="5" t="s">
         <v>1139</v>
       </c>
-      <c r="K35" s="4">
+      <c r="K52" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
+    <row r="53" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B53" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C53" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D53" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>1188</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G53" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="K36" s="4">
+      <c r="K53" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
+    <row r="54" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B54" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C54" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D54" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F54" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="J54" s="2" t="s">
         <v>1098</v>
       </c>
-      <c r="K37" s="4">
+      <c r="K54" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
+    <row r="55" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B55" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C55" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D55" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I38" s="5" t="s">
+      <c r="I55" s="5" t="s">
         <v>1146</v>
       </c>
-      <c r="K38" s="4">
+      <c r="K55" s="4">
         <v>4</v>
       </c>
     </row>
@@ -6090,7 +6316,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C735804-F835-2748-99C4-5C04B7D215F0}">
-  <dimension ref="A1:N187"/>
+  <dimension ref="A1:N210"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.83203125" bestFit="1" customWidth="1"/>
@@ -8721,7 +8947,7 @@
         <v>45</v>
       </c>
       <c r="D125" s="21" t="s">
-        <v>1223</v>
+        <v>562</v>
       </c>
       <c r="N125" s="21" t="s">
         <v>90</v>
@@ -8738,7 +8964,7 @@
         <v>45</v>
       </c>
       <c r="D126" s="21" t="s">
-        <v>1221</v>
+        <v>587</v>
       </c>
       <c r="N126" s="21" t="s">
         <v>90</v>
@@ -8775,7 +9001,7 @@
         <v>45</v>
       </c>
       <c r="D128" s="21" t="s">
-        <v>1222</v>
+        <v>568</v>
       </c>
       <c r="N128" s="21" t="s">
         <v>90</v>
@@ -9751,6 +9977,330 @@
         <v>97</v>
       </c>
       <c r="N187" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B191">
+        <v>1</v>
+      </c>
+      <c r="C191" t="s">
+        <v>45</v>
+      </c>
+      <c r="D191" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N191" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B192">
+        <v>2</v>
+      </c>
+      <c r="C192" t="s">
+        <v>46</v>
+      </c>
+      <c r="D192" t="s">
+        <v>50</v>
+      </c>
+      <c r="M192" t="s">
+        <v>99</v>
+      </c>
+      <c r="N192" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B193">
+        <v>3</v>
+      </c>
+      <c r="C193" t="s">
+        <v>45</v>
+      </c>
+      <c r="D193" t="s">
+        <v>1277</v>
+      </c>
+      <c r="N193" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B194">
+        <v>4</v>
+      </c>
+      <c r="C194" t="s">
+        <v>45</v>
+      </c>
+      <c r="D194" t="s">
+        <v>1278</v>
+      </c>
+      <c r="N194" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B195">
+        <v>5</v>
+      </c>
+      <c r="C195" t="s">
+        <v>46</v>
+      </c>
+      <c r="D195" t="s">
+        <v>50</v>
+      </c>
+      <c r="M195" t="s">
+        <v>99</v>
+      </c>
+      <c r="N195" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B196">
+        <v>6</v>
+      </c>
+      <c r="C196" t="s">
+        <v>45</v>
+      </c>
+      <c r="D196" t="s">
+        <v>1279</v>
+      </c>
+      <c r="N196" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B198">
+        <v>1</v>
+      </c>
+      <c r="C198" t="s">
+        <v>45</v>
+      </c>
+      <c r="D198" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N198" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B199">
+        <v>2</v>
+      </c>
+      <c r="C199" t="s">
+        <v>46</v>
+      </c>
+      <c r="D199" t="s">
+        <v>50</v>
+      </c>
+      <c r="M199" t="s">
+        <v>99</v>
+      </c>
+      <c r="N199" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B200">
+        <v>3</v>
+      </c>
+      <c r="C200" t="s">
+        <v>45</v>
+      </c>
+      <c r="D200" t="s">
+        <v>1277</v>
+      </c>
+      <c r="N200" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B201">
+        <v>4</v>
+      </c>
+      <c r="C201" t="s">
+        <v>45</v>
+      </c>
+      <c r="D201" t="s">
+        <v>1280</v>
+      </c>
+      <c r="N201" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B202">
+        <v>5</v>
+      </c>
+      <c r="C202" t="s">
+        <v>46</v>
+      </c>
+      <c r="D202" t="s">
+        <v>50</v>
+      </c>
+      <c r="M202" t="s">
+        <v>99</v>
+      </c>
+      <c r="N202" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B203">
+        <v>6</v>
+      </c>
+      <c r="C203" t="s">
+        <v>45</v>
+      </c>
+      <c r="D203" t="s">
+        <v>1279</v>
+      </c>
+      <c r="N203" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A205" s="5" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B205">
+        <v>1</v>
+      </c>
+      <c r="C205" t="s">
+        <v>45</v>
+      </c>
+      <c r="D205" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N205" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A206" s="5" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B206">
+        <v>2</v>
+      </c>
+      <c r="C206" t="s">
+        <v>46</v>
+      </c>
+      <c r="D206" t="s">
+        <v>50</v>
+      </c>
+      <c r="M206" t="s">
+        <v>99</v>
+      </c>
+      <c r="N206" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A207" s="5" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B207">
+        <v>3</v>
+      </c>
+      <c r="C207" t="s">
+        <v>45</v>
+      </c>
+      <c r="D207" t="s">
+        <v>1279</v>
+      </c>
+      <c r="N207" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A208" s="5" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B208">
+        <v>4</v>
+      </c>
+      <c r="C208" t="s">
+        <v>45</v>
+      </c>
+      <c r="D208" t="s">
+        <v>1280</v>
+      </c>
+      <c r="N208" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A209" s="5" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B209">
+        <v>5</v>
+      </c>
+      <c r="C209" t="s">
+        <v>46</v>
+      </c>
+      <c r="D209" t="s">
+        <v>50</v>
+      </c>
+      <c r="M209" t="s">
+        <v>99</v>
+      </c>
+      <c r="N209" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A210" s="5" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B210">
+        <v>6</v>
+      </c>
+      <c r="C210" t="s">
+        <v>45</v>
+      </c>
+      <c r="D210" t="s">
+        <v>1277</v>
+      </c>
+      <c r="N210" t="s">
         <v>90</v>
       </c>
     </row>
@@ -15457,7 +16007,7 @@
         <v>39</v>
       </c>
       <c r="L325" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.2">
@@ -15734,7 +16284,7 @@
         <v>39</v>
       </c>
       <c r="L343" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.2">
@@ -15748,7 +16298,7 @@
         <v>105</v>
       </c>
       <c r="E344" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="G344" t="s">
         <v>1025</v>
@@ -15769,7 +16319,7 @@
         <v>105</v>
       </c>
       <c r="E345" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="G345" t="s">
         <v>1026</v>
@@ -15799,7 +16349,7 @@
         <v>105</v>
       </c>
       <c r="E346" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="G346" t="s">
         <v>1027</v>
@@ -15829,7 +16379,7 @@
         <v>105</v>
       </c>
       <c r="E347" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="G347" t="s">
         <v>1028</v>
@@ -15859,7 +16409,7 @@
         <v>105</v>
       </c>
       <c r="E348" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="G348" t="s">
         <v>1029</v>
@@ -15946,7 +16496,7 @@
         <v>105</v>
       </c>
       <c r="E354" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="F354" t="s">
         <v>1031</v>
@@ -15970,7 +16520,7 @@
         <v>105</v>
       </c>
       <c r="E355" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="F355" t="s">
         <v>1031</v>
@@ -15994,7 +16544,7 @@
         <v>105</v>
       </c>
       <c r="E356" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="F356" t="s">
         <v>1031</v>
@@ -16055,7 +16605,7 @@
         <v>105</v>
       </c>
       <c r="E360" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="F360" t="s">
         <v>1037</v>
@@ -16080,7 +16630,7 @@
       </c>
       <c r="D361" s="32"/>
       <c r="E361" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="F361" t="s">
         <v>1037</v>
@@ -16174,7 +16724,7 @@
       </c>
       <c r="D369" s="32"/>
       <c r="E369" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="G369" t="s">
         <v>121</v>
@@ -16199,7 +16749,7 @@
       </c>
       <c r="D370" s="32"/>
       <c r="E370" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="G370" t="s">
         <v>123</v>
@@ -16233,7 +16783,7 @@
       </c>
       <c r="D371" s="32"/>
       <c r="E371" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="G371" t="s">
         <v>124</v>
@@ -16267,7 +16817,7 @@
       </c>
       <c r="D372" s="32"/>
       <c r="E372" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="F372" t="s">
         <v>111</v>
@@ -16414,7 +16964,7 @@
       </c>
       <c r="D381" s="32"/>
       <c r="E381" s="32" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="G381" t="s">
         <v>127</v>
@@ -16489,7 +17039,7 @@
       <c r="D386" s="32"/>
       <c r="E386" s="32"/>
       <c r="L386" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.2">
@@ -16504,10 +17054,10 @@
       </c>
       <c r="D387" s="32"/>
       <c r="E387" s="32" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="G387" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="H387" t="s">
         <v>113</v>
@@ -16594,7 +17144,7 @@
       </c>
       <c r="D393" s="32"/>
       <c r="E393" s="32" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="G393" t="s">
         <v>589</v>
@@ -16619,7 +17169,7 @@
       </c>
       <c r="D394" s="32"/>
       <c r="E394" s="32" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="G394" t="s">
         <v>590</v>
@@ -16644,7 +17194,7 @@
       </c>
       <c r="D395" s="32"/>
       <c r="E395" s="32" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="G395" t="s">
         <v>591</v>
@@ -16669,7 +17219,7 @@
       </c>
       <c r="D396" s="32"/>
       <c r="E396" s="32" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="G396" t="s">
         <v>592</v>
@@ -16703,7 +17253,7 @@
       </c>
       <c r="D397" s="32"/>
       <c r="E397" s="32" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="G397" t="s">
         <v>593</v>
@@ -16737,7 +17287,7 @@
       </c>
       <c r="D398" s="32"/>
       <c r="E398" s="32" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="G398" t="s">
         <v>594</v>
@@ -16771,7 +17321,7 @@
       </c>
       <c r="D399" s="32"/>
       <c r="E399" s="32" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="G399" t="s">
         <v>595</v>
@@ -16867,7 +17417,7 @@
         <v>105</v>
       </c>
       <c r="E407" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="G407" t="s">
         <v>597</v>
@@ -16891,7 +17441,7 @@
         <v>105</v>
       </c>
       <c r="E408" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="G408" t="s">
         <v>598</v>
@@ -16915,7 +17465,7 @@
         <v>105</v>
       </c>
       <c r="E409" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="G409" t="s">
         <v>599</v>
@@ -16939,7 +17489,7 @@
         <v>105</v>
       </c>
       <c r="E410" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="G410" t="s">
         <v>600</v>
@@ -16963,7 +17513,7 @@
         <v>105</v>
       </c>
       <c r="E411" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="G411" t="s">
         <v>601</v>
@@ -16987,7 +17537,7 @@
         <v>105</v>
       </c>
       <c r="E412" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="G412" t="s">
         <v>602</v>
@@ -17076,7 +17626,7 @@
         <v>105</v>
       </c>
       <c r="E419" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="G419" t="s">
         <v>604</v>
@@ -17100,7 +17650,7 @@
         <v>105</v>
       </c>
       <c r="E420" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="G420" t="s">
         <v>605</v>
@@ -17124,7 +17674,7 @@
         <v>105</v>
       </c>
       <c r="E421" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="G421" t="s">
         <v>606</v>
@@ -17148,7 +17698,7 @@
         <v>105</v>
       </c>
       <c r="E422" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="G422" t="s">
         <v>607</v>
@@ -17172,7 +17722,7 @@
         <v>105</v>
       </c>
       <c r="E423" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="G423" t="s">
         <v>608</v>
@@ -17205,7 +17755,7 @@
         <v>106</v>
       </c>
       <c r="E424" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F424" t="s">
         <v>111</v>
@@ -17274,7 +17824,7 @@
         <v>105</v>
       </c>
       <c r="E429" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F429" t="s">
         <v>612</v>
@@ -17301,7 +17851,7 @@
         <v>105</v>
       </c>
       <c r="E430" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F430" t="s">
         <v>612</v>
@@ -17328,7 +17878,7 @@
         <v>105</v>
       </c>
       <c r="E431" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F431" t="s">
         <v>612</v>
@@ -17364,7 +17914,7 @@
         <v>105</v>
       </c>
       <c r="E432" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F432" t="s">
         <v>612</v>
@@ -17428,7 +17978,7 @@
         <v>105</v>
       </c>
       <c r="E436" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F436" t="s">
         <v>619</v>
@@ -17483,7 +18033,7 @@
         <v>105</v>
       </c>
       <c r="E440" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F440" t="s">
         <v>625</v>
@@ -17510,7 +18060,7 @@
         <v>105</v>
       </c>
       <c r="E441" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F441" t="s">
         <v>625</v>
@@ -17537,7 +18087,7 @@
         <v>105</v>
       </c>
       <c r="E442" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F442" t="s">
         <v>625</v>
@@ -17564,7 +18114,7 @@
         <v>105</v>
       </c>
       <c r="E443" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F443" t="s">
         <v>625</v>
@@ -17628,7 +18178,7 @@
         <v>105</v>
       </c>
       <c r="E447" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F447" t="s">
         <v>632</v>
@@ -17664,7 +18214,7 @@
         <v>105</v>
       </c>
       <c r="E448" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F448" t="s">
         <v>632</v>
@@ -17700,7 +18250,7 @@
         <v>105</v>
       </c>
       <c r="E449" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F449" t="s">
         <v>632</v>
@@ -17736,7 +18286,7 @@
         <v>105</v>
       </c>
       <c r="E450" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F450" t="s">
         <v>632</v>
@@ -17772,7 +18322,7 @@
         <v>105</v>
       </c>
       <c r="E451" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F451" t="s">
         <v>632</v>
@@ -17808,7 +18358,7 @@
         <v>105</v>
       </c>
       <c r="E452" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F452" t="s">
         <v>632</v>
@@ -17844,7 +18394,7 @@
         <v>105</v>
       </c>
       <c r="E453" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F453" t="s">
         <v>632</v>
@@ -17880,7 +18430,7 @@
         <v>105</v>
       </c>
       <c r="E454" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F454" t="s">
         <v>632</v>
@@ -17916,7 +18466,7 @@
         <v>105</v>
       </c>
       <c r="E455" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F455" t="s">
         <v>632</v>
@@ -17980,7 +18530,7 @@
         <v>105</v>
       </c>
       <c r="E463" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="G463" t="s">
         <v>643</v>
@@ -18004,7 +18554,7 @@
         <v>105</v>
       </c>
       <c r="E464" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="G464" t="s">
         <v>644</v>
@@ -18028,7 +18578,7 @@
         <v>105</v>
       </c>
       <c r="E465" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="G465" t="s">
         <v>645</v>
@@ -18052,7 +18602,7 @@
         <v>105</v>
       </c>
       <c r="E466" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="G466" t="s">
         <v>646</v>
@@ -18085,7 +18635,7 @@
         <v>105</v>
       </c>
       <c r="E467" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="G467" t="s">
         <v>647</v>
@@ -18118,7 +18668,7 @@
         <v>105</v>
       </c>
       <c r="E468" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="G468" t="s">
         <v>648</v>
@@ -18151,7 +18701,7 @@
         <v>105</v>
       </c>
       <c r="E469" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="G469" t="s">
         <v>649</v>
@@ -18237,7 +18787,7 @@
         <v>105</v>
       </c>
       <c r="E475" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="F475" t="s">
         <v>652</v>
@@ -18264,7 +18814,7 @@
         <v>105</v>
       </c>
       <c r="E476" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="F476" t="s">
         <v>652</v>
@@ -18319,7 +18869,7 @@
         <v>105</v>
       </c>
       <c r="E481" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="G481" t="s">
         <v>657</v>
@@ -18343,7 +18893,7 @@
         <v>105</v>
       </c>
       <c r="E482" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="G482" t="s">
         <v>658</v>
@@ -18367,7 +18917,7 @@
         <v>105</v>
       </c>
       <c r="E483" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="G483" t="s">
         <v>659</v>
@@ -18400,7 +18950,7 @@
         <v>105</v>
       </c>
       <c r="E484" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="G484" t="s">
         <v>660</v>
@@ -18433,7 +18983,7 @@
         <v>105</v>
       </c>
       <c r="E485" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="G485" t="s">
         <v>661</v>
@@ -18519,7 +19069,7 @@
         <v>105</v>
       </c>
       <c r="E491" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="F491" t="s">
         <v>662</v>
@@ -18574,7 +19124,7 @@
         <v>105</v>
       </c>
       <c r="E495" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="F495" t="s">
         <v>665</v>
@@ -18629,7 +19179,7 @@
         <v>105</v>
       </c>
       <c r="E499" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="F499" t="s">
         <v>668</v>
@@ -18684,7 +19234,7 @@
         <v>105</v>
       </c>
       <c r="E503" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="F503" t="s">
         <v>670</v>
@@ -18739,7 +19289,7 @@
         <v>105</v>
       </c>
       <c r="E507" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="F507" t="s">
         <v>674</v>
@@ -18803,7 +19353,7 @@
         <v>105</v>
       </c>
       <c r="E511" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="F511" t="s">
         <v>675</v>
@@ -18867,7 +19417,7 @@
         <v>105</v>
       </c>
       <c r="E515" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="F515" t="s">
         <v>676</v>
@@ -18931,7 +19481,7 @@
         <v>105</v>
       </c>
       <c r="E519" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="F519" t="s">
         <v>677</v>
@@ -18986,7 +19536,7 @@
         <v>105</v>
       </c>
       <c r="E525" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G525" t="s">
         <v>688</v>
@@ -19010,7 +19560,7 @@
         <v>105</v>
       </c>
       <c r="E526" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G526" t="s">
         <v>689</v>
@@ -19034,7 +19584,7 @@
         <v>105</v>
       </c>
       <c r="E527" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G527" t="s">
         <v>690</v>
@@ -19058,7 +19608,7 @@
         <v>105</v>
       </c>
       <c r="E528" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G528" t="s">
         <v>691</v>
@@ -19138,7 +19688,7 @@
         <v>105</v>
       </c>
       <c r="E535" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="G535" t="s">
         <v>732</v>
@@ -19162,7 +19712,7 @@
         <v>105</v>
       </c>
       <c r="E536" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="G536" t="s">
         <v>733</v>
@@ -19186,7 +19736,7 @@
         <v>105</v>
       </c>
       <c r="E537" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="G537" t="s">
         <v>734</v>
@@ -19210,7 +19760,7 @@
         <v>105</v>
       </c>
       <c r="E538" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="G538" t="s">
         <v>735</v>
@@ -19243,7 +19793,7 @@
         <v>105</v>
       </c>
       <c r="E539" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="G539" t="s">
         <v>736</v>
@@ -19276,7 +19826,7 @@
         <v>105</v>
       </c>
       <c r="E540" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="G540" t="s">
         <v>737</v>
@@ -19309,7 +19859,7 @@
         <v>105</v>
       </c>
       <c r="E541" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="G541" t="s">
         <v>738</v>
@@ -19342,7 +19892,7 @@
         <v>105</v>
       </c>
       <c r="E542" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="G542" t="s">
         <v>739</v>
@@ -19375,7 +19925,7 @@
         <v>105</v>
       </c>
       <c r="E543" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="G543" t="s">
         <v>740</v>
@@ -19408,7 +19958,7 @@
         <v>105</v>
       </c>
       <c r="E544" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="G544" t="s">
         <v>741</v>
@@ -19441,7 +19991,7 @@
         <v>106</v>
       </c>
       <c r="E545" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F545" t="s">
         <v>111</v>
@@ -19510,7 +20060,7 @@
         <v>105</v>
       </c>
       <c r="E550" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F550" t="s">
         <v>755</v>
@@ -19537,7 +20087,7 @@
         <v>105</v>
       </c>
       <c r="E551" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F551" t="s">
         <v>755</v>
@@ -19564,7 +20114,7 @@
         <v>105</v>
       </c>
       <c r="E552" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F552" t="s">
         <v>755</v>
@@ -19591,7 +20141,7 @@
         <v>105</v>
       </c>
       <c r="E553" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F553" t="s">
         <v>755</v>
@@ -19627,7 +20177,7 @@
         <v>105</v>
       </c>
       <c r="E554" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F554" t="s">
         <v>755</v>
@@ -19691,7 +20241,7 @@
         <v>105</v>
       </c>
       <c r="E558" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F558" t="s">
         <v>756</v>
@@ -19718,7 +20268,7 @@
         <v>105</v>
       </c>
       <c r="E559" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F559" t="s">
         <v>756</v>
@@ -19742,7 +20292,7 @@
         <v>105</v>
       </c>
       <c r="E560" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F560" t="s">
         <v>756</v>
@@ -19766,7 +20316,7 @@
         <v>105</v>
       </c>
       <c r="E561" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F561" t="s">
         <v>756</v>
@@ -19790,7 +20340,7 @@
         <v>105</v>
       </c>
       <c r="E562" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F562" t="s">
         <v>756</v>
@@ -19814,7 +20364,7 @@
         <v>105</v>
       </c>
       <c r="E563" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F563" t="s">
         <v>756</v>
@@ -19838,7 +20388,7 @@
         <v>105</v>
       </c>
       <c r="E564" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F564" t="s">
         <v>756</v>
@@ -19862,7 +20412,7 @@
         <v>105</v>
       </c>
       <c r="E565" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F565" t="s">
         <v>756</v>
@@ -19886,7 +20436,7 @@
         <v>105</v>
       </c>
       <c r="E566" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F566" t="s">
         <v>756</v>
@@ -19947,7 +20497,7 @@
         <v>105</v>
       </c>
       <c r="E570" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F570" t="s">
         <v>757</v>
@@ -19999,7 +20549,7 @@
         <v>105</v>
       </c>
       <c r="E574" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F574" t="s">
         <v>758</v>
@@ -20054,7 +20604,7 @@
         <v>105</v>
       </c>
       <c r="E578" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F578" t="s">
         <v>759</v>
@@ -20078,7 +20628,7 @@
         <v>105</v>
       </c>
       <c r="E579" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F579" t="s">
         <v>759</v>
@@ -20102,7 +20652,7 @@
         <v>105</v>
       </c>
       <c r="E580" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F580" t="s">
         <v>759</v>
@@ -20135,7 +20685,7 @@
         <v>105</v>
       </c>
       <c r="E581" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F581" t="s">
         <v>759</v>
@@ -20168,7 +20718,7 @@
         <v>105</v>
       </c>
       <c r="E582" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F582" t="s">
         <v>759</v>
@@ -20201,7 +20751,7 @@
         <v>105</v>
       </c>
       <c r="E583" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F583" t="s">
         <v>759</v>
@@ -20234,7 +20784,7 @@
         <v>105</v>
       </c>
       <c r="E584" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F584" t="s">
         <v>759</v>
@@ -20295,7 +20845,7 @@
         <v>105</v>
       </c>
       <c r="E588" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F588" t="s">
         <v>760</v>
@@ -20319,7 +20869,7 @@
         <v>105</v>
       </c>
       <c r="E589" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F589" t="s">
         <v>760</v>
@@ -20371,7 +20921,7 @@
         <v>105</v>
       </c>
       <c r="E593" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F593" t="s">
         <v>761</v>
@@ -20426,7 +20976,7 @@
         <v>105</v>
       </c>
       <c r="E602" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="G602" t="s">
         <v>788</v>
@@ -20447,7 +20997,7 @@
         <v>105</v>
       </c>
       <c r="E603" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="G603" t="s">
         <v>789</v>
@@ -20477,7 +21027,7 @@
         <v>105</v>
       </c>
       <c r="E604" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="G604" t="s">
         <v>790</v>
@@ -20557,7 +21107,7 @@
         <v>105</v>
       </c>
       <c r="E611" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="G611" t="s">
         <v>791</v>
@@ -20578,7 +21128,7 @@
         <v>105</v>
       </c>
       <c r="E612" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="G612" t="s">
         <v>792</v>
@@ -20599,7 +21149,7 @@
         <v>105</v>
       </c>
       <c r="E613" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="G613" t="s">
         <v>793</v>
@@ -20629,7 +21179,7 @@
         <v>105</v>
       </c>
       <c r="E614" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="G614" t="s">
         <v>794</v>
@@ -20659,7 +21209,7 @@
         <v>106</v>
       </c>
       <c r="E615" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="F615" t="s">
         <v>111</v>
@@ -20728,7 +21278,7 @@
         <v>105</v>
       </c>
       <c r="E620" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="F620" t="s">
         <v>804</v>
@@ -20783,7 +21333,7 @@
         <v>105</v>
       </c>
       <c r="E624" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="F624" t="s">
         <v>805</v>
@@ -20807,7 +21357,7 @@
         <v>105</v>
       </c>
       <c r="E625" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="F625" t="s">
         <v>805</v>
@@ -20859,7 +21409,7 @@
         <v>105</v>
       </c>
       <c r="E630" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="G630" t="s">
         <v>807</v>
@@ -20880,7 +21430,7 @@
         <v>105</v>
       </c>
       <c r="E631" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="G631" t="s">
         <v>808</v>
@@ -20910,7 +21460,7 @@
         <v>105</v>
       </c>
       <c r="E632" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="G632" t="s">
         <v>809</v>
@@ -20940,7 +21490,7 @@
         <v>105</v>
       </c>
       <c r="E633" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="G633" t="s">
         <v>810</v>
@@ -20970,7 +21520,7 @@
         <v>105</v>
       </c>
       <c r="E634" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="G634" t="s">
         <v>811</v>
@@ -21000,7 +21550,7 @@
         <v>105</v>
       </c>
       <c r="E635" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="G635" t="s">
         <v>812</v>
@@ -21030,7 +21580,7 @@
         <v>105</v>
       </c>
       <c r="E636" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="G636" t="s">
         <v>813</v>
@@ -21060,7 +21610,7 @@
         <v>105</v>
       </c>
       <c r="E637" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="G637" t="s">
         <v>806</v>
@@ -21090,7 +21640,7 @@
         <v>106</v>
       </c>
       <c r="E638" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F638" t="s">
         <v>111</v>
@@ -21123,7 +21673,7 @@
         <v>106</v>
       </c>
       <c r="E639" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F639" t="s">
         <v>111</v>
@@ -21156,7 +21706,7 @@
         <v>106</v>
       </c>
       <c r="E640" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F640" t="s">
         <v>111</v>
@@ -21189,7 +21739,7 @@
         <v>106</v>
       </c>
       <c r="E641" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F641" t="s">
         <v>111</v>
@@ -21264,7 +21814,7 @@
         <v>105</v>
       </c>
       <c r="E646" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F646" t="s">
         <v>819</v>
@@ -21288,7 +21838,7 @@
         <v>105</v>
       </c>
       <c r="E647" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F647" t="s">
         <v>819</v>
@@ -21312,7 +21862,7 @@
         <v>105</v>
       </c>
       <c r="E648" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F648" t="s">
         <v>819</v>
@@ -21345,7 +21895,7 @@
         <v>105</v>
       </c>
       <c r="E649" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F649" t="s">
         <v>819</v>
@@ -21378,7 +21928,7 @@
         <v>105</v>
       </c>
       <c r="E650" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F650" t="s">
         <v>819</v>
@@ -21411,7 +21961,7 @@
         <v>105</v>
       </c>
       <c r="E651" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F651" t="s">
         <v>819</v>
@@ -21472,7 +22022,7 @@
         <v>105</v>
       </c>
       <c r="E655" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F655" t="s">
         <v>824</v>
@@ -21496,7 +22046,7 @@
         <v>105</v>
       </c>
       <c r="E656" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F656" t="s">
         <v>824</v>
@@ -21529,7 +22079,7 @@
         <v>105</v>
       </c>
       <c r="E657" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F657" t="s">
         <v>824</v>
@@ -21562,7 +22112,7 @@
         <v>105</v>
       </c>
       <c r="E658" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F658" t="s">
         <v>824</v>
@@ -21595,7 +22145,7 @@
         <v>105</v>
       </c>
       <c r="E659" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F659" t="s">
         <v>824</v>
@@ -21656,7 +22206,7 @@
         <v>105</v>
       </c>
       <c r="E663" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="G663" t="s">
         <v>836</v>
@@ -21680,7 +22230,7 @@
         <v>106</v>
       </c>
       <c r="E664" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="F664" t="s">
         <v>111</v>
@@ -21704,7 +22254,7 @@
         <v>106</v>
       </c>
       <c r="E665" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="F665" t="s">
         <v>111</v>
@@ -21767,7 +22317,7 @@
         <v>105</v>
       </c>
       <c r="E671" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="G671" t="s">
         <v>840</v>
@@ -21788,7 +22338,7 @@
         <v>105</v>
       </c>
       <c r="E672" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="G672" t="s">
         <v>841</v>
@@ -21809,7 +22359,7 @@
         <v>105</v>
       </c>
       <c r="E673" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="G673" t="s">
         <v>842</v>
@@ -21839,7 +22389,7 @@
         <v>105</v>
       </c>
       <c r="E674" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="G674" t="s">
         <v>843</v>
@@ -21869,7 +22419,7 @@
         <v>105</v>
       </c>
       <c r="E675" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="G675" t="s">
         <v>844</v>
@@ -21899,7 +22449,7 @@
         <v>105</v>
       </c>
       <c r="E676" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="G676" t="s">
         <v>845</v>
@@ -21929,7 +22479,7 @@
         <v>105</v>
       </c>
       <c r="E677" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="G677" t="s">
         <v>846</v>
@@ -21959,7 +22509,7 @@
         <v>105</v>
       </c>
       <c r="E678" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="G678" t="s">
         <v>847</v>
@@ -21989,7 +22539,7 @@
         <v>105</v>
       </c>
       <c r="E679" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="G679" t="s">
         <v>848</v>
@@ -22019,7 +22569,7 @@
         <v>105</v>
       </c>
       <c r="E680" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="G680" t="s">
         <v>839</v>
@@ -22049,7 +22599,7 @@
         <v>106</v>
       </c>
       <c r="E681" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="F681" t="s">
         <v>111</v>
@@ -22082,7 +22632,7 @@
         <v>106</v>
       </c>
       <c r="E682" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="F682" t="s">
         <v>111</v>
@@ -22154,7 +22704,7 @@
         <v>105</v>
       </c>
       <c r="E688" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="G688" t="s">
         <v>851</v>
@@ -22175,7 +22725,7 @@
         <v>105</v>
       </c>
       <c r="E689" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="G689" t="s">
         <v>852</v>
@@ -22196,7 +22746,7 @@
         <v>105</v>
       </c>
       <c r="E690" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="G690" t="s">
         <v>853</v>
@@ -22217,7 +22767,7 @@
         <v>106</v>
       </c>
       <c r="E691" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="F691" t="s">
         <v>111</v>
@@ -22283,7 +22833,7 @@
         <v>105</v>
       </c>
       <c r="E697" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="G697" t="s">
         <v>855</v>
@@ -22304,7 +22854,7 @@
         <v>105</v>
       </c>
       <c r="E698" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="G698" t="s">
         <v>856</v>
@@ -22325,7 +22875,7 @@
         <v>105</v>
       </c>
       <c r="E699" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="G699" t="s">
         <v>857</v>
@@ -22403,7 +22953,7 @@
         <v>105</v>
       </c>
       <c r="E705" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="F705" t="s">
         <v>861</v>
@@ -22427,7 +22977,7 @@
         <v>105</v>
       </c>
       <c r="E706" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="F706" t="s">
         <v>861</v>
@@ -22451,7 +23001,7 @@
         <v>105</v>
       </c>
       <c r="E707" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="F707" t="s">
         <v>861</v>
@@ -22503,7 +23053,7 @@
         <v>105</v>
       </c>
       <c r="E714" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="G714" t="s">
         <v>865</v>
@@ -22524,7 +23074,7 @@
         <v>105</v>
       </c>
       <c r="E715" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="G715" t="s">
         <v>866</v>
@@ -22554,7 +23104,7 @@
         <v>105</v>
       </c>
       <c r="E716" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="G716" t="s">
         <v>867</v>
@@ -22584,7 +23134,7 @@
         <v>105</v>
       </c>
       <c r="E717" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="G717" t="s">
         <v>868</v>
@@ -22614,7 +23164,7 @@
         <v>105</v>
       </c>
       <c r="E718" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="G718" t="s">
         <v>869</v>
@@ -22644,7 +23194,7 @@
         <v>106</v>
       </c>
       <c r="E719" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="F719" t="s">
         <v>111</v>
@@ -22668,7 +23218,7 @@
         <v>106</v>
       </c>
       <c r="E720" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="F720" t="s">
         <v>111</v>
@@ -22734,7 +23284,7 @@
         <v>105</v>
       </c>
       <c r="E725" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="F725" t="s">
         <v>875</v>
@@ -22758,7 +23308,7 @@
         <v>105</v>
       </c>
       <c r="E726" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="F726" t="s">
         <v>875</v>
@@ -22782,7 +23332,7 @@
         <v>105</v>
       </c>
       <c r="E727" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="F727" t="s">
         <v>875</v>
@@ -22806,7 +23356,7 @@
         <v>105</v>
       </c>
       <c r="E728" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="F728" t="s">
         <v>875</v>
@@ -22830,7 +23380,7 @@
         <v>105</v>
       </c>
       <c r="E729" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="F729" t="s">
         <v>875</v>
@@ -22882,7 +23432,7 @@
         <v>105</v>
       </c>
       <c r="E735" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="G735" t="s">
         <v>881</v>
@@ -22903,7 +23453,7 @@
         <v>105</v>
       </c>
       <c r="E736" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="G736" t="s">
         <v>882</v>
@@ -22924,7 +23474,7 @@
         <v>105</v>
       </c>
       <c r="E737" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="G737" t="s">
         <v>883</v>
@@ -22945,7 +23495,7 @@
         <v>105</v>
       </c>
       <c r="E738" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="G738" t="s">
         <v>884</v>
@@ -22966,7 +23516,7 @@
         <v>105</v>
       </c>
       <c r="E739" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="G739" t="s">
         <v>885</v>
@@ -23050,7 +23600,7 @@
         <v>105</v>
       </c>
       <c r="E746" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="G746" t="s">
         <v>886</v>
@@ -23071,7 +23621,7 @@
         <v>105</v>
       </c>
       <c r="E747" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="G747" t="s">
         <v>887</v>
@@ -23101,7 +23651,7 @@
         <v>105</v>
       </c>
       <c r="E748" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="G748" t="s">
         <v>888</v>
@@ -23131,7 +23681,7 @@
         <v>105</v>
       </c>
       <c r="E749" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="G749" t="s">
         <v>889</v>
@@ -23161,7 +23711,7 @@
         <v>105</v>
       </c>
       <c r="E750" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="G750" t="s">
         <v>890</v>
@@ -23191,7 +23741,7 @@
         <v>105</v>
       </c>
       <c r="E751" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="G751" t="s">
         <v>891</v>
@@ -23275,7 +23825,7 @@
         <v>105</v>
       </c>
       <c r="E758" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="G758" t="s">
         <v>892</v>
@@ -23296,7 +23846,7 @@
         <v>105</v>
       </c>
       <c r="E759" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="G759" t="s">
         <v>893</v>
@@ -23326,7 +23876,7 @@
         <v>105</v>
       </c>
       <c r="E760" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="G760" t="s">
         <v>894</v>
@@ -23356,7 +23906,7 @@
         <v>105</v>
       </c>
       <c r="E761" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="G761" t="s">
         <v>895</v>
@@ -23386,7 +23936,7 @@
         <v>105</v>
       </c>
       <c r="E762" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="G762" t="s">
         <v>896</v>
@@ -23416,7 +23966,7 @@
         <v>105</v>
       </c>
       <c r="E763" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="G763" t="s">
         <v>897</v>
@@ -23446,7 +23996,7 @@
         <v>105</v>
       </c>
       <c r="E764" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="G764" t="s">
         <v>898</v>
@@ -23530,7 +24080,7 @@
         <v>105</v>
       </c>
       <c r="E771" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="G771" t="s">
         <v>899</v>
@@ -23551,7 +24101,7 @@
         <v>105</v>
       </c>
       <c r="E772" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="G772" t="s">
         <v>900</v>
@@ -23572,7 +24122,7 @@
         <v>105</v>
       </c>
       <c r="E773" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="G773" t="s">
         <v>901</v>
@@ -23602,7 +24152,7 @@
         <v>105</v>
       </c>
       <c r="E774" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="G774" t="s">
         <v>902</v>
@@ -23632,7 +24182,7 @@
         <v>105</v>
       </c>
       <c r="E775" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="G775" t="s">
         <v>903</v>
@@ -23662,7 +24212,7 @@
         <v>106</v>
       </c>
       <c r="E776" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="F776" t="s">
         <v>111</v>
@@ -23695,7 +24245,7 @@
         <v>106</v>
       </c>
       <c r="E777" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="F777" t="s">
         <v>111</v>
@@ -23767,7 +24317,7 @@
         <v>105</v>
       </c>
       <c r="E783" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="G783" t="s">
         <v>906</v>
@@ -23788,7 +24338,7 @@
         <v>105</v>
       </c>
       <c r="E784" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="G784" t="s">
         <v>907</v>
@@ -23809,7 +24359,7 @@
         <v>105</v>
       </c>
       <c r="E785" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="G785" t="s">
         <v>908</v>
@@ -23839,7 +24389,7 @@
         <v>105</v>
       </c>
       <c r="E786" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="G786" t="s">
         <v>909</v>
@@ -23869,7 +24419,7 @@
         <v>106</v>
       </c>
       <c r="E787" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="F787" t="s">
         <v>111</v>
@@ -23944,7 +24494,7 @@
         <v>105</v>
       </c>
       <c r="E793" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="G793" t="s">
         <v>911</v>
@@ -23965,7 +24515,7 @@
         <v>105</v>
       </c>
       <c r="E794" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="G794" t="s">
         <v>912</v>
@@ -23995,7 +24545,7 @@
         <v>105</v>
       </c>
       <c r="E795" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="G795" t="s">
         <v>913</v>
@@ -24025,7 +24575,7 @@
         <v>105</v>
       </c>
       <c r="E796" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="G796" t="s">
         <v>914</v>
@@ -24055,7 +24605,7 @@
         <v>106</v>
       </c>
       <c r="E797" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="F797" t="s">
         <v>111</v>
@@ -24088,7 +24638,7 @@
         <v>106</v>
       </c>
       <c r="E798" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="F798" t="s">
         <v>111</v>
@@ -24121,7 +24671,7 @@
         <v>106</v>
       </c>
       <c r="E799" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="F799" t="s">
         <v>111</v>
@@ -24154,7 +24704,7 @@
         <v>106</v>
       </c>
       <c r="E800" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="F800" t="s">
         <v>111</v>
@@ -24226,7 +24776,7 @@
         <v>105</v>
       </c>
       <c r="E806" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="L806" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D806:J806)</f>
@@ -24298,7 +24848,7 @@
         <v>105</v>
       </c>
       <c r="E813" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="G813" t="s">
         <v>919</v>
@@ -24319,7 +24869,7 @@
         <v>105</v>
       </c>
       <c r="E814" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="G814" t="s">
         <v>920</v>
@@ -24349,7 +24899,7 @@
         <v>105</v>
       </c>
       <c r="E815" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="G815" t="s">
         <v>921</v>
@@ -24379,7 +24929,7 @@
         <v>105</v>
       </c>
       <c r="E816" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="G816" t="s">
         <v>922</v>
@@ -24409,7 +24959,7 @@
         <v>105</v>
       </c>
       <c r="E817" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="G817" t="s">
         <v>923</v>
@@ -24439,7 +24989,7 @@
         <v>105</v>
       </c>
       <c r="E818" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="G818" t="s">
         <v>924</v>
@@ -24523,7 +25073,7 @@
         <v>105</v>
       </c>
       <c r="E825" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="G825" t="s">
         <v>925</v>
@@ -24553,7 +25103,7 @@
         <v>105</v>
       </c>
       <c r="E826" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="G826" t="s">
         <v>926</v>
@@ -24583,7 +25133,7 @@
         <v>105</v>
       </c>
       <c r="E827" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="G827" t="s">
         <v>927</v>
@@ -24613,7 +25163,7 @@
         <v>105</v>
       </c>
       <c r="E828" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="G828" t="s">
         <v>928</v>
@@ -24643,7 +25193,7 @@
         <v>105</v>
       </c>
       <c r="E829" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="G829" t="s">
         <v>929</v>
@@ -24673,7 +25223,7 @@
         <v>105</v>
       </c>
       <c r="E830" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="G830" t="s">
         <v>930</v>
@@ -24703,7 +25253,7 @@
         <v>105</v>
       </c>
       <c r="E831" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="G831" t="s">
         <v>931</v>
@@ -24733,7 +25283,7 @@
         <v>105</v>
       </c>
       <c r="E832" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="G832" t="s">
         <v>932</v>
@@ -24763,7 +25313,7 @@
         <v>105</v>
       </c>
       <c r="E833" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="G833" t="s">
         <v>933</v>
@@ -24793,7 +25343,7 @@
         <v>105</v>
       </c>
       <c r="E834" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="G834" t="s">
         <v>936</v>
@@ -24823,7 +25373,7 @@
         <v>105</v>
       </c>
       <c r="E835" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="G835" t="s">
         <v>937</v>
@@ -24853,7 +25403,7 @@
         <v>105</v>
       </c>
       <c r="E836" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="G836" t="s">
         <v>938</v>
@@ -24883,7 +25433,7 @@
         <v>106</v>
       </c>
       <c r="E837" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="F837" t="s">
         <v>111</v>
@@ -24907,7 +25457,7 @@
         <v>106</v>
       </c>
       <c r="E838" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="F838" t="s">
         <v>111</v>
@@ -24970,7 +25520,7 @@
         <v>105</v>
       </c>
       <c r="E844" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="G844" t="s">
         <v>939</v>
@@ -24991,7 +25541,7 @@
         <v>105</v>
       </c>
       <c r="E845" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="G845" t="s">
         <v>940</v>
@@ -25021,7 +25571,7 @@
         <v>105</v>
       </c>
       <c r="E846" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="G846" t="s">
         <v>941</v>
@@ -25105,7 +25655,7 @@
         <v>105</v>
       </c>
       <c r="E853" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="G853" t="s">
         <v>942</v>
@@ -25126,7 +25676,7 @@
         <v>105</v>
       </c>
       <c r="E854" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="G854" t="s">
         <v>943</v>
@@ -25147,7 +25697,7 @@
         <v>105</v>
       </c>
       <c r="E855" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="G855" t="s">
         <v>944</v>
@@ -25177,7 +25727,7 @@
         <v>105</v>
       </c>
       <c r="E856" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="G856" t="s">
         <v>945</v>
@@ -25207,7 +25757,7 @@
         <v>106</v>
       </c>
       <c r="E857" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="F857" t="s">
         <v>111</v>
@@ -25231,7 +25781,7 @@
         <v>106</v>
       </c>
       <c r="E858" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="F858" t="s">
         <v>111</v>
@@ -25255,7 +25805,7 @@
         <v>106</v>
       </c>
       <c r="E859" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="F859" t="s">
         <v>111</v>
@@ -25330,7 +25880,7 @@
         <v>105</v>
       </c>
       <c r="E864" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="F864" t="s">
         <v>950</v>
@@ -25394,7 +25944,7 @@
         <v>105</v>
       </c>
       <c r="E872" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="G872" t="s">
         <v>952</v>
@@ -25415,7 +25965,7 @@
         <v>105</v>
       </c>
       <c r="E873" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="G873" t="s">
         <v>953</v>
@@ -25436,7 +25986,7 @@
         <v>105</v>
       </c>
       <c r="E874" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="G874" t="s">
         <v>954</v>
@@ -25457,7 +26007,7 @@
         <v>105</v>
       </c>
       <c r="E875" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="G875" t="s">
         <v>955</v>
@@ -25478,7 +26028,7 @@
         <v>105</v>
       </c>
       <c r="E876" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="G876" t="s">
         <v>956</v>
@@ -25508,7 +26058,7 @@
         <v>105</v>
       </c>
       <c r="E877" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="G877" t="s">
         <v>957</v>
@@ -25538,7 +26088,7 @@
         <v>105</v>
       </c>
       <c r="E878" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="G878" t="s">
         <v>958</v>
@@ -25568,7 +26118,7 @@
         <v>106</v>
       </c>
       <c r="E879" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="F879" t="s">
         <v>111</v>
@@ -25592,7 +26142,7 @@
         <v>106</v>
       </c>
       <c r="E880" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="F880" t="s">
         <v>111</v>
@@ -25655,7 +26205,7 @@
         <v>105</v>
       </c>
       <c r="E886" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="G886" t="s">
         <v>961</v>
@@ -25676,7 +26226,7 @@
         <v>105</v>
       </c>
       <c r="E887" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="G887" t="s">
         <v>962</v>
@@ -25697,7 +26247,7 @@
         <v>105</v>
       </c>
       <c r="E888" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="G888" t="s">
         <v>963</v>
@@ -25727,7 +26277,7 @@
         <v>105</v>
       </c>
       <c r="E889" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="G889" t="s">
         <v>964</v>
@@ -25814,7 +26364,7 @@
         <v>105</v>
       </c>
       <c r="E895" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F895" t="s">
         <v>965</v>
@@ -25869,7 +26419,7 @@
         <v>105</v>
       </c>
       <c r="E899" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F899" t="s">
         <v>965</v>
@@ -25924,7 +26474,7 @@
         <v>105</v>
       </c>
       <c r="E903" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F903" t="s">
         <v>965</v>
@@ -25988,7 +26538,7 @@
         <v>105</v>
       </c>
       <c r="E907" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F907" t="s">
         <v>965</v>
@@ -26043,7 +26593,7 @@
         <v>105</v>
       </c>
       <c r="E911" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F911" t="s">
         <v>965</v>
@@ -26098,7 +26648,7 @@
         <v>105</v>
       </c>
       <c r="E915" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F915" t="s">
         <v>965</v>
@@ -26153,7 +26703,7 @@
         <v>105</v>
       </c>
       <c r="E919" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="G919" t="s">
         <v>985</v>
@@ -26174,7 +26724,7 @@
         <v>105</v>
       </c>
       <c r="E920" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="G920" t="s">
         <v>986</v>
@@ -26195,7 +26745,7 @@
         <v>105</v>
       </c>
       <c r="E921" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="G921" t="s">
         <v>987</v>
@@ -26270,7 +26820,7 @@
         <v>105</v>
       </c>
       <c r="E928" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="G928" t="s">
         <v>988</v>
@@ -26291,7 +26841,7 @@
         <v>105</v>
       </c>
       <c r="E929" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="G929" t="s">
         <v>989</v>
@@ -26321,7 +26871,7 @@
         <v>106</v>
       </c>
       <c r="E930" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="F930" t="s">
         <v>111</v>
@@ -26345,7 +26895,7 @@
         <v>106</v>
       </c>
       <c r="E931" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="F931" t="s">
         <v>111</v>
@@ -26408,7 +26958,7 @@
         <v>105</v>
       </c>
       <c r="E937" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="G937" t="s">
         <v>992</v>
@@ -26429,7 +26979,7 @@
         <v>105</v>
       </c>
       <c r="E938" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="G938" t="s">
         <v>993</v>
@@ -26450,7 +27000,7 @@
         <v>105</v>
       </c>
       <c r="E939" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="G939" t="s">
         <v>994</v>
@@ -26471,7 +27021,7 @@
         <v>105</v>
       </c>
       <c r="E940" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="G940" t="s">
         <v>995</v>
@@ -26492,7 +27042,7 @@
         <v>105</v>
       </c>
       <c r="E941" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="G941" t="s">
         <v>996</v>
@@ -26522,7 +27072,7 @@
         <v>105</v>
       </c>
       <c r="E942" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="G942" t="s">
         <v>997</v>
@@ -26552,7 +27102,7 @@
         <v>106</v>
       </c>
       <c r="E943" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="F943" t="s">
         <v>111</v>
@@ -26576,7 +27126,7 @@
         <v>106</v>
       </c>
       <c r="E944" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="F944" t="s">
         <v>111</v>
@@ -26639,7 +27189,7 @@
         <v>105</v>
       </c>
       <c r="E950" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="G950" t="s">
         <v>1000</v>
@@ -26660,7 +27210,7 @@
         <v>105</v>
       </c>
       <c r="E951" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="G951" t="s">
         <v>1001</v>
@@ -26681,7 +27231,7 @@
         <v>105</v>
       </c>
       <c r="E952" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="G952" t="s">
         <v>1002</v>
@@ -26765,7 +27315,7 @@
         <v>105</v>
       </c>
       <c r="E959" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="G959" t="s">
         <v>1003</v>
@@ -26786,7 +27336,7 @@
         <v>105</v>
       </c>
       <c r="E960" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="G960" t="s">
         <v>1004</v>
@@ -26807,7 +27357,7 @@
         <v>105</v>
       </c>
       <c r="E961" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="G961" t="s">
         <v>1005</v>
@@ -26828,7 +27378,7 @@
         <v>105</v>
       </c>
       <c r="E962" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="G962" t="s">
         <v>1006</v>
@@ -26858,7 +27408,7 @@
         <v>106</v>
       </c>
       <c r="E963" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="F963" t="s">
         <v>111</v>
@@ -26921,7 +27471,7 @@
         <v>105</v>
       </c>
       <c r="E969" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="G969" t="s">
         <v>1008</v>
@@ -26942,7 +27492,7 @@
         <v>105</v>
       </c>
       <c r="E970" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="G970" t="s">
         <v>1009</v>
@@ -26963,7 +27513,7 @@
         <v>105</v>
       </c>
       <c r="E971" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="G971" t="s">
         <v>1010</v>
@@ -26984,7 +27534,7 @@
         <v>105</v>
       </c>
       <c r="E972" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="G972" t="s">
         <v>1011</v>
@@ -27014,7 +27564,7 @@
         <v>105</v>
       </c>
       <c r="E973" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="G973" t="s">
         <v>1012</v>
@@ -27044,7 +27594,7 @@
         <v>105</v>
       </c>
       <c r="E974" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="G974" t="s">
         <v>1013</v>
@@ -27074,7 +27624,7 @@
         <v>105</v>
       </c>
       <c r="E975" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="G975" t="s">
         <v>1014</v>
@@ -27104,7 +27654,7 @@
         <v>106</v>
       </c>
       <c r="E976" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="F976" t="s">
         <v>111</v>
@@ -27128,7 +27678,7 @@
         <v>106</v>
       </c>
       <c r="E977" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="F977" t="s">
         <v>111</v>
@@ -27191,7 +27741,7 @@
         <v>105</v>
       </c>
       <c r="E983" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="G983" t="s">
         <v>1017</v>
@@ -27212,7 +27762,7 @@
         <v>105</v>
       </c>
       <c r="E984" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="G984" t="s">
         <v>1018</v>
@@ -27242,7 +27792,7 @@
         <v>105</v>
       </c>
       <c r="E985" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="G985" t="s">
         <v>1019</v>
@@ -27272,7 +27822,7 @@
         <v>105</v>
       </c>
       <c r="E986" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="G986" t="s">
         <v>1020</v>
@@ -27302,7 +27852,7 @@
         <v>105</v>
       </c>
       <c r="E987" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="G987" t="s">
         <v>1021</v>
@@ -27332,7 +27882,7 @@
         <v>105</v>
       </c>
       <c r="E988" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="G988" t="s">
         <v>1022</v>
@@ -27416,7 +27966,7 @@
         <v>105</v>
       </c>
       <c r="E995" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="G995" t="s">
         <v>1023</v>
@@ -27437,7 +27987,7 @@
         <v>106</v>
       </c>
       <c r="E996" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="F996" t="s">
         <v>111</v>
@@ -27500,7 +28050,7 @@
         <v>105</v>
       </c>
       <c r="E1002" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="G1002" t="s">
         <v>1041</v>
@@ -27521,7 +28071,7 @@
         <v>105</v>
       </c>
       <c r="E1003" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="G1003" t="s">
         <v>1042</v>
@@ -27551,7 +28101,7 @@
         <v>105</v>
       </c>
       <c r="E1004" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="G1004" t="s">
         <v>1043</v>
@@ -27581,7 +28131,7 @@
         <v>105</v>
       </c>
       <c r="E1005" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="G1005" t="s">
         <v>1044</v>
@@ -27611,7 +28161,7 @@
         <v>105</v>
       </c>
       <c r="E1006" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="G1006" t="s">
         <v>1045</v>
@@ -27641,7 +28191,7 @@
         <v>105</v>
       </c>
       <c r="E1007" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="G1007" t="s">
         <v>1046</v>
@@ -27671,7 +28221,7 @@
         <v>105</v>
       </c>
       <c r="E1008" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="G1008" t="s">
         <v>1047</v>
@@ -27701,7 +28251,7 @@
         <v>105</v>
       </c>
       <c r="E1009" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="G1009" t="s">
         <v>1048</v>
@@ -27731,7 +28281,7 @@
         <v>105</v>
       </c>
       <c r="E1010" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="G1010" t="s">
         <v>1049</v>
@@ -27761,7 +28311,7 @@
         <v>105</v>
       </c>
       <c r="E1011" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="G1011" t="s">
         <v>1050</v>
@@ -27791,7 +28341,7 @@
         <v>105</v>
       </c>
       <c r="E1012" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="G1012" t="s">
         <v>1051</v>
@@ -27821,7 +28371,7 @@
         <v>105</v>
       </c>
       <c r="E1013" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="G1013" t="s">
         <v>1040</v>
@@ -27851,7 +28401,7 @@
         <v>106</v>
       </c>
       <c r="E1014" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="F1014" t="s">
         <v>111</v>
@@ -27875,7 +28425,7 @@
         <v>106</v>
       </c>
       <c r="E1015" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="F1015" t="s">
         <v>111</v>
@@ -27899,7 +28449,7 @@
         <v>106</v>
       </c>
       <c r="E1016" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="F1016" t="s">
         <v>111</v>
@@ -27971,7 +28521,7 @@
         <v>105</v>
       </c>
       <c r="E1022" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="G1022" t="s">
         <v>1055</v>
@@ -27992,7 +28542,7 @@
         <v>105</v>
       </c>
       <c r="E1023" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="G1023" t="s">
         <v>1056</v>
@@ -28022,7 +28572,7 @@
         <v>105</v>
       </c>
       <c r="E1024" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="G1024" t="s">
         <v>1057</v>
@@ -28052,7 +28602,7 @@
         <v>105</v>
       </c>
       <c r="E1025" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="G1025" t="s">
         <v>1058</v>
@@ -28082,7 +28632,7 @@
         <v>105</v>
       </c>
       <c r="E1026" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="G1026" t="s">
         <v>1059</v>
@@ -28166,7 +28716,7 @@
         <v>105</v>
       </c>
       <c r="E1033" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="G1033" t="s">
         <v>1061</v>
@@ -28187,7 +28737,7 @@
         <v>105</v>
       </c>
       <c r="E1034" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="G1034" t="s">
         <v>1062</v>
@@ -28208,7 +28758,7 @@
         <v>105</v>
       </c>
       <c r="E1035" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="G1035" t="s">
         <v>1063</v>
@@ -28229,7 +28779,7 @@
         <v>105</v>
       </c>
       <c r="E1036" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="G1036" t="s">
         <v>1064</v>
@@ -28259,7 +28809,7 @@
         <v>105</v>
       </c>
       <c r="E1037" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="G1037" t="s">
         <v>1065</v>
@@ -28289,7 +28839,7 @@
         <v>105</v>
       </c>
       <c r="E1038" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="G1038" t="s">
         <v>1066</v>
@@ -28319,7 +28869,7 @@
         <v>105</v>
       </c>
       <c r="E1039" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="G1039" t="s">
         <v>1067</v>
@@ -28349,7 +28899,7 @@
         <v>105</v>
       </c>
       <c r="E1040" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="G1040" t="s">
         <v>1068</v>
@@ -28379,7 +28929,7 @@
         <v>105</v>
       </c>
       <c r="E1041" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="G1041" t="s">
         <v>1060</v>
@@ -28409,7 +28959,7 @@
         <v>106</v>
       </c>
       <c r="E1042" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="F1042" t="s">
         <v>111</v>
@@ -28442,7 +28992,7 @@
         <v>106</v>
       </c>
       <c r="E1043" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="F1043" t="s">
         <v>111</v>
@@ -28514,7 +29064,7 @@
         <v>105</v>
       </c>
       <c r="E1049" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="G1049" t="s">
         <v>1071</v>
@@ -28544,7 +29094,7 @@
         <v>105</v>
       </c>
       <c r="E1050" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="G1050" t="s">
         <v>1072</v>
@@ -28574,7 +29124,7 @@
         <v>105</v>
       </c>
       <c r="E1051" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="G1051" t="s">
         <v>1073</v>
@@ -28604,7 +29154,7 @@
         <v>105</v>
       </c>
       <c r="E1052" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="G1052" t="s">
         <v>1074</v>
@@ -28634,7 +29184,7 @@
         <v>105</v>
       </c>
       <c r="E1053" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="G1053" t="s">
         <v>1075</v>
@@ -28718,7 +29268,7 @@
         <v>105</v>
       </c>
       <c r="E1060" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="G1060" t="s">
         <v>1076</v>
@@ -28748,7 +29298,7 @@
         <v>105</v>
       </c>
       <c r="E1061" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="G1061" t="s">
         <v>1077</v>
@@ -28778,7 +29328,7 @@
         <v>105</v>
       </c>
       <c r="E1062" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="G1062" t="s">
         <v>1078</v>
@@ -28808,7 +29358,7 @@
         <v>105</v>
       </c>
       <c r="E1063" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="G1063" t="s">
         <v>1079</v>
@@ -28838,7 +29388,7 @@
         <v>105</v>
       </c>
       <c r="E1064" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="G1064" t="s">
         <v>1080</v>
@@ -28868,7 +29418,7 @@
         <v>105</v>
       </c>
       <c r="E1065" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="G1065" t="s">
         <v>1081</v>
@@ -28898,7 +29448,7 @@
         <v>105</v>
       </c>
       <c r="E1066" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="G1066" t="s">
         <v>1082</v>
@@ -28928,7 +29478,7 @@
         <v>105</v>
       </c>
       <c r="E1067" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="G1067" t="s">
         <v>1083</v>
@@ -28958,7 +29508,7 @@
         <v>105</v>
       </c>
       <c r="E1068" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="G1068" t="s">
         <v>1084</v>
@@ -28988,7 +29538,7 @@
         <v>105</v>
       </c>
       <c r="E1069" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="G1069" t="s">
         <v>1085</v>
@@ -29018,7 +29568,7 @@
         <v>106</v>
       </c>
       <c r="E1070" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="F1070" t="s">
         <v>111</v>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DC3380-A992-124B-82C5-3098548C4EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D33B314-41E0-BC4B-A3AD-B9FAFA5F237B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="500" windowWidth="21640" windowHeight="19440" activeTab="3" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="2640" yWindow="500" windowWidth="21640" windowHeight="19440" activeTab="3" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5600" uniqueCount="1283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5889" uniqueCount="1366">
   <si>
     <t>page_id</t>
   </si>
@@ -3891,6 +3891,255 @@
   </si>
   <si>
     <t>bei Müttern im AR: *sꜣ⸗s*</t>
+  </si>
+  <si>
+    <t>seltenHierogl</t>
+  </si>
+  <si>
+    <t>Seltene Hieroglphen</t>
+  </si>
+  <si>
+    <t>pages/seltenHierogl</t>
+  </si>
+  <si>
+    <t>Hieroglyphe</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardF</t>
+  </si>
+  <si>
+    <t>A – Der Mann und seine Tätigkeiten</t>
+  </si>
+  <si>
+    <t>B – Die Frau und ihre Tätigkeiten</t>
+  </si>
+  <si>
+    <t>C – Gottheiten in Menschengestalt</t>
+  </si>
+  <si>
+    <t>D – Teile des menschlichen Körpers</t>
+  </si>
+  <si>
+    <t>E – Säugetiere</t>
+  </si>
+  <si>
+    <t>F – Teile von Säugetieren</t>
+  </si>
+  <si>
+    <t>G – Vögel</t>
+  </si>
+  <si>
+    <t>H – Teile von Vögeln</t>
+  </si>
+  <si>
+    <t>I – Amphibien und Reptilien</t>
+  </si>
+  <si>
+    <t>K – Fische und Teile von Fischen</t>
+  </si>
+  <si>
+    <t>L – Wirbellose und andere Tiere</t>
+  </si>
+  <si>
+    <t>M – Bäume und andere Pflanzen</t>
+  </si>
+  <si>
+    <t>N – Himmel, Erde und Wasser</t>
+  </si>
+  <si>
+    <t>O – Gebäude und Teile von Gebäuden</t>
+  </si>
+  <si>
+    <t>P – Schiffe und Teile von Schiffen</t>
+  </si>
+  <si>
+    <t>Q – Möbel</t>
+  </si>
+  <si>
+    <t>R – Tempel</t>
+  </si>
+  <si>
+    <t>S – Kronen</t>
+  </si>
+  <si>
+    <t>T – Krieg, Jagd und Schlachterei</t>
+  </si>
+  <si>
+    <t>U – Landwirtschaft und Handwerk</t>
+  </si>
+  <si>
+    <t>V – Seil, Faser, Korb usw.</t>
+  </si>
+  <si>
+    <t>W – Stein- und Tongefäße</t>
+  </si>
+  <si>
+    <t>X – Laibe und Kuchen</t>
+  </si>
+  <si>
+    <t>Y – Schreiben, Spiele und Musik</t>
+  </si>
+  <si>
+    <t>Z – Geometrische Figuren</t>
+  </si>
+  <si>
+    <t>Aa – unklassifizierte Hieroglyphen</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardA</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardB</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardC</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardD</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardE</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardG</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardH</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardI</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardK</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardL</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardM</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardN</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardO</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardP</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardQ</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardR</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardS</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardT</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardU</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardV</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardW</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardX</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardY</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardZ</t>
+  </si>
+  <si>
+    <t>tb_seltenHierogl_GardAa</t>
+  </si>
+  <si>
+    <t>F63_xnty_01</t>
+  </si>
+  <si>
+    <t>03_Hieroglyphen-selten/</t>
+  </si>
+  <si>
+    <t>*ḫnty*</t>
+  </si>
+  <si>
+    <t>vorn befindlich</t>
+  </si>
+  <si>
+    <t>Gardiner-Nr.</t>
+  </si>
+  <si>
+    <t>F63</t>
+  </si>
+  <si>
+    <t>N6B</t>
+  </si>
+  <si>
+    <t>N6B_nsw-bjt_01</t>
+  </si>
+  <si>
+    <t>König von Ober- und Unterägypten</t>
+  </si>
+  <si>
+    <t>N102_jmn_01</t>
+  </si>
+  <si>
+    <t>N102</t>
+  </si>
+  <si>
+    <t>projekt</t>
+  </si>
+  <si>
+    <t>Projekt</t>
+  </si>
+  <si>
+    <t>pages/projekt</t>
+  </si>
+  <si>
+    <t>Version:</t>
+  </si>
+  <si>
+    <t>RStudio 2025.09.1+401 "Cucumberleaf Sunflower" Release (20de356561bd58a6d88927cce948bd076d06e4ca, 2025-09-23) for macOS</t>
+  </si>
+  <si>
+    <t>Mozilla/5.0 (Macintosh; Intel Mac OS X 10_15_7)</t>
+  </si>
+  <si>
+    <t>AppleWebKit/537.36 (KHTML, like Gecko)</t>
+  </si>
+  <si>
+    <t>RStudio/2025.09.1+401</t>
+  </si>
+  <si>
+    <t>Chrome/138.0.7204.185</t>
+  </si>
+  <si>
+    <t>Github:</t>
+  </si>
+  <si>
+    <t>&lt;https://github.com/MarkusKut/Inschriftenschluessel.git&gt;</t>
+  </si>
+  <si>
+    <t>Mitarbeiter:</t>
+  </si>
+  <si>
+    <t>- **Projektleitung:** Prof. Friedhelm Hoffmann</t>
+  </si>
+  <si>
+    <t>- **Recherche, Datengrundlage:** Iulia Comșa</t>
+  </si>
+  <si>
+    <t>- **Programmierung, Hieroglyphensetzung:** Markus Kutschka</t>
+  </si>
+  <si>
+    <t>Diese Website wurde mit Quarto unter R erstellt:</t>
   </si>
 </sst>
 </file>
@@ -3900,7 +4149,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3921,6 +4170,14 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -3989,10 +4246,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4061,8 +4319,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4395,7 +4658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E50E2D7D-6A15-A747-8ABA-0F1F90941768}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
@@ -4679,6 +4942,40 @@
       </c>
       <c r="F16">
         <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1285</v>
+      </c>
+      <c r="F17">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F18">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -5313,13 +5610,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEDD5969-C8E3-C04D-AF17-FDEFB8218719}">
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.1640625" style="4" customWidth="1"/>
     <col min="3" max="3" width="7.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.1640625" style="4" customWidth="1"/>
     <col min="5" max="5" width="36.1640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="21.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.1640625" style="4" bestFit="1" customWidth="1"/>
@@ -6309,7 +6606,912 @@
         <v>4</v>
       </c>
     </row>
+    <row r="59" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K59" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K60" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K61" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>1291</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>1317</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K62" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>1292</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K63" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>1287</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K64" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K65" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>1320</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K66" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K67" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K68" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>1323</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K69" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>1299</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K70" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A71" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K71" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A72" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K72" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A73" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>1302</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K73" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A74" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K74" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A75" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>1329</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K75" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>1305</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K76" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K77" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A78" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>1332</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K78" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A79" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K79" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A80" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>1334</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K80" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A81" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K81" s="4">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A82" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K82" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A83" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K83" s="4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A84" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>1313</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K84" s="4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>1361</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K88" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E89" s="37" t="s">
+        <v>1362</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K89" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E90" s="37" t="s">
+        <v>1363</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K90" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E91" s="37" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K91" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K92" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K93" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K94" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K95" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K96" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K97" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E98" s="36" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K98" s="4">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E98" r:id="rId1" xr:uid="{0ACED111-27C4-D24A-8D2D-292F7EF8BCCB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10311,15 +11513,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62D4F70-2351-5545-A291-11D662F747FD}">
-  <dimension ref="A1:L1072"/>
+  <dimension ref="A1:L1093"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.6640625" style="27" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="54.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" customWidth="1"/>
     <col min="7" max="7" width="32.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
@@ -29615,6 +30817,204 @@
         <v>108</v>
       </c>
     </row>
+    <row r="1078" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1078" s="4" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B1078" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1078" t="s">
+        <v>1343</v>
+      </c>
+      <c r="L1078" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1079" s="4" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B1079" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1079" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E1079" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G1079" t="s">
+        <v>1339</v>
+      </c>
+      <c r="H1079" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1079" t="str">
+        <f t="shared" ref="L1079" si="140">_xlfn.TEXTJOIN("", TRUE, D1079:K1079)</f>
+        <v>03_Hieroglyphen-selten/F63_xnty_01.png</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1080" s="4" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B1080" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1080" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1080" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1081" s="4" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B1081" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1081" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1081" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1086" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B1086" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1086" t="s">
+        <v>1343</v>
+      </c>
+      <c r="L1086" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1087" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B1087" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1087" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E1087" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G1087" t="s">
+        <v>1346</v>
+      </c>
+      <c r="H1087" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1087" t="str">
+        <f t="shared" ref="L1087" si="141">_xlfn.TEXTJOIN("", TRUE, D1087:K1087)</f>
+        <v>03_Hieroglyphen-selten/N6B_nsw-bjt_01.png</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1088" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B1088" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1088" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1088" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1089" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B1089" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1089" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1089" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1090" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B1090" s="27">
+        <v>2</v>
+      </c>
+      <c r="C1090" t="s">
+        <v>1343</v>
+      </c>
+      <c r="L1090" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1091" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B1091" s="27">
+        <v>2</v>
+      </c>
+      <c r="C1091" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E1091" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G1091" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H1091" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1091" t="str">
+        <f t="shared" ref="L1091" si="142">_xlfn.TEXTJOIN("", TRUE, D1091:K1091)</f>
+        <v>03_Hieroglyphen-selten/N102_jmn_01.png</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1092" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B1092" s="27">
+        <v>2</v>
+      </c>
+      <c r="C1092" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1092" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1093" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B1093" s="27">
+        <v>2</v>
+      </c>
+      <c r="C1093" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1093" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D33B314-41E0-BC4B-A3AD-B9FAFA5F237B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130B32DD-00A9-154D-B757-5DC8FD20783D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2640" yWindow="500" windowWidth="21640" windowHeight="19440" activeTab="3" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
@@ -4130,9 +4130,6 @@
     <t>Mitarbeiter:</t>
   </si>
   <si>
-    <t>- **Projektleitung:** Prof. Friedhelm Hoffmann</t>
-  </si>
-  <si>
     <t>- **Recherche, Datengrundlage:** Iulia Comșa</t>
   </si>
   <si>
@@ -4140,6 +4137,9 @@
   </si>
   <si>
     <t>Diese Website wurde mit Quarto unter R erstellt:</t>
+  </si>
+  <si>
+    <t>- **Projektleitung:** Prof. Dr. Friedhelm Hoffmann</t>
   </si>
 </sst>
 </file>
@@ -4250,7 +4250,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4315,10 +4315,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7312,8 +7308,8 @@
       <c r="C89" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E89" s="37" t="s">
-        <v>1362</v>
+      <c r="E89" s="33" t="s">
+        <v>1365</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>54</v>
@@ -7332,8 +7328,8 @@
       <c r="C90" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E90" s="37" t="s">
-        <v>1363</v>
+      <c r="E90" s="33" t="s">
+        <v>1362</v>
       </c>
       <c r="G90" s="4" t="s">
         <v>54</v>
@@ -7352,8 +7348,8 @@
       <c r="C91" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E91" s="37" t="s">
-        <v>1364</v>
+      <c r="E91" s="33" t="s">
+        <v>1363</v>
       </c>
       <c r="G91" s="4" t="s">
         <v>54</v>
@@ -7376,7 +7372,7 @@
         <v>1353</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>54</v>
@@ -7498,7 +7494,7 @@
       <c r="D98" s="4" t="s">
         <v>1359</v>
       </c>
-      <c r="E98" s="36" t="s">
+      <c r="E98" s="32" t="s">
         <v>1360</v>
       </c>
       <c r="G98" s="4" t="s">
@@ -12422,7 +12418,7 @@
         <v>113</v>
       </c>
       <c r="L57" t="str">
-        <f t="shared" ref="L55:L58" si="8">_xlfn.TEXTJOIN("", TRUE, D57:J57)</f>
+        <f t="shared" ref="L57:L58" si="8">_xlfn.TEXTJOIN("", TRUE, D57:J57)</f>
         <v>02_Slots/Gaben/0030_Gefluegel/0020_Apd_Abk_02.png</v>
       </c>
     </row>
@@ -17821,16 +17817,15 @@
       </c>
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A361" s="32" t="s">
+      <c r="A361" t="s">
         <v>1030</v>
       </c>
-      <c r="B361" s="35">
+      <c r="B361" s="27">
         <v>2</v>
       </c>
-      <c r="C361" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D361" s="32"/>
+      <c r="C361" t="s">
+        <v>105</v>
+      </c>
       <c r="E361" t="s">
         <v>1223</v>
       </c>
@@ -17855,76 +17850,43 @@
       </c>
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A362" s="32" t="s">
+      <c r="A362" t="s">
         <v>1030</v>
       </c>
-      <c r="B362" s="35">
+      <c r="B362" s="27">
         <v>2</v>
       </c>
-      <c r="C362" s="32" t="s">
+      <c r="C362" t="s">
         <v>27</v>
       </c>
-      <c r="D362" s="32"/>
       <c r="L362" t="s">
         <v>1093</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A363" s="32"/>
-      <c r="B363" s="35"/>
-      <c r="C363" s="32"/>
-      <c r="D363" s="32"/>
-    </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A364" s="32"/>
-      <c r="B364" s="35"/>
-      <c r="C364" s="32"/>
-      <c r="D364" s="32"/>
-    </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A365" s="32"/>
-      <c r="B365" s="35"/>
-      <c r="C365" s="32"/>
-      <c r="D365" s="32"/>
-    </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A366" s="32"/>
-      <c r="B366" s="35"/>
-      <c r="C366" s="32"/>
-      <c r="D366" s="32"/>
-    </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A367" s="32"/>
-      <c r="B367" s="35"/>
-      <c r="C367" s="32"/>
-      <c r="D367" s="32"/>
-    </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A368" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B368" s="33">
+      <c r="A368" t="s">
+        <v>60</v>
+      </c>
+      <c r="B368" s="28">
         <v>20</v>
       </c>
-      <c r="C368" s="32" t="s">
+      <c r="C368" t="s">
         <v>39</v>
       </c>
-      <c r="D368" s="32"/>
       <c r="L368" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A369" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B369" s="33">
+      <c r="A369" t="s">
+        <v>60</v>
+      </c>
+      <c r="B369" s="28">
         <v>20</v>
       </c>
-      <c r="C369" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D369" s="32"/>
+      <c r="C369" t="s">
+        <v>105</v>
+      </c>
       <c r="E369" t="s">
         <v>1224</v>
       </c>
@@ -17940,16 +17902,15 @@
       </c>
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A370" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B370" s="33">
+      <c r="A370" t="s">
+        <v>60</v>
+      </c>
+      <c r="B370" s="28">
         <v>20</v>
       </c>
-      <c r="C370" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D370" s="32"/>
+      <c r="C370" t="s">
+        <v>105</v>
+      </c>
       <c r="E370" t="s">
         <v>1224</v>
       </c>
@@ -17974,16 +17935,15 @@
       </c>
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A371" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B371" s="33">
+      <c r="A371" t="s">
+        <v>60</v>
+      </c>
+      <c r="B371" s="28">
         <v>20</v>
       </c>
-      <c r="C371" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D371" s="32"/>
+      <c r="C371" t="s">
+        <v>105</v>
+      </c>
       <c r="E371" t="s">
         <v>1224</v>
       </c>
@@ -18008,16 +17968,15 @@
       </c>
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A372" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B372" s="33">
+      <c r="A372" t="s">
+        <v>60</v>
+      </c>
+      <c r="B372" s="28">
         <v>20</v>
       </c>
-      <c r="C372" s="32" t="s">
+      <c r="C372" t="s">
         <v>106</v>
       </c>
-      <c r="D372" s="32"/>
       <c r="E372" t="s">
         <v>1224</v>
       </c>
@@ -18036,67 +17995,57 @@
       </c>
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A373" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B373" s="33">
+      <c r="A373" t="s">
+        <v>60</v>
+      </c>
+      <c r="B373" s="28">
         <v>20</v>
       </c>
-      <c r="C373" s="32" t="s">
+      <c r="C373" t="s">
         <v>107</v>
       </c>
-      <c r="D373" s="32"/>
       <c r="L373" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A374" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B374" s="33">
+      <c r="A374" t="s">
+        <v>60</v>
+      </c>
+      <c r="B374" s="28">
         <v>20</v>
       </c>
-      <c r="C374" s="32" t="s">
+      <c r="C374" t="s">
         <v>108</v>
       </c>
-      <c r="D374" s="32"/>
       <c r="L374" t="s">
         <v>1170</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A375" s="32"/>
-      <c r="B375" s="35"/>
-      <c r="C375" s="32"/>
-      <c r="D375" s="32"/>
-    </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A376" s="32" t="s">
+      <c r="A376" t="s">
         <v>610</v>
       </c>
-      <c r="B376" s="35">
+      <c r="B376" s="27">
         <v>1</v>
       </c>
-      <c r="C376" s="32" t="s">
+      <c r="C376" t="s">
         <v>39</v>
       </c>
-      <c r="D376" s="32"/>
       <c r="L376" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A377" s="32" t="s">
+      <c r="A377" t="s">
         <v>610</v>
       </c>
-      <c r="B377" s="35">
+      <c r="B377" s="27">
         <v>1</v>
       </c>
-      <c r="C377" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D377" s="32"/>
+      <c r="C377" t="s">
+        <v>105</v>
+      </c>
       <c r="E377" t="s">
         <v>110</v>
       </c>
@@ -18115,38 +18064,29 @@
       </c>
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A378" s="32" t="s">
+      <c r="A378" t="s">
         <v>610</v>
       </c>
-      <c r="B378" s="35">
+      <c r="B378" s="27">
         <v>1</v>
       </c>
-      <c r="C378" s="32" t="s">
+      <c r="C378" t="s">
         <v>27</v>
       </c>
-      <c r="D378" s="32"/>
       <c r="L378" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A379" s="32"/>
-      <c r="B379" s="35"/>
-      <c r="C379" s="32"/>
-      <c r="D379" s="32"/>
-    </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A380" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B380" s="34">
+      <c r="A380" t="s">
+        <v>60</v>
+      </c>
+      <c r="B380" s="28">
         <v>30</v>
       </c>
-      <c r="C380" s="32" t="s">
+      <c r="C380" t="s">
         <v>39</v>
       </c>
-      <c r="D380" s="32"/>
-      <c r="E380" s="32"/>
       <c r="G380" t="s">
         <v>127</v>
       </c>
@@ -18155,17 +18095,16 @@
       </c>
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A381" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B381" s="34">
+      <c r="A381" t="s">
+        <v>60</v>
+      </c>
+      <c r="B381" s="28">
         <v>30</v>
       </c>
-      <c r="C381" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D381" s="32"/>
-      <c r="E381" s="32" t="s">
+      <c r="C381" t="s">
+        <v>105</v>
+      </c>
+      <c r="E381" t="s">
         <v>1225</v>
       </c>
       <c r="G381" t="s">
@@ -18180,82 +18119,69 @@
       </c>
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A382" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B382" s="34">
+      <c r="A382" t="s">
+        <v>60</v>
+      </c>
+      <c r="B382" s="28">
         <v>30</v>
       </c>
-      <c r="C382" s="32" t="s">
+      <c r="C382" t="s">
         <v>106</v>
       </c>
-      <c r="D382" s="32"/>
-      <c r="E382" s="32"/>
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A383" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B383" s="34">
+      <c r="A383" t="s">
+        <v>60</v>
+      </c>
+      <c r="B383" s="28">
         <v>30</v>
       </c>
-      <c r="C383" s="32" t="s">
+      <c r="C383" t="s">
         <v>107</v>
       </c>
-      <c r="D383" s="32"/>
-      <c r="E383" s="32"/>
       <c r="L383" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A384" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B384" s="34">
+      <c r="A384" t="s">
+        <v>60</v>
+      </c>
+      <c r="B384" s="28">
         <v>30</v>
       </c>
-      <c r="C384" s="32" t="s">
+      <c r="C384" t="s">
         <v>108</v>
       </c>
-      <c r="D384" s="32"/>
-      <c r="E384" s="32"/>
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A385" s="32"/>
-      <c r="B385" s="33"/>
-      <c r="C385" s="32"/>
-      <c r="D385" s="32"/>
-      <c r="E385" s="32"/>
+      <c r="B385" s="28"/>
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A386" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B386" s="33">
+      <c r="A386" t="s">
+        <v>60</v>
+      </c>
+      <c r="B386" s="28">
         <v>40</v>
       </c>
-      <c r="C386" s="32" t="s">
+      <c r="C386" t="s">
         <v>39</v>
       </c>
-      <c r="D386" s="32"/>
-      <c r="E386" s="32"/>
       <c r="L386" t="s">
         <v>1228</v>
       </c>
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A387" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B387" s="33">
+      <c r="A387" t="s">
+        <v>60</v>
+      </c>
+      <c r="B387" s="28">
         <v>40</v>
       </c>
-      <c r="C387" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D387" s="32"/>
-      <c r="E387" s="32" t="s">
+      <c r="C387" t="s">
+        <v>105</v>
+      </c>
+      <c r="E387" t="s">
         <v>1226</v>
       </c>
       <c r="G387" t="s">
@@ -18270,82 +18196,69 @@
       </c>
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A388" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B388" s="33">
+      <c r="A388" t="s">
+        <v>60</v>
+      </c>
+      <c r="B388" s="28">
         <v>40</v>
       </c>
-      <c r="C388" s="32" t="s">
+      <c r="C388" t="s">
         <v>106</v>
       </c>
-      <c r="D388" s="32"/>
-      <c r="E388" s="32"/>
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A389" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B389" s="33">
+      <c r="A389" t="s">
+        <v>60</v>
+      </c>
+      <c r="B389" s="28">
         <v>40</v>
       </c>
-      <c r="C389" s="32" t="s">
+      <c r="C389" t="s">
         <v>107</v>
       </c>
-      <c r="D389" s="32"/>
-      <c r="E389" s="32"/>
       <c r="L389" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A390" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B390" s="33">
+      <c r="A390" t="s">
+        <v>60</v>
+      </c>
+      <c r="B390" s="28">
         <v>40</v>
       </c>
-      <c r="C390" s="32" t="s">
+      <c r="C390" t="s">
         <v>108</v>
       </c>
-      <c r="D390" s="32"/>
-      <c r="E390" s="32"/>
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A391" s="32"/>
-      <c r="B391" s="33"/>
-      <c r="C391" s="32"/>
-      <c r="D391" s="32"/>
-      <c r="E391" s="32"/>
+      <c r="B391" s="28"/>
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A392" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B392" s="33">
+      <c r="A392" t="s">
+        <v>60</v>
+      </c>
+      <c r="B392" s="28">
         <v>50</v>
       </c>
-      <c r="C392" s="32" t="s">
+      <c r="C392" t="s">
         <v>39</v>
       </c>
-      <c r="D392" s="32"/>
-      <c r="E392" s="32"/>
       <c r="L392" t="s">
         <v>588</v>
       </c>
     </row>
     <row r="393" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A393" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B393" s="33">
+      <c r="A393" t="s">
+        <v>60</v>
+      </c>
+      <c r="B393" s="28">
         <v>50</v>
       </c>
-      <c r="C393" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D393" s="32"/>
-      <c r="E393" s="32" t="s">
+      <c r="C393" t="s">
+        <v>105</v>
+      </c>
+      <c r="E393" t="s">
         <v>1229</v>
       </c>
       <c r="G393" t="s">
@@ -18360,17 +18273,16 @@
       </c>
     </row>
     <row r="394" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A394" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B394" s="33">
+      <c r="A394" t="s">
+        <v>60</v>
+      </c>
+      <c r="B394" s="28">
         <v>50</v>
       </c>
-      <c r="C394" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D394" s="32"/>
-      <c r="E394" s="32" t="s">
+      <c r="C394" t="s">
+        <v>105</v>
+      </c>
+      <c r="E394" t="s">
         <v>1229</v>
       </c>
       <c r="G394" t="s">
@@ -18385,17 +18297,16 @@
       </c>
     </row>
     <row r="395" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A395" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B395" s="33">
+      <c r="A395" t="s">
+        <v>60</v>
+      </c>
+      <c r="B395" s="28">
         <v>50</v>
       </c>
-      <c r="C395" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D395" s="32"/>
-      <c r="E395" s="32" t="s">
+      <c r="C395" t="s">
+        <v>105</v>
+      </c>
+      <c r="E395" t="s">
         <v>1229</v>
       </c>
       <c r="G395" t="s">
@@ -18410,17 +18321,16 @@
       </c>
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A396" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B396" s="33">
+      <c r="A396" t="s">
+        <v>60</v>
+      </c>
+      <c r="B396" s="28">
         <v>50</v>
       </c>
-      <c r="C396" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D396" s="32"/>
-      <c r="E396" s="32" t="s">
+      <c r="C396" t="s">
+        <v>105</v>
+      </c>
+      <c r="E396" t="s">
         <v>1229</v>
       </c>
       <c r="G396" t="s">
@@ -18444,17 +18354,16 @@
       </c>
     </row>
     <row r="397" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A397" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B397" s="33">
+      <c r="A397" t="s">
+        <v>60</v>
+      </c>
+      <c r="B397" s="28">
         <v>50</v>
       </c>
-      <c r="C397" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D397" s="32"/>
-      <c r="E397" s="32" t="s">
+      <c r="C397" t="s">
+        <v>105</v>
+      </c>
+      <c r="E397" t="s">
         <v>1229</v>
       </c>
       <c r="G397" t="s">
@@ -18478,17 +18387,16 @@
       </c>
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A398" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B398" s="33">
+      <c r="A398" t="s">
+        <v>60</v>
+      </c>
+      <c r="B398" s="28">
         <v>50</v>
       </c>
-      <c r="C398" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D398" s="32"/>
-      <c r="E398" s="32" t="s">
+      <c r="C398" t="s">
+        <v>105</v>
+      </c>
+      <c r="E398" t="s">
         <v>1229</v>
       </c>
       <c r="G398" t="s">
@@ -18512,17 +18420,16 @@
       </c>
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A399" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B399" s="33">
+      <c r="A399" t="s">
+        <v>60</v>
+      </c>
+      <c r="B399" s="28">
         <v>50</v>
       </c>
-      <c r="C399" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D399" s="32"/>
-      <c r="E399" s="32" t="s">
+      <c r="C399" t="s">
+        <v>105</v>
+      </c>
+      <c r="E399" t="s">
         <v>1229</v>
       </c>
       <c r="G399" t="s">
@@ -18546,30 +18453,26 @@
       </c>
     </row>
     <row r="400" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A400" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B400" s="33">
+      <c r="A400" t="s">
+        <v>60</v>
+      </c>
+      <c r="B400" s="28">
         <v>50</v>
       </c>
-      <c r="C400" s="32" t="s">
+      <c r="C400" t="s">
         <v>106</v>
       </c>
-      <c r="D400" s="32"/>
-      <c r="E400" s="32"/>
     </row>
     <row r="401" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A401" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B401" s="33">
+      <c r="A401" t="s">
+        <v>60</v>
+      </c>
+      <c r="B401" s="28">
         <v>50</v>
       </c>
-      <c r="C401" s="32" t="s">
+      <c r="C401" t="s">
         <v>107</v>
       </c>
-      <c r="D401" s="32"/>
-      <c r="E401" s="32"/>
       <c r="L401" t="s">
         <v>130</v>
       </c>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130B32DD-00A9-154D-B757-5DC8FD20783D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB992A9E-A7CD-8D47-8644-ABE40EEF4031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="500" windowWidth="21640" windowHeight="19440" activeTab="3" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="-23400" yWindow="500" windowWidth="21640" windowHeight="17500" activeTab="3" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB992A9E-A7CD-8D47-8644-ABE40EEF4031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C19680-32BE-7B4C-8037-DD110809425E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23400" yWindow="500" windowWidth="21640" windowHeight="17500" activeTab="3" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C19680-32BE-7B4C-8037-DD110809425E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BCA7B9-1183-524F-B4F9-BA17E21388E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23400" yWindow="500" windowWidth="21640" windowHeight="17500" activeTab="3" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="16780" yWindow="500" windowWidth="21640" windowHeight="17500" activeTab="3" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5889" uniqueCount="1366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5957" uniqueCount="1380">
   <si>
     <t>page_id</t>
   </si>
@@ -4140,6 +4140,48 @@
   </si>
   <si>
     <t>- **Projektleitung:** Prof. Dr. Friedhelm Hoffmann</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>Information</t>
+  </si>
+  <si>
+    <t>pages/info</t>
+  </si>
+  <si>
+    <t>Zweck</t>
+  </si>
+  <si>
+    <t>Mit dem Inschriftenschlüssel, dessen Erstellung die LMU mit Geldern aus dem Fonds zur Förderung der Lehre ermöglicht hat, werden die wesentlichen ägyptischen Inschriftenformulare in strukturierter Weise für Lernende aufbereitet. So wird ein Hilfsmittel für die Lektüre von Originalinschriften geschaffen.</t>
+  </si>
+  <si>
+    <t>Hintergrund</t>
+  </si>
+  <si>
+    <t>Ein Verzeichnis von Hieroglyphen, die in Inschriften ggf. späterer Epochen häufig sind, aber etwa im Mittleren Reich noch nicht vorkommen oder aus anderen Gründen ungewohnt sind, rundet zusammen mit einem Wörterverzeichnis den Inschriftenschlüssel ab.</t>
+  </si>
+  <si>
+    <t>München 2026</t>
+  </si>
+  <si>
+    <t>Iulia Comşa, Friedhelm Hoffmann, Markus Kutschka</t>
+  </si>
+  <si>
+    <t>Erfahrungsgemäß fällt der Übergang von der Grammatikphase zur Lektüre und die Konfrontation mit tatsächlichen Inschriften in Ägypten oder im Museum aus verschiedenen Gründen vielen Studierenden schwer. Teils liegt es an ungewohnten Zeichenformen, die eine weit größere Varianz in ihrem Erscheinungsbild aufweisen als die gedruckten Hieroglyphen der Texteditionen; teils liegt es an den Schreibungen oder Wörtern, die in der Sprachausbildung nicht in der Frequenz vorkamen wie in den Inschriften; teils an der vielleicht suboptimalen Erhaltung; teils sind die Denkmäler aber auch einfach aus jüngeren Epochen und enthalten Phänomene, die im Unterricht noch nicht vorkamen, da sie für das Mittel- oder Altägyptische noch nicht relevant sind, die aber aufgrund der Häufigkeit jüngerer Inschriften in einem Museum prominenter sind.</t>
+  </si>
+  <si>
+    <t>Andererseits sind Inschriften trotz aller Vielfalt längst nicht so divers wie etwa Literaturwerke, sondern folgen innerhalb einer gewissen Variationsbreite, die je nach Ort, Zeit oder Aufwand unterschiedlich sein kann, bestimmten Formularen. Wenn man die kennt, findet man sich in ägyptischen Inschriften leichter zurecht. Dazu kommt ein gewisser Vorrat an Götterepitheta, und am Schluss bleiben womöglich nur die Titel und Namen des einstigen Stelenbesitzers ungelesen übrig.</t>
+  </si>
+  <si>
+    <t>Der Inschriftenschlüssel soll einen Überblick über die Grundtypen von Inschriften, die in ihnen vorgesehenen Elemente und die häufigsten Ausdrücke, die zur Ausfüllung dieser Positionen in Frage kommen, geben. Das soll in einer Weise geschehen, die strikt den Unterschied zwischen Inschriftentyp, den damit verbundenen Formularen und ihren Leerstellen sowie den konkreten Ausdrücken, die an einer Stelle stehen können, deutlich macht und zugleich je nach Epoche auch typische Schreibungen der für das Formular und seine Erkennbarkeit wichtigen Einzelwörter zeigt.</t>
+  </si>
+  <si>
+    <t>&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>Der Inschriftenschlüssel erinnert also zunächst an die häufigsten Formulare und ihren Aufbau und stellt dann die Elemente („Slots“) vor, also über alle Inschriftentypen hinweg im Wesentlichen [Gottheit], [König], [Gaben] und [Person]. Die Kenntnis der Inschriftenformulare stellt sicher, dass man stets weiß, wo in der Inschrift man sich gerade befindet, dass das Wort, auf das man nicht kommt, z. B. ein Götterepitheton sein muss etc., und verhindert „Flächenschäden“ im Textverständnis, aus denen man nicht mehr herausfindet.</t>
   </si>
 </sst>
 </file>
@@ -4149,7 +4191,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4179,6 +4221,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -4250,7 +4298,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4318,6 +4366,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4654,7 +4708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E50E2D7D-6A15-A747-8ABA-0F1F90941768}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
@@ -4972,6 +5026,23 @@
       </c>
       <c r="F18">
         <v>170</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F19">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -5606,7 +5677,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEDD5969-C8E3-C04D-AF17-FDEFB8218719}">
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="4" bestFit="1" customWidth="1"/>
@@ -7502,6 +7573,263 @@
       </c>
       <c r="K98" s="4">
         <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A101" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D101" s="34" t="s">
+        <v>1369</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K101" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="128" x14ac:dyDescent="0.2">
+      <c r="A102" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E102" s="35" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K102" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A103" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D103" s="34" t="s">
+        <v>1371</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K103" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="372" x14ac:dyDescent="0.2">
+      <c r="A104" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K104" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="221" x14ac:dyDescent="0.2">
+      <c r="A105" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K105" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" ht="221" x14ac:dyDescent="0.2">
+      <c r="A106" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K106" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A107" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D107" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K107" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="272" x14ac:dyDescent="0.2">
+      <c r="A108" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K108" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="238" x14ac:dyDescent="0.2">
+      <c r="A109" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K109" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+      <c r="A110" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K110" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A111" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="K111" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A112" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K112" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A113" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K113" s="4">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BCA7B9-1183-524F-B4F9-BA17E21388E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A8066E-EE5F-1949-B8FB-39A358186546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16780" yWindow="500" windowWidth="21640" windowHeight="17500" activeTab="3" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="15740" yWindow="500" windowWidth="22680" windowHeight="13920" activeTab="5" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5957" uniqueCount="1380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5996" uniqueCount="1384">
   <si>
     <t>page_id</t>
   </si>
@@ -4182,6 +4182,18 @@
   </si>
   <si>
     <t>Der Inschriftenschlüssel erinnert also zunächst an die häufigsten Formulare und ihren Aufbau und stellt dann die Elemente („Slots“) vor, also über alle Inschriftentypen hinweg im Wesentlichen [Gottheit], [König], [Gaben] und [Person]. Die Kenntnis der Inschriftenformulare stellt sicher, dass man stets weiß, wo in der Inschrift man sich gerade befindet, dass das Wort, auf das man nicht kommt, z. B. ein Götterepitheton sein muss etc., und verhindert „Flächenschäden“ im Textverständnis, aus denen man nicht mehr herausfindet.</t>
+  </si>
+  <si>
+    <t>0060_nb-WAs.t_Sp_01</t>
+  </si>
+  <si>
+    <t>0050_nb-WAs.t_NR_04</t>
+  </si>
+  <si>
+    <t>0070_nb-WAs.t_Gr_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -11837,7 +11849,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62D4F70-2351-5545-A291-11D662F747FD}">
-  <dimension ref="A1:L1093"/>
+  <dimension ref="A1:L1096"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.83203125" bestFit="1" customWidth="1"/>
@@ -24522,7 +24534,7 @@
         <v>1200</v>
       </c>
       <c r="L715" t="str">
-        <f t="shared" ref="L715:L718" si="104">_xlfn.TEXTJOIN("", TRUE, D715:K715)</f>
+        <f>_xlfn.TEXTJOIN("", TRUE, D715:K715)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0190_Month/0010_mnTw_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
@@ -24552,7 +24564,7 @@
         <v>1200</v>
       </c>
       <c r="L716" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" ref="L716:L718" si="104">_xlfn.TEXTJOIN("", TRUE, D716:K716)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0190_Month/0020_mnTw_NR_02.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
@@ -24726,7 +24738,7 @@
         <v>876</v>
       </c>
       <c r="L725" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D725:J725)</f>
+        <f>_xlfn.TEXTJOIN("", TRUE, D725:K725)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0190_Month/epitheta/01_nb-wAs.t/0001_nb-WAs.t_01.png</v>
       </c>
     </row>
@@ -24749,9 +24761,18 @@
       <c r="G726" t="s">
         <v>877</v>
       </c>
+      <c r="I726" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J726" t="s">
+        <v>1199</v>
+      </c>
+      <c r="K726" t="s">
+        <v>1200</v>
+      </c>
       <c r="L726" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D726:J726)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0190_Month/epitheta/01_nb-wAs.t/0010_nb-WAs.t_AR_01.png</v>
+        <f>_xlfn.TEXTJOIN("", TRUE, D726:K726)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0190_Month/epitheta/01_nb-wAs.t/0010_nb-WAs.t_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="727" spans="1:12" x14ac:dyDescent="0.2">
@@ -24773,9 +24794,18 @@
       <c r="G727" t="s">
         <v>878</v>
       </c>
+      <c r="I727" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J727" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K727" t="s">
+        <v>1200</v>
+      </c>
       <c r="L727" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D727:J727)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0190_Month/epitheta/01_nb-wAs.t/0020_nb-WAs.t_NR_01.png</v>
+        <f>_xlfn.TEXTJOIN("", TRUE, D727:K727)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0190_Month/epitheta/01_nb-wAs.t/0020_nb-WAs.t_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="728" spans="1:12" x14ac:dyDescent="0.2">
@@ -24797,9 +24827,18 @@
       <c r="G728" t="s">
         <v>879</v>
       </c>
+      <c r="I728" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J728" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K728" t="s">
+        <v>1200</v>
+      </c>
       <c r="L728" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D728:J728)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0190_Month/epitheta/01_nb-wAs.t/0030_nb-WAs.t_NR_02.png</v>
+        <f>_xlfn.TEXTJOIN("", TRUE, D728:K728)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0190_Month/epitheta/01_nb-wAs.t/0030_nb-WAs.t_NR_02.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="729" spans="1:12" x14ac:dyDescent="0.2">
@@ -24821,9 +24860,18 @@
       <c r="G729" t="s">
         <v>880</v>
       </c>
+      <c r="I729" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J729" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K729" t="s">
+        <v>1200</v>
+      </c>
       <c r="L729" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D729:J729)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0190_Month/epitheta/01_nb-wAs.t/0040_nb-WAs.t_NR_03.png</v>
+        <f>_xlfn.TEXTJOIN("", TRUE, D729:K729)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0190_Month/epitheta/01_nb-wAs.t/0040_nb-WAs.t_NR_03.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="730" spans="1:12" x14ac:dyDescent="0.2">
@@ -24834,66 +24882,118 @@
         <v>1</v>
       </c>
       <c r="C730" t="s">
+        <v>105</v>
+      </c>
+      <c r="E730" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F730" t="s">
+        <v>875</v>
+      </c>
+      <c r="G730" t="s">
+        <v>1381</v>
+      </c>
+      <c r="H730" t="s">
+        <v>113</v>
+      </c>
+      <c r="I730" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J730" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K730" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L730" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D730:K730)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0190_Month/epitheta/01_nb-wAs.t/0050_nb-WAs.t_NR_04.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="731" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A731" t="s">
+        <v>872</v>
+      </c>
+      <c r="B731" s="27">
+        <v>1</v>
+      </c>
+      <c r="C731" t="s">
+        <v>105</v>
+      </c>
+      <c r="E731" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F731" t="s">
+        <v>875</v>
+      </c>
+      <c r="G731" t="s">
+        <v>1380</v>
+      </c>
+      <c r="H731" t="s">
+        <v>113</v>
+      </c>
+      <c r="I731" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J731" t="s">
+        <v>1207</v>
+      </c>
+      <c r="K731" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L731" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D731:K731)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0190_Month/epitheta/01_nb-wAs.t/0060_nb-WAs.t_Sp_01.png &lt;sup&gt;(Sp.)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="732" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A732" t="s">
+        <v>872</v>
+      </c>
+      <c r="B732" s="27">
+        <v>1</v>
+      </c>
+      <c r="C732" t="s">
+        <v>105</v>
+      </c>
+      <c r="E732" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F732" t="s">
+        <v>875</v>
+      </c>
+      <c r="G732" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H732" t="s">
+        <v>113</v>
+      </c>
+      <c r="I732" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J732" t="s">
+        <v>1383</v>
+      </c>
+      <c r="K732" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L732" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D732:K732)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0190_Month/epitheta/01_nb-wAs.t/0070_nb-WAs.t_Gr_01.png &lt;sup&gt;  &lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="733" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A733" t="s">
+        <v>872</v>
+      </c>
+      <c r="B733" s="27">
+        <v>1</v>
+      </c>
+      <c r="C733" t="s">
         <v>27</v>
       </c>
-      <c r="L730" t="s">
+      <c r="L733" t="s">
         <v>874</v>
-      </c>
-    </row>
-    <row r="734" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A734" t="s">
-        <v>60</v>
-      </c>
-      <c r="B734" s="27">
-        <v>200</v>
-      </c>
-      <c r="C734" t="s">
-        <v>39</v>
-      </c>
-      <c r="L734" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="735" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A735" t="s">
-        <v>60</v>
-      </c>
-      <c r="B735" s="27">
-        <v>200</v>
-      </c>
-      <c r="C735" t="s">
-        <v>105</v>
-      </c>
-      <c r="E735" t="s">
-        <v>1244</v>
-      </c>
-      <c r="G735" t="s">
-        <v>881</v>
-      </c>
-      <c r="L735" t="str">
-        <f t="shared" ref="L735:L740" si="105">_xlfn.TEXTJOIN("", TRUE, D735:J735)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0200_Neith/0001_nj.t_01.png</v>
-      </c>
-    </row>
-    <row r="736" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A736" t="s">
-        <v>60</v>
-      </c>
-      <c r="B736" s="27">
-        <v>200</v>
-      </c>
-      <c r="C736" t="s">
-        <v>105</v>
-      </c>
-      <c r="E736" t="s">
-        <v>1244</v>
-      </c>
-      <c r="G736" t="s">
-        <v>882</v>
-      </c>
-      <c r="L736" t="str">
-        <f t="shared" si="105"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0200_Neith/0010_nj.t_02.png</v>
       </c>
     </row>
     <row r="737" spans="1:12" x14ac:dyDescent="0.2">
@@ -24904,17 +25004,10 @@
         <v>200</v>
       </c>
       <c r="C737" t="s">
-        <v>105</v>
-      </c>
-      <c r="E737" t="s">
-        <v>1244</v>
-      </c>
-      <c r="G737" t="s">
-        <v>883</v>
-      </c>
-      <c r="L737" t="str">
-        <f t="shared" si="105"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0200_Neith/0020_nj.t_03.png</v>
+        <v>39</v>
+      </c>
+      <c r="L737" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="738" spans="1:12" x14ac:dyDescent="0.2">
@@ -24931,11 +25024,11 @@
         <v>1244</v>
       </c>
       <c r="G738" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="L738" t="str">
-        <f t="shared" si="105"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0200_Neith/0030_nj.t_04.png</v>
+        <f>_xlfn.TEXTJOIN("", TRUE, D738:K738)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0200_Neith/0001_nj.t_01.png</v>
       </c>
     </row>
     <row r="739" spans="1:12" x14ac:dyDescent="0.2">
@@ -24952,20 +25045,11 @@
         <v>1244</v>
       </c>
       <c r="G739" t="s">
-        <v>885</v>
-      </c>
-      <c r="I739" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J739" t="s">
-        <v>1153</v>
-      </c>
-      <c r="K739" t="s">
-        <v>1200</v>
+        <v>882</v>
       </c>
       <c r="L739" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D739:K739)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0200_Neith/0040_nj.t_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0200_Neith/0010_nj.t_02.png</v>
       </c>
     </row>
     <row r="740" spans="1:12" x14ac:dyDescent="0.2">
@@ -24976,11 +25060,17 @@
         <v>200</v>
       </c>
       <c r="C740" t="s">
-        <v>106</v>
+        <v>105</v>
+      </c>
+      <c r="E740" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G740" t="s">
+        <v>883</v>
       </c>
       <c r="L740" t="str">
-        <f t="shared" si="105"/>
-        <v/>
+        <f>_xlfn.TEXTJOIN("", TRUE, D740:K740)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0200_Neith/0020_nj.t_03.png</v>
       </c>
     </row>
     <row r="741" spans="1:12" x14ac:dyDescent="0.2">
@@ -24991,10 +25081,17 @@
         <v>200</v>
       </c>
       <c r="C741" t="s">
-        <v>107</v>
-      </c>
-      <c r="L741" t="s">
-        <v>145</v>
+        <v>105</v>
+      </c>
+      <c r="E741" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G741" t="s">
+        <v>884</v>
+      </c>
+      <c r="L741" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D741:K741)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0200_Neith/0030_nj.t_04.png</v>
       </c>
     </row>
     <row r="742" spans="1:12" x14ac:dyDescent="0.2">
@@ -25005,7 +25102,55 @@
         <v>200</v>
       </c>
       <c r="C742" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="E742" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G742" t="s">
+        <v>885</v>
+      </c>
+      <c r="I742" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J742" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K742" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L742" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D742:K742)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0200_Neith/0040_nj.t_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="743" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A743" t="s">
+        <v>60</v>
+      </c>
+      <c r="B743" s="27">
+        <v>200</v>
+      </c>
+      <c r="C743" t="s">
+        <v>106</v>
+      </c>
+      <c r="L743" t="str">
+        <f t="shared" ref="L743" si="105">_xlfn.TEXTJOIN("", TRUE, D743:J743)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="744" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A744" t="s">
+        <v>60</v>
+      </c>
+      <c r="B744" s="27">
+        <v>200</v>
+      </c>
+      <c r="C744" t="s">
+        <v>107</v>
+      </c>
+      <c r="L744" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="745" spans="1:12" x14ac:dyDescent="0.2">
@@ -25013,64 +25158,10 @@
         <v>60</v>
       </c>
       <c r="B745" s="27">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C745" t="s">
-        <v>39</v>
-      </c>
-      <c r="L745" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="746" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A746" t="s">
-        <v>60</v>
-      </c>
-      <c r="B746" s="27">
-        <v>210</v>
-      </c>
-      <c r="C746" t="s">
-        <v>105</v>
-      </c>
-      <c r="E746" t="s">
-        <v>1245</v>
-      </c>
-      <c r="G746" t="s">
-        <v>886</v>
-      </c>
-      <c r="L746" t="str">
-        <f t="shared" ref="L746:L752" si="106">_xlfn.TEXTJOIN("", TRUE, D746:J746)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0210_Nut/0001_nw.t_01.png</v>
-      </c>
-    </row>
-    <row r="747" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A747" t="s">
-        <v>60</v>
-      </c>
-      <c r="B747" s="27">
-        <v>210</v>
-      </c>
-      <c r="C747" t="s">
-        <v>105</v>
-      </c>
-      <c r="E747" t="s">
-        <v>1245</v>
-      </c>
-      <c r="G747" t="s">
-        <v>887</v>
-      </c>
-      <c r="I747" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J747" t="s">
-        <v>1199</v>
-      </c>
-      <c r="K747" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L747" t="str">
-        <f t="shared" ref="L747:L751" si="107">_xlfn.TEXTJOIN("", TRUE, D747:K747)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0210_Nut/0010_nw.t_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <v>108</v>
       </c>
     </row>
     <row r="748" spans="1:12" x14ac:dyDescent="0.2">
@@ -25081,26 +25172,10 @@
         <v>210</v>
       </c>
       <c r="C748" t="s">
-        <v>105</v>
-      </c>
-      <c r="E748" t="s">
-        <v>1245</v>
-      </c>
-      <c r="G748" t="s">
-        <v>888</v>
-      </c>
-      <c r="I748" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J748" t="s">
-        <v>1199</v>
-      </c>
-      <c r="K748" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L748" t="str">
-        <f t="shared" si="107"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0210_Nut/0020_nw.t_AR_02.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <v>39</v>
+      </c>
+      <c r="L748" t="s">
+        <v>709</v>
       </c>
     </row>
     <row r="749" spans="1:12" x14ac:dyDescent="0.2">
@@ -25117,20 +25192,11 @@
         <v>1245</v>
       </c>
       <c r="G749" t="s">
-        <v>889</v>
-      </c>
-      <c r="I749" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J749" t="s">
-        <v>1199</v>
-      </c>
-      <c r="K749" t="s">
-        <v>1200</v>
+        <v>886</v>
       </c>
       <c r="L749" t="str">
-        <f t="shared" si="107"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0210_Nut/0030_nw.t_AR_03.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <f t="shared" ref="L749:L754" si="106">_xlfn.TEXTJOIN("", TRUE, D749:K749)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0210_Nut/0001_nw.t_01.png</v>
       </c>
     </row>
     <row r="750" spans="1:12" x14ac:dyDescent="0.2">
@@ -25147,20 +25213,20 @@
         <v>1245</v>
       </c>
       <c r="G750" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="I750" t="s">
         <v>1198</v>
       </c>
       <c r="J750" t="s">
-        <v>1153</v>
+        <v>1199</v>
       </c>
       <c r="K750" t="s">
         <v>1200</v>
       </c>
       <c r="L750" t="str">
-        <f t="shared" si="107"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0210_Nut/0040_nw.t_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+        <f t="shared" si="106"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0210_Nut/0010_nw.t_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="751" spans="1:12" x14ac:dyDescent="0.2">
@@ -25177,20 +25243,20 @@
         <v>1245</v>
       </c>
       <c r="G751" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="I751" t="s">
         <v>1198</v>
       </c>
       <c r="J751" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="K751" t="s">
         <v>1200</v>
       </c>
       <c r="L751" t="str">
-        <f t="shared" si="107"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0210_Nut/0050_nw.t_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+        <f t="shared" si="106"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0210_Nut/0020_nw.t_AR_02.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="752" spans="1:12" x14ac:dyDescent="0.2">
@@ -25201,11 +25267,26 @@
         <v>210</v>
       </c>
       <c r="C752" t="s">
-        <v>106</v>
+        <v>105</v>
+      </c>
+      <c r="E752" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G752" t="s">
+        <v>889</v>
+      </c>
+      <c r="I752" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J752" t="s">
+        <v>1199</v>
+      </c>
+      <c r="K752" t="s">
+        <v>1200</v>
       </c>
       <c r="L752" t="str">
         <f t="shared" si="106"/>
-        <v/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0210_Nut/0030_nw.t_AR_03.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="753" spans="1:12" x14ac:dyDescent="0.2">
@@ -25216,10 +25297,26 @@
         <v>210</v>
       </c>
       <c r="C753" t="s">
-        <v>107</v>
-      </c>
-      <c r="L753" t="s">
-        <v>146</v>
+        <v>105</v>
+      </c>
+      <c r="E753" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G753" t="s">
+        <v>890</v>
+      </c>
+      <c r="I753" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J753" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K753" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L753" t="str">
+        <f t="shared" si="106"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0210_Nut/0040_nw.t_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="754" spans="1:12" x14ac:dyDescent="0.2">
@@ -25230,7 +25327,55 @@
         <v>210</v>
       </c>
       <c r="C754" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="E754" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G754" t="s">
+        <v>891</v>
+      </c>
+      <c r="I754" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J754" t="s">
+        <v>1201</v>
+      </c>
+      <c r="K754" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L754" t="str">
+        <f t="shared" si="106"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0210_Nut/0050_nw.t_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="755" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A755" t="s">
+        <v>60</v>
+      </c>
+      <c r="B755" s="27">
+        <v>210</v>
+      </c>
+      <c r="C755" t="s">
+        <v>106</v>
+      </c>
+      <c r="L755" t="str">
+        <f t="shared" ref="L755" si="107">_xlfn.TEXTJOIN("", TRUE, D755:J755)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="756" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A756" t="s">
+        <v>60</v>
+      </c>
+      <c r="B756" s="27">
+        <v>210</v>
+      </c>
+      <c r="C756" t="s">
+        <v>107</v>
+      </c>
+      <c r="L756" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="757" spans="1:12" x14ac:dyDescent="0.2">
@@ -25238,64 +25383,10 @@
         <v>60</v>
       </c>
       <c r="B757" s="27">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C757" t="s">
-        <v>39</v>
-      </c>
-      <c r="L757" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="758" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A758" t="s">
-        <v>60</v>
-      </c>
-      <c r="B758" s="27">
-        <v>220</v>
-      </c>
-      <c r="C758" t="s">
-        <v>105</v>
-      </c>
-      <c r="E758" t="s">
-        <v>1246</v>
-      </c>
-      <c r="G758" t="s">
-        <v>892</v>
-      </c>
-      <c r="L758" t="str">
-        <f t="shared" ref="L758:L765" si="108">_xlfn.TEXTJOIN("", TRUE, D758:J758)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0220_Nephthys/0001_nb.t-Hw.t_01.png</v>
-      </c>
-    </row>
-    <row r="759" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A759" t="s">
-        <v>60</v>
-      </c>
-      <c r="B759" s="27">
-        <v>220</v>
-      </c>
-      <c r="C759" t="s">
-        <v>105</v>
-      </c>
-      <c r="E759" t="s">
-        <v>1246</v>
-      </c>
-      <c r="G759" t="s">
-        <v>893</v>
-      </c>
-      <c r="I759" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J759" t="s">
-        <v>1199</v>
-      </c>
-      <c r="K759" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L759" t="str">
-        <f t="shared" ref="L759:L764" si="109">_xlfn.TEXTJOIN("", TRUE, D759:K759)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0220_Nephthys/0010_nb.t-Hw.t_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <v>108</v>
       </c>
     </row>
     <row r="760" spans="1:12" x14ac:dyDescent="0.2">
@@ -25306,26 +25397,10 @@
         <v>220</v>
       </c>
       <c r="C760" t="s">
-        <v>105</v>
-      </c>
-      <c r="E760" t="s">
-        <v>1246</v>
-      </c>
-      <c r="G760" t="s">
-        <v>894</v>
-      </c>
-      <c r="I760" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J760" t="s">
-        <v>1153</v>
-      </c>
-      <c r="K760" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L760" t="str">
-        <f t="shared" si="109"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0220_Nephthys/0020_nb.t-Hw.t_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+        <v>39</v>
+      </c>
+      <c r="L760" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="761" spans="1:12" x14ac:dyDescent="0.2">
@@ -25342,20 +25417,11 @@
         <v>1246</v>
       </c>
       <c r="G761" t="s">
-        <v>895</v>
-      </c>
-      <c r="I761" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J761" t="s">
-        <v>1153</v>
-      </c>
-      <c r="K761" t="s">
-        <v>1200</v>
+        <v>892</v>
       </c>
       <c r="L761" t="str">
-        <f t="shared" si="109"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0220_Nephthys/0030_nb.t-Hw.t_NR_02.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+        <f t="shared" ref="L761:L767" si="108">_xlfn.TEXTJOIN("", TRUE, D761:K761)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0220_Nephthys/0001_nb.t-Hw.t_01.png</v>
       </c>
     </row>
     <row r="762" spans="1:12" x14ac:dyDescent="0.2">
@@ -25372,20 +25438,20 @@
         <v>1246</v>
       </c>
       <c r="G762" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="I762" t="s">
         <v>1198</v>
       </c>
       <c r="J762" t="s">
-        <v>1207</v>
+        <v>1199</v>
       </c>
       <c r="K762" t="s">
         <v>1200</v>
       </c>
       <c r="L762" t="str">
-        <f t="shared" si="109"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0220_Nephthys/0040_nb.t-Hw.t_SP_01.png &lt;sup&gt;(Sp.)&lt;/sup&gt;</v>
+        <f t="shared" si="108"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0220_Nephthys/0010_nb.t-Hw.t_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="763" spans="1:12" x14ac:dyDescent="0.2">
@@ -25402,20 +25468,20 @@
         <v>1246</v>
       </c>
       <c r="G763" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="I763" t="s">
         <v>1198</v>
       </c>
       <c r="J763" t="s">
-        <v>1201</v>
+        <v>1153</v>
       </c>
       <c r="K763" t="s">
         <v>1200</v>
       </c>
       <c r="L763" t="str">
-        <f t="shared" si="109"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0220_Nephthys/0050_nb.t-Hw.t_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+        <f t="shared" si="108"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0220_Nephthys/0020_nb.t-Hw.t_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="764" spans="1:12" x14ac:dyDescent="0.2">
@@ -25432,20 +25498,20 @@
         <v>1246</v>
       </c>
       <c r="G764" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="I764" t="s">
         <v>1198</v>
       </c>
       <c r="J764" t="s">
-        <v>1201</v>
+        <v>1153</v>
       </c>
       <c r="K764" t="s">
         <v>1200</v>
       </c>
       <c r="L764" t="str">
-        <f t="shared" si="109"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0220_Nephthys/0060_nb.t-Hw.t_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+        <f t="shared" si="108"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0220_Nephthys/0030_nb.t-Hw.t_NR_02.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="765" spans="1:12" x14ac:dyDescent="0.2">
@@ -25456,11 +25522,26 @@
         <v>220</v>
       </c>
       <c r="C765" t="s">
-        <v>106</v>
+        <v>105</v>
+      </c>
+      <c r="E765" t="s">
+        <v>1246</v>
+      </c>
+      <c r="G765" t="s">
+        <v>896</v>
+      </c>
+      <c r="I765" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J765" t="s">
+        <v>1207</v>
+      </c>
+      <c r="K765" t="s">
+        <v>1200</v>
       </c>
       <c r="L765" t="str">
         <f t="shared" si="108"/>
-        <v/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0220_Nephthys/0040_nb.t-Hw.t_SP_01.png &lt;sup&gt;(Sp.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="766" spans="1:12" x14ac:dyDescent="0.2">
@@ -25471,10 +25552,26 @@
         <v>220</v>
       </c>
       <c r="C766" t="s">
-        <v>107</v>
-      </c>
-      <c r="L766" t="s">
-        <v>147</v>
+        <v>105</v>
+      </c>
+      <c r="E766" t="s">
+        <v>1246</v>
+      </c>
+      <c r="G766" t="s">
+        <v>897</v>
+      </c>
+      <c r="I766" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J766" t="s">
+        <v>1201</v>
+      </c>
+      <c r="K766" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L766" t="str">
+        <f t="shared" si="108"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0220_Nephthys/0050_nb.t-Hw.t_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="767" spans="1:12" x14ac:dyDescent="0.2">
@@ -25485,7 +25582,55 @@
         <v>220</v>
       </c>
       <c r="C767" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="E767" t="s">
+        <v>1246</v>
+      </c>
+      <c r="G767" t="s">
+        <v>898</v>
+      </c>
+      <c r="I767" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J767" t="s">
+        <v>1201</v>
+      </c>
+      <c r="K767" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L767" t="str">
+        <f t="shared" si="108"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0220_Nephthys/0060_nb.t-Hw.t_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="768" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A768" t="s">
+        <v>60</v>
+      </c>
+      <c r="B768" s="27">
+        <v>220</v>
+      </c>
+      <c r="C768" t="s">
+        <v>106</v>
+      </c>
+      <c r="L768" t="str">
+        <f t="shared" ref="L768" si="109">_xlfn.TEXTJOIN("", TRUE, D768:J768)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="769" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A769" t="s">
+        <v>60</v>
+      </c>
+      <c r="B769" s="27">
+        <v>220</v>
+      </c>
+      <c r="C769" t="s">
+        <v>107</v>
+      </c>
+      <c r="L769" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="770" spans="1:12" x14ac:dyDescent="0.2">
@@ -25493,236 +25638,236 @@
         <v>60</v>
       </c>
       <c r="B770" s="27">
+        <v>220</v>
+      </c>
+      <c r="C770" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="773" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A773" t="s">
+        <v>60</v>
+      </c>
+      <c r="B773" s="27">
         <v>230</v>
       </c>
-      <c r="C770" t="s">
+      <c r="C773" t="s">
         <v>39</v>
       </c>
-      <c r="L770" t="s">
+      <c r="L773" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="771" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A771" t="s">
-        <v>60</v>
-      </c>
-      <c r="B771" s="27">
+    <row r="774" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A774" t="s">
+        <v>60</v>
+      </c>
+      <c r="B774" s="27">
         <v>230</v>
       </c>
-      <c r="C771" t="s">
-        <v>105</v>
-      </c>
-      <c r="E771" t="s">
+      <c r="C774" t="s">
+        <v>105</v>
+      </c>
+      <c r="E774" t="s">
         <v>1247</v>
       </c>
-      <c r="G771" t="s">
+      <c r="G774" t="s">
         <v>899</v>
       </c>
-      <c r="L771" t="str">
-        <f t="shared" ref="L771:L772" si="110">_xlfn.TEXTJOIN("", TRUE, D771:J771)</f>
+      <c r="L774" t="str">
+        <f t="shared" ref="L774:L775" si="110">_xlfn.TEXTJOIN("", TRUE, D774:J774)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0230_Nefertem/0001_nfr-tm_01.png</v>
       </c>
     </row>
-    <row r="772" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A772" t="s">
-        <v>60</v>
-      </c>
-      <c r="B772" s="27">
+    <row r="775" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A775" t="s">
+        <v>60</v>
+      </c>
+      <c r="B775" s="27">
         <v>230</v>
       </c>
-      <c r="C772" t="s">
-        <v>105</v>
-      </c>
-      <c r="E772" t="s">
+      <c r="C775" t="s">
+        <v>105</v>
+      </c>
+      <c r="E775" t="s">
         <v>1247</v>
       </c>
-      <c r="G772" t="s">
+      <c r="G775" t="s">
         <v>900</v>
       </c>
-      <c r="L772" t="str">
+      <c r="L775" t="str">
         <f t="shared" si="110"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0230_Nefertem/0010_nfr-tm_02.png</v>
       </c>
     </row>
-    <row r="773" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A773" t="s">
-        <v>60</v>
-      </c>
-      <c r="B773" s="27">
+    <row r="776" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A776" t="s">
+        <v>60</v>
+      </c>
+      <c r="B776" s="27">
         <v>230</v>
       </c>
-      <c r="C773" t="s">
-        <v>105</v>
-      </c>
-      <c r="E773" t="s">
+      <c r="C776" t="s">
+        <v>105</v>
+      </c>
+      <c r="E776" t="s">
         <v>1247</v>
       </c>
-      <c r="G773" t="s">
+      <c r="G776" t="s">
         <v>901</v>
       </c>
-      <c r="I773" t="s">
+      <c r="I776" t="s">
         <v>1198</v>
       </c>
-      <c r="J773" t="s">
+      <c r="J776" t="s">
         <v>1153</v>
       </c>
-      <c r="K773" t="s">
+      <c r="K776" t="s">
         <v>1200</v>
       </c>
-      <c r="L773" t="str">
-        <f t="shared" ref="L773:L777" si="111">_xlfn.TEXTJOIN("", TRUE, D773:K773)</f>
+      <c r="L776" t="str">
+        <f t="shared" ref="L776:L780" si="111">_xlfn.TEXTJOIN("", TRUE, D776:K776)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0230_Nefertem/0020_nfr-tm_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="774" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A774" t="s">
-        <v>60</v>
-      </c>
-      <c r="B774" s="27">
+    <row r="777" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A777" t="s">
+        <v>60</v>
+      </c>
+      <c r="B777" s="27">
         <v>230</v>
       </c>
-      <c r="C774" t="s">
-        <v>105</v>
-      </c>
-      <c r="E774" t="s">
+      <c r="C777" t="s">
+        <v>105</v>
+      </c>
+      <c r="E777" t="s">
         <v>1247</v>
       </c>
-      <c r="G774" t="s">
+      <c r="G777" t="s">
         <v>902</v>
       </c>
-      <c r="I774" t="s">
+      <c r="I777" t="s">
         <v>1198</v>
       </c>
-      <c r="J774" t="s">
+      <c r="J777" t="s">
         <v>1201</v>
       </c>
-      <c r="K774" t="s">
+      <c r="K777" t="s">
         <v>1200</v>
       </c>
-      <c r="L774" t="str">
+      <c r="L777" t="str">
         <f t="shared" si="111"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0230_Nefertem/0030_nfr-tm_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="775" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A775" t="s">
-        <v>60</v>
-      </c>
-      <c r="B775" s="27">
+    <row r="778" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A778" t="s">
+        <v>60</v>
+      </c>
+      <c r="B778" s="27">
         <v>230</v>
       </c>
-      <c r="C775" t="s">
-        <v>105</v>
-      </c>
-      <c r="E775" t="s">
+      <c r="C778" t="s">
+        <v>105</v>
+      </c>
+      <c r="E778" t="s">
         <v>1247</v>
       </c>
-      <c r="G775" t="s">
+      <c r="G778" t="s">
         <v>903</v>
       </c>
-      <c r="I775" t="s">
+      <c r="I778" t="s">
         <v>1198</v>
       </c>
-      <c r="J775" t="s">
+      <c r="J778" t="s">
         <v>1201</v>
       </c>
-      <c r="K775" t="s">
+      <c r="K778" t="s">
         <v>1200</v>
       </c>
-      <c r="L775" t="str">
+      <c r="L778" t="str">
         <f t="shared" si="111"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0230_Nefertem/0040_nfr-tm_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="776" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A776" t="s">
-        <v>60</v>
-      </c>
-      <c r="B776" s="27">
+    <row r="779" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A779" t="s">
+        <v>60</v>
+      </c>
+      <c r="B779" s="27">
         <v>230</v>
       </c>
-      <c r="C776" t="s">
+      <c r="C779" t="s">
         <v>106</v>
       </c>
-      <c r="E776" t="s">
+      <c r="E779" t="s">
         <v>1247</v>
       </c>
-      <c r="F776" t="s">
+      <c r="F779" t="s">
         <v>111</v>
       </c>
-      <c r="G776" t="s">
+      <c r="G779" t="s">
         <v>904</v>
       </c>
-      <c r="I776" t="s">
+      <c r="I779" t="s">
         <v>1198</v>
       </c>
-      <c r="J776" t="s">
+      <c r="J779" t="s">
         <v>1153</v>
       </c>
-      <c r="K776" t="s">
+      <c r="K779" t="s">
         <v>1200</v>
       </c>
-      <c r="L776" t="str">
+      <c r="L779" t="str">
         <f t="shared" si="111"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0230_Nefertem/det/0001_nfr-tm_det_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="777" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A777" t="s">
-        <v>60</v>
-      </c>
-      <c r="B777" s="27">
+    <row r="780" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A780" t="s">
+        <v>60</v>
+      </c>
+      <c r="B780" s="27">
         <v>230</v>
       </c>
-      <c r="C777" t="s">
+      <c r="C780" t="s">
         <v>106</v>
       </c>
-      <c r="E777" t="s">
+      <c r="E780" t="s">
         <v>1247</v>
       </c>
-      <c r="F777" t="s">
+      <c r="F780" t="s">
         <v>111</v>
       </c>
-      <c r="G777" t="s">
+      <c r="G780" t="s">
         <v>905</v>
       </c>
-      <c r="I777" t="s">
+      <c r="I780" t="s">
         <v>1198</v>
       </c>
-      <c r="J777" t="s">
+      <c r="J780" t="s">
         <v>1153</v>
       </c>
-      <c r="K777" t="s">
+      <c r="K780" t="s">
         <v>1200</v>
       </c>
-      <c r="L777" t="str">
+      <c r="L780" t="str">
         <f t="shared" si="111"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0230_Nefertem/det/0010_nfr-tm_det_NR_02.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="778" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A778" t="s">
-        <v>60</v>
-      </c>
-      <c r="B778" s="27">
+    <row r="781" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A781" t="s">
+        <v>60</v>
+      </c>
+      <c r="B781" s="27">
         <v>230</v>
       </c>
-      <c r="C778" t="s">
+      <c r="C781" t="s">
         <v>107</v>
       </c>
-      <c r="L778" t="s">
+      <c r="L781" t="s">
         <v>148</v>
-      </c>
-    </row>
-    <row r="779" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A779" t="s">
-        <v>60</v>
-      </c>
-      <c r="B779" s="27">
-        <v>230</v>
-      </c>
-      <c r="C779" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="782" spans="1:12" x14ac:dyDescent="0.2">
@@ -25730,55 +25875,10 @@
         <v>60</v>
       </c>
       <c r="B782" s="27">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C782" t="s">
-        <v>39</v>
-      </c>
-      <c r="L782" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="783" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A783" t="s">
-        <v>60</v>
-      </c>
-      <c r="B783" s="27">
-        <v>240</v>
-      </c>
-      <c r="C783" t="s">
-        <v>105</v>
-      </c>
-      <c r="E783" t="s">
-        <v>1248</v>
-      </c>
-      <c r="G783" t="s">
-        <v>906</v>
-      </c>
-      <c r="L783" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D783:J783)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0240_Nechbet/0001_nxb.t_01.png</v>
-      </c>
-    </row>
-    <row r="784" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A784" t="s">
-        <v>60</v>
-      </c>
-      <c r="B784" s="27">
-        <v>240</v>
-      </c>
-      <c r="C784" t="s">
-        <v>105</v>
-      </c>
-      <c r="E784" t="s">
-        <v>1248</v>
-      </c>
-      <c r="G784" t="s">
-        <v>907</v>
-      </c>
-      <c r="L784" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D784:J784)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0240_Nechbet/0010_nxb.t_02.png</v>
+        <v>108</v>
       </c>
     </row>
     <row r="785" spans="1:12" x14ac:dyDescent="0.2">
@@ -25789,26 +25889,10 @@
         <v>240</v>
       </c>
       <c r="C785" t="s">
-        <v>105</v>
-      </c>
-      <c r="E785" t="s">
-        <v>1248</v>
-      </c>
-      <c r="G785" t="s">
-        <v>908</v>
-      </c>
-      <c r="I785" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J785" t="s">
-        <v>1153</v>
-      </c>
-      <c r="K785" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L785" t="str">
-        <f t="shared" ref="L785:L787" si="112">_xlfn.TEXTJOIN("", TRUE, D785:K785)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0240_Nechbet/0020_nxb.t_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+        <v>39</v>
+      </c>
+      <c r="L785" t="s">
+        <v>712</v>
       </c>
     </row>
     <row r="786" spans="1:12" x14ac:dyDescent="0.2">
@@ -25825,81 +25909,142 @@
         <v>1248</v>
       </c>
       <c r="G786" t="s">
+        <v>906</v>
+      </c>
+      <c r="L786" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D786:J786)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0240_Nechbet/0001_nxb.t_01.png</v>
+      </c>
+    </row>
+    <row r="787" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A787" t="s">
+        <v>60</v>
+      </c>
+      <c r="B787" s="27">
+        <v>240</v>
+      </c>
+      <c r="C787" t="s">
+        <v>105</v>
+      </c>
+      <c r="E787" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G787" t="s">
+        <v>907</v>
+      </c>
+      <c r="L787" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D787:J787)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0240_Nechbet/0010_nxb.t_02.png</v>
+      </c>
+    </row>
+    <row r="788" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A788" t="s">
+        <v>60</v>
+      </c>
+      <c r="B788" s="27">
+        <v>240</v>
+      </c>
+      <c r="C788" t="s">
+        <v>105</v>
+      </c>
+      <c r="E788" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G788" t="s">
+        <v>908</v>
+      </c>
+      <c r="I788" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J788" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K788" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L788" t="str">
+        <f t="shared" ref="L788:L790" si="112">_xlfn.TEXTJOIN("", TRUE, D788:K788)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0240_Nechbet/0020_nxb.t_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="789" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A789" t="s">
+        <v>60</v>
+      </c>
+      <c r="B789" s="27">
+        <v>240</v>
+      </c>
+      <c r="C789" t="s">
+        <v>105</v>
+      </c>
+      <c r="E789" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G789" t="s">
         <v>909</v>
       </c>
-      <c r="I786" t="s">
+      <c r="I789" t="s">
         <v>1198</v>
       </c>
-      <c r="J786" t="s">
+      <c r="J789" t="s">
         <v>1201</v>
       </c>
-      <c r="K786" t="s">
+      <c r="K789" t="s">
         <v>1200</v>
       </c>
-      <c r="L786" t="str">
+      <c r="L789" t="str">
         <f t="shared" si="112"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0240_Nechbet/0030_nxb.t_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="787" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A787" t="s">
-        <v>60</v>
-      </c>
-      <c r="B787" s="27">
+    <row r="790" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A790" t="s">
+        <v>60</v>
+      </c>
+      <c r="B790" s="27">
         <v>240</v>
       </c>
-      <c r="C787" t="s">
+      <c r="C790" t="s">
         <v>106</v>
       </c>
-      <c r="E787" t="s">
+      <c r="E790" t="s">
         <v>1248</v>
       </c>
-      <c r="F787" t="s">
+      <c r="F790" t="s">
         <v>111</v>
       </c>
-      <c r="G787" t="s">
+      <c r="G790" t="s">
         <v>910</v>
       </c>
-      <c r="H787" t="s">
+      <c r="H790" t="s">
         <v>113</v>
       </c>
-      <c r="I787" t="s">
+      <c r="I790" t="s">
         <v>1198</v>
       </c>
-      <c r="J787" t="s">
+      <c r="J790" t="s">
         <v>1199</v>
       </c>
-      <c r="K787" t="s">
+      <c r="K790" t="s">
         <v>1200</v>
       </c>
-      <c r="L787" t="str">
+      <c r="L790" t="str">
         <f t="shared" si="112"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0240_Nechbet/det/0001_nxb.t_det_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="788" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A788" t="s">
-        <v>60</v>
-      </c>
-      <c r="B788" s="27">
+    <row r="791" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A791" t="s">
+        <v>60</v>
+      </c>
+      <c r="B791" s="27">
         <v>240</v>
       </c>
-      <c r="C788" t="s">
+      <c r="C791" t="s">
         <v>107</v>
       </c>
-      <c r="L788" t="s">
+      <c r="L791" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="789" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A789" t="s">
-        <v>60</v>
-      </c>
-      <c r="B789" s="27">
-        <v>240</v>
-      </c>
-      <c r="C789" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="792" spans="1:12" x14ac:dyDescent="0.2">
@@ -25907,64 +26052,10 @@
         <v>60</v>
       </c>
       <c r="B792" s="27">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C792" t="s">
-        <v>39</v>
-      </c>
-      <c r="L792" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="793" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A793" t="s">
-        <v>60</v>
-      </c>
-      <c r="B793" s="27">
-        <v>250</v>
-      </c>
-      <c r="C793" t="s">
-        <v>105</v>
-      </c>
-      <c r="E793" t="s">
-        <v>1249</v>
-      </c>
-      <c r="G793" t="s">
-        <v>911</v>
-      </c>
-      <c r="L793" t="str">
-        <f t="shared" ref="L793" si="113">_xlfn.TEXTJOIN("", TRUE, D793:J793)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0250_Re/0001_ra_01.png</v>
-      </c>
-    </row>
-    <row r="794" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A794" t="s">
-        <v>60</v>
-      </c>
-      <c r="B794" s="27">
-        <v>250</v>
-      </c>
-      <c r="C794" t="s">
-        <v>105</v>
-      </c>
-      <c r="E794" t="s">
-        <v>1249</v>
-      </c>
-      <c r="G794" t="s">
-        <v>912</v>
-      </c>
-      <c r="I794" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J794" t="s">
-        <v>1207</v>
-      </c>
-      <c r="K794" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L794" t="str">
-        <f t="shared" ref="L794:L800" si="114">_xlfn.TEXTJOIN("", TRUE, D794:K794)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0250_Re/0010_ra_SP_01.png &lt;sup&gt;(Sp.)&lt;/sup&gt;</v>
+        <v>108</v>
       </c>
     </row>
     <row r="795" spans="1:12" x14ac:dyDescent="0.2">
@@ -25975,213 +26066,267 @@
         <v>250</v>
       </c>
       <c r="C795" t="s">
-        <v>105</v>
-      </c>
-      <c r="E795" t="s">
+        <v>39</v>
+      </c>
+      <c r="L795" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="796" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A796" t="s">
+        <v>60</v>
+      </c>
+      <c r="B796" s="27">
+        <v>250</v>
+      </c>
+      <c r="C796" t="s">
+        <v>105</v>
+      </c>
+      <c r="E796" t="s">
         <v>1249</v>
       </c>
-      <c r="G795" t="s">
+      <c r="G796" t="s">
+        <v>911</v>
+      </c>
+      <c r="L796" t="str">
+        <f t="shared" ref="L796" si="113">_xlfn.TEXTJOIN("", TRUE, D796:J796)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0250_Re/0001_ra_01.png</v>
+      </c>
+    </row>
+    <row r="797" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A797" t="s">
+        <v>60</v>
+      </c>
+      <c r="B797" s="27">
+        <v>250</v>
+      </c>
+      <c r="C797" t="s">
+        <v>105</v>
+      </c>
+      <c r="E797" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G797" t="s">
+        <v>912</v>
+      </c>
+      <c r="I797" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J797" t="s">
+        <v>1207</v>
+      </c>
+      <c r="K797" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L797" t="str">
+        <f t="shared" ref="L797:L803" si="114">_xlfn.TEXTJOIN("", TRUE, D797:K797)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0250_Re/0010_ra_SP_01.png &lt;sup&gt;(Sp.)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="798" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A798" t="s">
+        <v>60</v>
+      </c>
+      <c r="B798" s="27">
+        <v>250</v>
+      </c>
+      <c r="C798" t="s">
+        <v>105</v>
+      </c>
+      <c r="E798" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G798" t="s">
         <v>913</v>
       </c>
-      <c r="I795" t="s">
+      <c r="I798" t="s">
         <v>1198</v>
       </c>
-      <c r="J795" t="s">
+      <c r="J798" t="s">
         <v>1201</v>
       </c>
-      <c r="K795" t="s">
+      <c r="K798" t="s">
         <v>1200</v>
       </c>
-      <c r="L795" t="str">
+      <c r="L798" t="str">
         <f t="shared" si="114"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0250_Re/0020_ra_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="796" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A796" t="s">
-        <v>60</v>
-      </c>
-      <c r="B796" s="27">
+    <row r="799" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A799" t="s">
+        <v>60</v>
+      </c>
+      <c r="B799" s="27">
         <v>250</v>
       </c>
-      <c r="C796" t="s">
-        <v>105</v>
-      </c>
-      <c r="E796" t="s">
+      <c r="C799" t="s">
+        <v>105</v>
+      </c>
+      <c r="E799" t="s">
         <v>1249</v>
       </c>
-      <c r="G796" t="s">
+      <c r="G799" t="s">
         <v>914</v>
       </c>
-      <c r="I796" t="s">
+      <c r="I799" t="s">
         <v>1198</v>
       </c>
-      <c r="J796" t="s">
+      <c r="J799" t="s">
         <v>1201</v>
       </c>
-      <c r="K796" t="s">
+      <c r="K799" t="s">
         <v>1200</v>
       </c>
-      <c r="L796" t="str">
+      <c r="L799" t="str">
         <f t="shared" si="114"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0250_Re/0030_ra_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="797" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A797" t="s">
-        <v>60</v>
-      </c>
-      <c r="B797" s="27">
+    <row r="800" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A800" t="s">
+        <v>60</v>
+      </c>
+      <c r="B800" s="27">
         <v>250</v>
       </c>
-      <c r="C797" t="s">
+      <c r="C800" t="s">
         <v>106</v>
       </c>
-      <c r="E797" t="s">
+      <c r="E800" t="s">
         <v>1249</v>
       </c>
-      <c r="F797" t="s">
+      <c r="F800" t="s">
         <v>111</v>
       </c>
-      <c r="G797" t="s">
+      <c r="G800" t="s">
         <v>915</v>
       </c>
-      <c r="I797" t="s">
+      <c r="I800" t="s">
         <v>1198</v>
       </c>
-      <c r="J797" t="s">
+      <c r="J800" t="s">
         <v>1199</v>
       </c>
-      <c r="K797" t="s">
+      <c r="K800" t="s">
         <v>1200</v>
       </c>
-      <c r="L797" t="str">
+      <c r="L800" t="str">
         <f t="shared" si="114"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0250_Re/det/0001_ra_det_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="798" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A798" t="s">
-        <v>60</v>
-      </c>
-      <c r="B798" s="27">
+    <row r="801" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A801" t="s">
+        <v>60</v>
+      </c>
+      <c r="B801" s="27">
         <v>250</v>
       </c>
-      <c r="C798" t="s">
+      <c r="C801" t="s">
         <v>106</v>
       </c>
-      <c r="E798" t="s">
+      <c r="E801" t="s">
         <v>1249</v>
       </c>
-      <c r="F798" t="s">
+      <c r="F801" t="s">
         <v>111</v>
       </c>
-      <c r="G798" t="s">
+      <c r="G801" t="s">
         <v>916</v>
       </c>
-      <c r="I798" t="s">
+      <c r="I801" t="s">
         <v>1198</v>
       </c>
-      <c r="J798" t="s">
+      <c r="J801" t="s">
         <v>1202</v>
       </c>
-      <c r="K798" t="s">
+      <c r="K801" t="s">
         <v>1200</v>
       </c>
-      <c r="L798" t="str">
+      <c r="L801" t="str">
         <f t="shared" si="114"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0250_Re/det/0010_ra_det_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="799" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A799" t="s">
-        <v>60</v>
-      </c>
-      <c r="B799" s="27">
+    <row r="802" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A802" t="s">
+        <v>60</v>
+      </c>
+      <c r="B802" s="27">
         <v>250</v>
       </c>
-      <c r="C799" t="s">
+      <c r="C802" t="s">
         <v>106</v>
       </c>
-      <c r="E799" t="s">
+      <c r="E802" t="s">
         <v>1249</v>
       </c>
-      <c r="F799" t="s">
+      <c r="F802" t="s">
         <v>111</v>
       </c>
-      <c r="G799" t="s">
+      <c r="G802" t="s">
         <v>917</v>
       </c>
-      <c r="I799" t="s">
+      <c r="I802" t="s">
         <v>1198</v>
       </c>
-      <c r="J799" t="s">
+      <c r="J802" t="s">
         <v>1153</v>
       </c>
-      <c r="K799" t="s">
+      <c r="K802" t="s">
         <v>1200</v>
       </c>
-      <c r="L799" t="str">
+      <c r="L802" t="str">
         <f t="shared" si="114"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0250_Re/det/0020_ra_det_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="800" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A800" t="s">
-        <v>60</v>
-      </c>
-      <c r="B800" s="27">
+    <row r="803" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A803" t="s">
+        <v>60</v>
+      </c>
+      <c r="B803" s="27">
         <v>250</v>
       </c>
-      <c r="C800" t="s">
+      <c r="C803" t="s">
         <v>106</v>
       </c>
-      <c r="E800" t="s">
+      <c r="E803" t="s">
         <v>1249</v>
       </c>
-      <c r="F800" t="s">
+      <c r="F803" t="s">
         <v>111</v>
       </c>
-      <c r="G800" t="s">
+      <c r="G803" t="s">
         <v>918</v>
       </c>
-      <c r="I800" t="s">
+      <c r="I803" t="s">
         <v>1198</v>
       </c>
-      <c r="J800" t="s">
+      <c r="J803" t="s">
         <v>1153</v>
       </c>
-      <c r="K800" t="s">
+      <c r="K803" t="s">
         <v>1200</v>
       </c>
-      <c r="L800" t="str">
+      <c r="L803" t="str">
         <f t="shared" si="114"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0250_Re/det/0030_ra_det_NR_02.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="801" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A801" t="s">
-        <v>60</v>
-      </c>
-      <c r="B801" s="27">
+    <row r="804" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A804" t="s">
+        <v>60</v>
+      </c>
+      <c r="B804" s="27">
         <v>250</v>
       </c>
-      <c r="C801" t="s">
+      <c r="C804" t="s">
         <v>107</v>
       </c>
-      <c r="L801" t="s">
+      <c r="L804" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="802" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A802" t="s">
-        <v>60</v>
-      </c>
-      <c r="B802" s="27">
-        <v>250</v>
-      </c>
-      <c r="C802" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="805" spans="1:12" x14ac:dyDescent="0.2">
@@ -26189,46 +26334,10 @@
         <v>60</v>
       </c>
       <c r="B805" s="27">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C805" t="s">
-        <v>39</v>
-      </c>
-      <c r="L805" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="806" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A806" t="s">
-        <v>60</v>
-      </c>
-      <c r="B806" s="27">
-        <v>260</v>
-      </c>
-      <c r="C806" t="s">
-        <v>105</v>
-      </c>
-      <c r="E806" t="s">
-        <v>1250</v>
-      </c>
-      <c r="L806" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D806:J806)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0260_Re-Harachte/</v>
-      </c>
-    </row>
-    <row r="807" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A807" t="s">
-        <v>60</v>
-      </c>
-      <c r="B807" s="27">
-        <v>260</v>
-      </c>
-      <c r="C807" t="s">
-        <v>106</v>
-      </c>
-      <c r="L807" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D807:J807)</f>
-        <v/>
+        <v>108</v>
       </c>
     </row>
     <row r="808" spans="1:12" x14ac:dyDescent="0.2">
@@ -26239,10 +26348,10 @@
         <v>260</v>
       </c>
       <c r="C808" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="L808" t="s">
-        <v>151</v>
+        <v>714</v>
       </c>
     </row>
     <row r="809" spans="1:12" x14ac:dyDescent="0.2">
@@ -26253,7 +26362,43 @@
         <v>260</v>
       </c>
       <c r="C809" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="E809" t="s">
+        <v>1250</v>
+      </c>
+      <c r="L809" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D809:J809)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0260_Re-Harachte/</v>
+      </c>
+    </row>
+    <row r="810" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A810" t="s">
+        <v>60</v>
+      </c>
+      <c r="B810" s="27">
+        <v>260</v>
+      </c>
+      <c r="C810" t="s">
+        <v>106</v>
+      </c>
+      <c r="L810" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D810:J810)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="811" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A811" t="s">
+        <v>60</v>
+      </c>
+      <c r="B811" s="27">
+        <v>260</v>
+      </c>
+      <c r="C811" t="s">
+        <v>107</v>
+      </c>
+      <c r="L811" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="812" spans="1:12" x14ac:dyDescent="0.2">
@@ -26261,64 +26406,10 @@
         <v>60</v>
       </c>
       <c r="B812" s="27">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C812" t="s">
-        <v>39</v>
-      </c>
-      <c r="L812" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="813" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A813" t="s">
-        <v>60</v>
-      </c>
-      <c r="B813" s="27">
-        <v>270</v>
-      </c>
-      <c r="C813" t="s">
-        <v>105</v>
-      </c>
-      <c r="E813" t="s">
-        <v>1251</v>
-      </c>
-      <c r="G813" t="s">
-        <v>919</v>
-      </c>
-      <c r="L813" t="str">
-        <f t="shared" ref="L813:L819" si="115">_xlfn.TEXTJOIN("", TRUE, D813:J813)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0270_Renenutet/0001_rnnwt.t_01.png</v>
-      </c>
-    </row>
-    <row r="814" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A814" t="s">
-        <v>60</v>
-      </c>
-      <c r="B814" s="27">
-        <v>270</v>
-      </c>
-      <c r="C814" t="s">
-        <v>105</v>
-      </c>
-      <c r="E814" t="s">
-        <v>1251</v>
-      </c>
-      <c r="G814" t="s">
-        <v>920</v>
-      </c>
-      <c r="I814" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J814" t="s">
-        <v>1199</v>
-      </c>
-      <c r="K814" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L814" t="str">
-        <f t="shared" ref="L814:L818" si="116">_xlfn.TEXTJOIN("", TRUE, D814:K814)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0270_Renenutet/0010_rnnwt.t_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <v>108</v>
       </c>
     </row>
     <row r="815" spans="1:12" x14ac:dyDescent="0.2">
@@ -26329,156 +26420,210 @@
         <v>270</v>
       </c>
       <c r="C815" t="s">
-        <v>105</v>
-      </c>
-      <c r="E815" t="s">
+        <v>39</v>
+      </c>
+      <c r="L815" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="816" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A816" t="s">
+        <v>60</v>
+      </c>
+      <c r="B816" s="27">
+        <v>270</v>
+      </c>
+      <c r="C816" t="s">
+        <v>105</v>
+      </c>
+      <c r="E816" t="s">
         <v>1251</v>
       </c>
-      <c r="G815" t="s">
+      <c r="G816" t="s">
+        <v>919</v>
+      </c>
+      <c r="L816" t="str">
+        <f t="shared" ref="L816:L822" si="115">_xlfn.TEXTJOIN("", TRUE, D816:J816)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0270_Renenutet/0001_rnnwt.t_01.png</v>
+      </c>
+    </row>
+    <row r="817" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A817" t="s">
+        <v>60</v>
+      </c>
+      <c r="B817" s="27">
+        <v>270</v>
+      </c>
+      <c r="C817" t="s">
+        <v>105</v>
+      </c>
+      <c r="E817" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G817" t="s">
+        <v>920</v>
+      </c>
+      <c r="I817" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J817" t="s">
+        <v>1199</v>
+      </c>
+      <c r="K817" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L817" t="str">
+        <f t="shared" ref="L817:L821" si="116">_xlfn.TEXTJOIN("", TRUE, D817:K817)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0270_Renenutet/0010_rnnwt.t_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="818" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A818" t="s">
+        <v>60</v>
+      </c>
+      <c r="B818" s="27">
+        <v>270</v>
+      </c>
+      <c r="C818" t="s">
+        <v>105</v>
+      </c>
+      <c r="E818" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G818" t="s">
         <v>921</v>
       </c>
-      <c r="I815" t="s">
+      <c r="I818" t="s">
         <v>1198</v>
       </c>
-      <c r="J815" t="s">
+      <c r="J818" t="s">
         <v>1199</v>
       </c>
-      <c r="K815" t="s">
+      <c r="K818" t="s">
         <v>1200</v>
       </c>
-      <c r="L815" t="str">
+      <c r="L818" t="str">
         <f t="shared" si="116"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0270_Renenutet/0020_rnnwt.t_AR_02.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="816" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A816" t="s">
-        <v>60</v>
-      </c>
-      <c r="B816" s="27">
+    <row r="819" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A819" t="s">
+        <v>60</v>
+      </c>
+      <c r="B819" s="27">
         <v>270</v>
       </c>
-      <c r="C816" t="s">
-        <v>105</v>
-      </c>
-      <c r="E816" t="s">
+      <c r="C819" t="s">
+        <v>105</v>
+      </c>
+      <c r="E819" t="s">
         <v>1251</v>
       </c>
-      <c r="G816" t="s">
+      <c r="G819" t="s">
         <v>922</v>
       </c>
-      <c r="I816" t="s">
+      <c r="I819" t="s">
         <v>1198</v>
       </c>
-      <c r="J816" t="s">
+      <c r="J819" t="s">
         <v>1206</v>
       </c>
-      <c r="K816" t="s">
+      <c r="K819" t="s">
         <v>1200</v>
       </c>
-      <c r="L816" t="str">
+      <c r="L819" t="str">
         <f t="shared" si="116"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0270_Renenutet/0030_rnnwt.t_D.18_01.png &lt;sup&gt;(D.18)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="817" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A817" t="s">
-        <v>60</v>
-      </c>
-      <c r="B817" s="27">
+    <row r="820" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A820" t="s">
+        <v>60</v>
+      </c>
+      <c r="B820" s="27">
         <v>270</v>
       </c>
-      <c r="C817" t="s">
-        <v>105</v>
-      </c>
-      <c r="E817" t="s">
+      <c r="C820" t="s">
+        <v>105</v>
+      </c>
+      <c r="E820" t="s">
         <v>1251</v>
       </c>
-      <c r="G817" t="s">
+      <c r="G820" t="s">
         <v>923</v>
       </c>
-      <c r="I817" t="s">
+      <c r="I820" t="s">
         <v>1198</v>
       </c>
-      <c r="J817" t="s">
+      <c r="J820" t="s">
         <v>1206</v>
       </c>
-      <c r="K817" t="s">
+      <c r="K820" t="s">
         <v>1200</v>
       </c>
-      <c r="L817" t="str">
+      <c r="L820" t="str">
         <f t="shared" si="116"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0270_Renenutet/0040_rnnwt.t_D.18_02.png &lt;sup&gt;(D.18)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="818" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A818" t="s">
-        <v>60</v>
-      </c>
-      <c r="B818" s="27">
+    <row r="821" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A821" t="s">
+        <v>60</v>
+      </c>
+      <c r="B821" s="27">
         <v>270</v>
       </c>
-      <c r="C818" t="s">
-        <v>105</v>
-      </c>
-      <c r="E818" t="s">
+      <c r="C821" t="s">
+        <v>105</v>
+      </c>
+      <c r="E821" t="s">
         <v>1251</v>
       </c>
-      <c r="G818" t="s">
+      <c r="G821" t="s">
         <v>924</v>
       </c>
-      <c r="I818" t="s">
+      <c r="I821" t="s">
         <v>1198</v>
       </c>
-      <c r="J818" t="s">
+      <c r="J821" t="s">
         <v>1206</v>
       </c>
-      <c r="K818" t="s">
+      <c r="K821" t="s">
         <v>1200</v>
       </c>
-      <c r="L818" t="str">
+      <c r="L821" t="str">
         <f t="shared" si="116"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0270_Renenutet/0050_rnnwt.t_D.18_03.png &lt;sup&gt;(D.18)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="819" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A819" t="s">
-        <v>60</v>
-      </c>
-      <c r="B819" s="27">
+    <row r="822" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A822" t="s">
+        <v>60</v>
+      </c>
+      <c r="B822" s="27">
         <v>270</v>
       </c>
-      <c r="C819" t="s">
+      <c r="C822" t="s">
         <v>106</v>
       </c>
-      <c r="L819" t="str">
+      <c r="L822" t="str">
         <f t="shared" si="115"/>
         <v/>
       </c>
     </row>
-    <row r="820" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A820" t="s">
-        <v>60</v>
-      </c>
-      <c r="B820" s="27">
+    <row r="823" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A823" t="s">
+        <v>60</v>
+      </c>
+      <c r="B823" s="27">
         <v>270</v>
       </c>
-      <c r="C820" t="s">
+      <c r="C823" t="s">
         <v>107</v>
       </c>
-      <c r="L820" t="s">
+      <c r="L823" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="821" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A821" t="s">
-        <v>60</v>
-      </c>
-      <c r="B821" s="27">
-        <v>270</v>
-      </c>
-      <c r="C821" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="824" spans="1:12" x14ac:dyDescent="0.2">
@@ -26486,446 +26631,446 @@
         <v>60</v>
       </c>
       <c r="B824" s="27">
+        <v>270</v>
+      </c>
+      <c r="C824" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="827" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A827" t="s">
+        <v>60</v>
+      </c>
+      <c r="B827" s="27">
         <v>280</v>
       </c>
-      <c r="C824" t="s">
+      <c r="C827" t="s">
         <v>39</v>
       </c>
-      <c r="L824" t="s">
+      <c r="L827" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="825" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A825" t="s">
-        <v>60</v>
-      </c>
-      <c r="B825" s="27">
+    <row r="828" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A828" t="s">
+        <v>60</v>
+      </c>
+      <c r="B828" s="27">
         <v>280</v>
       </c>
-      <c r="C825" t="s">
-        <v>105</v>
-      </c>
-      <c r="E825" t="s">
+      <c r="C828" t="s">
+        <v>105</v>
+      </c>
+      <c r="E828" t="s">
         <v>1252</v>
       </c>
-      <c r="G825" t="s">
+      <c r="G828" t="s">
         <v>925</v>
       </c>
-      <c r="I825" t="s">
+      <c r="I828" t="s">
         <v>1198</v>
       </c>
-      <c r="J825" t="s">
+      <c r="J828" t="s">
         <v>1199</v>
       </c>
-      <c r="K825" t="s">
+      <c r="K828" t="s">
         <v>1200</v>
       </c>
-      <c r="L825" t="str">
-        <f t="shared" ref="L825:L836" si="117">_xlfn.TEXTJOIN("", TRUE, D825:K825)</f>
+      <c r="L828" t="str">
+        <f t="shared" ref="L828:L839" si="117">_xlfn.TEXTJOIN("", TRUE, D828:K828)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0280_Hapi-Nilgott/0001_Hapj_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="826" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A826" t="s">
-        <v>60</v>
-      </c>
-      <c r="B826" s="27">
+    <row r="829" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A829" t="s">
+        <v>60</v>
+      </c>
+      <c r="B829" s="27">
         <v>280</v>
       </c>
-      <c r="C826" t="s">
-        <v>105</v>
-      </c>
-      <c r="E826" t="s">
+      <c r="C829" t="s">
+        <v>105</v>
+      </c>
+      <c r="E829" t="s">
         <v>1252</v>
       </c>
-      <c r="G826" t="s">
+      <c r="G829" t="s">
         <v>926</v>
       </c>
-      <c r="I826" t="s">
+      <c r="I829" t="s">
         <v>1198</v>
       </c>
-      <c r="J826" t="s">
+      <c r="J829" t="s">
         <v>1202</v>
       </c>
-      <c r="K826" t="s">
+      <c r="K829" t="s">
         <v>1200</v>
       </c>
-      <c r="L826" t="str">
+      <c r="L829" t="str">
         <f t="shared" si="117"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0280_Hapi-Nilgott/0010_Hapj_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="827" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A827" t="s">
-        <v>60</v>
-      </c>
-      <c r="B827" s="27">
+    <row r="830" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A830" t="s">
+        <v>60</v>
+      </c>
+      <c r="B830" s="27">
         <v>280</v>
       </c>
-      <c r="C827" t="s">
-        <v>105</v>
-      </c>
-      <c r="E827" t="s">
+      <c r="C830" t="s">
+        <v>105</v>
+      </c>
+      <c r="E830" t="s">
         <v>1252</v>
       </c>
-      <c r="G827" t="s">
+      <c r="G830" t="s">
         <v>927</v>
       </c>
-      <c r="I827" t="s">
+      <c r="I830" t="s">
         <v>1198</v>
       </c>
-      <c r="J827" t="s">
+      <c r="J830" t="s">
         <v>1202</v>
       </c>
-      <c r="K827" t="s">
+      <c r="K830" t="s">
         <v>1200</v>
       </c>
-      <c r="L827" t="str">
+      <c r="L830" t="str">
         <f t="shared" si="117"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0280_Hapi-Nilgott/0020_Hapj_MR_02.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="828" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A828" t="s">
-        <v>60</v>
-      </c>
-      <c r="B828" s="27">
+    <row r="831" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A831" t="s">
+        <v>60</v>
+      </c>
+      <c r="B831" s="27">
         <v>280</v>
       </c>
-      <c r="C828" t="s">
-        <v>105</v>
-      </c>
-      <c r="E828" t="s">
+      <c r="C831" t="s">
+        <v>105</v>
+      </c>
+      <c r="E831" t="s">
         <v>1252</v>
       </c>
-      <c r="G828" t="s">
+      <c r="G831" t="s">
         <v>928</v>
       </c>
-      <c r="I828" t="s">
+      <c r="I831" t="s">
         <v>1198</v>
       </c>
-      <c r="J828" t="s">
+      <c r="J831" t="s">
         <v>1202</v>
       </c>
-      <c r="K828" t="s">
+      <c r="K831" t="s">
         <v>1200</v>
       </c>
-      <c r="L828" t="str">
+      <c r="L831" t="str">
         <f t="shared" si="117"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0280_Hapi-Nilgott/0030_Hapj_MR_03.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="829" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A829" t="s">
-        <v>60</v>
-      </c>
-      <c r="B829" s="27">
+    <row r="832" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A832" t="s">
+        <v>60</v>
+      </c>
+      <c r="B832" s="27">
         <v>280</v>
       </c>
-      <c r="C829" t="s">
-        <v>105</v>
-      </c>
-      <c r="E829" t="s">
+      <c r="C832" t="s">
+        <v>105</v>
+      </c>
+      <c r="E832" t="s">
         <v>1252</v>
       </c>
-      <c r="G829" t="s">
+      <c r="G832" t="s">
         <v>929</v>
       </c>
-      <c r="I829" t="s">
+      <c r="I832" t="s">
         <v>1198</v>
       </c>
-      <c r="J829" t="s">
+      <c r="J832" t="s">
         <v>1202</v>
       </c>
-      <c r="K829" t="s">
+      <c r="K832" t="s">
         <v>1200</v>
       </c>
-      <c r="L829" t="str">
+      <c r="L832" t="str">
         <f t="shared" si="117"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0280_Hapi-Nilgott/0040_Hapj_MR_04.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="830" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A830" t="s">
-        <v>60</v>
-      </c>
-      <c r="B830" s="27">
+    <row r="833" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A833" t="s">
+        <v>60</v>
+      </c>
+      <c r="B833" s="27">
         <v>280</v>
       </c>
-      <c r="C830" t="s">
-        <v>105</v>
-      </c>
-      <c r="E830" t="s">
+      <c r="C833" t="s">
+        <v>105</v>
+      </c>
+      <c r="E833" t="s">
         <v>1252</v>
       </c>
-      <c r="G830" t="s">
+      <c r="G833" t="s">
         <v>930</v>
       </c>
-      <c r="I830" t="s">
+      <c r="I833" t="s">
         <v>1198</v>
       </c>
-      <c r="J830" t="s">
+      <c r="J833" t="s">
         <v>1202</v>
       </c>
-      <c r="K830" t="s">
+      <c r="K833" t="s">
         <v>1200</v>
       </c>
-      <c r="L830" t="str">
+      <c r="L833" t="str">
         <f t="shared" si="117"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0280_Hapi-Nilgott/0050_Hapj_MR_05.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="831" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A831" t="s">
-        <v>60</v>
-      </c>
-      <c r="B831" s="27">
+    <row r="834" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A834" t="s">
+        <v>60</v>
+      </c>
+      <c r="B834" s="27">
         <v>280</v>
       </c>
-      <c r="C831" t="s">
-        <v>105</v>
-      </c>
-      <c r="E831" t="s">
+      <c r="C834" t="s">
+        <v>105</v>
+      </c>
+      <c r="E834" t="s">
         <v>1252</v>
       </c>
-      <c r="G831" t="s">
+      <c r="G834" t="s">
         <v>931</v>
       </c>
-      <c r="I831" t="s">
+      <c r="I834" t="s">
         <v>1198</v>
       </c>
-      <c r="J831" t="s">
+      <c r="J834" t="s">
         <v>1202</v>
       </c>
-      <c r="K831" t="s">
+      <c r="K834" t="s">
         <v>1200</v>
       </c>
-      <c r="L831" t="str">
+      <c r="L834" t="str">
         <f t="shared" si="117"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0280_Hapi-Nilgott/0060_Hapj_MR_06.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="832" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A832" t="s">
-        <v>60</v>
-      </c>
-      <c r="B832" s="27">
+    <row r="835" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A835" t="s">
+        <v>60</v>
+      </c>
+      <c r="B835" s="27">
         <v>280</v>
       </c>
-      <c r="C832" t="s">
-        <v>105</v>
-      </c>
-      <c r="E832" t="s">
+      <c r="C835" t="s">
+        <v>105</v>
+      </c>
+      <c r="E835" t="s">
         <v>1252</v>
       </c>
-      <c r="G832" t="s">
+      <c r="G835" t="s">
         <v>932</v>
       </c>
-      <c r="I832" t="s">
+      <c r="I835" t="s">
         <v>1198</v>
       </c>
-      <c r="J832" t="s">
+      <c r="J835" t="s">
         <v>1209</v>
       </c>
-      <c r="K832" t="s">
+      <c r="K835" t="s">
         <v>1200</v>
       </c>
-      <c r="L832" t="str">
+      <c r="L835" t="str">
         <f t="shared" si="117"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0280_Hapi-Nilgott/0070_Hapj_Sait._01.png &lt;sup&gt;(Saït.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="833" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A833" t="s">
-        <v>60</v>
-      </c>
-      <c r="B833" s="27">
+    <row r="836" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A836" t="s">
+        <v>60</v>
+      </c>
+      <c r="B836" s="27">
         <v>280</v>
       </c>
-      <c r="C833" t="s">
-        <v>105</v>
-      </c>
-      <c r="E833" t="s">
+      <c r="C836" t="s">
+        <v>105</v>
+      </c>
+      <c r="E836" t="s">
         <v>1252</v>
       </c>
-      <c r="G833" t="s">
+      <c r="G836" t="s">
         <v>933</v>
       </c>
-      <c r="I833" t="s">
+      <c r="I836" t="s">
         <v>1198</v>
       </c>
-      <c r="J833" t="s">
+      <c r="J836" t="s">
         <v>1209</v>
       </c>
-      <c r="K833" t="s">
+      <c r="K836" t="s">
         <v>1200</v>
       </c>
-      <c r="L833" t="str">
+      <c r="L836" t="str">
         <f t="shared" si="117"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0280_Hapi-Nilgott/0080_Hapj_Sait._02.png &lt;sup&gt;(Saït.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="834" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A834" t="s">
-        <v>60</v>
-      </c>
-      <c r="B834" s="27">
+    <row r="837" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A837" t="s">
+        <v>60</v>
+      </c>
+      <c r="B837" s="27">
         <v>280</v>
       </c>
-      <c r="C834" t="s">
-        <v>105</v>
-      </c>
-      <c r="E834" t="s">
+      <c r="C837" t="s">
+        <v>105</v>
+      </c>
+      <c r="E837" t="s">
         <v>1252</v>
       </c>
-      <c r="G834" t="s">
+      <c r="G837" t="s">
         <v>936</v>
       </c>
-      <c r="I834" t="s">
+      <c r="I837" t="s">
         <v>1198</v>
       </c>
-      <c r="J834" t="s">
+      <c r="J837" t="s">
         <v>1210</v>
       </c>
-      <c r="K834" t="s">
+      <c r="K837" t="s">
         <v>1200</v>
       </c>
-      <c r="L834" t="str">
+      <c r="L837" t="str">
         <f t="shared" si="117"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0280_Hapi-Nilgott/0090_Hapj_SP-GR_01.png &lt;sup&gt;(Sp.–Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="835" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A835" t="s">
-        <v>60</v>
-      </c>
-      <c r="B835" s="27">
+    <row r="838" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A838" t="s">
+        <v>60</v>
+      </c>
+      <c r="B838" s="27">
         <v>280</v>
       </c>
-      <c r="C835" t="s">
-        <v>105</v>
-      </c>
-      <c r="E835" t="s">
+      <c r="C838" t="s">
+        <v>105</v>
+      </c>
+      <c r="E838" t="s">
         <v>1252</v>
       </c>
-      <c r="G835" t="s">
+      <c r="G838" t="s">
         <v>937</v>
       </c>
-      <c r="I835" t="s">
+      <c r="I838" t="s">
         <v>1198</v>
       </c>
-      <c r="J835" t="s">
+      <c r="J838" t="s">
         <v>1210</v>
       </c>
-      <c r="K835" t="s">
+      <c r="K838" t="s">
         <v>1200</v>
       </c>
-      <c r="L835" t="str">
+      <c r="L838" t="str">
         <f t="shared" si="117"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0280_Hapi-Nilgott/0100_Hapj_SP-GR_02.png &lt;sup&gt;(Sp.–Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="836" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A836" t="s">
-        <v>60</v>
-      </c>
-      <c r="B836" s="27">
+    <row r="839" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A839" t="s">
+        <v>60</v>
+      </c>
+      <c r="B839" s="27">
         <v>280</v>
       </c>
-      <c r="C836" t="s">
-        <v>105</v>
-      </c>
-      <c r="E836" t="s">
+      <c r="C839" t="s">
+        <v>105</v>
+      </c>
+      <c r="E839" t="s">
         <v>1252</v>
       </c>
-      <c r="G836" t="s">
+      <c r="G839" t="s">
         <v>938</v>
       </c>
-      <c r="I836" t="s">
+      <c r="I839" t="s">
         <v>1198</v>
       </c>
-      <c r="J836" t="s">
+      <c r="J839" t="s">
         <v>1210</v>
       </c>
-      <c r="K836" t="s">
+      <c r="K839" t="s">
         <v>1200</v>
       </c>
-      <c r="L836" t="str">
+      <c r="L839" t="str">
         <f t="shared" si="117"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0280_Hapi-Nilgott/0110_Hapj_SP-GR_03.png &lt;sup&gt;(Sp.–Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="837" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A837" t="s">
-        <v>60</v>
-      </c>
-      <c r="B837" s="27">
+    <row r="840" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A840" t="s">
+        <v>60</v>
+      </c>
+      <c r="B840" s="27">
         <v>280</v>
       </c>
-      <c r="C837" t="s">
+      <c r="C840" t="s">
         <v>106</v>
       </c>
-      <c r="E837" t="s">
+      <c r="E840" t="s">
         <v>1252</v>
       </c>
-      <c r="F837" t="s">
+      <c r="F840" t="s">
         <v>111</v>
       </c>
-      <c r="G837" t="s">
+      <c r="G840" t="s">
         <v>934</v>
       </c>
-      <c r="L837" t="str">
-        <f t="shared" ref="L837:L838" si="118">_xlfn.TEXTJOIN("", TRUE, D837:J837)</f>
+      <c r="L840" t="str">
+        <f t="shared" ref="L840:L841" si="118">_xlfn.TEXTJOIN("", TRUE, D840:J840)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0280_Hapi-Nilgott/det/0001_Hapj_det_01.png</v>
       </c>
     </row>
-    <row r="838" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A838" t="s">
-        <v>60</v>
-      </c>
-      <c r="B838" s="27">
+    <row r="841" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A841" t="s">
+        <v>60</v>
+      </c>
+      <c r="B841" s="27">
         <v>280</v>
       </c>
-      <c r="C838" t="s">
+      <c r="C841" t="s">
         <v>106</v>
       </c>
-      <c r="E838" t="s">
+      <c r="E841" t="s">
         <v>1252</v>
       </c>
-      <c r="F838" t="s">
+      <c r="F841" t="s">
         <v>111</v>
       </c>
-      <c r="G838" t="s">
+      <c r="G841" t="s">
         <v>935</v>
       </c>
-      <c r="L838" t="str">
+      <c r="L841" t="str">
         <f t="shared" si="118"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0280_Hapi-Nilgott/det/0010_Hapj_det_02.png</v>
       </c>
     </row>
-    <row r="839" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A839" t="s">
-        <v>60</v>
-      </c>
-      <c r="B839" s="27">
+    <row r="842" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A842" t="s">
+        <v>60</v>
+      </c>
+      <c r="B842" s="27">
         <v>280</v>
       </c>
-      <c r="C839" t="s">
+      <c r="C842" t="s">
         <v>107</v>
       </c>
-      <c r="L839" t="s">
+      <c r="L842" t="s">
         <v>153</v>
-      </c>
-    </row>
-    <row r="840" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A840" t="s">
-        <v>60</v>
-      </c>
-      <c r="B840" s="27">
-        <v>280</v>
-      </c>
-      <c r="C840" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="843" spans="1:12" x14ac:dyDescent="0.2">
@@ -26933,64 +27078,10 @@
         <v>60</v>
       </c>
       <c r="B843" s="27">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C843" t="s">
-        <v>39</v>
-      </c>
-      <c r="L843" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="844" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A844" t="s">
-        <v>60</v>
-      </c>
-      <c r="B844" s="27">
-        <v>290</v>
-      </c>
-      <c r="C844" t="s">
-        <v>105</v>
-      </c>
-      <c r="E844" t="s">
-        <v>1253</v>
-      </c>
-      <c r="G844" t="s">
-        <v>939</v>
-      </c>
-      <c r="L844" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D844:J844)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0290_Hathor/0001_Hwt-Hr_01.png</v>
-      </c>
-    </row>
-    <row r="845" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A845" t="s">
-        <v>60</v>
-      </c>
-      <c r="B845" s="27">
-        <v>290</v>
-      </c>
-      <c r="C845" t="s">
-        <v>105</v>
-      </c>
-      <c r="E845" t="s">
-        <v>1253</v>
-      </c>
-      <c r="G845" t="s">
-        <v>940</v>
-      </c>
-      <c r="I845" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J845" t="s">
-        <v>1199</v>
-      </c>
-      <c r="K845" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L845" t="str">
-        <f t="shared" ref="L845:L846" si="119">_xlfn.TEXTJOIN("", TRUE, D845:K845)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0290_Hathor/0010_Hwt-Hr_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <v>108</v>
       </c>
     </row>
     <row r="846" spans="1:12" x14ac:dyDescent="0.2">
@@ -27001,66 +27092,120 @@
         <v>290</v>
       </c>
       <c r="C846" t="s">
-        <v>105</v>
-      </c>
-      <c r="E846" t="s">
+        <v>39</v>
+      </c>
+      <c r="L846" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="847" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A847" t="s">
+        <v>60</v>
+      </c>
+      <c r="B847" s="27">
+        <v>290</v>
+      </c>
+      <c r="C847" t="s">
+        <v>105</v>
+      </c>
+      <c r="E847" t="s">
         <v>1253</v>
       </c>
-      <c r="G846" t="s">
+      <c r="G847" t="s">
+        <v>939</v>
+      </c>
+      <c r="L847" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D847:J847)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0290_Hathor/0001_Hwt-Hr_01.png</v>
+      </c>
+    </row>
+    <row r="848" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A848" t="s">
+        <v>60</v>
+      </c>
+      <c r="B848" s="27">
+        <v>290</v>
+      </c>
+      <c r="C848" t="s">
+        <v>105</v>
+      </c>
+      <c r="E848" t="s">
+        <v>1253</v>
+      </c>
+      <c r="G848" t="s">
+        <v>940</v>
+      </c>
+      <c r="I848" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J848" t="s">
+        <v>1199</v>
+      </c>
+      <c r="K848" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L848" t="str">
+        <f t="shared" ref="L848:L849" si="119">_xlfn.TEXTJOIN("", TRUE, D848:K848)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0290_Hathor/0010_Hwt-Hr_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="849" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A849" t="s">
+        <v>60</v>
+      </c>
+      <c r="B849" s="27">
+        <v>290</v>
+      </c>
+      <c r="C849" t="s">
+        <v>105</v>
+      </c>
+      <c r="E849" t="s">
+        <v>1253</v>
+      </c>
+      <c r="G849" t="s">
         <v>941</v>
       </c>
-      <c r="I846" t="s">
+      <c r="I849" t="s">
         <v>1198</v>
       </c>
-      <c r="J846" t="s">
+      <c r="J849" t="s">
         <v>1199</v>
       </c>
-      <c r="K846" t="s">
+      <c r="K849" t="s">
         <v>1200</v>
       </c>
-      <c r="L846" t="str">
+      <c r="L849" t="str">
         <f t="shared" si="119"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0290_Hathor/0020_Hwt-Hr_AR_02.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="847" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A847" t="s">
-        <v>60</v>
-      </c>
-      <c r="B847" s="27">
+    <row r="850" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A850" t="s">
+        <v>60</v>
+      </c>
+      <c r="B850" s="27">
         <v>290</v>
       </c>
-      <c r="C847" t="s">
+      <c r="C850" t="s">
         <v>106</v>
       </c>
-      <c r="L847" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D847:J847)</f>
+      <c r="L850" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D850:J850)</f>
         <v/>
       </c>
     </row>
-    <row r="848" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A848" t="s">
-        <v>60</v>
-      </c>
-      <c r="B848" s="27">
+    <row r="851" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A851" t="s">
+        <v>60</v>
+      </c>
+      <c r="B851" s="27">
         <v>290</v>
       </c>
-      <c r="C848" t="s">
+      <c r="C851" t="s">
         <v>107</v>
       </c>
-      <c r="L848" t="s">
+      <c r="L851" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="849" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A849" t="s">
-        <v>60</v>
-      </c>
-      <c r="B849" s="27">
-        <v>290</v>
-      </c>
-      <c r="C849" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="852" spans="1:12" x14ac:dyDescent="0.2">
@@ -27068,549 +27213,549 @@
         <v>60</v>
       </c>
       <c r="B852" s="27">
+        <v>290</v>
+      </c>
+      <c r="C852" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="855" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A855" t="s">
+        <v>60</v>
+      </c>
+      <c r="B855" s="27">
         <v>300</v>
       </c>
-      <c r="C852" t="s">
+      <c r="C855" t="s">
         <v>39</v>
       </c>
-      <c r="L852" t="s">
+      <c r="L855" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="853" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A853" t="s">
-        <v>60</v>
-      </c>
-      <c r="B853" s="27">
+    <row r="856" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A856" t="s">
+        <v>60</v>
+      </c>
+      <c r="B856" s="27">
         <v>300</v>
       </c>
-      <c r="C853" t="s">
-        <v>105</v>
-      </c>
-      <c r="E853" t="s">
+      <c r="C856" t="s">
+        <v>105</v>
+      </c>
+      <c r="E856" t="s">
         <v>1254</v>
       </c>
-      <c r="G853" t="s">
+      <c r="G856" t="s">
         <v>942</v>
       </c>
-      <c r="L853" t="str">
-        <f t="shared" ref="L853:L858" si="120">_xlfn.TEXTJOIN("", TRUE, D853:J853)</f>
+      <c r="L856" t="str">
+        <f t="shared" ref="L856:L861" si="120">_xlfn.TEXTJOIN("", TRUE, D856:J856)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0300_Apis/0001_Hp_01.png</v>
       </c>
     </row>
-    <row r="854" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A854" t="s">
-        <v>60</v>
-      </c>
-      <c r="B854" s="27">
+    <row r="857" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A857" t="s">
+        <v>60</v>
+      </c>
+      <c r="B857" s="27">
         <v>300</v>
       </c>
-      <c r="C854" t="s">
-        <v>105</v>
-      </c>
-      <c r="E854" t="s">
+      <c r="C857" t="s">
+        <v>105</v>
+      </c>
+      <c r="E857" t="s">
         <v>1254</v>
       </c>
-      <c r="G854" t="s">
+      <c r="G857" t="s">
         <v>943</v>
       </c>
-      <c r="L854" t="str">
+      <c r="L857" t="str">
         <f t="shared" si="120"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0300_Apis/0010_Hp_02.png</v>
       </c>
     </row>
-    <row r="855" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A855" t="s">
-        <v>60</v>
-      </c>
-      <c r="B855" s="27">
+    <row r="858" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A858" t="s">
+        <v>60</v>
+      </c>
+      <c r="B858" s="27">
         <v>300</v>
       </c>
-      <c r="C855" t="s">
-        <v>105</v>
-      </c>
-      <c r="E855" t="s">
+      <c r="C858" t="s">
+        <v>105</v>
+      </c>
+      <c r="E858" t="s">
         <v>1254</v>
       </c>
-      <c r="G855" t="s">
+      <c r="G858" t="s">
         <v>944</v>
       </c>
-      <c r="I855" t="s">
+      <c r="I858" t="s">
         <v>1198</v>
       </c>
-      <c r="J855" t="s">
+      <c r="J858" t="s">
         <v>1199</v>
       </c>
-      <c r="K855" t="s">
+      <c r="K858" t="s">
         <v>1200</v>
       </c>
-      <c r="L855" t="str">
-        <f t="shared" ref="L855:L856" si="121">_xlfn.TEXTJOIN("", TRUE, D855:K855)</f>
+      <c r="L858" t="str">
+        <f t="shared" ref="L858:L859" si="121">_xlfn.TEXTJOIN("", TRUE, D858:K858)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0300_Apis/0020_Hp_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="856" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A856" t="s">
-        <v>60</v>
-      </c>
-      <c r="B856" s="27">
+    <row r="859" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A859" t="s">
+        <v>60</v>
+      </c>
+      <c r="B859" s="27">
         <v>300</v>
       </c>
-      <c r="C856" t="s">
-        <v>105</v>
-      </c>
-      <c r="E856" t="s">
+      <c r="C859" t="s">
+        <v>105</v>
+      </c>
+      <c r="E859" t="s">
         <v>1254</v>
       </c>
-      <c r="G856" t="s">
+      <c r="G859" t="s">
         <v>945</v>
       </c>
-      <c r="I856" t="s">
+      <c r="I859" t="s">
         <v>1198</v>
       </c>
-      <c r="J856" t="s">
+      <c r="J859" t="s">
         <v>1153</v>
       </c>
-      <c r="K856" t="s">
+      <c r="K859" t="s">
         <v>1200</v>
       </c>
-      <c r="L856" t="str">
+      <c r="L859" t="str">
         <f t="shared" si="121"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0300_Apis/0030_Hp_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="857" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A857" t="s">
-        <v>60</v>
-      </c>
-      <c r="B857" s="27">
+    <row r="860" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A860" t="s">
+        <v>60</v>
+      </c>
+      <c r="B860" s="27">
         <v>300</v>
       </c>
-      <c r="C857" t="s">
+      <c r="C860" t="s">
         <v>106</v>
       </c>
-      <c r="E857" t="s">
+      <c r="E860" t="s">
         <v>1254</v>
       </c>
-      <c r="F857" t="s">
+      <c r="F860" t="s">
         <v>111</v>
       </c>
-      <c r="G857" t="s">
+      <c r="G860" t="s">
         <v>946</v>
       </c>
-      <c r="L857" t="str">
+      <c r="L860" t="str">
         <f t="shared" si="120"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0300_Apis/det/0001_Hp_det_01.png</v>
       </c>
     </row>
-    <row r="858" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A858" t="s">
-        <v>60</v>
-      </c>
-      <c r="B858" s="27">
+    <row r="861" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A861" t="s">
+        <v>60</v>
+      </c>
+      <c r="B861" s="27">
         <v>300</v>
       </c>
-      <c r="C858" t="s">
+      <c r="C861" t="s">
         <v>106</v>
       </c>
-      <c r="E858" t="s">
+      <c r="E861" t="s">
         <v>1254</v>
       </c>
-      <c r="F858" t="s">
+      <c r="F861" t="s">
         <v>111</v>
       </c>
-      <c r="G858" t="s">
+      <c r="G861" t="s">
         <v>947</v>
       </c>
-      <c r="L858" t="str">
+      <c r="L861" t="str">
         <f t="shared" si="120"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0300_Apis/det/0010_Hp_det_02.png</v>
       </c>
     </row>
-    <row r="859" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A859" t="s">
-        <v>60</v>
-      </c>
-      <c r="B859" s="27">
+    <row r="862" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A862" t="s">
+        <v>60</v>
+      </c>
+      <c r="B862" s="27">
         <v>300</v>
       </c>
-      <c r="C859" t="s">
+      <c r="C862" t="s">
         <v>106</v>
       </c>
-      <c r="E859" t="s">
+      <c r="E862" t="s">
         <v>1254</v>
       </c>
-      <c r="F859" t="s">
+      <c r="F862" t="s">
         <v>111</v>
       </c>
-      <c r="G859" t="s">
+      <c r="G862" t="s">
         <v>948</v>
       </c>
-      <c r="I859" t="s">
+      <c r="I862" t="s">
         <v>1198</v>
       </c>
-      <c r="J859" t="s">
+      <c r="J862" t="s">
         <v>1220</v>
       </c>
-      <c r="K859" t="s">
+      <c r="K862" t="s">
         <v>1200</v>
       </c>
-      <c r="L859" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D859:K859)</f>
+      <c r="L862" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D862:K862)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0300_Apis/det/0020_Hp_det_AR-SP_01.png &lt;sup&gt;(AR; Sp.)&lt;/sup&gt;</v>
-      </c>
-    </row>
-    <row r="860" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A860" t="s">
-        <v>60</v>
-      </c>
-      <c r="B860" s="27">
-        <v>300</v>
-      </c>
-      <c r="C860" t="s">
-        <v>107</v>
-      </c>
-      <c r="L860" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="861" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A861" t="s">
-        <v>60</v>
-      </c>
-      <c r="B861" s="27">
-        <v>300</v>
-      </c>
-      <c r="C861" t="s">
-        <v>108</v>
-      </c>
-      <c r="L861" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="863" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A863" t="s">
-        <v>949</v>
+        <v>60</v>
       </c>
       <c r="B863" s="27">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="C863" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="L863" t="s">
-        <v>684</v>
+        <v>155</v>
       </c>
     </row>
     <row r="864" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A864" t="s">
+        <v>60</v>
+      </c>
+      <c r="B864" s="27">
+        <v>300</v>
+      </c>
+      <c r="C864" t="s">
+        <v>108</v>
+      </c>
+      <c r="L864" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="866" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A866" t="s">
         <v>949</v>
       </c>
-      <c r="B864" s="27">
+      <c r="B866" s="27">
         <v>1</v>
       </c>
-      <c r="C864" t="s">
-        <v>105</v>
-      </c>
-      <c r="E864" t="s">
+      <c r="C866" t="s">
+        <v>39</v>
+      </c>
+      <c r="L866" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="867" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A867" t="s">
+        <v>949</v>
+      </c>
+      <c r="B867" s="27">
+        <v>1</v>
+      </c>
+      <c r="C867" t="s">
+        <v>105</v>
+      </c>
+      <c r="E867" t="s">
         <v>1254</v>
       </c>
-      <c r="F864" t="s">
+      <c r="F867" t="s">
         <v>950</v>
       </c>
-      <c r="G864" t="s">
+      <c r="G867" t="s">
         <v>951</v>
       </c>
-      <c r="H864" t="s">
+      <c r="H867" t="s">
         <v>113</v>
       </c>
-      <c r="I864" t="s">
+      <c r="I867" t="s">
         <v>1198</v>
       </c>
-      <c r="J864" t="s">
+      <c r="J867" t="s">
         <v>1219</v>
       </c>
-      <c r="K864" t="s">
+      <c r="K867" t="s">
         <v>1200</v>
       </c>
-      <c r="L864" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D864:K864)</f>
+      <c r="L867" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D867:K867)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0300_Apis/epitheta/01_anx/0001_anx_seit-NR_01.png &lt;sup&gt;(seit NR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="865" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A865" t="s">
+    <row r="868" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A868" t="s">
         <v>949</v>
       </c>
-      <c r="B865" s="27">
+      <c r="B868" s="27">
         <v>1</v>
       </c>
-      <c r="C865" t="s">
+      <c r="C868" t="s">
         <v>27</v>
       </c>
-      <c r="L865" t="s">
+      <c r="L868" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="871" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A871" t="s">
-        <v>60</v>
-      </c>
-      <c r="B871" s="27">
+    <row r="874" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A874" t="s">
+        <v>60</v>
+      </c>
+      <c r="B874" s="27">
         <v>310</v>
       </c>
-      <c r="C871" t="s">
+      <c r="C874" t="s">
         <v>39</v>
       </c>
-      <c r="L871" t="s">
+      <c r="L874" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="872" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A872" t="s">
-        <v>60</v>
-      </c>
-      <c r="B872" s="27">
+    <row r="875" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A875" t="s">
+        <v>60</v>
+      </c>
+      <c r="B875" s="27">
         <v>310</v>
       </c>
-      <c r="C872" t="s">
-        <v>105</v>
-      </c>
-      <c r="E872" t="s">
+      <c r="C875" t="s">
+        <v>105</v>
+      </c>
+      <c r="E875" t="s">
         <v>1255</v>
       </c>
-      <c r="G872" t="s">
+      <c r="G875" t="s">
         <v>952</v>
       </c>
-      <c r="L872" t="str">
-        <f t="shared" ref="L872:L880" si="122">_xlfn.TEXTJOIN("", TRUE, D872:J872)</f>
+      <c r="L875" t="str">
+        <f t="shared" ref="L875:L883" si="122">_xlfn.TEXTJOIN("", TRUE, D875:J875)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0310_Hapi-Horussohn/0001_Hpy_01.png</v>
       </c>
     </row>
-    <row r="873" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A873" t="s">
-        <v>60</v>
-      </c>
-      <c r="B873" s="27">
+    <row r="876" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A876" t="s">
+        <v>60</v>
+      </c>
+      <c r="B876" s="27">
         <v>310</v>
       </c>
-      <c r="C873" t="s">
-        <v>105</v>
-      </c>
-      <c r="E873" t="s">
+      <c r="C876" t="s">
+        <v>105</v>
+      </c>
+      <c r="E876" t="s">
         <v>1255</v>
       </c>
-      <c r="G873" t="s">
+      <c r="G876" t="s">
         <v>953</v>
       </c>
-      <c r="L873" t="str">
+      <c r="L876" t="str">
         <f t="shared" si="122"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0310_Hapi-Horussohn/0010_Hpy_02.png</v>
       </c>
     </row>
-    <row r="874" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A874" t="s">
-        <v>60</v>
-      </c>
-      <c r="B874" s="27">
+    <row r="877" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A877" t="s">
+        <v>60</v>
+      </c>
+      <c r="B877" s="27">
         <v>310</v>
       </c>
-      <c r="C874" t="s">
-        <v>105</v>
-      </c>
-      <c r="E874" t="s">
+      <c r="C877" t="s">
+        <v>105</v>
+      </c>
+      <c r="E877" t="s">
         <v>1255</v>
       </c>
-      <c r="G874" t="s">
+      <c r="G877" t="s">
         <v>954</v>
       </c>
-      <c r="L874" t="str">
+      <c r="L877" t="str">
         <f t="shared" si="122"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0310_Hapi-Horussohn/0020_Hpy_03.png</v>
       </c>
     </row>
-    <row r="875" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A875" t="s">
-        <v>60</v>
-      </c>
-      <c r="B875" s="27">
+    <row r="878" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A878" t="s">
+        <v>60</v>
+      </c>
+      <c r="B878" s="27">
         <v>310</v>
       </c>
-      <c r="C875" t="s">
-        <v>105</v>
-      </c>
-      <c r="E875" t="s">
+      <c r="C878" t="s">
+        <v>105</v>
+      </c>
+      <c r="E878" t="s">
         <v>1255</v>
       </c>
-      <c r="G875" t="s">
+      <c r="G878" t="s">
         <v>955</v>
       </c>
-      <c r="L875" t="str">
+      <c r="L878" t="str">
         <f t="shared" si="122"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0310_Hapi-Horussohn/0030_Hpy_04.png</v>
       </c>
     </row>
-    <row r="876" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A876" t="s">
-        <v>60</v>
-      </c>
-      <c r="B876" s="27">
+    <row r="879" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A879" t="s">
+        <v>60</v>
+      </c>
+      <c r="B879" s="27">
         <v>310</v>
       </c>
-      <c r="C876" t="s">
-        <v>105</v>
-      </c>
-      <c r="E876" t="s">
+      <c r="C879" t="s">
+        <v>105</v>
+      </c>
+      <c r="E879" t="s">
         <v>1255</v>
       </c>
-      <c r="G876" t="s">
+      <c r="G879" t="s">
         <v>956</v>
       </c>
-      <c r="I876" t="s">
+      <c r="I879" t="s">
         <v>1198</v>
       </c>
-      <c r="J876" t="s">
+      <c r="J879" t="s">
         <v>1199</v>
       </c>
-      <c r="K876" t="s">
+      <c r="K879" t="s">
         <v>1200</v>
       </c>
-      <c r="L876" t="str">
-        <f t="shared" ref="L876:L878" si="123">_xlfn.TEXTJOIN("", TRUE, D876:K876)</f>
+      <c r="L879" t="str">
+        <f t="shared" ref="L879:L881" si="123">_xlfn.TEXTJOIN("", TRUE, D879:K879)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0310_Hapi-Horussohn/0040_Hpy_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="877" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A877" t="s">
-        <v>60</v>
-      </c>
-      <c r="B877" s="27">
+    <row r="880" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A880" t="s">
+        <v>60</v>
+      </c>
+      <c r="B880" s="27">
         <v>310</v>
       </c>
-      <c r="C877" t="s">
-        <v>105</v>
-      </c>
-      <c r="E877" t="s">
+      <c r="C880" t="s">
+        <v>105</v>
+      </c>
+      <c r="E880" t="s">
         <v>1255</v>
       </c>
-      <c r="G877" t="s">
+      <c r="G880" t="s">
         <v>957</v>
       </c>
-      <c r="I877" t="s">
+      <c r="I880" t="s">
         <v>1198</v>
       </c>
-      <c r="J877" t="s">
+      <c r="J880" t="s">
         <v>1202</v>
       </c>
-      <c r="K877" t="s">
+      <c r="K880" t="s">
         <v>1200</v>
       </c>
-      <c r="L877" t="str">
+      <c r="L880" t="str">
         <f t="shared" si="123"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0310_Hapi-Horussohn/0050_Hpy_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="878" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A878" t="s">
-        <v>60</v>
-      </c>
-      <c r="B878" s="27">
+    <row r="881" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A881" t="s">
+        <v>60</v>
+      </c>
+      <c r="B881" s="27">
         <v>310</v>
       </c>
-      <c r="C878" t="s">
-        <v>105</v>
-      </c>
-      <c r="E878" t="s">
+      <c r="C881" t="s">
+        <v>105</v>
+      </c>
+      <c r="E881" t="s">
         <v>1255</v>
       </c>
-      <c r="G878" t="s">
+      <c r="G881" t="s">
         <v>958</v>
       </c>
-      <c r="I878" t="s">
+      <c r="I881" t="s">
         <v>1198</v>
       </c>
-      <c r="J878" t="s">
+      <c r="J881" t="s">
         <v>1214</v>
       </c>
-      <c r="K878" t="s">
+      <c r="K881" t="s">
         <v>1200</v>
       </c>
-      <c r="L878" t="str">
+      <c r="L881" t="str">
         <f t="shared" si="123"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0310_Hapi-Horussohn/0060_Hpy_MR-NR-GR_01.png &lt;sup&gt;(MR; NR; Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="879" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A879" t="s">
-        <v>60</v>
-      </c>
-      <c r="B879" s="27">
+    <row r="882" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A882" t="s">
+        <v>60</v>
+      </c>
+      <c r="B882" s="27">
         <v>310</v>
       </c>
-      <c r="C879" t="s">
+      <c r="C882" t="s">
         <v>106</v>
       </c>
-      <c r="E879" t="s">
+      <c r="E882" t="s">
         <v>1255</v>
       </c>
-      <c r="F879" t="s">
+      <c r="F882" t="s">
         <v>111</v>
       </c>
-      <c r="G879" t="s">
+      <c r="G882" t="s">
         <v>959</v>
       </c>
-      <c r="L879" t="str">
+      <c r="L882" t="str">
         <f t="shared" si="122"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0310_Hapi-Horussohn/det/0001_Hpy_det_01.png</v>
       </c>
     </row>
-    <row r="880" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A880" t="s">
-        <v>60</v>
-      </c>
-      <c r="B880" s="27">
+    <row r="883" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A883" t="s">
+        <v>60</v>
+      </c>
+      <c r="B883" s="27">
         <v>310</v>
       </c>
-      <c r="C880" t="s">
+      <c r="C883" t="s">
         <v>106</v>
       </c>
-      <c r="E880" t="s">
+      <c r="E883" t="s">
         <v>1255</v>
       </c>
-      <c r="F880" t="s">
+      <c r="F883" t="s">
         <v>111</v>
       </c>
-      <c r="G880" t="s">
+      <c r="G883" t="s">
         <v>960</v>
       </c>
-      <c r="L880" t="str">
+      <c r="L883" t="str">
         <f t="shared" si="122"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0310_Hapi-Horussohn/det/0010_Hpy_det_AR_01.png</v>
       </c>
     </row>
-    <row r="881" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A881" t="s">
-        <v>60</v>
-      </c>
-      <c r="B881" s="27">
+    <row r="884" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A884" t="s">
+        <v>60</v>
+      </c>
+      <c r="B884" s="27">
         <v>310</v>
       </c>
-      <c r="C881" t="s">
+      <c r="C884" t="s">
         <v>107</v>
       </c>
-      <c r="L881" t="s">
+      <c r="L884" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="882" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A882" t="s">
-        <v>60</v>
-      </c>
-      <c r="B882" s="27">
-        <v>310</v>
-      </c>
-      <c r="C882" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="885" spans="1:12" x14ac:dyDescent="0.2">
@@ -27618,55 +27763,10 @@
         <v>60</v>
       </c>
       <c r="B885" s="27">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C885" t="s">
-        <v>39</v>
-      </c>
-      <c r="L885" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="886" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A886" t="s">
-        <v>60</v>
-      </c>
-      <c r="B886" s="27">
-        <v>320</v>
-      </c>
-      <c r="C886" t="s">
-        <v>105</v>
-      </c>
-      <c r="E886" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G886" t="s">
-        <v>961</v>
-      </c>
-      <c r="L886" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D886:J886)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/0001_Hr_01.png</v>
-      </c>
-    </row>
-    <row r="887" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A887" t="s">
-        <v>60</v>
-      </c>
-      <c r="B887" s="27">
-        <v>320</v>
-      </c>
-      <c r="C887" t="s">
-        <v>105</v>
-      </c>
-      <c r="E887" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G887" t="s">
-        <v>962</v>
-      </c>
-      <c r="L887" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D887:J887)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/0010_Hr_02.png</v>
+        <v>108</v>
       </c>
     </row>
     <row r="888" spans="1:12" x14ac:dyDescent="0.2">
@@ -27677,26 +27777,10 @@
         <v>320</v>
       </c>
       <c r="C888" t="s">
-        <v>105</v>
-      </c>
-      <c r="E888" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G888" t="s">
-        <v>963</v>
-      </c>
-      <c r="I888" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J888" t="s">
-        <v>1199</v>
-      </c>
-      <c r="K888" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L888" t="str">
-        <f t="shared" ref="L888:L889" si="124">_xlfn.TEXTJOIN("", TRUE, D888:K888)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/0020_Hr_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <v>39</v>
+      </c>
+      <c r="L888" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="889" spans="1:12" x14ac:dyDescent="0.2">
@@ -27713,118 +27797,149 @@
         <v>1256</v>
       </c>
       <c r="G889" t="s">
+        <v>961</v>
+      </c>
+      <c r="L889" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D889:J889)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/0001_Hr_01.png</v>
+      </c>
+    </row>
+    <row r="890" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A890" t="s">
+        <v>60</v>
+      </c>
+      <c r="B890" s="27">
+        <v>320</v>
+      </c>
+      <c r="C890" t="s">
+        <v>105</v>
+      </c>
+      <c r="E890" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G890" t="s">
+        <v>962</v>
+      </c>
+      <c r="L890" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D890:J890)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/0010_Hr_02.png</v>
+      </c>
+    </row>
+    <row r="891" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A891" t="s">
+        <v>60</v>
+      </c>
+      <c r="B891" s="27">
+        <v>320</v>
+      </c>
+      <c r="C891" t="s">
+        <v>105</v>
+      </c>
+      <c r="E891" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G891" t="s">
+        <v>963</v>
+      </c>
+      <c r="I891" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J891" t="s">
+        <v>1199</v>
+      </c>
+      <c r="K891" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L891" t="str">
+        <f t="shared" ref="L891:L892" si="124">_xlfn.TEXTJOIN("", TRUE, D891:K891)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/0020_Hr_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="892" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A892" t="s">
+        <v>60</v>
+      </c>
+      <c r="B892" s="27">
+        <v>320</v>
+      </c>
+      <c r="C892" t="s">
+        <v>105</v>
+      </c>
+      <c r="E892" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G892" t="s">
         <v>964</v>
       </c>
-      <c r="I889" t="s">
+      <c r="I892" t="s">
         <v>1198</v>
       </c>
-      <c r="J889" t="s">
+      <c r="J892" t="s">
         <v>1202</v>
       </c>
-      <c r="K889" t="s">
+      <c r="K892" t="s">
         <v>1200</v>
       </c>
-      <c r="L889" t="str">
+      <c r="L892" t="str">
         <f t="shared" si="124"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/0030_Hr_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="890" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A890" t="s">
-        <v>60</v>
-      </c>
-      <c r="B890" s="27">
+    <row r="893" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A893" t="s">
+        <v>60</v>
+      </c>
+      <c r="B893" s="27">
         <v>320</v>
       </c>
-      <c r="C890" t="s">
+      <c r="C893" t="s">
         <v>106</v>
       </c>
-      <c r="L890" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D890:J890)</f>
+      <c r="L893" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D893:J893)</f>
         <v/>
-      </c>
-    </row>
-    <row r="891" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A891" t="s">
-        <v>60</v>
-      </c>
-      <c r="B891" s="27">
-        <v>320</v>
-      </c>
-      <c r="C891" t="s">
-        <v>107</v>
-      </c>
-      <c r="L891" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="892" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A892" t="s">
-        <v>60</v>
-      </c>
-      <c r="B892" s="27">
-        <v>320</v>
-      </c>
-      <c r="C892" t="s">
-        <v>108</v>
-      </c>
-      <c r="L892" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="894" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A894" t="s">
-        <v>968</v>
+        <v>60</v>
       </c>
       <c r="B894" s="27">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="C894" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="L894" t="s">
-        <v>983</v>
+        <v>157</v>
       </c>
     </row>
     <row r="895" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A895" t="s">
+        <v>60</v>
+      </c>
+      <c r="B895" s="27">
+        <v>320</v>
+      </c>
+      <c r="C895" t="s">
+        <v>108</v>
+      </c>
+      <c r="L895" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="897" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A897" t="s">
         <v>968</v>
       </c>
-      <c r="B895" s="27">
+      <c r="B897" s="27">
         <v>1</v>
       </c>
-      <c r="C895" t="s">
-        <v>105</v>
-      </c>
-      <c r="E895" t="s">
-        <v>1256</v>
-      </c>
-      <c r="F895" t="s">
-        <v>965</v>
-      </c>
-      <c r="G895" t="s">
-        <v>966</v>
-      </c>
-      <c r="H895" t="s">
-        <v>113</v>
-      </c>
-      <c r="L895" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D895:J895)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/epitheta/0001_m-Ax.t_01.png</v>
-      </c>
-    </row>
-    <row r="896" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A896" t="s">
-        <v>968</v>
-      </c>
-      <c r="B896" s="27">
-        <v>1</v>
-      </c>
-      <c r="C896" t="s">
-        <v>27</v>
-      </c>
-      <c r="L896" t="s">
-        <v>984</v>
+      <c r="C897" t="s">
+        <v>39</v>
+      </c>
+      <c r="L897" t="s">
+        <v>983</v>
       </c>
     </row>
     <row r="898" spans="1:12" x14ac:dyDescent="0.2">
@@ -27832,13 +27947,26 @@
         <v>968</v>
       </c>
       <c r="B898" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C898" t="s">
-        <v>39</v>
-      </c>
-      <c r="L898" t="s">
-        <v>982</v>
+        <v>105</v>
+      </c>
+      <c r="E898" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F898" t="s">
+        <v>965</v>
+      </c>
+      <c r="G898" t="s">
+        <v>966</v>
+      </c>
+      <c r="H898" t="s">
+        <v>113</v>
+      </c>
+      <c r="L898" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D898:J898)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/epitheta/0001_m-Ax.t_01.png</v>
       </c>
     </row>
     <row r="899" spans="1:12" x14ac:dyDescent="0.2">
@@ -27846,40 +27974,27 @@
         <v>968</v>
       </c>
       <c r="B899" s="27">
+        <v>1</v>
+      </c>
+      <c r="C899" t="s">
+        <v>27</v>
+      </c>
+      <c r="L899" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="901" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A901" t="s">
+        <v>968</v>
+      </c>
+      <c r="B901" s="27">
         <v>2</v>
       </c>
-      <c r="C899" t="s">
-        <v>105</v>
-      </c>
-      <c r="E899" t="s">
-        <v>1256</v>
-      </c>
-      <c r="F899" t="s">
-        <v>965</v>
-      </c>
-      <c r="G899" t="s">
-        <v>967</v>
-      </c>
-      <c r="H899" t="s">
-        <v>113</v>
-      </c>
-      <c r="L899" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D899:J899)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/epitheta/0001_nD-jt_01.png</v>
-      </c>
-    </row>
-    <row r="900" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A900" t="s">
-        <v>968</v>
-      </c>
-      <c r="B900" s="27">
-        <v>2</v>
-      </c>
-      <c r="C900" t="s">
-        <v>27</v>
-      </c>
-      <c r="L900" t="s">
-        <v>981</v>
+      <c r="C901" t="s">
+        <v>39</v>
+      </c>
+      <c r="L901" t="s">
+        <v>982</v>
       </c>
     </row>
     <row r="902" spans="1:12" x14ac:dyDescent="0.2">
@@ -27887,13 +28002,26 @@
         <v>968</v>
       </c>
       <c r="B902" s="27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C902" t="s">
-        <v>39</v>
-      </c>
-      <c r="L902" t="s">
-        <v>979</v>
+        <v>105</v>
+      </c>
+      <c r="E902" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F902" t="s">
+        <v>965</v>
+      </c>
+      <c r="G902" t="s">
+        <v>967</v>
+      </c>
+      <c r="H902" t="s">
+        <v>113</v>
+      </c>
+      <c r="L902" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D902:J902)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/epitheta/0001_nD-jt_01.png</v>
       </c>
     </row>
     <row r="903" spans="1:12" x14ac:dyDescent="0.2">
@@ -27901,49 +28029,27 @@
         <v>968</v>
       </c>
       <c r="B903" s="27">
+        <v>2</v>
+      </c>
+      <c r="C903" t="s">
+        <v>27</v>
+      </c>
+      <c r="L903" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="905" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A905" t="s">
+        <v>968</v>
+      </c>
+      <c r="B905" s="27">
         <v>3</v>
       </c>
-      <c r="C903" t="s">
-        <v>105</v>
-      </c>
-      <c r="E903" t="s">
-        <v>1256</v>
-      </c>
-      <c r="F903" t="s">
-        <v>965</v>
-      </c>
-      <c r="G903" t="s">
-        <v>969</v>
-      </c>
-      <c r="H903" t="s">
-        <v>113</v>
-      </c>
-      <c r="I903" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J903" t="s">
-        <v>1190</v>
-      </c>
-      <c r="K903" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L903" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D903:K903)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/epitheta/0001_pA-Xrd_SP_01.png &lt;sup&gt;(Spät.)&lt;/sup&gt;</v>
-      </c>
-    </row>
-    <row r="904" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A904" t="s">
-        <v>968</v>
-      </c>
-      <c r="B904" s="27">
-        <v>3</v>
-      </c>
-      <c r="C904" t="s">
-        <v>27</v>
-      </c>
-      <c r="L904" t="s">
-        <v>980</v>
+      <c r="C905" t="s">
+        <v>39</v>
+      </c>
+      <c r="L905" t="s">
+        <v>979</v>
       </c>
     </row>
     <row r="906" spans="1:12" x14ac:dyDescent="0.2">
@@ -27951,13 +28057,35 @@
         <v>968</v>
       </c>
       <c r="B906" s="27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C906" t="s">
-        <v>39</v>
-      </c>
-      <c r="L906" t="s">
-        <v>977</v>
+        <v>105</v>
+      </c>
+      <c r="E906" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F906" t="s">
+        <v>965</v>
+      </c>
+      <c r="G906" t="s">
+        <v>969</v>
+      </c>
+      <c r="H906" t="s">
+        <v>113</v>
+      </c>
+      <c r="I906" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J906" t="s">
+        <v>1190</v>
+      </c>
+      <c r="K906" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L906" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D906:K906)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/epitheta/0001_pA-Xrd_SP_01.png &lt;sup&gt;(Spät.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="907" spans="1:12" x14ac:dyDescent="0.2">
@@ -27965,40 +28093,27 @@
         <v>968</v>
       </c>
       <c r="B907" s="27">
+        <v>3</v>
+      </c>
+      <c r="C907" t="s">
+        <v>27</v>
+      </c>
+      <c r="L907" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="909" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A909" t="s">
+        <v>968</v>
+      </c>
+      <c r="B909" s="27">
         <v>4</v>
       </c>
-      <c r="C907" t="s">
-        <v>105</v>
-      </c>
-      <c r="E907" t="s">
-        <v>1256</v>
-      </c>
-      <c r="F907" t="s">
-        <v>965</v>
-      </c>
-      <c r="G907" t="s">
-        <v>970</v>
-      </c>
-      <c r="H907" t="s">
-        <v>113</v>
-      </c>
-      <c r="L907" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D907:J907)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/epitheta/0001_sA-s.t_01.png</v>
-      </c>
-    </row>
-    <row r="908" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A908" t="s">
-        <v>968</v>
-      </c>
-      <c r="B908" s="27">
-        <v>4</v>
-      </c>
-      <c r="C908" t="s">
-        <v>27</v>
-      </c>
-      <c r="L908" t="s">
-        <v>978</v>
+      <c r="C909" t="s">
+        <v>39</v>
+      </c>
+      <c r="L909" t="s">
+        <v>977</v>
       </c>
     </row>
     <row r="910" spans="1:12" x14ac:dyDescent="0.2">
@@ -28006,13 +28121,26 @@
         <v>968</v>
       </c>
       <c r="B910" s="27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C910" t="s">
-        <v>39</v>
-      </c>
-      <c r="L910" t="s">
-        <v>975</v>
+        <v>105</v>
+      </c>
+      <c r="E910" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F910" t="s">
+        <v>965</v>
+      </c>
+      <c r="G910" t="s">
+        <v>970</v>
+      </c>
+      <c r="H910" t="s">
+        <v>113</v>
+      </c>
+      <c r="L910" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D910:J910)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/epitheta/0001_sA-s.t_01.png</v>
       </c>
     </row>
     <row r="911" spans="1:12" x14ac:dyDescent="0.2">
@@ -28020,40 +28148,27 @@
         <v>968</v>
       </c>
       <c r="B911" s="27">
+        <v>4</v>
+      </c>
+      <c r="C911" t="s">
+        <v>27</v>
+      </c>
+      <c r="L911" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="913" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A913" t="s">
+        <v>968</v>
+      </c>
+      <c r="B913" s="27">
         <v>5</v>
       </c>
-      <c r="C911" t="s">
-        <v>105</v>
-      </c>
-      <c r="E911" t="s">
-        <v>1256</v>
-      </c>
-      <c r="F911" t="s">
-        <v>965</v>
-      </c>
-      <c r="G911" t="s">
-        <v>971</v>
-      </c>
-      <c r="H911" t="s">
-        <v>113</v>
-      </c>
-      <c r="L911" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D911:J911)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/epitheta/0001_smA-tA.wj_01.png</v>
-      </c>
-    </row>
-    <row r="912" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A912" t="s">
-        <v>968</v>
-      </c>
-      <c r="B912" s="27">
-        <v>5</v>
-      </c>
-      <c r="C912" t="s">
-        <v>27</v>
-      </c>
-      <c r="L912" t="s">
-        <v>976</v>
+      <c r="C913" t="s">
+        <v>39</v>
+      </c>
+      <c r="L913" t="s">
+        <v>975</v>
       </c>
     </row>
     <row r="914" spans="1:12" x14ac:dyDescent="0.2">
@@ -28061,13 +28176,26 @@
         <v>968</v>
       </c>
       <c r="B914" s="27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C914" t="s">
-        <v>39</v>
-      </c>
-      <c r="L914" t="s">
-        <v>973</v>
+        <v>105</v>
+      </c>
+      <c r="E914" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F914" t="s">
+        <v>965</v>
+      </c>
+      <c r="G914" t="s">
+        <v>971</v>
+      </c>
+      <c r="H914" t="s">
+        <v>113</v>
+      </c>
+      <c r="L914" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D914:J914)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/epitheta/0001_smA-tA.wj_01.png</v>
       </c>
     </row>
     <row r="915" spans="1:12" x14ac:dyDescent="0.2">
@@ -28075,96 +28203,68 @@
         <v>968</v>
       </c>
       <c r="B915" s="27">
+        <v>5</v>
+      </c>
+      <c r="C915" t="s">
+        <v>27</v>
+      </c>
+      <c r="L915" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="917" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A917" t="s">
+        <v>968</v>
+      </c>
+      <c r="B917" s="27">
         <v>6</v>
       </c>
-      <c r="C915" t="s">
-        <v>105</v>
-      </c>
-      <c r="E915" t="s">
-        <v>1256</v>
-      </c>
-      <c r="F915" t="s">
-        <v>965</v>
-      </c>
-      <c r="G915" t="s">
-        <v>972</v>
-      </c>
-      <c r="H915" t="s">
-        <v>113</v>
-      </c>
-      <c r="L915" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D915:J915)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/epitheta/0001_wr_01.png</v>
-      </c>
-    </row>
-    <row r="916" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A916" t="s">
-        <v>968</v>
-      </c>
-      <c r="B916" s="27">
-        <v>6</v>
-      </c>
-      <c r="C916" t="s">
-        <v>27</v>
-      </c>
-      <c r="L916" t="s">
-        <v>974</v>
+      <c r="C917" t="s">
+        <v>39</v>
+      </c>
+      <c r="L917" t="s">
+        <v>973</v>
       </c>
     </row>
     <row r="918" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A918" t="s">
-        <v>60</v>
+        <v>968</v>
       </c>
       <c r="B918" s="27">
-        <v>330</v>
+        <v>6</v>
       </c>
       <c r="C918" t="s">
-        <v>39</v>
-      </c>
-      <c r="L918" t="s">
-        <v>719</v>
+        <v>105</v>
+      </c>
+      <c r="E918" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F918" t="s">
+        <v>965</v>
+      </c>
+      <c r="G918" t="s">
+        <v>972</v>
+      </c>
+      <c r="H918" t="s">
+        <v>113</v>
+      </c>
+      <c r="L918" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D918:J918)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0320_Horus/epitheta/0001_wr_01.png</v>
       </c>
     </row>
     <row r="919" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A919" t="s">
-        <v>60</v>
+        <v>968</v>
       </c>
       <c r="B919" s="27">
-        <v>330</v>
+        <v>6</v>
       </c>
       <c r="C919" t="s">
-        <v>105</v>
-      </c>
-      <c r="E919" t="s">
-        <v>1257</v>
-      </c>
-      <c r="G919" t="s">
-        <v>985</v>
-      </c>
-      <c r="L919" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D919:J919)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0330_Harachte/0001_Hr-Axtj_01.png</v>
-      </c>
-    </row>
-    <row r="920" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A920" t="s">
-        <v>60</v>
-      </c>
-      <c r="B920" s="27">
-        <v>330</v>
-      </c>
-      <c r="C920" t="s">
-        <v>105</v>
-      </c>
-      <c r="E920" t="s">
-        <v>1257</v>
-      </c>
-      <c r="G920" t="s">
-        <v>986</v>
-      </c>
-      <c r="L920" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D920:J920)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0330_Harachte/0010_Hr-Axtj_02.png</v>
+        <v>27</v>
+      </c>
+      <c r="L919" t="s">
+        <v>974</v>
       </c>
     </row>
     <row r="921" spans="1:12" x14ac:dyDescent="0.2">
@@ -28175,17 +28275,10 @@
         <v>330</v>
       </c>
       <c r="C921" t="s">
-        <v>105</v>
-      </c>
-      <c r="E921" t="s">
-        <v>1257</v>
-      </c>
-      <c r="G921" t="s">
-        <v>987</v>
-      </c>
-      <c r="L921" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D921:J921)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0330_Harachte/0020_Hr-Axtj_03.png</v>
+        <v>39</v>
+      </c>
+      <c r="L921" t="s">
+        <v>719</v>
       </c>
     </row>
     <row r="922" spans="1:12" x14ac:dyDescent="0.2">
@@ -28196,11 +28289,17 @@
         <v>330</v>
       </c>
       <c r="C922" t="s">
-        <v>106</v>
+        <v>105</v>
+      </c>
+      <c r="E922" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G922" t="s">
+        <v>985</v>
       </c>
       <c r="L922" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D922:J922)</f>
-        <v/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0330_Harachte/0001_Hr-Axtj_01.png</v>
       </c>
     </row>
     <row r="923" spans="1:12" x14ac:dyDescent="0.2">
@@ -28211,10 +28310,17 @@
         <v>330</v>
       </c>
       <c r="C923" t="s">
-        <v>107</v>
-      </c>
-      <c r="L923" t="s">
-        <v>158</v>
+        <v>105</v>
+      </c>
+      <c r="E923" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G923" t="s">
+        <v>986</v>
+      </c>
+      <c r="L923" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D923:J923)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0330_Harachte/0010_Hr-Axtj_02.png</v>
       </c>
     </row>
     <row r="924" spans="1:12" x14ac:dyDescent="0.2">
@@ -28225,7 +28331,46 @@
         <v>330</v>
       </c>
       <c r="C924" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="E924" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G924" t="s">
+        <v>987</v>
+      </c>
+      <c r="L924" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D924:J924)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0330_Harachte/0020_Hr-Axtj_03.png</v>
+      </c>
+    </row>
+    <row r="925" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A925" t="s">
+        <v>60</v>
+      </c>
+      <c r="B925" s="27">
+        <v>330</v>
+      </c>
+      <c r="C925" t="s">
+        <v>106</v>
+      </c>
+      <c r="L925" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D925:J925)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="926" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A926" t="s">
+        <v>60</v>
+      </c>
+      <c r="B926" s="27">
+        <v>330</v>
+      </c>
+      <c r="C926" t="s">
+        <v>107</v>
+      </c>
+      <c r="L926" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="927" spans="1:12" x14ac:dyDescent="0.2">
@@ -28233,64 +28378,10 @@
         <v>60</v>
       </c>
       <c r="B927" s="27">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C927" t="s">
-        <v>39</v>
-      </c>
-      <c r="L927" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="928" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A928" t="s">
-        <v>60</v>
-      </c>
-      <c r="B928" s="27">
-        <v>340</v>
-      </c>
-      <c r="C928" t="s">
-        <v>105</v>
-      </c>
-      <c r="E928" t="s">
-        <v>1258</v>
-      </c>
-      <c r="G928" t="s">
-        <v>988</v>
-      </c>
-      <c r="L928" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D928:J928)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0340_Heqet/0001_Hqt_01.png</v>
-      </c>
-    </row>
-    <row r="929" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A929" t="s">
-        <v>60</v>
-      </c>
-      <c r="B929" s="27">
-        <v>340</v>
-      </c>
-      <c r="C929" t="s">
-        <v>105</v>
-      </c>
-      <c r="E929" t="s">
-        <v>1258</v>
-      </c>
-      <c r="G929" t="s">
-        <v>989</v>
-      </c>
-      <c r="I929" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J929" t="s">
-        <v>1206</v>
-      </c>
-      <c r="K929" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L929" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D929:K929)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0340_Heqet/0010_Hqt_D.18_01.png &lt;sup&gt;(D.18)&lt;/sup&gt;</v>
+        <v>108</v>
       </c>
     </row>
     <row r="930" spans="1:12" x14ac:dyDescent="0.2">
@@ -28301,20 +28392,10 @@
         <v>340</v>
       </c>
       <c r="C930" t="s">
-        <v>106</v>
-      </c>
-      <c r="E930" t="s">
-        <v>1258</v>
-      </c>
-      <c r="F930" t="s">
-        <v>111</v>
-      </c>
-      <c r="G930" t="s">
-        <v>990</v>
-      </c>
-      <c r="L930" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D930:J930)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0340_Heqet/det/0001_Hqt_det_01.png</v>
+        <v>39</v>
+      </c>
+      <c r="L930" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="931" spans="1:12" x14ac:dyDescent="0.2">
@@ -28325,20 +28406,17 @@
         <v>340</v>
       </c>
       <c r="C931" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E931" t="s">
         <v>1258</v>
       </c>
-      <c r="F931" t="s">
-        <v>111</v>
-      </c>
       <c r="G931" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="L931" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D931:J931)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0340_Heqet/det/0010_Hqt_det_02.png</v>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0340_Heqet/0001_Hqt_01.png</v>
       </c>
     </row>
     <row r="932" spans="1:12" x14ac:dyDescent="0.2">
@@ -28349,10 +28427,26 @@
         <v>340</v>
       </c>
       <c r="C932" t="s">
-        <v>107</v>
-      </c>
-      <c r="L932" t="s">
-        <v>159</v>
+        <v>105</v>
+      </c>
+      <c r="E932" t="s">
+        <v>1258</v>
+      </c>
+      <c r="G932" t="s">
+        <v>989</v>
+      </c>
+      <c r="I932" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J932" t="s">
+        <v>1206</v>
+      </c>
+      <c r="K932" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L932" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D932:K932)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0340_Heqet/0010_Hqt_D.18_01.png &lt;sup&gt;(D.18)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="933" spans="1:12" x14ac:dyDescent="0.2">
@@ -28363,7 +28457,58 @@
         <v>340</v>
       </c>
       <c r="C933" t="s">
-        <v>108</v>
+        <v>106</v>
+      </c>
+      <c r="E933" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F933" t="s">
+        <v>111</v>
+      </c>
+      <c r="G933" t="s">
+        <v>990</v>
+      </c>
+      <c r="L933" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D933:J933)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0340_Heqet/det/0001_Hqt_det_01.png</v>
+      </c>
+    </row>
+    <row r="934" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A934" t="s">
+        <v>60</v>
+      </c>
+      <c r="B934" s="27">
+        <v>340</v>
+      </c>
+      <c r="C934" t="s">
+        <v>106</v>
+      </c>
+      <c r="E934" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F934" t="s">
+        <v>111</v>
+      </c>
+      <c r="G934" t="s">
+        <v>991</v>
+      </c>
+      <c r="L934" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D934:J934)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0340_Heqet/det/0010_Hqt_det_02.png</v>
+      </c>
+    </row>
+    <row r="935" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A935" t="s">
+        <v>60</v>
+      </c>
+      <c r="B935" s="27">
+        <v>340</v>
+      </c>
+      <c r="C935" t="s">
+        <v>107</v>
+      </c>
+      <c r="L935" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="936" spans="1:12" x14ac:dyDescent="0.2">
@@ -28371,230 +28516,230 @@
         <v>60</v>
       </c>
       <c r="B936" s="27">
+        <v>340</v>
+      </c>
+      <c r="C936" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="939" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A939" t="s">
+        <v>60</v>
+      </c>
+      <c r="B939" s="27">
         <v>350</v>
       </c>
-      <c r="C936" t="s">
+      <c r="C939" t="s">
         <v>39</v>
       </c>
-      <c r="L936" t="s">
+      <c r="L939" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="937" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A937" t="s">
-        <v>60</v>
-      </c>
-      <c r="B937" s="27">
+    <row r="940" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A940" t="s">
+        <v>60</v>
+      </c>
+      <c r="B940" s="27">
         <v>350</v>
       </c>
-      <c r="C937" t="s">
-        <v>105</v>
-      </c>
-      <c r="E937" t="s">
+      <c r="C940" t="s">
+        <v>105</v>
+      </c>
+      <c r="E940" t="s">
         <v>1259</v>
       </c>
-      <c r="G937" t="s">
+      <c r="G940" t="s">
         <v>992</v>
       </c>
-      <c r="L937" t="str">
-        <f t="shared" ref="L937:L944" si="125">_xlfn.TEXTJOIN("", TRUE, D937:J937)</f>
+      <c r="L940" t="str">
+        <f t="shared" ref="L940:L947" si="125">_xlfn.TEXTJOIN("", TRUE, D940:J940)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0350_Chnum/0001_Xnm.w_01.png</v>
       </c>
     </row>
-    <row r="938" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A938" t="s">
-        <v>60</v>
-      </c>
-      <c r="B938" s="27">
+    <row r="941" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A941" t="s">
+        <v>60</v>
+      </c>
+      <c r="B941" s="27">
         <v>350</v>
       </c>
-      <c r="C938" t="s">
-        <v>105</v>
-      </c>
-      <c r="E938" t="s">
+      <c r="C941" t="s">
+        <v>105</v>
+      </c>
+      <c r="E941" t="s">
         <v>1259</v>
       </c>
-      <c r="G938" t="s">
+      <c r="G941" t="s">
         <v>993</v>
       </c>
-      <c r="L938" t="str">
+      <c r="L941" t="str">
         <f t="shared" si="125"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0350_Chnum/0010_Xnm.w_02.png</v>
       </c>
     </row>
-    <row r="939" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A939" t="s">
-        <v>60</v>
-      </c>
-      <c r="B939" s="27">
+    <row r="942" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A942" t="s">
+        <v>60</v>
+      </c>
+      <c r="B942" s="27">
         <v>350</v>
       </c>
-      <c r="C939" t="s">
-        <v>105</v>
-      </c>
-      <c r="E939" t="s">
+      <c r="C942" t="s">
+        <v>105</v>
+      </c>
+      <c r="E942" t="s">
         <v>1259</v>
       </c>
-      <c r="G939" t="s">
+      <c r="G942" t="s">
         <v>994</v>
       </c>
-      <c r="L939" t="str">
+      <c r="L942" t="str">
         <f t="shared" si="125"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0350_Chnum/0020_Xnm.w_03.png</v>
       </c>
     </row>
-    <row r="940" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A940" t="s">
-        <v>60</v>
-      </c>
-      <c r="B940" s="27">
+    <row r="943" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A943" t="s">
+        <v>60</v>
+      </c>
+      <c r="B943" s="27">
         <v>350</v>
       </c>
-      <c r="C940" t="s">
-        <v>105</v>
-      </c>
-      <c r="E940" t="s">
+      <c r="C943" t="s">
+        <v>105</v>
+      </c>
+      <c r="E943" t="s">
         <v>1259</v>
       </c>
-      <c r="G940" t="s">
+      <c r="G943" t="s">
         <v>995</v>
       </c>
-      <c r="L940" t="str">
+      <c r="L943" t="str">
         <f t="shared" si="125"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0350_Chnum/0030_Xnm.w_04.png</v>
       </c>
     </row>
-    <row r="941" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A941" t="s">
-        <v>60</v>
-      </c>
-      <c r="B941" s="27">
+    <row r="944" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A944" t="s">
+        <v>60</v>
+      </c>
+      <c r="B944" s="27">
         <v>350</v>
       </c>
-      <c r="C941" t="s">
-        <v>105</v>
-      </c>
-      <c r="E941" t="s">
+      <c r="C944" t="s">
+        <v>105</v>
+      </c>
+      <c r="E944" t="s">
         <v>1259</v>
       </c>
-      <c r="G941" t="s">
+      <c r="G944" t="s">
         <v>996</v>
       </c>
-      <c r="I941" t="s">
+      <c r="I944" t="s">
         <v>1198</v>
       </c>
-      <c r="J941" t="s">
+      <c r="J944" t="s">
         <v>1201</v>
       </c>
-      <c r="K941" t="s">
+      <c r="K944" t="s">
         <v>1200</v>
       </c>
-      <c r="L941" t="str">
-        <f t="shared" ref="L941:L942" si="126">_xlfn.TEXTJOIN("", TRUE, D941:K941)</f>
+      <c r="L944" t="str">
+        <f t="shared" ref="L944:L945" si="126">_xlfn.TEXTJOIN("", TRUE, D944:K944)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0350_Chnum/0040_Xnm.w_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="942" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A942" t="s">
-        <v>60</v>
-      </c>
-      <c r="B942" s="27">
+    <row r="945" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A945" t="s">
+        <v>60</v>
+      </c>
+      <c r="B945" s="27">
         <v>350</v>
       </c>
-      <c r="C942" t="s">
-        <v>105</v>
-      </c>
-      <c r="E942" t="s">
+      <c r="C945" t="s">
+        <v>105</v>
+      </c>
+      <c r="E945" t="s">
         <v>1259</v>
       </c>
-      <c r="G942" t="s">
+      <c r="G945" t="s">
         <v>997</v>
       </c>
-      <c r="I942" t="s">
+      <c r="I945" t="s">
         <v>1198</v>
       </c>
-      <c r="J942" t="s">
+      <c r="J945" t="s">
         <v>1201</v>
       </c>
-      <c r="K942" t="s">
+      <c r="K945" t="s">
         <v>1200</v>
       </c>
-      <c r="L942" t="str">
+      <c r="L945" t="str">
         <f t="shared" si="126"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0350_Chnum/0050_Xnm.w_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="943" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A943" t="s">
-        <v>60</v>
-      </c>
-      <c r="B943" s="27">
+    <row r="946" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A946" t="s">
+        <v>60</v>
+      </c>
+      <c r="B946" s="27">
         <v>350</v>
       </c>
-      <c r="C943" t="s">
+      <c r="C946" t="s">
         <v>106</v>
       </c>
-      <c r="E943" t="s">
+      <c r="E946" t="s">
         <v>1259</v>
       </c>
-      <c r="F943" t="s">
+      <c r="F946" t="s">
         <v>111</v>
       </c>
-      <c r="G943" t="s">
+      <c r="G946" t="s">
         <v>998</v>
       </c>
-      <c r="L943" t="str">
+      <c r="L946" t="str">
         <f t="shared" si="125"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0350_Chnum/det/0001_Xnm.w_det_01.png</v>
       </c>
     </row>
-    <row r="944" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A944" t="s">
-        <v>60</v>
-      </c>
-      <c r="B944" s="27">
+    <row r="947" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A947" t="s">
+        <v>60</v>
+      </c>
+      <c r="B947" s="27">
         <v>350</v>
       </c>
-      <c r="C944" t="s">
+      <c r="C947" t="s">
         <v>106</v>
       </c>
-      <c r="E944" t="s">
+      <c r="E947" t="s">
         <v>1259</v>
       </c>
-      <c r="F944" t="s">
+      <c r="F947" t="s">
         <v>111</v>
       </c>
-      <c r="G944" t="s">
+      <c r="G947" t="s">
         <v>999</v>
       </c>
-      <c r="L944" t="str">
+      <c r="L947" t="str">
         <f t="shared" si="125"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0350_Chnum/det/0010_Xnm.w_det_02.png</v>
       </c>
     </row>
-    <row r="945" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A945" t="s">
-        <v>60</v>
-      </c>
-      <c r="B945" s="27">
+    <row r="948" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A948" t="s">
+        <v>60</v>
+      </c>
+      <c r="B948" s="27">
         <v>350</v>
       </c>
-      <c r="C945" t="s">
+      <c r="C948" t="s">
         <v>107</v>
       </c>
-      <c r="L945" t="s">
+      <c r="L948" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="946" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A946" t="s">
-        <v>60</v>
-      </c>
-      <c r="B946" s="27">
-        <v>350</v>
-      </c>
-      <c r="C946" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="949" spans="1:12" x14ac:dyDescent="0.2">
@@ -28602,55 +28747,10 @@
         <v>60</v>
       </c>
       <c r="B949" s="27">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C949" t="s">
-        <v>39</v>
-      </c>
-      <c r="L949" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="950" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A950" t="s">
-        <v>60</v>
-      </c>
-      <c r="B950" s="27">
-        <v>360</v>
-      </c>
-      <c r="C950" t="s">
-        <v>105</v>
-      </c>
-      <c r="E950" t="s">
-        <v>1260</v>
-      </c>
-      <c r="G950" t="s">
-        <v>1000</v>
-      </c>
-      <c r="L950" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D950:J950)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0360_Chons/0001_Xnsw_01.png</v>
-      </c>
-    </row>
-    <row r="951" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A951" t="s">
-        <v>60</v>
-      </c>
-      <c r="B951" s="27">
-        <v>360</v>
-      </c>
-      <c r="C951" t="s">
-        <v>105</v>
-      </c>
-      <c r="E951" t="s">
-        <v>1260</v>
-      </c>
-      <c r="G951" t="s">
-        <v>1001</v>
-      </c>
-      <c r="L951" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D951:J951)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0360_Chons/0010_Xnsw_02.png</v>
+        <v>108</v>
       </c>
     </row>
     <row r="952" spans="1:12" x14ac:dyDescent="0.2">
@@ -28661,26 +28761,10 @@
         <v>360</v>
       </c>
       <c r="C952" t="s">
-        <v>105</v>
-      </c>
-      <c r="E952" t="s">
-        <v>1260</v>
-      </c>
-      <c r="G952" t="s">
-        <v>1002</v>
-      </c>
-      <c r="I952" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J952" t="s">
-        <v>1153</v>
-      </c>
-      <c r="K952" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L952" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D952:K952)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0360_Chons/0020_Xnsw_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+        <v>39</v>
+      </c>
+      <c r="L952" t="s">
+        <v>722</v>
       </c>
     </row>
     <row r="953" spans="1:12" x14ac:dyDescent="0.2">
@@ -28691,11 +28775,17 @@
         <v>360</v>
       </c>
       <c r="C953" t="s">
-        <v>106</v>
+        <v>105</v>
+      </c>
+      <c r="E953" t="s">
+        <v>1260</v>
+      </c>
+      <c r="G953" t="s">
+        <v>1000</v>
       </c>
       <c r="L953" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D953:J953)</f>
-        <v/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0360_Chons/0001_Xnsw_01.png</v>
       </c>
     </row>
     <row r="954" spans="1:12" x14ac:dyDescent="0.2">
@@ -28706,10 +28796,17 @@
         <v>360</v>
       </c>
       <c r="C954" t="s">
-        <v>107</v>
-      </c>
-      <c r="L954" t="s">
-        <v>161</v>
+        <v>105</v>
+      </c>
+      <c r="E954" t="s">
+        <v>1260</v>
+      </c>
+      <c r="G954" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L954" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D954:J954)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0360_Chons/0010_Xnsw_02.png</v>
       </c>
     </row>
     <row r="955" spans="1:12" x14ac:dyDescent="0.2">
@@ -28720,7 +28817,55 @@
         <v>360</v>
       </c>
       <c r="C955" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="E955" t="s">
+        <v>1260</v>
+      </c>
+      <c r="G955" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I955" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J955" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K955" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L955" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D955:K955)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0360_Chons/0020_Xnsw_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="956" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A956" t="s">
+        <v>60</v>
+      </c>
+      <c r="B956" s="27">
+        <v>360</v>
+      </c>
+      <c r="C956" t="s">
+        <v>106</v>
+      </c>
+      <c r="L956" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D956:J956)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="957" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A957" t="s">
+        <v>60</v>
+      </c>
+      <c r="B957" s="27">
+        <v>360</v>
+      </c>
+      <c r="C957" t="s">
+        <v>107</v>
+      </c>
+      <c r="L957" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="958" spans="1:12" x14ac:dyDescent="0.2">
@@ -28728,55 +28873,10 @@
         <v>60</v>
       </c>
       <c r="B958" s="27">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C958" t="s">
-        <v>39</v>
-      </c>
-      <c r="L958" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="959" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A959" t="s">
-        <v>60</v>
-      </c>
-      <c r="B959" s="27">
-        <v>370</v>
-      </c>
-      <c r="C959" t="s">
-        <v>105</v>
-      </c>
-      <c r="E959" t="s">
-        <v>1261</v>
-      </c>
-      <c r="G959" t="s">
-        <v>1003</v>
-      </c>
-      <c r="L959" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D959:J959)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0001_sbk_01.png</v>
-      </c>
-    </row>
-    <row r="960" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A960" t="s">
-        <v>60</v>
-      </c>
-      <c r="B960" s="27">
-        <v>370</v>
-      </c>
-      <c r="C960" t="s">
-        <v>105</v>
-      </c>
-      <c r="E960" t="s">
-        <v>1261</v>
-      </c>
-      <c r="G960" t="s">
-        <v>1004</v>
-      </c>
-      <c r="L960" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D960:J960)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0010_sbk_02.png</v>
+        <v>108</v>
       </c>
     </row>
     <row r="961" spans="1:12" x14ac:dyDescent="0.2">
@@ -28787,17 +28887,10 @@
         <v>370</v>
       </c>
       <c r="C961" t="s">
-        <v>105</v>
-      </c>
-      <c r="E961" t="s">
-        <v>1261</v>
-      </c>
-      <c r="G961" t="s">
-        <v>1005</v>
-      </c>
-      <c r="L961" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D961:J961)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0020_sbk_03.png</v>
+        <v>39</v>
+      </c>
+      <c r="L961" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="962" spans="1:12" x14ac:dyDescent="0.2">
@@ -28814,20 +28907,11 @@
         <v>1261</v>
       </c>
       <c r="G962" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I962" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J962" t="s">
-        <v>1153</v>
-      </c>
-      <c r="K962" t="s">
-        <v>1200</v>
+        <v>1003</v>
       </c>
       <c r="L962" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D962:K962)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0030_sbk_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+        <f>_xlfn.TEXTJOIN("", TRUE, D962:J962)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0001_sbk_01.png</v>
       </c>
     </row>
     <row r="963" spans="1:12" x14ac:dyDescent="0.2">
@@ -28838,20 +28922,17 @@
         <v>370</v>
       </c>
       <c r="C963" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E963" t="s">
         <v>1261</v>
       </c>
-      <c r="F963" t="s">
-        <v>111</v>
-      </c>
       <c r="G963" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="L963" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, D963:J963)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/det/0001_sbk_det_01.png</v>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0010_sbk_02.png</v>
       </c>
     </row>
     <row r="964" spans="1:12" x14ac:dyDescent="0.2">
@@ -28862,10 +28943,17 @@
         <v>370</v>
       </c>
       <c r="C964" t="s">
-        <v>107</v>
-      </c>
-      <c r="L964" t="s">
-        <v>162</v>
+        <v>105</v>
+      </c>
+      <c r="E964" t="s">
+        <v>1261</v>
+      </c>
+      <c r="G964" t="s">
+        <v>1005</v>
+      </c>
+      <c r="L964" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D964:J964)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0020_sbk_03.png</v>
       </c>
     </row>
     <row r="965" spans="1:12" x14ac:dyDescent="0.2">
@@ -28876,7 +28964,64 @@
         <v>370</v>
       </c>
       <c r="C965" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="E965" t="s">
+        <v>1261</v>
+      </c>
+      <c r="G965" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I965" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J965" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K965" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L965" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D965:K965)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0030_sbk_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="966" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A966" t="s">
+        <v>60</v>
+      </c>
+      <c r="B966" s="27">
+        <v>370</v>
+      </c>
+      <c r="C966" t="s">
+        <v>106</v>
+      </c>
+      <c r="E966" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F966" t="s">
+        <v>111</v>
+      </c>
+      <c r="G966" t="s">
+        <v>1007</v>
+      </c>
+      <c r="L966" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D966:J966)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/det/0001_sbk_det_01.png</v>
+      </c>
+    </row>
+    <row r="967" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A967" t="s">
+        <v>60</v>
+      </c>
+      <c r="B967" s="27">
+        <v>370</v>
+      </c>
+      <c r="C967" t="s">
+        <v>107</v>
+      </c>
+      <c r="L967" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="968" spans="1:12" x14ac:dyDescent="0.2">
@@ -28884,269 +29029,269 @@
         <v>60</v>
       </c>
       <c r="B968" s="27">
+        <v>370</v>
+      </c>
+      <c r="C968" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="971" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A971" t="s">
+        <v>60</v>
+      </c>
+      <c r="B971" s="27">
         <v>380</v>
       </c>
-      <c r="C968" t="s">
+      <c r="C971" t="s">
         <v>39</v>
       </c>
-      <c r="L968" t="s">
+      <c r="L971" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="969" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A969" t="s">
-        <v>60</v>
-      </c>
-      <c r="B969" s="27">
+    <row r="972" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A972" t="s">
+        <v>60</v>
+      </c>
+      <c r="B972" s="27">
         <v>380</v>
       </c>
-      <c r="C969" t="s">
-        <v>105</v>
-      </c>
-      <c r="E969" t="s">
+      <c r="C972" t="s">
+        <v>105</v>
+      </c>
+      <c r="E972" t="s">
         <v>1262</v>
       </c>
-      <c r="G969" t="s">
+      <c r="G972" t="s">
         <v>1008</v>
       </c>
-      <c r="L969" t="str">
-        <f t="shared" ref="L969:L977" si="127">_xlfn.TEXTJOIN("", TRUE, D969:J969)</f>
+      <c r="L972" t="str">
+        <f t="shared" ref="L972:L980" si="127">_xlfn.TEXTJOIN("", TRUE, D972:J972)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0001_srq.t_01.png</v>
       </c>
     </row>
-    <row r="970" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A970" t="s">
-        <v>60</v>
-      </c>
-      <c r="B970" s="27">
+    <row r="973" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A973" t="s">
+        <v>60</v>
+      </c>
+      <c r="B973" s="27">
         <v>380</v>
       </c>
-      <c r="C970" t="s">
-        <v>105</v>
-      </c>
-      <c r="E970" t="s">
+      <c r="C973" t="s">
+        <v>105</v>
+      </c>
+      <c r="E973" t="s">
         <v>1262</v>
       </c>
-      <c r="G970" t="s">
+      <c r="G973" t="s">
         <v>1009</v>
       </c>
-      <c r="L970" t="str">
+      <c r="L973" t="str">
         <f t="shared" si="127"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0010_srq.t_02.png</v>
       </c>
     </row>
-    <row r="971" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A971" t="s">
-        <v>60</v>
-      </c>
-      <c r="B971" s="27">
+    <row r="974" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A974" t="s">
+        <v>60</v>
+      </c>
+      <c r="B974" s="27">
         <v>380</v>
       </c>
-      <c r="C971" t="s">
-        <v>105</v>
-      </c>
-      <c r="E971" t="s">
+      <c r="C974" t="s">
+        <v>105</v>
+      </c>
+      <c r="E974" t="s">
         <v>1262</v>
       </c>
-      <c r="G971" t="s">
+      <c r="G974" t="s">
         <v>1010</v>
       </c>
-      <c r="L971" t="str">
+      <c r="L974" t="str">
         <f t="shared" si="127"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0020_srq.t_03.png</v>
       </c>
     </row>
-    <row r="972" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A972" t="s">
-        <v>60</v>
-      </c>
-      <c r="B972" s="27">
+    <row r="975" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A975" t="s">
+        <v>60</v>
+      </c>
+      <c r="B975" s="27">
         <v>380</v>
       </c>
-      <c r="C972" t="s">
-        <v>105</v>
-      </c>
-      <c r="E972" t="s">
+      <c r="C975" t="s">
+        <v>105</v>
+      </c>
+      <c r="E975" t="s">
         <v>1262</v>
       </c>
-      <c r="G972" t="s">
+      <c r="G975" t="s">
         <v>1011</v>
       </c>
-      <c r="I972" t="s">
+      <c r="I975" t="s">
         <v>1198</v>
       </c>
-      <c r="J972" t="s">
+      <c r="J975" t="s">
         <v>1215</v>
       </c>
-      <c r="K972" t="s">
+      <c r="K975" t="s">
         <v>1200</v>
       </c>
-      <c r="L972" t="str">
-        <f t="shared" ref="L972:L975" si="128">_xlfn.TEXTJOIN("", TRUE, D972:K972)</f>
+      <c r="L975" t="str">
+        <f t="shared" ref="L975:L978" si="128">_xlfn.TEXTJOIN("", TRUE, D975:K975)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0030_srq.t_Pyr.-MR_01.png &lt;sup&gt;(Pyr.; NR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="973" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A973" t="s">
-        <v>60</v>
-      </c>
-      <c r="B973" s="27">
+    <row r="976" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A976" t="s">
+        <v>60</v>
+      </c>
+      <c r="B976" s="27">
         <v>380</v>
       </c>
-      <c r="C973" t="s">
-        <v>105</v>
-      </c>
-      <c r="E973" t="s">
+      <c r="C976" t="s">
+        <v>105</v>
+      </c>
+      <c r="E976" t="s">
         <v>1262</v>
       </c>
-      <c r="G973" t="s">
+      <c r="G976" t="s">
         <v>1012</v>
       </c>
-      <c r="I973" t="s">
+      <c r="I976" t="s">
         <v>1198</v>
       </c>
-      <c r="J973" t="s">
+      <c r="J976" t="s">
         <v>1201</v>
       </c>
-      <c r="K973" t="s">
+      <c r="K976" t="s">
         <v>1200</v>
       </c>
-      <c r="L973" t="str">
+      <c r="L976" t="str">
         <f t="shared" si="128"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0040_srq.t_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="974" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A974" t="s">
-        <v>60</v>
-      </c>
-      <c r="B974" s="27">
+    <row r="977" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A977" t="s">
+        <v>60</v>
+      </c>
+      <c r="B977" s="27">
         <v>380</v>
       </c>
-      <c r="C974" t="s">
-        <v>105</v>
-      </c>
-      <c r="E974" t="s">
+      <c r="C977" t="s">
+        <v>105</v>
+      </c>
+      <c r="E977" t="s">
         <v>1262</v>
       </c>
-      <c r="G974" t="s">
+      <c r="G977" t="s">
         <v>1013</v>
       </c>
-      <c r="I974" t="s">
+      <c r="I977" t="s">
         <v>1198</v>
       </c>
-      <c r="J974" t="s">
+      <c r="J977" t="s">
         <v>1201</v>
       </c>
-      <c r="K974" t="s">
+      <c r="K977" t="s">
         <v>1200</v>
       </c>
-      <c r="L974" t="str">
+      <c r="L977" t="str">
         <f t="shared" si="128"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0050_srq.t_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="975" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A975" t="s">
-        <v>60</v>
-      </c>
-      <c r="B975" s="27">
+    <row r="978" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A978" t="s">
+        <v>60</v>
+      </c>
+      <c r="B978" s="27">
         <v>380</v>
       </c>
-      <c r="C975" t="s">
-        <v>105</v>
-      </c>
-      <c r="E975" t="s">
+      <c r="C978" t="s">
+        <v>105</v>
+      </c>
+      <c r="E978" t="s">
         <v>1262</v>
       </c>
-      <c r="G975" t="s">
+      <c r="G978" t="s">
         <v>1014</v>
       </c>
-      <c r="I975" t="s">
+      <c r="I978" t="s">
         <v>1198</v>
       </c>
-      <c r="J975" t="s">
+      <c r="J978" t="s">
         <v>1201</v>
       </c>
-      <c r="K975" t="s">
+      <c r="K978" t="s">
         <v>1200</v>
       </c>
-      <c r="L975" t="str">
+      <c r="L978" t="str">
         <f t="shared" si="128"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0060_srq.t_GR_03.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="976" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A976" t="s">
-        <v>60</v>
-      </c>
-      <c r="B976" s="27">
+    <row r="979" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A979" t="s">
+        <v>60</v>
+      </c>
+      <c r="B979" s="27">
         <v>380</v>
       </c>
-      <c r="C976" t="s">
+      <c r="C979" t="s">
         <v>106</v>
       </c>
-      <c r="E976" t="s">
+      <c r="E979" t="s">
         <v>1262</v>
       </c>
-      <c r="F976" t="s">
+      <c r="F979" t="s">
         <v>111</v>
       </c>
-      <c r="G976" t="s">
+      <c r="G979" t="s">
         <v>1015</v>
       </c>
-      <c r="L976" t="str">
+      <c r="L979" t="str">
         <f t="shared" si="127"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/det/0001_srq.t_det_01.png</v>
       </c>
     </row>
-    <row r="977" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A977" t="s">
-        <v>60</v>
-      </c>
-      <c r="B977" s="27">
+    <row r="980" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A980" t="s">
+        <v>60</v>
+      </c>
+      <c r="B980" s="27">
         <v>380</v>
       </c>
-      <c r="C977" t="s">
+      <c r="C980" t="s">
         <v>106</v>
       </c>
-      <c r="E977" t="s">
+      <c r="E980" t="s">
         <v>1262</v>
       </c>
-      <c r="F977" t="s">
+      <c r="F980" t="s">
         <v>111</v>
       </c>
-      <c r="G977" t="s">
+      <c r="G980" t="s">
         <v>1016</v>
       </c>
-      <c r="L977" t="str">
+      <c r="L980" t="str">
         <f t="shared" si="127"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/det/0010_srq.t_det_02.png</v>
       </c>
     </row>
-    <row r="978" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A978" t="s">
-        <v>60</v>
-      </c>
-      <c r="B978" s="27">
+    <row r="981" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A981" t="s">
+        <v>60</v>
+      </c>
+      <c r="B981" s="27">
         <v>380</v>
       </c>
-      <c r="C978" t="s">
+      <c r="C981" t="s">
         <v>107</v>
       </c>
-      <c r="L978" t="s">
+      <c r="L981" t="s">
         <v>163</v>
-      </c>
-    </row>
-    <row r="979" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A979" t="s">
-        <v>60</v>
-      </c>
-      <c r="B979" s="27">
-        <v>380</v>
-      </c>
-      <c r="C979" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="982" spans="1:12" x14ac:dyDescent="0.2">
@@ -29154,64 +29299,10 @@
         <v>60</v>
       </c>
       <c r="B982" s="27">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C982" t="s">
-        <v>39</v>
-      </c>
-      <c r="L982" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="983" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A983" t="s">
-        <v>60</v>
-      </c>
-      <c r="B983" s="27">
-        <v>390</v>
-      </c>
-      <c r="C983" t="s">
-        <v>105</v>
-      </c>
-      <c r="E983" t="s">
-        <v>1263</v>
-      </c>
-      <c r="G983" t="s">
-        <v>1017</v>
-      </c>
-      <c r="L983" t="str">
-        <f t="shared" ref="L983:L989" si="129">_xlfn.TEXTJOIN("", TRUE, D983:J983)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0001_sxm.t_01.png</v>
-      </c>
-    </row>
-    <row r="984" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A984" t="s">
-        <v>60</v>
-      </c>
-      <c r="B984" s="27">
-        <v>390</v>
-      </c>
-      <c r="C984" t="s">
-        <v>105</v>
-      </c>
-      <c r="E984" t="s">
-        <v>1263</v>
-      </c>
-      <c r="G984" t="s">
-        <v>1018</v>
-      </c>
-      <c r="I984" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J984" t="s">
-        <v>1199</v>
-      </c>
-      <c r="K984" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L984" t="str">
-        <f t="shared" ref="L984:L988" si="130">_xlfn.TEXTJOIN("", TRUE, D984:K984)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0010_sxm.t_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <v>108</v>
       </c>
     </row>
     <row r="985" spans="1:12" x14ac:dyDescent="0.2">
@@ -29222,156 +29313,210 @@
         <v>390</v>
       </c>
       <c r="C985" t="s">
-        <v>105</v>
-      </c>
-      <c r="E985" t="s">
+        <v>39</v>
+      </c>
+      <c r="L985" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="986" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A986" t="s">
+        <v>60</v>
+      </c>
+      <c r="B986" s="27">
+        <v>390</v>
+      </c>
+      <c r="C986" t="s">
+        <v>105</v>
+      </c>
+      <c r="E986" t="s">
         <v>1263</v>
       </c>
-      <c r="G985" t="s">
+      <c r="G986" t="s">
+        <v>1017</v>
+      </c>
+      <c r="L986" t="str">
+        <f t="shared" ref="L986:L992" si="129">_xlfn.TEXTJOIN("", TRUE, D986:J986)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0001_sxm.t_01.png</v>
+      </c>
+    </row>
+    <row r="987" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A987" t="s">
+        <v>60</v>
+      </c>
+      <c r="B987" s="27">
+        <v>390</v>
+      </c>
+      <c r="C987" t="s">
+        <v>105</v>
+      </c>
+      <c r="E987" t="s">
+        <v>1263</v>
+      </c>
+      <c r="G987" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I987" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J987" t="s">
+        <v>1199</v>
+      </c>
+      <c r="K987" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L987" t="str">
+        <f t="shared" ref="L987:L991" si="130">_xlfn.TEXTJOIN("", TRUE, D987:K987)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0010_sxm.t_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="988" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A988" t="s">
+        <v>60</v>
+      </c>
+      <c r="B988" s="27">
+        <v>390</v>
+      </c>
+      <c r="C988" t="s">
+        <v>105</v>
+      </c>
+      <c r="E988" t="s">
+        <v>1263</v>
+      </c>
+      <c r="G988" t="s">
         <v>1019</v>
       </c>
-      <c r="I985" t="s">
+      <c r="I988" t="s">
         <v>1198</v>
       </c>
-      <c r="J985" t="s">
+      <c r="J988" t="s">
         <v>1199</v>
       </c>
-      <c r="K985" t="s">
+      <c r="K988" t="s">
         <v>1200</v>
       </c>
-      <c r="L985" t="str">
+      <c r="L988" t="str">
         <f t="shared" si="130"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0020_sxm.t_AR_02.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="986" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A986" t="s">
-        <v>60</v>
-      </c>
-      <c r="B986" s="27">
+    <row r="989" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A989" t="s">
+        <v>60</v>
+      </c>
+      <c r="B989" s="27">
         <v>390</v>
       </c>
-      <c r="C986" t="s">
-        <v>105</v>
-      </c>
-      <c r="E986" t="s">
+      <c r="C989" t="s">
+        <v>105</v>
+      </c>
+      <c r="E989" t="s">
         <v>1263</v>
       </c>
-      <c r="G986" t="s">
+      <c r="G989" t="s">
         <v>1020</v>
       </c>
-      <c r="I986" t="s">
+      <c r="I989" t="s">
         <v>1198</v>
       </c>
-      <c r="J986" t="s">
+      <c r="J989" t="s">
         <v>1153</v>
       </c>
-      <c r="K986" t="s">
+      <c r="K989" t="s">
         <v>1200</v>
       </c>
-      <c r="L986" t="str">
+      <c r="L989" t="str">
         <f t="shared" si="130"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0030_sxm.t_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="987" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A987" t="s">
-        <v>60</v>
-      </c>
-      <c r="B987" s="27">
+    <row r="990" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A990" t="s">
+        <v>60</v>
+      </c>
+      <c r="B990" s="27">
         <v>390</v>
       </c>
-      <c r="C987" t="s">
-        <v>105</v>
-      </c>
-      <c r="E987" t="s">
+      <c r="C990" t="s">
+        <v>105</v>
+      </c>
+      <c r="E990" t="s">
         <v>1263</v>
       </c>
-      <c r="G987" t="s">
+      <c r="G990" t="s">
         <v>1021</v>
       </c>
-      <c r="I987" t="s">
+      <c r="I990" t="s">
         <v>1198</v>
       </c>
-      <c r="J987" t="s">
+      <c r="J990" t="s">
         <v>1201</v>
       </c>
-      <c r="K987" t="s">
+      <c r="K990" t="s">
         <v>1200</v>
       </c>
-      <c r="L987" t="str">
+      <c r="L990" t="str">
         <f t="shared" si="130"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0040_sxm.t_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="988" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A988" t="s">
-        <v>60</v>
-      </c>
-      <c r="B988" s="27">
+    <row r="991" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A991" t="s">
+        <v>60</v>
+      </c>
+      <c r="B991" s="27">
         <v>390</v>
       </c>
-      <c r="C988" t="s">
-        <v>105</v>
-      </c>
-      <c r="E988" t="s">
+      <c r="C991" t="s">
+        <v>105</v>
+      </c>
+      <c r="E991" t="s">
         <v>1263</v>
       </c>
-      <c r="G988" t="s">
+      <c r="G991" t="s">
         <v>1022</v>
       </c>
-      <c r="I988" t="s">
+      <c r="I991" t="s">
         <v>1198</v>
       </c>
-      <c r="J988" t="s">
+      <c r="J991" t="s">
         <v>1201</v>
       </c>
-      <c r="K988" t="s">
+      <c r="K991" t="s">
         <v>1200</v>
       </c>
-      <c r="L988" t="str">
+      <c r="L991" t="str">
         <f t="shared" si="130"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0050_sxm.t_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="989" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A989" t="s">
-        <v>60</v>
-      </c>
-      <c r="B989" s="27">
+    <row r="992" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A992" t="s">
+        <v>60</v>
+      </c>
+      <c r="B992" s="27">
         <v>390</v>
       </c>
-      <c r="C989" t="s">
+      <c r="C992" t="s">
         <v>106</v>
       </c>
-      <c r="L989" t="str">
+      <c r="L992" t="str">
         <f t="shared" si="129"/>
         <v/>
       </c>
     </row>
-    <row r="990" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A990" t="s">
-        <v>60</v>
-      </c>
-      <c r="B990" s="27">
+    <row r="993" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A993" t="s">
+        <v>60</v>
+      </c>
+      <c r="B993" s="27">
         <v>390</v>
       </c>
-      <c r="C990" t="s">
+      <c r="C993" t="s">
         <v>107</v>
       </c>
-      <c r="L990" t="s">
+      <c r="L993" t="s">
         <v>164</v>
-      </c>
-    </row>
-    <row r="991" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A991" t="s">
-        <v>60</v>
-      </c>
-      <c r="B991" s="27">
-        <v>390</v>
-      </c>
-      <c r="C991" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="994" spans="1:12" x14ac:dyDescent="0.2">
@@ -29379,58 +29524,10 @@
         <v>60</v>
       </c>
       <c r="B994" s="27">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C994" t="s">
-        <v>39</v>
-      </c>
-      <c r="L994" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="995" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A995" t="s">
-        <v>60</v>
-      </c>
-      <c r="B995" s="27">
-        <v>400</v>
-      </c>
-      <c r="C995" t="s">
-        <v>105</v>
-      </c>
-      <c r="E995" t="s">
-        <v>1264</v>
-      </c>
-      <c r="G995" t="s">
-        <v>1023</v>
-      </c>
-      <c r="L995" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D995:J995)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0400_Sokar/0001_skr_01.png</v>
-      </c>
-    </row>
-    <row r="996" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A996" t="s">
-        <v>60</v>
-      </c>
-      <c r="B996" s="27">
-        <v>400</v>
-      </c>
-      <c r="C996" t="s">
-        <v>106</v>
-      </c>
-      <c r="E996" t="s">
-        <v>1264</v>
-      </c>
-      <c r="F996" t="s">
-        <v>111</v>
-      </c>
-      <c r="G996" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L996" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D996:J996)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0400_Sokar/det/0001_skr_det_01.png</v>
+        <v>108</v>
       </c>
     </row>
     <row r="997" spans="1:12" x14ac:dyDescent="0.2">
@@ -29441,10 +29538,10 @@
         <v>400</v>
       </c>
       <c r="C997" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="L997" t="s">
-        <v>165</v>
+        <v>726</v>
       </c>
     </row>
     <row r="998" spans="1:12" x14ac:dyDescent="0.2">
@@ -29455,7 +29552,55 @@
         <v>400</v>
       </c>
       <c r="C998" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="E998" t="s">
+        <v>1264</v>
+      </c>
+      <c r="G998" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L998" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D998:J998)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0400_Sokar/0001_skr_01.png</v>
+      </c>
+    </row>
+    <row r="999" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A999" t="s">
+        <v>60</v>
+      </c>
+      <c r="B999" s="27">
+        <v>400</v>
+      </c>
+      <c r="C999" t="s">
+        <v>106</v>
+      </c>
+      <c r="E999" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F999" t="s">
+        <v>111</v>
+      </c>
+      <c r="G999" t="s">
+        <v>1024</v>
+      </c>
+      <c r="L999" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D999:J999)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0400_Sokar/det/0001_skr_det_01.png</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1000" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1000" s="27">
+        <v>400</v>
+      </c>
+      <c r="C1000" t="s">
+        <v>107</v>
+      </c>
+      <c r="L1000" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="1001" spans="1:12" x14ac:dyDescent="0.2">
@@ -29463,64 +29608,10 @@
         <v>60</v>
       </c>
       <c r="B1001" s="27">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C1001" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1001" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="1002" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1002" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1002" s="27">
-        <v>410</v>
-      </c>
-      <c r="C1002" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1002" t="s">
-        <v>1265</v>
-      </c>
-      <c r="G1002" t="s">
-        <v>1041</v>
-      </c>
-      <c r="L1002" t="str">
-        <f t="shared" ref="L1002:L1015" si="131">_xlfn.TEXTJOIN("", TRUE, D1002:J1002)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0001_stX_01.png</v>
-      </c>
-    </row>
-    <row r="1003" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1003" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1003" s="27">
-        <v>410</v>
-      </c>
-      <c r="C1003" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1003" t="s">
-        <v>1265</v>
-      </c>
-      <c r="G1003" t="s">
-        <v>1042</v>
-      </c>
-      <c r="I1003" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J1003" t="s">
-        <v>1199</v>
-      </c>
-      <c r="K1003" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L1003" t="str">
-        <f t="shared" ref="L1003:L1013" si="132">_xlfn.TEXTJOIN("", TRUE, D1003:K1003)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0010_stX_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1004" spans="1:12" x14ac:dyDescent="0.2">
@@ -29531,402 +29622,456 @@
         <v>410</v>
       </c>
       <c r="C1004" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1004" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1004" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1005" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1005" s="27">
+        <v>410</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1005" t="s">
         <v>1265</v>
       </c>
-      <c r="G1004" t="s">
+      <c r="G1005" t="s">
+        <v>1041</v>
+      </c>
+      <c r="L1005" t="str">
+        <f t="shared" ref="L1005:L1018" si="131">_xlfn.TEXTJOIN("", TRUE, D1005:J1005)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0001_stX_01.png</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1006" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1006" s="27">
+        <v>410</v>
+      </c>
+      <c r="C1006" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1006" t="s">
+        <v>1265</v>
+      </c>
+      <c r="G1006" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I1006" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J1006" t="s">
+        <v>1199</v>
+      </c>
+      <c r="K1006" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L1006" t="str">
+        <f t="shared" ref="L1006:L1016" si="132">_xlfn.TEXTJOIN("", TRUE, D1006:K1006)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0010_stX_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1007" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1007" s="27">
+        <v>410</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1007" t="s">
+        <v>1265</v>
+      </c>
+      <c r="G1007" t="s">
         <v>1043</v>
       </c>
-      <c r="I1004" t="s">
+      <c r="I1007" t="s">
         <v>1198</v>
       </c>
-      <c r="J1004" t="s">
+      <c r="J1007" t="s">
         <v>1202</v>
       </c>
-      <c r="K1004" t="s">
+      <c r="K1007" t="s">
         <v>1200</v>
       </c>
-      <c r="L1004" t="str">
+      <c r="L1007" t="str">
         <f t="shared" si="132"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0020_stX_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1005" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1005" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1005" s="27">
+    <row r="1008" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1008" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1008" s="27">
         <v>410</v>
       </c>
-      <c r="C1005" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1005" t="s">
+      <c r="C1008" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1008" t="s">
         <v>1265</v>
       </c>
-      <c r="G1005" t="s">
+      <c r="G1008" t="s">
         <v>1044</v>
       </c>
-      <c r="I1005" t="s">
+      <c r="I1008" t="s">
         <v>1198</v>
       </c>
-      <c r="J1005" t="s">
+      <c r="J1008" t="s">
         <v>1216</v>
       </c>
-      <c r="K1005" t="s">
+      <c r="K1008" t="s">
         <v>1200</v>
       </c>
-      <c r="L1005" t="str">
+      <c r="L1008" t="str">
         <f t="shared" si="132"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0030_stX_MR-SP_01.png &lt;sup&gt;(MR; Sp.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1006" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1006" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1006" s="27">
+    <row r="1009" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1009" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1009" s="27">
         <v>410</v>
       </c>
-      <c r="C1006" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1006" t="s">
+      <c r="C1009" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1009" t="s">
         <v>1265</v>
       </c>
-      <c r="G1006" t="s">
+      <c r="G1009" t="s">
         <v>1045</v>
       </c>
-      <c r="I1006" t="s">
+      <c r="I1009" t="s">
         <v>1198</v>
       </c>
-      <c r="J1006" t="s">
+      <c r="J1009" t="s">
         <v>1153</v>
       </c>
-      <c r="K1006" t="s">
+      <c r="K1009" t="s">
         <v>1200</v>
       </c>
-      <c r="L1006" t="str">
+      <c r="L1009" t="str">
         <f t="shared" si="132"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0040_stX_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1007" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1007" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1007" s="27">
+    <row r="1010" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1010" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1010" s="27">
         <v>410</v>
       </c>
-      <c r="C1007" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1007" t="s">
+      <c r="C1010" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1010" t="s">
         <v>1265</v>
       </c>
-      <c r="G1007" t="s">
+      <c r="G1010" t="s">
         <v>1046</v>
       </c>
-      <c r="I1007" t="s">
+      <c r="I1010" t="s">
         <v>1198</v>
       </c>
-      <c r="J1007" t="s">
+      <c r="J1010" t="s">
         <v>1206</v>
       </c>
-      <c r="K1007" t="s">
+      <c r="K1010" t="s">
         <v>1200</v>
       </c>
-      <c r="L1007" t="str">
+      <c r="L1010" t="str">
         <f t="shared" si="132"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0050_stX_D.18_01.png &lt;sup&gt;(D.18)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1008" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1008" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1008" s="27">
+    <row r="1011" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1011" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1011" s="27">
         <v>410</v>
       </c>
-      <c r="C1008" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1008" t="s">
+      <c r="C1011" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1011" t="s">
         <v>1265</v>
       </c>
-      <c r="G1008" t="s">
+      <c r="G1011" t="s">
         <v>1047</v>
       </c>
-      <c r="I1008" t="s">
+      <c r="I1011" t="s">
         <v>1198</v>
       </c>
-      <c r="J1008" t="s">
+      <c r="J1011" t="s">
         <v>1206</v>
       </c>
-      <c r="K1008" t="s">
+      <c r="K1011" t="s">
         <v>1200</v>
       </c>
-      <c r="L1008" t="str">
+      <c r="L1011" t="str">
         <f t="shared" si="132"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0060_stX_D.18_02.png &lt;sup&gt;(D.18)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1009" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1009" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1009" s="27">
+    <row r="1012" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1012" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1012" s="27">
         <v>410</v>
       </c>
-      <c r="C1009" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1009" t="s">
+      <c r="C1012" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1012" t="s">
         <v>1265</v>
       </c>
-      <c r="G1009" t="s">
+      <c r="G1012" t="s">
         <v>1048</v>
       </c>
-      <c r="I1009" t="s">
+      <c r="I1012" t="s">
         <v>1198</v>
       </c>
-      <c r="J1009" t="s">
+      <c r="J1012" t="s">
         <v>1206</v>
       </c>
-      <c r="K1009" t="s">
+      <c r="K1012" t="s">
         <v>1200</v>
       </c>
-      <c r="L1009" t="str">
+      <c r="L1012" t="str">
         <f t="shared" si="132"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0070_stX_D.18_03.png &lt;sup&gt;(D.18)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1010" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1010" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1010" s="27">
+    <row r="1013" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1013" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1013" s="27">
         <v>410</v>
       </c>
-      <c r="C1010" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1010" t="s">
+      <c r="C1013" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1013" t="s">
         <v>1265</v>
       </c>
-      <c r="G1010" t="s">
+      <c r="G1013" t="s">
         <v>1049</v>
       </c>
-      <c r="I1010" t="s">
+      <c r="I1013" t="s">
         <v>1198</v>
       </c>
-      <c r="J1010" t="s">
+      <c r="J1013" t="s">
         <v>1211</v>
       </c>
-      <c r="K1010" t="s">
+      <c r="K1013" t="s">
         <v>1200</v>
       </c>
-      <c r="L1010" t="str">
+      <c r="L1013" t="str">
         <f t="shared" si="132"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0080_stX_D.19_01.png &lt;sup&gt;(D.19)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1011" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1011" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1011" s="27">
+    <row r="1014" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1014" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1014" s="27">
         <v>410</v>
       </c>
-      <c r="C1011" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1011" t="s">
+      <c r="C1014" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1014" t="s">
         <v>1265</v>
       </c>
-      <c r="G1011" t="s">
+      <c r="G1014" t="s">
         <v>1050</v>
       </c>
-      <c r="I1011" t="s">
+      <c r="I1014" t="s">
         <v>1198</v>
       </c>
-      <c r="J1011" t="s">
+      <c r="J1014" t="s">
         <v>1211</v>
       </c>
-      <c r="K1011" t="s">
+      <c r="K1014" t="s">
         <v>1200</v>
       </c>
-      <c r="L1011" t="str">
+      <c r="L1014" t="str">
         <f t="shared" si="132"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0090_stX_D.19_02.png &lt;sup&gt;(D.19)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1012" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1012" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1012" s="27">
+    <row r="1015" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1015" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1015" s="27">
         <v>410</v>
       </c>
-      <c r="C1012" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1012" t="s">
+      <c r="C1015" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1015" t="s">
         <v>1265</v>
       </c>
-      <c r="G1012" t="s">
+      <c r="G1015" t="s">
         <v>1051</v>
       </c>
-      <c r="I1012" t="s">
+      <c r="I1015" t="s">
         <v>1198</v>
       </c>
-      <c r="J1012" t="s">
+      <c r="J1015" t="s">
         <v>1201</v>
       </c>
-      <c r="K1012" t="s">
+      <c r="K1015" t="s">
         <v>1200</v>
       </c>
-      <c r="L1012" t="str">
+      <c r="L1015" t="str">
         <f t="shared" si="132"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0100_stX_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1013" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1013" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1013" s="27">
+    <row r="1016" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1016" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1016" s="27">
         <v>410</v>
       </c>
-      <c r="C1013" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1013" t="s">
+      <c r="C1016" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1016" t="s">
         <v>1265</v>
       </c>
-      <c r="G1013" t="s">
+      <c r="G1016" t="s">
         <v>1040</v>
       </c>
-      <c r="I1013" t="s">
+      <c r="I1016" t="s">
         <v>1198</v>
       </c>
-      <c r="J1013" t="s">
+      <c r="J1016" t="s">
         <v>1201</v>
       </c>
-      <c r="K1013" t="s">
+      <c r="K1016" t="s">
         <v>1200</v>
       </c>
-      <c r="L1013" t="str">
+      <c r="L1016" t="str">
         <f t="shared" si="132"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0110_stX_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1014" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1014" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1014" s="27">
+    <row r="1017" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1017" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1017" s="27">
         <v>410</v>
       </c>
-      <c r="C1014" t="s">
+      <c r="C1017" t="s">
         <v>106</v>
       </c>
-      <c r="E1014" t="s">
+      <c r="E1017" t="s">
         <v>1265</v>
       </c>
-      <c r="F1014" t="s">
+      <c r="F1017" t="s">
         <v>111</v>
       </c>
-      <c r="G1014" t="s">
+      <c r="G1017" t="s">
         <v>1052</v>
       </c>
-      <c r="L1014" t="str">
+      <c r="L1017" t="str">
         <f t="shared" si="131"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/det/0001_stX_det_01.png</v>
       </c>
     </row>
-    <row r="1015" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1015" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1015" s="27">
+    <row r="1018" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1018" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1018" s="27">
         <v>410</v>
       </c>
-      <c r="C1015" t="s">
+      <c r="C1018" t="s">
         <v>106</v>
       </c>
-      <c r="E1015" t="s">
+      <c r="E1018" t="s">
         <v>1265</v>
       </c>
-      <c r="F1015" t="s">
+      <c r="F1018" t="s">
         <v>111</v>
       </c>
-      <c r="G1015" t="s">
+      <c r="G1018" t="s">
         <v>1053</v>
       </c>
-      <c r="L1015" t="str">
+      <c r="L1018" t="str">
         <f t="shared" si="131"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/det/0010_stX_det_02.png</v>
       </c>
     </row>
-    <row r="1016" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1016" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1016" s="27">
+    <row r="1019" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1019" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1019" s="27">
         <v>410</v>
       </c>
-      <c r="C1016" t="s">
+      <c r="C1019" t="s">
         <v>106</v>
       </c>
-      <c r="E1016" t="s">
+      <c r="E1019" t="s">
         <v>1265</v>
       </c>
-      <c r="F1016" t="s">
+      <c r="F1019" t="s">
         <v>111</v>
       </c>
-      <c r="G1016" t="s">
+      <c r="G1019" t="s">
         <v>1054</v>
       </c>
-      <c r="I1016" t="s">
+      <c r="I1019" t="s">
         <v>1198</v>
       </c>
-      <c r="J1016" t="s">
+      <c r="J1019" t="s">
         <v>1202</v>
       </c>
-      <c r="K1016" t="s">
+      <c r="K1019" t="s">
         <v>1200</v>
       </c>
-      <c r="L1016" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D1016:K1016)</f>
+      <c r="L1019" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D1019:K1019)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/det/0020_stX_det_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1017" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1017" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1017" s="27">
+    <row r="1020" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1020" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1020" s="27">
         <v>410</v>
       </c>
-      <c r="C1017" t="s">
+      <c r="C1020" t="s">
         <v>107</v>
       </c>
-      <c r="L1017" t="s">
+      <c r="L1020" t="s">
         <v>167</v>
-      </c>
-    </row>
-    <row r="1018" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1018" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1018" s="27">
-        <v>410</v>
-      </c>
-      <c r="C1018" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="1021" spans="1:12" x14ac:dyDescent="0.2">
@@ -29934,64 +30079,10 @@
         <v>60</v>
       </c>
       <c r="B1021" s="27">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C1021" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1021" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="1022" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1022" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1022" s="27">
-        <v>420</v>
-      </c>
-      <c r="C1022" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1022" t="s">
-        <v>1266</v>
-      </c>
-      <c r="G1022" t="s">
-        <v>1055</v>
-      </c>
-      <c r="L1022" t="str">
-        <f t="shared" ref="L1022:L1027" si="133">_xlfn.TEXTJOIN("", TRUE, D1022:J1022)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0001_Sw_01.png</v>
-      </c>
-    </row>
-    <row r="1023" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1023" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1023" s="27">
-        <v>420</v>
-      </c>
-      <c r="C1023" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1023" t="s">
-        <v>1266</v>
-      </c>
-      <c r="G1023" t="s">
-        <v>1056</v>
-      </c>
-      <c r="I1023" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J1023" t="s">
-        <v>1199</v>
-      </c>
-      <c r="K1023" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L1023" t="str">
-        <f t="shared" ref="L1023:L1026" si="134">_xlfn.TEXTJOIN("", TRUE, D1023:K1023)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0010_Sw_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1024" spans="1:12" x14ac:dyDescent="0.2">
@@ -30002,126 +30093,180 @@
         <v>420</v>
       </c>
       <c r="C1024" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1024" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1024" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1025" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1025" s="27">
+        <v>420</v>
+      </c>
+      <c r="C1025" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1025" t="s">
         <v>1266</v>
       </c>
-      <c r="G1024" t="s">
+      <c r="G1025" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L1025" t="str">
+        <f t="shared" ref="L1025:L1030" si="133">_xlfn.TEXTJOIN("", TRUE, D1025:J1025)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0001_Sw_01.png</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1026" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1026" s="27">
+        <v>420</v>
+      </c>
+      <c r="C1026" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1026" t="s">
+        <v>1266</v>
+      </c>
+      <c r="G1026" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I1026" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J1026" t="s">
+        <v>1199</v>
+      </c>
+      <c r="K1026" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L1026" t="str">
+        <f t="shared" ref="L1026:L1029" si="134">_xlfn.TEXTJOIN("", TRUE, D1026:K1026)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0010_Sw_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1027" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1027" s="27">
+        <v>420</v>
+      </c>
+      <c r="C1027" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1027" t="s">
+        <v>1266</v>
+      </c>
+      <c r="G1027" t="s">
         <v>1057</v>
       </c>
-      <c r="I1024" t="s">
+      <c r="I1027" t="s">
         <v>1198</v>
       </c>
-      <c r="J1024" t="s">
+      <c r="J1027" t="s">
         <v>1202</v>
       </c>
-      <c r="K1024" t="s">
+      <c r="K1027" t="s">
         <v>1200</v>
       </c>
-      <c r="L1024" t="str">
+      <c r="L1027" t="str">
         <f t="shared" si="134"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0020_Sw_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1025" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1025" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1025" s="27">
+    <row r="1028" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1028" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1028" s="27">
         <v>420</v>
       </c>
-      <c r="C1025" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1025" t="s">
+      <c r="C1028" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1028" t="s">
         <v>1266</v>
       </c>
-      <c r="G1025" t="s">
+      <c r="G1028" t="s">
         <v>1058</v>
       </c>
-      <c r="I1025" t="s">
+      <c r="I1028" t="s">
         <v>1198</v>
       </c>
-      <c r="J1025" t="s">
+      <c r="J1028" t="s">
         <v>1153</v>
       </c>
-      <c r="K1025" t="s">
+      <c r="K1028" t="s">
         <v>1200</v>
       </c>
-      <c r="L1025" t="str">
+      <c r="L1028" t="str">
         <f t="shared" si="134"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0030_Sw_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1026" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1026" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1026" s="27">
+    <row r="1029" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1029" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1029" s="27">
         <v>420</v>
       </c>
-      <c r="C1026" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1026" t="s">
+      <c r="C1029" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1029" t="s">
         <v>1266</v>
       </c>
-      <c r="G1026" t="s">
+      <c r="G1029" t="s">
         <v>1059</v>
       </c>
-      <c r="I1026" t="s">
+      <c r="I1029" t="s">
         <v>1198</v>
       </c>
-      <c r="J1026" t="s">
+      <c r="J1029" t="s">
         <v>1201</v>
       </c>
-      <c r="K1026" t="s">
+      <c r="K1029" t="s">
         <v>1200</v>
       </c>
-      <c r="L1026" t="str">
+      <c r="L1029" t="str">
         <f t="shared" si="134"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0040_Sw_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1027" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1027" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1027" s="27">
+    <row r="1030" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1030" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1030" s="27">
         <v>420</v>
       </c>
-      <c r="C1027" t="s">
+      <c r="C1030" t="s">
         <v>106</v>
       </c>
-      <c r="L1027" t="str">
+      <c r="L1030" t="str">
         <f t="shared" si="133"/>
         <v/>
       </c>
     </row>
-    <row r="1028" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1028" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1028" s="27">
+    <row r="1031" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1031" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1031" s="27">
         <v>420</v>
       </c>
-      <c r="C1028" t="s">
+      <c r="C1031" t="s">
         <v>107</v>
       </c>
-      <c r="L1028" t="s">
+      <c r="L1031" t="s">
         <v>168</v>
-      </c>
-    </row>
-    <row r="1029" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1029" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1029" s="27">
-        <v>420</v>
-      </c>
-      <c r="C1029" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="1032" spans="1:12" x14ac:dyDescent="0.2">
@@ -30129,347 +30274,347 @@
         <v>60</v>
       </c>
       <c r="B1032" s="27">
+        <v>420</v>
+      </c>
+      <c r="C1032" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1035" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1035" s="27">
         <v>430</v>
       </c>
-      <c r="C1032" t="s">
+      <c r="C1035" t="s">
         <v>39</v>
       </c>
-      <c r="L1032" t="s">
+      <c r="L1035" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="1033" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1033" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1033" s="27">
+    <row r="1036" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1036" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1036" s="27">
         <v>430</v>
       </c>
-      <c r="C1033" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1033" t="s">
+      <c r="C1036" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1036" t="s">
         <v>1267</v>
       </c>
-      <c r="G1033" t="s">
+      <c r="G1036" t="s">
         <v>1061</v>
       </c>
-      <c r="L1033" t="str">
-        <f t="shared" ref="L1033:L1035" si="135">_xlfn.TEXTJOIN("", TRUE, D1033:J1033)</f>
+      <c r="L1036" t="str">
+        <f t="shared" ref="L1036:L1038" si="135">_xlfn.TEXTJOIN("", TRUE, D1036:J1036)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0001_qbH-snw=f_01.png</v>
       </c>
     </row>
-    <row r="1034" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1034" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1034" s="27">
+    <row r="1037" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1037" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1037" s="27">
         <v>430</v>
       </c>
-      <c r="C1034" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1034" t="s">
+      <c r="C1037" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1037" t="s">
         <v>1267</v>
       </c>
-      <c r="G1034" t="s">
+      <c r="G1037" t="s">
         <v>1062</v>
       </c>
-      <c r="L1034" t="str">
+      <c r="L1037" t="str">
         <f t="shared" si="135"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0010_qbH-snw=f_02.png</v>
       </c>
     </row>
-    <row r="1035" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1035" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1035" s="27">
+    <row r="1038" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1038" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1038" s="27">
         <v>430</v>
       </c>
-      <c r="C1035" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1035" t="s">
+      <c r="C1038" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1038" t="s">
         <v>1267</v>
       </c>
-      <c r="G1035" t="s">
+      <c r="G1038" t="s">
         <v>1063</v>
       </c>
-      <c r="L1035" t="str">
+      <c r="L1038" t="str">
         <f t="shared" si="135"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0020_qbH-snw=f_03.png</v>
       </c>
     </row>
-    <row r="1036" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1036" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1036" s="27">
+    <row r="1039" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1039" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1039" s="27">
         <v>430</v>
       </c>
-      <c r="C1036" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1036" t="s">
+      <c r="C1039" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1039" t="s">
         <v>1267</v>
       </c>
-      <c r="G1036" t="s">
+      <c r="G1039" t="s">
         <v>1064</v>
       </c>
-      <c r="I1036" t="s">
+      <c r="I1039" t="s">
         <v>1198</v>
       </c>
-      <c r="J1036" t="s">
+      <c r="J1039" t="s">
         <v>1202</v>
       </c>
-      <c r="K1036" t="s">
+      <c r="K1039" t="s">
         <v>1200</v>
       </c>
-      <c r="L1036" t="str">
-        <f t="shared" ref="L1036:L1043" si="136">_xlfn.TEXTJOIN("", TRUE, D1036:K1036)</f>
+      <c r="L1039" t="str">
+        <f t="shared" ref="L1039:L1046" si="136">_xlfn.TEXTJOIN("", TRUE, D1039:K1039)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0030_qbH-snw=f_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1037" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1037" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1037" s="27">
+    <row r="1040" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1040" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1040" s="27">
         <v>430</v>
       </c>
-      <c r="C1037" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1037" t="s">
+      <c r="C1040" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1040" t="s">
         <v>1267</v>
       </c>
-      <c r="G1037" t="s">
+      <c r="G1040" t="s">
         <v>1065</v>
       </c>
-      <c r="I1037" t="s">
+      <c r="I1040" t="s">
         <v>1198</v>
       </c>
-      <c r="J1037" t="s">
+      <c r="J1040" t="s">
         <v>1202</v>
       </c>
-      <c r="K1037" t="s">
+      <c r="K1040" t="s">
         <v>1200</v>
       </c>
-      <c r="L1037" t="str">
+      <c r="L1040" t="str">
         <f t="shared" si="136"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0040_qbH-snw=f_MR_02.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1038" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1038" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1038" s="27">
+    <row r="1041" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1041" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1041" s="27">
         <v>430</v>
       </c>
-      <c r="C1038" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1038" t="s">
+      <c r="C1041" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1041" t="s">
         <v>1267</v>
       </c>
-      <c r="G1038" t="s">
+      <c r="G1041" t="s">
         <v>1066</v>
       </c>
-      <c r="I1038" t="s">
+      <c r="I1041" t="s">
         <v>1198</v>
       </c>
-      <c r="J1038" t="s">
+      <c r="J1041" t="s">
         <v>1201</v>
       </c>
-      <c r="K1038" t="s">
+      <c r="K1041" t="s">
         <v>1200</v>
       </c>
-      <c r="L1038" t="str">
+      <c r="L1041" t="str">
         <f t="shared" si="136"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0050_qbH-snw=f_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1039" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1039" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1039" s="27">
+    <row r="1042" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1042" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1042" s="27">
         <v>430</v>
       </c>
-      <c r="C1039" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1039" t="s">
+      <c r="C1042" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1042" t="s">
         <v>1267</v>
       </c>
-      <c r="G1039" t="s">
+      <c r="G1042" t="s">
         <v>1067</v>
       </c>
-      <c r="I1039" t="s">
+      <c r="I1042" t="s">
         <v>1198</v>
       </c>
-      <c r="J1039" t="s">
+      <c r="J1042" t="s">
         <v>1201</v>
       </c>
-      <c r="K1039" t="s">
+      <c r="K1042" t="s">
         <v>1200</v>
       </c>
-      <c r="L1039" t="str">
+      <c r="L1042" t="str">
         <f t="shared" si="136"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0060_qbH-snw=f_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1040" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1040" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1040" s="27">
+    <row r="1043" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1043" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1043" s="27">
         <v>430</v>
       </c>
-      <c r="C1040" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1040" t="s">
+      <c r="C1043" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1043" t="s">
         <v>1267</v>
       </c>
-      <c r="G1040" t="s">
+      <c r="G1043" t="s">
         <v>1068</v>
       </c>
-      <c r="I1040" t="s">
+      <c r="I1043" t="s">
         <v>1198</v>
       </c>
-      <c r="J1040" t="s">
+      <c r="J1043" t="s">
         <v>1201</v>
       </c>
-      <c r="K1040" t="s">
+      <c r="K1043" t="s">
         <v>1200</v>
       </c>
-      <c r="L1040" t="str">
+      <c r="L1043" t="str">
         <f t="shared" si="136"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0070_qbH-snw=f_GR_03.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1041" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1041" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1041" s="27">
+    <row r="1044" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1044" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1044" s="27">
         <v>430</v>
       </c>
-      <c r="C1041" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1041" t="s">
+      <c r="C1044" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1044" t="s">
         <v>1267</v>
       </c>
-      <c r="G1041" t="s">
+      <c r="G1044" t="s">
         <v>1060</v>
       </c>
-      <c r="I1041" t="s">
+      <c r="I1044" t="s">
         <v>1198</v>
       </c>
-      <c r="J1041" t="s">
+      <c r="J1044" t="s">
         <v>1201</v>
       </c>
-      <c r="K1041" t="s">
+      <c r="K1044" t="s">
         <v>1200</v>
       </c>
-      <c r="L1041" t="str">
+      <c r="L1044" t="str">
         <f t="shared" si="136"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0080_qbH-snw=f_GR_04.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1042" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1042" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1042" s="27">
+    <row r="1045" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1045" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1045" s="27">
         <v>430</v>
       </c>
-      <c r="C1042" t="s">
+      <c r="C1045" t="s">
         <v>106</v>
       </c>
-      <c r="E1042" t="s">
+      <c r="E1045" t="s">
         <v>1267</v>
       </c>
-      <c r="F1042" t="s">
+      <c r="F1045" t="s">
         <v>111</v>
       </c>
-      <c r="G1042" t="s">
+      <c r="G1045" t="s">
         <v>1069</v>
       </c>
-      <c r="I1042" t="s">
+      <c r="I1045" t="s">
         <v>1198</v>
       </c>
-      <c r="J1042" t="s">
+      <c r="J1045" t="s">
         <v>1201</v>
       </c>
-      <c r="K1042" t="s">
+      <c r="K1045" t="s">
         <v>1200</v>
       </c>
-      <c r="L1042" t="str">
+      <c r="L1045" t="str">
         <f t="shared" si="136"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/det/0001_qbH-snw=f_det_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1043" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1043" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1043" s="27">
+    <row r="1046" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1046" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1046" s="27">
         <v>430</v>
       </c>
-      <c r="C1043" t="s">
+      <c r="C1046" t="s">
         <v>106</v>
       </c>
-      <c r="E1043" t="s">
+      <c r="E1046" t="s">
         <v>1267</v>
       </c>
-      <c r="F1043" t="s">
+      <c r="F1046" t="s">
         <v>111</v>
       </c>
-      <c r="G1043" t="s">
+      <c r="G1046" t="s">
         <v>1070</v>
       </c>
-      <c r="I1043" t="s">
+      <c r="I1046" t="s">
         <v>1198</v>
       </c>
-      <c r="J1043" t="s">
+      <c r="J1046" t="s">
         <v>1201</v>
       </c>
-      <c r="K1043" t="s">
+      <c r="K1046" t="s">
         <v>1200</v>
       </c>
-      <c r="L1043" t="str">
+      <c r="L1046" t="str">
         <f t="shared" si="136"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/det/0010_qbH-snw=f_det_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1044" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1044" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1044" s="27">
+    <row r="1047" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1047" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1047" s="27">
         <v>430</v>
       </c>
-      <c r="C1044" t="s">
+      <c r="C1047" t="s">
         <v>107</v>
       </c>
-      <c r="L1044" t="s">
+      <c r="L1047" t="s">
         <v>169</v>
-      </c>
-    </row>
-    <row r="1045" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1045" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1045" s="27">
-        <v>430</v>
-      </c>
-      <c r="C1045" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="1048" spans="1:12" x14ac:dyDescent="0.2">
@@ -30477,203 +30622,203 @@
         <v>60</v>
       </c>
       <c r="B1048" s="27">
+        <v>430</v>
+      </c>
+      <c r="C1048" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1051" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1051" s="27">
         <v>440</v>
       </c>
-      <c r="C1048" t="s">
+      <c r="C1051" t="s">
         <v>39</v>
       </c>
-      <c r="L1048" t="s">
+      <c r="L1051" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="1049" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1049" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1049" s="27">
+    <row r="1052" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1052" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1052" s="27">
         <v>440</v>
       </c>
-      <c r="C1049" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1049" t="s">
+      <c r="C1052" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1052" t="s">
         <v>1268</v>
       </c>
-      <c r="G1049" t="s">
+      <c r="G1052" t="s">
         <v>1071</v>
       </c>
-      <c r="I1049" t="s">
+      <c r="I1052" t="s">
         <v>1198</v>
       </c>
-      <c r="J1049" t="s">
+      <c r="J1052" t="s">
         <v>1199</v>
       </c>
-      <c r="K1049" t="s">
+      <c r="K1052" t="s">
         <v>1200</v>
       </c>
-      <c r="L1049" t="str">
-        <f t="shared" ref="L1049:L1053" si="137">_xlfn.TEXTJOIN("", TRUE, D1049:K1049)</f>
+      <c r="L1052" t="str">
+        <f t="shared" ref="L1052:L1056" si="137">_xlfn.TEXTJOIN("", TRUE, D1052:K1052)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0440_Duamutef/0001_dwA-mw.t=f_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1050" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1050" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1050" s="27">
+    <row r="1053" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1053" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1053" s="27">
         <v>440</v>
       </c>
-      <c r="C1050" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1050" t="s">
+      <c r="C1053" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1053" t="s">
         <v>1268</v>
       </c>
-      <c r="G1050" t="s">
+      <c r="G1053" t="s">
         <v>1072</v>
       </c>
-      <c r="I1050" t="s">
+      <c r="I1053" t="s">
         <v>1198</v>
       </c>
-      <c r="J1050" t="s">
+      <c r="J1053" t="s">
         <v>1199</v>
       </c>
-      <c r="K1050" t="s">
+      <c r="K1053" t="s">
         <v>1200</v>
       </c>
-      <c r="L1050" t="str">
+      <c r="L1053" t="str">
         <f t="shared" si="137"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0440_Duamutef/0010_dwA-mw.t=f_AR_02.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1051" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1051" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1051" s="27">
+    <row r="1054" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1054" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1054" s="27">
         <v>440</v>
       </c>
-      <c r="C1051" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1051" t="s">
+      <c r="C1054" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1054" t="s">
         <v>1268</v>
       </c>
-      <c r="G1051" t="s">
+      <c r="G1054" t="s">
         <v>1073</v>
       </c>
-      <c r="I1051" t="s">
+      <c r="I1054" t="s">
         <v>1198</v>
       </c>
-      <c r="J1051" t="s">
+      <c r="J1054" t="s">
         <v>1202</v>
       </c>
-      <c r="K1051" t="s">
+      <c r="K1054" t="s">
         <v>1200</v>
       </c>
-      <c r="L1051" t="str">
+      <c r="L1054" t="str">
         <f t="shared" si="137"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0440_Duamutef/0020_dwA-mw.t=f_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1052" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1052" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1052" s="27">
+    <row r="1055" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1055" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1055" s="27">
         <v>440</v>
       </c>
-      <c r="C1052" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1052" t="s">
+      <c r="C1055" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1055" t="s">
         <v>1268</v>
       </c>
-      <c r="G1052" t="s">
+      <c r="G1055" t="s">
         <v>1074</v>
       </c>
-      <c r="I1052" t="s">
+      <c r="I1055" t="s">
         <v>1198</v>
       </c>
-      <c r="J1052" t="s">
+      <c r="J1055" t="s">
         <v>1202</v>
       </c>
-      <c r="K1052" t="s">
+      <c r="K1055" t="s">
         <v>1200</v>
       </c>
-      <c r="L1052" t="str">
+      <c r="L1055" t="str">
         <f t="shared" si="137"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0440_Duamutef/0030_dwA-mw.t=f_MR_02.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1053" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1053" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1053" s="27">
+    <row r="1056" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1056" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1056" s="27">
         <v>440</v>
       </c>
-      <c r="C1053" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1053" t="s">
+      <c r="C1056" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1056" t="s">
         <v>1268</v>
       </c>
-      <c r="G1053" t="s">
+      <c r="G1056" t="s">
         <v>1075</v>
       </c>
-      <c r="I1053" t="s">
+      <c r="I1056" t="s">
         <v>1198</v>
       </c>
-      <c r="J1053" t="s">
+      <c r="J1056" t="s">
         <v>1202</v>
       </c>
-      <c r="K1053" t="s">
+      <c r="K1056" t="s">
         <v>1200</v>
       </c>
-      <c r="L1053" t="str">
+      <c r="L1056" t="str">
         <f t="shared" si="137"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0440_Duamutef/0040_dwA-mw.t=f_MR_03.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1054" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1054" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1054" s="27">
+    <row r="1057" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1057" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1057" s="27">
         <v>440</v>
       </c>
-      <c r="C1054" t="s">
+      <c r="C1057" t="s">
         <v>106</v>
       </c>
-      <c r="L1054" t="str">
-        <f t="shared" ref="L1054" si="138">_xlfn.TEXTJOIN("", TRUE, D1054:J1054)</f>
+      <c r="L1057" t="str">
+        <f t="shared" ref="L1057" si="138">_xlfn.TEXTJOIN("", TRUE, D1057:J1057)</f>
         <v/>
       </c>
     </row>
-    <row r="1055" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1055" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1055" s="27">
+    <row r="1058" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1058" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1058" s="27">
         <v>440</v>
       </c>
-      <c r="C1055" t="s">
+      <c r="C1058" t="s">
         <v>107</v>
       </c>
-      <c r="L1055" t="s">
+      <c r="L1058" t="s">
         <v>170</v>
-      </c>
-    </row>
-    <row r="1056" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1056" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1056" s="27">
-        <v>440</v>
-      </c>
-      <c r="C1056" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="1059" spans="1:12" x14ac:dyDescent="0.2">
@@ -30681,423 +30826,382 @@
         <v>60</v>
       </c>
       <c r="B1059" s="27">
+        <v>440</v>
+      </c>
+      <c r="C1059" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1062" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1062" s="27">
         <v>450</v>
       </c>
-      <c r="C1059" t="s">
+      <c r="C1062" t="s">
         <v>39</v>
       </c>
-      <c r="L1059" t="s">
+      <c r="L1062" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="1060" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1060" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1060" s="27">
+    <row r="1063" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1063" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1063" s="27">
         <v>450</v>
       </c>
-      <c r="C1060" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1060" t="s">
+      <c r="C1063" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1063" t="s">
         <v>1269</v>
       </c>
-      <c r="G1060" t="s">
+      <c r="G1063" t="s">
         <v>1076</v>
       </c>
-      <c r="I1060" t="s">
+      <c r="I1063" t="s">
         <v>1198</v>
       </c>
-      <c r="J1060" t="s">
+      <c r="J1063" t="s">
         <v>1199</v>
       </c>
-      <c r="K1060" t="s">
+      <c r="K1063" t="s">
         <v>1200</v>
       </c>
-      <c r="L1060" t="str">
-        <f t="shared" ref="L1060:L1070" si="139">_xlfn.TEXTJOIN("", TRUE, D1060:K1060)</f>
+      <c r="L1063" t="str">
+        <f t="shared" ref="L1063:L1073" si="139">_xlfn.TEXTJOIN("", TRUE, D1063:K1063)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0001_DHwtj_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1061" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1061" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1061" s="27">
+    <row r="1064" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1064" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1064" s="27">
         <v>450</v>
       </c>
-      <c r="C1061" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1061" t="s">
+      <c r="C1064" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1064" t="s">
         <v>1269</v>
       </c>
-      <c r="G1061" t="s">
+      <c r="G1064" t="s">
         <v>1077</v>
       </c>
-      <c r="I1061" t="s">
+      <c r="I1064" t="s">
         <v>1198</v>
       </c>
-      <c r="J1061" t="s">
+      <c r="J1064" t="s">
         <v>1202</v>
       </c>
-      <c r="K1061" t="s">
+      <c r="K1064" t="s">
         <v>1200</v>
       </c>
-      <c r="L1061" t="str">
+      <c r="L1064" t="str">
         <f t="shared" si="139"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0010_DHwtj_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1062" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1062" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1062" s="27">
+    <row r="1065" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1065" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1065" s="27">
         <v>450</v>
       </c>
-      <c r="C1062" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1062" t="s">
+      <c r="C1065" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1065" t="s">
         <v>1269</v>
       </c>
-      <c r="G1062" t="s">
+      <c r="G1065" t="s">
         <v>1078</v>
       </c>
-      <c r="I1062" t="s">
+      <c r="I1065" t="s">
         <v>1198</v>
       </c>
-      <c r="J1062" t="s">
+      <c r="J1065" t="s">
         <v>1202</v>
       </c>
-      <c r="K1062" t="s">
+      <c r="K1065" t="s">
         <v>1200</v>
       </c>
-      <c r="L1062" t="str">
+      <c r="L1065" t="str">
         <f t="shared" si="139"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0020_DHwtj_MR_02.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1063" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1063" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1063" s="27">
+    <row r="1066" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1066" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1066" s="27">
         <v>450</v>
       </c>
-      <c r="C1063" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1063" t="s">
+      <c r="C1066" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1066" t="s">
         <v>1269</v>
       </c>
-      <c r="G1063" t="s">
+      <c r="G1066" t="s">
         <v>1079</v>
       </c>
-      <c r="I1063" t="s">
+      <c r="I1066" t="s">
         <v>1198</v>
       </c>
-      <c r="J1063" t="s">
+      <c r="J1066" t="s">
         <v>1202</v>
       </c>
-      <c r="K1063" t="s">
+      <c r="K1066" t="s">
         <v>1200</v>
       </c>
-      <c r="L1063" t="str">
+      <c r="L1066" t="str">
         <f t="shared" si="139"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0030_DHwtj_MR_03.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1064" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1064" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1064" s="27">
+    <row r="1067" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1067" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1067" s="27">
         <v>450</v>
       </c>
-      <c r="C1064" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1064" t="s">
+      <c r="C1067" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1067" t="s">
         <v>1269</v>
       </c>
-      <c r="G1064" t="s">
+      <c r="G1067" t="s">
         <v>1080</v>
       </c>
-      <c r="I1064" t="s">
+      <c r="I1067" t="s">
         <v>1198</v>
       </c>
-      <c r="J1064" t="s">
+      <c r="J1067" t="s">
         <v>1202</v>
       </c>
-      <c r="K1064" t="s">
+      <c r="K1067" t="s">
         <v>1200</v>
       </c>
-      <c r="L1064" t="str">
+      <c r="L1067" t="str">
         <f t="shared" si="139"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0040_DHwtj_MR_04.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1065" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1065" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1065" s="27">
+    <row r="1068" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1068" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1068" s="27">
         <v>450</v>
       </c>
-      <c r="C1065" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1065" t="s">
+      <c r="C1068" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1068" t="s">
         <v>1269</v>
       </c>
-      <c r="G1065" t="s">
+      <c r="G1068" t="s">
         <v>1081</v>
       </c>
-      <c r="I1065" t="s">
+      <c r="I1068" t="s">
         <v>1198</v>
       </c>
-      <c r="J1065" t="s">
+      <c r="J1068" t="s">
         <v>1202</v>
       </c>
-      <c r="K1065" t="s">
+      <c r="K1068" t="s">
         <v>1200</v>
       </c>
-      <c r="L1065" t="str">
+      <c r="L1068" t="str">
         <f t="shared" si="139"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0050_DHwtj_MR_05.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1066" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1066" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1066" s="27">
+    <row r="1069" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1069" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1069" s="27">
         <v>450</v>
       </c>
-      <c r="C1066" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1066" t="s">
+      <c r="C1069" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1069" t="s">
         <v>1269</v>
       </c>
-      <c r="G1066" t="s">
+      <c r="G1069" t="s">
         <v>1082</v>
       </c>
-      <c r="I1066" t="s">
+      <c r="I1069" t="s">
         <v>1198</v>
       </c>
-      <c r="J1066" t="s">
+      <c r="J1069" t="s">
         <v>1207</v>
       </c>
-      <c r="K1066" t="s">
+      <c r="K1069" t="s">
         <v>1200</v>
       </c>
-      <c r="L1066" t="str">
+      <c r="L1069" t="str">
         <f t="shared" si="139"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0060_DHwtj_SP_01.png &lt;sup&gt;(Sp.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1067" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1067" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1067" s="27">
+    <row r="1070" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1070" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1070" s="27">
         <v>450</v>
       </c>
-      <c r="C1067" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1067" t="s">
+      <c r="C1070" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1070" t="s">
         <v>1269</v>
       </c>
-      <c r="G1067" t="s">
+      <c r="G1070" t="s">
         <v>1083</v>
       </c>
-      <c r="I1067" t="s">
+      <c r="I1070" t="s">
         <v>1198</v>
       </c>
-      <c r="J1067" t="s">
+      <c r="J1070" t="s">
         <v>1207</v>
       </c>
-      <c r="K1067" t="s">
+      <c r="K1070" t="s">
         <v>1200</v>
       </c>
-      <c r="L1067" t="str">
+      <c r="L1070" t="str">
         <f t="shared" si="139"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0070_DHwtj_SP_02.png &lt;sup&gt;(Sp.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1068" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1068" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1068" s="27">
+    <row r="1071" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1071" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1071" s="27">
         <v>450</v>
       </c>
-      <c r="C1068" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1068" t="s">
+      <c r="C1071" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1071" t="s">
         <v>1269</v>
       </c>
-      <c r="G1068" t="s">
+      <c r="G1071" t="s">
         <v>1084</v>
       </c>
-      <c r="I1068" t="s">
+      <c r="I1071" t="s">
         <v>1198</v>
       </c>
-      <c r="J1068" t="s">
+      <c r="J1071" t="s">
         <v>1217</v>
       </c>
-      <c r="K1068" t="s">
+      <c r="K1071" t="s">
         <v>1200</v>
       </c>
-      <c r="L1068" t="str">
+      <c r="L1071" t="str">
         <f t="shared" si="139"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0080_DHwtj_SP-GR_01.png &lt;sup&gt;(Sp.; Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1069" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1069" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1069" s="27">
+    <row r="1072" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1072" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1072" s="27">
         <v>450</v>
       </c>
-      <c r="C1069" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1069" t="s">
+      <c r="C1072" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1072" t="s">
         <v>1269</v>
       </c>
-      <c r="G1069" t="s">
+      <c r="G1072" t="s">
         <v>1085</v>
       </c>
-      <c r="I1069" t="s">
+      <c r="I1072" t="s">
         <v>1198</v>
       </c>
-      <c r="J1069" t="s">
+      <c r="J1072" t="s">
         <v>1217</v>
       </c>
-      <c r="K1069" t="s">
+      <c r="K1072" t="s">
         <v>1200</v>
       </c>
-      <c r="L1069" t="str">
+      <c r="L1072" t="str">
         <f t="shared" si="139"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0090_DHwtj_SP-GR_02.png &lt;sup&gt;(Sp.; Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1070" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1070" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1070" s="27">
+    <row r="1073" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1073" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1073" s="27">
         <v>450</v>
       </c>
-      <c r="C1070" t="s">
+      <c r="C1073" t="s">
         <v>106</v>
       </c>
-      <c r="E1070" t="s">
+      <c r="E1073" t="s">
         <v>1269</v>
       </c>
-      <c r="F1070" t="s">
+      <c r="F1073" t="s">
         <v>111</v>
       </c>
-      <c r="G1070" t="s">
+      <c r="G1073" t="s">
         <v>1086</v>
       </c>
-      <c r="I1070" t="s">
+      <c r="I1073" t="s">
         <v>1198</v>
       </c>
-      <c r="J1070" t="s">
+      <c r="J1073" t="s">
         <v>1207</v>
       </c>
-      <c r="K1070" t="s">
+      <c r="K1073" t="s">
         <v>1200</v>
       </c>
-      <c r="L1070" t="str">
+      <c r="L1073" t="str">
         <f t="shared" si="139"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/det/0001_DHwtj_det_SP_01.png &lt;sup&gt;(Sp.)&lt;/sup&gt;</v>
       </c>
     </row>
-    <row r="1071" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1071" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1071" s="27">
+    <row r="1074" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1074" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1074" s="27">
         <v>450</v>
       </c>
-      <c r="C1071" t="s">
+      <c r="C1074" t="s">
         <v>107</v>
       </c>
-      <c r="L1071" t="s">
+      <c r="L1074" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="1072" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1072" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1072" s="27">
+    <row r="1075" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1075" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1075" s="27">
         <v>450</v>
       </c>
-      <c r="C1072" t="s">
+      <c r="C1075" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="1078" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1078" s="4" t="s">
-        <v>1287</v>
-      </c>
-      <c r="B1078" s="27">
-        <v>1</v>
-      </c>
-      <c r="C1078" t="s">
-        <v>1343</v>
-      </c>
-      <c r="L1078" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="1079" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1079" s="4" t="s">
-        <v>1287</v>
-      </c>
-      <c r="B1079" s="27">
-        <v>1</v>
-      </c>
-      <c r="C1079" t="s">
-        <v>1286</v>
-      </c>
-      <c r="E1079" t="s">
-        <v>1340</v>
-      </c>
-      <c r="G1079" t="s">
-        <v>1339</v>
-      </c>
-      <c r="H1079" t="s">
-        <v>113</v>
-      </c>
-      <c r="L1079" t="str">
-        <f t="shared" ref="L1079" si="140">_xlfn.TEXTJOIN("", TRUE, D1079:K1079)</f>
-        <v>03_Hieroglyphen-selten/F63_xnty_01.png</v>
-      </c>
-    </row>
-    <row r="1080" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1080" s="4" t="s">
-        <v>1287</v>
-      </c>
-      <c r="B1080" s="27">
-        <v>1</v>
-      </c>
-      <c r="C1080" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1080" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="1081" spans="1:12" x14ac:dyDescent="0.2">
@@ -31108,62 +31212,62 @@
         <v>1</v>
       </c>
       <c r="C1081" t="s">
+        <v>1343</v>
+      </c>
+      <c r="L1081" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1082" s="4" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B1082" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1082" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E1082" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G1082" t="s">
+        <v>1339</v>
+      </c>
+      <c r="H1082" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1082" t="str">
+        <f t="shared" ref="L1082" si="140">_xlfn.TEXTJOIN("", TRUE, D1082:K1082)</f>
+        <v>03_Hieroglyphen-selten/F63_xnty_01.png</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1083" s="4" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B1083" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1083" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1083" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1084" s="4" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B1084" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1084" t="s">
         <v>27</v>
       </c>
-      <c r="L1081" t="s">
+      <c r="L1084" t="s">
         <v>1342</v>
-      </c>
-    </row>
-    <row r="1086" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1086" s="4" t="s">
-        <v>1325</v>
-      </c>
-      <c r="B1086" s="27">
-        <v>1</v>
-      </c>
-      <c r="C1086" t="s">
-        <v>1343</v>
-      </c>
-      <c r="L1086" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="1087" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1087" s="4" t="s">
-        <v>1325</v>
-      </c>
-      <c r="B1087" s="27">
-        <v>1</v>
-      </c>
-      <c r="C1087" t="s">
-        <v>1286</v>
-      </c>
-      <c r="E1087" t="s">
-        <v>1340</v>
-      </c>
-      <c r="G1087" t="s">
-        <v>1346</v>
-      </c>
-      <c r="H1087" t="s">
-        <v>113</v>
-      </c>
-      <c r="L1087" t="str">
-        <f t="shared" ref="L1087" si="141">_xlfn.TEXTJOIN("", TRUE, D1087:K1087)</f>
-        <v>03_Hieroglyphen-selten/N6B_nsw-bjt_01.png</v>
-      </c>
-    </row>
-    <row r="1088" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1088" s="4" t="s">
-        <v>1325</v>
-      </c>
-      <c r="B1088" s="27">
-        <v>1</v>
-      </c>
-      <c r="C1088" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1088" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="1089" spans="1:12" x14ac:dyDescent="0.2">
@@ -31174,10 +31278,10 @@
         <v>1</v>
       </c>
       <c r="C1089" t="s">
-        <v>27</v>
+        <v>1343</v>
       </c>
       <c r="L1089" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="1090" spans="1:12" x14ac:dyDescent="0.2">
@@ -31185,13 +31289,23 @@
         <v>1325</v>
       </c>
       <c r="B1090" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1090" t="s">
-        <v>1343</v>
-      </c>
-      <c r="L1090" t="s">
-        <v>1349</v>
+        <v>1286</v>
+      </c>
+      <c r="E1090" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G1090" t="s">
+        <v>1346</v>
+      </c>
+      <c r="H1090" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1090" t="str">
+        <f t="shared" ref="L1090" si="141">_xlfn.TEXTJOIN("", TRUE, D1090:K1090)</f>
+        <v>03_Hieroglyphen-selten/N6B_nsw-bjt_01.png</v>
       </c>
     </row>
     <row r="1091" spans="1:12" x14ac:dyDescent="0.2">
@@ -31199,23 +31313,13 @@
         <v>1325</v>
       </c>
       <c r="B1091" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1091" t="s">
-        <v>1286</v>
-      </c>
-      <c r="E1091" t="s">
-        <v>1340</v>
-      </c>
-      <c r="G1091" t="s">
-        <v>1348</v>
-      </c>
-      <c r="H1091" t="s">
-        <v>113</v>
-      </c>
-      <c r="L1091" t="str">
-        <f t="shared" ref="L1091" si="142">_xlfn.TEXTJOIN("", TRUE, D1091:K1091)</f>
-        <v>03_Hieroglyphen-selten/N102_jmn_01.png</v>
+        <v>39</v>
+      </c>
+      <c r="L1091" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="1092" spans="1:12" x14ac:dyDescent="0.2">
@@ -31223,13 +31327,13 @@
         <v>1325</v>
       </c>
       <c r="B1092" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1092" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L1092" t="s">
-        <v>177</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="1093" spans="1:12" x14ac:dyDescent="0.2">
@@ -31240,16 +31344,68 @@
         <v>2</v>
       </c>
       <c r="C1093" t="s">
+        <v>1343</v>
+      </c>
+      <c r="L1093" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1094" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B1094" s="27">
+        <v>2</v>
+      </c>
+      <c r="C1094" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E1094" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G1094" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H1094" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1094" t="str">
+        <f t="shared" ref="L1094" si="142">_xlfn.TEXTJOIN("", TRUE, D1094:K1094)</f>
+        <v>03_Hieroglyphen-selten/N102_jmn_01.png</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1095" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B1095" s="27">
+        <v>2</v>
+      </c>
+      <c r="C1095" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1095" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1096" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B1096" s="27">
+        <v>2</v>
+      </c>
+      <c r="C1096" t="s">
         <v>27</v>
       </c>
-      <c r="L1093" t="s">
+      <c r="L1096" t="s">
         <v>112</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="L33 L952 L962" formula="1"/>
+    <ignoredError sqref="L33 L955 L965" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9791674-86FC-9044-9746-58D43CD73EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BCE710-6790-D84E-9B89-45738A059ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16200" activeTab="4" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="18380" windowHeight="16200" activeTab="4" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BCE710-6790-D84E-9B89-45738A059ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A159D984-DFC7-FC4E-B540-1EA140129EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="18380" windowHeight="16200" activeTab="4" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="18380" windowHeight="16200" activeTab="3" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6318" uniqueCount="1444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6326" uniqueCount="1445">
   <si>
     <t>page_id</t>
   </si>
@@ -4374,6 +4374,32 @@
   </si>
   <si>
     <t>0010_jn_02</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hoffmann, Friedhelm 2021. Einige Beobachtungen zur Rückenschutzformel. In Ullmann, Martina, Gabriele Pieke, Friedhelm Hoffmann, and Christian Bayer (eds), </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Up and down the Nile: ägyptologische Studien für Regine Schulz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 187-204. Münster: Zaphon.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -4383,7 +4409,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4419,6 +4445,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -7034,6 +7068,9 @@
       <c r="D59" s="4" t="s">
         <v>1433</v>
       </c>
+      <c r="G59" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="I59" s="4" t="s">
         <v>1432</v>
       </c>
@@ -7054,11 +7091,34 @@
       <c r="D60" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="G60" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="I60" s="4" t="s">
         <v>1405</v>
       </c>
       <c r="K60" s="4">
         <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E61" t="s">
+        <v>1444</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D438127-D079-C443-9535-F2A8F2FD2A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E2934E-3A32-3D4B-9D3E-E27ED654FC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19840" activeTab="5" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19840" activeTab="4" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6585" uniqueCount="1488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6721" uniqueCount="1502">
   <si>
     <t>page_id</t>
   </si>
@@ -4529,6 +4529,48 @@
   </si>
   <si>
     <t>er hat als sein Denkmal gemacht</t>
+  </si>
+  <si>
+    <t>*it*</t>
+  </si>
+  <si>
+    <t>02-1_jt/</t>
+  </si>
+  <si>
+    <t>0001_jt_AR_01.png</t>
+  </si>
+  <si>
+    <t>0010_jt_AR_02.png</t>
+  </si>
+  <si>
+    <t>0020_jt_AR_03.png</t>
+  </si>
+  <si>
+    <t>0030_jt_MR_01.png</t>
+  </si>
+  <si>
+    <t>0040_jt_Gr_01.png</t>
+  </si>
+  <si>
+    <t>0050_jt_Gr_02.png</t>
+  </si>
+  <si>
+    <t>03-1_mw.t/</t>
+  </si>
+  <si>
+    <t>0030_mw.t_seit-MR_01.png</t>
+  </si>
+  <si>
+    <t>0040_mw.t_seit-MR_02.png</t>
+  </si>
+  <si>
+    <t>0050_mw.t_seit-MR_03.png</t>
+  </si>
+  <si>
+    <t>0060_mw.t_NR_01.png</t>
+  </si>
+  <si>
+    <t>0070_mw.t_Sp_01.png</t>
   </si>
 </sst>
 </file>
@@ -8433,7 +8475,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C735804-F835-2748-99C4-5C04B7D215F0}">
-  <dimension ref="A1:N281"/>
+  <dimension ref="A1:N308"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
@@ -9447,7 +9489,7 @@
         <v>112</v>
       </c>
       <c r="L45" s="6" t="str">
-        <f t="shared" ref="L45:L49" si="4">_xlfn.TEXTJOIN("", TRUE, E45:K45)</f>
+        <f t="shared" ref="L45:L50" si="4">_xlfn.TEXTJOIN("", TRUE, E45:K45)</f>
         <v>01_Textgattung/02_Denkmaelerformel/01_jrj.n=f-m-mn.w=f/0010_jrj.n=f m mn.w=f n jt=f_01.png</v>
       </c>
       <c r="N45" s="6" t="s">
@@ -9597,690 +9639,685 @@
         <v>112</v>
       </c>
       <c r="L50" s="6" t="str">
-        <f t="shared" ref="L50" si="5">_xlfn.TEXTJOIN("", TRUE, E50:K50)</f>
+        <f t="shared" si="4"/>
         <v>01_Textgattung/02_Denkmaelerformel/01_jrj.n=f-m-mn.w=f/0060_jr.t n=f_01.png</v>
       </c>
       <c r="N50" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="52" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B52" s="12">
-        <v>1</v>
-      </c>
-      <c r="C52" s="12" t="s">
+    <row r="51" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B51" s="6">
+        <v>19</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>1488</v>
+      </c>
+      <c r="N51" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B52" s="6">
+        <v>20</v>
+      </c>
+      <c r="C52" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F52" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G52" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="H52" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="I52" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="L52" s="12" t="str">
-        <f t="shared" ref="L52" si="6">_xlfn.TEXTJOIN("", TRUE, E52:K52)</f>
-        <v>01_Textgattung/03_Hymnus/01_dwA/0001_dwA_01.png</v>
-      </c>
-      <c r="N52" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B53" s="12">
-        <v>2</v>
-      </c>
-      <c r="C53" s="12" t="s">
+      <c r="F52" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>1490</v>
+      </c>
+      <c r="L52" s="6" t="str">
+        <f t="shared" ref="L52:L54" si="5">_xlfn.TEXTJOIN("", TRUE, E52:K52)</f>
+        <v>01_Textgattung/02_Denkmaelerformel/02-1_jt/0001_jt_AR_01.png</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B53" s="6">
+        <v>21</v>
+      </c>
+      <c r="C53" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D53" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="N53" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B54" s="12">
-        <v>3</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="M54" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="N54" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B55" s="12">
-        <v>4</v>
-      </c>
-      <c r="C55" s="12" t="s">
+      <c r="D53" s="6" t="s">
+        <v>1145</v>
+      </c>
+      <c r="N53" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B54" s="6">
+        <v>22</v>
+      </c>
+      <c r="C54" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G55" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="H55" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="I55" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="L55" s="12" t="str">
-        <f t="shared" ref="L55" si="7">_xlfn.TEXTJOIN("", TRUE, E55:K55)</f>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0001_rDj.t-jAw_01.png</v>
-      </c>
-      <c r="N55" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B56" s="12">
-        <v>5</v>
-      </c>
-      <c r="C56" s="12" t="s">
+      <c r="F54" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>1491</v>
+      </c>
+      <c r="L54" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v>01_Textgattung/02_Denkmaelerformel/02-1_jt/0010_jt_AR_02.png</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B55" s="6">
+        <v>23</v>
+      </c>
+      <c r="C55" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D56" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="N56" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B57" s="12">
-        <v>6</v>
-      </c>
-      <c r="C57" s="12" t="s">
+      <c r="D55" s="6" t="s">
+        <v>1145</v>
+      </c>
+      <c r="N55" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B56" s="6">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F57" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G57" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="H57" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="I57" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="L57" s="12" t="str">
-        <f t="shared" ref="L57" si="8">_xlfn.TEXTJOIN("", TRUE, E57:K57)</f>
-        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0001_sn-tA-n_01.png</v>
-      </c>
-      <c r="N57" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B58" s="12">
-        <v>7</v>
-      </c>
-      <c r="C58" s="12" t="s">
+      <c r="F56" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>1492</v>
+      </c>
+      <c r="L56" s="6" t="str">
+        <f t="shared" ref="L56:L58" si="6">_xlfn.TEXTJOIN("", TRUE, E56:K56)</f>
+        <v>01_Textgattung/02_Denkmaelerformel/02-1_jt/0020_jt_AR_03.png</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B57" s="6">
+        <v>25</v>
+      </c>
+      <c r="C57" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D58" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="N58" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B59" s="12">
-        <v>8</v>
-      </c>
-      <c r="C59" s="12" t="s">
+      <c r="D57" s="6" t="s">
+        <v>1145</v>
+      </c>
+      <c r="N57" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B58" s="6">
+        <v>26</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F59" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G59" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="H59" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="I59" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="L59" s="12" t="str">
-        <f t="shared" ref="L59" si="9">_xlfn.TEXTJOIN("", TRUE, E59:K59)</f>
-        <v>01_Textgattung/03_Hymnus/04_jn/0001_jn_01.png</v>
-      </c>
-      <c r="N59" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B60" s="12">
-        <v>9</v>
-      </c>
-      <c r="C60" s="12" t="s">
+      <c r="F58" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>1493</v>
+      </c>
+      <c r="L58" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v>01_Textgattung/02_Denkmaelerformel/02-1_jt/0030_jt_MR_01.png</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B59" s="6">
+        <v>27</v>
+      </c>
+      <c r="C59" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D60" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="N60" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B61" s="12">
-        <v>10</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="M61" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="N61" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B62" s="12">
-        <v>11</v>
-      </c>
-      <c r="C62" s="12" t="s">
+      <c r="D59" s="6" t="s">
+        <v>1408</v>
+      </c>
+      <c r="N59" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B60" s="6">
+        <v>28</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F62" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G62" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="H62" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="L62" s="12" t="str">
-        <f t="shared" ref="L62" si="10">_xlfn.TEXTJOIN("", TRUE, E62:K62)</f>
-        <v>01_Textgattung/03_Hymnus/05_Dd=f/0001_Dd=f_01.png</v>
-      </c>
-      <c r="N62" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B63" s="12">
-        <v>12</v>
-      </c>
-      <c r="C63" s="12" t="s">
+      <c r="F60" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>1494</v>
+      </c>
+      <c r="L60" s="6" t="str">
+        <f t="shared" ref="L60" si="7">_xlfn.TEXTJOIN("", TRUE, E60:K60)</f>
+        <v>01_Textgattung/02_Denkmaelerformel/02-1_jt/0040_jt_Gr_01.png</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B61" s="6">
+        <v>29</v>
+      </c>
+      <c r="C61" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D63" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="N63" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B64" s="12">
-        <v>13</v>
-      </c>
-      <c r="C64" s="12" t="s">
+      <c r="D61" s="6" t="s">
+        <v>1146</v>
+      </c>
+      <c r="N61" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B62" s="6">
+        <v>30</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F64" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G64" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="H64" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="I64" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="L64" s="12" t="str">
-        <f t="shared" ref="L64" si="11">_xlfn.TEXTJOIN("", TRUE, E64:K64)</f>
-        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0001_jnD-Hr_01.png</v>
-      </c>
-      <c r="N64" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B65" s="12">
-        <v>14</v>
-      </c>
-      <c r="C65" s="12" t="s">
+      <c r="F62" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>1495</v>
+      </c>
+      <c r="L62" s="6" t="str">
+        <f t="shared" ref="L62" si="8">_xlfn.TEXTJOIN("", TRUE, E62:K62)</f>
+        <v>01_Textgattung/02_Denkmaelerformel/02-1_jt/0050_jt_Gr_02.png</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B63" s="6">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D65" s="12" t="s">
-        <v>539</v>
-      </c>
-      <c r="N65" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B66" s="12">
-        <v>15</v>
-      </c>
-      <c r="C66" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="N66" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="13" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B67" s="12">
-        <v>16</v>
-      </c>
-      <c r="C67" s="12" t="s">
+      <c r="D63" s="6" t="s">
+        <v>1146</v>
+      </c>
+      <c r="N63" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B64" s="6">
+        <v>32</v>
+      </c>
+      <c r="C64" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D67" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="N67" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="13" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B68" s="12">
-        <v>17</v>
-      </c>
-      <c r="C68" s="12" t="s">
+      <c r="D64" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B65" s="6">
+        <v>33</v>
+      </c>
+      <c r="C65" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F68" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G68" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="H68" s="12" t="s">
-        <v>1080</v>
-      </c>
-      <c r="L68" s="12" t="str">
-        <f t="shared" ref="L68:L81" si="12">_xlfn.TEXTJOIN("", TRUE, E68:K68)</f>
-        <v>01_Textgattung/03_Hymnus/01_dwA/0001_dwA_01.png</v>
-      </c>
-      <c r="N68" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="13" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B69" s="12">
-        <v>18</v>
-      </c>
-      <c r="C69" s="12" t="s">
+      <c r="F65" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>1496</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="L65" s="6" t="str">
+        <f t="shared" ref="L65:L68" si="9">_xlfn.TEXTJOIN("", TRUE, E65:K65)</f>
+        <v>01_Textgattung/02_Denkmaelerformel/03-1_mw.t/0001_mw.t_01.png</v>
+      </c>
+      <c r="N65" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B66" s="6">
+        <v>34</v>
+      </c>
+      <c r="C66" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F69" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G69" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="H69" s="12" t="s">
-        <v>1081</v>
-      </c>
-      <c r="L69" s="12" t="str">
-        <f t="shared" si="12"/>
-        <v>01_Textgattung/03_Hymnus/01_dwA/0010_dwA_02.png</v>
-      </c>
-      <c r="N69" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="13" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B70" s="12">
-        <v>19</v>
-      </c>
-      <c r="C70" s="12" t="s">
+      <c r="F66" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>1496</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="L66" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>01_Textgattung/02_Denkmaelerformel/03-1_mw.t/0010_mw.t_02.png</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B67" s="6">
+        <v>35</v>
+      </c>
+      <c r="C67" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F70" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G70" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="H70" s="12" t="s">
-        <v>1084</v>
-      </c>
-      <c r="L70" s="12" t="str">
-        <f t="shared" ref="L70" si="13">_xlfn.TEXTJOIN("", TRUE, E70:K70)</f>
-        <v>01_Textgattung/03_Hymnus/01_dwA/0020_dwA_seit-MR_01.png</v>
-      </c>
-      <c r="N70" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="13" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B71" s="12">
-        <v>20</v>
-      </c>
-      <c r="C71" s="12" t="s">
+      <c r="F67" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>1496</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="L67" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>01_Textgattung/02_Denkmaelerformel/03-1_mw.t/0020_mw.t_03.png</v>
+      </c>
+      <c r="N67" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B68" s="6">
+        <v>36</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>1496</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>1497</v>
+      </c>
+      <c r="L68" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>01_Textgattung/02_Denkmaelerformel/03-1_mw.t/0030_mw.t_seit-MR_01.png</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B69" s="6">
+        <v>37</v>
+      </c>
+      <c r="C69" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D71" s="12" t="s">
-        <v>1143</v>
-      </c>
-      <c r="N71" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="13" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B72" s="12">
-        <v>21</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="N72" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="13" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B73" s="12">
-        <v>22</v>
-      </c>
-      <c r="C73" s="12" t="s">
+      <c r="D69" s="6" t="s">
+        <v>1408</v>
+      </c>
+      <c r="N69" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B70" s="6">
+        <v>38</v>
+      </c>
+      <c r="C70" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F73" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G73" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="H73" s="12" t="s">
-        <v>1076</v>
-      </c>
-      <c r="L73" s="12" t="str">
-        <f t="shared" si="12"/>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0001_rDj.t-jAw_01.png</v>
-      </c>
-      <c r="N73" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="13" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B74" s="12">
-        <v>23</v>
-      </c>
-      <c r="C74" s="12" t="s">
+      <c r="F70" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>1496</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>1498</v>
+      </c>
+      <c r="L70" s="6" t="str">
+        <f t="shared" ref="L70:L72" si="10">_xlfn.TEXTJOIN("", TRUE, E70:K70)</f>
+        <v>01_Textgattung/02_Denkmaelerformel/03-1_mw.t/0040_mw.t_seit-MR_02.png</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B71" s="6">
+        <v>39</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>1408</v>
+      </c>
+      <c r="N71" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B72" s="6">
+        <v>40</v>
+      </c>
+      <c r="C72" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F74" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G74" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="H74" s="12" t="s">
-        <v>1078</v>
-      </c>
-      <c r="L74" s="12" t="str">
-        <f t="shared" si="12"/>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0010_rDj.t-jAw_NR_01.png</v>
-      </c>
-      <c r="N74" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="13" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B75" s="12">
-        <v>24</v>
-      </c>
-      <c r="C75" s="12" t="s">
+      <c r="F72" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>1496</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>1499</v>
+      </c>
+      <c r="L72" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>01_Textgattung/02_Denkmaelerformel/03-1_mw.t/0050_mw.t_seit-MR_03.png</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B73" s="6">
+        <v>41</v>
+      </c>
+      <c r="C73" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="D73" s="6" t="s">
+        <v>1408</v>
+      </c>
+      <c r="N73" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B74" s="6">
+        <v>42</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>1496</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>1500</v>
+      </c>
+      <c r="L74" s="6" t="str">
+        <f t="shared" ref="L74" si="11">_xlfn.TEXTJOIN("", TRUE, E74:K74)</f>
+        <v>01_Textgattung/02_Denkmaelerformel/03-1_mw.t/0060_mw.t_NR_01.png</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B75" s="6">
+        <v>43</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D75" s="6" t="s">
         <v>1144</v>
       </c>
-      <c r="N75" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="13" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B76" s="12">
-        <v>25</v>
-      </c>
-      <c r="C76" s="12" t="s">
+      <c r="N75" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B76" s="6">
+        <v>44</v>
+      </c>
+      <c r="C76" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F76" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G76" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="H76" s="12" t="s">
-        <v>1079</v>
-      </c>
-      <c r="L76" s="12" t="str">
-        <f t="shared" ref="L76" si="14">_xlfn.TEXTJOIN("", TRUE, E76:K76)</f>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0020_rDj.t-jAw_NR_02.png</v>
-      </c>
-      <c r="N76" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="13" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B77" s="12">
-        <v>26</v>
-      </c>
-      <c r="C77" s="12" t="s">
+      <c r="F76" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>1496</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>1501</v>
+      </c>
+      <c r="L76" s="6" t="str">
+        <f t="shared" ref="L76:L77" si="12">_xlfn.TEXTJOIN("", TRUE, E76:K76)</f>
+        <v>01_Textgattung/02_Denkmaelerformel/03-1_mw.t/0070_mw.t_Sp_01.png</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B77" s="6">
         <v>45</v>
       </c>
-      <c r="D77" s="12" t="s">
-        <v>1144</v>
-      </c>
-      <c r="N77" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="13" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B78" s="12">
-        <v>27</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F78" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G78" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="H78" s="12" t="s">
-        <v>1077</v>
-      </c>
-      <c r="L78" s="12" t="str">
-        <f t="shared" ref="L78" si="15">_xlfn.TEXTJOIN("", TRUE, E78:K78)</f>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0030_rDj.t-jAw_NR_03.png</v>
-      </c>
-      <c r="N78" s="12" t="s">
-        <v>93</v>
+      <c r="C77" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>1409</v>
+      </c>
+      <c r="N77" s="6" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="13" t="s">
-        <v>1073</v>
+        <v>358</v>
       </c>
       <c r="B79" s="12">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>1144</v>
+        <v>47</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="H79" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="I79" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="L79" s="12" t="str">
+        <f t="shared" ref="L79" si="13">_xlfn.TEXTJOIN("", TRUE, E79:K79)</f>
+        <v>01_Textgattung/03_Hymnus/01_dwA/0001_dwA_01.png</v>
       </c>
       <c r="N79" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="80" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="13" t="s">
-        <v>1073</v>
+        <v>358</v>
       </c>
       <c r="B80" s="12">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="N80" s="12" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="13" t="s">
-        <v>1073</v>
+        <v>358</v>
       </c>
       <c r="B81" s="12">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F81" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G81" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="H81" s="12" t="s">
-        <v>1082</v>
-      </c>
-      <c r="L81" s="12" t="str">
-        <f t="shared" si="12"/>
-        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0001_sn-tA-n_01.png</v>
+        <v>46</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M81" s="12" t="s">
+        <v>97</v>
       </c>
       <c r="N81" s="12" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="82" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="13" t="s">
-        <v>1073</v>
+        <v>358</v>
       </c>
       <c r="B82" s="12">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>47</v>
@@ -10289,45 +10326,64 @@
         <v>447</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>1083</v>
+        <v>364</v>
+      </c>
+      <c r="I82" s="12" t="s">
+        <v>112</v>
       </c>
       <c r="L82" s="12" t="str">
-        <f t="shared" ref="L82" si="16">_xlfn.TEXTJOIN("", TRUE, E82:K82)</f>
-        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0010_sn-tA-n_NR_01.png</v>
+        <f t="shared" ref="L82" si="14">_xlfn.TEXTJOIN("", TRUE, E82:K82)</f>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0001_rDj.t-jAw_01.png</v>
       </c>
       <c r="N82" s="12" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="83" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="13" t="s">
-        <v>1073</v>
+        <v>358</v>
       </c>
       <c r="B83" s="12">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C83" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>1144</v>
+        <v>365</v>
       </c>
       <c r="N83" s="12" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="84" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="13" t="s">
-        <v>1073</v>
+        <v>358</v>
       </c>
       <c r="B84" s="12">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>91</v>
+        <v>47</v>
+      </c>
+      <c r="F84" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G84" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="H84" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="I84" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="L84" s="12" t="str">
+        <f t="shared" ref="L84" si="15">_xlfn.TEXTJOIN("", TRUE, E84:K84)</f>
+        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0001_sn-tA-n_01.png</v>
       </c>
       <c r="N84" s="12" t="s">
         <v>90</v>
@@ -10335,27 +10391,27 @@
     </row>
     <row r="85" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="13" t="s">
-        <v>1075</v>
+        <v>358</v>
       </c>
       <c r="B85" s="12">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N85" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="13" t="s">
-        <v>1075</v>
+        <v>358</v>
       </c>
       <c r="B86" s="12">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C86" s="12" t="s">
         <v>47</v>
@@ -10367,66 +10423,62 @@
         <v>370</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>1085</v>
+        <v>371</v>
+      </c>
+      <c r="I86" s="12" t="s">
+        <v>112</v>
       </c>
       <c r="L86" s="12" t="str">
-        <f t="shared" ref="L86:L87" si="17">_xlfn.TEXTJOIN("", TRUE, E86:K86)</f>
+        <f t="shared" ref="L86" si="16">_xlfn.TEXTJOIN("", TRUE, E86:K86)</f>
         <v>01_Textgattung/03_Hymnus/04_jn/0001_jn_01.png</v>
       </c>
       <c r="N86" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="87" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="13" t="s">
-        <v>1075</v>
+        <v>358</v>
       </c>
       <c r="B87" s="12">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F87" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G87" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="H87" s="12" t="s">
-        <v>1086</v>
-      </c>
-      <c r="L87" s="12" t="str">
-        <f t="shared" si="17"/>
-        <v>01_Textgattung/03_Hymnus/04_jn/0010_jn_02.png</v>
+        <v>45</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>369</v>
       </c>
       <c r="N87" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="88" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="13" t="s">
-        <v>1075</v>
+        <v>358</v>
       </c>
       <c r="B88" s="12">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>372</v>
+        <v>50</v>
+      </c>
+      <c r="M88" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="N88" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="89" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="13" t="s">
-        <v>1075</v>
+        <v>358</v>
       </c>
       <c r="B89" s="12">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C89" s="12" t="s">
         <v>47</v>
@@ -10444,36 +10496,36 @@
         <v>112</v>
       </c>
       <c r="L89" s="12" t="str">
-        <f t="shared" ref="L89" si="18">_xlfn.TEXTJOIN("", TRUE, E89:K89)</f>
+        <f t="shared" ref="L89" si="17">_xlfn.TEXTJOIN("", TRUE, E89:K89)</f>
         <v>01_Textgattung/03_Hymnus/05_Dd=f/0001_Dd=f_01.png</v>
       </c>
       <c r="N89" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="13" t="s">
-        <v>1074</v>
+        <v>358</v>
       </c>
       <c r="B90" s="12">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>1087</v>
+        <v>372</v>
       </c>
       <c r="N90" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="91" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="13" t="s">
-        <v>1074</v>
+        <v>358</v>
       </c>
       <c r="B91" s="12">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C91" s="12" t="s">
         <v>47</v>
@@ -10491,1589 +10543,1582 @@
         <v>112</v>
       </c>
       <c r="L91" s="12" t="str">
-        <f t="shared" ref="L91" si="19">_xlfn.TEXTJOIN("", TRUE, E91:K91)</f>
+        <f t="shared" ref="L91" si="18">_xlfn.TEXTJOIN("", TRUE, E91:K91)</f>
         <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0001_jnD-Hr_01.png</v>
       </c>
       <c r="N91" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="B92" s="12">
+        <v>14</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="N92" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="B93" s="12">
+        <v>15</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="N93" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B94" s="12">
+        <v>16</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="N94" s="12" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="101" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="17" t="s">
+    <row r="95" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B95" s="12">
+        <v>17</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F95" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G95" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="H95" s="12" t="s">
+        <v>1080</v>
+      </c>
+      <c r="L95" s="12" t="str">
+        <f t="shared" ref="L95:L108" si="19">_xlfn.TEXTJOIN("", TRUE, E95:K95)</f>
+        <v>01_Textgattung/03_Hymnus/01_dwA/0001_dwA_01.png</v>
+      </c>
+      <c r="N95" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B96" s="12">
+        <v>18</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F96" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G96" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="H96" s="12" t="s">
+        <v>1081</v>
+      </c>
+      <c r="L96" s="12" t="str">
+        <f t="shared" si="19"/>
+        <v>01_Textgattung/03_Hymnus/01_dwA/0010_dwA_02.png</v>
+      </c>
+      <c r="N96" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B97" s="12">
+        <v>19</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F97" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G97" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="H97" s="12" t="s">
+        <v>1084</v>
+      </c>
+      <c r="L97" s="12" t="str">
+        <f t="shared" ref="L97" si="20">_xlfn.TEXTJOIN("", TRUE, E97:K97)</f>
+        <v>01_Textgattung/03_Hymnus/01_dwA/0020_dwA_seit-MR_01.png</v>
+      </c>
+      <c r="N97" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B98" s="12">
+        <v>20</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>1143</v>
+      </c>
+      <c r="N98" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B99" s="12">
+        <v>21</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="N99" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B100" s="12">
+        <v>22</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F100" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G100" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="H100" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="L100" s="12" t="str">
+        <f t="shared" si="19"/>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0001_rDj.t-jAw_01.png</v>
+      </c>
+      <c r="N100" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B101" s="12">
+        <v>23</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F101" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G101" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="H101" s="12" t="s">
+        <v>1078</v>
+      </c>
+      <c r="L101" s="12" t="str">
+        <f t="shared" si="19"/>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0010_rDj.t-jAw_NR_01.png</v>
+      </c>
+      <c r="N101" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B102" s="12">
+        <v>24</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>1144</v>
+      </c>
+      <c r="N102" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B103" s="12">
+        <v>25</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F103" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G103" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="H103" s="12" t="s">
+        <v>1079</v>
+      </c>
+      <c r="L103" s="12" t="str">
+        <f t="shared" ref="L103" si="21">_xlfn.TEXTJOIN("", TRUE, E103:K103)</f>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0020_rDj.t-jAw_NR_02.png</v>
+      </c>
+      <c r="N103" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B104" s="12">
+        <v>26</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>1144</v>
+      </c>
+      <c r="N104" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B105" s="12">
+        <v>27</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F105" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G105" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="H105" s="12" t="s">
+        <v>1077</v>
+      </c>
+      <c r="L105" s="12" t="str">
+        <f t="shared" ref="L105" si="22">_xlfn.TEXTJOIN("", TRUE, E105:K105)</f>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0030_rDj.t-jAw_NR_03.png</v>
+      </c>
+      <c r="N105" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B106" s="12">
+        <v>28</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>1144</v>
+      </c>
+      <c r="N106" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B107" s="12">
+        <v>29</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="N107" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B108" s="12">
+        <v>30</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F108" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G108" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="H108" s="12" t="s">
+        <v>1082</v>
+      </c>
+      <c r="L108" s="12" t="str">
+        <f t="shared" si="19"/>
+        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0001_sn-tA-n_01.png</v>
+      </c>
+      <c r="N108" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B109" s="12">
+        <v>31</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F109" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G109" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="H109" s="12" t="s">
+        <v>1083</v>
+      </c>
+      <c r="L109" s="12" t="str">
+        <f t="shared" ref="L109" si="23">_xlfn.TEXTJOIN("", TRUE, E109:K109)</f>
+        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0010_sn-tA-n_NR_01.png</v>
+      </c>
+      <c r="N109" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B110" s="12">
+        <v>32</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>1144</v>
+      </c>
+      <c r="N110" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B111" s="12">
+        <v>33</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="N111" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="13" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B112" s="12">
+        <v>34</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="N112" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="13" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B113" s="12">
+        <v>35</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F113" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G113" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="H113" s="12" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L113" s="12" t="str">
+        <f t="shared" ref="L113:L114" si="24">_xlfn.TEXTJOIN("", TRUE, E113:K113)</f>
+        <v>01_Textgattung/03_Hymnus/04_jn/0001_jn_01.png</v>
+      </c>
+      <c r="N113" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="13" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B114" s="12">
+        <v>36</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F114" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G114" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="H114" s="12" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L114" s="12" t="str">
+        <f t="shared" si="24"/>
+        <v>01_Textgattung/03_Hymnus/04_jn/0010_jn_02.png</v>
+      </c>
+      <c r="N114" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="13" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B115" s="12">
+        <v>37</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="N115" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="13" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B116" s="12">
+        <v>38</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F116" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G116" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="H116" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="I116" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="L116" s="12" t="str">
+        <f t="shared" ref="L116" si="25">_xlfn.TEXTJOIN("", TRUE, E116:K116)</f>
+        <v>01_Textgattung/03_Hymnus/05_Dd=f/0001_Dd=f_01.png</v>
+      </c>
+      <c r="N116" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="13" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B117" s="12">
+        <v>39</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>1087</v>
+      </c>
+      <c r="N117" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="13" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B118" s="12">
+        <v>40</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F118" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G118" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="H118" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="I118" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="L118" s="12" t="str">
+        <f t="shared" ref="L118" si="26">_xlfn.TEXTJOIN("", TRUE, E118:K118)</f>
+        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0001_jnD-Hr_01.png</v>
+      </c>
+      <c r="N118" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="17" t="s">
         <v>445</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B128" s="16">
         <v>1</v>
       </c>
-      <c r="C101" s="16" t="s">
+      <c r="C128" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D101" s="16" t="s">
+      <c r="D128" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="M101" s="16" t="s">
+      <c r="M128" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="N101" s="16" t="s">
+      <c r="N128" s="16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="102" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="17" t="s">
+    <row r="129" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="17" t="s">
         <v>445</v>
       </c>
-      <c r="B102" s="16">
+      <c r="B129" s="16">
         <v>2</v>
       </c>
-      <c r="C102" s="16" t="s">
+      <c r="C129" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D102" s="16" t="s">
+      <c r="D129" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="M102" s="16" t="s">
+      <c r="M129" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="N102" s="16" t="s">
+      <c r="N129" s="16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="103" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="17" t="s">
+    <row r="130" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="17" t="s">
         <v>445</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B130" s="16">
         <v>3</v>
       </c>
-      <c r="C103" s="16" t="s">
+      <c r="C130" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F103" s="16" t="s">
+      <c r="F130" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="G103" s="16" t="s">
+      <c r="G130" s="16" t="s">
         <v>449</v>
       </c>
-      <c r="H103" s="16" t="s">
+      <c r="H130" s="16" t="s">
         <v>448</v>
       </c>
-      <c r="I103" s="16" t="s">
+      <c r="I130" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="L103" s="16" t="str">
-        <f t="shared" ref="L103" si="20">_xlfn.TEXTJOIN("", TRUE, E103:K103)</f>
+      <c r="L130" s="16" t="str">
+        <f t="shared" ref="L130" si="27">_xlfn.TEXTJOIN("", TRUE, E130:K130)</f>
         <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0001_mry_01.png</v>
       </c>
-      <c r="N103" s="16" t="s">
+      <c r="N130" s="16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="104" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="17" t="s">
+    <row r="131" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="17" t="s">
         <v>445</v>
       </c>
-      <c r="B104" s="16">
+      <c r="B131" s="16">
         <v>4</v>
       </c>
-      <c r="C104" s="16" t="s">
+      <c r="C131" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D104" s="16" t="s">
+      <c r="D131" s="16" t="s">
         <v>446</v>
       </c>
-      <c r="N104" s="16" t="s">
+      <c r="N131" s="16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="17" t="s">
+    <row r="132" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="17" t="s">
         <v>445</v>
       </c>
-      <c r="B105" s="16">
+      <c r="B132" s="16">
         <v>5</v>
       </c>
-      <c r="C105" s="16" t="s">
+      <c r="C132" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="N105" s="16" t="s">
+      <c r="N132" s="16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="106" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="17" t="s">
+    <row r="133" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="B106" s="16">
+      <c r="B133" s="16">
         <v>6</v>
       </c>
-      <c r="C106" s="16" t="s">
+      <c r="C133" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D106" s="16" t="s">
+      <c r="D133" s="16" t="s">
         <v>446</v>
       </c>
-      <c r="N106" s="16" t="s">
+      <c r="N133" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="107" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="17" t="s">
+    <row r="134" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="B107" s="16">
+      <c r="B134" s="16">
         <v>7</v>
       </c>
-      <c r="C107" s="16" t="s">
+      <c r="C134" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F107" s="16" t="s">
+      <c r="F134" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="G107" s="16" t="s">
+      <c r="G134" s="16" t="s">
         <v>449</v>
       </c>
-      <c r="H107" s="16" t="s">
+      <c r="H134" s="16" t="s">
         <v>448</v>
       </c>
-      <c r="I107" s="16" t="s">
+      <c r="I134" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="L107" s="16" t="str">
-        <f t="shared" ref="L107" si="21">_xlfn.TEXTJOIN("", TRUE, E107:K107)</f>
+      <c r="L134" s="16" t="str">
+        <f t="shared" ref="L134" si="28">_xlfn.TEXTJOIN("", TRUE, E134:K134)</f>
         <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0001_mry_01.png</v>
       </c>
-      <c r="N107" s="16" t="s">
+      <c r="N134" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="108" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="17" t="s">
+    <row r="135" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="B108" s="16">
+      <c r="B135" s="16">
         <v>8</v>
       </c>
-      <c r="C108" s="16" t="s">
+      <c r="C135" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F108" s="16" t="s">
+      <c r="F135" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="G108" s="16" t="s">
+      <c r="G135" s="16" t="s">
         <v>449</v>
       </c>
-      <c r="H108" s="16" t="s">
+      <c r="H135" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="I108" s="16" t="s">
+      <c r="I135" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="L108" s="16" t="str">
-        <f t="shared" ref="L108:L111" si="22">_xlfn.TEXTJOIN("", TRUE, E108:K108)</f>
+      <c r="L135" s="16" t="str">
+        <f t="shared" ref="L135:L138" si="29">_xlfn.TEXTJOIN("", TRUE, E135:K135)</f>
         <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0010_mry_02.png</v>
       </c>
-      <c r="N108" s="16" t="s">
+      <c r="N135" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="109" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="17" t="s">
+    <row r="136" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="B109" s="16">
+      <c r="B136" s="16">
         <v>9</v>
       </c>
-      <c r="C109" s="16" t="s">
+      <c r="C136" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F109" s="16" t="s">
+      <c r="F136" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="G109" s="16" t="s">
+      <c r="G136" s="16" t="s">
         <v>449</v>
       </c>
-      <c r="H109" s="16" t="s">
+      <c r="H136" s="16" t="s">
         <v>452</v>
       </c>
-      <c r="I109" s="16" t="s">
+      <c r="I136" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="L109" s="16" t="str">
-        <f t="shared" si="22"/>
+      <c r="L136" s="16" t="str">
+        <f t="shared" si="29"/>
         <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0020_mry_03.png</v>
       </c>
-      <c r="N109" s="16" t="s">
+      <c r="N136" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="110" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="17" t="s">
+    <row r="137" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="B110" s="16">
+      <c r="B137" s="16">
         <v>10</v>
       </c>
-      <c r="C110" s="16" t="s">
+      <c r="C137" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F110" s="16" t="s">
+      <c r="F137" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="G110" s="16" t="s">
+      <c r="G137" s="16" t="s">
         <v>449</v>
       </c>
-      <c r="H110" s="16" t="s">
+      <c r="H137" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="I110" s="16" t="s">
+      <c r="I137" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="L110" s="16" t="str">
-        <f t="shared" si="22"/>
+      <c r="L137" s="16" t="str">
+        <f t="shared" si="29"/>
         <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0030_mry_04.png</v>
       </c>
-      <c r="N110" s="16" t="s">
+      <c r="N137" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="111" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="17" t="s">
+    <row r="138" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="B111" s="16">
+      <c r="B138" s="16">
         <v>11</v>
       </c>
-      <c r="C111" s="16" t="s">
+      <c r="C138" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F111" s="16" t="s">
+      <c r="F138" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="G111" s="16" t="s">
+      <c r="G138" s="16" t="s">
         <v>449</v>
       </c>
-      <c r="H111" s="16" t="s">
+      <c r="H138" s="16" t="s">
         <v>454</v>
       </c>
-      <c r="I111" s="16" t="s">
+      <c r="I138" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="L111" s="16" t="str">
-        <f t="shared" si="22"/>
+      <c r="L138" s="16" t="str">
+        <f t="shared" si="29"/>
         <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0040_mry_05.png</v>
       </c>
-      <c r="N111" s="16" t="s">
+      <c r="N138" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="112" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="17" t="s">
+    <row r="139" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="B112" s="16">
+      <c r="B139" s="16">
         <v>12</v>
       </c>
-      <c r="C112" s="16" t="s">
+      <c r="C139" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F112" s="16" t="s">
+      <c r="F139" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="G112" s="16" t="s">
+      <c r="G139" s="16" t="s">
         <v>449</v>
       </c>
-      <c r="H112" s="16" t="s">
+      <c r="H139" s="16" t="s">
         <v>455</v>
       </c>
-      <c r="I112" s="16" t="s">
+      <c r="I139" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="L112" s="16" t="str">
-        <f t="shared" ref="L112" si="23">_xlfn.TEXTJOIN("", TRUE, E112:K112)</f>
+      <c r="L139" s="16" t="str">
+        <f t="shared" ref="L139" si="30">_xlfn.TEXTJOIN("", TRUE, E139:K139)</f>
         <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0050_mry_AR_02.png</v>
       </c>
-      <c r="N112" s="16" t="s">
+      <c r="N139" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="113" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="17" t="s">
+    <row r="140" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="B113" s="16">
+      <c r="B140" s="16">
         <v>13</v>
       </c>
-      <c r="C113" s="16" t="s">
+      <c r="C140" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D113" s="16" t="s">
+      <c r="D140" s="16" t="s">
         <v>1145</v>
       </c>
-      <c r="N113" s="16" t="s">
+      <c r="N140" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="115" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="18" t="s">
+    <row r="142" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="18" t="s">
         <v>458</v>
       </c>
-      <c r="B115" s="18">
+      <c r="B142" s="18">
         <v>1</v>
       </c>
-      <c r="C115" s="18" t="s">
+      <c r="C142" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D115" s="18" t="s">
+      <c r="D142" s="18" t="s">
         <v>477</v>
       </c>
-      <c r="M115" s="18" t="s">
+      <c r="M142" s="18" t="s">
         <v>461</v>
       </c>
-      <c r="N115" s="18" t="s">
+      <c r="N142" s="18" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="116" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="18" t="s">
+    <row r="143" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="18" t="s">
         <v>458</v>
       </c>
-      <c r="B116" s="18">
+      <c r="B143" s="18">
         <v>2</v>
       </c>
-      <c r="C116" s="18" t="s">
+      <c r="C143" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F116" s="18" t="s">
+      <c r="F143" s="18" t="s">
         <v>464</v>
       </c>
-      <c r="G116" s="18" t="s">
+      <c r="G143" s="18" t="s">
         <v>465</v>
       </c>
-      <c r="H116" s="18" t="s">
+      <c r="H143" s="18" t="s">
         <v>467</v>
       </c>
-      <c r="I116" s="18" t="s">
+      <c r="I143" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="L116" s="18" t="str">
-        <f t="shared" ref="L116" si="24">_xlfn.TEXTJOIN("", TRUE, E116:K116)</f>
+      <c r="L143" s="18" t="str">
+        <f t="shared" ref="L143" si="31">_xlfn.TEXTJOIN("", TRUE, E143:K143)</f>
         <v>01_Textgattung/05_Historische-Koenigsinschrift/01_xr-Hm-n/0001_xr Hm n_01.png</v>
       </c>
-      <c r="N116" s="18" t="s">
+      <c r="N143" s="18" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="117" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="18" t="s">
+    <row r="144" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="18" t="s">
         <v>458</v>
       </c>
-      <c r="B117" s="18">
+      <c r="B144" s="18">
         <v>3</v>
       </c>
-      <c r="C117" s="18" t="s">
+      <c r="C144" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D117" s="18" t="s">
+      <c r="D144" s="18" t="s">
         <v>466</v>
       </c>
-      <c r="N117" s="18" t="s">
+      <c r="N144" s="18" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="118" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="18" t="s">
+    <row r="145" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="18" t="s">
         <v>458</v>
       </c>
-      <c r="B118" s="18">
+      <c r="B145" s="18">
         <v>4</v>
       </c>
-      <c r="C118" s="18" t="s">
+      <c r="C145" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D118" s="18" t="s">
+      <c r="D145" s="18" t="s">
         <v>324</v>
       </c>
-      <c r="M118" s="18" t="s">
+      <c r="M145" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="N118" s="18" t="s">
+      <c r="N145" s="18" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="119" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="18" t="s">
+    <row r="146" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="18" t="s">
         <v>458</v>
       </c>
-      <c r="B119" s="18">
+      <c r="B146" s="18">
         <v>5</v>
       </c>
-      <c r="C119" s="18" t="s">
+      <c r="C146" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D119" s="18" t="s">
+      <c r="D146" s="18" t="s">
         <v>471</v>
       </c>
-      <c r="N119" s="18" t="s">
+      <c r="N146" s="18" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="120" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="18" t="s">
+    <row r="147" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="18" t="s">
         <v>458</v>
       </c>
-      <c r="B120" s="18">
+      <c r="B147" s="18">
         <v>6</v>
       </c>
-      <c r="C120" s="18" t="s">
+      <c r="C147" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="N120" s="18" t="s">
+      <c r="N147" s="18" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="121" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="18" t="s">
+    <row r="148" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="18" t="s">
         <v>459</v>
       </c>
-      <c r="B121" s="18">
+      <c r="B148" s="18">
         <v>7</v>
       </c>
-      <c r="C121" s="18" t="s">
+      <c r="C148" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D121" s="18" t="s">
+      <c r="D148" s="18" t="s">
         <v>472</v>
       </c>
-      <c r="N121" s="18" t="s">
+      <c r="N148" s="18" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="122" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="18" t="s">
+    <row r="149" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="18" t="s">
         <v>459</v>
       </c>
-      <c r="B122" s="18">
+      <c r="B149" s="18">
         <v>8</v>
       </c>
-      <c r="C122" s="18" t="s">
+      <c r="C149" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F122" s="18" t="s">
+      <c r="F149" s="18" t="s">
         <v>464</v>
       </c>
-      <c r="G122" s="18" t="s">
+      <c r="G149" s="18" t="s">
         <v>465</v>
       </c>
-      <c r="H122" s="18" t="s">
+      <c r="H149" s="18" t="s">
         <v>467</v>
       </c>
-      <c r="I122" s="18" t="s">
+      <c r="I149" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="L122" s="18" t="str">
-        <f t="shared" ref="L122" si="25">_xlfn.TEXTJOIN("", TRUE, E122:K122)</f>
+      <c r="L149" s="18" t="str">
+        <f t="shared" ref="L149" si="32">_xlfn.TEXTJOIN("", TRUE, E149:K149)</f>
         <v>01_Textgattung/05_Historische-Koenigsinschrift/01_xr-Hm-n/0001_xr Hm n_01.png</v>
       </c>
-      <c r="N122" s="18" t="s">
+      <c r="N149" s="18" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="123" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="18" t="s">
+    <row r="150" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="18" t="s">
         <v>459</v>
       </c>
-      <c r="B123" s="18">
+      <c r="B150" s="18">
         <v>9</v>
       </c>
-      <c r="C123" s="18" t="s">
+      <c r="C150" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F123" s="18" t="s">
+      <c r="F150" s="18" t="s">
         <v>464</v>
       </c>
-      <c r="G123" s="18" t="s">
+      <c r="G150" s="18" t="s">
         <v>465</v>
       </c>
-      <c r="H123" s="18" t="s">
+      <c r="H150" s="18" t="s">
         <v>474</v>
       </c>
-      <c r="I123" s="18" t="s">
+      <c r="I150" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="L123" s="18" t="str">
-        <f t="shared" ref="L123:L125" si="26">_xlfn.TEXTJOIN("", TRUE, E123:K123)</f>
+      <c r="L150" s="18" t="str">
+        <f t="shared" ref="L150:L152" si="33">_xlfn.TEXTJOIN("", TRUE, E150:K150)</f>
         <v>01_Textgattung/05_Historische-Koenigsinschrift/01_xr-Hm-n/0010_xr Hm n_02.png</v>
       </c>
-      <c r="N123" s="18" t="s">
+      <c r="N150" s="18" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="124" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="18" t="s">
+    <row r="151" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="18" t="s">
         <v>459</v>
       </c>
-      <c r="B124" s="18">
+      <c r="B151" s="18">
         <v>10</v>
       </c>
-      <c r="C124" s="18" t="s">
+      <c r="C151" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F124" s="18" t="s">
+      <c r="F151" s="18" t="s">
         <v>464</v>
       </c>
-      <c r="G124" s="18" t="s">
+      <c r="G151" s="18" t="s">
         <v>465</v>
       </c>
-      <c r="H124" s="18" t="s">
+      <c r="H151" s="18" t="s">
         <v>475</v>
       </c>
-      <c r="I124" s="18" t="s">
+      <c r="I151" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="L124" s="18" t="str">
-        <f t="shared" si="26"/>
+      <c r="L151" s="18" t="str">
+        <f t="shared" si="33"/>
         <v>01_Textgattung/05_Historische-Koenigsinschrift/01_xr-Hm-n/0020_Hm n_01.png</v>
       </c>
-      <c r="N124" s="18" t="s">
+      <c r="N151" s="18" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="125" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="18" t="s">
+    <row r="152" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="18" t="s">
         <v>459</v>
       </c>
-      <c r="B125" s="18">
+      <c r="B152" s="18">
         <v>11</v>
       </c>
-      <c r="C125" s="18" t="s">
+      <c r="C152" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F125" s="18" t="s">
+      <c r="F152" s="18" t="s">
         <v>464</v>
       </c>
-      <c r="G125" s="18" t="s">
+      <c r="G152" s="18" t="s">
         <v>465</v>
       </c>
-      <c r="H125" s="18" t="s">
+      <c r="H152" s="18" t="s">
         <v>476</v>
       </c>
-      <c r="I125" s="18" t="s">
+      <c r="I152" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="L125" s="18" t="str">
-        <f t="shared" si="26"/>
+      <c r="L152" s="18" t="str">
+        <f t="shared" si="33"/>
         <v>01_Textgattung/05_Historische-Koenigsinschrift/01_xr-Hm-n/0030_Hm n_02.png</v>
       </c>
-      <c r="N125" s="18" t="s">
+      <c r="N152" s="18" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="126" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="18" t="s">
+    <row r="153" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="18" t="s">
         <v>459</v>
       </c>
-      <c r="B126" s="18">
+      <c r="B153" s="18">
         <v>12</v>
       </c>
-      <c r="C126" s="18" t="s">
+      <c r="C153" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D126" s="18" t="s">
+      <c r="D153" s="18" t="s">
         <v>470</v>
       </c>
-      <c r="N126" s="18" t="s">
+      <c r="N153" s="18" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="127" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="18" t="s">
+    <row r="154" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="18" t="s">
         <v>459</v>
       </c>
-      <c r="B127" s="18">
+      <c r="B154" s="18">
         <v>13</v>
       </c>
-      <c r="C127" s="18" t="s">
+      <c r="C154" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F127" s="18" t="s">
+      <c r="F154" s="18" t="s">
         <v>468</v>
       </c>
-      <c r="H127" s="18" t="s">
+      <c r="H154" s="18" t="s">
         <v>469</v>
       </c>
-      <c r="I127" s="18" t="s">
+      <c r="I154" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="L127" s="18" t="str">
-        <f t="shared" ref="L127" si="27">_xlfn.TEXTJOIN("", TRUE, E127:K127)</f>
+      <c r="L154" s="18" t="str">
+        <f t="shared" ref="L154" si="34">_xlfn.TEXTJOIN("", TRUE, E154:K154)</f>
         <v>02_Slots/Koenig/04_Thronname_01.png</v>
       </c>
-      <c r="N127" s="18" t="s">
+      <c r="N154" s="18" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="128" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="18" t="s">
+    <row r="155" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="18" t="s">
         <v>459</v>
       </c>
-      <c r="B128" s="18">
+      <c r="B155" s="18">
         <v>14</v>
       </c>
-      <c r="C128" s="18" t="s">
+      <c r="C155" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F128" s="18" t="s">
+      <c r="F155" s="18" t="s">
         <v>468</v>
       </c>
-      <c r="H128" s="18" t="s">
+      <c r="H155" s="18" t="s">
         <v>473</v>
       </c>
-      <c r="I128" s="18" t="s">
+      <c r="I155" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="L128" s="18" t="str">
-        <f t="shared" ref="L128" si="28">_xlfn.TEXTJOIN("", TRUE, E128:K128)</f>
+      <c r="L155" s="18" t="str">
+        <f t="shared" ref="L155" si="35">_xlfn.TEXTJOIN("", TRUE, E155:K155)</f>
         <v>02_Slots/Koenig/04_Thronname_Gr._02.png</v>
       </c>
-      <c r="N128" s="18" t="s">
+      <c r="N155" s="18" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="129" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="18" t="s">
+    <row r="156" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="18" t="s">
         <v>459</v>
       </c>
-      <c r="B129" s="18">
+      <c r="B156" s="18">
         <v>15</v>
       </c>
-      <c r="C129" s="18" t="s">
+      <c r="C156" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D129" s="18" t="s">
+      <c r="D156" s="18" t="s">
         <v>1146</v>
       </c>
-      <c r="N129" s="18" t="s">
+      <c r="N156" s="18" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="131" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="21" t="s">
+    <row r="158" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="21" t="s">
         <v>543</v>
       </c>
-      <c r="B131" s="21">
+      <c r="B158" s="21">
         <v>1</v>
       </c>
-      <c r="C131" s="21" t="s">
+      <c r="C158" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D131" s="21" t="s">
+      <c r="D158" s="21" t="s">
         <v>542</v>
       </c>
-      <c r="N131" s="21" t="s">
+      <c r="N158" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="132" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="21" t="s">
+    <row r="159" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="21" t="s">
         <v>543</v>
       </c>
-      <c r="B132" s="21">
+      <c r="B159" s="21">
         <v>2</v>
       </c>
-      <c r="C132" s="21" t="s">
+      <c r="C159" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D132" s="21" t="s">
+      <c r="D159" s="21" t="s">
         <v>562</v>
       </c>
-      <c r="N132" s="21" t="s">
+      <c r="N159" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="133" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="21" t="s">
+    <row r="160" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="21" t="s">
         <v>543</v>
       </c>
-      <c r="B133" s="21">
+      <c r="B160" s="21">
         <v>3</v>
       </c>
-      <c r="C133" s="21" t="s">
+      <c r="C160" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D133" s="21" t="s">
+      <c r="D160" s="21" t="s">
         <v>544</v>
       </c>
-      <c r="M133" s="21" t="s">
+      <c r="M160" s="21" t="s">
         <v>547</v>
       </c>
-      <c r="N133" s="21" t="s">
+      <c r="N160" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="134" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="21" t="s">
+    <row r="161" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="21" t="s">
         <v>543</v>
       </c>
-      <c r="B134" s="21">
+      <c r="B161" s="21">
         <v>4</v>
       </c>
-      <c r="C134" s="21" t="s">
+      <c r="C161" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D134" s="21" t="s">
+      <c r="D161" s="21" t="s">
         <v>548</v>
       </c>
-      <c r="M134" s="21" t="s">
+      <c r="M161" s="21" t="s">
         <v>1391</v>
       </c>
-      <c r="N134" s="21" t="s">
+      <c r="N161" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="135" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="21" t="s">
+    <row r="162" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="21" t="s">
         <v>543</v>
       </c>
-      <c r="B135" s="21">
+      <c r="B162" s="21">
         <v>5</v>
       </c>
-      <c r="C135" s="21" t="s">
+      <c r="C162" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="N135" s="21" t="s">
+      <c r="N162" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="136" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="22" t="s">
+    <row r="163" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="22" t="s">
         <v>1366</v>
       </c>
-      <c r="B136" s="21">
+      <c r="B163" s="21">
         <v>6</v>
       </c>
-      <c r="C136" s="21" t="s">
+      <c r="C163" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D136" s="21" t="s">
+      <c r="D163" s="21" t="s">
         <v>549</v>
       </c>
-      <c r="N136" s="21" t="s">
+      <c r="N163" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="137" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="22" t="s">
+    <row r="164" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="22" t="s">
         <v>1366</v>
       </c>
-      <c r="B137" s="21">
+      <c r="B164" s="21">
         <v>7</v>
       </c>
-      <c r="C137" s="21" t="s">
+      <c r="C164" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D137" s="21" t="s">
+      <c r="D164" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="M137" s="21" t="s">
+      <c r="M164" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="N137" s="21" t="s">
+      <c r="N164" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="138" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="22" t="s">
+    <row r="165" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="22" t="s">
         <v>1366</v>
       </c>
-      <c r="B138" s="21">
+      <c r="B165" s="21">
         <v>8</v>
       </c>
-      <c r="C138" s="21" t="s">
+      <c r="C165" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D138" s="21" t="s">
+      <c r="D165" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="N138" s="21" t="s">
+      <c r="N165" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="139" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="22" t="s">
+    <row r="166" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="22" t="s">
         <v>1366</v>
       </c>
-      <c r="B139" s="21">
+      <c r="B166" s="21">
         <v>9</v>
       </c>
-      <c r="C139" s="21" t="s">
+      <c r="C166" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D139" s="21" t="s">
+      <c r="D166" s="21" t="s">
         <v>324</v>
       </c>
-      <c r="M139" s="21" t="s">
+      <c r="M166" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="N139" s="21" t="s">
+      <c r="N166" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="140" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="22" t="s">
+    <row r="167" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="22" t="s">
         <v>1366</v>
       </c>
-      <c r="B140" s="21">
+      <c r="B167" s="21">
         <v>10</v>
       </c>
-      <c r="C140" s="21" t="s">
+      <c r="C167" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D140" s="21" t="s">
+      <c r="D167" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="N140" s="21" t="s">
+      <c r="N167" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="141" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="22" t="s">
+    <row r="168" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="22" t="s">
         <v>1366</v>
       </c>
-      <c r="B141" s="21">
+      <c r="B168" s="21">
         <v>11</v>
       </c>
-      <c r="C141" s="21" t="s">
+      <c r="C168" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D141" s="21" t="s">
+      <c r="D168" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="M141" s="21" t="s">
+      <c r="M168" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="N141" s="21" t="s">
+      <c r="N168" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="142" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="22" t="s">
+    <row r="169" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="22" t="s">
         <v>1366</v>
       </c>
-      <c r="B142" s="21">
+      <c r="B169" s="21">
         <v>12</v>
       </c>
-      <c r="C142" s="21" t="s">
+      <c r="C169" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D142" s="21" t="s">
+      <c r="D169" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="N142" s="21" t="s">
+      <c r="N169" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="143" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="22" t="s">
+    <row r="170" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="22" t="s">
         <v>1366</v>
       </c>
-      <c r="B143" s="21">
+      <c r="B170" s="21">
         <v>13</v>
       </c>
-      <c r="C143" s="21" t="s">
+      <c r="C170" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D143" s="21" t="s">
+      <c r="D170" s="21" t="s">
         <v>550</v>
       </c>
-      <c r="N143" s="21" t="s">
+      <c r="N170" s="21" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="145" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A145" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B145">
-        <v>1</v>
-      </c>
-      <c r="C145" t="s">
-        <v>47</v>
-      </c>
-      <c r="F145" t="s">
-        <v>1379</v>
-      </c>
-      <c r="G145" t="s">
-        <v>1380</v>
-      </c>
-      <c r="H145" t="s">
-        <v>1092</v>
-      </c>
-      <c r="I145" t="s">
-        <v>112</v>
-      </c>
-      <c r="L145" t="str">
-        <f t="shared" ref="L145" si="29">_xlfn.TEXTJOIN("", TRUE, E145:K145)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0001_Dd-mdw_01.png</v>
-      </c>
-      <c r="N145" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A146" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B146">
-        <v>2</v>
-      </c>
-      <c r="C146" t="s">
-        <v>45</v>
-      </c>
-      <c r="D146" t="s">
-        <v>1093</v>
-      </c>
-      <c r="N146" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="147" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A147" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B147">
-        <v>3</v>
-      </c>
-      <c r="C147" t="s">
-        <v>47</v>
-      </c>
-      <c r="F147" t="s">
-        <v>1379</v>
-      </c>
-      <c r="G147" t="s">
-        <v>1430</v>
-      </c>
-      <c r="H147" t="s">
-        <v>371</v>
-      </c>
-      <c r="I147" t="s">
-        <v>112</v>
-      </c>
-      <c r="L147" t="str">
-        <f t="shared" ref="L147" si="30">_xlfn.TEXTJOIN("", TRUE, E147:K147)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/02_jn/0001_jn_01.png</v>
-      </c>
-      <c r="N147" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="148" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A148" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B148">
-        <v>4</v>
-      </c>
-      <c r="C148" t="s">
-        <v>45</v>
-      </c>
-      <c r="D148" t="s">
-        <v>369</v>
-      </c>
-      <c r="N148" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="149" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A149" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B149">
-        <v>5</v>
-      </c>
-      <c r="C149" t="s">
-        <v>46</v>
-      </c>
-      <c r="D149" t="s">
-        <v>48</v>
-      </c>
-      <c r="M149" t="s">
-        <v>97</v>
-      </c>
-      <c r="N149" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="150" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A150" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B150">
-        <v>6</v>
-      </c>
-      <c r="C150" t="s">
-        <v>45</v>
-      </c>
-      <c r="D150" t="s">
-        <v>326</v>
-      </c>
-      <c r="N150" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="151" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A151" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B151">
-        <v>7</v>
-      </c>
-      <c r="C151" t="s">
-        <v>46</v>
-      </c>
-      <c r="D151" t="s">
-        <v>324</v>
-      </c>
-      <c r="M151" t="s">
-        <v>325</v>
-      </c>
-      <c r="N151" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="152" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A152" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B152">
-        <v>8</v>
-      </c>
-      <c r="C152" t="s">
-        <v>45</v>
-      </c>
-      <c r="D152" t="s">
-        <v>326</v>
-      </c>
-      <c r="N152" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A153" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B153">
-        <v>9</v>
-      </c>
-      <c r="C153" t="s">
-        <v>46</v>
-      </c>
-      <c r="D153" t="s">
-        <v>50</v>
-      </c>
-      <c r="M153" t="s">
-        <v>99</v>
-      </c>
-      <c r="N153" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A154" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B154">
-        <v>10</v>
-      </c>
-      <c r="C154" t="s">
-        <v>47</v>
-      </c>
-      <c r="F154" t="s">
-        <v>1098</v>
-      </c>
-      <c r="H154" t="s">
-        <v>1099</v>
-      </c>
-      <c r="I154" t="s">
-        <v>112</v>
-      </c>
-      <c r="L154" t="str">
-        <f t="shared" ref="L154" si="31">_xlfn.TEXTJOIN("", TRUE, E154:K154)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0001_dj.n(=j)-n=k_01.png</v>
-      </c>
-      <c r="N154" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="155" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A155" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B155">
-        <v>11</v>
-      </c>
-      <c r="C155" t="s">
-        <v>45</v>
-      </c>
-      <c r="D155" t="s">
-        <v>1097</v>
-      </c>
-      <c r="N155" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="156" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A156" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B156">
-        <v>12</v>
-      </c>
-      <c r="C156" t="s">
-        <v>46</v>
-      </c>
-      <c r="D156" t="s">
-        <v>49</v>
-      </c>
-      <c r="M156" t="s">
-        <v>98</v>
-      </c>
-      <c r="N156" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="157" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A157" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B157">
-        <v>13</v>
-      </c>
-      <c r="C157" t="s">
-        <v>47</v>
-      </c>
-      <c r="F157" t="s">
-        <v>1094</v>
-      </c>
-      <c r="H157" t="s">
-        <v>1095</v>
-      </c>
-      <c r="I157" t="s">
-        <v>112</v>
-      </c>
-      <c r="L157" t="str">
-        <f t="shared" ref="L157" si="32">_xlfn.TEXTJOIN("", TRUE, E157:K157)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/03_xrj/04_xrj_01.png</v>
-      </c>
-      <c r="N157" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="158" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A158" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B158">
-        <v>14</v>
-      </c>
-      <c r="C158" t="s">
-        <v>45</v>
-      </c>
-      <c r="D158" t="s">
-        <v>1136</v>
-      </c>
-      <c r="N158" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="159" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A159" s="5" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B159">
-        <v>1</v>
-      </c>
-      <c r="C159" t="s">
-        <v>17</v>
-      </c>
-      <c r="D159" t="s">
-        <v>1093</v>
-      </c>
-      <c r="N159" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="160" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A160" s="5" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B160">
-        <v>2</v>
-      </c>
-      <c r="C160" t="s">
-        <v>47</v>
-      </c>
-      <c r="F160" t="s">
-        <v>1379</v>
-      </c>
-      <c r="G160" t="s">
-        <v>1380</v>
-      </c>
-      <c r="H160" t="s">
-        <v>1100</v>
-      </c>
-      <c r="L160" t="str">
-        <f t="shared" ref="L160:L162" si="33">_xlfn.TEXTJOIN("", TRUE, E160:K160)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0001_Dd-mdw_01.png</v>
-      </c>
-      <c r="N160" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="161" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A161" s="5" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B161">
-        <v>3</v>
-      </c>
-      <c r="C161" t="s">
-        <v>47</v>
-      </c>
-      <c r="F161" t="s">
-        <v>1379</v>
-      </c>
-      <c r="G161" t="s">
-        <v>1380</v>
-      </c>
-      <c r="H161" t="s">
-        <v>1101</v>
-      </c>
-      <c r="L161" t="str">
-        <f t="shared" si="33"/>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0010_Dd-mdw_02.png</v>
-      </c>
-      <c r="N161" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="162" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A162" s="5" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B162">
-        <v>4</v>
-      </c>
-      <c r="C162" t="s">
-        <v>47</v>
-      </c>
-      <c r="F162" t="s">
-        <v>1379</v>
-      </c>
-      <c r="G162" t="s">
-        <v>1380</v>
-      </c>
-      <c r="H162" t="s">
-        <v>1102</v>
-      </c>
-      <c r="L162" t="str">
-        <f t="shared" si="33"/>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0020_Dd-mdw_NR_01.png</v>
-      </c>
-      <c r="N162" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A163" s="5" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B163">
-        <v>5</v>
-      </c>
-      <c r="C163" t="s">
-        <v>45</v>
-      </c>
-      <c r="D163" t="s">
-        <v>1144</v>
-      </c>
-      <c r="N163" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="164" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A164" s="5" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B164">
-        <v>6</v>
-      </c>
-      <c r="C164" t="s">
-        <v>17</v>
-      </c>
-      <c r="D164" t="s">
-        <v>369</v>
-      </c>
-      <c r="N164" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A165" s="5" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B165">
-        <v>7</v>
-      </c>
-      <c r="C165" t="s">
-        <v>47</v>
-      </c>
-      <c r="F165" t="s">
-        <v>1379</v>
-      </c>
-      <c r="G165" t="s">
-        <v>1430</v>
-      </c>
-      <c r="H165" t="s">
-        <v>371</v>
-      </c>
-      <c r="I165" t="s">
-        <v>112</v>
-      </c>
-      <c r="L165" t="str">
-        <f t="shared" ref="L165" si="34">_xlfn.TEXTJOIN("", TRUE, E165:K165)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/02_jn/0001_jn_01.png</v>
-      </c>
-      <c r="N165" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A166" s="5" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B166">
-        <v>8</v>
-      </c>
-      <c r="C166" t="s">
-        <v>47</v>
-      </c>
-      <c r="F166" t="s">
-        <v>1379</v>
-      </c>
-      <c r="G166" t="s">
-        <v>1430</v>
-      </c>
-      <c r="H166" t="s">
-        <v>1431</v>
-      </c>
-      <c r="I166" t="s">
-        <v>112</v>
-      </c>
-      <c r="L166" t="str">
-        <f t="shared" ref="L166" si="35">_xlfn.TEXTJOIN("", TRUE, E166:K166)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/02_jn/0010_jn_02.png</v>
-      </c>
-      <c r="N166" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="167" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A167" s="5" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B167">
-        <v>9</v>
-      </c>
-      <c r="C167" t="s">
-        <v>45</v>
-      </c>
-      <c r="D167" t="s">
-        <v>1144</v>
-      </c>
-      <c r="N167" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="168" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A168" s="5" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B168">
-        <v>10</v>
-      </c>
-      <c r="C168" t="s">
-        <v>17</v>
-      </c>
-      <c r="D168" t="s">
-        <v>1097</v>
-      </c>
-      <c r="N168" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="169" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A169" s="5" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B169">
-        <v>11</v>
-      </c>
-      <c r="C169" t="s">
-        <v>47</v>
-      </c>
-      <c r="F169" t="s">
-        <v>1377</v>
-      </c>
-      <c r="G169" t="s">
-        <v>1378</v>
-      </c>
-      <c r="H169" t="s">
-        <v>1104</v>
-      </c>
-      <c r="L169" t="str">
-        <f t="shared" ref="L169:L173" si="36">_xlfn.TEXTJOIN("", TRUE, E169:K169)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0001_dj.n(=j)-n=k_01.png</v>
-      </c>
-      <c r="N169" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="170" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A170" s="5" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B170">
-        <v>12</v>
-      </c>
-      <c r="C170" t="s">
-        <v>47</v>
-      </c>
-      <c r="F170" t="s">
-        <v>1377</v>
-      </c>
-      <c r="G170" t="s">
-        <v>1378</v>
-      </c>
-      <c r="H170" t="s">
-        <v>1105</v>
-      </c>
-      <c r="L170" t="str">
-        <f t="shared" si="36"/>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0010_dj.n(=j)-n=k_02.png</v>
-      </c>
-      <c r="N170" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="171" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A171" s="5" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B171">
-        <v>13</v>
-      </c>
-      <c r="C171" t="s">
-        <v>47</v>
-      </c>
-      <c r="F171" t="s">
-        <v>1377</v>
-      </c>
-      <c r="G171" t="s">
-        <v>1378</v>
-      </c>
-      <c r="H171" t="s">
-        <v>1106</v>
-      </c>
-      <c r="L171" t="str">
-        <f t="shared" si="36"/>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0020_dj.n(=j)-n=k_03.png</v>
-      </c>
-      <c r="N171" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="172" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A172" s="5" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="B172">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C172" t="s">
         <v>47</v>
       </c>
       <c r="F172" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="G172" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="H172" t="s">
-        <v>1107</v>
+        <v>1092</v>
+      </c>
+      <c r="I172" t="s">
+        <v>112</v>
       </c>
       <c r="L172" t="str">
-        <f t="shared" si="36"/>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0030_dj.n(=j)-n=k_04.png</v>
+        <f t="shared" ref="L172" si="36">_xlfn.TEXTJOIN("", TRUE, E172:K172)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0001_Dd-mdw_01.png</v>
       </c>
       <c r="N172" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="173" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A173" s="5" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="B173">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C173" t="s">
+        <v>45</v>
+      </c>
+      <c r="D173" t="s">
+        <v>1093</v>
+      </c>
+      <c r="N173" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A174" s="5" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B174">
+        <v>3</v>
+      </c>
+      <c r="C174" t="s">
         <v>47</v>
       </c>
-      <c r="F173" t="s">
-        <v>1377</v>
-      </c>
-      <c r="G173" t="s">
-        <v>1378</v>
-      </c>
-      <c r="H173" t="s">
-        <v>1108</v>
-      </c>
-      <c r="L173" t="str">
-        <f t="shared" si="36"/>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0040_dj.n(=j)-n=T_01.png</v>
-      </c>
-      <c r="N173" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A174" s="5"/>
+      <c r="F174" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G174" t="s">
+        <v>1430</v>
+      </c>
+      <c r="H174" t="s">
+        <v>371</v>
+      </c>
+      <c r="I174" t="s">
+        <v>112</v>
+      </c>
+      <c r="L174" t="str">
+        <f t="shared" ref="L174" si="37">_xlfn.TEXTJOIN("", TRUE, E174:K174)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/02_jn/0001_jn_01.png</v>
+      </c>
+      <c r="N174" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="175" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A175" s="5" t="s">
-        <v>1371</v>
+        <v>1091</v>
       </c>
       <c r="B175">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C175" t="s">
-        <v>47</v>
-      </c>
-      <c r="F175" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G175" t="s">
-        <v>1376</v>
-      </c>
-      <c r="H175" t="s">
-        <v>1381</v>
-      </c>
-      <c r="I175" t="s">
-        <v>112</v>
-      </c>
-      <c r="L175" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, E175:K175)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0010_sA_seit-MR_02.png</v>
+        <v>45</v>
+      </c>
+      <c r="D175" t="s">
+        <v>369</v>
       </c>
       <c r="N175" t="s">
         <v>90</v>
@@ -12081,16 +12126,19 @@
     </row>
     <row r="176" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A176" s="5" t="s">
-        <v>1371</v>
+        <v>1091</v>
       </c>
       <c r="B176">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C176" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D176" t="s">
-        <v>1229</v>
+        <v>48</v>
+      </c>
+      <c r="M176" t="s">
+        <v>97</v>
       </c>
       <c r="N176" t="s">
         <v>90</v>
@@ -12098,29 +12146,16 @@
     </row>
     <row r="177" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A177" s="5" t="s">
-        <v>1371</v>
+        <v>1091</v>
       </c>
       <c r="B177">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C177" t="s">
-        <v>47</v>
-      </c>
-      <c r="F177" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G177" t="s">
-        <v>1383</v>
-      </c>
-      <c r="H177" t="s">
-        <v>1386</v>
-      </c>
-      <c r="I177" t="s">
-        <v>112</v>
-      </c>
-      <c r="L177" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, E177:K177)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/02_anx/0001_anx_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D177" t="s">
+        <v>326</v>
       </c>
       <c r="N177" t="s">
         <v>90</v>
@@ -12128,16 +12163,19 @@
     </row>
     <row r="178" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A178" s="5" t="s">
-        <v>1371</v>
+        <v>1091</v>
       </c>
       <c r="B178">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C178" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D178" t="s">
-        <v>644</v>
+        <v>324</v>
+      </c>
+      <c r="M178" t="s">
+        <v>325</v>
       </c>
       <c r="N178" t="s">
         <v>90</v>
@@ -12145,29 +12183,16 @@
     </row>
     <row r="179" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A179" s="5" t="s">
-        <v>1371</v>
+        <v>1091</v>
       </c>
       <c r="B179">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C179" t="s">
-        <v>47</v>
-      </c>
-      <c r="F179" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G179" t="s">
-        <v>1384</v>
-      </c>
-      <c r="H179" t="s">
-        <v>1388</v>
-      </c>
-      <c r="I179" t="s">
-        <v>112</v>
-      </c>
-      <c r="L179" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, E179:K179)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0010_HA_02.png</v>
+        <v>45</v>
+      </c>
+      <c r="D179" t="s">
+        <v>326</v>
       </c>
       <c r="N179" t="s">
         <v>90</v>
@@ -12175,29 +12200,19 @@
     </row>
     <row r="180" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A180" s="5" t="s">
-        <v>1371</v>
+        <v>1091</v>
       </c>
       <c r="B180">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C180" t="s">
-        <v>47</v>
-      </c>
-      <c r="F180" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G180" t="s">
-        <v>1385</v>
-      </c>
-      <c r="H180" t="s">
-        <v>1387</v>
-      </c>
-      <c r="I180" t="s">
-        <v>112</v>
-      </c>
-      <c r="L180" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, E180:K180)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/04_=f-nb/0001_=f-nb_01.png</v>
+        <v>46</v>
+      </c>
+      <c r="D180" t="s">
+        <v>50</v>
+      </c>
+      <c r="M180" t="s">
+        <v>99</v>
       </c>
       <c r="N180" t="s">
         <v>90</v>
@@ -12205,445 +12220,606 @@
     </row>
     <row r="181" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A181" s="5" t="s">
-        <v>1371</v>
+        <v>1091</v>
       </c>
       <c r="B181">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C181" t="s">
-        <v>45</v>
-      </c>
-      <c r="D181" t="s">
-        <v>1382</v>
+        <v>47</v>
+      </c>
+      <c r="F181" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H181" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I181" t="s">
+        <v>112</v>
+      </c>
+      <c r="L181" t="str">
+        <f t="shared" ref="L181" si="38">_xlfn.TEXTJOIN("", TRUE, E181:K181)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0001_dj.n(=j)-n=k_01.png</v>
       </c>
       <c r="N181" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A182" s="5"/>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A183" s="5"/>
+    <row r="182" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A182" s="5" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B182">
+        <v>11</v>
+      </c>
+      <c r="C182" t="s">
+        <v>45</v>
+      </c>
+      <c r="D182" t="s">
+        <v>1097</v>
+      </c>
+      <c r="N182" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A183" s="5" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B183">
+        <v>12</v>
+      </c>
+      <c r="C183" t="s">
+        <v>46</v>
+      </c>
+      <c r="D183" t="s">
+        <v>49</v>
+      </c>
+      <c r="M183" t="s">
+        <v>98</v>
+      </c>
+      <c r="N183" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="184" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A184" s="2" t="s">
-        <v>1420</v>
+      <c r="A184" s="5" t="s">
+        <v>1091</v>
       </c>
       <c r="B184">
+        <v>13</v>
+      </c>
+      <c r="C184" t="s">
+        <v>47</v>
+      </c>
+      <c r="F184" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H184" t="s">
+        <v>1095</v>
+      </c>
+      <c r="I184" t="s">
+        <v>112</v>
+      </c>
+      <c r="L184" t="str">
+        <f t="shared" ref="L184" si="39">_xlfn.TEXTJOIN("", TRUE, E184:K184)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/03_xrj/04_xrj_01.png</v>
+      </c>
+      <c r="N184" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A185" s="5" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B185">
+        <v>14</v>
+      </c>
+      <c r="C185" t="s">
+        <v>45</v>
+      </c>
+      <c r="D185" t="s">
+        <v>1136</v>
+      </c>
+      <c r="N185" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A186" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B186">
         <v>1</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C186" t="s">
         <v>17</v>
       </c>
-      <c r="D184" t="s">
-        <v>1422</v>
-      </c>
-    </row>
-    <row r="185" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A185" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="B185">
-        <v>2</v>
-      </c>
-      <c r="C185" t="s">
-        <v>47</v>
-      </c>
-      <c r="F185" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G185" t="s">
-        <v>1411</v>
-      </c>
-      <c r="H185" t="s">
-        <v>1412</v>
-      </c>
-      <c r="L185" t="str">
-        <f t="shared" ref="L185:L200" si="37">_xlfn.TEXTJOIN("", TRUE, E185:K185)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0001_sA-anx-HA=f-nb_MR_01.png</v>
-      </c>
-      <c r="N185" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="186" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A186" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="B186">
-        <v>3</v>
-      </c>
-      <c r="C186" t="s">
-        <v>45</v>
-      </c>
       <c r="D186" t="s">
-        <v>1408</v>
+        <v>1093</v>
       </c>
       <c r="N186" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="187" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A187" s="2" t="s">
-        <v>1420</v>
+      <c r="A187" s="5" t="s">
+        <v>1096</v>
       </c>
       <c r="B187">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C187" t="s">
         <v>47</v>
       </c>
       <c r="F187" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="G187" t="s">
-        <v>1411</v>
+        <v>1380</v>
       </c>
       <c r="H187" t="s">
-        <v>1413</v>
+        <v>1100</v>
       </c>
       <c r="L187" t="str">
-        <f t="shared" si="37"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0010_sA-anx-HA=f-nb-NR_01.png</v>
+        <f t="shared" ref="L187:L189" si="40">_xlfn.TEXTJOIN("", TRUE, E187:K187)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0001_Dd-mdw_01.png</v>
       </c>
       <c r="N187" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="188" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A188" s="2" t="s">
-        <v>1420</v>
+      <c r="A188" s="5" t="s">
+        <v>1096</v>
       </c>
       <c r="B188">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C188" t="s">
-        <v>45</v>
-      </c>
-      <c r="D188" t="s">
-        <v>1144</v>
+        <v>47</v>
+      </c>
+      <c r="F188" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G188" t="s">
+        <v>1380</v>
+      </c>
+      <c r="H188" t="s">
+        <v>1101</v>
+      </c>
+      <c r="L188" t="str">
+        <f t="shared" si="40"/>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0010_Dd-mdw_02.png</v>
       </c>
       <c r="N188" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="189" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A189" s="2" t="s">
-        <v>1420</v>
+      <c r="A189" s="5" t="s">
+        <v>1096</v>
       </c>
       <c r="B189">
+        <v>4</v>
+      </c>
+      <c r="C189" t="s">
+        <v>47</v>
+      </c>
+      <c r="F189" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G189" t="s">
+        <v>1380</v>
+      </c>
+      <c r="H189" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L189" t="str">
+        <f t="shared" si="40"/>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0020_Dd-mdw_NR_01.png</v>
+      </c>
+      <c r="N189" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A190" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B190">
+        <v>5</v>
+      </c>
+      <c r="C190" t="s">
+        <v>45</v>
+      </c>
+      <c r="D190" t="s">
+        <v>1144</v>
+      </c>
+      <c r="N190" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A191" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B191">
         <v>6</v>
       </c>
-      <c r="C189" t="s">
+      <c r="C191" t="s">
         <v>17</v>
       </c>
-      <c r="D189" t="s">
-        <v>1423</v>
-      </c>
-      <c r="N189" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="190" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A190" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="B190">
-        <v>7</v>
-      </c>
-      <c r="C190" t="s">
-        <v>47</v>
-      </c>
-      <c r="F190" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G190" t="s">
-        <v>1411</v>
-      </c>
-      <c r="H190" t="s">
-        <v>1414</v>
-      </c>
-      <c r="L190" t="str">
-        <f t="shared" si="37"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0020_sA-anx-HA=f_01.png</v>
-      </c>
-      <c r="N190" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="191" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A191" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="B191">
-        <v>8</v>
-      </c>
-      <c r="C191" t="s">
-        <v>47</v>
-      </c>
-      <c r="F191" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G191" t="s">
-        <v>1411</v>
-      </c>
-      <c r="H191" t="s">
-        <v>1415</v>
-      </c>
-      <c r="L191" t="str">
-        <f t="shared" si="37"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0030_sA-anx-HA=f_02.png</v>
+      <c r="D191" t="s">
+        <v>369</v>
       </c>
       <c r="N191" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="192" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A192" s="2" t="s">
-        <v>1420</v>
+      <c r="A192" s="5" t="s">
+        <v>1096</v>
       </c>
       <c r="B192">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C192" t="s">
-        <v>17</v>
-      </c>
-      <c r="D192" t="s">
-        <v>1424</v>
+        <v>47</v>
+      </c>
+      <c r="F192" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G192" t="s">
+        <v>1430</v>
+      </c>
+      <c r="H192" t="s">
+        <v>371</v>
+      </c>
+      <c r="I192" t="s">
+        <v>112</v>
+      </c>
+      <c r="L192" t="str">
+        <f t="shared" ref="L192" si="41">_xlfn.TEXTJOIN("", TRUE, E192:K192)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/02_jn/0001_jn_01.png</v>
       </c>
       <c r="N192" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="193" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A193" s="2" t="s">
-        <v>1420</v>
+      <c r="A193" s="5" t="s">
+        <v>1096</v>
       </c>
       <c r="B193">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C193" t="s">
         <v>47</v>
       </c>
       <c r="F193" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="G193" t="s">
-        <v>1411</v>
+        <v>1430</v>
       </c>
       <c r="H193" t="s">
-        <v>1416</v>
+        <v>1431</v>
+      </c>
+      <c r="I193" t="s">
+        <v>112</v>
       </c>
       <c r="L193" t="str">
-        <f t="shared" si="37"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0040_sA-anx-wAs-HA=f_01.png</v>
+        <f t="shared" ref="L193" si="42">_xlfn.TEXTJOIN("", TRUE, E193:K193)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/02_jn/0010_jn_02.png</v>
       </c>
       <c r="N193" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="194" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A194" s="2" t="s">
-        <v>1420</v>
+      <c r="A194" s="5" t="s">
+        <v>1096</v>
       </c>
       <c r="B194">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C194" t="s">
-        <v>47</v>
-      </c>
-      <c r="F194" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G194" t="s">
-        <v>1411</v>
-      </c>
-      <c r="H194" t="s">
-        <v>1417</v>
-      </c>
-      <c r="L194" t="str">
-        <f t="shared" si="37"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0050_sA-anx-wAs-HA=f_NR-selten-Gr-oft_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D194" t="s">
+        <v>1144</v>
       </c>
       <c r="N194" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="195" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A195" s="2" t="s">
-        <v>1420</v>
+      <c r="A195" s="5" t="s">
+        <v>1096</v>
       </c>
       <c r="B195">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C195" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D195" t="s">
-        <v>1427</v>
+        <v>1097</v>
       </c>
       <c r="N195" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="196" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A196" s="2" t="s">
-        <v>1420</v>
+      <c r="A196" s="5" t="s">
+        <v>1096</v>
       </c>
       <c r="B196">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C196" t="s">
-        <v>17</v>
-      </c>
-      <c r="D196" t="s">
-        <v>1425</v>
+        <v>47</v>
+      </c>
+      <c r="F196" t="s">
+        <v>1377</v>
+      </c>
+      <c r="G196" t="s">
+        <v>1378</v>
+      </c>
+      <c r="H196" t="s">
+        <v>1104</v>
+      </c>
+      <c r="L196" t="str">
+        <f t="shared" ref="L196:L200" si="43">_xlfn.TEXTJOIN("", TRUE, E196:K196)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0001_dj.n(=j)-n=k_01.png</v>
       </c>
       <c r="N196" t="s">
-        <v>1410</v>
+        <v>95</v>
       </c>
     </row>
     <row r="197" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A197" s="2" t="s">
-        <v>1420</v>
+      <c r="A197" s="5" t="s">
+        <v>1096</v>
       </c>
       <c r="B197">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C197" t="s">
         <v>47</v>
       </c>
       <c r="F197" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="G197" t="s">
-        <v>1411</v>
+        <v>1378</v>
       </c>
       <c r="H197" t="s">
-        <v>1418</v>
+        <v>1105</v>
       </c>
       <c r="L197" t="str">
-        <f t="shared" si="37"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0060_sA-anx-Dd-wAs-HA=f_D.18_01.png</v>
+        <f t="shared" si="43"/>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0010_dj.n(=j)-n=k_02.png</v>
       </c>
       <c r="N197" t="s">
-        <v>1410</v>
+        <v>95</v>
       </c>
     </row>
     <row r="198" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A198" s="2" t="s">
-        <v>1420</v>
+      <c r="A198" s="5" t="s">
+        <v>1096</v>
       </c>
       <c r="B198">
+        <v>13</v>
+      </c>
+      <c r="C198" t="s">
+        <v>47</v>
+      </c>
+      <c r="F198" t="s">
+        <v>1377</v>
+      </c>
+      <c r="G198" t="s">
+        <v>1378</v>
+      </c>
+      <c r="H198" t="s">
+        <v>1106</v>
+      </c>
+      <c r="L198" t="str">
+        <f t="shared" si="43"/>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0020_dj.n(=j)-n=k_03.png</v>
+      </c>
+      <c r="N198" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A199" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B199">
+        <v>14</v>
+      </c>
+      <c r="C199" t="s">
+        <v>47</v>
+      </c>
+      <c r="F199" t="s">
+        <v>1377</v>
+      </c>
+      <c r="G199" t="s">
+        <v>1378</v>
+      </c>
+      <c r="H199" t="s">
+        <v>1107</v>
+      </c>
+      <c r="L199" t="str">
+        <f t="shared" si="43"/>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0030_dj.n(=j)-n=k_04.png</v>
+      </c>
+      <c r="N199" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A200" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B200">
         <v>15</v>
-      </c>
-      <c r="C198" t="s">
-        <v>45</v>
-      </c>
-      <c r="D198" t="s">
-        <v>1428</v>
-      </c>
-      <c r="N198" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="199" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A199" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="B199">
-        <v>16</v>
-      </c>
-      <c r="C199" t="s">
-        <v>17</v>
-      </c>
-      <c r="D199" t="s">
-        <v>1426</v>
-      </c>
-      <c r="N199" t="s">
-        <v>1429</v>
-      </c>
-    </row>
-    <row r="200" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A200" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="B200">
-        <v>17</v>
       </c>
       <c r="C200" t="s">
         <v>47</v>
       </c>
       <c r="F200" t="s">
+        <v>1377</v>
+      </c>
+      <c r="G200" t="s">
+        <v>1378</v>
+      </c>
+      <c r="H200" t="s">
+        <v>1108</v>
+      </c>
+      <c r="L200" t="str">
+        <f t="shared" si="43"/>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0040_dj.n(=j)-n=T_01.png</v>
+      </c>
+      <c r="N200" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A201" s="5"/>
+    </row>
+    <row r="202" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A202" s="5" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B202">
+        <v>1</v>
+      </c>
+      <c r="C202" t="s">
+        <v>47</v>
+      </c>
+      <c r="F202" t="s">
         <v>1375</v>
       </c>
-      <c r="G200" t="s">
-        <v>1411</v>
-      </c>
-      <c r="H200" t="s">
-        <v>1419</v>
-      </c>
-      <c r="L200" t="str">
-        <f t="shared" si="37"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0070_sA-anx-Dd-wAs-snb-HA=f_D.18_01.png</v>
-      </c>
-      <c r="N200" t="s">
-        <v>1429</v>
-      </c>
-    </row>
-    <row r="201" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A201" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="B201">
-        <v>18</v>
-      </c>
-      <c r="C201" t="s">
+      <c r="G202" t="s">
+        <v>1376</v>
+      </c>
+      <c r="H202" t="s">
+        <v>1381</v>
+      </c>
+      <c r="I202" t="s">
+        <v>112</v>
+      </c>
+      <c r="L202" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, E202:K202)</f>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0010_sA_seit-MR_02.png</v>
+      </c>
+      <c r="N202" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A203" s="5" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B203">
+        <v>2</v>
+      </c>
+      <c r="C203" t="s">
         <v>45</v>
       </c>
-      <c r="D201" t="s">
-        <v>1428</v>
-      </c>
-      <c r="N201" t="s">
-        <v>1429</v>
-      </c>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A202" s="5"/>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A203" s="5"/>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A204" s="5"/>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A205" s="5"/>
+      <c r="D203" t="s">
+        <v>1229</v>
+      </c>
+      <c r="N203" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A204" s="5" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B204">
+        <v>3</v>
+      </c>
+      <c r="C204" t="s">
+        <v>47</v>
+      </c>
+      <c r="F204" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G204" t="s">
+        <v>1383</v>
+      </c>
+      <c r="H204" t="s">
+        <v>1386</v>
+      </c>
+      <c r="I204" t="s">
+        <v>112</v>
+      </c>
+      <c r="L204" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, E204:K204)</f>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/02_anx/0001_anx_01.png</v>
+      </c>
+      <c r="N204" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A205" s="5" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B205">
+        <v>4</v>
+      </c>
+      <c r="C205" t="s">
+        <v>45</v>
+      </c>
+      <c r="D205" t="s">
+        <v>644</v>
+      </c>
+      <c r="N205" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="206" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A206" s="2" t="s">
-        <v>1393</v>
+      <c r="A206" s="5" t="s">
+        <v>1371</v>
       </c>
       <c r="B206">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>17</v>
-      </c>
-      <c r="D206" t="s">
-        <v>1229</v>
+        <v>47</v>
+      </c>
+      <c r="F206" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G206" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H206" t="s">
+        <v>1388</v>
+      </c>
+      <c r="I206" t="s">
+        <v>112</v>
+      </c>
+      <c r="L206" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, E206:K206)</f>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0010_HA_02.png</v>
       </c>
       <c r="N206" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="207" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A207" s="2" t="s">
-        <v>1393</v>
+      <c r="A207" s="5" t="s">
+        <v>1371</v>
       </c>
       <c r="B207">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C207" t="s">
         <v>47</v>
@@ -12652,113 +12828,65 @@
         <v>1375</v>
       </c>
       <c r="G207" t="s">
-        <v>1376</v>
+        <v>1385</v>
       </c>
       <c r="H207" t="s">
-        <v>1394</v>
+        <v>1387</v>
+      </c>
+      <c r="I207" t="s">
+        <v>112</v>
       </c>
       <c r="L207" t="str">
-        <f t="shared" ref="L207:L218" si="38">_xlfn.TEXTJOIN("", TRUE, E207:K207)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0001_sA_01.png</v>
+        <f>_xlfn.TEXTJOIN("", TRUE, E207:K207)</f>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/04_=f-nb/0001_=f-nb_01.png</v>
       </c>
       <c r="N207" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="208" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A208" s="2" t="s">
-        <v>1393</v>
+      <c r="A208" s="5" t="s">
+        <v>1371</v>
       </c>
       <c r="B208">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C208" t="s">
-        <v>47</v>
-      </c>
-      <c r="F208" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G208" t="s">
-        <v>1376</v>
-      </c>
-      <c r="H208" t="s">
-        <v>1395</v>
-      </c>
-      <c r="L208" t="str">
-        <f t="shared" si="38"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0010_sA_seit-MR_02.png</v>
+        <v>45</v>
+      </c>
+      <c r="D208" t="s">
+        <v>1382</v>
       </c>
       <c r="N208" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="209" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A209" s="2" t="s">
-        <v>1393</v>
-      </c>
-      <c r="B209">
-        <v>4</v>
-      </c>
-      <c r="C209" t="s">
-        <v>45</v>
-      </c>
-      <c r="D209" t="s">
-        <v>1143</v>
-      </c>
-      <c r="N209" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="210" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A210" s="2" t="s">
-        <v>1393</v>
-      </c>
-      <c r="B210">
-        <v>5</v>
-      </c>
-      <c r="C210" t="s">
-        <v>47</v>
-      </c>
-      <c r="F210" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G210" t="s">
-        <v>1376</v>
-      </c>
-      <c r="H210" t="s">
-        <v>1396</v>
-      </c>
-      <c r="L210" t="str">
-        <f t="shared" si="38"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0020_sA_MR_01.png</v>
-      </c>
-      <c r="N210" t="s">
-        <v>93</v>
-      </c>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A209" s="5"/>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A210" s="5"/>
     </row>
     <row r="211" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B211">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C211" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D211" t="s">
-        <v>1408</v>
-      </c>
-      <c r="N211" t="s">
-        <v>93</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="212" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B212">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C212" t="s">
         <v>47</v>
@@ -12767,42 +12895,42 @@
         <v>1375</v>
       </c>
       <c r="G212" t="s">
-        <v>1376</v>
+        <v>1411</v>
       </c>
       <c r="H212" t="s">
-        <v>1397</v>
+        <v>1412</v>
       </c>
       <c r="L212" t="str">
-        <f t="shared" si="38"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0030_sA_NR_01.png</v>
+        <f t="shared" ref="L212:L227" si="44">_xlfn.TEXTJOIN("", TRUE, E212:K212)</f>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0001_sA-anx-HA=f-nb_MR_01.png</v>
       </c>
       <c r="N212" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="213" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B213">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C213" t="s">
         <v>45</v>
       </c>
       <c r="D213" t="s">
-        <v>1144</v>
+        <v>1408</v>
       </c>
       <c r="N213" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="214" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B214">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C214" t="s">
         <v>47</v>
@@ -12811,25 +12939,25 @@
         <v>1375</v>
       </c>
       <c r="G214" t="s">
-        <v>1376</v>
+        <v>1411</v>
       </c>
       <c r="H214" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="L214" t="str">
-        <f t="shared" si="38"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0040_sA_NR_02.png</v>
+        <f t="shared" si="44"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0010_sA-anx-HA=f-nb-NR_01.png</v>
       </c>
       <c r="N214" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="215" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B215">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C215" t="s">
         <v>45</v>
@@ -12838,31 +12966,21 @@
         <v>1144</v>
       </c>
       <c r="N215" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="216" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B216">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C216" t="s">
-        <v>47</v>
-      </c>
-      <c r="F216" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G216" t="s">
-        <v>1376</v>
-      </c>
-      <c r="H216" t="s">
-        <v>1399</v>
-      </c>
-      <c r="L216" t="str">
-        <f t="shared" si="38"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0050_sA_GR_01.png</v>
+        <v>17</v>
+      </c>
+      <c r="D216" t="s">
+        <v>1423</v>
       </c>
       <c r="N216" t="s">
         <v>93</v>
@@ -12870,16 +12988,26 @@
     </row>
     <row r="217" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B217">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C217" t="s">
-        <v>45</v>
-      </c>
-      <c r="D217" t="s">
-        <v>1146</v>
+        <v>47</v>
+      </c>
+      <c r="F217" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G217" t="s">
+        <v>1411</v>
+      </c>
+      <c r="H217" t="s">
+        <v>1414</v>
+      </c>
+      <c r="L217" t="str">
+        <f t="shared" si="44"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0020_sA-anx-HA=f_01.png</v>
       </c>
       <c r="N217" t="s">
         <v>93</v>
@@ -12887,10 +13015,10 @@
     </row>
     <row r="218" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B218">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C218" t="s">
         <v>47</v>
@@ -12899,14 +13027,14 @@
         <v>1375</v>
       </c>
       <c r="G218" t="s">
-        <v>1376</v>
+        <v>1411</v>
       </c>
       <c r="H218" t="s">
-        <v>1400</v>
+        <v>1415</v>
       </c>
       <c r="L218" t="str">
-        <f t="shared" si="38"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0060_sA_GR_02.png</v>
+        <f t="shared" si="44"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0030_sA-anx-HA=f_02.png</v>
       </c>
       <c r="N218" t="s">
         <v>93</v>
@@ -12914,33 +13042,43 @@
     </row>
     <row r="219" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B219">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C219" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D219" t="s">
-        <v>1146</v>
+        <v>1424</v>
       </c>
       <c r="N219" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="220" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B220">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C220" t="s">
-        <v>17</v>
-      </c>
-      <c r="D220" t="s">
-        <v>644</v>
+        <v>47</v>
+      </c>
+      <c r="F220" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G220" t="s">
+        <v>1411</v>
+      </c>
+      <c r="H220" t="s">
+        <v>1416</v>
+      </c>
+      <c r="L220" t="str">
+        <f t="shared" si="44"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0040_sA-anx-wAs-HA=f_01.png</v>
       </c>
       <c r="N220" t="s">
         <v>95</v>
@@ -12948,10 +13086,10 @@
     </row>
     <row r="221" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A221" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B221">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C221" t="s">
         <v>47</v>
@@ -12960,17 +13098,14 @@
         <v>1375</v>
       </c>
       <c r="G221" t="s">
-        <v>1383</v>
+        <v>1411</v>
       </c>
       <c r="H221" t="s">
-        <v>1386</v>
-      </c>
-      <c r="I221" t="s">
-        <v>112</v>
+        <v>1417</v>
       </c>
       <c r="L221" t="str">
-        <f t="shared" ref="L221" si="39">_xlfn.TEXTJOIN("", TRUE, E221:K221)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/02_anx/0001_anx_01.png</v>
+        <f t="shared" si="44"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0050_sA-anx-wAs-HA=f_NR-selten-Gr-oft_01.png</v>
       </c>
       <c r="N221" t="s">
         <v>95</v>
@@ -12978,43 +13113,33 @@
     </row>
     <row r="222" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B222">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C222" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D222" t="s">
-        <v>1401</v>
+        <v>1427</v>
       </c>
       <c r="N222" t="s">
-        <v>1410</v>
+        <v>95</v>
       </c>
     </row>
     <row r="223" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B223">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C223" t="s">
-        <v>47</v>
-      </c>
-      <c r="F223" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G223" t="s">
-        <v>1384</v>
-      </c>
-      <c r="H223" t="s">
-        <v>1402</v>
-      </c>
-      <c r="L223" t="str">
-        <f t="shared" ref="L223:L231" si="40">_xlfn.TEXTJOIN("", TRUE, E223:K223)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0001_HA_01.png</v>
+        <v>17</v>
+      </c>
+      <c r="D223" t="s">
+        <v>1425</v>
       </c>
       <c r="N223" t="s">
         <v>1410</v>
@@ -13022,10 +13147,10 @@
     </row>
     <row r="224" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B224">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C224" t="s">
         <v>47</v>
@@ -13034,14 +13159,14 @@
         <v>1375</v>
       </c>
       <c r="G224" t="s">
-        <v>1384</v>
+        <v>1411</v>
       </c>
       <c r="H224" t="s">
-        <v>1403</v>
+        <v>1418</v>
       </c>
       <c r="L224" t="str">
-        <f t="shared" si="40"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0010_HA_02.png</v>
+        <f t="shared" si="44"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0060_sA-anx-Dd-wAs-HA=f_D.18_01.png</v>
       </c>
       <c r="N224" t="s">
         <v>1410</v>
@@ -13049,26 +13174,16 @@
     </row>
     <row r="225" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B225">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C225" t="s">
-        <v>47</v>
-      </c>
-      <c r="F225" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G225" t="s">
-        <v>1384</v>
-      </c>
-      <c r="H225" t="s">
-        <v>1404</v>
-      </c>
-      <c r="L225" t="str">
-        <f t="shared" si="40"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0020_HA_MR_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D225" t="s">
+        <v>1428</v>
       </c>
       <c r="N225" t="s">
         <v>1410</v>
@@ -13076,27 +13191,27 @@
     </row>
     <row r="226" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B226">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C226" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D226" t="s">
-        <v>1408</v>
+        <v>1426</v>
       </c>
       <c r="N226" t="s">
-        <v>1410</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="227" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B227">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C227" t="s">
         <v>47</v>
@@ -13105,616 +13220,695 @@
         <v>1375</v>
       </c>
       <c r="G227" t="s">
-        <v>1384</v>
+        <v>1411</v>
       </c>
       <c r="H227" t="s">
-        <v>1405</v>
+        <v>1419</v>
       </c>
       <c r="L227" t="str">
-        <f t="shared" si="40"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0030_HA_MR_02.png</v>
+        <f t="shared" si="44"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0070_sA-anx-Dd-wAs-snb-HA=f_D.18_01.png</v>
       </c>
       <c r="N227" t="s">
-        <v>1410</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="228" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B228">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C228" t="s">
         <v>45</v>
       </c>
       <c r="D228" t="s">
+        <v>1428</v>
+      </c>
+      <c r="N228" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A229" s="5"/>
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A230" s="5"/>
+    </row>
+    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A231" s="5"/>
+    </row>
+    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A232" s="5"/>
+    </row>
+    <row r="233" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A233" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B233">
+        <v>1</v>
+      </c>
+      <c r="C233" t="s">
+        <v>17</v>
+      </c>
+      <c r="D233" t="s">
+        <v>1229</v>
+      </c>
+      <c r="N233" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A234" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B234">
+        <v>2</v>
+      </c>
+      <c r="C234" t="s">
+        <v>47</v>
+      </c>
+      <c r="F234" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G234" t="s">
+        <v>1376</v>
+      </c>
+      <c r="H234" t="s">
+        <v>1394</v>
+      </c>
+      <c r="L234" t="str">
+        <f t="shared" ref="L234:L245" si="45">_xlfn.TEXTJOIN("", TRUE, E234:K234)</f>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0001_sA_01.png</v>
+      </c>
+      <c r="N234" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A235" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B235">
+        <v>3</v>
+      </c>
+      <c r="C235" t="s">
+        <v>47</v>
+      </c>
+      <c r="F235" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G235" t="s">
+        <v>1376</v>
+      </c>
+      <c r="H235" t="s">
+        <v>1395</v>
+      </c>
+      <c r="L235" t="str">
+        <f t="shared" si="45"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0010_sA_seit-MR_02.png</v>
+      </c>
+      <c r="N235" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A236" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B236">
+        <v>4</v>
+      </c>
+      <c r="C236" t="s">
+        <v>45</v>
+      </c>
+      <c r="D236" t="s">
+        <v>1143</v>
+      </c>
+      <c r="N236" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A237" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B237">
+        <v>5</v>
+      </c>
+      <c r="C237" t="s">
+        <v>47</v>
+      </c>
+      <c r="F237" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G237" t="s">
+        <v>1376</v>
+      </c>
+      <c r="H237" t="s">
+        <v>1396</v>
+      </c>
+      <c r="L237" t="str">
+        <f t="shared" si="45"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0020_sA_MR_01.png</v>
+      </c>
+      <c r="N237" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A238" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B238">
+        <v>6</v>
+      </c>
+      <c r="C238" t="s">
+        <v>45</v>
+      </c>
+      <c r="D238" t="s">
         <v>1408</v>
       </c>
-      <c r="N228" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="229" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A229" s="2" t="s">
+      <c r="N238" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A239" s="2" t="s">
         <v>1393</v>
       </c>
-      <c r="B229">
-        <v>24</v>
-      </c>
-      <c r="C229" t="s">
+      <c r="B239">
+        <v>7</v>
+      </c>
+      <c r="C239" t="s">
         <v>47</v>
       </c>
-      <c r="F229" t="s">
+      <c r="F239" t="s">
         <v>1375</v>
       </c>
-      <c r="G229" t="s">
-        <v>1384</v>
-      </c>
-      <c r="H229" t="s">
-        <v>1406</v>
-      </c>
-      <c r="L229" t="str">
-        <f t="shared" si="40"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0040_HA_NR_01.png</v>
-      </c>
-      <c r="N229" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="230" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A230" s="2" t="s">
+      <c r="G239" t="s">
+        <v>1376</v>
+      </c>
+      <c r="H239" t="s">
+        <v>1397</v>
+      </c>
+      <c r="L239" t="str">
+        <f t="shared" si="45"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0030_sA_NR_01.png</v>
+      </c>
+      <c r="N239" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A240" s="2" t="s">
         <v>1393</v>
       </c>
-      <c r="B230">
-        <v>25</v>
-      </c>
-      <c r="C230" t="s">
+      <c r="B240">
+        <v>8</v>
+      </c>
+      <c r="C240" t="s">
         <v>45</v>
       </c>
-      <c r="D230" t="s">
+      <c r="D240" t="s">
         <v>1144</v>
       </c>
-      <c r="N230" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="231" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A231" s="2" t="s">
+      <c r="N240" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A241" s="2" t="s">
         <v>1393</v>
       </c>
-      <c r="B231">
-        <v>26</v>
-      </c>
-      <c r="C231" t="s">
+      <c r="B241">
+        <v>9</v>
+      </c>
+      <c r="C241" t="s">
         <v>47</v>
       </c>
-      <c r="F231" t="s">
+      <c r="F241" t="s">
         <v>1375</v>
       </c>
-      <c r="G231" t="s">
-        <v>1384</v>
-      </c>
-      <c r="H231" t="s">
-        <v>1407</v>
-      </c>
-      <c r="L231" t="str">
-        <f t="shared" si="40"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0050_HA_Sp_01.png</v>
-      </c>
-      <c r="N231" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="232" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A232" s="2" t="s">
+      <c r="G241" t="s">
+        <v>1376</v>
+      </c>
+      <c r="H241" t="s">
+        <v>1398</v>
+      </c>
+      <c r="L241" t="str">
+        <f t="shared" si="45"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0040_sA_NR_02.png</v>
+      </c>
+      <c r="N241" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A242" s="2" t="s">
         <v>1393</v>
       </c>
-      <c r="B232">
-        <v>27</v>
-      </c>
-      <c r="C232" t="s">
+      <c r="B242">
+        <v>10</v>
+      </c>
+      <c r="C242" t="s">
         <v>45</v>
       </c>
-      <c r="D232" t="s">
-        <v>1409</v>
-      </c>
-    </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A233" s="5"/>
-    </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A234" s="5"/>
-    </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A235" s="5"/>
-    </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A236" s="5"/>
-    </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A237" s="5"/>
-    </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A238" s="5"/>
-    </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A239" s="5"/>
-    </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A240" s="5"/>
-    </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A241" s="5"/>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A242" s="5"/>
-    </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A243" s="5"/>
-    </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A244" s="5"/>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A246" t="s">
-        <v>1044</v>
+      <c r="D242" t="s">
+        <v>1144</v>
+      </c>
+      <c r="N242" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A243" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B243">
+        <v>11</v>
+      </c>
+      <c r="C243" t="s">
+        <v>47</v>
+      </c>
+      <c r="F243" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G243" t="s">
+        <v>1376</v>
+      </c>
+      <c r="H243" t="s">
+        <v>1399</v>
+      </c>
+      <c r="L243" t="str">
+        <f t="shared" si="45"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0050_sA_GR_01.png</v>
+      </c>
+      <c r="N243" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="244" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A244" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B244">
+        <v>12</v>
+      </c>
+      <c r="C244" t="s">
+        <v>45</v>
+      </c>
+      <c r="D244" t="s">
+        <v>1146</v>
+      </c>
+      <c r="N244" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="245" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A245" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B245">
+        <v>13</v>
+      </c>
+      <c r="C245" t="s">
+        <v>47</v>
+      </c>
+      <c r="F245" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G245" t="s">
+        <v>1376</v>
+      </c>
+      <c r="H245" t="s">
+        <v>1400</v>
+      </c>
+      <c r="L245" t="str">
+        <f t="shared" si="45"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0060_sA_GR_02.png</v>
+      </c>
+      <c r="N245" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="246" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A246" s="2" t="s">
+        <v>1393</v>
       </c>
       <c r="B246">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C246" t="s">
         <v>45</v>
       </c>
       <c r="D246" t="s">
-        <v>1049</v>
+        <v>1146</v>
       </c>
       <c r="N246" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A247" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B247" s="27">
-        <v>2</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="247" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A247" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B247">
+        <v>15</v>
       </c>
       <c r="C247" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D247" t="s">
-        <v>1055</v>
+        <v>644</v>
       </c>
       <c r="N247" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A248" t="s">
-        <v>1044</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A248" s="2" t="s">
+        <v>1393</v>
       </c>
       <c r="B248">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C248" t="s">
         <v>47</v>
       </c>
       <c r="F248" t="s">
-        <v>417</v>
+        <v>1375</v>
       </c>
       <c r="G248" t="s">
-        <v>418</v>
+        <v>1383</v>
       </c>
       <c r="H248" t="s">
-        <v>419</v>
+        <v>1386</v>
       </c>
       <c r="I248" t="s">
         <v>112</v>
       </c>
       <c r="L248" t="str">
-        <f t="shared" ref="L248:L249" si="41">_xlfn.TEXTJOIN("", TRUE, E248:K248)</f>
-        <v>02_Slots/Personennamen/Namen/f/01_tA-dj-Gottheit/01_tA-dj_01.png</v>
+        <f t="shared" ref="L248" si="46">_xlfn.TEXTJOIN("", TRUE, E248:K248)</f>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/02_anx/0001_anx_01.png</v>
       </c>
       <c r="N248" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A249" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B249" s="27">
-        <v>4</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="249" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A249" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B249">
+        <v>17</v>
       </c>
       <c r="C249" t="s">
+        <v>17</v>
+      </c>
+      <c r="D249" t="s">
+        <v>1401</v>
+      </c>
+      <c r="N249" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A250" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B250">
+        <v>18</v>
+      </c>
+      <c r="C250" t="s">
         <v>47</v>
       </c>
-      <c r="F249" t="s">
-        <v>417</v>
-      </c>
-      <c r="G249" t="s">
-        <v>418</v>
-      </c>
-      <c r="H249" t="s">
-        <v>420</v>
-      </c>
-      <c r="I249" t="s">
-        <v>112</v>
-      </c>
-      <c r="L249" t="str">
-        <f t="shared" si="41"/>
-        <v>02_Slots/Personennamen/Namen/f/01_tA-dj-Gottheit/01_tA-dj_02.png</v>
-      </c>
-      <c r="N249" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A250" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B250">
-        <v>5</v>
-      </c>
-      <c r="C250" t="s">
-        <v>45</v>
-      </c>
-      <c r="D250" t="s">
-        <v>1046</v>
+      <c r="F250" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G250" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H250" t="s">
+        <v>1402</v>
+      </c>
+      <c r="L250" t="str">
+        <f t="shared" ref="L250:L258" si="47">_xlfn.TEXTJOIN("", TRUE, E250:K250)</f>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0001_HA_01.png</v>
       </c>
       <c r="N250" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A251" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B251" s="27">
-        <v>6</v>
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="251" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A251" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B251">
+        <v>19</v>
       </c>
       <c r="C251" t="s">
-        <v>46</v>
-      </c>
-      <c r="D251" t="s">
-        <v>48</v>
-      </c>
-      <c r="M251" t="s">
-        <v>97</v>
+        <v>47</v>
+      </c>
+      <c r="F251" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G251" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H251" t="s">
+        <v>1403</v>
+      </c>
+      <c r="L251" t="str">
+        <f t="shared" si="47"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0010_HA_02.png</v>
       </c>
       <c r="N251" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B252" s="27"/>
-    </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A253" t="s">
-        <v>1045</v>
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="252" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A252" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B252">
+        <v>20</v>
+      </c>
+      <c r="C252" t="s">
+        <v>47</v>
+      </c>
+      <c r="F252" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G252" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H252" t="s">
+        <v>1404</v>
+      </c>
+      <c r="L252" t="str">
+        <f t="shared" si="47"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0020_HA_MR_01.png</v>
+      </c>
+      <c r="N252" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A253" s="2" t="s">
+        <v>1393</v>
       </c>
       <c r="B253">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C253" t="s">
         <v>45</v>
       </c>
       <c r="D253" t="s">
-        <v>1049</v>
+        <v>1408</v>
       </c>
       <c r="N253" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A254" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B254" s="27">
-        <v>2</v>
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A254" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B254">
+        <v>22</v>
       </c>
       <c r="C254" t="s">
+        <v>47</v>
+      </c>
+      <c r="F254" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G254" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H254" t="s">
+        <v>1405</v>
+      </c>
+      <c r="L254" t="str">
+        <f t="shared" si="47"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0030_HA_MR_02.png</v>
+      </c>
+      <c r="N254" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A255" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B255">
+        <v>23</v>
+      </c>
+      <c r="C255" t="s">
         <v>45</v>
       </c>
-      <c r="D254" t="s">
-        <v>1056</v>
-      </c>
-      <c r="N254" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A255" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B255">
-        <v>3</v>
-      </c>
-      <c r="C255" t="s">
-        <v>47</v>
-      </c>
-      <c r="F255" t="s">
-        <v>422</v>
-      </c>
-      <c r="G255" t="s">
-        <v>443</v>
-      </c>
-      <c r="H255" t="s">
-        <v>423</v>
-      </c>
-      <c r="I255" t="s">
-        <v>112</v>
-      </c>
-      <c r="L255" t="str">
-        <f t="shared" ref="L255:L256" si="42">_xlfn.TEXTJOIN("", TRUE, E255:K255)</f>
-        <v>02_Slots/Personennamen/Namen/m/01_pA-dj-Gottheit/01_pA-dj_01.png</v>
+      <c r="D255" t="s">
+        <v>1408</v>
       </c>
       <c r="N255" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A256" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B256" s="27">
-        <v>4</v>
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="256" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A256" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B256">
+        <v>24</v>
       </c>
       <c r="C256" t="s">
         <v>47</v>
       </c>
       <c r="F256" t="s">
-        <v>422</v>
+        <v>1375</v>
       </c>
       <c r="G256" t="s">
-        <v>443</v>
+        <v>1384</v>
       </c>
       <c r="H256" t="s">
-        <v>424</v>
-      </c>
-      <c r="I256" t="s">
-        <v>112</v>
+        <v>1406</v>
       </c>
       <c r="L256" t="str">
-        <f t="shared" si="42"/>
-        <v>02_Slots/Personennamen/Namen/m/01_pA-dj-Gottheit/01_pA-dj_02.png</v>
+        <f t="shared" si="47"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0040_HA_NR_01.png</v>
       </c>
       <c r="N256" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A257" t="s">
-        <v>1045</v>
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A257" s="2" t="s">
+        <v>1393</v>
       </c>
       <c r="B257">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C257" t="s">
         <v>45</v>
       </c>
       <c r="D257" t="s">
-        <v>1046</v>
+        <v>1144</v>
       </c>
       <c r="N257" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A258" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B258" s="27">
-        <v>6</v>
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A258" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B258">
+        <v>26</v>
       </c>
       <c r="C258" t="s">
-        <v>46</v>
-      </c>
-      <c r="D258" t="s">
-        <v>48</v>
-      </c>
-      <c r="M258" t="s">
-        <v>97</v>
+        <v>47</v>
+      </c>
+      <c r="F258" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G258" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H258" t="s">
+        <v>1407</v>
+      </c>
+      <c r="L258" t="str">
+        <f t="shared" si="47"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0050_HA_Sp_01.png</v>
       </c>
       <c r="N258" t="s">
-        <v>90</v>
-      </c>
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A259" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B259">
+        <v>27</v>
+      </c>
+      <c r="C259" t="s">
+        <v>45</v>
+      </c>
+      <c r="D259" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A260" s="5"/>
+    </row>
+    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A261" s="5"/>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A262" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B262">
-        <v>1</v>
-      </c>
-      <c r="C262" t="s">
-        <v>45</v>
-      </c>
-      <c r="D262" t="s">
-        <v>1049</v>
-      </c>
-      <c r="N262" t="s">
-        <v>90</v>
-      </c>
+      <c r="A262" s="5"/>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A263" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B263">
-        <v>2</v>
-      </c>
-      <c r="C263" t="s">
-        <v>46</v>
-      </c>
-      <c r="D263" t="s">
-        <v>50</v>
-      </c>
-      <c r="M263" t="s">
-        <v>99</v>
-      </c>
-      <c r="N263" t="s">
-        <v>90</v>
-      </c>
+      <c r="A263" s="5"/>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A264" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B264">
-        <v>3</v>
-      </c>
-      <c r="C264" t="s">
-        <v>45</v>
-      </c>
-      <c r="D264" t="s">
-        <v>1226</v>
-      </c>
-      <c r="N264" t="s">
-        <v>90</v>
-      </c>
+      <c r="A264" s="5"/>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A265" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B265">
-        <v>4</v>
-      </c>
-      <c r="C265" t="s">
-        <v>45</v>
-      </c>
-      <c r="D265" t="s">
-        <v>1227</v>
-      </c>
-      <c r="N265" t="s">
-        <v>90</v>
-      </c>
+      <c r="A265" s="5"/>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A266" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B266">
-        <v>5</v>
-      </c>
-      <c r="C266" t="s">
-        <v>46</v>
-      </c>
-      <c r="D266" t="s">
-        <v>50</v>
-      </c>
-      <c r="M266" t="s">
-        <v>99</v>
-      </c>
-      <c r="N266" t="s">
-        <v>90</v>
-      </c>
+      <c r="A266" s="5"/>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A267" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B267">
-        <v>6</v>
-      </c>
-      <c r="C267" t="s">
-        <v>45</v>
-      </c>
-      <c r="D267" t="s">
-        <v>1228</v>
-      </c>
-      <c r="N267" t="s">
-        <v>90</v>
-      </c>
+      <c r="A267" s="5"/>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A268" s="5"/>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A269" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B269">
-        <v>1</v>
-      </c>
-      <c r="C269" t="s">
-        <v>45</v>
-      </c>
-      <c r="D269" t="s">
-        <v>1049</v>
-      </c>
-      <c r="N269" t="s">
-        <v>90</v>
-      </c>
+      <c r="A269" s="5"/>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A270" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B270">
-        <v>2</v>
-      </c>
-      <c r="C270" t="s">
-        <v>46</v>
-      </c>
-      <c r="D270" t="s">
-        <v>50</v>
-      </c>
-      <c r="M270" t="s">
-        <v>99</v>
-      </c>
-      <c r="N270" t="s">
-        <v>90</v>
-      </c>
+      <c r="A270" s="5"/>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A271" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B271">
-        <v>3</v>
-      </c>
-      <c r="C271" t="s">
-        <v>45</v>
-      </c>
-      <c r="D271" t="s">
-        <v>1226</v>
-      </c>
-      <c r="N271" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A272" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B272">
-        <v>4</v>
-      </c>
-      <c r="C272" t="s">
-        <v>45</v>
-      </c>
-      <c r="D272" t="s">
-        <v>1229</v>
-      </c>
-      <c r="N272" t="s">
-        <v>90</v>
-      </c>
+      <c r="A271" s="5"/>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>1224</v>
+        <v>1044</v>
       </c>
       <c r="B273">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C273" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D273" t="s">
-        <v>50</v>
-      </c>
-      <c r="M273" t="s">
-        <v>99</v>
+        <v>1049</v>
       </c>
       <c r="N273" t="s">
         <v>90</v>
@@ -13722,126 +13916,573 @@
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B274">
-        <v>6</v>
+        <v>1044</v>
+      </c>
+      <c r="B274" s="27">
+        <v>2</v>
       </c>
       <c r="C274" t="s">
         <v>45</v>
       </c>
       <c r="D274" t="s">
-        <v>1228</v>
+        <v>1055</v>
       </c>
       <c r="N274" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="276" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A276" s="5" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B276">
-        <v>1</v>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B275">
+        <v>3</v>
+      </c>
+      <c r="C275" t="s">
+        <v>47</v>
+      </c>
+      <c r="F275" t="s">
+        <v>417</v>
+      </c>
+      <c r="G275" t="s">
+        <v>418</v>
+      </c>
+      <c r="H275" t="s">
+        <v>419</v>
+      </c>
+      <c r="I275" t="s">
+        <v>112</v>
+      </c>
+      <c r="L275" t="str">
+        <f t="shared" ref="L275:L276" si="48">_xlfn.TEXTJOIN("", TRUE, E275:K275)</f>
+        <v>02_Slots/Personennamen/Namen/f/01_tA-dj-Gottheit/01_tA-dj_01.png</v>
+      </c>
+      <c r="N275" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B276" s="27">
+        <v>4</v>
       </c>
       <c r="C276" t="s">
-        <v>45</v>
-      </c>
-      <c r="D276" t="s">
-        <v>1049</v>
+        <v>47</v>
+      </c>
+      <c r="F276" t="s">
+        <v>417</v>
+      </c>
+      <c r="G276" t="s">
+        <v>418</v>
+      </c>
+      <c r="H276" t="s">
+        <v>420</v>
+      </c>
+      <c r="I276" t="s">
+        <v>112</v>
+      </c>
+      <c r="L276" t="str">
+        <f t="shared" si="48"/>
+        <v>02_Slots/Personennamen/Namen/f/01_tA-dj-Gottheit/01_tA-dj_02.png</v>
       </c>
       <c r="N276" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="277" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A277" s="5" t="s">
-        <v>1225</v>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>1044</v>
       </c>
       <c r="B277">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C277" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D277" t="s">
-        <v>50</v>
-      </c>
-      <c r="M277" t="s">
-        <v>99</v>
+        <v>1046</v>
       </c>
       <c r="N277" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="278" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A278" s="5" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B278">
-        <v>3</v>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B278" s="27">
+        <v>6</v>
       </c>
       <c r="C278" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D278" t="s">
-        <v>1228</v>
+        <v>48</v>
+      </c>
+      <c r="M278" t="s">
+        <v>97</v>
       </c>
       <c r="N278" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="279" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A279" s="5" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B279">
-        <v>4</v>
-      </c>
-      <c r="C279" t="s">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B279" s="27"/>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B280">
+        <v>1</v>
+      </c>
+      <c r="C280" t="s">
         <v>45</v>
       </c>
-      <c r="D279" t="s">
-        <v>1229</v>
-      </c>
-      <c r="N279" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="280" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A280" s="5" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B280">
-        <v>5</v>
-      </c>
-      <c r="C280" t="s">
-        <v>46</v>
-      </c>
       <c r="D280" t="s">
-        <v>50</v>
-      </c>
-      <c r="M280" t="s">
-        <v>99</v>
+        <v>1049</v>
       </c>
       <c r="N280" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="281" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A281" s="5" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B281">
-        <v>6</v>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B281" s="27">
+        <v>2</v>
       </c>
       <c r="C281" t="s">
         <v>45</v>
       </c>
       <c r="D281" t="s">
+        <v>1056</v>
+      </c>
+      <c r="N281" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B282">
+        <v>3</v>
+      </c>
+      <c r="C282" t="s">
+        <v>47</v>
+      </c>
+      <c r="F282" t="s">
+        <v>422</v>
+      </c>
+      <c r="G282" t="s">
+        <v>443</v>
+      </c>
+      <c r="H282" t="s">
+        <v>423</v>
+      </c>
+      <c r="I282" t="s">
+        <v>112</v>
+      </c>
+      <c r="L282" t="str">
+        <f t="shared" ref="L282:L283" si="49">_xlfn.TEXTJOIN("", TRUE, E282:K282)</f>
+        <v>02_Slots/Personennamen/Namen/m/01_pA-dj-Gottheit/01_pA-dj_01.png</v>
+      </c>
+      <c r="N282" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B283" s="27">
+        <v>4</v>
+      </c>
+      <c r="C283" t="s">
+        <v>47</v>
+      </c>
+      <c r="F283" t="s">
+        <v>422</v>
+      </c>
+      <c r="G283" t="s">
+        <v>443</v>
+      </c>
+      <c r="H283" t="s">
+        <v>424</v>
+      </c>
+      <c r="I283" t="s">
+        <v>112</v>
+      </c>
+      <c r="L283" t="str">
+        <f t="shared" si="49"/>
+        <v>02_Slots/Personennamen/Namen/m/01_pA-dj-Gottheit/01_pA-dj_02.png</v>
+      </c>
+      <c r="N283" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B284">
+        <v>5</v>
+      </c>
+      <c r="C284" t="s">
+        <v>45</v>
+      </c>
+      <c r="D284" t="s">
+        <v>1046</v>
+      </c>
+      <c r="N284" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B285" s="27">
+        <v>6</v>
+      </c>
+      <c r="C285" t="s">
+        <v>46</v>
+      </c>
+      <c r="D285" t="s">
+        <v>48</v>
+      </c>
+      <c r="M285" t="s">
+        <v>97</v>
+      </c>
+      <c r="N285" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A289" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B289">
+        <v>1</v>
+      </c>
+      <c r="C289" t="s">
+        <v>45</v>
+      </c>
+      <c r="D289" t="s">
+        <v>1049</v>
+      </c>
+      <c r="N289" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B290">
+        <v>2</v>
+      </c>
+      <c r="C290" t="s">
+        <v>46</v>
+      </c>
+      <c r="D290" t="s">
+        <v>50</v>
+      </c>
+      <c r="M290" t="s">
+        <v>99</v>
+      </c>
+      <c r="N290" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B291">
+        <v>3</v>
+      </c>
+      <c r="C291" t="s">
+        <v>45</v>
+      </c>
+      <c r="D291" t="s">
         <v>1226</v>
       </c>
-      <c r="N281" t="s">
+      <c r="N291" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A292" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B292">
+        <v>4</v>
+      </c>
+      <c r="C292" t="s">
+        <v>45</v>
+      </c>
+      <c r="D292" t="s">
+        <v>1227</v>
+      </c>
+      <c r="N292" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A293" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B293">
+        <v>5</v>
+      </c>
+      <c r="C293" t="s">
+        <v>46</v>
+      </c>
+      <c r="D293" t="s">
+        <v>50</v>
+      </c>
+      <c r="M293" t="s">
+        <v>99</v>
+      </c>
+      <c r="N293" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A294" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B294">
+        <v>6</v>
+      </c>
+      <c r="C294" t="s">
+        <v>45</v>
+      </c>
+      <c r="D294" t="s">
+        <v>1228</v>
+      </c>
+      <c r="N294" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="296" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A296" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B296">
+        <v>1</v>
+      </c>
+      <c r="C296" t="s">
+        <v>45</v>
+      </c>
+      <c r="D296" t="s">
+        <v>1049</v>
+      </c>
+      <c r="N296" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="297" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A297" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B297">
+        <v>2</v>
+      </c>
+      <c r="C297" t="s">
+        <v>46</v>
+      </c>
+      <c r="D297" t="s">
+        <v>50</v>
+      </c>
+      <c r="M297" t="s">
+        <v>99</v>
+      </c>
+      <c r="N297" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="298" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A298" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B298">
+        <v>3</v>
+      </c>
+      <c r="C298" t="s">
+        <v>45</v>
+      </c>
+      <c r="D298" t="s">
+        <v>1226</v>
+      </c>
+      <c r="N298" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="299" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A299" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B299">
+        <v>4</v>
+      </c>
+      <c r="C299" t="s">
+        <v>45</v>
+      </c>
+      <c r="D299" t="s">
+        <v>1229</v>
+      </c>
+      <c r="N299" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="300" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A300" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B300">
+        <v>5</v>
+      </c>
+      <c r="C300" t="s">
+        <v>46</v>
+      </c>
+      <c r="D300" t="s">
+        <v>50</v>
+      </c>
+      <c r="M300" t="s">
+        <v>99</v>
+      </c>
+      <c r="N300" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="301" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A301" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B301">
+        <v>6</v>
+      </c>
+      <c r="C301" t="s">
+        <v>45</v>
+      </c>
+      <c r="D301" t="s">
+        <v>1228</v>
+      </c>
+      <c r="N301" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="303" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A303" s="5" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B303">
+        <v>1</v>
+      </c>
+      <c r="C303" t="s">
+        <v>45</v>
+      </c>
+      <c r="D303" t="s">
+        <v>1049</v>
+      </c>
+      <c r="N303" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="304" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A304" s="5" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B304">
+        <v>2</v>
+      </c>
+      <c r="C304" t="s">
+        <v>46</v>
+      </c>
+      <c r="D304" t="s">
+        <v>50</v>
+      </c>
+      <c r="M304" t="s">
+        <v>99</v>
+      </c>
+      <c r="N304" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="305" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A305" s="5" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B305">
+        <v>3</v>
+      </c>
+      <c r="C305" t="s">
+        <v>45</v>
+      </c>
+      <c r="D305" t="s">
+        <v>1228</v>
+      </c>
+      <c r="N305" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="306" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A306" s="5" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B306">
+        <v>4</v>
+      </c>
+      <c r="C306" t="s">
+        <v>45</v>
+      </c>
+      <c r="D306" t="s">
+        <v>1229</v>
+      </c>
+      <c r="N306" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="307" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A307" s="5" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B307">
+        <v>5</v>
+      </c>
+      <c r="C307" t="s">
+        <v>46</v>
+      </c>
+      <c r="D307" t="s">
+        <v>50</v>
+      </c>
+      <c r="M307" t="s">
+        <v>99</v>
+      </c>
+      <c r="N307" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="308" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A308" s="5" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B308">
+        <v>6</v>
+      </c>
+      <c r="C308" t="s">
+        <v>45</v>
+      </c>
+      <c r="D308" t="s">
+        <v>1226</v>
+      </c>
+      <c r="N308" t="s">
         <v>90</v>
       </c>
     </row>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E2934E-3A32-3D4B-9D3E-E27ED654FC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A65100-16B1-4D45-93E5-4AADA291EF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19840" activeTab="4" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="-28800" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="5" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6721" uniqueCount="1502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6758" uniqueCount="1513">
   <si>
     <t>page_id</t>
   </si>
@@ -4572,6 +4572,39 @@
   <si>
     <t>0070_mw.t_Sp_01.png</t>
   </si>
+  <si>
+    <t>[[table:tb_epith_chons_001|Öffne]]</t>
+  </si>
+  <si>
+    <t>tb_epith_chons_001</t>
+  </si>
+  <si>
+    <t>0001_m-WAs.t_NR_01.png</t>
+  </si>
+  <si>
+    <t>0010_m-WAs.t_NR_02.png</t>
+  </si>
+  <si>
+    <t>epitheta/01-m-wAs.t/</t>
+  </si>
+  <si>
+    <t>*m wꜣs.t*</t>
+  </si>
+  <si>
+    <t>in Theben</t>
+  </si>
+  <si>
+    <t>*pꜣ iri sḫr.w m wꜣs.t*</t>
+  </si>
+  <si>
+    <t>der die Pläne in Theben macht</t>
+  </si>
+  <si>
+    <t>0001_pA-jrj-sxr.w-m-WAs.t_Sp_01.png</t>
+  </si>
+  <si>
+    <t>epitheta/02-pA-jrj-sxr.w-m-WAs.t/</t>
+  </si>
 </sst>
 </file>
 
@@ -4580,7 +4613,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4621,6 +4654,13 @@
       <i/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4695,7 +4735,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4781,6 +4821,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -5740,7 +5781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="7" customFormat="1" ht="136" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" s="7" customFormat="1" ht="119" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>62</v>
       </c>
@@ -10221,7 +10262,7 @@
         <v>1501</v>
       </c>
       <c r="L76" s="6" t="str">
-        <f t="shared" ref="L76:L77" si="12">_xlfn.TEXTJOIN("", TRUE, E76:K76)</f>
+        <f t="shared" ref="L76" si="12">_xlfn.TEXTJOIN("", TRUE, E76:K76)</f>
         <v>01_Textgattung/02_Denkmaelerformel/03-1_mw.t/0070_mw.t_Sp_01.png</v>
       </c>
       <c r="N76" s="6" t="s">
@@ -14493,16 +14534,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62D4F70-2351-5545-A291-11D662F747FD}">
-  <dimension ref="A1:L1135"/>
+  <dimension ref="A1:L1148"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.6640625" style="27" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.1640625" customWidth="1"/>
-    <col min="6" max="6" width="24.83203125" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="5" max="5" width="46.5" customWidth="1"/>
+    <col min="6" max="6" width="20.5" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="4.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -32370,7 +32411,7 @@
         <v>955</v>
       </c>
       <c r="L992" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D992:J992)</f>
+        <f t="shared" ref="L992:L993" si="129">_xlfn.TEXTJOIN("", TRUE, D992:K992)</f>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0360_Chons/0001_Xnsw_01.png</v>
       </c>
     </row>
@@ -32391,7 +32432,7 @@
         <v>956</v>
       </c>
       <c r="L993" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D993:J993)</f>
+        <f t="shared" si="129"/>
         <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0360_Chons/0010_Xnsw_02.png</v>
       </c>
     </row>
@@ -32464,238 +32505,195 @@
       <c r="C997" t="s">
         <v>108</v>
       </c>
+      <c r="L997" s="39" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="998" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L998" s="39"/>
+    </row>
+    <row r="999" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A999" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B999" s="27">
+        <v>1</v>
+      </c>
+      <c r="C999" t="s">
+        <v>39</v>
+      </c>
+      <c r="L999" s="39" t="s">
+        <v>1507</v>
+      </c>
     </row>
     <row r="1000" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1000" t="s">
-        <v>60</v>
+        <v>1503</v>
       </c>
       <c r="B1000" s="27">
-        <v>370</v>
+        <v>1</v>
       </c>
       <c r="C1000" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1000" t="s">
-        <v>678</v>
+        <v>105</v>
+      </c>
+      <c r="E1000" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F1000" t="s">
+        <v>1506</v>
+      </c>
+      <c r="G1000" t="s">
+        <v>1504</v>
+      </c>
+      <c r="I1000" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1000" t="s">
+        <v>1103</v>
+      </c>
+      <c r="K1000" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1000" t="str">
+        <f t="shared" ref="L1000:L1001" si="130">_xlfn.TEXTJOIN("", TRUE, D1000:K1000)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0360_Chons/epitheta/01-m-wAs.t/0001_m-WAs.t_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1001" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1001" t="s">
-        <v>60</v>
+        <v>1503</v>
       </c>
       <c r="B1001" s="27">
-        <v>370</v>
+        <v>1</v>
       </c>
       <c r="C1001" t="s">
         <v>105</v>
       </c>
       <c r="E1001" t="s">
-        <v>1210</v>
+        <v>1209</v>
+      </c>
+      <c r="F1001" t="s">
+        <v>1506</v>
       </c>
       <c r="G1001" t="s">
-        <v>958</v>
+        <v>1505</v>
+      </c>
+      <c r="I1001" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1001" t="s">
+        <v>1103</v>
+      </c>
+      <c r="K1001" t="s">
+        <v>1149</v>
       </c>
       <c r="L1001" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D1001:J1001)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0001_sbk_01.png</v>
+        <f t="shared" si="130"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0360_Chons/epitheta/01-m-wAs.t/0010_m-WAs.t_NR_02.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1002" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1002" t="s">
-        <v>60</v>
+        <v>1503</v>
       </c>
       <c r="B1002" s="27">
-        <v>370</v>
+        <v>1</v>
       </c>
       <c r="C1002" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1002" t="s">
-        <v>1210</v>
-      </c>
-      <c r="G1002" t="s">
-        <v>959</v>
-      </c>
-      <c r="L1002" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D1002:J1002)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0010_sbk_02.png</v>
+        <v>27</v>
+      </c>
+      <c r="L1002" s="39" t="s">
+        <v>1508</v>
       </c>
     </row>
     <row r="1003" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1003" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1003" s="27">
-        <v>370</v>
-      </c>
-      <c r="C1003" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1003" t="s">
-        <v>1210</v>
-      </c>
-      <c r="G1003" t="s">
-        <v>960</v>
-      </c>
-      <c r="L1003" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D1003:J1003)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0020_sbk_03.png</v>
-      </c>
+      <c r="L1003" s="39"/>
     </row>
     <row r="1004" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1004" t="s">
-        <v>60</v>
+        <v>1503</v>
       </c>
       <c r="B1004" s="27">
-        <v>370</v>
+        <v>2</v>
       </c>
       <c r="C1004" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1004" t="s">
-        <v>1210</v>
-      </c>
-      <c r="G1004" t="s">
-        <v>961</v>
-      </c>
-      <c r="I1004" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1004" t="s">
-        <v>1103</v>
-      </c>
-      <c r="K1004" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1004" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D1004:K1004)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0030_sbk_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+        <v>39</v>
+      </c>
+      <c r="L1004" s="39" t="s">
+        <v>1509</v>
       </c>
     </row>
     <row r="1005" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1005" t="s">
-        <v>60</v>
+        <v>1503</v>
       </c>
       <c r="B1005" s="27">
-        <v>370</v>
+        <v>2</v>
       </c>
       <c r="C1005" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E1005" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F1005" t="s">
-        <v>110</v>
+        <v>1512</v>
       </c>
       <c r="G1005" t="s">
-        <v>962</v>
+        <v>1511</v>
+      </c>
+      <c r="I1005" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1005" t="s">
+        <v>1156</v>
+      </c>
+      <c r="K1005" t="s">
+        <v>1149</v>
       </c>
       <c r="L1005" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D1005:J1005)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/det/0001_sbk_det_01.png</v>
+        <f t="shared" ref="L1005" si="131">_xlfn.TEXTJOIN("", TRUE, D1005:K1005)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0360_Chons/epitheta/02-pA-jrj-sxr.w-m-WAs.t/0001_pA-jrj-sxr.w-m-WAs.t_Sp_01.png &lt;sup&gt;(Sp.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1006" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1006" t="s">
-        <v>60</v>
+        <v>1503</v>
       </c>
       <c r="B1006" s="27">
-        <v>370</v>
+        <v>2</v>
       </c>
       <c r="C1006" t="s">
-        <v>107</v>
-      </c>
-      <c r="L1006" t="s">
-        <v>160</v>
+        <v>27</v>
+      </c>
+      <c r="L1006" s="39" t="s">
+        <v>1510</v>
       </c>
     </row>
     <row r="1007" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1007" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1007" s="27">
-        <v>370</v>
-      </c>
-      <c r="C1007" t="s">
-        <v>108</v>
-      </c>
+      <c r="L1007" s="39"/>
+    </row>
+    <row r="1008" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L1008" s="39"/>
+    </row>
+    <row r="1009" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L1009" s="39"/>
     </row>
     <row r="1010" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1010" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1010" s="27">
-        <v>380</v>
-      </c>
-      <c r="C1010" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1010" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="1011" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1011" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1011" s="27">
-        <v>380</v>
-      </c>
-      <c r="C1011" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1011" t="s">
-        <v>1211</v>
-      </c>
-      <c r="G1011" t="s">
-        <v>963</v>
-      </c>
-      <c r="L1011" t="str">
-        <f t="shared" ref="L1011:L1019" si="129">_xlfn.TEXTJOIN("", TRUE, D1011:J1011)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0001_srq.t_01.png</v>
-      </c>
-    </row>
-    <row r="1012" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1012" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1012" s="27">
-        <v>380</v>
-      </c>
-      <c r="C1012" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1012" t="s">
-        <v>1211</v>
-      </c>
-      <c r="G1012" t="s">
-        <v>964</v>
-      </c>
-      <c r="L1012" t="str">
-        <f t="shared" si="129"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0010_srq.t_02.png</v>
-      </c>
+      <c r="L1010" s="39"/>
     </row>
     <row r="1013" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1013" t="s">
         <v>60</v>
       </c>
       <c r="B1013" s="27">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C1013" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1013" t="s">
-        <v>1211</v>
-      </c>
-      <c r="G1013" t="s">
-        <v>965</v>
-      </c>
-      <c r="L1013" t="str">
-        <f t="shared" si="129"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0020_srq.t_03.png</v>
+        <v>39</v>
+      </c>
+      <c r="L1013" t="s">
+        <v>678</v>
       </c>
     </row>
     <row r="1014" spans="1:12" x14ac:dyDescent="0.2">
@@ -32703,29 +32701,20 @@
         <v>60</v>
       </c>
       <c r="B1014" s="27">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C1014" t="s">
         <v>105</v>
       </c>
       <c r="E1014" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="G1014" t="s">
-        <v>966</v>
-      </c>
-      <c r="I1014" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1014" t="s">
-        <v>1164</v>
-      </c>
-      <c r="K1014" t="s">
-        <v>1149</v>
+        <v>958</v>
       </c>
       <c r="L1014" t="str">
-        <f t="shared" ref="L1014:L1017" si="130">_xlfn.TEXTJOIN("", TRUE, D1014:K1014)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0030_srq.t_Pyr.-MR_01.png &lt;sup&gt;(Pyr.; NR)&lt;/sup&gt;</v>
+        <f>_xlfn.TEXTJOIN("", TRUE, D1014:J1014)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0001_sbk_01.png</v>
       </c>
     </row>
     <row r="1015" spans="1:12" x14ac:dyDescent="0.2">
@@ -32733,29 +32722,20 @@
         <v>60</v>
       </c>
       <c r="B1015" s="27">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C1015" t="s">
         <v>105</v>
       </c>
       <c r="E1015" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="G1015" t="s">
-        <v>967</v>
-      </c>
-      <c r="I1015" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1015" t="s">
-        <v>1150</v>
-      </c>
-      <c r="K1015" t="s">
-        <v>1149</v>
+        <v>959</v>
       </c>
       <c r="L1015" t="str">
-        <f t="shared" si="130"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0040_srq.t_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+        <f>_xlfn.TEXTJOIN("", TRUE, D1015:J1015)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0010_sbk_02.png</v>
       </c>
     </row>
     <row r="1016" spans="1:12" x14ac:dyDescent="0.2">
@@ -32763,29 +32743,20 @@
         <v>60</v>
       </c>
       <c r="B1016" s="27">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C1016" t="s">
         <v>105</v>
       </c>
       <c r="E1016" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="G1016" t="s">
-        <v>968</v>
-      </c>
-      <c r="I1016" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1016" t="s">
-        <v>1150</v>
-      </c>
-      <c r="K1016" t="s">
-        <v>1149</v>
+        <v>960</v>
       </c>
       <c r="L1016" t="str">
-        <f t="shared" si="130"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0050_srq.t_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+        <f>_xlfn.TEXTJOIN("", TRUE, D1016:J1016)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0020_sbk_03.png</v>
       </c>
     </row>
     <row r="1017" spans="1:12" x14ac:dyDescent="0.2">
@@ -32793,29 +32764,29 @@
         <v>60</v>
       </c>
       <c r="B1017" s="27">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C1017" t="s">
         <v>105</v>
       </c>
       <c r="E1017" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="G1017" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="I1017" t="s">
         <v>1147</v>
       </c>
       <c r="J1017" t="s">
-        <v>1150</v>
+        <v>1103</v>
       </c>
       <c r="K1017" t="s">
         <v>1149</v>
       </c>
       <c r="L1017" t="str">
-        <f t="shared" si="130"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0060_srq.t_GR_03.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+        <f>_xlfn.TEXTJOIN("", TRUE, D1017:K1017)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/0030_sbk_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1018" spans="1:12" x14ac:dyDescent="0.2">
@@ -32823,23 +32794,23 @@
         <v>60</v>
       </c>
       <c r="B1018" s="27">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C1018" t="s">
         <v>106</v>
       </c>
       <c r="E1018" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="F1018" t="s">
         <v>110</v>
       </c>
       <c r="G1018" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="L1018" t="str">
-        <f t="shared" si="129"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/det/0001_srq.t_det_01.png</v>
+        <f>_xlfn.TEXTJOIN("", TRUE, D1018:J1018)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0370_Sobek/det/0001_sbk_det_01.png</v>
       </c>
     </row>
     <row r="1019" spans="1:12" x14ac:dyDescent="0.2">
@@ -32847,23 +32818,13 @@
         <v>60</v>
       </c>
       <c r="B1019" s="27">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C1019" t="s">
-        <v>106</v>
-      </c>
-      <c r="E1019" t="s">
-        <v>1211</v>
-      </c>
-      <c r="F1019" t="s">
-        <v>110</v>
-      </c>
-      <c r="G1019" t="s">
-        <v>971</v>
-      </c>
-      <c r="L1019" t="str">
-        <f t="shared" si="129"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/det/0010_srq.t_det_02.png</v>
+        <v>107</v>
+      </c>
+      <c r="L1019" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="1020" spans="1:12" x14ac:dyDescent="0.2">
@@ -32871,24 +32832,24 @@
         <v>60</v>
       </c>
       <c r="B1020" s="27">
+        <v>370</v>
+      </c>
+      <c r="C1020" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1023" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1023" s="27">
         <v>380</v>
       </c>
-      <c r="C1020" t="s">
-        <v>107</v>
-      </c>
-      <c r="L1020" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="1021" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1021" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1021" s="27">
-        <v>380</v>
-      </c>
-      <c r="C1021" t="s">
-        <v>108</v>
+      <c r="C1023" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1023" t="s">
+        <v>679</v>
       </c>
     </row>
     <row r="1024" spans="1:12" x14ac:dyDescent="0.2">
@@ -32896,13 +32857,20 @@
         <v>60</v>
       </c>
       <c r="B1024" s="27">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C1024" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1024" t="s">
-        <v>680</v>
+        <v>105</v>
+      </c>
+      <c r="E1024" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G1024" t="s">
+        <v>963</v>
+      </c>
+      <c r="L1024" t="str">
+        <f t="shared" ref="L1024:L1032" si="132">_xlfn.TEXTJOIN("", TRUE, D1024:J1024)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0001_srq.t_01.png</v>
       </c>
     </row>
     <row r="1025" spans="1:12" x14ac:dyDescent="0.2">
@@ -32910,20 +32878,20 @@
         <v>60</v>
       </c>
       <c r="B1025" s="27">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C1025" t="s">
         <v>105</v>
       </c>
       <c r="E1025" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G1025" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="L1025" t="str">
-        <f t="shared" ref="L1025:L1031" si="131">_xlfn.TEXTJOIN("", TRUE, D1025:J1025)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0001_sxm.t_01.png</v>
+        <f t="shared" si="132"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0010_srq.t_02.png</v>
       </c>
     </row>
     <row r="1026" spans="1:12" x14ac:dyDescent="0.2">
@@ -32931,29 +32899,20 @@
         <v>60</v>
       </c>
       <c r="B1026" s="27">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C1026" t="s">
         <v>105</v>
       </c>
       <c r="E1026" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G1026" t="s">
-        <v>973</v>
-      </c>
-      <c r="I1026" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1026" t="s">
-        <v>1148</v>
-      </c>
-      <c r="K1026" t="s">
-        <v>1149</v>
+        <v>965</v>
       </c>
       <c r="L1026" t="str">
-        <f t="shared" ref="L1026:L1030" si="132">_xlfn.TEXTJOIN("", TRUE, D1026:K1026)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0010_sxm.t_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <f t="shared" si="132"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0020_srq.t_03.png</v>
       </c>
     </row>
     <row r="1027" spans="1:12" x14ac:dyDescent="0.2">
@@ -32961,29 +32920,29 @@
         <v>60</v>
       </c>
       <c r="B1027" s="27">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C1027" t="s">
         <v>105</v>
       </c>
       <c r="E1027" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G1027" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="I1027" t="s">
         <v>1147</v>
       </c>
       <c r="J1027" t="s">
-        <v>1148</v>
+        <v>1164</v>
       </c>
       <c r="K1027" t="s">
         <v>1149</v>
       </c>
       <c r="L1027" t="str">
-        <f t="shared" si="132"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0020_sxm.t_AR_02.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <f t="shared" ref="L1027:L1030" si="133">_xlfn.TEXTJOIN("", TRUE, D1027:K1027)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0030_srq.t_Pyr.-MR_01.png &lt;sup&gt;(Pyr.; NR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1028" spans="1:12" x14ac:dyDescent="0.2">
@@ -32991,29 +32950,29 @@
         <v>60</v>
       </c>
       <c r="B1028" s="27">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C1028" t="s">
         <v>105</v>
       </c>
       <c r="E1028" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G1028" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="I1028" t="s">
         <v>1147</v>
       </c>
       <c r="J1028" t="s">
-        <v>1103</v>
+        <v>1150</v>
       </c>
       <c r="K1028" t="s">
         <v>1149</v>
       </c>
       <c r="L1028" t="str">
-        <f t="shared" si="132"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0030_sxm.t_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+        <f t="shared" si="133"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0040_srq.t_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1029" spans="1:12" x14ac:dyDescent="0.2">
@@ -33021,16 +32980,16 @@
         <v>60</v>
       </c>
       <c r="B1029" s="27">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C1029" t="s">
         <v>105</v>
       </c>
       <c r="E1029" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G1029" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="I1029" t="s">
         <v>1147</v>
@@ -33042,8 +33001,8 @@
         <v>1149</v>
       </c>
       <c r="L1029" t="str">
-        <f t="shared" si="132"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0040_sxm.t_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+        <f t="shared" si="133"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0050_srq.t_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1030" spans="1:12" x14ac:dyDescent="0.2">
@@ -33051,16 +33010,16 @@
         <v>60</v>
       </c>
       <c r="B1030" s="27">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C1030" t="s">
         <v>105</v>
       </c>
       <c r="E1030" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G1030" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="I1030" t="s">
         <v>1147</v>
@@ -33072,8 +33031,8 @@
         <v>1149</v>
       </c>
       <c r="L1030" t="str">
-        <f t="shared" si="132"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0050_sxm.t_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+        <f t="shared" si="133"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/0060_srq.t_GR_03.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1031" spans="1:12" x14ac:dyDescent="0.2">
@@ -33081,14 +33040,23 @@
         <v>60</v>
       </c>
       <c r="B1031" s="27">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C1031" t="s">
         <v>106</v>
       </c>
+      <c r="E1031" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F1031" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1031" t="s">
+        <v>970</v>
+      </c>
       <c r="L1031" t="str">
-        <f t="shared" si="131"/>
-        <v/>
+        <f t="shared" si="132"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/det/0001_srq.t_det_01.png</v>
       </c>
     </row>
     <row r="1032" spans="1:12" x14ac:dyDescent="0.2">
@@ -33096,13 +33064,23 @@
         <v>60</v>
       </c>
       <c r="B1032" s="27">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C1032" t="s">
-        <v>107</v>
-      </c>
-      <c r="L1032" t="s">
-        <v>162</v>
+        <v>106</v>
+      </c>
+      <c r="E1032" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F1032" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1032" t="s">
+        <v>971</v>
+      </c>
+      <c r="L1032" t="str">
+        <f t="shared" si="132"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0380_Selkis/det/0010_srq.t_det_02.png</v>
       </c>
     </row>
     <row r="1033" spans="1:12" x14ac:dyDescent="0.2">
@@ -33110,24 +33088,24 @@
         <v>60</v>
       </c>
       <c r="B1033" s="27">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C1033" t="s">
+        <v>107</v>
+      </c>
+      <c r="L1033" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1034" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1034" s="27">
+        <v>380</v>
+      </c>
+      <c r="C1034" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="1036" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1036" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1036" s="27">
-        <v>400</v>
-      </c>
-      <c r="C1036" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1036" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="1037" spans="1:12" x14ac:dyDescent="0.2">
@@ -33135,20 +33113,13 @@
         <v>60</v>
       </c>
       <c r="B1037" s="27">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C1037" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1037" t="s">
-        <v>1213</v>
-      </c>
-      <c r="G1037" t="s">
-        <v>978</v>
-      </c>
-      <c r="L1037" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D1037:J1037)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0400_Sokar/0001_skr_01.png</v>
+        <v>39</v>
+      </c>
+      <c r="L1037" t="s">
+        <v>680</v>
       </c>
     </row>
     <row r="1038" spans="1:12" x14ac:dyDescent="0.2">
@@ -33156,23 +33127,20 @@
         <v>60</v>
       </c>
       <c r="B1038" s="27">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C1038" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E1038" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F1038" t="s">
-        <v>110</v>
+        <v>1212</v>
       </c>
       <c r="G1038" t="s">
-        <v>979</v>
+        <v>972</v>
       </c>
       <c r="L1038" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D1038:J1038)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0400_Sokar/det/0001_skr_det_01.png</v>
+        <f t="shared" ref="L1038:L1044" si="134">_xlfn.TEXTJOIN("", TRUE, D1038:J1038)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0001_sxm.t_01.png</v>
       </c>
     </row>
     <row r="1039" spans="1:12" x14ac:dyDescent="0.2">
@@ -33180,13 +33148,29 @@
         <v>60</v>
       </c>
       <c r="B1039" s="27">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C1039" t="s">
-        <v>107</v>
-      </c>
-      <c r="L1039" t="s">
-        <v>163</v>
+        <v>105</v>
+      </c>
+      <c r="E1039" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G1039" t="s">
+        <v>973</v>
+      </c>
+      <c r="I1039" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1039" t="s">
+        <v>1148</v>
+      </c>
+      <c r="K1039" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1039" t="str">
+        <f t="shared" ref="L1039:L1043" si="135">_xlfn.TEXTJOIN("", TRUE, D1039:K1039)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0010_sxm.t_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1040" spans="1:12" x14ac:dyDescent="0.2">
@@ -33194,10 +33178,89 @@
         <v>60</v>
       </c>
       <c r="B1040" s="27">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C1040" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="E1040" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G1040" t="s">
+        <v>974</v>
+      </c>
+      <c r="I1040" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1040" t="s">
+        <v>1148</v>
+      </c>
+      <c r="K1040" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1040" t="str">
+        <f t="shared" si="135"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0020_sxm.t_AR_02.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1041" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1041" s="27">
+        <v>390</v>
+      </c>
+      <c r="C1041" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1041" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G1041" t="s">
+        <v>975</v>
+      </c>
+      <c r="I1041" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1041" t="s">
+        <v>1103</v>
+      </c>
+      <c r="K1041" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1041" t="str">
+        <f t="shared" si="135"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0030_sxm.t_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1042" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1042" s="27">
+        <v>390</v>
+      </c>
+      <c r="C1042" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1042" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G1042" t="s">
+        <v>976</v>
+      </c>
+      <c r="I1042" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1042" t="s">
+        <v>1150</v>
+      </c>
+      <c r="K1042" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1042" t="str">
+        <f t="shared" si="135"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0040_sxm.t_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1043" spans="1:12" x14ac:dyDescent="0.2">
@@ -33205,13 +33268,29 @@
         <v>60</v>
       </c>
       <c r="B1043" s="27">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="C1043" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1043" t="s">
-        <v>682</v>
+        <v>105</v>
+      </c>
+      <c r="E1043" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G1043" t="s">
+        <v>977</v>
+      </c>
+      <c r="I1043" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1043" t="s">
+        <v>1150</v>
+      </c>
+      <c r="K1043" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1043" t="str">
+        <f t="shared" si="135"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0390_Sachmet/0050_sxm.t_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1044" spans="1:12" x14ac:dyDescent="0.2">
@@ -33219,20 +33298,14 @@
         <v>60</v>
       </c>
       <c r="B1044" s="27">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="C1044" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1044" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G1044" t="s">
-        <v>996</v>
+        <v>106</v>
       </c>
       <c r="L1044" t="str">
-        <f t="shared" ref="L1044:L1057" si="133">_xlfn.TEXTJOIN("", TRUE, D1044:J1044)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0001_stX_01.png</v>
+        <f t="shared" si="134"/>
+        <v/>
       </c>
     </row>
     <row r="1045" spans="1:12" x14ac:dyDescent="0.2">
@@ -33240,29 +33313,13 @@
         <v>60</v>
       </c>
       <c r="B1045" s="27">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="C1045" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1045" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G1045" t="s">
-        <v>997</v>
-      </c>
-      <c r="I1045" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1045" t="s">
-        <v>1148</v>
-      </c>
-      <c r="K1045" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1045" t="str">
-        <f t="shared" ref="L1045:L1055" si="134">_xlfn.TEXTJOIN("", TRUE, D1045:K1045)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0010_stX_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <v>107</v>
+      </c>
+      <c r="L1045" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="1046" spans="1:12" x14ac:dyDescent="0.2">
@@ -33270,89 +33327,10 @@
         <v>60</v>
       </c>
       <c r="B1046" s="27">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="C1046" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1046" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G1046" t="s">
-        <v>998</v>
-      </c>
-      <c r="I1046" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1046" t="s">
-        <v>1151</v>
-      </c>
-      <c r="K1046" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1046" t="str">
-        <f t="shared" si="134"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0020_stX_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
-      </c>
-    </row>
-    <row r="1047" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1047" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1047" s="27">
-        <v>410</v>
-      </c>
-      <c r="C1047" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1047" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G1047" t="s">
-        <v>999</v>
-      </c>
-      <c r="I1047" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1047" t="s">
-        <v>1165</v>
-      </c>
-      <c r="K1047" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1047" t="str">
-        <f t="shared" si="134"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0030_stX_MR-SP_01.png &lt;sup&gt;(MR; Sp.)&lt;/sup&gt;</v>
-      </c>
-    </row>
-    <row r="1048" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1048" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1048" s="27">
-        <v>410</v>
-      </c>
-      <c r="C1048" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1048" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G1048" t="s">
-        <v>1000</v>
-      </c>
-      <c r="I1048" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1048" t="s">
-        <v>1103</v>
-      </c>
-      <c r="K1048" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1048" t="str">
-        <f t="shared" si="134"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0040_stX_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1049" spans="1:12" x14ac:dyDescent="0.2">
@@ -33360,29 +33338,13 @@
         <v>60</v>
       </c>
       <c r="B1049" s="27">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C1049" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1049" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G1049" t="s">
-        <v>1001</v>
-      </c>
-      <c r="I1049" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1049" t="s">
-        <v>1155</v>
-      </c>
-      <c r="K1049" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1049" t="str">
-        <f t="shared" si="134"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0050_stX_D.18_01.png &lt;sup&gt;(D.18)&lt;/sup&gt;</v>
+        <v>39</v>
+      </c>
+      <c r="L1049" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="1050" spans="1:12" x14ac:dyDescent="0.2">
@@ -33390,29 +33352,20 @@
         <v>60</v>
       </c>
       <c r="B1050" s="27">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C1050" t="s">
         <v>105</v>
       </c>
       <c r="E1050" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G1050" t="s">
-        <v>1002</v>
-      </c>
-      <c r="I1050" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1050" t="s">
-        <v>1155</v>
-      </c>
-      <c r="K1050" t="s">
-        <v>1149</v>
+        <v>978</v>
       </c>
       <c r="L1050" t="str">
-        <f t="shared" si="134"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0060_stX_D.18_02.png &lt;sup&gt;(D.18)&lt;/sup&gt;</v>
+        <f>_xlfn.TEXTJOIN("", TRUE, D1050:J1050)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0400_Sokar/0001_skr_01.png</v>
       </c>
     </row>
     <row r="1051" spans="1:12" x14ac:dyDescent="0.2">
@@ -33420,29 +33373,23 @@
         <v>60</v>
       </c>
       <c r="B1051" s="27">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C1051" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E1051" t="s">
-        <v>1214</v>
+        <v>1213</v>
+      </c>
+      <c r="F1051" t="s">
+        <v>110</v>
       </c>
       <c r="G1051" t="s">
-        <v>1003</v>
-      </c>
-      <c r="I1051" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1051" t="s">
-        <v>1155</v>
-      </c>
-      <c r="K1051" t="s">
-        <v>1149</v>
+        <v>979</v>
       </c>
       <c r="L1051" t="str">
-        <f t="shared" si="134"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0070_stX_D.18_03.png &lt;sup&gt;(D.18)&lt;/sup&gt;</v>
+        <f>_xlfn.TEXTJOIN("", TRUE, D1051:J1051)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0400_Sokar/det/0001_skr_det_01.png</v>
       </c>
     </row>
     <row r="1052" spans="1:12" x14ac:dyDescent="0.2">
@@ -33450,29 +33397,13 @@
         <v>60</v>
       </c>
       <c r="B1052" s="27">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C1052" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1052" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G1052" t="s">
-        <v>1004</v>
-      </c>
-      <c r="I1052" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1052" t="s">
-        <v>1160</v>
-      </c>
-      <c r="K1052" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1052" t="str">
-        <f t="shared" si="134"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0080_stX_D.19_01.png &lt;sup&gt;(D.19)&lt;/sup&gt;</v>
+        <v>107</v>
+      </c>
+      <c r="L1052" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="1053" spans="1:12" x14ac:dyDescent="0.2">
@@ -33480,89 +33411,10 @@
         <v>60</v>
       </c>
       <c r="B1053" s="27">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C1053" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1053" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G1053" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I1053" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1053" t="s">
-        <v>1160</v>
-      </c>
-      <c r="K1053" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1053" t="str">
-        <f t="shared" si="134"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0090_stX_D.19_02.png &lt;sup&gt;(D.19)&lt;/sup&gt;</v>
-      </c>
-    </row>
-    <row r="1054" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1054" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1054" s="27">
-        <v>410</v>
-      </c>
-      <c r="C1054" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1054" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G1054" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I1054" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1054" t="s">
-        <v>1150</v>
-      </c>
-      <c r="K1054" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1054" t="str">
-        <f t="shared" si="134"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0100_stX_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
-      </c>
-    </row>
-    <row r="1055" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1055" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1055" s="27">
-        <v>410</v>
-      </c>
-      <c r="C1055" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1055" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G1055" t="s">
-        <v>995</v>
-      </c>
-      <c r="I1055" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1055" t="s">
-        <v>1150</v>
-      </c>
-      <c r="K1055" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1055" t="str">
-        <f t="shared" si="134"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0110_stX_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1056" spans="1:12" x14ac:dyDescent="0.2">
@@ -33573,20 +33425,10 @@
         <v>410</v>
       </c>
       <c r="C1056" t="s">
-        <v>106</v>
-      </c>
-      <c r="E1056" t="s">
-        <v>1214</v>
-      </c>
-      <c r="F1056" t="s">
-        <v>110</v>
-      </c>
-      <c r="G1056" t="s">
-        <v>1007</v>
-      </c>
-      <c r="L1056" t="str">
-        <f t="shared" si="133"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/det/0001_stX_det_01.png</v>
+        <v>39</v>
+      </c>
+      <c r="L1056" t="s">
+        <v>682</v>
       </c>
     </row>
     <row r="1057" spans="1:12" x14ac:dyDescent="0.2">
@@ -33597,20 +33439,17 @@
         <v>410</v>
       </c>
       <c r="C1057" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E1057" t="s">
         <v>1214</v>
       </c>
-      <c r="F1057" t="s">
-        <v>110</v>
-      </c>
       <c r="G1057" t="s">
-        <v>1008</v>
+        <v>996</v>
       </c>
       <c r="L1057" t="str">
-        <f t="shared" si="133"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/det/0010_stX_det_02.png</v>
+        <f t="shared" ref="L1057:L1070" si="136">_xlfn.TEXTJOIN("", TRUE, D1057:J1057)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0001_stX_01.png</v>
       </c>
     </row>
     <row r="1058" spans="1:12" x14ac:dyDescent="0.2">
@@ -33621,29 +33460,26 @@
         <v>410</v>
       </c>
       <c r="C1058" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E1058" t="s">
         <v>1214</v>
       </c>
-      <c r="F1058" t="s">
-        <v>110</v>
-      </c>
       <c r="G1058" t="s">
-        <v>1009</v>
+        <v>997</v>
       </c>
       <c r="I1058" t="s">
         <v>1147</v>
       </c>
       <c r="J1058" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="K1058" t="s">
         <v>1149</v>
       </c>
       <c r="L1058" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, D1058:K1058)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/det/0020_stX_det_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+        <f t="shared" ref="L1058:L1068" si="137">_xlfn.TEXTJOIN("", TRUE, D1058:K1058)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0010_stX_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1059" spans="1:12" x14ac:dyDescent="0.2">
@@ -33654,10 +33490,26 @@
         <v>410</v>
       </c>
       <c r="C1059" t="s">
-        <v>107</v>
-      </c>
-      <c r="L1059" t="s">
-        <v>165</v>
+        <v>105</v>
+      </c>
+      <c r="E1059" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G1059" t="s">
+        <v>998</v>
+      </c>
+      <c r="I1059" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1059" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K1059" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1059" t="str">
+        <f t="shared" si="137"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0020_stX_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1060" spans="1:12" x14ac:dyDescent="0.2">
@@ -33668,7 +33520,86 @@
         <v>410</v>
       </c>
       <c r="C1060" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="E1060" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G1060" t="s">
+        <v>999</v>
+      </c>
+      <c r="I1060" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1060" t="s">
+        <v>1165</v>
+      </c>
+      <c r="K1060" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1060" t="str">
+        <f t="shared" si="137"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0030_stX_MR-SP_01.png &lt;sup&gt;(MR; Sp.)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1061" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1061" s="27">
+        <v>410</v>
+      </c>
+      <c r="C1061" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1061" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G1061" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I1061" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1061" t="s">
+        <v>1103</v>
+      </c>
+      <c r="K1061" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1061" t="str">
+        <f t="shared" si="137"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0040_stX_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1062" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1062" s="27">
+        <v>410</v>
+      </c>
+      <c r="C1062" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1062" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G1062" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I1062" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1062" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K1062" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1062" t="str">
+        <f t="shared" si="137"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0050_stX_D.18_01.png &lt;sup&gt;(D.18)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1063" spans="1:12" x14ac:dyDescent="0.2">
@@ -33676,13 +33607,29 @@
         <v>60</v>
       </c>
       <c r="B1063" s="27">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C1063" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1063" t="s">
-        <v>683</v>
+        <v>105</v>
+      </c>
+      <c r="E1063" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G1063" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I1063" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1063" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K1063" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1063" t="str">
+        <f t="shared" si="137"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0060_stX_D.18_02.png &lt;sup&gt;(D.18)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1064" spans="1:12" x14ac:dyDescent="0.2">
@@ -33690,20 +33637,29 @@
         <v>60</v>
       </c>
       <c r="B1064" s="27">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C1064" t="s">
         <v>105</v>
       </c>
       <c r="E1064" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="G1064" t="s">
-        <v>1010</v>
+        <v>1003</v>
+      </c>
+      <c r="I1064" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1064" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K1064" t="s">
+        <v>1149</v>
       </c>
       <c r="L1064" t="str">
-        <f t="shared" ref="L1064:L1069" si="135">_xlfn.TEXTJOIN("", TRUE, D1064:J1064)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0001_Sw_01.png</v>
+        <f t="shared" si="137"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0070_stX_D.18_03.png &lt;sup&gt;(D.18)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1065" spans="1:12" x14ac:dyDescent="0.2">
@@ -33711,29 +33667,29 @@
         <v>60</v>
       </c>
       <c r="B1065" s="27">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C1065" t="s">
         <v>105</v>
       </c>
       <c r="E1065" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="G1065" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="I1065" t="s">
         <v>1147</v>
       </c>
       <c r="J1065" t="s">
-        <v>1148</v>
+        <v>1160</v>
       </c>
       <c r="K1065" t="s">
         <v>1149</v>
       </c>
       <c r="L1065" t="str">
-        <f t="shared" ref="L1065:L1068" si="136">_xlfn.TEXTJOIN("", TRUE, D1065:K1065)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0010_Sw_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <f t="shared" si="137"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0080_stX_D.19_01.png &lt;sup&gt;(D.19)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1066" spans="1:12" x14ac:dyDescent="0.2">
@@ -33741,29 +33697,29 @@
         <v>60</v>
       </c>
       <c r="B1066" s="27">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C1066" t="s">
         <v>105</v>
       </c>
       <c r="E1066" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="G1066" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="I1066" t="s">
         <v>1147</v>
       </c>
       <c r="J1066" t="s">
-        <v>1151</v>
+        <v>1160</v>
       </c>
       <c r="K1066" t="s">
         <v>1149</v>
       </c>
       <c r="L1066" t="str">
-        <f t="shared" si="136"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0020_Sw_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+        <f t="shared" si="137"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0090_stX_D.19_02.png &lt;sup&gt;(D.19)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1067" spans="1:12" x14ac:dyDescent="0.2">
@@ -33771,29 +33727,29 @@
         <v>60</v>
       </c>
       <c r="B1067" s="27">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C1067" t="s">
         <v>105</v>
       </c>
       <c r="E1067" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="G1067" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="I1067" t="s">
         <v>1147</v>
       </c>
       <c r="J1067" t="s">
-        <v>1103</v>
+        <v>1150</v>
       </c>
       <c r="K1067" t="s">
         <v>1149</v>
       </c>
       <c r="L1067" t="str">
-        <f t="shared" si="136"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0030_Sw_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
+        <f t="shared" si="137"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0100_stX_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1068" spans="1:12" x14ac:dyDescent="0.2">
@@ -33801,16 +33757,16 @@
         <v>60</v>
       </c>
       <c r="B1068" s="27">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C1068" t="s">
         <v>105</v>
       </c>
       <c r="E1068" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="G1068" t="s">
-        <v>1014</v>
+        <v>995</v>
       </c>
       <c r="I1068" t="s">
         <v>1147</v>
@@ -33822,8 +33778,8 @@
         <v>1149</v>
       </c>
       <c r="L1068" t="str">
-        <f t="shared" si="136"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0040_Sw_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+        <f t="shared" si="137"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/0110_stX_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1069" spans="1:12" x14ac:dyDescent="0.2">
@@ -33831,14 +33787,23 @@
         <v>60</v>
       </c>
       <c r="B1069" s="27">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C1069" t="s">
         <v>106</v>
       </c>
+      <c r="E1069" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F1069" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1069" t="s">
+        <v>1007</v>
+      </c>
       <c r="L1069" t="str">
-        <f t="shared" si="135"/>
-        <v/>
+        <f t="shared" si="136"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/det/0001_stX_det_01.png</v>
       </c>
     </row>
     <row r="1070" spans="1:12" x14ac:dyDescent="0.2">
@@ -33846,13 +33811,23 @@
         <v>60</v>
       </c>
       <c r="B1070" s="27">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C1070" t="s">
-        <v>107</v>
-      </c>
-      <c r="L1070" t="s">
-        <v>166</v>
+        <v>106</v>
+      </c>
+      <c r="E1070" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F1070" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1070" t="s">
+        <v>1008</v>
+      </c>
+      <c r="L1070" t="str">
+        <f t="shared" si="136"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/det/0010_stX_det_02.png</v>
       </c>
     </row>
     <row r="1071" spans="1:12" x14ac:dyDescent="0.2">
@@ -33860,45 +33835,57 @@
         <v>60</v>
       </c>
       <c r="B1071" s="27">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C1071" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1071" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F1071" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1071" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I1071" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1071" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K1071" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1071" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, D1071:K1071)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0410_Seth/det/0020_stX_det_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1072" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1072" s="27">
+        <v>410</v>
+      </c>
+      <c r="C1072" t="s">
+        <v>107</v>
+      </c>
+      <c r="L1072" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1073" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1073" s="27">
+        <v>410</v>
+      </c>
+      <c r="C1073" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="1074" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1074" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1074" s="27">
-        <v>430</v>
-      </c>
-      <c r="C1074" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1074" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="1075" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1075" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1075" s="27">
-        <v>430</v>
-      </c>
-      <c r="C1075" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1075" t="s">
-        <v>1216</v>
-      </c>
-      <c r="G1075" t="s">
-        <v>1016</v>
-      </c>
-      <c r="L1075" t="str">
-        <f t="shared" ref="L1075:L1077" si="137">_xlfn.TEXTJOIN("", TRUE, D1075:J1075)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0001_qbH-snw=f_01.png</v>
       </c>
     </row>
     <row r="1076" spans="1:12" x14ac:dyDescent="0.2">
@@ -33906,20 +33893,13 @@
         <v>60</v>
       </c>
       <c r="B1076" s="27">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C1076" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1076" t="s">
-        <v>1216</v>
-      </c>
-      <c r="G1076" t="s">
-        <v>1017</v>
-      </c>
-      <c r="L1076" t="str">
-        <f t="shared" si="137"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0010_qbH-snw=f_02.png</v>
+        <v>39</v>
+      </c>
+      <c r="L1076" t="s">
+        <v>683</v>
       </c>
     </row>
     <row r="1077" spans="1:12" x14ac:dyDescent="0.2">
@@ -33927,20 +33907,20 @@
         <v>60</v>
       </c>
       <c r="B1077" s="27">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C1077" t="s">
         <v>105</v>
       </c>
       <c r="E1077" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="G1077" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="L1077" t="str">
-        <f t="shared" si="137"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0020_qbH-snw=f_03.png</v>
+        <f t="shared" ref="L1077:L1082" si="138">_xlfn.TEXTJOIN("", TRUE, D1077:J1077)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0001_Sw_01.png</v>
       </c>
     </row>
     <row r="1078" spans="1:12" x14ac:dyDescent="0.2">
@@ -33948,29 +33928,29 @@
         <v>60</v>
       </c>
       <c r="B1078" s="27">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C1078" t="s">
         <v>105</v>
       </c>
       <c r="E1078" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="G1078" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
       <c r="I1078" t="s">
         <v>1147</v>
       </c>
       <c r="J1078" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="K1078" t="s">
         <v>1149</v>
       </c>
       <c r="L1078" t="str">
-        <f t="shared" ref="L1078:L1085" si="138">_xlfn.TEXTJOIN("", TRUE, D1078:K1078)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0030_qbH-snw=f_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+        <f t="shared" ref="L1078:L1081" si="139">_xlfn.TEXTJOIN("", TRUE, D1078:K1078)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0010_Sw_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1079" spans="1:12" x14ac:dyDescent="0.2">
@@ -33978,16 +33958,16 @@
         <v>60</v>
       </c>
       <c r="B1079" s="27">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C1079" t="s">
         <v>105</v>
       </c>
       <c r="E1079" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="G1079" t="s">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="I1079" t="s">
         <v>1147</v>
@@ -33999,8 +33979,8 @@
         <v>1149</v>
       </c>
       <c r="L1079" t="str">
-        <f t="shared" si="138"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0040_qbH-snw=f_MR_02.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+        <f t="shared" si="139"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0020_Sw_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1080" spans="1:12" x14ac:dyDescent="0.2">
@@ -34008,29 +33988,29 @@
         <v>60</v>
       </c>
       <c r="B1080" s="27">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C1080" t="s">
         <v>105</v>
       </c>
       <c r="E1080" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="G1080" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="I1080" t="s">
         <v>1147</v>
       </c>
       <c r="J1080" t="s">
-        <v>1150</v>
+        <v>1103</v>
       </c>
       <c r="K1080" t="s">
         <v>1149</v>
       </c>
       <c r="L1080" t="str">
-        <f t="shared" si="138"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0050_qbH-snw=f_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+        <f t="shared" si="139"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0030_Sw_NR_01.png &lt;sup&gt;(NR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1081" spans="1:12" x14ac:dyDescent="0.2">
@@ -34038,16 +34018,16 @@
         <v>60</v>
       </c>
       <c r="B1081" s="27">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C1081" t="s">
         <v>105</v>
       </c>
       <c r="E1081" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="G1081" t="s">
-        <v>1022</v>
+        <v>1014</v>
       </c>
       <c r="I1081" t="s">
         <v>1147</v>
@@ -34059,8 +34039,8 @@
         <v>1149</v>
       </c>
       <c r="L1081" t="str">
-        <f t="shared" si="138"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0060_qbH-snw=f_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+        <f t="shared" si="139"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0420_Schu/0040_Sw_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1082" spans="1:12" x14ac:dyDescent="0.2">
@@ -34068,29 +34048,14 @@
         <v>60</v>
       </c>
       <c r="B1082" s="27">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C1082" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1082" t="s">
-        <v>1216</v>
-      </c>
-      <c r="G1082" t="s">
-        <v>1023</v>
-      </c>
-      <c r="I1082" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1082" t="s">
-        <v>1150</v>
-      </c>
-      <c r="K1082" t="s">
-        <v>1149</v>
+        <v>106</v>
       </c>
       <c r="L1082" t="str">
         <f t="shared" si="138"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0070_qbH-snw=f_GR_03.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+        <v/>
       </c>
     </row>
     <row r="1083" spans="1:12" x14ac:dyDescent="0.2">
@@ -34098,29 +34063,13 @@
         <v>60</v>
       </c>
       <c r="B1083" s="27">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C1083" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1083" t="s">
-        <v>1216</v>
-      </c>
-      <c r="G1083" t="s">
-        <v>1015</v>
-      </c>
-      <c r="I1083" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1083" t="s">
-        <v>1150</v>
-      </c>
-      <c r="K1083" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1083" t="str">
-        <f t="shared" si="138"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0080_qbH-snw=f_GR_04.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+        <v>107</v>
+      </c>
+      <c r="L1083" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="1084" spans="1:12" x14ac:dyDescent="0.2">
@@ -34128,79 +34077,10 @@
         <v>60</v>
       </c>
       <c r="B1084" s="27">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C1084" t="s">
-        <v>106</v>
-      </c>
-      <c r="E1084" t="s">
-        <v>1216</v>
-      </c>
-      <c r="F1084" t="s">
-        <v>110</v>
-      </c>
-      <c r="G1084" t="s">
-        <v>1024</v>
-      </c>
-      <c r="I1084" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1084" t="s">
-        <v>1150</v>
-      </c>
-      <c r="K1084" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1084" t="str">
-        <f t="shared" si="138"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/det/0001_qbH-snw=f_det_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
-      </c>
-    </row>
-    <row r="1085" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1085" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1085" s="27">
-        <v>430</v>
-      </c>
-      <c r="C1085" t="s">
-        <v>106</v>
-      </c>
-      <c r="E1085" t="s">
-        <v>1216</v>
-      </c>
-      <c r="F1085" t="s">
-        <v>110</v>
-      </c>
-      <c r="G1085" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I1085" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1085" t="s">
-        <v>1150</v>
-      </c>
-      <c r="K1085" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1085" t="str">
-        <f t="shared" si="138"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/det/0010_qbH-snw=f_det_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
-      </c>
-    </row>
-    <row r="1086" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1086" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1086" s="27">
-        <v>430</v>
-      </c>
-      <c r="C1086" t="s">
-        <v>107</v>
-      </c>
-      <c r="L1086" t="s">
-        <v>167</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1087" spans="1:12" x14ac:dyDescent="0.2">
@@ -34211,7 +34091,52 @@
         <v>430</v>
       </c>
       <c r="C1087" t="s">
-        <v>108</v>
+        <v>39</v>
+      </c>
+      <c r="L1087" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1088" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1088" s="27">
+        <v>430</v>
+      </c>
+      <c r="C1088" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1088" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G1088" t="s">
+        <v>1016</v>
+      </c>
+      <c r="L1088" t="str">
+        <f t="shared" ref="L1088:L1090" si="140">_xlfn.TEXTJOIN("", TRUE, D1088:J1088)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0001_qbH-snw=f_01.png</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1089" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1089" s="27">
+        <v>430</v>
+      </c>
+      <c r="C1089" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1089" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G1089" t="s">
+        <v>1017</v>
+      </c>
+      <c r="L1089" t="str">
+        <f t="shared" si="140"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0010_qbH-snw=f_02.png</v>
       </c>
     </row>
     <row r="1090" spans="1:12" x14ac:dyDescent="0.2">
@@ -34219,13 +34144,20 @@
         <v>60</v>
       </c>
       <c r="B1090" s="27">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C1090" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1090" t="s">
-        <v>685</v>
+        <v>105</v>
+      </c>
+      <c r="E1090" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G1090" t="s">
+        <v>1018</v>
+      </c>
+      <c r="L1090" t="str">
+        <f t="shared" si="140"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0020_qbH-snw=f_03.png</v>
       </c>
     </row>
     <row r="1091" spans="1:12" x14ac:dyDescent="0.2">
@@ -34233,29 +34165,29 @@
         <v>60</v>
       </c>
       <c r="B1091" s="27">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C1091" t="s">
         <v>105</v>
       </c>
       <c r="E1091" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="G1091" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="I1091" t="s">
         <v>1147</v>
       </c>
       <c r="J1091" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="K1091" t="s">
         <v>1149</v>
       </c>
       <c r="L1091" t="str">
-        <f t="shared" ref="L1091:L1095" si="139">_xlfn.TEXTJOIN("", TRUE, D1091:K1091)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0440_Duamutef/0001_dwA-mw.t=f_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <f t="shared" ref="L1091:L1098" si="141">_xlfn.TEXTJOIN("", TRUE, D1091:K1091)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0030_qbH-snw=f_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1092" spans="1:12" x14ac:dyDescent="0.2">
@@ -34263,29 +34195,29 @@
         <v>60</v>
       </c>
       <c r="B1092" s="27">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C1092" t="s">
         <v>105</v>
       </c>
       <c r="E1092" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="G1092" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
       <c r="I1092" t="s">
         <v>1147</v>
       </c>
       <c r="J1092" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="K1092" t="s">
         <v>1149</v>
       </c>
       <c r="L1092" t="str">
-        <f t="shared" si="139"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0440_Duamutef/0010_dwA-mw.t=f_AR_02.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+        <f t="shared" si="141"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0040_qbH-snw=f_MR_02.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1093" spans="1:12" x14ac:dyDescent="0.2">
@@ -34293,29 +34225,29 @@
         <v>60</v>
       </c>
       <c r="B1093" s="27">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C1093" t="s">
         <v>105</v>
       </c>
       <c r="E1093" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="G1093" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="I1093" t="s">
         <v>1147</v>
       </c>
       <c r="J1093" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="K1093" t="s">
         <v>1149</v>
       </c>
       <c r="L1093" t="str">
-        <f t="shared" si="139"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0440_Duamutef/0020_dwA-mw.t=f_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+        <f t="shared" si="141"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0050_qbH-snw=f_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1094" spans="1:12" x14ac:dyDescent="0.2">
@@ -34323,29 +34255,29 @@
         <v>60</v>
       </c>
       <c r="B1094" s="27">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C1094" t="s">
         <v>105</v>
       </c>
       <c r="E1094" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="G1094" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="I1094" t="s">
         <v>1147</v>
       </c>
       <c r="J1094" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="K1094" t="s">
         <v>1149</v>
       </c>
       <c r="L1094" t="str">
-        <f t="shared" si="139"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0440_Duamutef/0030_dwA-mw.t=f_MR_02.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+        <f t="shared" si="141"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0060_qbH-snw=f_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1095" spans="1:12" x14ac:dyDescent="0.2">
@@ -34353,29 +34285,29 @@
         <v>60</v>
       </c>
       <c r="B1095" s="27">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C1095" t="s">
         <v>105</v>
       </c>
       <c r="E1095" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="G1095" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
       <c r="I1095" t="s">
         <v>1147</v>
       </c>
       <c r="J1095" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="K1095" t="s">
         <v>1149</v>
       </c>
       <c r="L1095" t="str">
-        <f t="shared" si="139"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0440_Duamutef/0040_dwA-mw.t=f_MR_03.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+        <f t="shared" si="141"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0070_qbH-snw=f_GR_03.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1096" spans="1:12" x14ac:dyDescent="0.2">
@@ -34383,14 +34315,29 @@
         <v>60</v>
       </c>
       <c r="B1096" s="27">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C1096" t="s">
-        <v>106</v>
+        <v>105</v>
+      </c>
+      <c r="E1096" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G1096" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I1096" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1096" t="s">
+        <v>1150</v>
+      </c>
+      <c r="K1096" t="s">
+        <v>1149</v>
       </c>
       <c r="L1096" t="str">
-        <f t="shared" ref="L1096" si="140">_xlfn.TEXTJOIN("", TRUE, D1096:J1096)</f>
-        <v/>
+        <f t="shared" si="141"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/0080_qbH-snw=f_GR_04.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1097" spans="1:12" x14ac:dyDescent="0.2">
@@ -34398,13 +34345,32 @@
         <v>60</v>
       </c>
       <c r="B1097" s="27">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C1097" t="s">
-        <v>107</v>
-      </c>
-      <c r="L1097" t="s">
-        <v>168</v>
+        <v>106</v>
+      </c>
+      <c r="E1097" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F1097" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1097" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I1097" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1097" t="s">
+        <v>1150</v>
+      </c>
+      <c r="K1097" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1097" t="str">
+        <f t="shared" si="141"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/det/0001_qbH-snw=f_det_GR_01.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1098" spans="1:12" x14ac:dyDescent="0.2">
@@ -34412,54 +34378,57 @@
         <v>60</v>
       </c>
       <c r="B1098" s="27">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C1098" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1098" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F1098" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1098" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I1098" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1098" t="s">
+        <v>1150</v>
+      </c>
+      <c r="K1098" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1098" t="str">
+        <f t="shared" si="141"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0430_Qebehsenuef/det/0010_qbH-snw=f_det_GR_02.png &lt;sup&gt;(Gr.)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1099" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1099" s="27">
+        <v>430</v>
+      </c>
+      <c r="C1099" t="s">
+        <v>107</v>
+      </c>
+      <c r="L1099" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1100" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1100" s="27">
+        <v>430</v>
+      </c>
+      <c r="C1100" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="1101" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1101" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1101" s="27">
-        <v>450</v>
-      </c>
-      <c r="C1101" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1101" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="1102" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1102" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1102" s="27">
-        <v>450</v>
-      </c>
-      <c r="C1102" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1102" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G1102" t="s">
-        <v>1031</v>
-      </c>
-      <c r="I1102" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1102" t="s">
-        <v>1148</v>
-      </c>
-      <c r="K1102" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1102" t="str">
-        <f t="shared" ref="L1102:L1112" si="141">_xlfn.TEXTJOIN("", TRUE, D1102:K1102)</f>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0001_DHwtj_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1103" spans="1:12" x14ac:dyDescent="0.2">
@@ -34467,29 +34436,13 @@
         <v>60</v>
       </c>
       <c r="B1103" s="27">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C1103" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1103" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G1103" t="s">
-        <v>1032</v>
-      </c>
-      <c r="I1103" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1103" t="s">
-        <v>1151</v>
-      </c>
-      <c r="K1103" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1103" t="str">
-        <f t="shared" si="141"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0010_DHwtj_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+        <v>39</v>
+      </c>
+      <c r="L1103" t="s">
+        <v>685</v>
       </c>
     </row>
     <row r="1104" spans="1:12" x14ac:dyDescent="0.2">
@@ -34497,29 +34450,29 @@
         <v>60</v>
       </c>
       <c r="B1104" s="27">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C1104" t="s">
         <v>105</v>
       </c>
       <c r="E1104" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G1104" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
       <c r="I1104" t="s">
         <v>1147</v>
       </c>
       <c r="J1104" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="K1104" t="s">
         <v>1149</v>
       </c>
       <c r="L1104" t="str">
-        <f t="shared" si="141"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0020_DHwtj_MR_02.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+        <f t="shared" ref="L1104:L1108" si="142">_xlfn.TEXTJOIN("", TRUE, D1104:K1104)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0440_Duamutef/0001_dwA-mw.t=f_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1105" spans="1:12" x14ac:dyDescent="0.2">
@@ -34527,29 +34480,29 @@
         <v>60</v>
       </c>
       <c r="B1105" s="27">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C1105" t="s">
         <v>105</v>
       </c>
       <c r="E1105" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G1105" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="I1105" t="s">
         <v>1147</v>
       </c>
       <c r="J1105" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="K1105" t="s">
         <v>1149</v>
       </c>
       <c r="L1105" t="str">
-        <f t="shared" si="141"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0030_DHwtj_MR_03.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+        <f t="shared" si="142"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0440_Duamutef/0010_dwA-mw.t=f_AR_02.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1106" spans="1:12" x14ac:dyDescent="0.2">
@@ -34557,16 +34510,16 @@
         <v>60</v>
       </c>
       <c r="B1106" s="27">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C1106" t="s">
         <v>105</v>
       </c>
       <c r="E1106" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G1106" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="I1106" t="s">
         <v>1147</v>
@@ -34578,8 +34531,8 @@
         <v>1149</v>
       </c>
       <c r="L1106" t="str">
-        <f t="shared" si="141"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0040_DHwtj_MR_04.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+        <f t="shared" si="142"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0440_Duamutef/0020_dwA-mw.t=f_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1107" spans="1:12" x14ac:dyDescent="0.2">
@@ -34587,16 +34540,16 @@
         <v>60</v>
       </c>
       <c r="B1107" s="27">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C1107" t="s">
         <v>105</v>
       </c>
       <c r="E1107" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G1107" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="I1107" t="s">
         <v>1147</v>
@@ -34608,8 +34561,8 @@
         <v>1149</v>
       </c>
       <c r="L1107" t="str">
-        <f t="shared" si="141"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0050_DHwtj_MR_05.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+        <f t="shared" si="142"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0440_Duamutef/0030_dwA-mw.t=f_MR_02.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1108" spans="1:12" x14ac:dyDescent="0.2">
@@ -34617,29 +34570,29 @@
         <v>60</v>
       </c>
       <c r="B1108" s="27">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C1108" t="s">
         <v>105</v>
       </c>
       <c r="E1108" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G1108" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="I1108" t="s">
         <v>1147</v>
       </c>
       <c r="J1108" t="s">
-        <v>1156</v>
+        <v>1151</v>
       </c>
       <c r="K1108" t="s">
         <v>1149</v>
       </c>
       <c r="L1108" t="str">
-        <f t="shared" si="141"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0060_DHwtj_SP_01.png &lt;sup&gt;(Sp.)&lt;/sup&gt;</v>
+        <f t="shared" si="142"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0440_Duamutef/0040_dwA-mw.t=f_MR_03.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
       </c>
     </row>
     <row r="1109" spans="1:12" x14ac:dyDescent="0.2">
@@ -34647,29 +34600,14 @@
         <v>60</v>
       </c>
       <c r="B1109" s="27">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C1109" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1109" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G1109" t="s">
-        <v>1038</v>
-      </c>
-      <c r="I1109" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1109" t="s">
-        <v>1156</v>
-      </c>
-      <c r="K1109" t="s">
-        <v>1149</v>
+        <v>106</v>
       </c>
       <c r="L1109" t="str">
-        <f t="shared" si="141"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0070_DHwtj_SP_02.png &lt;sup&gt;(Sp.)&lt;/sup&gt;</v>
+        <f t="shared" ref="L1109" si="143">_xlfn.TEXTJOIN("", TRUE, D1109:J1109)</f>
+        <v/>
       </c>
     </row>
     <row r="1110" spans="1:12" x14ac:dyDescent="0.2">
@@ -34677,29 +34615,13 @@
         <v>60</v>
       </c>
       <c r="B1110" s="27">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C1110" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1110" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G1110" t="s">
-        <v>1039</v>
-      </c>
-      <c r="I1110" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1110" t="s">
-        <v>1166</v>
-      </c>
-      <c r="K1110" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1110" t="str">
-        <f t="shared" si="141"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0080_DHwtj_SP-GR_01.png &lt;sup&gt;(Sp.; Gr.)&lt;/sup&gt;</v>
+        <v>107</v>
+      </c>
+      <c r="L1110" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="1111" spans="1:12" x14ac:dyDescent="0.2">
@@ -34707,76 +34629,10 @@
         <v>60</v>
       </c>
       <c r="B1111" s="27">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C1111" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1111" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G1111" t="s">
-        <v>1040</v>
-      </c>
-      <c r="I1111" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1111" t="s">
-        <v>1166</v>
-      </c>
-      <c r="K1111" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1111" t="str">
-        <f t="shared" si="141"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0090_DHwtj_SP-GR_02.png &lt;sup&gt;(Sp.; Gr.)&lt;/sup&gt;</v>
-      </c>
-    </row>
-    <row r="1112" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1112" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1112" s="27">
-        <v>450</v>
-      </c>
-      <c r="C1112" t="s">
-        <v>106</v>
-      </c>
-      <c r="E1112" t="s">
-        <v>1218</v>
-      </c>
-      <c r="F1112" t="s">
-        <v>110</v>
-      </c>
-      <c r="G1112" t="s">
-        <v>1041</v>
-      </c>
-      <c r="I1112" t="s">
-        <v>1147</v>
-      </c>
-      <c r="J1112" t="s">
-        <v>1156</v>
-      </c>
-      <c r="K1112" t="s">
-        <v>1149</v>
-      </c>
-      <c r="L1112" t="str">
-        <f t="shared" si="141"/>
-        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/det/0001_DHwtj_det_SP_01.png &lt;sup&gt;(Sp.)&lt;/sup&gt;</v>
-      </c>
-    </row>
-    <row r="1113" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1113" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1113" s="27">
-        <v>450</v>
-      </c>
-      <c r="C1113" t="s">
-        <v>107</v>
-      </c>
-      <c r="L1113" t="s">
-        <v>169</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1114" spans="1:12" x14ac:dyDescent="0.2">
@@ -34787,211 +34643,572 @@
         <v>450</v>
       </c>
       <c r="C1114" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1114" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1115" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1115" s="27">
+        <v>450</v>
+      </c>
+      <c r="C1115" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1115" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G1115" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I1115" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1115" t="s">
+        <v>1148</v>
+      </c>
+      <c r="K1115" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1115" t="str">
+        <f t="shared" ref="L1115:L1125" si="144">_xlfn.TEXTJOIN("", TRUE, D1115:K1115)</f>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0001_DHwtj_AR_01.png &lt;sup&gt;(AR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1116" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1116" s="27">
+        <v>450</v>
+      </c>
+      <c r="C1116" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1116" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G1116" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1116" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1116" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K1116" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1116" t="str">
+        <f t="shared" si="144"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0010_DHwtj_MR_01.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1117" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1117" s="27">
+        <v>450</v>
+      </c>
+      <c r="C1117" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1117" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G1117" t="s">
+        <v>1033</v>
+      </c>
+      <c r="I1117" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1117" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K1117" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1117" t="str">
+        <f t="shared" si="144"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0020_DHwtj_MR_02.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1118" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1118" s="27">
+        <v>450</v>
+      </c>
+      <c r="C1118" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1118" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G1118" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I1118" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1118" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K1118" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1118" t="str">
+        <f t="shared" si="144"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0030_DHwtj_MR_03.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1119" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1119" s="27">
+        <v>450</v>
+      </c>
+      <c r="C1119" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1119" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G1119" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I1119" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1119" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K1119" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1119" t="str">
+        <f t="shared" si="144"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0040_DHwtj_MR_04.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1120" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1120" s="27">
+        <v>450</v>
+      </c>
+      <c r="C1120" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1120" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G1120" t="s">
+        <v>1036</v>
+      </c>
+      <c r="I1120" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1120" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K1120" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1120" t="str">
+        <f t="shared" si="144"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0050_DHwtj_MR_05.png &lt;sup&gt;(MR)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1121" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1121" s="27">
+        <v>450</v>
+      </c>
+      <c r="C1121" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1121" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G1121" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I1121" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1121" t="s">
+        <v>1156</v>
+      </c>
+      <c r="K1121" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1121" t="str">
+        <f t="shared" si="144"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0060_DHwtj_SP_01.png &lt;sup&gt;(Sp.)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1122" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1122" s="27">
+        <v>450</v>
+      </c>
+      <c r="C1122" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1122" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G1122" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I1122" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1122" t="s">
+        <v>1156</v>
+      </c>
+      <c r="K1122" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1122" t="str">
+        <f t="shared" si="144"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0070_DHwtj_SP_02.png &lt;sup&gt;(Sp.)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1123" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1123" s="27">
+        <v>450</v>
+      </c>
+      <c r="C1123" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1123" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G1123" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I1123" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1123" t="s">
+        <v>1166</v>
+      </c>
+      <c r="K1123" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1123" t="str">
+        <f t="shared" si="144"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0080_DHwtj_SP-GR_01.png &lt;sup&gt;(Sp.; Gr.)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1124" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1124" s="27">
+        <v>450</v>
+      </c>
+      <c r="C1124" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1124" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G1124" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I1124" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1124" t="s">
+        <v>1166</v>
+      </c>
+      <c r="K1124" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1124" t="str">
+        <f t="shared" si="144"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/0090_DHwtj_SP-GR_02.png &lt;sup&gt;(Sp.; Gr.)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1125" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1125" s="27">
+        <v>450</v>
+      </c>
+      <c r="C1125" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1125" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F1125" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1125" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I1125" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J1125" t="s">
+        <v>1156</v>
+      </c>
+      <c r="K1125" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1125" t="str">
+        <f t="shared" si="144"/>
+        <v>02_Slots/Gottheit/Goetter-mit-Epitheta/0450_Thot/det/0001_DHwtj_det_SP_01.png &lt;sup&gt;(Sp.)&lt;/sup&gt;</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1126" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1126" s="27">
+        <v>450</v>
+      </c>
+      <c r="C1126" t="s">
+        <v>107</v>
+      </c>
+      <c r="L1126" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1127" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1127" s="27">
+        <v>450</v>
+      </c>
+      <c r="C1127" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="1120" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1120" s="4" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B1120" s="27">
-        <v>1</v>
-      </c>
-      <c r="C1120" t="s">
-        <v>1292</v>
-      </c>
-      <c r="L1120" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="1121" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1121" s="4" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B1121" s="27">
-        <v>1</v>
-      </c>
-      <c r="C1121" t="s">
-        <v>1235</v>
-      </c>
-      <c r="E1121" t="s">
-        <v>1289</v>
-      </c>
-      <c r="G1121" t="s">
-        <v>1288</v>
-      </c>
-      <c r="H1121" t="s">
-        <v>112</v>
-      </c>
-      <c r="L1121" t="str">
-        <f t="shared" ref="L1121" si="142">_xlfn.TEXTJOIN("", TRUE, D1121:K1121)</f>
-        <v>03_Hieroglyphen-selten/F63_xnty_01.png</v>
-      </c>
-    </row>
-    <row r="1122" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1122" s="4" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B1122" s="27">
-        <v>1</v>
-      </c>
-      <c r="C1122" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1122" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="1123" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1123" s="4" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B1123" s="27">
-        <v>1</v>
-      </c>
-      <c r="C1123" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1123" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="1128" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1128" s="4" t="s">
-        <v>1274</v>
-      </c>
-      <c r="B1128" s="27">
-        <v>1</v>
-      </c>
-      <c r="C1128" t="s">
-        <v>1292</v>
-      </c>
-      <c r="L1128" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="1129" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1129" s="4" t="s">
-        <v>1274</v>
-      </c>
-      <c r="B1129" s="27">
-        <v>1</v>
-      </c>
-      <c r="C1129" t="s">
-        <v>1235</v>
-      </c>
-      <c r="E1129" t="s">
-        <v>1289</v>
-      </c>
-      <c r="G1129" t="s">
-        <v>1295</v>
-      </c>
-      <c r="H1129" t="s">
-        <v>112</v>
-      </c>
-      <c r="L1129" t="str">
-        <f t="shared" ref="L1129" si="143">_xlfn.TEXTJOIN("", TRUE, D1129:K1129)</f>
-        <v>03_Hieroglyphen-selten/N6B_nsw-bjt_01.png</v>
-      </c>
-    </row>
-    <row r="1130" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1130" s="4" t="s">
-        <v>1274</v>
-      </c>
-      <c r="B1130" s="27">
-        <v>1</v>
-      </c>
-      <c r="C1130" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1130" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="1131" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1131" s="4" t="s">
-        <v>1274</v>
-      </c>
-      <c r="B1131" s="27">
-        <v>1</v>
-      </c>
-      <c r="C1131" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1131" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="1132" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1132" s="4" t="s">
-        <v>1274</v>
-      </c>
-      <c r="B1132" s="27">
-        <v>2</v>
-      </c>
-      <c r="C1132" t="s">
-        <v>1292</v>
-      </c>
-      <c r="L1132" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="1133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1133" s="4" t="s">
-        <v>1274</v>
+        <v>1236</v>
       </c>
       <c r="B1133" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1133" t="s">
-        <v>1235</v>
-      </c>
-      <c r="E1133" t="s">
-        <v>1289</v>
-      </c>
-      <c r="G1133" t="s">
-        <v>1297</v>
-      </c>
-      <c r="H1133" t="s">
-        <v>112</v>
-      </c>
-      <c r="L1133" t="str">
-        <f t="shared" ref="L1133" si="144">_xlfn.TEXTJOIN("", TRUE, D1133:K1133)</f>
-        <v>03_Hieroglyphen-selten/N102_jmn_01.png</v>
+        <v>1292</v>
+      </c>
+      <c r="L1133" t="s">
+        <v>1293</v>
       </c>
     </row>
     <row r="1134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1134" s="4" t="s">
-        <v>1274</v>
+        <v>1236</v>
       </c>
       <c r="B1134" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1134" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1134" t="s">
-        <v>175</v>
+        <v>1235</v>
+      </c>
+      <c r="E1134" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G1134" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H1134" t="s">
+        <v>112</v>
+      </c>
+      <c r="L1134" t="str">
+        <f t="shared" ref="L1134" si="145">_xlfn.TEXTJOIN("", TRUE, D1134:K1134)</f>
+        <v>03_Hieroglyphen-selten/F63_xnty_01.png</v>
       </c>
     </row>
     <row r="1135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1135" s="4" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B1135" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1135" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1135" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1136" s="4" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B1136" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1136" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1136" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1141" s="4" t="s">
         <v>1274</v>
       </c>
-      <c r="B1135" s="27">
+      <c r="B1141" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1141" t="s">
+        <v>1292</v>
+      </c>
+      <c r="L1141" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1142" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B1142" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1142" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E1142" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G1142" t="s">
+        <v>1295</v>
+      </c>
+      <c r="H1142" t="s">
+        <v>112</v>
+      </c>
+      <c r="L1142" t="str">
+        <f t="shared" ref="L1142" si="146">_xlfn.TEXTJOIN("", TRUE, D1142:K1142)</f>
+        <v>03_Hieroglyphen-selten/N6B_nsw-bjt_01.png</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1143" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B1143" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1143" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1143" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1144" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B1144" s="27">
+        <v>1</v>
+      </c>
+      <c r="C1144" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1144" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1145" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B1145" s="27">
         <v>2</v>
       </c>
-      <c r="C1135" t="s">
+      <c r="C1145" t="s">
+        <v>1292</v>
+      </c>
+      <c r="L1145" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1146" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B1146" s="27">
+        <v>2</v>
+      </c>
+      <c r="C1146" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E1146" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G1146" t="s">
+        <v>1297</v>
+      </c>
+      <c r="H1146" t="s">
+        <v>112</v>
+      </c>
+      <c r="L1146" t="str">
+        <f t="shared" ref="L1146" si="147">_xlfn.TEXTJOIN("", TRUE, D1146:K1146)</f>
+        <v>03_Hieroglyphen-selten/N102_jmn_01.png</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1147" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B1147" s="27">
+        <v>2</v>
+      </c>
+      <c r="C1147" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1147" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1148" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B1148" s="27">
+        <v>2</v>
+      </c>
+      <c r="C1148" t="s">
         <v>27</v>
       </c>
-      <c r="L1135" t="s">
+      <c r="L1148" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="L37 L994 L1004" formula="1"/>
+    <ignoredError sqref="L37 L1017 L971" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB71792-C53D-9142-BD77-EA14D47A75E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F1CB81C-762A-C34D-B819-5AB222486A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="4" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28920" windowHeight="19840" activeTab="4" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7303" uniqueCount="1588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7320" uniqueCount="1590">
   <si>
     <t>page_id</t>
   </si>
@@ -4829,6 +4829,12 @@
   </si>
   <si>
     <t>&lt;b&gt;[narrativer Text]&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Lobpreisungen für Gottheit&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="vertical-align:-75%"&gt;&amp;nbsp;&lt;/span&gt;&lt;br/&gt;</t>
   </si>
 </sst>
 </file>
@@ -8762,7 +8768,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C735804-F835-2748-99C4-5C04B7D215F0}">
-  <dimension ref="A1:N389"/>
+  <dimension ref="A1:N393"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
@@ -10701,23 +10707,10 @@
         <v>8</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F86" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G86" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="H86" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="I86" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="L86" s="12" t="str">
-        <f t="shared" ref="L86" si="16">_xlfn.TEXTJOIN("", TRUE, E86:K86)</f>
-        <v>01_Textgattung/03_Hymnus/04_jn/0001_jn_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>1589</v>
       </c>
       <c r="N86" s="12" t="s">
         <v>90</v>
@@ -10731,10 +10724,23 @@
         <v>9</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>369</v>
+        <v>47</v>
+      </c>
+      <c r="F87" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G87" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="H87" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="I87" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="L87" s="12" t="str">
+        <f t="shared" ref="L87" si="16">_xlfn.TEXTJOIN("", TRUE, E87:K87)</f>
+        <v>01_Textgattung/03_Hymnus/04_jn/0001_jn_01.png</v>
       </c>
       <c r="N87" s="12" t="s">
         <v>90</v>
@@ -10748,13 +10754,10 @@
         <v>10</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="M88" s="12" t="s">
-        <v>99</v>
+        <v>369</v>
       </c>
       <c r="N88" s="12" t="s">
         <v>90</v>
@@ -10768,23 +10771,13 @@
         <v>11</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F89" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G89" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="H89" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="I89" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="L89" s="12" t="str">
-        <f t="shared" ref="L89" si="17">_xlfn.TEXTJOIN("", TRUE, E89:K89)</f>
-        <v>01_Textgattung/03_Hymnus/05_Dd=f/0001_Dd=f_01.png</v>
+        <v>46</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M89" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="N89" s="12" t="s">
         <v>90</v>
@@ -10798,10 +10791,23 @@
         <v>12</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D90" s="12" t="s">
-        <v>372</v>
+        <v>47</v>
+      </c>
+      <c r="F90" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G90" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="H90" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="I90" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="L90" s="12" t="str">
+        <f t="shared" ref="L90" si="17">_xlfn.TEXTJOIN("", TRUE, E90:K90)</f>
+        <v>01_Textgattung/03_Hymnus/05_Dd=f/0001_Dd=f_01.png</v>
       </c>
       <c r="N90" s="12" t="s">
         <v>90</v>
@@ -10815,23 +10821,10 @@
         <v>13</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F91" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G91" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="H91" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="I91" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="L91" s="12" t="str">
-        <f t="shared" ref="L91" si="18">_xlfn.TEXTJOIN("", TRUE, E91:K91)</f>
-        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0001_jnD-Hr_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>372</v>
       </c>
       <c r="N91" s="12" t="s">
         <v>90</v>
@@ -10848,7 +10841,7 @@
         <v>45</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>533</v>
+        <v>1589</v>
       </c>
       <c r="N92" s="12" t="s">
         <v>90</v>
@@ -10862,125 +10855,111 @@
         <v>15</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>91</v>
+        <v>47</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G93" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="H93" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="I93" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="L93" s="12" t="str">
+        <f t="shared" ref="L93" si="18">_xlfn.TEXTJOIN("", TRUE, E93:K93)</f>
+        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0001_jnD-Hr_01.png</v>
       </c>
       <c r="N93" s="12" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="94" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="13"/>
+      <c r="A94" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="B94" s="12">
+        <v>16</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="N94" s="12" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="95" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="13" t="s">
-        <v>1066</v>
+        <v>358</v>
       </c>
       <c r="B95" s="12">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>360</v>
+        <v>48</v>
+      </c>
+      <c r="M95" s="12" t="s">
+        <v>97</v>
       </c>
       <c r="N95" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="96" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="13" t="s">
-        <v>1066</v>
+        <v>358</v>
       </c>
       <c r="B96" s="12">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F96" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G96" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="H96" s="12" t="s">
-        <v>1070</v>
-      </c>
-      <c r="L96" s="12" t="str">
-        <f t="shared" ref="L96:L147" si="19">_xlfn.TEXTJOIN("", TRUE, E96:K96)</f>
-        <v>01_Textgattung/03_Hymnus/01_dwA/0001_dwA_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>1588</v>
       </c>
       <c r="N96" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="97" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="13" t="s">
-        <v>1066</v>
+        <v>358</v>
       </c>
       <c r="B97" s="12">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F97" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G97" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="H97" s="12" t="s">
-        <v>1520</v>
-      </c>
-      <c r="L97" s="12" t="str">
-        <f t="shared" si="19"/>
-        <v>01_Textgattung/03_Hymnus/01_dwA/0010_dwA_AR_01.png</v>
+        <v>91</v>
       </c>
       <c r="N97" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="98" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="13" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B98" s="12">
-        <v>4</v>
-      </c>
-      <c r="C98" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>1130</v>
-      </c>
-      <c r="N98" s="12" t="s">
-        <v>92</v>
-      </c>
+      <c r="A98" s="13"/>
     </row>
     <row r="99" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A99" s="13" t="s">
         <v>1066</v>
       </c>
       <c r="B99" s="12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F99" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G99" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="H99" s="12" t="s">
-        <v>1521</v>
-      </c>
-      <c r="L99" s="12" t="str">
-        <f t="shared" ref="L99" si="20">_xlfn.TEXTJOIN("", TRUE, E99:K99)</f>
-        <v>01_Textgattung/03_Hymnus/01_dwA/0020_dwA_Pyr_01.png</v>
+        <v>17</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>360</v>
       </c>
       <c r="N99" s="12" t="s">
         <v>92</v>
@@ -10991,13 +10970,23 @@
         <v>1066</v>
       </c>
       <c r="B100" s="12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D100" s="12" t="s">
-        <v>1529</v>
+        <v>47</v>
+      </c>
+      <c r="F100" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G100" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="H100" s="12" t="s">
+        <v>1070</v>
+      </c>
+      <c r="L100" s="12" t="str">
+        <f t="shared" ref="L100:L151" si="19">_xlfn.TEXTJOIN("", TRUE, E100:K100)</f>
+        <v>01_Textgattung/03_Hymnus/01_dwA/0001_dwA_01.png</v>
       </c>
       <c r="N100" s="12" t="s">
         <v>92</v>
@@ -11008,7 +10997,7 @@
         <v>1066</v>
       </c>
       <c r="B101" s="12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C101" s="12" t="s">
         <v>47</v>
@@ -11020,11 +11009,11 @@
         <v>362</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="L101" s="12" t="str">
-        <f t="shared" ref="L101:L115" si="21">_xlfn.TEXTJOIN("", TRUE, E101:K101)</f>
-        <v>01_Textgattung/03_Hymnus/01_dwA/0030_dwA_seit-MR_01.png</v>
+        <f t="shared" si="19"/>
+        <v>01_Textgattung/03_Hymnus/01_dwA/0010_dwA_AR_01.png</v>
       </c>
       <c r="N101" s="12" t="s">
         <v>92</v>
@@ -11035,13 +11024,13 @@
         <v>1066</v>
       </c>
       <c r="B102" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C102" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="N102" s="12" t="s">
         <v>92</v>
@@ -11052,7 +11041,7 @@
         <v>1066</v>
       </c>
       <c r="B103" s="12">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C103" s="12" t="s">
         <v>47</v>
@@ -11064,11 +11053,11 @@
         <v>362</v>
       </c>
       <c r="H103" s="12" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="L103" s="12" t="str">
-        <f t="shared" si="21"/>
-        <v>01_Textgattung/03_Hymnus/01_dwA/0040_dwA_seit-MR_02.png</v>
+        <f t="shared" ref="L103" si="20">_xlfn.TEXTJOIN("", TRUE, E103:K103)</f>
+        <v>01_Textgattung/03_Hymnus/01_dwA/0020_dwA_Pyr_01.png</v>
       </c>
       <c r="N103" s="12" t="s">
         <v>92</v>
@@ -11079,13 +11068,13 @@
         <v>1066</v>
       </c>
       <c r="B104" s="12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C104" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>1128</v>
+        <v>1529</v>
       </c>
       <c r="N104" s="12" t="s">
         <v>92</v>
@@ -11096,7 +11085,7 @@
         <v>1066</v>
       </c>
       <c r="B105" s="12">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>47</v>
@@ -11108,11 +11097,11 @@
         <v>362</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="L105" s="12" t="str">
-        <f t="shared" si="21"/>
-        <v>01_Textgattung/03_Hymnus/01_dwA/0050_dwA_seit-MR_03.png</v>
+        <f t="shared" ref="L105:L119" si="21">_xlfn.TEXTJOIN("", TRUE, E105:K105)</f>
+        <v>01_Textgattung/03_Hymnus/01_dwA/0030_dwA_seit-MR_01.png</v>
       </c>
       <c r="N105" s="12" t="s">
         <v>92</v>
@@ -11123,7 +11112,7 @@
         <v>1066</v>
       </c>
       <c r="B106" s="12">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C106" s="12" t="s">
         <v>45</v>
@@ -11140,7 +11129,7 @@
         <v>1066</v>
       </c>
       <c r="B107" s="12">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C107" s="12" t="s">
         <v>47</v>
@@ -11152,11 +11141,11 @@
         <v>362</v>
       </c>
       <c r="H107" s="12" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="L107" s="12" t="str">
         <f t="shared" si="21"/>
-        <v>01_Textgattung/03_Hymnus/01_dwA/0060_dwA_seit-MR_04.png</v>
+        <v>01_Textgattung/03_Hymnus/01_dwA/0040_dwA_seit-MR_02.png</v>
       </c>
       <c r="N107" s="12" t="s">
         <v>92</v>
@@ -11167,7 +11156,7 @@
         <v>1066</v>
       </c>
       <c r="B108" s="12">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C108" s="12" t="s">
         <v>45</v>
@@ -11184,7 +11173,7 @@
         <v>1066</v>
       </c>
       <c r="B109" s="12">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C109" s="12" t="s">
         <v>47</v>
@@ -11196,11 +11185,11 @@
         <v>362</v>
       </c>
       <c r="H109" s="12" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="L109" s="12" t="str">
         <f t="shared" si="21"/>
-        <v>01_Textgattung/03_Hymnus/01_dwA/0070_dwA_Ende-NR_01.png</v>
+        <v>01_Textgattung/03_Hymnus/01_dwA/0050_dwA_seit-MR_03.png</v>
       </c>
       <c r="N109" s="12" t="s">
         <v>92</v>
@@ -11211,13 +11200,13 @@
         <v>1066</v>
       </c>
       <c r="B110" s="12">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C110" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="N110" s="12" t="s">
         <v>92</v>
@@ -11228,7 +11217,7 @@
         <v>1066</v>
       </c>
       <c r="B111" s="12">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C111" s="12" t="s">
         <v>47</v>
@@ -11240,11 +11229,11 @@
         <v>362</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="L111" s="12" t="str">
         <f t="shared" si="21"/>
-        <v>01_Textgattung/03_Hymnus/01_dwA/0080_dwA_Ende-NR_02.png</v>
+        <v>01_Textgattung/03_Hymnus/01_dwA/0060_dwA_seit-MR_04.png</v>
       </c>
       <c r="N111" s="12" t="s">
         <v>92</v>
@@ -11255,13 +11244,13 @@
         <v>1066</v>
       </c>
       <c r="B112" s="12">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C112" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="N112" s="12" t="s">
         <v>92</v>
@@ -11272,7 +11261,7 @@
         <v>1066</v>
       </c>
       <c r="B113" s="12">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C113" s="12" t="s">
         <v>47</v>
@@ -11284,11 +11273,11 @@
         <v>362</v>
       </c>
       <c r="H113" s="12" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="L113" s="12" t="str">
         <f t="shared" si="21"/>
-        <v>01_Textgattung/03_Hymnus/01_dwA/0090_dwA_Sp_01.png</v>
+        <v>01_Textgattung/03_Hymnus/01_dwA/0070_dwA_Ende-NR_01.png</v>
       </c>
       <c r="N113" s="12" t="s">
         <v>92</v>
@@ -11299,13 +11288,13 @@
         <v>1066</v>
       </c>
       <c r="B114" s="12">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C114" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>1394</v>
+        <v>1126</v>
       </c>
       <c r="N114" s="12" t="s">
         <v>92</v>
@@ -11316,7 +11305,7 @@
         <v>1066</v>
       </c>
       <c r="B115" s="12">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C115" s="12" t="s">
         <v>47</v>
@@ -11328,11 +11317,11 @@
         <v>362</v>
       </c>
       <c r="H115" s="12" t="s">
-        <v>1519</v>
+        <v>1527</v>
       </c>
       <c r="L115" s="12" t="str">
         <f t="shared" si="21"/>
-        <v>01_Textgattung/03_Hymnus/01_dwA/0100_dwA_Sp_02.png</v>
+        <v>01_Textgattung/03_Hymnus/01_dwA/0080_dwA_Ende-NR_02.png</v>
       </c>
       <c r="N115" s="12" t="s">
         <v>92</v>
@@ -11343,13 +11332,13 @@
         <v>1066</v>
       </c>
       <c r="B116" s="12">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C116" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>1394</v>
+        <v>1126</v>
       </c>
       <c r="N116" s="12" t="s">
         <v>92</v>
@@ -11360,16 +11349,26 @@
         <v>1066</v>
       </c>
       <c r="B117" s="12">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D117" s="12" t="s">
-        <v>365</v>
+        <v>47</v>
+      </c>
+      <c r="F117" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G117" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="H117" s="12" t="s">
+        <v>1528</v>
+      </c>
+      <c r="L117" s="12" t="str">
+        <f t="shared" si="21"/>
+        <v>01_Textgattung/03_Hymnus/01_dwA/0090_dwA_Sp_01.png</v>
       </c>
       <c r="N117" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="118" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -11377,26 +11376,16 @@
         <v>1066</v>
       </c>
       <c r="B118" s="12">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F118" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G118" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="H118" s="12" t="s">
-        <v>1069</v>
-      </c>
-      <c r="L118" s="12" t="str">
-        <f t="shared" ref="L118" si="22">_xlfn.TEXTJOIN("", TRUE, E118:K118)</f>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0001_rDj.t-jAw_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>1394</v>
       </c>
       <c r="N118" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="119" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -11404,7 +11393,7 @@
         <v>1066</v>
       </c>
       <c r="B119" s="12">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C119" s="12" t="s">
         <v>47</v>
@@ -11413,17 +11402,17 @@
         <v>447</v>
       </c>
       <c r="G119" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H119" s="12" t="s">
-        <v>1530</v>
+        <v>1519</v>
       </c>
       <c r="L119" s="12" t="str">
-        <f t="shared" si="19"/>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0010_rDj.t-jAw_02.png</v>
+        <f t="shared" si="21"/>
+        <v>01_Textgattung/03_Hymnus/01_dwA/0100_dwA_Sp_02.png</v>
       </c>
       <c r="N119" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="120" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -11431,26 +11420,16 @@
         <v>1066</v>
       </c>
       <c r="B120" s="12">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F120" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G120" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="H120" s="12" t="s">
-        <v>1531</v>
-      </c>
-      <c r="L120" s="12" t="str">
-        <f t="shared" si="19"/>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0020_rDj.t-jAw_NR_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>1394</v>
       </c>
       <c r="N120" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="121" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -11458,13 +11437,13 @@
         <v>1066</v>
       </c>
       <c r="B121" s="12">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>1129</v>
+        <v>365</v>
       </c>
       <c r="N121" s="12" t="s">
         <v>93</v>
@@ -11475,7 +11454,7 @@
         <v>1066</v>
       </c>
       <c r="B122" s="12">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C122" s="12" t="s">
         <v>47</v>
@@ -11487,11 +11466,11 @@
         <v>363</v>
       </c>
       <c r="H122" s="12" t="s">
-        <v>1532</v>
+        <v>1069</v>
       </c>
       <c r="L122" s="12" t="str">
-        <f t="shared" ref="L122" si="23">_xlfn.TEXTJOIN("", TRUE, E122:K122)</f>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0030_rDj.t-jAw_NR_02.png</v>
+        <f t="shared" ref="L122" si="22">_xlfn.TEXTJOIN("", TRUE, E122:K122)</f>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0001_rDj.t-jAw_01.png</v>
       </c>
       <c r="N122" s="12" t="s">
         <v>93</v>
@@ -11502,13 +11481,23 @@
         <v>1066</v>
       </c>
       <c r="B123" s="12">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D123" s="12" t="s">
-        <v>1129</v>
+        <v>47</v>
+      </c>
+      <c r="F123" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G123" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="H123" s="12" t="s">
+        <v>1530</v>
+      </c>
+      <c r="L123" s="12" t="str">
+        <f t="shared" si="19"/>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0010_rDj.t-jAw_02.png</v>
       </c>
       <c r="N123" s="12" t="s">
         <v>93</v>
@@ -11519,7 +11508,7 @@
         <v>1066</v>
       </c>
       <c r="B124" s="12">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C124" s="12" t="s">
         <v>47</v>
@@ -11531,11 +11520,11 @@
         <v>363</v>
       </c>
       <c r="H124" s="12" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="L124" s="12" t="str">
-        <f t="shared" ref="L124" si="24">_xlfn.TEXTJOIN("", TRUE, E124:K124)</f>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0040_rDj.t-jAw_NR_03.png</v>
+        <f t="shared" si="19"/>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0020_rDj.t-jAw_NR_01.png</v>
       </c>
       <c r="N124" s="12" t="s">
         <v>93</v>
@@ -11546,7 +11535,7 @@
         <v>1066</v>
       </c>
       <c r="B125" s="12">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C125" s="12" t="s">
         <v>45</v>
@@ -11563,7 +11552,7 @@
         <v>1066</v>
       </c>
       <c r="B126" s="12">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C126" s="12" t="s">
         <v>47</v>
@@ -11575,11 +11564,11 @@
         <v>363</v>
       </c>
       <c r="H126" s="12" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="L126" s="12" t="str">
-        <f t="shared" ref="L126" si="25">_xlfn.TEXTJOIN("", TRUE, E126:K126)</f>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0050_rDj.t-jAw_NR_04.png</v>
+        <f t="shared" ref="L126" si="23">_xlfn.TEXTJOIN("", TRUE, E126:K126)</f>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0030_rDj.t-jAw_NR_02.png</v>
       </c>
       <c r="N126" s="12" t="s">
         <v>93</v>
@@ -11590,7 +11579,7 @@
         <v>1066</v>
       </c>
       <c r="B127" s="12">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C127" s="12" t="s">
         <v>45</v>
@@ -11607,7 +11596,7 @@
         <v>1066</v>
       </c>
       <c r="B128" s="12">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C128" s="12" t="s">
         <v>47</v>
@@ -11619,11 +11608,11 @@
         <v>363</v>
       </c>
       <c r="H128" s="12" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="L128" s="12" t="str">
-        <f t="shared" ref="L128:L144" si="26">_xlfn.TEXTJOIN("", TRUE, E128:K128)</f>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0060_rDj.t-jAw_NR_05.png</v>
+        <f t="shared" ref="L128" si="24">_xlfn.TEXTJOIN("", TRUE, E128:K128)</f>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0040_rDj.t-jAw_NR_03.png</v>
       </c>
       <c r="N128" s="12" t="s">
         <v>93</v>
@@ -11634,7 +11623,7 @@
         <v>1066</v>
       </c>
       <c r="B129" s="12">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C129" s="12" t="s">
         <v>45</v>
@@ -11651,16 +11640,26 @@
         <v>1066</v>
       </c>
       <c r="B130" s="12">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D130" s="12" t="s">
-        <v>1546</v>
+        <v>47</v>
+      </c>
+      <c r="F130" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G130" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="H130" s="12" t="s">
+        <v>1534</v>
+      </c>
+      <c r="L130" s="12" t="str">
+        <f t="shared" ref="L130" si="25">_xlfn.TEXTJOIN("", TRUE, E130:K130)</f>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0050_rDj.t-jAw_NR_04.png</v>
       </c>
       <c r="N130" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="131" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -11668,26 +11667,16 @@
         <v>1066</v>
       </c>
       <c r="B131" s="12">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F131" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G131" s="12" t="s">
-        <v>1544</v>
-      </c>
-      <c r="H131" s="12" t="s">
-        <v>1536</v>
-      </c>
-      <c r="L131" s="12" t="str">
-        <f t="shared" si="26"/>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0001_jAw_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D131" s="12" t="s">
+        <v>1129</v>
       </c>
       <c r="N131" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="132" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -11695,7 +11684,7 @@
         <v>1066</v>
       </c>
       <c r="B132" s="12">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C132" s="12" t="s">
         <v>47</v>
@@ -11704,17 +11693,17 @@
         <v>447</v>
       </c>
       <c r="G132" s="12" t="s">
-        <v>1544</v>
+        <v>363</v>
       </c>
       <c r="H132" s="12" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="L132" s="12" t="str">
-        <f t="shared" si="26"/>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0010_jAw_AR_01.png</v>
+        <f t="shared" ref="L132:L148" si="26">_xlfn.TEXTJOIN("", TRUE, E132:K132)</f>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/0060_rDj.t-jAw_NR_05.png</v>
       </c>
       <c r="N132" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="133" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -11722,16 +11711,16 @@
         <v>1066</v>
       </c>
       <c r="B133" s="12">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C133" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="N133" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="134" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -11739,23 +11728,13 @@
         <v>1066</v>
       </c>
       <c r="B134" s="12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F134" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G134" s="12" t="s">
-        <v>1544</v>
-      </c>
-      <c r="H134" s="12" t="s">
-        <v>1538</v>
-      </c>
-      <c r="L134" s="12" t="str">
-        <f t="shared" si="26"/>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0020_jAw_AR_02.png</v>
+        <v>17</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>1546</v>
       </c>
       <c r="N134" s="12" t="s">
         <v>95</v>
@@ -11766,13 +11745,23 @@
         <v>1066</v>
       </c>
       <c r="B135" s="12">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D135" s="12" t="s">
-        <v>1130</v>
+        <v>47</v>
+      </c>
+      <c r="F135" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G135" s="12" t="s">
+        <v>1544</v>
+      </c>
+      <c r="H135" s="12" t="s">
+        <v>1536</v>
+      </c>
+      <c r="L135" s="12" t="str">
+        <f t="shared" si="26"/>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0001_jAw_01.png</v>
       </c>
       <c r="N135" s="12" t="s">
         <v>95</v>
@@ -11783,7 +11772,7 @@
         <v>1066</v>
       </c>
       <c r="B136" s="12">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C136" s="12" t="s">
         <v>47</v>
@@ -11795,11 +11784,11 @@
         <v>1544</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="L136" s="12" t="str">
         <f t="shared" si="26"/>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0030_jAw_NR_01.png</v>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0010_jAw_AR_01.png</v>
       </c>
       <c r="N136" s="12" t="s">
         <v>95</v>
@@ -11810,13 +11799,13 @@
         <v>1066</v>
       </c>
       <c r="B137" s="12">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C137" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="N137" s="12" t="s">
         <v>95</v>
@@ -11827,7 +11816,7 @@
         <v>1066</v>
       </c>
       <c r="B138" s="12">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C138" s="12" t="s">
         <v>47</v>
@@ -11839,11 +11828,11 @@
         <v>1544</v>
       </c>
       <c r="H138" s="12" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="L138" s="12" t="str">
         <f t="shared" si="26"/>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0040_jAw_D.18_01.png</v>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0020_jAw_AR_02.png</v>
       </c>
       <c r="N138" s="12" t="s">
         <v>95</v>
@@ -11854,13 +11843,13 @@
         <v>1066</v>
       </c>
       <c r="B139" s="12">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C139" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D139" s="12" t="s">
-        <v>1413</v>
+        <v>1130</v>
       </c>
       <c r="N139" s="12" t="s">
         <v>95</v>
@@ -11871,7 +11860,7 @@
         <v>1066</v>
       </c>
       <c r="B140" s="12">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C140" s="12" t="s">
         <v>47</v>
@@ -11883,11 +11872,11 @@
         <v>1544</v>
       </c>
       <c r="H140" s="12" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="L140" s="12" t="str">
         <f t="shared" si="26"/>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0050_jAw_Gr_01.png</v>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0030_jAw_NR_01.png</v>
       </c>
       <c r="N140" s="12" t="s">
         <v>95</v>
@@ -11898,13 +11887,13 @@
         <v>1066</v>
       </c>
       <c r="B141" s="12">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C141" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="N141" s="12" t="s">
         <v>95</v>
@@ -11915,7 +11904,7 @@
         <v>1066</v>
       </c>
       <c r="B142" s="12">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C142" s="12" t="s">
         <v>47</v>
@@ -11927,11 +11916,11 @@
         <v>1544</v>
       </c>
       <c r="H142" s="12" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="L142" s="12" t="str">
         <f t="shared" si="26"/>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0060_jAw_Gr_02.png</v>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0040_jAw_D.18_01.png</v>
       </c>
       <c r="N142" s="12" t="s">
         <v>95</v>
@@ -11942,13 +11931,13 @@
         <v>1066</v>
       </c>
       <c r="B143" s="12">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C143" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D143" s="12" t="s">
-        <v>1131</v>
+        <v>1413</v>
       </c>
       <c r="N143" s="12" t="s">
         <v>95</v>
@@ -11959,7 +11948,7 @@
         <v>1066</v>
       </c>
       <c r="B144" s="12">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C144" s="12" t="s">
         <v>47</v>
@@ -11971,11 +11960,11 @@
         <v>1544</v>
       </c>
       <c r="H144" s="12" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="L144" s="12" t="str">
         <f t="shared" si="26"/>
-        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0070_jAw_Abk_01.png</v>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0050_jAw_Gr_01.png</v>
       </c>
       <c r="N144" s="12" t="s">
         <v>95</v>
@@ -11986,13 +11975,13 @@
         <v>1066</v>
       </c>
       <c r="B145" s="12">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C145" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D145" s="12" t="s">
-        <v>1545</v>
+        <v>1131</v>
       </c>
       <c r="N145" s="12" t="s">
         <v>95</v>
@@ -12003,16 +11992,26 @@
         <v>1066</v>
       </c>
       <c r="B146" s="12">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D146" s="12" t="s">
-        <v>1547</v>
+        <v>47</v>
+      </c>
+      <c r="F146" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G146" s="12" t="s">
+        <v>1544</v>
+      </c>
+      <c r="H146" s="12" t="s">
+        <v>1542</v>
+      </c>
+      <c r="L146" s="12" t="str">
+        <f t="shared" si="26"/>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0060_jAw_Gr_02.png</v>
       </c>
       <c r="N146" s="12" t="s">
-        <v>1395</v>
+        <v>95</v>
       </c>
     </row>
     <row r="147" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -12020,26 +12019,16 @@
         <v>1066</v>
       </c>
       <c r="B147" s="12">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F147" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G147" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="H147" s="12" t="s">
-        <v>1548</v>
-      </c>
-      <c r="L147" s="12" t="str">
-        <f t="shared" si="19"/>
-        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0010_sn-tA_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D147" s="12" t="s">
+        <v>1131</v>
       </c>
       <c r="N147" s="12" t="s">
-        <v>1395</v>
+        <v>95</v>
       </c>
     </row>
     <row r="148" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -12047,7 +12036,7 @@
         <v>1066</v>
       </c>
       <c r="B148" s="12">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C148" s="12" t="s">
         <v>47</v>
@@ -12056,17 +12045,17 @@
         <v>447</v>
       </c>
       <c r="G148" s="12" t="s">
-        <v>366</v>
+        <v>1544</v>
       </c>
       <c r="H148" s="12" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="L148" s="12" t="str">
-        <f t="shared" ref="L148" si="27">_xlfn.TEXTJOIN("", TRUE, E148:K148)</f>
-        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0020_sn-tA_NR_01.png</v>
+        <f t="shared" si="26"/>
+        <v>01_Textgattung/03_Hymnus/02_rDj.t-jAw/02_jAw/0070_jAw_Abk_01.png</v>
       </c>
       <c r="N148" s="12" t="s">
-        <v>1395</v>
+        <v>95</v>
       </c>
     </row>
     <row r="149" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -12074,16 +12063,16 @@
         <v>1066</v>
       </c>
       <c r="B149" s="12">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C149" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>1129</v>
+        <v>1545</v>
       </c>
       <c r="N149" s="12" t="s">
-        <v>1395</v>
+        <v>95</v>
       </c>
     </row>
     <row r="150" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -12091,23 +12080,13 @@
         <v>1066</v>
       </c>
       <c r="B150" s="12">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F150" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G150" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="H150" s="12" t="s">
-        <v>1550</v>
-      </c>
-      <c r="L150" s="12" t="str">
-        <f t="shared" ref="L150" si="28">_xlfn.TEXTJOIN("", TRUE, E150:K150)</f>
-        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0030_sn-tA_NR_02.png</v>
+        <v>17</v>
+      </c>
+      <c r="D150" s="12" t="s">
+        <v>1547</v>
       </c>
       <c r="N150" s="12" t="s">
         <v>1395</v>
@@ -12118,13 +12097,23 @@
         <v>1066</v>
       </c>
       <c r="B151" s="12">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D151" s="12" t="s">
-        <v>1129</v>
+        <v>47</v>
+      </c>
+      <c r="F151" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G151" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="H151" s="12" t="s">
+        <v>1548</v>
+      </c>
+      <c r="L151" s="12" t="str">
+        <f t="shared" si="19"/>
+        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0010_sn-tA_01.png</v>
       </c>
       <c r="N151" s="12" t="s">
         <v>1395</v>
@@ -12135,7 +12124,7 @@
         <v>1066</v>
       </c>
       <c r="B152" s="12">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C152" s="12" t="s">
         <v>47</v>
@@ -12147,11 +12136,11 @@
         <v>366</v>
       </c>
       <c r="H152" s="12" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="L152" s="12" t="str">
-        <f t="shared" ref="L152" si="29">_xlfn.TEXTJOIN("", TRUE, E152:K152)</f>
-        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0040_sn-tA_NR_03.png</v>
+        <f t="shared" ref="L152" si="27">_xlfn.TEXTJOIN("", TRUE, E152:K152)</f>
+        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0020_sn-tA_NR_01.png</v>
       </c>
       <c r="N152" s="12" t="s">
         <v>1395</v>
@@ -12162,7 +12151,7 @@
         <v>1066</v>
       </c>
       <c r="B153" s="12">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C153" s="12" t="s">
         <v>45</v>
@@ -12179,7 +12168,7 @@
         <v>1066</v>
       </c>
       <c r="B154" s="12">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C154" s="12" t="s">
         <v>47</v>
@@ -12191,11 +12180,11 @@
         <v>366</v>
       </c>
       <c r="H154" s="12" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="L154" s="12" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, E154:K154)</f>
-        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0050_sn-tA_D.18_01.png</v>
+        <f t="shared" ref="L154" si="28">_xlfn.TEXTJOIN("", TRUE, E154:K154)</f>
+        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0030_sn-tA_NR_02.png</v>
       </c>
       <c r="N154" s="12" t="s">
         <v>1395</v>
@@ -12206,13 +12195,13 @@
         <v>1066</v>
       </c>
       <c r="B155" s="12">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C155" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D155" s="12" t="s">
-        <v>1413</v>
+        <v>1129</v>
       </c>
       <c r="N155" s="12" t="s">
         <v>1395</v>
@@ -12223,7 +12212,7 @@
         <v>1066</v>
       </c>
       <c r="B156" s="12">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C156" s="12" t="s">
         <v>47</v>
@@ -12235,11 +12224,11 @@
         <v>366</v>
       </c>
       <c r="H156" s="12" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="L156" s="12" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, E156:K156)</f>
-        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0060_sn-tA_Abk-MR-NR_01.png</v>
+        <f t="shared" ref="L156" si="29">_xlfn.TEXTJOIN("", TRUE, E156:K156)</f>
+        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0040_sn-tA_NR_03.png</v>
       </c>
       <c r="N156" s="12" t="s">
         <v>1395</v>
@@ -12250,13 +12239,13 @@
         <v>1066</v>
       </c>
       <c r="B157" s="12">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C157" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D157" s="12" t="s">
-        <v>1555</v>
+        <v>1129</v>
       </c>
       <c r="N157" s="12" t="s">
         <v>1395</v>
@@ -12267,7 +12256,7 @@
         <v>1066</v>
       </c>
       <c r="B158" s="12">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C158" s="12" t="s">
         <v>47</v>
@@ -12279,11 +12268,11 @@
         <v>366</v>
       </c>
       <c r="H158" s="12" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="L158" s="12" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, E158:K158)</f>
-        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0070_sn-tA_Abk-Gr_01.png</v>
+        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0050_sn-tA_D.18_01.png</v>
       </c>
       <c r="N158" s="12" t="s">
         <v>1395</v>
@@ -12294,13 +12283,13 @@
         <v>1066</v>
       </c>
       <c r="B159" s="12">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C159" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D159" s="12" t="s">
-        <v>1556</v>
+        <v>1413</v>
       </c>
       <c r="N159" s="12" t="s">
         <v>1395</v>
@@ -12311,128 +12300,118 @@
         <v>1066</v>
       </c>
       <c r="B160" s="12">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>91</v>
+        <v>47</v>
+      </c>
+      <c r="F160" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G160" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="H160" s="12" t="s">
+        <v>1553</v>
+      </c>
+      <c r="L160" s="12" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, E160:K160)</f>
+        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0060_sn-tA_Abk-MR-NR_01.png</v>
       </c>
       <c r="N160" s="12" t="s">
         <v>1395</v>
       </c>
     </row>
     <row r="161" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="13"/>
+      <c r="A161" s="13" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B161" s="12">
+        <v>63</v>
+      </c>
+      <c r="C161" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D161" s="12" t="s">
+        <v>1555</v>
+      </c>
+      <c r="N161" s="12" t="s">
+        <v>1395</v>
+      </c>
     </row>
     <row r="162" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A162" s="13" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B162" s="12">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D162" s="12" t="s">
-        <v>369</v>
+        <v>47</v>
+      </c>
+      <c r="F162" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G162" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="H162" s="12" t="s">
+        <v>1554</v>
+      </c>
+      <c r="L162" s="12" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, E162:K162)</f>
+        <v>01_Textgattung/03_Hymnus/03_sn-tA-n/0070_sn-tA_Abk-Gr_01.png</v>
       </c>
       <c r="N162" s="12" t="s">
-        <v>92</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="163" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A163" s="13" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B163" s="12">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="C163" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F163" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G163" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="H163" s="12" t="s">
-        <v>1071</v>
-      </c>
-      <c r="L163" s="12" t="str">
-        <f t="shared" ref="L163:L164" si="30">_xlfn.TEXTJOIN("", TRUE, E163:K163)</f>
-        <v>01_Textgattung/03_Hymnus/04_jn/0001_jn_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D163" s="12" t="s">
+        <v>1556</v>
       </c>
       <c r="N163" s="12" t="s">
-        <v>92</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="164" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A164" s="13" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B164" s="12">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="C164" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F164" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G164" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="H164" s="12" t="s">
-        <v>1506</v>
-      </c>
-      <c r="L164" s="12" t="str">
-        <f t="shared" si="30"/>
-        <v>01_Textgattung/03_Hymnus/04_jn/0010_jn_01.png</v>
+        <v>91</v>
       </c>
       <c r="N164" s="12" t="s">
-        <v>92</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="165" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="13" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B165" s="12">
-        <v>4</v>
-      </c>
-      <c r="C165" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F165" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G165" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="H165" s="12" t="s">
-        <v>1507</v>
-      </c>
-      <c r="L165" s="12" t="str">
-        <f t="shared" ref="L165:L169" si="31">_xlfn.TEXTJOIN("", TRUE, E165:K165)</f>
-        <v>01_Textgattung/03_Hymnus/04_jn/0020_jn_AR_01.png</v>
-      </c>
-      <c r="N165" s="12" t="s">
-        <v>92</v>
-      </c>
+      <c r="A165" s="13"/>
     </row>
     <row r="166" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A166" s="13" t="s">
         <v>1068</v>
       </c>
       <c r="B166" s="12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C166" s="12" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>1130</v>
+        <v>369</v>
       </c>
       <c r="N166" s="12" t="s">
         <v>92</v>
@@ -12443,7 +12422,7 @@
         <v>1068</v>
       </c>
       <c r="B167" s="12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C167" s="12" t="s">
         <v>47</v>
@@ -12455,11 +12434,11 @@
         <v>370</v>
       </c>
       <c r="H167" s="12" t="s">
-        <v>1508</v>
+        <v>1071</v>
       </c>
       <c r="L167" s="12" t="str">
-        <f t="shared" ref="L167" si="32">_xlfn.TEXTJOIN("", TRUE, E167:K167)</f>
-        <v>01_Textgattung/03_Hymnus/04_jn/0030_jn_AR_02.png</v>
+        <f t="shared" ref="L167:L168" si="30">_xlfn.TEXTJOIN("", TRUE, E167:K167)</f>
+        <v>01_Textgattung/03_Hymnus/04_jn/0001_jn_01.png</v>
       </c>
       <c r="N167" s="12" t="s">
         <v>92</v>
@@ -12470,13 +12449,23 @@
         <v>1068</v>
       </c>
       <c r="B168" s="12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C168" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D168" s="12" t="s">
-        <v>1130</v>
+        <v>47</v>
+      </c>
+      <c r="F168" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G168" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="H168" s="12" t="s">
+        <v>1506</v>
+      </c>
+      <c r="L168" s="12" t="str">
+        <f t="shared" si="30"/>
+        <v>01_Textgattung/03_Hymnus/04_jn/0010_jn_01.png</v>
       </c>
       <c r="N168" s="12" t="s">
         <v>92</v>
@@ -12487,7 +12476,7 @@
         <v>1068</v>
       </c>
       <c r="B169" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C169" s="12" t="s">
         <v>47</v>
@@ -12499,11 +12488,11 @@
         <v>370</v>
       </c>
       <c r="H169" s="12" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="L169" s="12" t="str">
-        <f t="shared" si="31"/>
-        <v>01_Textgattung/03_Hymnus/04_jn/0040_jn_NR_01.png</v>
+        <f t="shared" ref="L169:L173" si="31">_xlfn.TEXTJOIN("", TRUE, E169:K169)</f>
+        <v>01_Textgattung/03_Hymnus/04_jn/0020_jn_AR_01.png</v>
       </c>
       <c r="N169" s="12" t="s">
         <v>92</v>
@@ -12514,13 +12503,13 @@
         <v>1068</v>
       </c>
       <c r="B170" s="12">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C170" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D170" s="12" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="N170" s="12" t="s">
         <v>92</v>
@@ -12531,16 +12520,26 @@
         <v>1068</v>
       </c>
       <c r="B171" s="12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C171" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D171" s="40" t="s">
-        <v>1498</v>
+        <v>47</v>
+      </c>
+      <c r="F171" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G171" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="H171" s="12" t="s">
+        <v>1508</v>
+      </c>
+      <c r="L171" s="12" t="str">
+        <f t="shared" ref="L171" si="32">_xlfn.TEXTJOIN("", TRUE, E171:K171)</f>
+        <v>01_Textgattung/03_Hymnus/04_jn/0030_jn_AR_02.png</v>
       </c>
       <c r="N171" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="172" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -12548,26 +12547,16 @@
         <v>1068</v>
       </c>
       <c r="B172" s="12">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C172" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F172" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G172" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="H172" s="12" t="s">
-        <v>1499</v>
-      </c>
-      <c r="L172" s="12" t="str">
-        <f t="shared" ref="L172:L175" si="33">_xlfn.TEXTJOIN("", TRUE, E172:K172)</f>
-        <v>01_Textgattung/03_Hymnus/05_Dd=f/0010_Dd_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D172" s="12" t="s">
+        <v>1130</v>
       </c>
       <c r="N172" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="173" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -12575,7 +12564,7 @@
         <v>1068</v>
       </c>
       <c r="B173" s="12">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C173" s="12" t="s">
         <v>47</v>
@@ -12584,17 +12573,17 @@
         <v>447</v>
       </c>
       <c r="G173" s="12" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H173" s="12" t="s">
-        <v>1500</v>
+        <v>1505</v>
       </c>
       <c r="L173" s="12" t="str">
-        <f t="shared" si="33"/>
-        <v>01_Textgattung/03_Hymnus/05_Dd=f/0020_Dd_seitMR_01.png</v>
+        <f t="shared" si="31"/>
+        <v>01_Textgattung/03_Hymnus/04_jn/0040_jn_NR_01.png</v>
       </c>
       <c r="N173" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="174" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -12602,16 +12591,16 @@
         <v>1068</v>
       </c>
       <c r="B174" s="12">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C174" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D174" s="12" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="N174" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="175" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -12619,23 +12608,13 @@
         <v>1068</v>
       </c>
       <c r="B175" s="12">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C175" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F175" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G175" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="H175" s="12" t="s">
-        <v>1501</v>
-      </c>
-      <c r="L175" s="12" t="str">
-        <f t="shared" si="33"/>
-        <v>01_Textgattung/03_Hymnus/05_Dd=f/0030_Dd_Sp_Gr_01.png</v>
+        <v>17</v>
+      </c>
+      <c r="D175" s="40" t="s">
+        <v>1498</v>
       </c>
       <c r="N175" s="12" t="s">
         <v>93</v>
@@ -12646,13 +12625,23 @@
         <v>1068</v>
       </c>
       <c r="B176" s="12">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D176" s="12" t="s">
-        <v>1504</v>
+        <v>47</v>
+      </c>
+      <c r="F176" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G176" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="H176" s="12" t="s">
+        <v>1499</v>
+      </c>
+      <c r="L176" s="12" t="str">
+        <f t="shared" ref="L176:L179" si="33">_xlfn.TEXTJOIN("", TRUE, E176:K176)</f>
+        <v>01_Textgattung/03_Hymnus/05_Dd=f/0010_Dd_01.png</v>
       </c>
       <c r="N176" s="12" t="s">
         <v>93</v>
@@ -12663,7 +12652,7 @@
         <v>1068</v>
       </c>
       <c r="B177" s="12">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C177" s="12" t="s">
         <v>47</v>
@@ -12675,11 +12664,11 @@
         <v>373</v>
       </c>
       <c r="H177" s="12" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="L177" s="12" t="str">
-        <f t="shared" ref="L177" si="34">_xlfn.TEXTJOIN("", TRUE, E177:K177)</f>
-        <v>01_Textgattung/03_Hymnus/05_Dd=f/0040_Dd_Gr_01.png</v>
+        <f t="shared" si="33"/>
+        <v>01_Textgattung/03_Hymnus/05_Dd=f/0020_Dd_seitMR_01.png</v>
       </c>
       <c r="N177" s="12" t="s">
         <v>93</v>
@@ -12690,13 +12679,13 @@
         <v>1068</v>
       </c>
       <c r="B178" s="12">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D178" s="12" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="N178" s="12" t="s">
         <v>93</v>
@@ -12707,7 +12696,7 @@
         <v>1068</v>
       </c>
       <c r="B179" s="12">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C179" s="12" t="s">
         <v>47</v>
@@ -12719,11 +12708,11 @@
         <v>373</v>
       </c>
       <c r="H179" s="12" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="L179" s="12" t="str">
-        <f t="shared" ref="L179" si="35">_xlfn.TEXTJOIN("", TRUE, E179:K179)</f>
-        <v>01_Textgattung/03_Hymnus/05_Dd=f/0050_Dd_Gr_02.png</v>
+        <f t="shared" si="33"/>
+        <v>01_Textgattung/03_Hymnus/05_Dd=f/0030_Dd_Sp_Gr_01.png</v>
       </c>
       <c r="N179" s="12" t="s">
         <v>93</v>
@@ -12734,13 +12723,13 @@
         <v>1068</v>
       </c>
       <c r="B180" s="12">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C180" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D180" s="12" t="s">
-        <v>1131</v>
+        <v>1504</v>
       </c>
       <c r="N180" s="12" t="s">
         <v>93</v>
@@ -12751,138 +12740,118 @@
         <v>1068</v>
       </c>
       <c r="B181" s="12">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C181" s="12" t="s">
-        <v>91</v>
+        <v>47</v>
+      </c>
+      <c r="F181" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G181" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="H181" s="12" t="s">
+        <v>1502</v>
+      </c>
+      <c r="L181" s="12" t="str">
+        <f t="shared" ref="L181" si="34">_xlfn.TEXTJOIN("", TRUE, E181:K181)</f>
+        <v>01_Textgattung/03_Hymnus/05_Dd=f/0040_Dd_Gr_01.png</v>
       </c>
       <c r="N181" s="12" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="182" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="13"/>
+      <c r="A182" s="13" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B182" s="12">
+        <v>17</v>
+      </c>
+      <c r="C182" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D182" s="12" t="s">
+        <v>1131</v>
+      </c>
+      <c r="N182" s="12" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="183" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A183" s="13" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B183" s="12">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D183" s="12" t="s">
-        <v>1072</v>
+        <v>47</v>
+      </c>
+      <c r="F183" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G183" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="H183" s="12" t="s">
+        <v>1503</v>
+      </c>
+      <c r="L183" s="12" t="str">
+        <f t="shared" ref="L183" si="35">_xlfn.TEXTJOIN("", TRUE, E183:K183)</f>
+        <v>01_Textgattung/03_Hymnus/05_Dd=f/0050_Dd_Gr_02.png</v>
       </c>
       <c r="N183" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="184" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A184" s="13" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B184" s="12">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F184" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G184" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="H184" s="12" t="s">
-        <v>1509</v>
-      </c>
-      <c r="L184" s="12" t="str">
-        <f t="shared" ref="L184" si="36">_xlfn.TEXTJOIN("", TRUE, E184:K184)</f>
-        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0001_jnD-Hr_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D184" s="12" t="s">
+        <v>1131</v>
       </c>
       <c r="N184" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="185" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A185" s="13" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B185" s="12">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C185" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F185" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G185" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="H185" s="12" t="s">
-        <v>1510</v>
-      </c>
-      <c r="L185" s="12" t="str">
-        <f t="shared" ref="L185:L199" si="37">_xlfn.TEXTJOIN("", TRUE, E185:K185)</f>
-        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0010_jnD-Hr_01.png</v>
+        <v>91</v>
       </c>
       <c r="N185" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="186" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="13" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B186" s="12">
-        <v>4</v>
-      </c>
-      <c r="C186" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F186" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G186" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="H186" s="12" t="s">
-        <v>1511</v>
-      </c>
-      <c r="L186" s="12" t="str">
-        <f t="shared" si="37"/>
-        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0020_jnD-Hr_02.png</v>
-      </c>
-      <c r="N186" s="12" t="s">
-        <v>92</v>
-      </c>
+      <c r="A186" s="13"/>
     </row>
     <row r="187" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A187" s="13" t="s">
         <v>1067</v>
       </c>
       <c r="B187" s="12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C187" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F187" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="G187" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="H187" s="12" t="s">
-        <v>1512</v>
-      </c>
-      <c r="L187" s="12" t="str">
-        <f t="shared" si="37"/>
-        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0030_jnD-Hr_AR_01.png</v>
+        <v>17</v>
+      </c>
+      <c r="D187" s="12" t="s">
+        <v>1072</v>
       </c>
       <c r="N187" s="12" t="s">
         <v>92</v>
@@ -12893,13 +12862,23 @@
         <v>1067</v>
       </c>
       <c r="B188" s="12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C188" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D188" s="12" t="s">
-        <v>1130</v>
+        <v>47</v>
+      </c>
+      <c r="F188" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G188" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="H188" s="12" t="s">
+        <v>1509</v>
+      </c>
+      <c r="L188" s="12" t="str">
+        <f t="shared" ref="L188" si="36">_xlfn.TEXTJOIN("", TRUE, E188:K188)</f>
+        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0001_jnD-Hr_01.png</v>
       </c>
       <c r="N188" s="12" t="s">
         <v>92</v>
@@ -12910,7 +12889,7 @@
         <v>1067</v>
       </c>
       <c r="B189" s="12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C189" s="12" t="s">
         <v>47</v>
@@ -12922,11 +12901,11 @@
         <v>375</v>
       </c>
       <c r="H189" s="12" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="L189" s="12" t="str">
-        <f t="shared" si="37"/>
-        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0040_jnD-Hr_AR_MR_01.png</v>
+        <f t="shared" ref="L189:L203" si="37">_xlfn.TEXTJOIN("", TRUE, E189:K189)</f>
+        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0010_jnD-Hr_01.png</v>
       </c>
       <c r="N189" s="12" t="s">
         <v>92</v>
@@ -12937,13 +12916,23 @@
         <v>1067</v>
       </c>
       <c r="B190" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D190" s="12" t="s">
-        <v>1125</v>
+        <v>47</v>
+      </c>
+      <c r="F190" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G190" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="H190" s="12" t="s">
+        <v>1511</v>
+      </c>
+      <c r="L190" s="12" t="str">
+        <f t="shared" si="37"/>
+        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0020_jnD-Hr_02.png</v>
       </c>
       <c r="N190" s="12" t="s">
         <v>92</v>
@@ -12954,7 +12943,7 @@
         <v>1067</v>
       </c>
       <c r="B191" s="12">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C191" s="12" t="s">
         <v>47</v>
@@ -12966,11 +12955,11 @@
         <v>375</v>
       </c>
       <c r="H191" s="12" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="L191" s="12" t="str">
         <f t="shared" si="37"/>
-        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0050_jnD-Hr_AR_MR_02.png</v>
+        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0030_jnD-Hr_AR_01.png</v>
       </c>
       <c r="N191" s="12" t="s">
         <v>92</v>
@@ -12981,13 +12970,13 @@
         <v>1067</v>
       </c>
       <c r="B192" s="12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C192" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D192" s="12" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="N192" s="12" t="s">
         <v>92</v>
@@ -12998,7 +12987,7 @@
         <v>1067</v>
       </c>
       <c r="B193" s="12">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C193" s="12" t="s">
         <v>47</v>
@@ -13010,11 +12999,11 @@
         <v>375</v>
       </c>
       <c r="H193" s="12" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="L193" s="12" t="str">
         <f t="shared" si="37"/>
-        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0060_jnD-Hr_NR_01.png</v>
+        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0040_jnD-Hr_AR_MR_01.png</v>
       </c>
       <c r="N193" s="12" t="s">
         <v>92</v>
@@ -13025,13 +13014,13 @@
         <v>1067</v>
       </c>
       <c r="B194" s="12">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C194" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D194" s="12" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="N194" s="12" t="s">
         <v>92</v>
@@ -13042,7 +13031,7 @@
         <v>1067</v>
       </c>
       <c r="B195" s="12">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C195" s="12" t="s">
         <v>47</v>
@@ -13054,11 +13043,11 @@
         <v>375</v>
       </c>
       <c r="H195" s="12" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="L195" s="12" t="str">
         <f t="shared" si="37"/>
-        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0070_jnD-Hr_D18_01.png</v>
+        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0050_jnD-Hr_AR_MR_02.png</v>
       </c>
       <c r="N195" s="12" t="s">
         <v>92</v>
@@ -13069,13 +13058,13 @@
         <v>1067</v>
       </c>
       <c r="B196" s="12">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C196" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D196" s="12" t="s">
-        <v>1413</v>
+        <v>1125</v>
       </c>
       <c r="N196" s="12" t="s">
         <v>92</v>
@@ -13086,7 +13075,7 @@
         <v>1067</v>
       </c>
       <c r="B197" s="12">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C197" s="12" t="s">
         <v>47</v>
@@ -13098,11 +13087,11 @@
         <v>375</v>
       </c>
       <c r="H197" s="12" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="L197" s="12" t="str">
         <f t="shared" si="37"/>
-        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0080_jnD-Hr_Gr_01.png</v>
+        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0060_jnD-Hr_NR_01.png</v>
       </c>
       <c r="N197" s="12" t="s">
         <v>92</v>
@@ -13113,13 +13102,13 @@
         <v>1067</v>
       </c>
       <c r="B198" s="12">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C198" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D198" s="12" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="N198" s="12" t="s">
         <v>92</v>
@@ -13130,7 +13119,7 @@
         <v>1067</v>
       </c>
       <c r="B199" s="12">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C199" s="12" t="s">
         <v>47</v>
@@ -13142,11 +13131,11 @@
         <v>375</v>
       </c>
       <c r="H199" s="12" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="L199" s="12" t="str">
         <f t="shared" si="37"/>
-        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0090_jnD-Hr_Gr_02.png</v>
+        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0070_jnD-Hr_D18_01.png</v>
       </c>
       <c r="N199" s="12" t="s">
         <v>92</v>
@@ -13157,13 +13146,13 @@
         <v>1067</v>
       </c>
       <c r="B200" s="12">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C200" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D200" s="12" t="s">
-        <v>1131</v>
+        <v>1413</v>
       </c>
       <c r="N200" s="12" t="s">
         <v>92</v>
@@ -13174,100 +13163,101 @@
         <v>1067</v>
       </c>
       <c r="B201" s="12">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>91</v>
+        <v>47</v>
+      </c>
+      <c r="F201" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G201" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="H201" s="12" t="s">
+        <v>1517</v>
+      </c>
+      <c r="L201" s="12" t="str">
+        <f t="shared" si="37"/>
+        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0080_jnD-Hr_Gr_01.png</v>
       </c>
       <c r="N201" s="12" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="209" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="17" t="s">
-        <v>445</v>
-      </c>
-      <c r="B209" s="16">
-        <v>1</v>
-      </c>
-      <c r="C209" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D209" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="M209" s="16" t="s">
-        <v>325</v>
-      </c>
-      <c r="N209" s="16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="210" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="17" t="s">
-        <v>445</v>
-      </c>
-      <c r="B210" s="16">
-        <v>2</v>
-      </c>
-      <c r="C210" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D210" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="M210" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="N210" s="16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="211" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="17" t="s">
-        <v>445</v>
-      </c>
-      <c r="B211" s="16">
-        <v>3</v>
-      </c>
-      <c r="C211" s="16" t="s">
+    <row r="202" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A202" s="13" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B202" s="12">
+        <v>16</v>
+      </c>
+      <c r="C202" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D202" s="12" t="s">
+        <v>1131</v>
+      </c>
+      <c r="N202" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="13" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B203" s="12">
+        <v>17</v>
+      </c>
+      <c r="C203" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F211" s="16" t="s">
-        <v>456</v>
-      </c>
-      <c r="G211" s="16" t="s">
-        <v>449</v>
-      </c>
-      <c r="H211" s="16" t="s">
-        <v>448</v>
-      </c>
-      <c r="I211" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="L211" s="16" t="str">
-        <f t="shared" ref="L211" si="38">_xlfn.TEXTJOIN("", TRUE, E211:K211)</f>
-        <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0001_mry_01.png</v>
-      </c>
-      <c r="N211" s="16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="212" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="17" t="s">
-        <v>445</v>
-      </c>
-      <c r="B212" s="16">
-        <v>4</v>
-      </c>
-      <c r="C212" s="16" t="s">
+      <c r="F203" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G203" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="H203" s="12" t="s">
+        <v>1518</v>
+      </c>
+      <c r="L203" s="12" t="str">
+        <f t="shared" si="37"/>
+        <v>01_Textgattung/03_Hymnus/06_jnD-Hr/0090_jnD-Hr_Gr_02.png</v>
+      </c>
+      <c r="N203" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A204" s="13" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B204" s="12">
+        <v>18</v>
+      </c>
+      <c r="C204" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D212" s="16" t="s">
-        <v>446</v>
-      </c>
-      <c r="N212" s="16" t="s">
-        <v>90</v>
+      <c r="D204" s="12" t="s">
+        <v>1131</v>
+      </c>
+      <c r="N204" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="13" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B205" s="12">
+        <v>19</v>
+      </c>
+      <c r="C205" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="N205" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="213" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -13275,10 +13265,16 @@
         <v>445</v>
       </c>
       <c r="B213" s="16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C213" s="16" t="s">
-        <v>91</v>
+        <v>46</v>
+      </c>
+      <c r="D213" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="M213" s="16" t="s">
+        <v>325</v>
       </c>
       <c r="N213" s="16" t="s">
         <v>90</v>
@@ -13286,27 +13282,30 @@
     </row>
     <row r="214" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A214" s="17" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B214" s="16">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C214" s="16" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D214" s="16" t="s">
-        <v>446</v>
+        <v>48</v>
+      </c>
+      <c r="M214" s="16" t="s">
+        <v>97</v>
       </c>
       <c r="N214" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="215" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A215" s="17" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B215" s="16">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C215" s="16" t="s">
         <v>47</v>
@@ -13324,71 +13323,42 @@
         <v>112</v>
       </c>
       <c r="L215" s="16" t="str">
-        <f t="shared" ref="L215" si="39">_xlfn.TEXTJOIN("", TRUE, E215:K215)</f>
+        <f t="shared" ref="L215" si="38">_xlfn.TEXTJOIN("", TRUE, E215:K215)</f>
         <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0001_mry_01.png</v>
       </c>
       <c r="N215" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="216" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A216" s="17" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B216" s="16">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C216" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F216" s="16" t="s">
-        <v>456</v>
-      </c>
-      <c r="G216" s="16" t="s">
-        <v>449</v>
-      </c>
-      <c r="H216" s="16" t="s">
-        <v>451</v>
-      </c>
-      <c r="I216" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="L216" s="16" t="str">
-        <f t="shared" ref="L216:L219" si="40">_xlfn.TEXTJOIN("", TRUE, E216:K216)</f>
-        <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0010_mry_02.png</v>
+        <v>45</v>
+      </c>
+      <c r="D216" s="16" t="s">
+        <v>446</v>
       </c>
       <c r="N216" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="217" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A217" s="17" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B217" s="16">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C217" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F217" s="16" t="s">
-        <v>456</v>
-      </c>
-      <c r="G217" s="16" t="s">
-        <v>449</v>
-      </c>
-      <c r="H217" s="16" t="s">
-        <v>452</v>
-      </c>
-      <c r="I217" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="L217" s="16" t="str">
-        <f t="shared" si="40"/>
-        <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0020_mry_03.png</v>
+        <v>91</v>
       </c>
       <c r="N217" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="218" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -13396,26 +13366,13 @@
         <v>450</v>
       </c>
       <c r="B218" s="16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C218" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F218" s="16" t="s">
-        <v>456</v>
-      </c>
-      <c r="G218" s="16" t="s">
-        <v>449</v>
-      </c>
-      <c r="H218" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="I218" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="L218" s="16" t="str">
-        <f t="shared" si="40"/>
-        <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0030_mry_04.png</v>
+        <v>17</v>
+      </c>
+      <c r="D218" s="16" t="s">
+        <v>446</v>
       </c>
       <c r="N218" s="16" t="s">
         <v>92</v>
@@ -13426,7 +13383,7 @@
         <v>450</v>
       </c>
       <c r="B219" s="16">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C219" s="16" t="s">
         <v>47</v>
@@ -13438,14 +13395,14 @@
         <v>449</v>
       </c>
       <c r="H219" s="16" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="I219" s="16" t="s">
         <v>112</v>
       </c>
       <c r="L219" s="16" t="str">
-        <f t="shared" si="40"/>
-        <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0040_mry_05.png</v>
+        <f t="shared" ref="L219" si="39">_xlfn.TEXTJOIN("", TRUE, E219:K219)</f>
+        <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0001_mry_01.png</v>
       </c>
       <c r="N219" s="16" t="s">
         <v>92</v>
@@ -13456,7 +13413,7 @@
         <v>450</v>
       </c>
       <c r="B220" s="16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C220" s="16" t="s">
         <v>47</v>
@@ -13468,14 +13425,14 @@
         <v>449</v>
       </c>
       <c r="H220" s="16" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="I220" s="16" t="s">
         <v>112</v>
       </c>
       <c r="L220" s="16" t="str">
-        <f t="shared" ref="L220" si="41">_xlfn.TEXTJOIN("", TRUE, E220:K220)</f>
-        <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0050_mry_AR_02.png</v>
+        <f t="shared" ref="L220:L223" si="40">_xlfn.TEXTJOIN("", TRUE, E220:K220)</f>
+        <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0010_mry_02.png</v>
       </c>
       <c r="N220" s="16" t="s">
         <v>92</v>
@@ -13486,103 +13443,136 @@
         <v>450</v>
       </c>
       <c r="B221" s="16">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C221" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D221" s="16" t="s">
-        <v>1130</v>
+        <v>47</v>
+      </c>
+      <c r="F221" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="G221" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="H221" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="I221" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="L221" s="16" t="str">
+        <f t="shared" si="40"/>
+        <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0020_mry_03.png</v>
       </c>
       <c r="N221" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="223" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A223" s="18" t="s">
-        <v>458</v>
-      </c>
-      <c r="B223" s="18">
-        <v>1</v>
-      </c>
-      <c r="C223" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D223" s="18" t="s">
-        <v>476</v>
-      </c>
-      <c r="M223" s="18" t="s">
-        <v>461</v>
-      </c>
-      <c r="N223" s="18" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="224" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A224" s="18" t="s">
-        <v>458</v>
-      </c>
-      <c r="B224" s="18">
-        <v>2</v>
-      </c>
-      <c r="C224" s="18" t="s">
+    <row r="222" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="B222" s="16">
+        <v>10</v>
+      </c>
+      <c r="C222" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F224" s="18" t="s">
-        <v>464</v>
-      </c>
-      <c r="G224" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="H224" s="18" t="s">
-        <v>467</v>
-      </c>
-      <c r="I224" s="18" t="s">
+      <c r="F222" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="G222" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="H222" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="I222" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="L224" s="18" t="str">
-        <f t="shared" ref="L224" si="42">_xlfn.TEXTJOIN("", TRUE, E224:K224)</f>
-        <v>01_Textgattung/05_Historische-Koenigsinschrift/01_xr-Hm-n/0001_xr Hm n_01.png</v>
-      </c>
-      <c r="N224" s="18" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="225" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A225" s="18" t="s">
-        <v>458</v>
-      </c>
-      <c r="B225" s="18">
-        <v>3</v>
-      </c>
-      <c r="C225" s="18" t="s">
+      <c r="L222" s="16" t="str">
+        <f t="shared" si="40"/>
+        <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0030_mry_04.png</v>
+      </c>
+      <c r="N222" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A223" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="B223" s="16">
+        <v>11</v>
+      </c>
+      <c r="C223" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F223" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="G223" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="H223" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="I223" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="L223" s="16" t="str">
+        <f t="shared" si="40"/>
+        <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0040_mry_05.png</v>
+      </c>
+      <c r="N223" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="B224" s="16">
+        <v>12</v>
+      </c>
+      <c r="C224" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F224" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="G224" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="H224" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="I224" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="L224" s="16" t="str">
+        <f t="shared" ref="L224" si="41">_xlfn.TEXTJOIN("", TRUE, E224:K224)</f>
+        <v>01_Textgattung/04_Koenig-geliebt-von-Gottheit-Formel/01_mry/0050_mry_AR_02.png</v>
+      </c>
+      <c r="N224" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="B225" s="16">
+        <v>13</v>
+      </c>
+      <c r="C225" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D225" s="18" t="s">
-        <v>466</v>
-      </c>
-      <c r="N225" s="18" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="226" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A226" s="18" t="s">
-        <v>458</v>
-      </c>
-      <c r="B226" s="18">
-        <v>4</v>
-      </c>
-      <c r="C226" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D226" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="M226" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="N226" s="18" t="s">
-        <v>90</v>
+      <c r="D225" s="16" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N225" s="16" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="227" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
@@ -13590,13 +13580,16 @@
         <v>458</v>
       </c>
       <c r="B227" s="18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C227" s="18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D227" s="18" t="s">
-        <v>1587</v>
+        <v>476</v>
+      </c>
+      <c r="M227" s="18" t="s">
+        <v>461</v>
       </c>
       <c r="N227" s="18" t="s">
         <v>90</v>
@@ -13607,10 +13600,26 @@
         <v>458</v>
       </c>
       <c r="B228" s="18">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C228" s="18" t="s">
-        <v>91</v>
+        <v>47</v>
+      </c>
+      <c r="F228" s="18" t="s">
+        <v>464</v>
+      </c>
+      <c r="G228" s="18" t="s">
+        <v>465</v>
+      </c>
+      <c r="H228" s="18" t="s">
+        <v>467</v>
+      </c>
+      <c r="I228" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="L228" s="18" t="str">
+        <f t="shared" ref="L228" si="42">_xlfn.TEXTJOIN("", TRUE, E228:K228)</f>
+        <v>01_Textgattung/05_Historische-Koenigsinschrift/01_xr-Hm-n/0001_xr Hm n_01.png</v>
       </c>
       <c r="N228" s="18" t="s">
         <v>90</v>
@@ -13618,109 +13627,70 @@
     </row>
     <row r="229" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A229" s="18" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B229" s="18">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C229" s="18" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D229" s="18" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="N229" s="18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="230" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A230" s="18" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B230" s="18">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C230" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F230" s="18" t="s">
-        <v>464</v>
-      </c>
-      <c r="G230" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="H230" s="18" t="s">
-        <v>467</v>
-      </c>
-      <c r="I230" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="L230" s="18" t="str">
-        <f t="shared" ref="L230" si="43">_xlfn.TEXTJOIN("", TRUE, E230:K230)</f>
-        <v>01_Textgattung/05_Historische-Koenigsinschrift/01_xr-Hm-n/0001_xr Hm n_01.png</v>
+        <v>46</v>
+      </c>
+      <c r="D230" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="M230" s="18" t="s">
+        <v>325</v>
       </c>
       <c r="N230" s="18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="231" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A231" s="18" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B231" s="18">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C231" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F231" s="18" t="s">
-        <v>464</v>
-      </c>
-      <c r="G231" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="H231" s="18" t="s">
-        <v>473</v>
-      </c>
-      <c r="I231" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="L231" s="18" t="str">
-        <f t="shared" ref="L231:L233" si="44">_xlfn.TEXTJOIN("", TRUE, E231:K231)</f>
-        <v>01_Textgattung/05_Historische-Koenigsinschrift/01_xr-Hm-n/0010_xr Hm n_02.png</v>
+        <v>45</v>
+      </c>
+      <c r="D231" s="18" t="s">
+        <v>1587</v>
       </c>
       <c r="N231" s="18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="232" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A232" s="18" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B232" s="18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C232" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F232" s="18" t="s">
-        <v>464</v>
-      </c>
-      <c r="G232" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="H232" s="18" t="s">
-        <v>474</v>
-      </c>
-      <c r="I232" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="L232" s="18" t="str">
-        <f t="shared" si="44"/>
-        <v>01_Textgattung/05_Historische-Koenigsinschrift/01_xr-Hm-n/0020_Hm n_01.png</v>
+        <v>91</v>
       </c>
       <c r="N232" s="18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="233" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
@@ -13728,26 +13698,13 @@
         <v>459</v>
       </c>
       <c r="B233" s="18">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C233" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F233" s="18" t="s">
-        <v>464</v>
-      </c>
-      <c r="G233" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="H233" s="18" t="s">
-        <v>475</v>
-      </c>
-      <c r="I233" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="L233" s="18" t="str">
-        <f t="shared" si="44"/>
-        <v>01_Textgattung/05_Historische-Koenigsinschrift/01_xr-Hm-n/0030_Hm n_02.png</v>
+        <v>17</v>
+      </c>
+      <c r="D233" s="18" t="s">
+        <v>471</v>
       </c>
       <c r="N233" s="18" t="s">
         <v>92</v>
@@ -13758,16 +13715,29 @@
         <v>459</v>
       </c>
       <c r="B234" s="18">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C234" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D234" s="18" t="s">
-        <v>470</v>
+        <v>47</v>
+      </c>
+      <c r="F234" s="18" t="s">
+        <v>464</v>
+      </c>
+      <c r="G234" s="18" t="s">
+        <v>465</v>
+      </c>
+      <c r="H234" s="18" t="s">
+        <v>467</v>
+      </c>
+      <c r="I234" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="L234" s="18" t="str">
+        <f t="shared" ref="L234" si="43">_xlfn.TEXTJOIN("", TRUE, E234:K234)</f>
+        <v>01_Textgattung/05_Historische-Koenigsinschrift/01_xr-Hm-n/0001_xr Hm n_01.png</v>
       </c>
       <c r="N234" s="18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="235" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
@@ -13775,26 +13745,29 @@
         <v>459</v>
       </c>
       <c r="B235" s="18">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C235" s="18" t="s">
         <v>47</v>
       </c>
       <c r="F235" s="18" t="s">
-        <v>468</v>
+        <v>464</v>
+      </c>
+      <c r="G235" s="18" t="s">
+        <v>465</v>
       </c>
       <c r="H235" s="18" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="I235" s="18" t="s">
         <v>112</v>
       </c>
       <c r="L235" s="18" t="str">
-        <f t="shared" ref="L235" si="45">_xlfn.TEXTJOIN("", TRUE, E235:K235)</f>
-        <v>02_Slots/Koenig/04_Thronname_01.png</v>
+        <f t="shared" ref="L235:L237" si="44">_xlfn.TEXTJOIN("", TRUE, E235:K235)</f>
+        <v>01_Textgattung/05_Historische-Koenigsinschrift/01_xr-Hm-n/0010_xr Hm n_02.png</v>
       </c>
       <c r="N235" s="18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="236" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
@@ -13802,26 +13775,29 @@
         <v>459</v>
       </c>
       <c r="B236" s="18">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C236" s="18" t="s">
         <v>47</v>
       </c>
       <c r="F236" s="18" t="s">
-        <v>468</v>
+        <v>464</v>
+      </c>
+      <c r="G236" s="18" t="s">
+        <v>465</v>
       </c>
       <c r="H236" s="18" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I236" s="18" t="s">
         <v>112</v>
       </c>
       <c r="L236" s="18" t="str">
-        <f t="shared" ref="L236" si="46">_xlfn.TEXTJOIN("", TRUE, E236:K236)</f>
-        <v>02_Slots/Koenig/04_Thronname_Gr._02.png</v>
+        <f t="shared" si="44"/>
+        <v>01_Textgattung/05_Historische-Koenigsinschrift/01_xr-Hm-n/0020_Hm n_01.png</v>
       </c>
       <c r="N236" s="18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="237" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
@@ -13829,90 +13805,117 @@
         <v>459</v>
       </c>
       <c r="B237" s="18">
+        <v>11</v>
+      </c>
+      <c r="C237" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F237" s="18" t="s">
+        <v>464</v>
+      </c>
+      <c r="G237" s="18" t="s">
+        <v>465</v>
+      </c>
+      <c r="H237" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="I237" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="L237" s="18" t="str">
+        <f t="shared" si="44"/>
+        <v>01_Textgattung/05_Historische-Koenigsinschrift/01_xr-Hm-n/0030_Hm n_02.png</v>
+      </c>
+      <c r="N237" s="18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A238" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="B238" s="18">
+        <v>12</v>
+      </c>
+      <c r="C238" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D238" s="18" t="s">
+        <v>470</v>
+      </c>
+      <c r="N238" s="18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A239" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="B239" s="18">
+        <v>13</v>
+      </c>
+      <c r="C239" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F239" s="18" t="s">
+        <v>468</v>
+      </c>
+      <c r="H239" s="18" t="s">
+        <v>469</v>
+      </c>
+      <c r="I239" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="L239" s="18" t="str">
+        <f t="shared" ref="L239" si="45">_xlfn.TEXTJOIN("", TRUE, E239:K239)</f>
+        <v>02_Slots/Koenig/04_Thronname_01.png</v>
+      </c>
+      <c r="N239" s="18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A240" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="B240" s="18">
+        <v>14</v>
+      </c>
+      <c r="C240" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F240" s="18" t="s">
+        <v>468</v>
+      </c>
+      <c r="H240" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="I240" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="L240" s="18" t="str">
+        <f t="shared" ref="L240" si="46">_xlfn.TEXTJOIN("", TRUE, E240:K240)</f>
+        <v>02_Slots/Koenig/04_Thronname_Gr._02.png</v>
+      </c>
+      <c r="N240" s="18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A241" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="B241" s="18">
         <v>15</v>
       </c>
-      <c r="C237" s="18" t="s">
+      <c r="C241" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D237" s="18" t="s">
+      <c r="D241" s="18" t="s">
         <v>1131</v>
       </c>
-      <c r="N237" s="18" t="s">
+      <c r="N241" s="18" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="239" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A239" s="21" t="s">
-        <v>536</v>
-      </c>
-      <c r="B239" s="21">
-        <v>1</v>
-      </c>
-      <c r="C239" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D239" s="21" t="s">
-        <v>535</v>
-      </c>
-      <c r="N239" s="21" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="240" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A240" s="21" t="s">
-        <v>536</v>
-      </c>
-      <c r="B240" s="21">
-        <v>2</v>
-      </c>
-      <c r="C240" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D240" s="21" t="s">
-        <v>555</v>
-      </c>
-      <c r="N240" s="21" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="241" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A241" s="21" t="s">
-        <v>536</v>
-      </c>
-      <c r="B241" s="21">
-        <v>3</v>
-      </c>
-      <c r="C241" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="D241" s="21" t="s">
-        <v>537</v>
-      </c>
-      <c r="M241" s="21" t="s">
-        <v>540</v>
-      </c>
-      <c r="N241" s="21" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="242" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="21" t="s">
-        <v>536</v>
-      </c>
-      <c r="B242" s="21">
-        <v>4</v>
-      </c>
-      <c r="C242" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="D242" s="21" t="s">
-        <v>541</v>
-      </c>
-      <c r="M242" s="21" t="s">
-        <v>1376</v>
-      </c>
-      <c r="N242" s="21" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="243" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
@@ -13920,84 +13923,84 @@
         <v>536</v>
       </c>
       <c r="B243" s="21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C243" s="21" t="s">
-        <v>91</v>
+        <v>45</v>
+      </c>
+      <c r="D243" s="21" t="s">
+        <v>535</v>
       </c>
       <c r="N243" s="21" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="244" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A244" s="22" t="s">
-        <v>1351</v>
+      <c r="A244" s="21" t="s">
+        <v>536</v>
       </c>
       <c r="B244" s="21">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C244" s="21" t="s">
         <v>45</v>
       </c>
       <c r="D244" s="21" t="s">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="N244" s="21" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="245" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A245" s="22" t="s">
-        <v>1351</v>
+      <c r="A245" s="21" t="s">
+        <v>536</v>
       </c>
       <c r="B245" s="21">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C245" s="21" t="s">
         <v>46</v>
       </c>
       <c r="D245" s="21" t="s">
-        <v>48</v>
+        <v>537</v>
       </c>
       <c r="M245" s="21" t="s">
-        <v>97</v>
+        <v>540</v>
       </c>
       <c r="N245" s="21" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="246" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A246" s="22" t="s">
-        <v>1351</v>
+      <c r="A246" s="21" t="s">
+        <v>536</v>
       </c>
       <c r="B246" s="21">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C246" s="21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D246" s="21" t="s">
-        <v>326</v>
+        <v>541</v>
+      </c>
+      <c r="M246" s="21" t="s">
+        <v>1376</v>
       </c>
       <c r="N246" s="21" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="247" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A247" s="22" t="s">
-        <v>1351</v>
+      <c r="A247" s="21" t="s">
+        <v>536</v>
       </c>
       <c r="B247" s="21">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C247" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="D247" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="M247" s="21" t="s">
-        <v>325</v>
+        <v>91</v>
       </c>
       <c r="N247" s="21" t="s">
         <v>90</v>
@@ -14008,13 +14011,13 @@
         <v>1351</v>
       </c>
       <c r="B248" s="21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C248" s="21" t="s">
         <v>45</v>
       </c>
       <c r="D248" s="21" t="s">
-        <v>326</v>
+        <v>542</v>
       </c>
       <c r="N248" s="21" t="s">
         <v>90</v>
@@ -14025,16 +14028,16 @@
         <v>1351</v>
       </c>
       <c r="B249" s="21">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C249" s="21" t="s">
         <v>46</v>
       </c>
       <c r="D249" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M249" s="21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="N249" s="21" t="s">
         <v>90</v>
@@ -14045,7 +14048,7 @@
         <v>1351</v>
       </c>
       <c r="B250" s="21">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C250" s="21" t="s">
         <v>45</v>
@@ -14062,109 +14065,89 @@
         <v>1351</v>
       </c>
       <c r="B251" s="21">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C251" s="21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D251" s="21" t="s">
-        <v>543</v>
+        <v>324</v>
+      </c>
+      <c r="M251" s="21" t="s">
+        <v>325</v>
       </c>
       <c r="N251" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="253" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A253" s="5" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B253">
-        <v>1</v>
-      </c>
-      <c r="C253" t="s">
-        <v>47</v>
-      </c>
-      <c r="F253" t="s">
-        <v>1364</v>
-      </c>
-      <c r="G253" t="s">
-        <v>1365</v>
-      </c>
-      <c r="H253" t="s">
-        <v>1077</v>
-      </c>
-      <c r="I253" t="s">
-        <v>112</v>
-      </c>
-      <c r="L253" t="str">
-        <f t="shared" ref="L253" si="47">_xlfn.TEXTJOIN("", TRUE, E253:K253)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0001_Dd-mdw_01.png</v>
-      </c>
-      <c r="N253" t="s">
+    <row r="252" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A252" s="22" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B252" s="21">
+        <v>10</v>
+      </c>
+      <c r="C252" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D252" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="N252" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="254" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A254" s="5" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B254">
-        <v>2</v>
-      </c>
-      <c r="C254" t="s">
+    <row r="253" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A253" s="22" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B253" s="21">
+        <v>11</v>
+      </c>
+      <c r="C253" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D253" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="M253" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="N253" s="21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A254" s="22" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B254" s="21">
+        <v>12</v>
+      </c>
+      <c r="C254" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D254" t="s">
-        <v>1078</v>
-      </c>
-      <c r="N254" t="s">
+      <c r="D254" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="N254" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="255" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A255" s="5" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B255">
-        <v>3</v>
-      </c>
-      <c r="C255" t="s">
-        <v>47</v>
-      </c>
-      <c r="F255" t="s">
-        <v>1364</v>
-      </c>
-      <c r="G255" t="s">
-        <v>1415</v>
-      </c>
-      <c r="H255" t="s">
-        <v>371</v>
-      </c>
-      <c r="I255" t="s">
-        <v>112</v>
-      </c>
-      <c r="L255" t="str">
-        <f t="shared" ref="L255" si="48">_xlfn.TEXTJOIN("", TRUE, E255:K255)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/02_jn/0001_jn_01.png</v>
-      </c>
-      <c r="N255" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="256" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A256" s="5" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B256">
-        <v>4</v>
-      </c>
-      <c r="C256" t="s">
+    <row r="255" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A255" s="22" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B255" s="21">
+        <v>13</v>
+      </c>
+      <c r="C255" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D256" t="s">
-        <v>369</v>
-      </c>
-      <c r="N256" t="s">
+      <c r="D255" s="21" t="s">
+        <v>543</v>
+      </c>
+      <c r="N255" s="21" t="s">
         <v>90</v>
       </c>
     </row>
@@ -14173,16 +14156,26 @@
         <v>1076</v>
       </c>
       <c r="B257">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C257" t="s">
-        <v>46</v>
-      </c>
-      <c r="D257" t="s">
-        <v>48</v>
-      </c>
-      <c r="M257" t="s">
-        <v>97</v>
+        <v>47</v>
+      </c>
+      <c r="F257" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G257" t="s">
+        <v>1365</v>
+      </c>
+      <c r="H257" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I257" t="s">
+        <v>112</v>
+      </c>
+      <c r="L257" t="str">
+        <f t="shared" ref="L257" si="47">_xlfn.TEXTJOIN("", TRUE, E257:K257)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0001_Dd-mdw_01.png</v>
       </c>
       <c r="N257" t="s">
         <v>90</v>
@@ -14193,13 +14186,13 @@
         <v>1076</v>
       </c>
       <c r="B258">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C258" t="s">
         <v>45</v>
       </c>
       <c r="D258" t="s">
-        <v>326</v>
+        <v>1078</v>
       </c>
       <c r="N258" t="s">
         <v>90</v>
@@ -14210,16 +14203,26 @@
         <v>1076</v>
       </c>
       <c r="B259">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C259" t="s">
-        <v>46</v>
-      </c>
-      <c r="D259" t="s">
-        <v>324</v>
-      </c>
-      <c r="M259" t="s">
-        <v>325</v>
+        <v>47</v>
+      </c>
+      <c r="F259" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G259" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H259" t="s">
+        <v>371</v>
+      </c>
+      <c r="I259" t="s">
+        <v>112</v>
+      </c>
+      <c r="L259" t="str">
+        <f t="shared" ref="L259" si="48">_xlfn.TEXTJOIN("", TRUE, E259:K259)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/02_jn/0001_jn_01.png</v>
       </c>
       <c r="N259" t="s">
         <v>90</v>
@@ -14230,13 +14233,13 @@
         <v>1076</v>
       </c>
       <c r="B260">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C260" t="s">
         <v>45</v>
       </c>
       <c r="D260" t="s">
-        <v>326</v>
+        <v>369</v>
       </c>
       <c r="N260" t="s">
         <v>90</v>
@@ -14247,16 +14250,16 @@
         <v>1076</v>
       </c>
       <c r="B261">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C261" t="s">
         <v>46</v>
       </c>
       <c r="D261" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M261" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="N261" t="s">
         <v>90</v>
@@ -14267,23 +14270,13 @@
         <v>1076</v>
       </c>
       <c r="B262">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C262" t="s">
-        <v>47</v>
-      </c>
-      <c r="F262" t="s">
-        <v>1083</v>
-      </c>
-      <c r="H262" t="s">
-        <v>1084</v>
-      </c>
-      <c r="I262" t="s">
-        <v>112</v>
-      </c>
-      <c r="L262" t="str">
-        <f t="shared" ref="L262" si="49">_xlfn.TEXTJOIN("", TRUE, E262:K262)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0001_dj.n(=j)-n=k_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D262" t="s">
+        <v>326</v>
       </c>
       <c r="N262" t="s">
         <v>90</v>
@@ -14294,13 +14287,16 @@
         <v>1076</v>
       </c>
       <c r="B263">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C263" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D263" t="s">
-        <v>1082</v>
+        <v>324</v>
+      </c>
+      <c r="M263" t="s">
+        <v>325</v>
       </c>
       <c r="N263" t="s">
         <v>90</v>
@@ -14311,16 +14307,13 @@
         <v>1076</v>
       </c>
       <c r="B264">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C264" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D264" t="s">
-        <v>49</v>
-      </c>
-      <c r="M264" t="s">
-        <v>98</v>
+        <v>326</v>
       </c>
       <c r="N264" t="s">
         <v>90</v>
@@ -14331,23 +14324,16 @@
         <v>1076</v>
       </c>
       <c r="B265">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C265" t="s">
-        <v>47</v>
-      </c>
-      <c r="F265" t="s">
-        <v>1079</v>
-      </c>
-      <c r="H265" t="s">
-        <v>1080</v>
-      </c>
-      <c r="I265" t="s">
-        <v>112</v>
-      </c>
-      <c r="L265" t="str">
-        <f t="shared" ref="L265" si="50">_xlfn.TEXTJOIN("", TRUE, E265:K265)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/03_xrj/04_xrj_01.png</v>
+        <v>46</v>
+      </c>
+      <c r="D265" t="s">
+        <v>50</v>
+      </c>
+      <c r="M265" t="s">
+        <v>99</v>
       </c>
       <c r="N265" t="s">
         <v>90</v>
@@ -14358,13 +14344,23 @@
         <v>1076</v>
       </c>
       <c r="B266">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C266" t="s">
-        <v>45</v>
-      </c>
-      <c r="D266" t="s">
-        <v>1121</v>
+        <v>47</v>
+      </c>
+      <c r="F266" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H266" t="s">
+        <v>1084</v>
+      </c>
+      <c r="I266" t="s">
+        <v>112</v>
+      </c>
+      <c r="L266" t="str">
+        <f t="shared" ref="L266" si="49">_xlfn.TEXTJOIN("", TRUE, E266:K266)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0001_dj.n(=j)-n=k_01.png</v>
       </c>
       <c r="N266" t="s">
         <v>90</v>
@@ -14372,100 +14368,83 @@
     </row>
     <row r="267" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A267" s="5" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="B267">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C267" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D267" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="N267" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="268" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A268" s="5" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="B268">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C268" t="s">
-        <v>47</v>
-      </c>
-      <c r="F268" t="s">
-        <v>1364</v>
-      </c>
-      <c r="G268" t="s">
-        <v>1365</v>
-      </c>
-      <c r="H268" t="s">
-        <v>1085</v>
-      </c>
-      <c r="L268" t="str">
-        <f t="shared" ref="L268:L270" si="51">_xlfn.TEXTJOIN("", TRUE, E268:K268)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0001_Dd-mdw_01.png</v>
+        <v>46</v>
+      </c>
+      <c r="D268" t="s">
+        <v>49</v>
+      </c>
+      <c r="M268" t="s">
+        <v>98</v>
       </c>
       <c r="N268" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="269" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A269" s="5" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="B269">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C269" t="s">
         <v>47</v>
       </c>
       <c r="F269" t="s">
-        <v>1364</v>
-      </c>
-      <c r="G269" t="s">
-        <v>1365</v>
+        <v>1079</v>
       </c>
       <c r="H269" t="s">
-        <v>1086</v>
+        <v>1080</v>
+      </c>
+      <c r="I269" t="s">
+        <v>112</v>
       </c>
       <c r="L269" t="str">
-        <f t="shared" si="51"/>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0010_Dd-mdw_02.png</v>
+        <f t="shared" ref="L269" si="50">_xlfn.TEXTJOIN("", TRUE, E269:K269)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/03_xrj/04_xrj_01.png</v>
       </c>
       <c r="N269" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="270" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A270" s="5" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="B270">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C270" t="s">
-        <v>47</v>
-      </c>
-      <c r="F270" t="s">
-        <v>1364</v>
-      </c>
-      <c r="G270" t="s">
-        <v>1365</v>
-      </c>
-      <c r="H270" t="s">
-        <v>1087</v>
-      </c>
-      <c r="L270" t="str">
-        <f t="shared" si="51"/>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0020_Dd-mdw_NR_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D270" t="s">
+        <v>1121</v>
       </c>
       <c r="N270" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="271" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -14473,13 +14452,13 @@
         <v>1081</v>
       </c>
       <c r="B271">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C271" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D271" t="s">
-        <v>1129</v>
+        <v>1078</v>
       </c>
       <c r="N271" t="s">
         <v>92</v>
@@ -14490,16 +14469,26 @@
         <v>1081</v>
       </c>
       <c r="B272">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C272" t="s">
-        <v>17</v>
-      </c>
-      <c r="D272" t="s">
-        <v>369</v>
+        <v>47</v>
+      </c>
+      <c r="F272" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G272" t="s">
+        <v>1365</v>
+      </c>
+      <c r="H272" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L272" t="str">
+        <f t="shared" ref="L272:L274" si="51">_xlfn.TEXTJOIN("", TRUE, E272:K272)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0001_Dd-mdw_01.png</v>
       </c>
       <c r="N272" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="273" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -14507,7 +14496,7 @@
         <v>1081</v>
       </c>
       <c r="B273">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C273" t="s">
         <v>47</v>
@@ -14516,20 +14505,17 @@
         <v>1364</v>
       </c>
       <c r="G273" t="s">
-        <v>1415</v>
+        <v>1365</v>
       </c>
       <c r="H273" t="s">
-        <v>371</v>
-      </c>
-      <c r="I273" t="s">
-        <v>112</v>
+        <v>1086</v>
       </c>
       <c r="L273" t="str">
-        <f t="shared" ref="L273" si="52">_xlfn.TEXTJOIN("", TRUE, E273:K273)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/02_jn/0001_jn_01.png</v>
+        <f t="shared" si="51"/>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0010_Dd-mdw_02.png</v>
       </c>
       <c r="N273" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="274" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -14537,7 +14523,7 @@
         <v>1081</v>
       </c>
       <c r="B274">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C274" t="s">
         <v>47</v>
@@ -14546,20 +14532,17 @@
         <v>1364</v>
       </c>
       <c r="G274" t="s">
-        <v>1415</v>
+        <v>1365</v>
       </c>
       <c r="H274" t="s">
-        <v>1416</v>
-      </c>
-      <c r="I274" t="s">
-        <v>112</v>
+        <v>1087</v>
       </c>
       <c r="L274" t="str">
-        <f t="shared" ref="L274" si="53">_xlfn.TEXTJOIN("", TRUE, E274:K274)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/02_jn/0010_jn_02.png</v>
+        <f t="shared" si="51"/>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/01_Dd-mdw/0020_Dd-mdw_NR_01.png</v>
       </c>
       <c r="N274" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="275" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -14567,7 +14550,7 @@
         <v>1081</v>
       </c>
       <c r="B275">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C275" t="s">
         <v>45</v>
@@ -14576,7 +14559,7 @@
         <v>1129</v>
       </c>
       <c r="N275" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="276" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -14584,16 +14567,16 @@
         <v>1081</v>
       </c>
       <c r="B276">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C276" t="s">
         <v>17</v>
       </c>
       <c r="D276" t="s">
-        <v>1082</v>
+        <v>369</v>
       </c>
       <c r="N276" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="277" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -14601,26 +14584,29 @@
         <v>1081</v>
       </c>
       <c r="B277">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C277" t="s">
         <v>47</v>
       </c>
       <c r="F277" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="G277" t="s">
-        <v>1363</v>
+        <v>1415</v>
       </c>
       <c r="H277" t="s">
-        <v>1089</v>
+        <v>371</v>
+      </c>
+      <c r="I277" t="s">
+        <v>112</v>
       </c>
       <c r="L277" t="str">
-        <f t="shared" ref="L277:L281" si="54">_xlfn.TEXTJOIN("", TRUE, E277:K277)</f>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0001_dj.n(=j)-n=k_01.png</v>
+        <f t="shared" ref="L277" si="52">_xlfn.TEXTJOIN("", TRUE, E277:K277)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/02_jn/0001_jn_01.png</v>
       </c>
       <c r="N277" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="278" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -14628,26 +14614,29 @@
         <v>1081</v>
       </c>
       <c r="B278">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C278" t="s">
         <v>47</v>
       </c>
       <c r="F278" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="G278" t="s">
-        <v>1363</v>
+        <v>1415</v>
       </c>
       <c r="H278" t="s">
-        <v>1090</v>
+        <v>1416</v>
+      </c>
+      <c r="I278" t="s">
+        <v>112</v>
       </c>
       <c r="L278" t="str">
-        <f t="shared" si="54"/>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0010_dj.n(=j)-n=k_02.png</v>
+        <f t="shared" ref="L278" si="53">_xlfn.TEXTJOIN("", TRUE, E278:K278)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/01_Dd-mdw-jn/02_jn/0010_jn_02.png</v>
       </c>
       <c r="N278" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="279" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -14655,26 +14644,16 @@
         <v>1081</v>
       </c>
       <c r="B279">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C279" t="s">
-        <v>47</v>
-      </c>
-      <c r="F279" t="s">
-        <v>1362</v>
-      </c>
-      <c r="G279" t="s">
-        <v>1363</v>
-      </c>
-      <c r="H279" t="s">
-        <v>1091</v>
-      </c>
-      <c r="L279" t="str">
-        <f t="shared" si="54"/>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0020_dj.n(=j)-n=k_03.png</v>
+        <v>45</v>
+      </c>
+      <c r="D279" t="s">
+        <v>1129</v>
       </c>
       <c r="N279" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="280" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -14682,23 +14661,13 @@
         <v>1081</v>
       </c>
       <c r="B280">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C280" t="s">
-        <v>47</v>
-      </c>
-      <c r="F280" t="s">
-        <v>1362</v>
-      </c>
-      <c r="G280" t="s">
-        <v>1363</v>
-      </c>
-      <c r="H280" t="s">
-        <v>1092</v>
-      </c>
-      <c r="L280" t="str">
-        <f t="shared" si="54"/>
-        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0030_dj.n(=j)-n=k_04.png</v>
+        <v>17</v>
+      </c>
+      <c r="D280" t="s">
+        <v>1082</v>
       </c>
       <c r="N280" t="s">
         <v>95</v>
@@ -14709,7 +14678,7 @@
         <v>1081</v>
       </c>
       <c r="B281">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C281" t="s">
         <v>47</v>
@@ -14721,119 +14690,133 @@
         <v>1363</v>
       </c>
       <c r="H281" t="s">
+        <v>1089</v>
+      </c>
+      <c r="L281" t="str">
+        <f t="shared" ref="L281:L285" si="54">_xlfn.TEXTJOIN("", TRUE, E281:K281)</f>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0001_dj.n(=j)-n=k_01.png</v>
+      </c>
+      <c r="N281" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A282" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B282">
+        <v>12</v>
+      </c>
+      <c r="C282" t="s">
+        <v>47</v>
+      </c>
+      <c r="F282" t="s">
+        <v>1362</v>
+      </c>
+      <c r="G282" t="s">
+        <v>1363</v>
+      </c>
+      <c r="H282" t="s">
+        <v>1090</v>
+      </c>
+      <c r="L282" t="str">
+        <f t="shared" si="54"/>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0010_dj.n(=j)-n=k_02.png</v>
+      </c>
+      <c r="N282" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A283" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B283">
+        <v>13</v>
+      </c>
+      <c r="C283" t="s">
+        <v>47</v>
+      </c>
+      <c r="F283" t="s">
+        <v>1362</v>
+      </c>
+      <c r="G283" t="s">
+        <v>1363</v>
+      </c>
+      <c r="H283" t="s">
+        <v>1091</v>
+      </c>
+      <c r="L283" t="str">
+        <f t="shared" si="54"/>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0020_dj.n(=j)-n=k_03.png</v>
+      </c>
+      <c r="N283" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A284" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B284">
+        <v>14</v>
+      </c>
+      <c r="C284" t="s">
+        <v>47</v>
+      </c>
+      <c r="F284" t="s">
+        <v>1362</v>
+      </c>
+      <c r="G284" t="s">
+        <v>1363</v>
+      </c>
+      <c r="H284" t="s">
+        <v>1092</v>
+      </c>
+      <c r="L284" t="str">
+        <f t="shared" si="54"/>
+        <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0030_dj.n(=j)-n=k_04.png</v>
+      </c>
+      <c r="N284" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A285" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B285">
+        <v>15</v>
+      </c>
+      <c r="C285" t="s">
+        <v>47</v>
+      </c>
+      <c r="F285" t="s">
+        <v>1362</v>
+      </c>
+      <c r="G285" t="s">
+        <v>1363</v>
+      </c>
+      <c r="H285" t="s">
         <v>1093</v>
       </c>
-      <c r="L281" t="str">
+      <c r="L285" t="str">
         <f t="shared" si="54"/>
         <v>01_Textgattung/07_Beischriften/03_Woertliche-Rede/02_dj.n(=j)-n=k/0040_dj.n(=j)-n=T_01.png</v>
       </c>
-      <c r="N281" t="s">
+      <c r="N285" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A282" s="5"/>
-    </row>
-    <row r="283" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A283" s="5" t="s">
-        <v>1356</v>
-      </c>
-      <c r="B283">
-        <v>1</v>
-      </c>
-      <c r="C283" t="s">
-        <v>47</v>
-      </c>
-      <c r="F283" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G283" t="s">
-        <v>1361</v>
-      </c>
-      <c r="H283" t="s">
-        <v>1366</v>
-      </c>
-      <c r="I283" t="s">
-        <v>112</v>
-      </c>
-      <c r="L283" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, E283:K283)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0010_sA_seit-MR_02.png</v>
-      </c>
-      <c r="N283" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="284" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A284" s="5" t="s">
-        <v>1356</v>
-      </c>
-      <c r="B284">
-        <v>2</v>
-      </c>
-      <c r="C284" t="s">
-        <v>45</v>
-      </c>
-      <c r="D284" t="s">
-        <v>1214</v>
-      </c>
-      <c r="N284" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="285" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A285" s="5" t="s">
-        <v>1356</v>
-      </c>
-      <c r="B285">
-        <v>3</v>
-      </c>
-      <c r="C285" t="s">
-        <v>47</v>
-      </c>
-      <c r="F285" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G285" t="s">
-        <v>1368</v>
-      </c>
-      <c r="H285" t="s">
-        <v>1371</v>
-      </c>
-      <c r="I285" t="s">
-        <v>112</v>
-      </c>
-      <c r="L285" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, E285:K285)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/02_anx/0001_anx_01.png</v>
-      </c>
-      <c r="N285" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="286" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A286" s="5" t="s">
-        <v>1356</v>
-      </c>
-      <c r="B286">
-        <v>4</v>
-      </c>
-      <c r="C286" t="s">
-        <v>45</v>
-      </c>
-      <c r="D286" t="s">
-        <v>637</v>
-      </c>
-      <c r="N286" t="s">
-        <v>90</v>
-      </c>
+    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A286" s="5"/>
     </row>
     <row r="287" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A287" s="5" t="s">
         <v>1356</v>
       </c>
       <c r="B287">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C287" t="s">
         <v>47</v>
@@ -14842,17 +14825,17 @@
         <v>1360</v>
       </c>
       <c r="G287" t="s">
-        <v>1369</v>
+        <v>1361</v>
       </c>
       <c r="H287" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="I287" t="s">
         <v>112</v>
       </c>
       <c r="L287" t="str">
         <f>_xlfn.TEXTJOIN("", TRUE, E287:K287)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0010_HA_02.png</v>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0010_sA_seit-MR_02.png</v>
       </c>
       <c r="N287" t="s">
         <v>90</v>
@@ -14863,26 +14846,13 @@
         <v>1356</v>
       </c>
       <c r="B288">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C288" t="s">
-        <v>47</v>
-      </c>
-      <c r="F288" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G288" t="s">
-        <v>1370</v>
-      </c>
-      <c r="H288" t="s">
-        <v>1372</v>
-      </c>
-      <c r="I288" t="s">
-        <v>112</v>
-      </c>
-      <c r="L288" t="str">
-        <f>_xlfn.TEXTJOIN("", TRUE, E288:K288)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/04_=f-nb/0001_=f-nb_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D288" t="s">
+        <v>1214</v>
       </c>
       <c r="N288" t="s">
         <v>90</v>
@@ -14893,124 +14863,143 @@
         <v>1356</v>
       </c>
       <c r="B289">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C289" t="s">
-        <v>45</v>
-      </c>
-      <c r="D289" t="s">
-        <v>1367</v>
+        <v>47</v>
+      </c>
+      <c r="F289" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G289" t="s">
+        <v>1368</v>
+      </c>
+      <c r="H289" t="s">
+        <v>1371</v>
+      </c>
+      <c r="I289" t="s">
+        <v>112</v>
+      </c>
+      <c r="L289" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, E289:K289)</f>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/02_anx/0001_anx_01.png</v>
       </c>
       <c r="N289" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A290" s="5"/>
-    </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A291" s="5"/>
+    <row r="290" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A290" s="5" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B290">
+        <v>4</v>
+      </c>
+      <c r="C290" t="s">
+        <v>45</v>
+      </c>
+      <c r="D290" t="s">
+        <v>637</v>
+      </c>
+      <c r="N290" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A291" s="5" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B291">
+        <v>5</v>
+      </c>
+      <c r="C291" t="s">
+        <v>47</v>
+      </c>
+      <c r="F291" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G291" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H291" t="s">
+        <v>1373</v>
+      </c>
+      <c r="I291" t="s">
+        <v>112</v>
+      </c>
+      <c r="L291" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, E291:K291)</f>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0010_HA_02.png</v>
+      </c>
+      <c r="N291" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="292" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A292" s="2" t="s">
-        <v>1405</v>
+      <c r="A292" s="5" t="s">
+        <v>1356</v>
       </c>
       <c r="B292">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C292" t="s">
-        <v>17</v>
-      </c>
-      <c r="D292" t="s">
-        <v>1407</v>
+        <v>47</v>
+      </c>
+      <c r="F292" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G292" t="s">
+        <v>1370</v>
+      </c>
+      <c r="H292" t="s">
+        <v>1372</v>
+      </c>
+      <c r="I292" t="s">
+        <v>112</v>
+      </c>
+      <c r="L292" t="str">
+        <f>_xlfn.TEXTJOIN("", TRUE, E292:K292)</f>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/04_=f-nb/0001_=f-nb_01.png</v>
+      </c>
+      <c r="N292" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="293" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A293" s="2" t="s">
-        <v>1405</v>
+      <c r="A293" s="5" t="s">
+        <v>1356</v>
       </c>
       <c r="B293">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C293" t="s">
-        <v>47</v>
-      </c>
-      <c r="F293" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G293" t="s">
-        <v>1396</v>
-      </c>
-      <c r="H293" t="s">
-        <v>1397</v>
-      </c>
-      <c r="L293" t="str">
-        <f t="shared" ref="L293:L308" si="55">_xlfn.TEXTJOIN("", TRUE, E293:K293)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0001_sA-anx-HA=f-nb_MR_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D293" t="s">
+        <v>1367</v>
       </c>
       <c r="N293" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="294" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A294" s="2" t="s">
-        <v>1405</v>
-      </c>
-      <c r="B294">
-        <v>3</v>
-      </c>
-      <c r="C294" t="s">
-        <v>45</v>
-      </c>
-      <c r="D294" t="s">
-        <v>1393</v>
-      </c>
-      <c r="N294" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="295" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A295" s="2" t="s">
-        <v>1405</v>
-      </c>
-      <c r="B295">
-        <v>4</v>
-      </c>
-      <c r="C295" t="s">
-        <v>47</v>
-      </c>
-      <c r="F295" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G295" t="s">
-        <v>1396</v>
-      </c>
-      <c r="H295" t="s">
-        <v>1398</v>
-      </c>
-      <c r="L295" t="str">
-        <f t="shared" si="55"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0010_sA-anx-HA=f-nb-NR_01.png</v>
-      </c>
-      <c r="N295" t="s">
-        <v>92</v>
-      </c>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A294" s="5"/>
+    </row>
+    <row r="295" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A295" s="5"/>
     </row>
     <row r="296" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A296" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="B296">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C296" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D296" t="s">
-        <v>1129</v>
-      </c>
-      <c r="N296" t="s">
-        <v>92</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="297" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15018,16 +15007,26 @@
         <v>1405</v>
       </c>
       <c r="B297">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C297" t="s">
-        <v>17</v>
-      </c>
-      <c r="D297" t="s">
-        <v>1408</v>
+        <v>47</v>
+      </c>
+      <c r="F297" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G297" t="s">
+        <v>1396</v>
+      </c>
+      <c r="H297" t="s">
+        <v>1397</v>
+      </c>
+      <c r="L297" t="str">
+        <f t="shared" ref="L297:L312" si="55">_xlfn.TEXTJOIN("", TRUE, E297:K297)</f>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0001_sA-anx-HA=f-nb_MR_01.png</v>
       </c>
       <c r="N297" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="298" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15035,26 +15034,16 @@
         <v>1405</v>
       </c>
       <c r="B298">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C298" t="s">
-        <v>47</v>
-      </c>
-      <c r="F298" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G298" t="s">
-        <v>1396</v>
-      </c>
-      <c r="H298" t="s">
-        <v>1399</v>
-      </c>
-      <c r="L298" t="str">
-        <f t="shared" si="55"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0020_sA-anx-HA=f_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D298" t="s">
+        <v>1393</v>
       </c>
       <c r="N298" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="299" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15062,7 +15051,7 @@
         <v>1405</v>
       </c>
       <c r="B299">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C299" t="s">
         <v>47</v>
@@ -15074,14 +15063,14 @@
         <v>1396</v>
       </c>
       <c r="H299" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="L299" t="str">
         <f t="shared" si="55"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0030_sA-anx-HA=f_02.png</v>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0010_sA-anx-HA=f-nb-NR_01.png</v>
       </c>
       <c r="N299" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="300" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15089,16 +15078,16 @@
         <v>1405</v>
       </c>
       <c r="B300">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C300" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D300" t="s">
-        <v>1409</v>
+        <v>1129</v>
       </c>
       <c r="N300" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="301" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15106,26 +15095,16 @@
         <v>1405</v>
       </c>
       <c r="B301">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C301" t="s">
-        <v>47</v>
-      </c>
-      <c r="F301" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G301" t="s">
-        <v>1396</v>
-      </c>
-      <c r="H301" t="s">
-        <v>1401</v>
-      </c>
-      <c r="L301" t="str">
-        <f t="shared" si="55"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0040_sA-anx-wAs-HA=f_01.png</v>
+        <v>17</v>
+      </c>
+      <c r="D301" t="s">
+        <v>1408</v>
       </c>
       <c r="N301" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="302" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15133,7 +15112,7 @@
         <v>1405</v>
       </c>
       <c r="B302">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C302" t="s">
         <v>47</v>
@@ -15145,14 +15124,14 @@
         <v>1396</v>
       </c>
       <c r="H302" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="L302" t="str">
         <f t="shared" si="55"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0050_sA-anx-wAs-HA=f_NR-selten-Gr-oft_01.png</v>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0020_sA-anx-HA=f_01.png</v>
       </c>
       <c r="N302" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="303" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15160,16 +15139,26 @@
         <v>1405</v>
       </c>
       <c r="B303">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C303" t="s">
-        <v>45</v>
-      </c>
-      <c r="D303" t="s">
-        <v>1412</v>
+        <v>47</v>
+      </c>
+      <c r="F303" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G303" t="s">
+        <v>1396</v>
+      </c>
+      <c r="H303" t="s">
+        <v>1400</v>
+      </c>
+      <c r="L303" t="str">
+        <f t="shared" si="55"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0030_sA-anx-HA=f_02.png</v>
       </c>
       <c r="N303" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="304" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15177,16 +15166,16 @@
         <v>1405</v>
       </c>
       <c r="B304">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C304" t="s">
         <v>17</v>
       </c>
       <c r="D304" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="N304" t="s">
-        <v>1395</v>
+        <v>95</v>
       </c>
     </row>
     <row r="305" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15194,7 +15183,7 @@
         <v>1405</v>
       </c>
       <c r="B305">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C305" t="s">
         <v>47</v>
@@ -15206,14 +15195,14 @@
         <v>1396</v>
       </c>
       <c r="H305" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="L305" t="str">
         <f t="shared" si="55"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0060_sA-anx-Dd-wAs-HA=f_D.18_01.png</v>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0040_sA-anx-wAs-HA=f_01.png</v>
       </c>
       <c r="N305" t="s">
-        <v>1395</v>
+        <v>95</v>
       </c>
     </row>
     <row r="306" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15221,16 +15210,26 @@
         <v>1405</v>
       </c>
       <c r="B306">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C306" t="s">
-        <v>45</v>
-      </c>
-      <c r="D306" t="s">
-        <v>1413</v>
+        <v>47</v>
+      </c>
+      <c r="F306" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G306" t="s">
+        <v>1396</v>
+      </c>
+      <c r="H306" t="s">
+        <v>1402</v>
+      </c>
+      <c r="L306" t="str">
+        <f t="shared" si="55"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0050_sA-anx-wAs-HA=f_NR-selten-Gr-oft_01.png</v>
       </c>
       <c r="N306" t="s">
-        <v>1395</v>
+        <v>95</v>
       </c>
     </row>
     <row r="307" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15238,16 +15237,16 @@
         <v>1405</v>
       </c>
       <c r="B307">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C307" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D307" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="N307" t="s">
-        <v>1414</v>
+        <v>95</v>
       </c>
     </row>
     <row r="308" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15255,26 +15254,16 @@
         <v>1405</v>
       </c>
       <c r="B308">
+        <v>13</v>
+      </c>
+      <c r="C308" t="s">
         <v>17</v>
       </c>
-      <c r="C308" t="s">
-        <v>47</v>
-      </c>
-      <c r="F308" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G308" t="s">
-        <v>1396</v>
-      </c>
-      <c r="H308" t="s">
-        <v>1404</v>
-      </c>
-      <c r="L308" t="str">
-        <f t="shared" si="55"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0070_sA-anx-Dd-wAs-snb-HA=f_D.18_01.png</v>
+      <c r="D308" t="s">
+        <v>1410</v>
       </c>
       <c r="N308" t="s">
-        <v>1414</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="309" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15282,140 +15271,130 @@
         <v>1405</v>
       </c>
       <c r="B309">
+        <v>14</v>
+      </c>
+      <c r="C309" t="s">
+        <v>47</v>
+      </c>
+      <c r="F309" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G309" t="s">
+        <v>1396</v>
+      </c>
+      <c r="H309" t="s">
+        <v>1403</v>
+      </c>
+      <c r="L309" t="str">
+        <f t="shared" si="55"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0060_sA-anx-Dd-wAs-HA=f_D.18_01.png</v>
+      </c>
+      <c r="N309" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="310" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A310" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B310">
+        <v>15</v>
+      </c>
+      <c r="C310" t="s">
+        <v>45</v>
+      </c>
+      <c r="D310" t="s">
+        <v>1413</v>
+      </c>
+      <c r="N310" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="311" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A311" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B311">
+        <v>16</v>
+      </c>
+      <c r="C311" t="s">
+        <v>17</v>
+      </c>
+      <c r="D311" t="s">
+        <v>1411</v>
+      </c>
+      <c r="N311" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="312" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A312" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B312">
+        <v>17</v>
+      </c>
+      <c r="C312" t="s">
+        <v>47</v>
+      </c>
+      <c r="F312" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G312" t="s">
+        <v>1396</v>
+      </c>
+      <c r="H312" t="s">
+        <v>1404</v>
+      </c>
+      <c r="L312" t="str">
+        <f t="shared" si="55"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/formel-gesamt/0070_sA-anx-Dd-wAs-snb-HA=f_D.18_01.png</v>
+      </c>
+      <c r="N312" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="313" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A313" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B313">
         <v>18</v>
       </c>
-      <c r="C309" t="s">
+      <c r="C313" t="s">
         <v>45</v>
       </c>
-      <c r="D309" t="s">
+      <c r="D313" t="s">
         <v>1413</v>
       </c>
-      <c r="N309" t="s">
+      <c r="N313" t="s">
         <v>1414</v>
       </c>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A310" s="5"/>
-    </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A311" s="5"/>
-    </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A312" s="5"/>
-    </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A313" s="5"/>
-    </row>
-    <row r="314" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A314" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="B314">
-        <v>1</v>
-      </c>
-      <c r="C314" t="s">
-        <v>17</v>
-      </c>
-      <c r="D314" t="s">
-        <v>1214</v>
-      </c>
-      <c r="N314" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="315" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A315" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="B315">
-        <v>2</v>
-      </c>
-      <c r="C315" t="s">
-        <v>47</v>
-      </c>
-      <c r="F315" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G315" t="s">
-        <v>1361</v>
-      </c>
-      <c r="H315" t="s">
-        <v>1379</v>
-      </c>
-      <c r="L315" t="str">
-        <f t="shared" ref="L315:L326" si="56">_xlfn.TEXTJOIN("", TRUE, E315:K315)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0001_sA_01.png</v>
-      </c>
-      <c r="N315" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="316" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A316" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="B316">
-        <v>3</v>
-      </c>
-      <c r="C316" t="s">
-        <v>47</v>
-      </c>
-      <c r="F316" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G316" t="s">
-        <v>1361</v>
-      </c>
-      <c r="H316" t="s">
-        <v>1380</v>
-      </c>
-      <c r="L316" t="str">
-        <f t="shared" si="56"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0010_sA_seit-MR_02.png</v>
-      </c>
-      <c r="N316" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="317" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A317" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="B317">
-        <v>4</v>
-      </c>
-      <c r="C317" t="s">
-        <v>45</v>
-      </c>
-      <c r="D317" t="s">
-        <v>1128</v>
-      </c>
-      <c r="N317" t="s">
-        <v>93</v>
-      </c>
+    <row r="314" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A314" s="5"/>
+    </row>
+    <row r="315" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A315" s="5"/>
+    </row>
+    <row r="316" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A316" s="5"/>
+    </row>
+    <row r="317" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A317" s="5"/>
     </row>
     <row r="318" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A318" s="2" t="s">
         <v>1378</v>
       </c>
       <c r="B318">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C318" t="s">
-        <v>47</v>
-      </c>
-      <c r="F318" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G318" t="s">
-        <v>1361</v>
-      </c>
-      <c r="H318" t="s">
-        <v>1381</v>
-      </c>
-      <c r="L318" t="str">
-        <f t="shared" si="56"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0020_sA_MR_01.png</v>
+        <v>17</v>
+      </c>
+      <c r="D318" t="s">
+        <v>1214</v>
       </c>
       <c r="N318" t="s">
         <v>93</v>
@@ -15426,13 +15405,23 @@
         <v>1378</v>
       </c>
       <c r="B319">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C319" t="s">
-        <v>45</v>
-      </c>
-      <c r="D319" t="s">
-        <v>1393</v>
+        <v>47</v>
+      </c>
+      <c r="F319" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G319" t="s">
+        <v>1361</v>
+      </c>
+      <c r="H319" t="s">
+        <v>1379</v>
+      </c>
+      <c r="L319" t="str">
+        <f t="shared" ref="L319:L330" si="56">_xlfn.TEXTJOIN("", TRUE, E319:K319)</f>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0001_sA_01.png</v>
       </c>
       <c r="N319" t="s">
         <v>93</v>
@@ -15443,7 +15432,7 @@
         <v>1378</v>
       </c>
       <c r="B320">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C320" t="s">
         <v>47</v>
@@ -15455,11 +15444,11 @@
         <v>1361</v>
       </c>
       <c r="H320" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="L320" t="str">
         <f t="shared" si="56"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0030_sA_NR_01.png</v>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0010_sA_seit-MR_02.png</v>
       </c>
       <c r="N320" t="s">
         <v>93</v>
@@ -15470,13 +15459,13 @@
         <v>1378</v>
       </c>
       <c r="B321">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C321" t="s">
         <v>45</v>
       </c>
       <c r="D321" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="N321" t="s">
         <v>93</v>
@@ -15487,7 +15476,7 @@
         <v>1378</v>
       </c>
       <c r="B322">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C322" t="s">
         <v>47</v>
@@ -15499,11 +15488,11 @@
         <v>1361</v>
       </c>
       <c r="H322" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="L322" t="str">
         <f t="shared" si="56"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0040_sA_NR_02.png</v>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0020_sA_MR_01.png</v>
       </c>
       <c r="N322" t="s">
         <v>93</v>
@@ -15514,13 +15503,13 @@
         <v>1378</v>
       </c>
       <c r="B323">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C323" t="s">
         <v>45</v>
       </c>
       <c r="D323" t="s">
-        <v>1129</v>
+        <v>1393</v>
       </c>
       <c r="N323" t="s">
         <v>93</v>
@@ -15531,7 +15520,7 @@
         <v>1378</v>
       </c>
       <c r="B324">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C324" t="s">
         <v>47</v>
@@ -15543,11 +15532,11 @@
         <v>1361</v>
       </c>
       <c r="H324" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="L324" t="str">
         <f t="shared" si="56"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0050_sA_GR_01.png</v>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0030_sA_NR_01.png</v>
       </c>
       <c r="N324" t="s">
         <v>93</v>
@@ -15558,13 +15547,13 @@
         <v>1378</v>
       </c>
       <c r="B325">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C325" t="s">
         <v>45</v>
       </c>
       <c r="D325" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="N325" t="s">
         <v>93</v>
@@ -15575,7 +15564,7 @@
         <v>1378</v>
       </c>
       <c r="B326">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C326" t="s">
         <v>47</v>
@@ -15587,11 +15576,11 @@
         <v>1361</v>
       </c>
       <c r="H326" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="L326" t="str">
         <f t="shared" si="56"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0060_sA_GR_02.png</v>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0040_sA_NR_02.png</v>
       </c>
       <c r="N326" t="s">
         <v>93</v>
@@ -15602,13 +15591,13 @@
         <v>1378</v>
       </c>
       <c r="B327">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C327" t="s">
         <v>45</v>
       </c>
       <c r="D327" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="N327" t="s">
         <v>93</v>
@@ -15619,16 +15608,26 @@
         <v>1378</v>
       </c>
       <c r="B328">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C328" t="s">
-        <v>17</v>
-      </c>
-      <c r="D328" t="s">
-        <v>637</v>
+        <v>47</v>
+      </c>
+      <c r="F328" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G328" t="s">
+        <v>1361</v>
+      </c>
+      <c r="H328" t="s">
+        <v>1384</v>
+      </c>
+      <c r="L328" t="str">
+        <f t="shared" si="56"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0050_sA_GR_01.png</v>
       </c>
       <c r="N328" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="329" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15636,29 +15635,16 @@
         <v>1378</v>
       </c>
       <c r="B329">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C329" t="s">
-        <v>47</v>
-      </c>
-      <c r="F329" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G329" t="s">
-        <v>1368</v>
-      </c>
-      <c r="H329" t="s">
-        <v>1371</v>
-      </c>
-      <c r="I329" t="s">
-        <v>112</v>
-      </c>
-      <c r="L329" t="str">
-        <f t="shared" ref="L329" si="57">_xlfn.TEXTJOIN("", TRUE, E329:K329)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/02_anx/0001_anx_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D329" t="s">
+        <v>1131</v>
       </c>
       <c r="N329" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="330" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15666,16 +15652,26 @@
         <v>1378</v>
       </c>
       <c r="B330">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C330" t="s">
-        <v>17</v>
-      </c>
-      <c r="D330" t="s">
-        <v>1386</v>
+        <v>47</v>
+      </c>
+      <c r="F330" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G330" t="s">
+        <v>1361</v>
+      </c>
+      <c r="H330" t="s">
+        <v>1385</v>
+      </c>
+      <c r="L330" t="str">
+        <f t="shared" si="56"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/01_sA/0060_sA_GR_02.png</v>
       </c>
       <c r="N330" t="s">
-        <v>1395</v>
+        <v>93</v>
       </c>
     </row>
     <row r="331" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15683,26 +15679,16 @@
         <v>1378</v>
       </c>
       <c r="B331">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C331" t="s">
-        <v>47</v>
-      </c>
-      <c r="F331" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G331" t="s">
-        <v>1369</v>
-      </c>
-      <c r="H331" t="s">
-        <v>1387</v>
-      </c>
-      <c r="L331" t="str">
-        <f t="shared" ref="L331:L339" si="58">_xlfn.TEXTJOIN("", TRUE, E331:K331)</f>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0001_HA_01.png</v>
+        <v>45</v>
+      </c>
+      <c r="D331" t="s">
+        <v>1131</v>
       </c>
       <c r="N331" t="s">
-        <v>1395</v>
+        <v>93</v>
       </c>
     </row>
     <row r="332" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15710,26 +15696,16 @@
         <v>1378</v>
       </c>
       <c r="B332">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C332" t="s">
-        <v>47</v>
-      </c>
-      <c r="F332" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G332" t="s">
-        <v>1369</v>
-      </c>
-      <c r="H332" t="s">
-        <v>1388</v>
-      </c>
-      <c r="L332" t="str">
-        <f t="shared" si="58"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0010_HA_02.png</v>
+        <v>17</v>
+      </c>
+      <c r="D332" t="s">
+        <v>637</v>
       </c>
       <c r="N332" t="s">
-        <v>1395</v>
+        <v>95</v>
       </c>
     </row>
     <row r="333" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15737,7 +15713,7 @@
         <v>1378</v>
       </c>
       <c r="B333">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C333" t="s">
         <v>47</v>
@@ -15746,17 +15722,20 @@
         <v>1360</v>
       </c>
       <c r="G333" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H333" t="s">
-        <v>1389</v>
+        <v>1371</v>
+      </c>
+      <c r="I333" t="s">
+        <v>112</v>
       </c>
       <c r="L333" t="str">
-        <f t="shared" si="58"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0020_HA_MR_01.png</v>
+        <f t="shared" ref="L333" si="57">_xlfn.TEXTJOIN("", TRUE, E333:K333)</f>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/02_anx/0001_anx_01.png</v>
       </c>
       <c r="N333" t="s">
-        <v>1395</v>
+        <v>95</v>
       </c>
     </row>
     <row r="334" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -15764,13 +15743,13 @@
         <v>1378</v>
       </c>
       <c r="B334">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C334" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D334" t="s">
-        <v>1393</v>
+        <v>1386</v>
       </c>
       <c r="N334" t="s">
         <v>1395</v>
@@ -15781,7 +15760,7 @@
         <v>1378</v>
       </c>
       <c r="B335">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C335" t="s">
         <v>47</v>
@@ -15793,11 +15772,11 @@
         <v>1369</v>
       </c>
       <c r="H335" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="L335" t="str">
-        <f t="shared" si="58"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0030_HA_MR_02.png</v>
+        <f t="shared" ref="L335:L343" si="58">_xlfn.TEXTJOIN("", TRUE, E335:K335)</f>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0001_HA_01.png</v>
       </c>
       <c r="N335" t="s">
         <v>1395</v>
@@ -15808,13 +15787,23 @@
         <v>1378</v>
       </c>
       <c r="B336">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C336" t="s">
-        <v>45</v>
-      </c>
-      <c r="D336" t="s">
-        <v>1393</v>
+        <v>47</v>
+      </c>
+      <c r="F336" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G336" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H336" t="s">
+        <v>1388</v>
+      </c>
+      <c r="L336" t="str">
+        <f t="shared" si="58"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0010_HA_02.png</v>
       </c>
       <c r="N336" t="s">
         <v>1395</v>
@@ -15825,7 +15814,7 @@
         <v>1378</v>
       </c>
       <c r="B337">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C337" t="s">
         <v>47</v>
@@ -15837,11 +15826,11 @@
         <v>1369</v>
       </c>
       <c r="H337" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="L337" t="str">
         <f t="shared" si="58"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0040_HA_NR_01.png</v>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0020_HA_MR_01.png</v>
       </c>
       <c r="N337" t="s">
         <v>1395</v>
@@ -15852,13 +15841,13 @@
         <v>1378</v>
       </c>
       <c r="B338">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C338" t="s">
         <v>45</v>
       </c>
       <c r="D338" t="s">
-        <v>1129</v>
+        <v>1393</v>
       </c>
       <c r="N338" t="s">
         <v>1395</v>
@@ -15869,7 +15858,7 @@
         <v>1378</v>
       </c>
       <c r="B339">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C339" t="s">
         <v>47</v>
@@ -15881,11 +15870,11 @@
         <v>1369</v>
       </c>
       <c r="H339" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="L339" t="str">
         <f t="shared" si="58"/>
-        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0050_HA_Sp_01.png</v>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0030_HA_MR_02.png</v>
       </c>
       <c r="N339" t="s">
         <v>1395</v>
@@ -15896,26 +15885,102 @@
         <v>1378</v>
       </c>
       <c r="B340">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C340" t="s">
         <v>45</v>
       </c>
       <c r="D340" t="s">
+        <v>1393</v>
+      </c>
+      <c r="N340" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="341" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A341" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B341">
+        <v>24</v>
+      </c>
+      <c r="C341" t="s">
+        <v>47</v>
+      </c>
+      <c r="F341" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G341" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H341" t="s">
+        <v>1391</v>
+      </c>
+      <c r="L341" t="str">
+        <f t="shared" si="58"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0040_HA_NR_01.png</v>
+      </c>
+      <c r="N341" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="342" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A342" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B342">
+        <v>25</v>
+      </c>
+      <c r="C342" t="s">
+        <v>45</v>
+      </c>
+      <c r="D342" t="s">
+        <v>1129</v>
+      </c>
+      <c r="N342" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="343" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A343" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B343">
+        <v>26</v>
+      </c>
+      <c r="C343" t="s">
+        <v>47</v>
+      </c>
+      <c r="F343" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G343" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H343" t="s">
+        <v>1392</v>
+      </c>
+      <c r="L343" t="str">
+        <f t="shared" si="58"/>
+        <v>01_Textgattung/07_Beischriften/04_Rueckenschutzformel/03_HA/0050_HA_Sp_01.png</v>
+      </c>
+      <c r="N343" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="344" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A344" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B344">
+        <v>27</v>
+      </c>
+      <c r="C344" t="s">
+        <v>45</v>
+      </c>
+      <c r="D344" t="s">
         <v>1394</v>
       </c>
-    </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A341" s="5"/>
-    </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A342" s="5"/>
-    </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A343" s="5"/>
-    </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A344" s="5"/>
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A345" s="5"/>
@@ -15941,112 +16006,30 @@
     <row r="352" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A352" s="5"/>
     </row>
+    <row r="353" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A353" s="5"/>
+    </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A354" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B354">
-        <v>1</v>
-      </c>
-      <c r="C354" t="s">
-        <v>45</v>
-      </c>
-      <c r="D354" t="s">
-        <v>1042</v>
-      </c>
-      <c r="N354" t="s">
-        <v>90</v>
-      </c>
+      <c r="A354" s="5"/>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A355" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B355" s="27">
-        <v>2</v>
-      </c>
-      <c r="C355" t="s">
-        <v>45</v>
-      </c>
-      <c r="D355" t="s">
-        <v>1048</v>
-      </c>
-      <c r="N355" t="s">
-        <v>90</v>
-      </c>
+      <c r="A355" s="5"/>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A356" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B356">
-        <v>3</v>
-      </c>
-      <c r="C356" t="s">
-        <v>47</v>
-      </c>
-      <c r="F356" t="s">
-        <v>417</v>
-      </c>
-      <c r="G356" t="s">
-        <v>418</v>
-      </c>
-      <c r="H356" t="s">
-        <v>419</v>
-      </c>
-      <c r="I356" t="s">
-        <v>112</v>
-      </c>
-      <c r="L356" t="str">
-        <f t="shared" ref="L356:L357" si="59">_xlfn.TEXTJOIN("", TRUE, E356:K356)</f>
-        <v>02_Slots/Personennamen/Namen/f/01_tA-dj-Gottheit/01_tA-dj_01.png</v>
-      </c>
-      <c r="N356" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A357" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B357" s="27">
-        <v>4</v>
-      </c>
-      <c r="C357" t="s">
-        <v>47</v>
-      </c>
-      <c r="F357" t="s">
-        <v>417</v>
-      </c>
-      <c r="G357" t="s">
-        <v>418</v>
-      </c>
-      <c r="H357" t="s">
-        <v>420</v>
-      </c>
-      <c r="I357" t="s">
-        <v>112</v>
-      </c>
-      <c r="L357" t="str">
-        <f t="shared" si="59"/>
-        <v>02_Slots/Personennamen/Namen/f/01_tA-dj-Gottheit/01_tA-dj_02.png</v>
-      </c>
-      <c r="N357" t="s">
-        <v>90</v>
-      </c>
+      <c r="A356" s="5"/>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>1037</v>
       </c>
       <c r="B358">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C358" t="s">
         <v>45</v>
       </c>
       <c r="D358" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="N358" t="s">
         <v>90</v>
@@ -16057,36 +16040,73 @@
         <v>1037</v>
       </c>
       <c r="B359" s="27">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C359" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D359" t="s">
-        <v>48</v>
-      </c>
-      <c r="M359" t="s">
-        <v>97</v>
+        <v>1048</v>
       </c>
       <c r="N359" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B360" s="27"/>
+      <c r="A360" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B360">
+        <v>3</v>
+      </c>
+      <c r="C360" t="s">
+        <v>47</v>
+      </c>
+      <c r="F360" t="s">
+        <v>417</v>
+      </c>
+      <c r="G360" t="s">
+        <v>418</v>
+      </c>
+      <c r="H360" t="s">
+        <v>419</v>
+      </c>
+      <c r="I360" t="s">
+        <v>112</v>
+      </c>
+      <c r="L360" t="str">
+        <f t="shared" ref="L360:L361" si="59">_xlfn.TEXTJOIN("", TRUE, E360:K360)</f>
+        <v>02_Slots/Personennamen/Namen/f/01_tA-dj-Gottheit/01_tA-dj_01.png</v>
+      </c>
+      <c r="N360" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B361">
-        <v>1</v>
+        <v>1037</v>
+      </c>
+      <c r="B361" s="27">
+        <v>4</v>
       </c>
       <c r="C361" t="s">
-        <v>45</v>
-      </c>
-      <c r="D361" t="s">
-        <v>1042</v>
+        <v>47</v>
+      </c>
+      <c r="F361" t="s">
+        <v>417</v>
+      </c>
+      <c r="G361" t="s">
+        <v>418</v>
+      </c>
+      <c r="H361" t="s">
+        <v>420</v>
+      </c>
+      <c r="I361" t="s">
+        <v>112</v>
+      </c>
+      <c r="L361" t="str">
+        <f t="shared" si="59"/>
+        <v>02_Slots/Personennamen/Namen/f/01_tA-dj-Gottheit/01_tA-dj_02.png</v>
       </c>
       <c r="N361" t="s">
         <v>90</v>
@@ -16094,16 +16114,16 @@
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B362" s="27">
-        <v>2</v>
+        <v>1037</v>
+      </c>
+      <c r="B362">
+        <v>5</v>
       </c>
       <c r="C362" t="s">
         <v>45</v>
       </c>
       <c r="D362" t="s">
-        <v>1049</v>
+        <v>1039</v>
       </c>
       <c r="N362" t="s">
         <v>90</v>
@@ -16111,76 +16131,39 @@
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B363">
-        <v>3</v>
+        <v>1037</v>
+      </c>
+      <c r="B363" s="27">
+        <v>6</v>
       </c>
       <c r="C363" t="s">
-        <v>47</v>
-      </c>
-      <c r="F363" t="s">
-        <v>422</v>
-      </c>
-      <c r="G363" t="s">
-        <v>443</v>
-      </c>
-      <c r="H363" t="s">
-        <v>423</v>
-      </c>
-      <c r="I363" t="s">
-        <v>112</v>
-      </c>
-      <c r="L363" t="str">
-        <f t="shared" ref="L363:L364" si="60">_xlfn.TEXTJOIN("", TRUE, E363:K363)</f>
-        <v>02_Slots/Personennamen/Namen/m/01_pA-dj-Gottheit/01_pA-dj_01.png</v>
+        <v>46</v>
+      </c>
+      <c r="D363" t="s">
+        <v>48</v>
+      </c>
+      <c r="M363" t="s">
+        <v>97</v>
       </c>
       <c r="N363" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A364" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B364" s="27">
-        <v>4</v>
-      </c>
-      <c r="C364" t="s">
-        <v>47</v>
-      </c>
-      <c r="F364" t="s">
-        <v>422</v>
-      </c>
-      <c r="G364" t="s">
-        <v>443</v>
-      </c>
-      <c r="H364" t="s">
-        <v>424</v>
-      </c>
-      <c r="I364" t="s">
-        <v>112</v>
-      </c>
-      <c r="L364" t="str">
-        <f t="shared" si="60"/>
-        <v>02_Slots/Personennamen/Namen/m/01_pA-dj-Gottheit/01_pA-dj_02.png</v>
-      </c>
-      <c r="N364" t="s">
-        <v>90</v>
-      </c>
+      <c r="B364" s="27"/>
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>1038</v>
       </c>
       <c r="B365">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C365" t="s">
         <v>45</v>
       </c>
       <c r="D365" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="N365" t="s">
         <v>90</v>
@@ -16191,89 +16174,112 @@
         <v>1038</v>
       </c>
       <c r="B366" s="27">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C366" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D366" t="s">
-        <v>48</v>
-      </c>
-      <c r="M366" t="s">
-        <v>97</v>
+        <v>1049</v>
       </c>
       <c r="N366" t="s">
         <v>90</v>
       </c>
     </row>
+    <row r="367" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A367" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B367">
+        <v>3</v>
+      </c>
+      <c r="C367" t="s">
+        <v>47</v>
+      </c>
+      <c r="F367" t="s">
+        <v>422</v>
+      </c>
+      <c r="G367" t="s">
+        <v>443</v>
+      </c>
+      <c r="H367" t="s">
+        <v>423</v>
+      </c>
+      <c r="I367" t="s">
+        <v>112</v>
+      </c>
+      <c r="L367" t="str">
+        <f t="shared" ref="L367:L368" si="60">_xlfn.TEXTJOIN("", TRUE, E367:K367)</f>
+        <v>02_Slots/Personennamen/Namen/m/01_pA-dj-Gottheit/01_pA-dj_01.png</v>
+      </c>
+      <c r="N367" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="368" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A368" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B368" s="27">
+        <v>4</v>
+      </c>
+      <c r="C368" t="s">
+        <v>47</v>
+      </c>
+      <c r="F368" t="s">
+        <v>422</v>
+      </c>
+      <c r="G368" t="s">
+        <v>443</v>
+      </c>
+      <c r="H368" t="s">
+        <v>424</v>
+      </c>
+      <c r="I368" t="s">
+        <v>112</v>
+      </c>
+      <c r="L368" t="str">
+        <f t="shared" si="60"/>
+        <v>02_Slots/Personennamen/Namen/m/01_pA-dj-Gottheit/01_pA-dj_02.png</v>
+      </c>
+      <c r="N368" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="369" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A369" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B369">
+        <v>5</v>
+      </c>
+      <c r="C369" t="s">
+        <v>45</v>
+      </c>
+      <c r="D369" t="s">
+        <v>1039</v>
+      </c>
+      <c r="N369" t="s">
+        <v>90</v>
+      </c>
+    </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>1208</v>
-      </c>
-      <c r="B370">
-        <v>1</v>
+        <v>1038</v>
+      </c>
+      <c r="B370" s="27">
+        <v>6</v>
       </c>
       <c r="C370" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D370" t="s">
-        <v>1042</v>
+        <v>48</v>
+      </c>
+      <c r="M370" t="s">
+        <v>97</v>
       </c>
       <c r="N370" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A371" t="s">
-        <v>1208</v>
-      </c>
-      <c r="B371">
-        <v>2</v>
-      </c>
-      <c r="C371" t="s">
-        <v>46</v>
-      </c>
-      <c r="D371" t="s">
-        <v>50</v>
-      </c>
-      <c r="M371" t="s">
-        <v>99</v>
-      </c>
-      <c r="N371" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A372" t="s">
-        <v>1208</v>
-      </c>
-      <c r="B372">
-        <v>3</v>
-      </c>
-      <c r="C372" t="s">
-        <v>45</v>
-      </c>
-      <c r="D372" t="s">
-        <v>1211</v>
-      </c>
-      <c r="N372" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A373" t="s">
-        <v>1208</v>
-      </c>
-      <c r="B373">
-        <v>4</v>
-      </c>
-      <c r="C373" t="s">
-        <v>45</v>
-      </c>
-      <c r="D373" t="s">
-        <v>1212</v>
-      </c>
-      <c r="N373" t="s">
         <v>90</v>
       </c>
     </row>
@@ -16282,16 +16288,13 @@
         <v>1208</v>
       </c>
       <c r="B374">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C374" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D374" t="s">
-        <v>50</v>
-      </c>
-      <c r="M374" t="s">
-        <v>99</v>
+        <v>1042</v>
       </c>
       <c r="N374" t="s">
         <v>90</v>
@@ -16302,30 +16305,50 @@
         <v>1208</v>
       </c>
       <c r="B375">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C375" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D375" t="s">
-        <v>1213</v>
+        <v>50</v>
+      </c>
+      <c r="M375" t="s">
+        <v>99</v>
       </c>
       <c r="N375" t="s">
         <v>90</v>
       </c>
     </row>
+    <row r="376" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A376" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B376">
+        <v>3</v>
+      </c>
+      <c r="C376" t="s">
+        <v>45</v>
+      </c>
+      <c r="D376" t="s">
+        <v>1211</v>
+      </c>
+      <c r="N376" t="s">
+        <v>90</v>
+      </c>
+    </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B377">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C377" t="s">
         <v>45</v>
       </c>
       <c r="D377" t="s">
-        <v>1042</v>
+        <v>1212</v>
       </c>
       <c r="N377" t="s">
         <v>90</v>
@@ -16333,10 +16356,10 @@
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B378">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C378" t="s">
         <v>46</v>
@@ -16353,35 +16376,18 @@
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B379">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C379" t="s">
         <v>45</v>
       </c>
       <c r="D379" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="N379" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A380" t="s">
-        <v>1209</v>
-      </c>
-      <c r="B380">
-        <v>4</v>
-      </c>
-      <c r="C380" t="s">
-        <v>45</v>
-      </c>
-      <c r="D380" t="s">
-        <v>1214</v>
-      </c>
-      <c r="N380" t="s">
         <v>90</v>
       </c>
     </row>
@@ -16390,16 +16396,13 @@
         <v>1209</v>
       </c>
       <c r="B381">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C381" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D381" t="s">
-        <v>50</v>
-      </c>
-      <c r="M381" t="s">
-        <v>99</v>
+        <v>1042</v>
       </c>
       <c r="N381" t="s">
         <v>90</v>
@@ -16410,41 +16413,61 @@
         <v>1209</v>
       </c>
       <c r="B382">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C382" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D382" t="s">
-        <v>1213</v>
+        <v>50</v>
+      </c>
+      <c r="M382" t="s">
+        <v>99</v>
       </c>
       <c r="N382" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="384" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A384" s="5" t="s">
-        <v>1210</v>
+    <row r="383" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A383" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B383">
+        <v>3</v>
+      </c>
+      <c r="C383" t="s">
+        <v>45</v>
+      </c>
+      <c r="D383" t="s">
+        <v>1211</v>
+      </c>
+      <c r="N383" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="384" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A384" t="s">
+        <v>1209</v>
       </c>
       <c r="B384">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C384" t="s">
         <v>45</v>
       </c>
       <c r="D384" t="s">
-        <v>1042</v>
+        <v>1214</v>
       </c>
       <c r="N384" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="385" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A385" s="5" t="s">
-        <v>1210</v>
+    <row r="385" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A385" t="s">
+        <v>1209</v>
       </c>
       <c r="B385">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C385" t="s">
         <v>46</v>
@@ -16459,12 +16482,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="386" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A386" s="5" t="s">
-        <v>1210</v>
+    <row r="386" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A386" t="s">
+        <v>1209</v>
       </c>
       <c r="B386">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C386" t="s">
         <v>45</v>
@@ -16473,23 +16496,6 @@
         <v>1213</v>
       </c>
       <c r="N386" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="387" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="A387" s="5" t="s">
-        <v>1210</v>
-      </c>
-      <c r="B387">
-        <v>4</v>
-      </c>
-      <c r="C387" t="s">
-        <v>45</v>
-      </c>
-      <c r="D387" t="s">
-        <v>1214</v>
-      </c>
-      <c r="N387" t="s">
         <v>90</v>
       </c>
     </row>
@@ -16498,16 +16504,13 @@
         <v>1210</v>
       </c>
       <c r="B388">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C388" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D388" t="s">
-        <v>50</v>
-      </c>
-      <c r="M388" t="s">
-        <v>99</v>
+        <v>1042</v>
       </c>
       <c r="N388" t="s">
         <v>90</v>
@@ -16518,15 +16521,89 @@
         <v>1210</v>
       </c>
       <c r="B389">
+        <v>2</v>
+      </c>
+      <c r="C389" t="s">
+        <v>46</v>
+      </c>
+      <c r="D389" t="s">
+        <v>50</v>
+      </c>
+      <c r="M389" t="s">
+        <v>99</v>
+      </c>
+      <c r="N389" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="390" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A390" s="5" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B390">
+        <v>3</v>
+      </c>
+      <c r="C390" t="s">
+        <v>45</v>
+      </c>
+      <c r="D390" t="s">
+        <v>1213</v>
+      </c>
+      <c r="N390" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="391" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A391" s="5" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B391">
+        <v>4</v>
+      </c>
+      <c r="C391" t="s">
+        <v>45</v>
+      </c>
+      <c r="D391" t="s">
+        <v>1214</v>
+      </c>
+      <c r="N391" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="392" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A392" s="5" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B392">
+        <v>5</v>
+      </c>
+      <c r="C392" t="s">
+        <v>46</v>
+      </c>
+      <c r="D392" t="s">
+        <v>50</v>
+      </c>
+      <c r="M392" t="s">
+        <v>99</v>
+      </c>
+      <c r="N392" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="393" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A393" s="5" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B393">
         <v>6</v>
       </c>
-      <c r="C389" t="s">
+      <c r="C393" t="s">
         <v>45</v>
       </c>
-      <c r="D389" t="s">
+      <c r="D393" t="s">
         <v>1211</v>
       </c>
-      <c r="N389" t="s">
+      <c r="N393" t="s">
         <v>90</v>
       </c>
     </row>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F1CB81C-762A-C34D-B819-5AB222486A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E7655D-00EF-2A4F-98F2-3C4F9749DDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28920" windowHeight="19840" activeTab="4" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28920" windowHeight="19720" activeTab="2" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
   <sheets>
     <sheet name="pages" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7320" uniqueCount="1590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7358" uniqueCount="1599">
   <si>
     <t>page_id</t>
   </si>
@@ -4835,6 +4835,33 @@
   </si>
   <si>
     <t>&lt;span style="vertical-align:-75%"&gt;&amp;nbsp;&lt;/span&gt;&lt;br/&gt;</t>
+  </si>
+  <si>
+    <t>gl_saitenformel</t>
+  </si>
+  <si>
+    <t>- erstmals in der 18. Dynastie belegt</t>
+  </si>
+  <si>
+    <t>gl_saitenformel_var</t>
+  </si>
+  <si>
+    <t>- Jansen-Winkeln, Karl 2000. Zum Verständnis der "Saitischen Formel". Studien zur Altägyptischen Kultur 28, 83-124.</t>
+  </si>
+  <si>
+    <t>- Meulenaere, H. J. A. de 1997-2000. Sculptures mendésiennes de Basse Époque. Jaarbericht van het Vooraziatisch-Egyptisch Genootschap Ex Oriente Lux 35-36, 33-39: F. 81</t>
+  </si>
+  <si>
+    <t>- NR: Klotz, David 2016. Get thee behind me, City God! New Kingdom versions of the so-called "Saite Formula". Zeitschrift für ägyptische Sprache und Altertumskunde 143 (2), 204-213. DOI: 10.1515/zaes-2016-0014.</t>
+  </si>
+  <si>
+    <t>gl_anruf-lebenden</t>
+  </si>
+  <si>
+    <t>- *swꜣi⸗sn*: seit der 3. Zwischenzeit auch ohne *ti* geschrieben</t>
+  </si>
+  <si>
+    <t>- Shubert, Steven Blake 2007. Those who (still) live on earth: a study of the ancient Egyptian Appeal to the Living texts. Toronto; Ottawa: University of Toronto; Library and Archives Canada.</t>
   </si>
 </sst>
 </file>
@@ -4897,7 +4924,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4952,6 +4979,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -4966,7 +4999,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -5054,6 +5087,25 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -5556,20 +5608,20 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="10" spans="1:6" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="44" t="s">
         <v>1075</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="44">
         <v>80</v>
       </c>
     </row>
@@ -5750,7 +5802,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{244ECE21-4B85-B642-91D8-6A98EB98549E}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -5857,6 +5909,34 @@
         <v>6</v>
       </c>
     </row>
+    <row r="8" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="31">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="44">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5864,7 +5944,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{056542A6-A652-DC44-866D-D4A0E101DC42}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" style="4" bestFit="1" customWidth="1"/>
@@ -6488,6 +6568,150 @@
       </c>
       <c r="F42" s="22">
         <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" s="41" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" s="42"/>
+      <c r="E44" s="41" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F44" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" s="41" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A45" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="B45" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" s="43" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F45" s="41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" s="41" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="D46" s="42"/>
+      <c r="E46" s="41" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F46" s="41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" s="41" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+      <c r="A47" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="43" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F47" s="41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" s="41" customFormat="1" ht="119" x14ac:dyDescent="0.2">
+      <c r="A48" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="D48" s="43" t="s">
+        <v>1594</v>
+      </c>
+      <c r="F48" s="41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" s="41" customFormat="1" ht="136" x14ac:dyDescent="0.2">
+      <c r="A49" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" s="43" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F49" s="41">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" s="45" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" s="46"/>
+      <c r="E51" s="45" t="s">
+        <v>1596</v>
+      </c>
+      <c r="F51" s="45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" s="45" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A52" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="B52" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="D52" s="47" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F52" s="45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" s="45" customFormat="1" ht="119" x14ac:dyDescent="0.2">
+      <c r="A53" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="D53" s="47" t="s">
+        <v>1598</v>
+      </c>
+      <c r="F53" s="45">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E7655D-00EF-2A4F-98F2-3C4F9749DDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025196C3-13CD-724D-903E-E4AAF262479C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28920" windowHeight="19720" activeTab="2" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667AE678-28CB-7041-A7C1-DBC4555ED58D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB50F9D0-EA03-B64F-B377-58447F99F590}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20220" windowHeight="16120" activeTab="2" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Markus/Documents/Arbeit/Inschriftenschluessel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698C15F0-969D-BA40-9A5F-36B05D42CFAA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F041A75D-8A37-1C4F-9330-B224F2AD60D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4880" yWindow="500" windowWidth="20220" windowHeight="16120" xr2:uid="{F025A444-F8B0-5C41-A37E-BEE791B22240}"/>
   </bookViews>
@@ -4880,7 +4880,7 @@
     <t>- Meulenaere, H. J. A. de 1997–2000. Sculptures mendésiennes de Basse Époque. Jaarbericht van het Vooraziatisch-Egyptisch Genootschap Ex Oriente Lux 35–36, 33–39: F. 81</t>
   </si>
   <si>
-    <t>"&amp;#32;"</t>
+    <t>Inschriftenschlüssel</t>
   </si>
 </sst>
 </file>
